--- a/s60_signal/position-00763-000063.xlsx
+++ b/s60_signal/position-00763-000063.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2586" uniqueCount="344">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2589" uniqueCount="347">
   <si>
     <t>trade_time</t>
   </si>
@@ -478,6 +478,9 @@
     <t>2021-03-19</t>
   </si>
   <si>
+    <t>2021-11-24</t>
+  </si>
+  <si>
     <t>2017-03-17</t>
   </si>
   <si>
@@ -808,6 +811,9 @@
     <t>2021-03-26</t>
   </si>
   <si>
+    <t>2021-11-26</t>
+  </si>
+  <si>
     <t>2017-02-08</t>
   </si>
   <si>
@@ -1046,6 +1052,9 @@
   </si>
   <si>
     <t>2021-01-21</t>
+  </si>
+  <si>
+    <t>2021-11-23</t>
   </si>
 </sst>
 </file>
@@ -1403,7 +1412,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P858"/>
+  <dimension ref="A1:P859"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -1464,7 +1473,7 @@
         <v>8.357775317423281</v>
       </c>
       <c r="D2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E2">
         <v>9.239078272099615</v>
@@ -1500,7 +1509,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -1514,7 +1523,7 @@
         <v>9.433191964550923</v>
       </c>
       <c r="D3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E3">
         <v>9.285575452539577</v>
@@ -1550,7 +1559,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -1564,7 +1573,7 @@
         <v>9.420218808988363</v>
       </c>
       <c r="D4" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E4">
         <v>9.285575452539577</v>
@@ -1600,7 +1609,7 @@
         <v>1</v>
       </c>
       <c r="P4" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -1614,7 +1623,7 @@
         <v>9.27302954676334</v>
       </c>
       <c r="D5" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E5">
         <v>9.285575452539577</v>
@@ -1650,7 +1659,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -1664,7 +1673,7 @@
         <v>8.163141562328137</v>
       </c>
       <c r="D6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E6">
         <v>8.870417830135191</v>
@@ -1700,7 +1709,7 @@
         <v>1</v>
       </c>
       <c r="P6" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -1714,7 +1723,7 @@
         <v>8.167981542028786</v>
       </c>
       <c r="D7" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E7">
         <v>8.870417830135191</v>
@@ -1750,7 +1759,7 @@
         <v>1</v>
       </c>
       <c r="P7" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -1764,7 +1773,7 @@
         <v>9.039124544167011</v>
       </c>
       <c r="D8" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E8">
         <v>9.113918803782131</v>
@@ -1800,7 +1809,7 @@
         <v>1</v>
       </c>
       <c r="P8" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -1814,7 +1823,7 @@
         <v>9.052076876787602</v>
       </c>
       <c r="D9" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E9">
         <v>9.113918803782131</v>
@@ -1850,7 +1859,7 @@
         <v>1</v>
       </c>
       <c r="P9" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -1864,7 +1873,7 @@
         <v>8.972076876787604</v>
       </c>
       <c r="D10" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E10">
         <v>9.113918803782131</v>
@@ -1900,7 +1909,7 @@
         <v>1</v>
       </c>
       <c r="P10" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -1914,7 +1923,7 @@
         <v>1.247895028504875</v>
       </c>
       <c r="D11" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E11">
         <v>5.93332434483856</v>
@@ -1950,7 +1959,7 @@
         <v>1</v>
       </c>
       <c r="P11" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -1964,7 +1973,7 @@
         <v>2.464515501370315</v>
       </c>
       <c r="D12" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E12">
         <v>5.93332434483856</v>
@@ -2000,7 +2009,7 @@
         <v>1</v>
       </c>
       <c r="P12" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -2050,7 +2059,7 @@
         <v>1</v>
       </c>
       <c r="P13" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -2064,7 +2073,7 @@
         <v>1.224092499726471</v>
       </c>
       <c r="D14" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E14">
         <v>5.913320521841428</v>
@@ -2100,7 +2109,7 @@
         <v>1</v>
       </c>
       <c r="P14" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -2114,7 +2123,7 @@
         <v>2.442814384300704</v>
       </c>
       <c r="D15" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E15">
         <v>5.913320521841428</v>
@@ -2150,7 +2159,7 @@
         <v>1</v>
       </c>
       <c r="P15" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -2164,7 +2173,7 @@
         <v>8.399951396166678</v>
       </c>
       <c r="D16" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E16">
         <v>7.154665097353277</v>
@@ -2200,7 +2209,7 @@
         <v>1</v>
       </c>
       <c r="P16" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -2214,7 +2223,7 @@
         <v>1.231818368992485</v>
       </c>
       <c r="D17" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E17">
         <v>5.919813400087062</v>
@@ -2250,7 +2259,7 @@
         <v>1</v>
       </c>
       <c r="P17" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -2264,7 +2273,7 @@
         <v>2.449858173427781</v>
       </c>
       <c r="D18" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E18">
         <v>5.919813400087062</v>
@@ -2300,7 +2309,7 @@
         <v>1</v>
       </c>
       <c r="P18" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -2350,7 +2359,7 @@
         <v>1</v>
       </c>
       <c r="P19" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="20" spans="1:16">
@@ -2364,7 +2373,7 @@
         <v>1.145797529921555</v>
       </c>
       <c r="D20" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E20">
         <v>5.847520844331356</v>
@@ -2400,7 +2409,7 @@
         <v>1</v>
       </c>
       <c r="P20" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -2414,7 +2423,7 @@
         <v>2.37143170385038</v>
       </c>
       <c r="D21" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E21">
         <v>5.847520844331356</v>
@@ -2450,7 +2459,7 @@
         <v>1</v>
       </c>
       <c r="P21" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -2464,7 +2473,7 @@
         <v>8.323251570058975</v>
       </c>
       <c r="D22" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E22">
         <v>6.49770468378167</v>
@@ -2500,7 +2509,7 @@
         <v>1</v>
       </c>
       <c r="P22" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="23" spans="1:16">
@@ -2514,7 +2523,7 @@
         <v>8.298928068060523</v>
       </c>
       <c r="D23" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E23">
         <v>6.513844529583032</v>
@@ -2600,7 +2609,7 @@
         <v>1</v>
       </c>
       <c r="P24" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="25" spans="1:16">
@@ -2650,7 +2659,7 @@
         <v>1</v>
       </c>
       <c r="P25" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="26" spans="1:16">
@@ -2664,7 +2673,7 @@
         <v>4.521898732172186</v>
       </c>
       <c r="D26" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E26">
         <v>7.471272137184702</v>
@@ -2700,7 +2709,7 @@
         <v>1</v>
       </c>
       <c r="P26" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="27" spans="1:16">
@@ -2750,7 +2759,7 @@
         <v>1</v>
       </c>
       <c r="P27" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="28" spans="1:16">
@@ -2800,7 +2809,7 @@
         <v>1</v>
       </c>
       <c r="P28" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -2814,7 +2823,7 @@
         <v>10.06347633639325</v>
       </c>
       <c r="D29" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E29">
         <v>8.926863738767604</v>
@@ -2850,7 +2859,7 @@
         <v>1</v>
       </c>
       <c r="P29" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -3014,7 +3023,7 @@
         <v>10.57243502356749</v>
       </c>
       <c r="D33" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E33">
         <v>11.2289160904059</v>
@@ -3064,7 +3073,7 @@
         <v>10.58025171866791</v>
       </c>
       <c r="D34" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E34">
         <v>11.2289160904059</v>
@@ -3114,7 +3123,7 @@
         <v>6.89098969886382</v>
       </c>
       <c r="D35" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E35">
         <v>9.162922766970905</v>
@@ -3150,7 +3159,7 @@
         <v>1</v>
       </c>
       <c r="P35" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -3200,7 +3209,7 @@
         <v>1</v>
       </c>
       <c r="P36" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="37" spans="1:16">
@@ -3250,7 +3259,7 @@
         <v>1</v>
       </c>
       <c r="P37" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="38" spans="1:16">
@@ -3300,7 +3309,7 @@
         <v>1</v>
       </c>
       <c r="P38" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="39" spans="1:16">
@@ -3314,7 +3323,7 @@
         <v>10.57710841036202</v>
       </c>
       <c r="D39" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E39">
         <v>10.91875227586742</v>
@@ -3350,7 +3359,7 @@
         <v>1</v>
       </c>
       <c r="P39" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="40" spans="1:16">
@@ -3364,7 +3373,7 @@
         <v>10.58544939256899</v>
       </c>
       <c r="D40" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E40">
         <v>10.91875227586742</v>
@@ -3400,7 +3409,7 @@
         <v>1</v>
       </c>
       <c r="P40" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="41" spans="1:16">
@@ -3450,7 +3459,7 @@
         <v>1</v>
       </c>
       <c r="P41" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="42" spans="1:16">
@@ -3500,7 +3509,7 @@
         <v>1</v>
       </c>
       <c r="P42" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="43" spans="1:16">
@@ -3550,7 +3559,7 @@
         <v>1</v>
       </c>
       <c r="P43" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="44" spans="1:16">
@@ -3564,7 +3573,7 @@
         <v>10.50706987192051</v>
       </c>
       <c r="D44" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E44">
         <v>9.836117792760128</v>
@@ -3600,7 +3609,7 @@
         <v>1</v>
       </c>
       <c r="P44" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -3764,7 +3773,7 @@
         <v>11.00643298606593</v>
       </c>
       <c r="D48" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E48">
         <v>10.08970532444388</v>
@@ -3850,7 +3859,7 @@
         <v>1</v>
       </c>
       <c r="P49" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="50" spans="1:16">
@@ -3900,7 +3909,7 @@
         <v>1</v>
       </c>
       <c r="P50" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="51" spans="1:16">
@@ -3950,7 +3959,7 @@
         <v>1</v>
       </c>
       <c r="P51" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="52" spans="1:16">
@@ -4000,7 +4009,7 @@
         <v>1</v>
       </c>
       <c r="P52" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="53" spans="1:16">
@@ -4050,7 +4059,7 @@
         <v>1</v>
       </c>
       <c r="P53" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="54" spans="1:16">
@@ -4100,7 +4109,7 @@
         <v>1</v>
       </c>
       <c r="P54" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="55" spans="1:16">
@@ -4114,7 +4123,7 @@
         <v>10.96451987407661</v>
       </c>
       <c r="D55" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E55">
         <v>9.918825279734797</v>
@@ -4150,7 +4159,7 @@
         <v>1</v>
       </c>
       <c r="P55" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="56" spans="1:16">
@@ -4200,7 +4209,7 @@
         <v>1</v>
       </c>
       <c r="P56" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="57" spans="1:16">
@@ -4250,7 +4259,7 @@
         <v>1</v>
       </c>
       <c r="P57" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="58" spans="1:16">
@@ -4300,7 +4309,7 @@
         <v>1</v>
       </c>
       <c r="P58" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="59" spans="1:16">
@@ -4350,7 +4359,7 @@
         <v>1</v>
       </c>
       <c r="P59" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="60" spans="1:16">
@@ -4400,7 +4409,7 @@
         <v>1</v>
       </c>
       <c r="P60" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="61" spans="1:16">
@@ -4450,7 +4459,7 @@
         <v>1</v>
       </c>
       <c r="P61" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="62" spans="1:16">
@@ -4500,7 +4509,7 @@
         <v>1</v>
       </c>
       <c r="P62" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="63" spans="1:16">
@@ -4514,7 +4523,7 @@
         <v>10.70295290100141</v>
       </c>
       <c r="D63" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E63">
         <v>8.905400692050126</v>
@@ -4550,7 +4559,7 @@
         <v>1</v>
       </c>
       <c r="P63" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="64" spans="1:16">
@@ -4564,7 +4573,7 @@
         <v>11.20304517915771</v>
       </c>
       <c r="D64" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E64">
         <v>8.905400692050126</v>
@@ -4600,7 +4609,7 @@
         <v>1</v>
       </c>
       <c r="P64" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="65" spans="1:16">
@@ -4650,7 +4659,7 @@
         <v>1</v>
       </c>
       <c r="P65" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="66" spans="1:16">
@@ -4664,7 +4673,7 @@
         <v>10.69564352718713</v>
       </c>
       <c r="D66" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E66">
         <v>10.68408451836947</v>
@@ -4700,7 +4709,7 @@
         <v>1</v>
       </c>
       <c r="P66" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="67" spans="1:16">
@@ -4714,7 +4723,7 @@
         <v>11.03068966626528</v>
       </c>
       <c r="D67" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E67">
         <v>10.68408451836947</v>
@@ -4750,7 +4759,7 @@
         <v>1</v>
       </c>
       <c r="P67" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="68" spans="1:16">
@@ -4800,7 +4809,7 @@
         <v>1</v>
       </c>
       <c r="P68" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="69" spans="1:16">
@@ -4814,7 +4823,7 @@
         <v>10.52605158161457</v>
       </c>
       <c r="D69" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E69">
         <v>8.71498607743235</v>
@@ -4850,7 +4859,7 @@
         <v>1</v>
       </c>
       <c r="P69" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="70" spans="1:16">
@@ -4864,7 +4873,7 @@
         <v>11.02061569354003</v>
       </c>
       <c r="D70" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E70">
         <v>8.71498607743235</v>
@@ -4900,7 +4909,7 @@
         <v>1</v>
       </c>
       <c r="P70" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="71" spans="1:16">
@@ -4950,7 +4959,7 @@
         <v>1</v>
       </c>
       <c r="P71" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="72" spans="1:16">
@@ -4964,7 +4973,7 @@
         <v>10.52396325368498</v>
       </c>
       <c r="D72" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E72">
         <v>8.806051581614568</v>
@@ -5000,7 +5009,7 @@
         <v>1</v>
       </c>
       <c r="P72" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="73" spans="1:16">
@@ -5014,7 +5023,7 @@
         <v>10.8562453096477</v>
       </c>
       <c r="D73" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E73">
         <v>8.806051581614568</v>
@@ -5050,7 +5059,7 @@
         <v>1</v>
       </c>
       <c r="P73" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="74" spans="1:16">
@@ -5064,7 +5073,7 @@
         <v>10.34525014922946</v>
       </c>
       <c r="D74" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E74">
         <v>8.520373424517821</v>
@@ -5114,7 +5123,7 @@
         <v>10.83416421639288</v>
       </c>
       <c r="D75" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E75">
         <v>8.520373424517821</v>
@@ -5264,7 +5273,7 @@
         <v>10.34849797468624</v>
       </c>
       <c r="D78" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E78">
         <v>8.625250149229462</v>
@@ -5314,7 +5323,7 @@
         <v>10.67795500826794</v>
       </c>
       <c r="D79" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E79">
         <v>8.625250149229462</v>
@@ -5364,7 +5373,7 @@
         <v>10.18864383981015</v>
       </c>
       <c r="D80" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E80">
         <v>8.351804133128983</v>
@@ -5400,7 +5409,7 @@
         <v>1</v>
       </c>
       <c r="P80" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="81" spans="1:16">
@@ -5414,7 +5423,7 @@
         <v>10.67266395980422</v>
       </c>
       <c r="D81" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E81">
         <v>8.351804133128983</v>
@@ -5450,7 +5459,7 @@
         <v>1</v>
       </c>
       <c r="P81" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="82" spans="1:16">
@@ -5500,7 +5509,7 @@
         <v>1</v>
       </c>
       <c r="P82" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="83" spans="1:16">
@@ -5550,7 +5559,7 @@
         <v>1</v>
       </c>
       <c r="P83" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="84" spans="1:16">
@@ -5564,7 +5573,7 @@
         <v>10.19651372648243</v>
       </c>
       <c r="D84" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E84">
         <v>8.468643839810152</v>
@@ -5600,7 +5609,7 @@
         <v>1</v>
       </c>
       <c r="P84" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="85" spans="1:16">
@@ -5614,7 +5623,7 @@
         <v>10.52352378647946</v>
       </c>
       <c r="D85" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E85">
         <v>8.468643839810152</v>
@@ -5650,7 +5659,7 @@
         <v>1</v>
       </c>
       <c r="P85" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="86" spans="1:16">
@@ -5664,7 +5673,7 @@
         <v>-1.278554542763944</v>
       </c>
       <c r="D86" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E86">
         <v>0.01420169243589342</v>
@@ -5700,7 +5709,7 @@
         <v>1</v>
       </c>
       <c r="P86" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="87" spans="1:16">
@@ -5714,7 +5723,7 @@
         <v>-2.406586639852707</v>
       </c>
       <c r="D87" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E87">
         <v>0.01420169243589342</v>
@@ -5750,7 +5759,7 @@
         <v>1</v>
       </c>
       <c r="P87" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="88" spans="1:16">
@@ -5800,7 +5809,7 @@
         <v>1</v>
       </c>
       <c r="P88" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="89" spans="1:16">
@@ -5814,7 +5823,7 @@
         <v>-1.341212522415489</v>
       </c>
       <c r="D89" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E89">
         <v>0.1246199151405953</v>
@@ -5850,7 +5859,7 @@
         <v>1</v>
       </c>
       <c r="P89" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="90" spans="1:16">
@@ -5864,7 +5873,7 @@
         <v>-2.475362406493851</v>
       </c>
       <c r="D90" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E90">
         <v>0.1246199151405953</v>
@@ -5900,7 +5909,7 @@
         <v>1</v>
       </c>
       <c r="P90" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="91" spans="1:16">
@@ -5950,7 +5959,7 @@
         <v>1</v>
       </c>
       <c r="P91" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="92" spans="1:16">
@@ -5964,7 +5973,7 @@
         <v>-2.566016320350375</v>
       </c>
       <c r="D92" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E92">
         <v>0.02954385914472724</v>
@@ -6114,7 +6123,7 @@
         <v>-2.663355023194697</v>
       </c>
       <c r="D95" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E95">
         <v>0.03872013419191234</v>
@@ -6150,7 +6159,7 @@
         <v>1</v>
       </c>
       <c r="P95" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="96" spans="1:16">
@@ -6200,7 +6209,7 @@
         <v>1</v>
       </c>
       <c r="P96" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="97" spans="1:16">
@@ -6250,7 +6259,7 @@
         <v>1</v>
       </c>
       <c r="P97" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="98" spans="1:16">
@@ -6264,7 +6273,7 @@
         <v>-2.748103967913549</v>
       </c>
       <c r="D98" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E98">
         <v>-0.04760949385741853</v>
@@ -6300,7 +6309,7 @@
         <v>1</v>
       </c>
       <c r="P98" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="99" spans="1:16">
@@ -6314,7 +6323,7 @@
         <v>1.170412609918055</v>
       </c>
       <c r="D99" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E99">
         <v>1.469846093587645</v>
@@ -6350,7 +6359,7 @@
         <v>1</v>
       </c>
       <c r="P99" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="100" spans="1:16">
@@ -6364,7 +6373,7 @@
         <v>1.197090465141786</v>
       </c>
       <c r="D100" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E100">
         <v>1.469846093587645</v>
@@ -6400,7 +6409,7 @@
         <v>1</v>
       </c>
       <c r="P100" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="101" spans="1:16">
@@ -6414,7 +6423,7 @@
         <v>-2.807295369205091</v>
       </c>
       <c r="D101" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E101">
         <v>0.3363998775430197</v>
@@ -6450,7 +6459,7 @@
         <v>1</v>
       </c>
       <c r="P101" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="102" spans="1:16">
@@ -6500,7 +6509,7 @@
         <v>1</v>
       </c>
       <c r="P102" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="103" spans="1:16">
@@ -6600,7 +6609,7 @@
         <v>1</v>
       </c>
       <c r="P104" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="105" spans="1:16">
@@ -6614,7 +6623,7 @@
         <v>1.819034812951433</v>
       </c>
       <c r="D105" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E105">
         <v>1.780382458905816</v>
@@ -6650,7 +6659,7 @@
         <v>1</v>
       </c>
       <c r="P105" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="106" spans="1:16">
@@ -6664,7 +6673,7 @@
         <v>1.278232359359254</v>
       </c>
       <c r="D106" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E106">
         <v>1.780382458905816</v>
@@ -6700,7 +6709,7 @@
         <v>1</v>
       </c>
       <c r="P106" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="107" spans="1:16">
@@ -6714,7 +6723,7 @@
         <v>-1.27500579580901</v>
       </c>
       <c r="D107" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E107">
         <v>0.204597470791132</v>
@@ -6750,7 +6759,7 @@
         <v>1</v>
       </c>
       <c r="P107" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="108" spans="1:16">
@@ -6764,7 +6773,7 @@
         <v>-1.164182632644362</v>
       </c>
       <c r="D108" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E108">
         <v>0.204597470791132</v>
@@ -6800,7 +6809,7 @@
         <v>1</v>
       </c>
       <c r="P108" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="109" spans="1:16">
@@ -6850,7 +6859,7 @@
         <v>1</v>
       </c>
       <c r="P109" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="110" spans="1:16">
@@ -6900,7 +6909,7 @@
         <v>1</v>
       </c>
       <c r="P110" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="111" spans="1:16">
@@ -6914,7 +6923,7 @@
         <v>-1.330656541117063</v>
       </c>
       <c r="D111" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E111">
         <v>0.1498300706466971</v>
@@ -6950,7 +6959,7 @@
         <v>1</v>
       </c>
       <c r="P111" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="112" spans="1:16">
@@ -6964,7 +6973,7 @@
         <v>-1.089957636312631</v>
       </c>
       <c r="D112" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E112">
         <v>0.1498300706466971</v>
@@ -7000,7 +7009,7 @@
         <v>1</v>
       </c>
       <c r="P112" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="113" spans="1:16">
@@ -7014,7 +7023,7 @@
         <v>1.663161219313913</v>
       </c>
       <c r="D113" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E113">
         <v>1.394552474924428</v>
@@ -7050,7 +7059,7 @@
         <v>1</v>
       </c>
       <c r="P113" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="114" spans="1:16">
@@ -7064,7 +7073,7 @@
         <v>2.020453841772007</v>
       </c>
       <c r="D114" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E114">
         <v>1.394552474924428</v>
@@ -7100,7 +7109,7 @@
         <v>1</v>
       </c>
       <c r="P114" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="115" spans="1:16">
@@ -7150,7 +7159,7 @@
         <v>1</v>
       </c>
       <c r="P115" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="116" spans="1:16">
@@ -7200,7 +7209,7 @@
         <v>1</v>
       </c>
       <c r="P116" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="117" spans="1:16">
@@ -7250,7 +7259,7 @@
         <v>1</v>
       </c>
       <c r="P117" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="118" spans="1:16">
@@ -7300,7 +7309,7 @@
         <v>1</v>
       </c>
       <c r="P118" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="119" spans="1:16">
@@ -7350,7 +7359,7 @@
         <v>1</v>
       </c>
       <c r="P119" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="120" spans="1:16">
@@ -7400,7 +7409,7 @@
         <v>1</v>
       </c>
       <c r="P120" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="121" spans="1:16">
@@ -7450,7 +7459,7 @@
         <v>1</v>
       </c>
       <c r="P121" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="122" spans="1:16">
@@ -7500,7 +7509,7 @@
         <v>1</v>
       </c>
       <c r="P122" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="123" spans="1:16">
@@ -7550,7 +7559,7 @@
         <v>1</v>
       </c>
       <c r="P123" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="124" spans="1:16">
@@ -7600,7 +7609,7 @@
         <v>1</v>
       </c>
       <c r="P124" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="125" spans="1:16">
@@ -7714,7 +7723,7 @@
         <v>1.583716178161136</v>
       </c>
       <c r="D127" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E127">
         <v>1.731188504841963</v>
@@ -7764,7 +7773,7 @@
         <v>1.943294205912665</v>
       </c>
       <c r="D128" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E128">
         <v>1.731188504841963</v>
@@ -7814,7 +7823,7 @@
         <v>1.440029121201585</v>
       </c>
       <c r="D129" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E129">
         <v>1.731188504841963</v>
@@ -7900,7 +7909,7 @@
         <v>1</v>
       </c>
       <c r="P130" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="131" spans="1:16">
@@ -7950,7 +7959,7 @@
         <v>1</v>
       </c>
       <c r="P131" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="132" spans="1:16">
@@ -8000,7 +8009,7 @@
         <v>1</v>
       </c>
       <c r="P132" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="133" spans="1:16">
@@ -8050,7 +8059,7 @@
         <v>1</v>
       </c>
       <c r="P133" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="134" spans="1:16">
@@ -8100,7 +8109,7 @@
         <v>1</v>
       </c>
       <c r="P134" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="135" spans="1:16">
@@ -8114,7 +8123,7 @@
         <v>-0.8820242128746258</v>
       </c>
       <c r="D135" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E135">
         <v>0.3526024044326252</v>
@@ -8150,7 +8159,7 @@
         <v>1</v>
       </c>
       <c r="P135" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="136" spans="1:16">
@@ -8164,7 +8173,7 @@
         <v>-1.173427909927172</v>
       </c>
       <c r="D136" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E136">
         <v>0.3526024044326252</v>
@@ -8200,7 +8209,7 @@
         <v>1</v>
       </c>
       <c r="P136" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="137" spans="1:16">
@@ -8250,7 +8259,7 @@
         <v>1</v>
       </c>
       <c r="P137" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="138" spans="1:16">
@@ -8300,7 +8309,7 @@
         <v>1</v>
       </c>
       <c r="P138" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="139" spans="1:16">
@@ -8350,7 +8359,7 @@
         <v>1</v>
       </c>
       <c r="P139" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="140" spans="1:16">
@@ -8664,7 +8673,7 @@
         <v>1.916709703800588</v>
       </c>
       <c r="D146" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E146">
         <v>1.625228926806798</v>
@@ -8714,7 +8723,7 @@
         <v>1.775844332123576</v>
       </c>
       <c r="D147" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E147">
         <v>1.625228926806798</v>
@@ -8764,7 +8773,7 @@
         <v>1.706459737440355</v>
       </c>
       <c r="D148" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E148">
         <v>1.625228926806798</v>
@@ -8814,7 +8823,7 @@
         <v>1.898407474064776</v>
       </c>
       <c r="D149" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E149">
         <v>1.579058157468399</v>
@@ -8850,7 +8859,7 @@
         <v>1</v>
       </c>
       <c r="P149" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="150" spans="1:16">
@@ -8864,7 +8873,7 @@
         <v>1.757671173119327</v>
       </c>
       <c r="D150" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E150">
         <v>1.579058157468399</v>
@@ -8900,7 +8909,7 @@
         <v>1</v>
       </c>
       <c r="P150" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="151" spans="1:16">
@@ -8914,7 +8923,7 @@
         <v>1.688493091606606</v>
       </c>
       <c r="D151" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E151">
         <v>1.579058157468399</v>
@@ -8950,7 +8959,7 @@
         <v>1</v>
       </c>
       <c r="P151" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="152" spans="1:16">
@@ -9000,7 +9009,7 @@
         <v>1</v>
       </c>
       <c r="P152" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="153" spans="1:16">
@@ -9050,7 +9059,7 @@
         <v>1</v>
       </c>
       <c r="P153" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="154" spans="1:16">
@@ -9100,7 +9109,7 @@
         <v>1</v>
       </c>
       <c r="P154" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="155" spans="1:16">
@@ -9150,7 +9159,7 @@
         <v>1</v>
       </c>
       <c r="P155" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="156" spans="1:16">
@@ -9200,7 +9209,7 @@
         <v>1</v>
       </c>
       <c r="P156" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="157" spans="1:16">
@@ -9250,7 +9259,7 @@
         <v>1</v>
       </c>
       <c r="P157" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="158" spans="1:16">
@@ -9400,7 +9409,7 @@
         <v>1</v>
       </c>
       <c r="P160" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="161" spans="1:16">
@@ -9450,7 +9459,7 @@
         <v>1</v>
       </c>
       <c r="P161" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="162" spans="1:16">
@@ -9500,7 +9509,7 @@
         <v>1</v>
       </c>
       <c r="P162" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="163" spans="1:16">
@@ -9550,7 +9559,7 @@
         <v>1</v>
       </c>
       <c r="P163" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="164" spans="1:16">
@@ -9564,7 +9573,7 @@
         <v>2.0418888555804</v>
       </c>
       <c r="D164" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E164">
         <v>2.091052252009925</v>
@@ -9614,7 +9623,7 @@
         <v>2.437529947263654</v>
       </c>
       <c r="D165" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E165">
         <v>2.091052252009925</v>
@@ -9664,7 +9673,7 @@
         <v>2.035427646090795</v>
       </c>
       <c r="D166" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E166">
         <v>1.677256780401082</v>
@@ -9700,7 +9709,7 @@
         <v>1</v>
       </c>
       <c r="P166" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="167" spans="1:16">
@@ -9714,7 +9723,7 @@
         <v>2.4319519246827</v>
       </c>
       <c r="D167" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E167">
         <v>1.677256780401082</v>
@@ -9750,7 +9759,7 @@
         <v>1</v>
       </c>
       <c r="P167" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="168" spans="1:16">
@@ -9800,7 +9809,7 @@
         <v>1</v>
       </c>
       <c r="P168" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="169" spans="1:16">
@@ -9850,7 +9859,7 @@
         <v>1</v>
       </c>
       <c r="P169" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="170" spans="1:16">
@@ -9900,7 +9909,7 @@
         <v>1</v>
       </c>
       <c r="P170" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="171" spans="1:16">
@@ -9950,7 +9959,7 @@
         <v>1</v>
       </c>
       <c r="P171" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="172" spans="1:16">
@@ -10000,7 +10009,7 @@
         <v>1</v>
       </c>
       <c r="P172" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="173" spans="1:16">
@@ -10014,7 +10023,7 @@
         <v>2.053037839433713</v>
       </c>
       <c r="D173" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E173">
         <v>2.029053723158555</v>
@@ -10050,7 +10059,7 @@
         <v>1</v>
       </c>
       <c r="P173" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="174" spans="1:16">
@@ -10164,7 +10173,7 @@
         <v>2.072439051471395</v>
       </c>
       <c r="D176" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E176">
         <v>2.198537473651809</v>
@@ -10200,7 +10209,7 @@
         <v>1</v>
       </c>
       <c r="P176" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="177" spans="1:16">
@@ -10214,7 +10223,7 @@
         <v>2.176038435736924</v>
       </c>
       <c r="D177" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E177">
         <v>2.198537473651809</v>
@@ -10250,7 +10259,7 @@
         <v>1</v>
       </c>
       <c r="P177" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="178" spans="1:16">
@@ -10300,7 +10309,7 @@
         <v>1</v>
       </c>
       <c r="P178" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="179" spans="1:16">
@@ -10364,7 +10373,7 @@
         <v>2.199572666349018</v>
       </c>
       <c r="D180" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E180">
         <v>2.369622868222606</v>
@@ -10564,7 +10573,7 @@
         <v>2.441204477380014</v>
       </c>
       <c r="D184" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E184">
         <v>3.019740173907834</v>
@@ -10664,7 +10673,7 @@
         <v>2.450942264059425</v>
       </c>
       <c r="D186" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E186">
         <v>3.396065694761221</v>
@@ -10714,7 +10723,7 @@
         <v>2.93271297523739</v>
       </c>
       <c r="D187" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E187">
         <v>3.396065694761221</v>
@@ -10814,7 +10823,7 @@
         <v>2.613291041571109</v>
       </c>
       <c r="D189" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E189">
         <v>1.747095958240026</v>
@@ -10864,7 +10873,7 @@
         <v>2.94332933323569</v>
       </c>
       <c r="D190" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E190">
         <v>3.513960124909904</v>
@@ -11014,7 +11023,7 @@
         <v>2.630002520413537</v>
       </c>
       <c r="D193" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E193">
         <v>1.763414225815572</v>
@@ -11064,7 +11073,7 @@
         <v>2.960405936825934</v>
       </c>
       <c r="D194" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E194">
         <v>2.688557154970242</v>
@@ -11264,7 +11273,7 @@
         <v>2.642059072099817</v>
       </c>
       <c r="D198" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E198">
         <v>1.775187093932763</v>
@@ -11314,7 +11323,7 @@
         <v>2.972725908969226</v>
       </c>
       <c r="D199" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E199">
         <v>2.375803028433923</v>
@@ -11464,7 +11473,7 @@
         <v>2.666955617984192</v>
       </c>
       <c r="D202" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E202">
         <v>1.799497838737505</v>
@@ -11514,7 +11523,7 @@
         <v>2.998166412998973</v>
       </c>
       <c r="D203" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E203">
         <v>1.736641978102437</v>
@@ -11664,7 +11673,7 @@
         <v>2.973643871143521</v>
       </c>
       <c r="D206" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E206">
         <v>1.818524938691256</v>
@@ -11714,7 +11723,7 @@
         <v>3.018077732744034</v>
       </c>
       <c r="D207" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E207">
         <v>1.759533446033025</v>
@@ -11864,7 +11873,7 @@
         <v>2.990082102112254</v>
       </c>
       <c r="D210" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E210">
         <v>1.83485077149952</v>
@@ -11914,7 +11923,7 @@
         <v>3.03516225313547</v>
       </c>
       <c r="D211" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E211">
         <v>1.779175024575153</v>
@@ -12000,7 +12009,7 @@
         <v>1</v>
       </c>
       <c r="P212" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="213" spans="1:16">
@@ -12050,7 +12059,7 @@
         <v>1</v>
       </c>
       <c r="P213" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="214" spans="1:16">
@@ -12064,7 +12073,7 @@
         <v>3.005496469975766</v>
       </c>
       <c r="D214" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E214">
         <v>1.850159741975929</v>
@@ -12100,7 +12109,7 @@
         <v>1</v>
       </c>
       <c r="P214" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="215" spans="1:16">
@@ -12114,7 +12123,7 @@
         <v>3.051182655974811</v>
       </c>
       <c r="D215" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E215">
         <v>1.797593217971041</v>
@@ -12150,7 +12159,7 @@
         <v>1</v>
       </c>
       <c r="P215" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="216" spans="1:16">
@@ -12264,7 +12273,7 @@
         <v>3.018931533510157</v>
       </c>
       <c r="D218" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E218">
         <v>1.863502941828035</v>
@@ -12314,7 +12323,7 @@
         <v>3.06514593568235</v>
       </c>
       <c r="D219" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E219">
         <v>1.813646396450594</v>
@@ -12464,7 +12473,7 @@
         <v>3.033933076549712</v>
       </c>
       <c r="D222" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E222">
         <v>1.878401910214327</v>
@@ -12514,7 +12523,7 @@
         <v>3.080737282978161</v>
       </c>
       <c r="D223" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E223">
         <v>1.831571317108114</v>
@@ -12564,7 +12573,7 @@
         <v>1.639859271051932</v>
       </c>
       <c r="D224" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E224">
         <v>1.9209216037227</v>
@@ -12714,7 +12723,7 @@
         <v>3.05833801181463</v>
       </c>
       <c r="D227" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E227">
         <v>1.902639974127007</v>
@@ -12764,7 +12773,7 @@
         <v>3.106101728518452</v>
       </c>
       <c r="D228" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E228">
         <v>1.860732085911838</v>
@@ -12850,7 +12859,7 @@
         <v>1</v>
       </c>
       <c r="P229" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="230" spans="1:16">
@@ -12900,7 +12909,7 @@
         <v>1</v>
       </c>
       <c r="P230" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="231" spans="1:16">
@@ -12914,7 +12923,7 @@
         <v>3.085055612872655</v>
       </c>
       <c r="D231" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E231">
         <v>1.929174890733353</v>
@@ -12950,7 +12959,7 @@
         <v>1</v>
       </c>
       <c r="P231" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="232" spans="1:16">
@@ -12964,7 +12973,7 @@
         <v>3.13386976517363</v>
       </c>
       <c r="D232" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E232">
         <v>1.892656193842708</v>
@@ -13000,7 +13009,7 @@
         <v>1</v>
       </c>
       <c r="P232" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="233" spans="1:16">
@@ -13064,7 +13073,7 @@
         <v>3.103034611570727</v>
       </c>
       <c r="D234" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E234">
         <v>1.947030956106994</v>
@@ -13114,7 +13123,7 @@
         <v>3.152555630487182</v>
       </c>
       <c r="D235" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E235">
         <v>1.914138792287073</v>
@@ -13164,7 +13173,7 @@
         <v>1.641725609550694</v>
       </c>
       <c r="D236" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E236">
         <v>1.89319910743864</v>
@@ -13250,7 +13259,7 @@
         <v>1</v>
       </c>
       <c r="P237" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="238" spans="1:16">
@@ -13264,7 +13273,7 @@
         <v>3.11979974827751</v>
       </c>
       <c r="D238" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E238">
         <v>1.963681459400396</v>
@@ -13300,7 +13309,7 @@
         <v>1</v>
       </c>
       <c r="P238" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="239" spans="1:16">
@@ -13314,7 +13323,7 @@
         <v>3.169979909320897</v>
       </c>
       <c r="D239" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E239">
         <v>1.934170981275177</v>
@@ -13350,7 +13359,7 @@
         <v>1</v>
       </c>
       <c r="P239" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="240" spans="1:16">
@@ -13364,7 +13373,7 @@
         <v>1.664480342106565</v>
       </c>
       <c r="D240" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E240">
         <v>2.221652319966786</v>
@@ -13400,7 +13409,7 @@
         <v>1</v>
       </c>
       <c r="P240" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="241" spans="1:16">
@@ -13464,7 +13473,7 @@
         <v>3.136490860930856</v>
       </c>
       <c r="D242" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E242">
         <v>1.980258444787738</v>
@@ -13514,7 +13523,7 @@
         <v>3.187327253753777</v>
       </c>
       <c r="D243" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E243">
         <v>1.954114721009688</v>
@@ -13714,7 +13723,7 @@
         <v>3.154470288152615</v>
       </c>
       <c r="D247" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E247">
         <v>1.998114935754989</v>
@@ -13764,7 +13773,7 @@
         <v>3.206013564438956</v>
       </c>
       <c r="D248" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E248">
         <v>1.975597831484915</v>
@@ -13950,7 +13959,7 @@
         <v>1</v>
       </c>
       <c r="P251" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="252" spans="1:16">
@@ -14000,7 +14009,7 @@
         <v>1</v>
       </c>
       <c r="P252" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="253" spans="1:16">
@@ -14014,7 +14023,7 @@
         <v>3.175183381627829</v>
       </c>
       <c r="D253" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E253">
         <v>2.406837822852639</v>
@@ -14050,7 +14059,7 @@
         <v>1</v>
       </c>
       <c r="P253" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="254" spans="1:16">
@@ -14064,7 +14073,7 @@
         <v>3.227541018854222</v>
       </c>
       <c r="D254" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E254">
         <v>2.000347322662993</v>
@@ -14100,7 +14109,7 @@
         <v>1</v>
       </c>
       <c r="P254" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="255" spans="1:16">
@@ -14150,7 +14159,7 @@
         <v>1</v>
       </c>
       <c r="P255" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="256" spans="1:16">
@@ -14200,7 +14209,7 @@
         <v>1</v>
       </c>
       <c r="P256" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="257" spans="1:16">
@@ -14314,7 +14323,7 @@
         <v>3.194491499183421</v>
       </c>
       <c r="D259" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E259">
         <v>2.42485873257119</v>
@@ -14364,7 +14373,7 @@
         <v>3.247608258980375</v>
       </c>
       <c r="D260" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E260">
         <v>2.023418047742236</v>
@@ -14614,7 +14623,7 @@
         <v>3.213727962726566</v>
       </c>
       <c r="D265" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E265">
         <v>2.442812765211459</v>
@@ -14664,7 +14673,7 @@
         <v>3.26760102792778</v>
       </c>
       <c r="D266" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E266">
         <v>2.046403155463022</v>
@@ -14864,7 +14873,7 @@
         <v>3.233647867837396</v>
       </c>
       <c r="D270" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E270">
         <v>2.461404676648234</v>
@@ -14914,7 +14923,7 @@
         <v>3.288304108795105</v>
       </c>
       <c r="D271" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E271">
         <v>2.070204888236475</v>
@@ -15114,7 +15123,7 @@
         <v>3.249417008017017</v>
       </c>
       <c r="D275" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E275">
         <v>2.476122540815881</v>
@@ -15164,7 +15173,7 @@
         <v>3.304693232263839</v>
       </c>
       <c r="D276" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E276">
         <v>2.089046989066485</v>
@@ -15314,7 +15323,7 @@
         <v>1.914875661806953</v>
       </c>
       <c r="D279" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E279">
         <v>2.109898465499843</v>
@@ -15400,7 +15409,7 @@
         <v>1</v>
       </c>
       <c r="P280" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="281" spans="1:16">
@@ -15414,7 +15423,7 @@
         <v>3.261163134684622</v>
       </c>
       <c r="D281" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E281">
         <v>2.487085592372312</v>
@@ -15450,7 +15459,7 @@
         <v>1</v>
       </c>
       <c r="P281" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="282" spans="1:16">
@@ -15464,7 +15473,7 @@
         <v>3.316901172458547</v>
       </c>
       <c r="D282" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E282">
         <v>2.103082104520595</v>
@@ -15500,7 +15509,7 @@
         <v>1</v>
       </c>
       <c r="P282" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="283" spans="1:16">
@@ -15550,7 +15559,7 @@
         <v>1</v>
       </c>
       <c r="P283" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="284" spans="1:16">
@@ -15600,7 +15609,7 @@
         <v>1</v>
       </c>
       <c r="P284" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="285" spans="1:16">
@@ -15614,7 +15623,7 @@
         <v>1.930296217842372</v>
       </c>
       <c r="D285" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E285">
         <v>2.383746445952788</v>
@@ -15650,7 +15659,7 @@
         <v>1</v>
       </c>
       <c r="P285" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="286" spans="1:16">
@@ -15700,7 +15709,7 @@
         <v>1</v>
       </c>
       <c r="P286" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="287" spans="1:16">
@@ -15714,7 +15723,7 @@
         <v>3.267778188252251</v>
       </c>
       <c r="D287" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E287">
         <v>2.493259642368766</v>
@@ -15750,7 +15759,7 @@
         <v>1</v>
       </c>
       <c r="P287" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="288" spans="1:16">
@@ -15764,7 +15773,7 @@
         <v>3.323776305055329</v>
       </c>
       <c r="D288" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E288">
         <v>2.110986245450121</v>
@@ -15800,7 +15809,7 @@
         <v>1</v>
       </c>
       <c r="P288" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="289" spans="1:16">
@@ -15850,7 +15859,7 @@
         <v>1</v>
       </c>
       <c r="P289" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="290" spans="1:16">
@@ -15900,7 +15909,7 @@
         <v>1</v>
       </c>
       <c r="P290" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="291" spans="1:16">
@@ -15950,7 +15959,7 @@
         <v>1</v>
       </c>
       <c r="P291" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="292" spans="1:16">
@@ -15964,7 +15973,7 @@
         <v>3.278598009747792</v>
       </c>
       <c r="D292" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E292">
         <v>2.503358142431271</v>
@@ -16014,7 +16023,7 @@
         <v>3.335021521242147</v>
       </c>
       <c r="D293" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E293">
         <v>2.123914544980693</v>
@@ -16164,7 +16173,7 @@
         <v>1.953185079463765</v>
       </c>
       <c r="D296" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E296">
         <v>1.673185079463764</v>
@@ -16214,7 +16223,7 @@
         <v>1.838424946780282</v>
       </c>
       <c r="D297" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E297">
         <v>1.673185079463764</v>
@@ -16264,7 +16273,7 @@
         <v>3.286491586851236</v>
       </c>
       <c r="D298" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E298">
         <v>2.510725481061151</v>
@@ -16314,7 +16323,7 @@
         <v>3.343225444112052</v>
       </c>
       <c r="D299" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E299">
         <v>2.133346357622241</v>
@@ -16464,7 +16473,7 @@
         <v>1.963547929404697</v>
       </c>
       <c r="D302" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E302">
         <v>2.040362444937774</v>
@@ -16514,7 +16523,7 @@
         <v>1.849314035194777</v>
       </c>
       <c r="D303" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E303">
         <v>2.040362444937774</v>
@@ -16564,7 +16573,7 @@
         <v>3.287218803551511</v>
       </c>
       <c r="D304" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E304">
         <v>2.511404216648074</v>
@@ -16614,7 +16623,7 @@
         <v>3.34398125223815</v>
       </c>
       <c r="D305" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E305">
         <v>2.134215288346162</v>
@@ -16764,7 +16773,7 @@
         <v>1.964502634406085</v>
       </c>
       <c r="D308" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E308">
         <v>2.034789980466009</v>
@@ -16814,7 +16823,7 @@
         <v>1.850317221309513</v>
       </c>
       <c r="D309" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E309">
         <v>2.034789980466009</v>
@@ -16864,7 +16873,7 @@
         <v>3.309574328279867</v>
       </c>
       <c r="D310" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E310">
         <v>2.532269373061208</v>
@@ -16914,7 +16923,7 @@
         <v>3.367215712126766</v>
       </c>
       <c r="D311" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E311">
         <v>2.160927274303631</v>
@@ -17164,7 +17173,7 @@
         <v>3.386581638751728</v>
       </c>
       <c r="D316" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E316">
         <v>2.183191719551736</v>
@@ -17264,7 +17273,7 @@
         <v>2.018313648949551</v>
       </c>
       <c r="D318" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E318">
         <v>2.020805677582523</v>
@@ -17314,7 +17323,7 @@
         <v>1.906860826435267</v>
       </c>
       <c r="D319" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E319">
         <v>2.020805677582523</v>
@@ -17364,7 +17373,7 @@
         <v>1.784750528729781</v>
       </c>
       <c r="D320" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E320">
         <v>2.020805677582523</v>
@@ -17414,7 +17423,7 @@
         <v>3.376305833526885</v>
       </c>
       <c r="D321" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E321">
         <v>2.171377923742256</v>
@@ -17450,7 +17459,7 @@
         <v>1</v>
       </c>
       <c r="P321" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="322" spans="1:16">
@@ -17500,7 +17509,7 @@
         <v>1</v>
       </c>
       <c r="P322" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="323" spans="1:16">
@@ -17550,7 +17559,7 @@
         <v>1</v>
       </c>
       <c r="P323" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="324" spans="1:16">
@@ -17600,7 +17609,7 @@
         <v>1</v>
       </c>
       <c r="P324" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="325" spans="1:16">
@@ -17614,7 +17623,7 @@
         <v>3.346413966869674</v>
       </c>
       <c r="D325" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E325">
         <v>2.137012109937338</v>
@@ -17650,7 +17659,7 @@
         <v>1</v>
       </c>
       <c r="P325" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="326" spans="1:16">
@@ -17700,7 +17709,7 @@
         <v>1</v>
       </c>
       <c r="P326" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="327" spans="1:16">
@@ -17714,7 +17723,7 @@
         <v>1.853546169841817</v>
       </c>
       <c r="D327" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E327">
         <v>1.909412654865697</v>
@@ -17750,7 +17759,7 @@
         <v>1</v>
       </c>
       <c r="P327" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="328" spans="1:16">
@@ -17764,7 +17773,7 @@
         <v>1.729057523143315</v>
       </c>
       <c r="D328" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E328">
         <v>1.909412654865697</v>
@@ -17800,7 +17809,7 @@
         <v>1</v>
       </c>
       <c r="P328" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="329" spans="1:16">
@@ -17814,7 +17823,7 @@
         <v>1.90213361560998</v>
       </c>
       <c r="D329" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E329">
         <v>1.909412654865697</v>
@@ -17850,7 +17859,7 @@
         <v>1</v>
       </c>
       <c r="P329" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="330" spans="1:16">
@@ -17864,7 +17873,7 @@
         <v>3.335708401471214</v>
       </c>
       <c r="D330" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E330">
         <v>2.124704231296676</v>
@@ -17900,7 +17909,7 @@
         <v>1</v>
       </c>
       <c r="P330" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="331" spans="1:16">
@@ -17950,7 +17959,7 @@
         <v>1</v>
       </c>
       <c r="P331" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="332" spans="1:16">
@@ -17964,7 +17973,7 @@
         <v>1.839336644715903</v>
       </c>
       <c r="D332" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E332">
         <v>2.572020438006287</v>
@@ -18000,7 +18009,7 @@
         <v>1</v>
       </c>
       <c r="P332" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="333" spans="1:16">
@@ -18014,7 +18023,7 @@
         <v>1.714214115855647</v>
       </c>
       <c r="D333" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E333">
         <v>2.572020438006287</v>
@@ -18050,7 +18059,7 @@
         <v>1</v>
       </c>
       <c r="P333" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="334" spans="1:16">
@@ -18064,7 +18073,7 @@
         <v>1.88846993345668</v>
       </c>
       <c r="D334" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E334">
         <v>2.572020438006287</v>
@@ -18100,7 +18109,7 @@
         <v>1</v>
       </c>
       <c r="P334" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="335" spans="1:16">
@@ -18114,7 +18123,7 @@
         <v>3.319807569063805</v>
       </c>
       <c r="D335" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E335">
         <v>2.106423504565129</v>
@@ -18214,7 +18223,7 @@
         <v>1.818231428017253</v>
       </c>
       <c r="D337" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E337">
         <v>2.552327466291189</v>
@@ -18264,7 +18273,7 @@
         <v>1.692167402501294</v>
       </c>
       <c r="D338" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E338">
         <v>2.552327466291189</v>
@@ -18314,7 +18323,7 @@
         <v>1.86817544998933</v>
       </c>
       <c r="D339" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E339">
         <v>2.552327466291189</v>
@@ -18364,7 +18373,7 @@
         <v>3.297653300651016</v>
       </c>
       <c r="D340" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E340">
         <v>2.080953383478715</v>
@@ -18400,7 +18409,7 @@
         <v>1</v>
       </c>
       <c r="P340" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="341" spans="1:16">
@@ -18450,7 +18459,7 @@
         <v>1</v>
       </c>
       <c r="P341" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="342" spans="1:16">
@@ -18464,7 +18473,7 @@
         <v>1.788826009252247</v>
       </c>
       <c r="D342" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E342">
         <v>2.524889696365481</v>
@@ -18500,7 +18509,7 @@
         <v>1</v>
       </c>
       <c r="P342" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="343" spans="1:16">
@@ -18514,7 +18523,7 @@
         <v>1.661450217843427</v>
       </c>
       <c r="D343" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E343">
         <v>2.524889696365481</v>
@@ -18550,7 +18559,7 @@
         <v>1</v>
       </c>
       <c r="P343" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="344" spans="1:16">
@@ -18564,7 +18573,7 @@
         <v>1.839899607409848</v>
       </c>
       <c r="D344" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E344">
         <v>2.524889696365481</v>
@@ -18600,7 +18609,7 @@
         <v>1</v>
       </c>
       <c r="P344" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="345" spans="1:16">
@@ -18614,7 +18623,7 @@
         <v>3.263703117123406</v>
       </c>
       <c r="D345" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E345">
         <v>2.041921840245493</v>
@@ -18714,7 +18723,7 @@
         <v>1.743763841313463</v>
       </c>
       <c r="D347" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E347">
         <v>2.48284284077948</v>
@@ -18764,7 +18773,7 @@
         <v>1.614377841669459</v>
       </c>
       <c r="D348" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E348">
         <v>2.48284284077948</v>
@@ -18814,7 +18823,7 @@
         <v>1.796568452118031</v>
       </c>
       <c r="D349" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E349">
         <v>2.48284284077948</v>
@@ -18864,7 +18873,7 @@
         <v>3.242126022559422</v>
       </c>
       <c r="D350" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E350">
         <v>2.017115279225386</v>
@@ -18900,7 +18909,7 @@
         <v>1</v>
       </c>
       <c r="P350" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="351" spans="1:16">
@@ -18950,7 +18959,7 @@
         <v>1</v>
       </c>
       <c r="P351" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="352" spans="1:16">
@@ -18964,7 +18973,7 @@
         <v>1.715124506916858</v>
       </c>
       <c r="D352" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E352">
         <v>2.456119893071122</v>
@@ -19000,7 +19009,7 @@
         <v>1</v>
       </c>
       <c r="P352" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="353" spans="1:16">
@@ -19014,7 +19023,7 @@
         <v>1.584460916147354</v>
       </c>
       <c r="D353" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E353">
         <v>2.456119893071122</v>
@@ -19050,7 +19059,7 @@
         <v>1</v>
       </c>
       <c r="P353" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="354" spans="1:16">
@@ -19064,7 +19073,7 @@
         <v>1.769029265635051</v>
       </c>
       <c r="D354" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E354">
         <v>2.456119893071122</v>
@@ -19100,7 +19109,7 @@
         <v>1</v>
       </c>
       <c r="P354" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="355" spans="1:16">
@@ -19114,7 +19123,7 @@
         <v>3.218796578894542</v>
       </c>
       <c r="D355" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E355">
         <v>1.990294093169876</v>
@@ -19214,7 +19223,7 @@
         <v>1.684159274947191</v>
       </c>
       <c r="D357" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E357">
         <v>2.427226684058535</v>
@@ -19264,7 +19273,7 @@
         <v>1.552114335539635</v>
       </c>
       <c r="D358" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E358">
         <v>2.427226684058535</v>
@@ -19314,7 +19323,7 @@
         <v>1.739253528325928</v>
       </c>
       <c r="D359" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E359">
         <v>2.427226684058535</v>
@@ -19364,7 +19373,7 @@
         <v>3.223084813618858</v>
       </c>
       <c r="D360" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E360">
         <v>1.995224152499308</v>
@@ -19400,7 +19409,7 @@
         <v>1</v>
       </c>
       <c r="P360" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="361" spans="1:16">
@@ -19414,7 +19423,7 @@
         <v>1.689851060181606</v>
       </c>
       <c r="D361" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E361">
         <v>2.432537606340457</v>
@@ -19450,7 +19459,7 @@
         <v>1</v>
       </c>
       <c r="P361" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="362" spans="1:16">
@@ -19464,7 +19473,7 @@
         <v>1.558060029409038</v>
       </c>
       <c r="D362" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E362">
         <v>2.432537606340457</v>
@@ -19500,7 +19509,7 @@
         <v>1</v>
       </c>
       <c r="P362" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="363" spans="1:16">
@@ -19514,7 +19523,7 @@
         <v>1.5546355793606</v>
       </c>
       <c r="D363" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E363">
         <v>2.429478755941318</v>
@@ -19564,7 +19573,7 @@
         <v>2.749895863416445</v>
       </c>
       <c r="D364" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E364">
         <v>2.144120683335579</v>
@@ -19600,7 +19609,7 @@
         <v>1</v>
       </c>
       <c r="P364" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="365" spans="1:16">
@@ -19614,7 +19623,7 @@
         <v>1.575757316392718</v>
       </c>
       <c r="D365" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E365">
         <v>2.448345503254703</v>
@@ -19650,7 +19659,7 @@
         <v>1</v>
       </c>
       <c r="P365" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="366" spans="1:16">
@@ -19664,7 +19673,7 @@
         <v>1.708690594836302</v>
       </c>
       <c r="D366" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E366">
         <v>1.95524223097577</v>
@@ -19700,7 +19709,7 @@
         <v>1</v>
       </c>
       <c r="P366" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="367" spans="1:16">
@@ -19714,7 +19723,7 @@
         <v>2.776972324350222</v>
       </c>
       <c r="D367" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E367">
         <v>2.170167242074328</v>
@@ -19750,7 +19759,7 @@
         <v>1</v>
       </c>
       <c r="P367" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="368" spans="1:16">
@@ -19764,7 +19773,7 @@
         <v>1.603764011567165</v>
       </c>
       <c r="D368" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E368">
         <v>2.473362159798427</v>
@@ -19800,7 +19809,7 @@
         <v>1</v>
       </c>
       <c r="P368" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="369" spans="1:16">
@@ -19814,7 +19823,7 @@
         <v>1.733308579562596</v>
       </c>
       <c r="D369" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E369">
         <v>2.069952921130998</v>
@@ -19850,7 +19859,7 @@
         <v>1</v>
       </c>
       <c r="P369" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="370" spans="1:16">
@@ -19864,7 +19873,7 @@
         <v>2.804318151096002</v>
       </c>
       <c r="D370" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E370">
         <v>2.196472920808915</v>
@@ -19900,7 +19909,7 @@
         <v>1</v>
       </c>
       <c r="P370" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="371" spans="1:16">
@@ -19914,7 +19923,7 @@
         <v>1.632049326839176</v>
       </c>
       <c r="D371" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E371">
         <v>2.498627690521825</v>
@@ -19950,7 +19959,7 @@
         <v>1</v>
       </c>
       <c r="P371" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="372" spans="1:16">
@@ -19964,7 +19973,7 @@
         <v>1.758171472346181</v>
       </c>
       <c r="D372" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E372">
         <v>2.648741745065742</v>
@@ -20000,7 +20009,7 @@
         <v>1</v>
       </c>
       <c r="P372" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="373" spans="1:16">
@@ -20014,7 +20023,7 @@
         <v>1.836308899819077</v>
       </c>
       <c r="D373" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E373">
         <v>2.387421432319158</v>
@@ -20050,7 +20059,7 @@
         <v>1</v>
       </c>
       <c r="P373" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="374" spans="1:16">
@@ -20100,7 +20109,7 @@
         <v>1</v>
       </c>
       <c r="P374" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="375" spans="1:16">
@@ -20114,7 +20123,7 @@
         <v>1.66686196794393</v>
       </c>
       <c r="D375" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E375">
         <v>2.529723679551338</v>
@@ -20150,7 +20159,7 @@
         <v>1</v>
       </c>
       <c r="P375" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="376" spans="1:16">
@@ -20164,7 +20173,7 @@
         <v>1.844881242140559</v>
       </c>
       <c r="D376" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E376">
         <v>2.529723679551338</v>
@@ -20200,7 +20209,7 @@
         <v>1</v>
       </c>
       <c r="P376" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="377" spans="1:16">
@@ -20214,7 +20223,7 @@
         <v>1.788771907765661</v>
       </c>
       <c r="D377" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E377">
         <v>2.679961622497764</v>
@@ -20250,7 +20259,7 @@
         <v>1</v>
       </c>
       <c r="P377" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="378" spans="1:16">
@@ -20264,7 +20273,7 @@
         <v>1.861508767932467</v>
       </c>
       <c r="D378" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E378">
         <v>2.411732640096055</v>
@@ -20300,7 +20309,7 @@
         <v>1</v>
       </c>
       <c r="P378" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="379" spans="1:16">
@@ -20350,7 +20359,7 @@
         <v>1</v>
       </c>
       <c r="P379" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="380" spans="1:16">
@@ -20364,7 +20373,7 @@
         <v>1.693616991646184</v>
       </c>
       <c r="D380" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E380">
         <v>2.55362229502915</v>
@@ -20400,7 +20409,7 @@
         <v>1</v>
       </c>
       <c r="P380" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="381" spans="1:16">
@@ -20414,7 +20423,7 @@
         <v>1.869509828609061</v>
       </c>
       <c r="D381" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E381">
         <v>2.55362229502915</v>
@@ -20450,7 +20459,7 @@
         <v>1</v>
       </c>
       <c r="P381" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="382" spans="1:16">
@@ -20464,7 +20473,7 @@
         <v>2.574954921244757</v>
       </c>
       <c r="D382" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E382">
         <v>2.17950982860906</v>
@@ -20500,7 +20509,7 @@
         <v>1</v>
       </c>
       <c r="P382" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="383" spans="1:16">
@@ -20514,7 +20523,7 @@
         <v>1.812289668813548</v>
       </c>
       <c r="D383" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E383">
         <v>2.703955451583056</v>
@@ -20550,7 +20559,7 @@
         <v>1</v>
       </c>
       <c r="P383" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="384" spans="1:16">
@@ -20564,7 +20573,7 @@
         <v>1.878354735459471</v>
       </c>
       <c r="D384" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E384">
         <v>2.42798454327702</v>
@@ -20600,7 +20609,7 @@
         <v>1</v>
       </c>
       <c r="P384" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="385" spans="1:16">
@@ -20650,7 +20659,7 @@
         <v>1</v>
       </c>
       <c r="P385" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="386" spans="1:16">
@@ -20664,7 +20673,7 @@
         <v>1.711502571778759</v>
       </c>
       <c r="D386" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E386">
         <v>2.569598382620882</v>
@@ -20700,7 +20709,7 @@
         <v>1</v>
       </c>
       <c r="P386" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="387" spans="1:16">
@@ -20714,7 +20723,7 @@
         <v>1.885973897627895</v>
       </c>
       <c r="D387" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E387">
         <v>2.569598382620882</v>
@@ -20750,7 +20759,7 @@
         <v>1</v>
       </c>
       <c r="P387" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="388" spans="1:16">
@@ -20764,7 +20773,7 @@
         <v>2.591185607841933</v>
       </c>
       <c r="D388" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E388">
         <v>2.195973897627894</v>
@@ -20800,7 +20809,7 @@
         <v>1</v>
       </c>
       <c r="P388" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="389" spans="1:16">
@@ -20814,7 +20823,7 @@
         <v>1.828011157399832</v>
       </c>
       <c r="D389" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E389">
         <v>2.719995188926148</v>
@@ -20850,7 +20859,7 @@
         <v>1</v>
       </c>
       <c r="P389" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="390" spans="1:16">
@@ -20864,7 +20873,7 @@
         <v>1.884937981108568</v>
       </c>
       <c r="D390" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E390">
         <v>2.434335634167709</v>
@@ -20900,7 +20909,7 @@
         <v>1</v>
       </c>
       <c r="P390" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="391" spans="1:16">
@@ -20950,7 +20959,7 @@
         <v>1</v>
       </c>
       <c r="P391" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="392" spans="1:16">
@@ -20964,7 +20973,7 @@
         <v>1.718492088255065</v>
       </c>
       <c r="D392" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E392">
         <v>2.575841687373739</v>
@@ -21000,7 +21009,7 @@
         <v>1</v>
       </c>
       <c r="P392" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="393" spans="1:16">
@@ -21014,7 +21023,7 @@
         <v>1.892407900932305</v>
       </c>
       <c r="D393" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E393">
         <v>2.575841687373739</v>
@@ -21050,7 +21059,7 @@
         <v>1</v>
       </c>
       <c r="P393" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="394" spans="1:16">
@@ -21064,7 +21073,7 @@
         <v>1.834154967256232</v>
       </c>
       <c r="D394" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E394">
         <v>2.726263367403121</v>
@@ -21100,7 +21109,7 @@
         <v>1</v>
       </c>
       <c r="P394" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="395" spans="1:16">
@@ -21114,7 +21123,7 @@
         <v>2.791624887079966</v>
       </c>
       <c r="D395" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E395">
         <v>2.637829766815571</v>
@@ -21150,7 +21159,7 @@
         <v>1</v>
       </c>
       <c r="P395" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="396" spans="1:16">
@@ -21164,7 +21173,7 @@
         <v>1.897004594528006</v>
       </c>
       <c r="D396" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E396">
         <v>2.445976724695786</v>
@@ -21200,7 +21209,7 @@
         <v>1</v>
       </c>
       <c r="P396" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="397" spans="1:16">
@@ -21250,7 +21259,7 @@
         <v>1</v>
       </c>
       <c r="P397" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="398" spans="1:16">
@@ -21264,7 +21273,7 @@
         <v>1.731303366734398</v>
       </c>
       <c r="D398" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E398">
         <v>2.587285213702252</v>
@@ -21300,7 +21309,7 @@
         <v>1</v>
       </c>
       <c r="P398" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="399" spans="1:16">
@@ -21314,7 +21323,7 @@
         <v>1.904200963921582</v>
       </c>
       <c r="D399" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E399">
         <v>2.587285213702252</v>
@@ -21350,7 +21359,7 @@
         <v>1</v>
       </c>
       <c r="P399" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="400" spans="1:16">
@@ -21364,7 +21373,7 @@
         <v>1.845416126631299</v>
       </c>
       <c r="D400" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E400">
         <v>2.737752485469994</v>
@@ -21400,7 +21409,7 @@
         <v>1</v>
       </c>
       <c r="P400" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="401" spans="1:16">
@@ -21414,7 +21423,7 @@
         <v>2.802612496024871</v>
       </c>
       <c r="D401" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E401">
         <v>2.813453713263602</v>
@@ -21450,7 +21459,7 @@
         <v>1</v>
       </c>
       <c r="P401" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="402" spans="1:16">
@@ -21464,7 +21473,7 @@
         <v>1.915149243214803</v>
       </c>
       <c r="D402" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E402">
         <v>2.463481511716044</v>
@@ -21500,7 +21509,7 @@
         <v>1</v>
       </c>
       <c r="P402" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="403" spans="1:16">
@@ -21550,7 +21559,7 @@
         <v>1</v>
       </c>
       <c r="P403" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="404" spans="1:16">
@@ -21564,7 +21573,7 @@
         <v>1.750567773337632</v>
       </c>
       <c r="D404" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E404">
         <v>2.60449292209162</v>
@@ -21600,7 +21609,7 @@
         <v>1</v>
       </c>
       <c r="P404" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="405" spans="1:16">
@@ -21614,7 +21623,7 @@
         <v>1.921934272965604</v>
       </c>
       <c r="D405" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E405">
         <v>2.60449292209162</v>
@@ -21650,7 +21659,7 @@
         <v>1</v>
       </c>
       <c r="P405" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="406" spans="1:16">
@@ -21664,7 +21673,7 @@
         <v>1.862349608592151</v>
       </c>
       <c r="D406" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E406">
         <v>2.75502875046649</v>
@@ -21700,7 +21709,7 @@
         <v>1</v>
       </c>
       <c r="P406" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="407" spans="1:16">
@@ -21714,7 +21723,7 @@
         <v>2.819134638342948</v>
       </c>
       <c r="D407" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E407">
         <v>2.769730713091974</v>
@@ -21750,7 +21759,7 @@
         <v>1</v>
       </c>
       <c r="P407" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="408" spans="1:16">
@@ -21764,7 +21773,7 @@
         <v>1.92753511972947</v>
       </c>
       <c r="D408" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E408">
         <v>2.475430606691152</v>
@@ -21864,7 +21873,7 @@
         <v>1.76371801754653</v>
       </c>
       <c r="D410" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E410">
         <v>2.616239225637646</v>
@@ -21914,7 +21923,7 @@
         <v>1.934039361347697</v>
       </c>
       <c r="D411" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E411">
         <v>2.616239225637646</v>
@@ -21964,7 +21973,7 @@
         <v>1.873908720049794</v>
       </c>
       <c r="D412" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E412">
         <v>2.766821852034614</v>
@@ -22014,7 +22023,7 @@
         <v>2.830412961668017</v>
       </c>
       <c r="D413" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E413">
         <v>2.221708855759843</v>
@@ -22064,7 +22073,7 @@
         <v>1.937685341557977</v>
       </c>
       <c r="D414" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E414">
         <v>2.485222886188172</v>
@@ -22100,7 +22109,7 @@
         <v>1</v>
       </c>
       <c r="P414" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="415" spans="1:16">
@@ -22150,7 +22159,7 @@
         <v>1</v>
       </c>
       <c r="P415" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="416" spans="1:16">
@@ -22164,7 +22173,7 @@
         <v>1.774494638455131</v>
       </c>
       <c r="D416" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E416">
         <v>2.625865317623621</v>
@@ -22200,7 +22209,7 @@
         <v>1</v>
       </c>
       <c r="P416" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="417" spans="1:16">
@@ -22214,7 +22223,7 @@
         <v>1.943959477391676</v>
       </c>
       <c r="D417" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E417">
         <v>2.625865317623621</v>
@@ -22250,7 +22259,7 @@
         <v>1</v>
       </c>
       <c r="P417" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="418" spans="1:16">
@@ -22264,7 +22273,7 @@
         <v>1.883381408179421</v>
       </c>
       <c r="D418" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E418">
         <v>2.776486294984675</v>
@@ -22300,7 +22309,7 @@
         <v>1</v>
       </c>
       <c r="P418" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="419" spans="1:16">
@@ -22314,7 +22323,7 @@
         <v>2.839655544013116</v>
       </c>
       <c r="D419" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E419">
         <v>2.231475567947474</v>
@@ -22350,7 +22359,7 @@
         <v>1</v>
       </c>
       <c r="P419" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="420" spans="1:16">
@@ -22364,7 +22373,7 @@
         <v>1.950149148490695</v>
       </c>
       <c r="D420" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E420">
         <v>2.49724716340538</v>
@@ -22400,7 +22409,7 @@
         <v>1</v>
       </c>
       <c r="P420" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="421" spans="1:16">
@@ -22450,7 +22459,7 @@
         <v>1</v>
       </c>
       <c r="P421" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="422" spans="1:16">
@@ -22464,7 +22473,7 @@
         <v>1.787727622389998</v>
       </c>
       <c r="D422" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E422">
         <v>2.637685527472915</v>
@@ -22500,7 +22509,7 @@
         <v>1</v>
       </c>
       <c r="P422" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="423" spans="1:16">
@@ -22514,7 +22523,7 @@
         <v>1.956140729507283</v>
       </c>
       <c r="D423" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E423">
         <v>2.637685527472915</v>
@@ -22550,7 +22559,7 @@
         <v>1</v>
       </c>
       <c r="P423" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="424" spans="1:16">
@@ -22564,7 +22573,7 @@
         <v>1.895013248150637</v>
       </c>
       <c r="D424" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E424">
         <v>2.788353597303487</v>
@@ -22600,7 +22609,7 @@
         <v>1</v>
       </c>
       <c r="P424" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="425" spans="1:16">
@@ -22614,7 +22623,7 @@
         <v>2.85100482916722</v>
       </c>
       <c r="D425" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E425">
         <v>2.243468450185002</v>
@@ -22650,7 +22659,7 @@
         <v>1</v>
       </c>
       <c r="P425" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="426" spans="1:16">
@@ -22714,7 +22723,7 @@
         <v>1.796280604882195</v>
       </c>
       <c r="D427" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E427">
         <v>2.645325380161676</v>
@@ -22764,7 +22773,7 @@
         <v>1.964013937590256</v>
       </c>
       <c r="D428" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E428">
         <v>2.645325380161676</v>
@@ -22814,7 +22823,7 @@
         <v>1.902531350198938</v>
       </c>
       <c r="D429" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E429">
         <v>2.796023887652364</v>
@@ -22864,7 +22873,7 @@
         <v>2.858340305254835</v>
       </c>
       <c r="D430" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E430">
         <v>2.251219907627515</v>
@@ -22950,7 +22959,7 @@
         <v>1</v>
       </c>
       <c r="P431" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="432" spans="1:16">
@@ -22964,7 +22973,7 @@
         <v>1.81059278070445</v>
       </c>
       <c r="D432" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E432">
         <v>2.658109565682619</v>
@@ -23000,7 +23009,7 @@
         <v>1</v>
       </c>
       <c r="P432" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="433" spans="1:16">
@@ -23014,7 +23023,7 @@
         <v>1.977188609521534</v>
       </c>
       <c r="D433" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E433">
         <v>2.658109565682619</v>
@@ -23050,7 +23059,7 @@
         <v>1</v>
       </c>
       <c r="P433" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="434" spans="1:16">
@@ -23064,7 +23073,7 @@
         <v>1.915111803679711</v>
       </c>
       <c r="D434" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E434">
         <v>2.808859006183351</v>
@@ -23100,7 +23109,7 @@
         <v>1</v>
       </c>
       <c r="P434" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="435" spans="1:16">
@@ -23114,7 +23123,7 @@
         <v>2.870615160675342</v>
       </c>
       <c r="D435" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E435">
         <v>2.26419084751862</v>
@@ -23150,7 +23159,7 @@
         <v>1</v>
       </c>
       <c r="P435" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="436" spans="1:16">
@@ -23200,7 +23209,7 @@
         <v>1</v>
       </c>
       <c r="P436" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="437" spans="1:16">
@@ -23214,7 +23223,7 @@
         <v>1.82632056259726</v>
       </c>
       <c r="D437" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E437">
         <v>2.672158224953424</v>
@@ -23250,7 +23259,7 @@
         <v>1</v>
       </c>
       <c r="P437" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="438" spans="1:16">
@@ -23264,7 +23273,7 @@
         <v>1.991666377906849</v>
       </c>
       <c r="D438" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E438">
         <v>2.672158224953424</v>
@@ -23300,7 +23309,7 @@
         <v>1</v>
       </c>
       <c r="P438" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="439" spans="1:16">
@@ -23314,7 +23323,7 @@
         <v>1.928936579934245</v>
       </c>
       <c r="D439" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E439">
         <v>2.822963636208222</v>
@@ -23350,7 +23359,7 @@
         <v>1</v>
       </c>
       <c r="P439" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="440" spans="1:16">
@@ -23364,7 +23373,7 @@
         <v>2.884104112405478</v>
       </c>
       <c r="D440" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E440">
         <v>2.278444732887671</v>
@@ -23400,7 +23409,7 @@
         <v>1</v>
       </c>
       <c r="P440" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="441" spans="1:16">
@@ -23414,7 +23423,7 @@
         <v>1.850091985515281</v>
       </c>
       <c r="D441" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E441">
         <v>2.693391773538558</v>
@@ -23464,7 +23473,7 @@
         <v>2.013548494377055</v>
       </c>
       <c r="D442" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E442">
         <v>2.693391773538558</v>
@@ -23514,7 +23523,7 @@
         <v>1.949831745274995</v>
       </c>
       <c r="D443" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E443">
         <v>2.844281780604454</v>
@@ -23564,7 +23573,7 @@
         <v>2.90449170287965</v>
       </c>
       <c r="D444" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E444">
         <v>2.29998846611349</v>
@@ -23614,7 +23623,7 @@
         <v>1.883787347386825</v>
       </c>
       <c r="D445" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E445">
         <v>2.723489765815277</v>
@@ -23650,7 +23659,7 @@
         <v>1</v>
       </c>
       <c r="P445" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="446" spans="1:16">
@@ -23664,7 +23673,7 @@
         <v>2.044565814439117</v>
       </c>
       <c r="D446" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E446">
         <v>2.723489765815277</v>
@@ -23700,7 +23709,7 @@
         <v>1</v>
       </c>
       <c r="P446" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="447" spans="1:16">
@@ -23714,7 +23723,7 @@
         <v>2.74752944335815</v>
       </c>
       <c r="D447" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E447">
         <v>2.354565814439116</v>
@@ -23750,7 +23759,7 @@
         <v>1</v>
       </c>
       <c r="P447" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="448" spans="1:16">
@@ -23764,7 +23773,7 @@
         <v>1.979450088272404</v>
       </c>
       <c r="D448" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E448">
         <v>2.874499685200998</v>
@@ -23800,7 +23809,7 @@
         <v>1</v>
       </c>
       <c r="P448" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="449" spans="1:16">
@@ -23814,7 +23823,7 @@
         <v>2.933390571958093</v>
       </c>
       <c r="D449" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E449">
         <v>2.330526136896243</v>
@@ -23850,7 +23859,7 @@
         <v>1</v>
       </c>
       <c r="P449" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="450" spans="1:16">
@@ -23900,7 +23909,7 @@
         <v>1</v>
       </c>
       <c r="P450" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="451" spans="1:16">
@@ -23914,7 +23923,7 @@
         <v>1.920897553279229</v>
       </c>
       <c r="D451" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E451">
         <v>2.756638028018099</v>
@@ -23950,7 +23959,7 @@
         <v>1</v>
       </c>
       <c r="P451" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="452" spans="1:16">
@@ -23964,7 +23973,7 @@
         <v>2.078726573362612</v>
       </c>
       <c r="D452" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E452">
         <v>2.756638028018099</v>
@@ -24000,7 +24009,7 @@
         <v>1</v>
       </c>
       <c r="P452" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="453" spans="1:16">
@@ -24014,7 +24023,7 @@
         <v>2.012070091316616</v>
       </c>
       <c r="D453" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E453">
         <v>2.907780012193474</v>
@@ -24050,7 +24059,7 @@
         <v>1</v>
       </c>
       <c r="P453" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="454" spans="1:16">
@@ -24064,7 +24073,7 @@
         <v>2.965218186264387</v>
       </c>
       <c r="D454" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E454">
         <v>2.364158636661127</v>
@@ -24100,7 +24109,7 @@
         <v>1</v>
       </c>
       <c r="P454" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="455" spans="1:16">
@@ -24114,7 +24123,7 @@
         <v>1.971362962924253</v>
       </c>
       <c r="D455" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E455">
         <v>2.801715671508852</v>
@@ -24164,7 +24173,7 @@
         <v>2.125181090426125</v>
       </c>
       <c r="D456" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E456">
         <v>2.801715671508852</v>
@@ -24214,7 +24223,7 @@
         <v>2.056429365986798</v>
       </c>
       <c r="D457" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E457">
         <v>2.95303724788937</v>
@@ -24264,7 +24273,7 @@
         <v>3.008499907703719</v>
       </c>
       <c r="D458" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E458">
         <v>2.409894784904068</v>
@@ -24314,7 +24323,7 @@
         <v>2.008171638992437</v>
       </c>
       <c r="D459" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E459">
         <v>2.834594595683633</v>
@@ -24350,7 +24359,7 @@
         <v>1</v>
       </c>
       <c r="P459" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="460" spans="1:16">
@@ -24364,7 +24373,7 @@
         <v>2.159064284529219</v>
       </c>
       <c r="D460" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E460">
         <v>2.834594595683633</v>
@@ -24400,7 +24409,7 @@
         <v>1</v>
       </c>
       <c r="P460" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="461" spans="1:16">
@@ -24414,7 +24423,7 @@
         <v>2.088784323242461</v>
       </c>
       <c r="D461" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E461">
         <v>2.986047163793931</v>
@@ -24450,7 +24459,7 @@
         <v>1</v>
       </c>
       <c r="P461" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="462" spans="1:16">
@@ -24464,7 +24473,7 @@
         <v>3.040068914580697</v>
       </c>
       <c r="D462" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E462">
         <v>2.443254012088044</v>
@@ -24500,7 +24509,7 @@
         <v>1</v>
       </c>
       <c r="P462" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="463" spans="1:16">
@@ -24514,7 +24523,7 @@
         <v>2.067700645146257</v>
       </c>
       <c r="D463" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E463">
         <v>2.887768191927794</v>
@@ -24564,7 +24573,7 @@
         <v>2.213862041083626</v>
       </c>
       <c r="D464" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E464">
         <v>2.887768191927794</v>
@@ -24614,7 +24623,7 @@
         <v>2.914425852356924</v>
       </c>
       <c r="D465" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E465">
         <v>2.523862041083625</v>
@@ -24664,7 +24673,7 @@
         <v>2.141110531498665</v>
       </c>
       <c r="D466" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E466">
         <v>3.039432607035081</v>
@@ -24714,7 +24723,7 @@
         <v>3.091124040854972</v>
       </c>
       <c r="D467" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E467">
         <v>2.497204380654495</v>
@@ -24764,7 +24773,7 @@
         <v>2.102053433035913</v>
       </c>
       <c r="D468" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E468">
         <v>2.918453422391508</v>
@@ -24800,7 +24809,7 @@
         <v>1</v>
       </c>
       <c r="P468" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="469" spans="1:16">
@@ -24814,7 +24823,7 @@
         <v>2.245484536222857</v>
       </c>
       <c r="D469" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E469">
         <v>2.918453422391508</v>
@@ -24850,7 +24859,7 @@
         <v>1</v>
       </c>
       <c r="P469" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="470" spans="1:16">
@@ -24864,7 +24873,7 @@
         <v>2.945600090477427</v>
       </c>
       <c r="D470" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E470">
         <v>2.555484536222856</v>
@@ -24900,7 +24909,7 @@
         <v>1</v>
       </c>
       <c r="P470" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="471" spans="1:16">
@@ -24914,7 +24923,7 @@
         <v>2.171306754305586</v>
       </c>
       <c r="D471" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E471">
         <v>3.070240089412991</v>
@@ -24950,7 +24959,7 @@
         <v>1</v>
       </c>
       <c r="P471" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="472" spans="1:16">
@@ -24964,7 +24973,7 @@
         <v>3.120586752176706</v>
       </c>
       <c r="D472" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E472">
         <v>2.528337868136934</v>
@@ -25000,7 +25009,7 @@
         <v>1</v>
       </c>
       <c r="P472" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="473" spans="1:16">
@@ -25014,7 +25023,7 @@
         <v>2.150109762840597</v>
       </c>
       <c r="D473" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E473">
         <v>2.961379183177897</v>
@@ -25050,7 +25059,7 @@
         <v>1</v>
       </c>
       <c r="P473" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="474" spans="1:16">
@@ -25064,7 +25073,7 @@
         <v>2.289721442425034</v>
       </c>
       <c r="D474" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E474">
         <v>2.961379183177897</v>
@@ -25100,7 +25109,7 @@
         <v>1</v>
       </c>
       <c r="P474" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="475" spans="1:16">
@@ -25114,7 +25123,7 @@
         <v>2.989209927132926</v>
       </c>
       <c r="D475" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E475">
         <v>2.599721442425032</v>
@@ -25150,7 +25159,7 @@
         <v>1</v>
       </c>
       <c r="P475" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="476" spans="1:16">
@@ -25164,7 +25173,7 @@
         <v>2.213548439222873</v>
       </c>
       <c r="D476" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E476">
         <v>3.113336869166659</v>
@@ -25200,7 +25209,7 @@
         <v>1</v>
       </c>
       <c r="P476" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="477" spans="1:16">
@@ -25214,7 +25223,7 @@
         <v>3.161802323290331</v>
       </c>
       <c r="D477" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E477">
         <v>2.571890698470007</v>
@@ -25250,7 +25259,7 @@
         <v>1</v>
       </c>
       <c r="P477" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="478" spans="1:16">
@@ -25264,7 +25273,7 @@
         <v>2.189716387261424</v>
       </c>
       <c r="D478" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E478">
         <v>2.99675734235807</v>
@@ -25314,7 +25323,7 @@
         <v>2.326180209388927</v>
       </c>
       <c r="D479" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E479">
         <v>2.99675734235807</v>
@@ -25364,7 +25373,7 @@
         <v>2.248362803037622</v>
       </c>
       <c r="D480" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E480">
         <v>3.148855977188184</v>
@@ -25414,7 +25423,7 @@
         <v>3.19577099405695</v>
       </c>
       <c r="D481" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E481">
         <v>2.607785670068477</v>
@@ -25464,7 +25473,7 @@
         <v>2.215826782258592</v>
       </c>
       <c r="D482" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E482">
         <v>3.020080150700736</v>
@@ -25500,7 +25509,7 @@
         <v>1</v>
       </c>
       <c r="P482" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="483" spans="1:16">
@@ -25514,7 +25523,7 @@
         <v>2.350215400987747</v>
       </c>
       <c r="D483" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E483">
         <v>3.020080150700736</v>
@@ -25550,7 +25559,7 @@
         <v>1</v>
       </c>
       <c r="P483" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="484" spans="1:16">
@@ -25564,7 +25573,7 @@
         <v>2.271313933159689</v>
       </c>
       <c r="D484" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E484">
         <v>3.172271705086001</v>
@@ -25600,7 +25609,7 @@
         <v>1</v>
       </c>
       <c r="P484" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="485" spans="1:16">
@@ -25614,7 +25623,7 @@
         <v>3.218164606848116</v>
       </c>
       <c r="D485" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E485">
         <v>2.631449183446694</v>
@@ -25650,7 +25659,7 @@
         <v>1</v>
       </c>
       <c r="P485" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="486" spans="1:16">
@@ -25700,7 +25709,7 @@
         <v>1</v>
       </c>
       <c r="P486" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="487" spans="1:16">
@@ -25714,7 +25723,7 @@
         <v>2.227304742320833</v>
       </c>
       <c r="D487" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E487">
         <v>3.030332705774125</v>
@@ -25750,7 +25759,7 @@
         <v>1</v>
       </c>
       <c r="P487" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="488" spans="1:16">
@@ -25764,7 +25773,7 @@
         <v>2.360781115113841</v>
       </c>
       <c r="D488" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E488">
         <v>3.030332705774125</v>
@@ -25800,7 +25809,7 @@
         <v>1</v>
       </c>
       <c r="P488" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="489" spans="1:16">
@@ -25814,7 +25823,7 @@
         <v>2.28140310090123</v>
       </c>
       <c r="D489" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E489">
         <v>3.182565106992353</v>
@@ -25850,7 +25859,7 @@
         <v>1</v>
       </c>
       <c r="P489" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="490" spans="1:16">
@@ -25864,7 +25873,7 @@
         <v>3.228008693591889</v>
       </c>
       <c r="D490" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E490">
         <v>2.641851510240944</v>
@@ -25900,7 +25909,7 @@
         <v>1</v>
       </c>
       <c r="P490" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="491" spans="1:16">
@@ -25914,7 +25923,7 @@
         <v>2.326764722017106</v>
       </c>
       <c r="D491" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E491">
         <v>2.338905512271317</v>
@@ -25950,7 +25959,7 @@
         <v>1</v>
       </c>
       <c r="P491" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="492" spans="1:16">
@@ -25964,7 +25973,7 @@
         <v>2.245345573811253</v>
       </c>
       <c r="D492" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E492">
         <v>3.046447469845635</v>
@@ -26000,7 +26009,7 @@
         <v>1</v>
       </c>
       <c r="P492" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="493" spans="1:16">
@@ -26014,7 +26023,7 @@
         <v>2.377388096414631</v>
       </c>
       <c r="D493" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E493">
         <v>3.046447469845635</v>
@@ -26050,7 +26059,7 @@
         <v>1</v>
       </c>
       <c r="P493" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="494" spans="1:16">
@@ -26064,7 +26073,7 @@
         <v>2.297261055983554</v>
       </c>
       <c r="D494" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E494">
         <v>3.198744073311161</v>
@@ -26100,7 +26109,7 @@
         <v>1</v>
       </c>
       <c r="P494" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="495" spans="1:16">
@@ -26114,7 +26123,7 @@
         <v>3.243481435190432</v>
       </c>
       <c r="D495" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E495">
         <v>2.658201682552544</v>
@@ -26150,7 +26159,7 @@
         <v>1</v>
       </c>
       <c r="P495" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="496" spans="1:16">
@@ -26200,7 +26209,7 @@
         <v>1</v>
       </c>
       <c r="P496" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="497" spans="1:16">
@@ -26214,7 +26223,7 @@
         <v>2.301170929293026</v>
       </c>
       <c r="D497" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E497">
         <v>3.202733093853617</v>
@@ -26264,7 +26273,7 @@
         <v>3.247296331820319</v>
       </c>
       <c r="D498" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E498">
         <v>2.662232914952593</v>
@@ -26364,7 +26373,7 @@
         <v>2.309276220482282</v>
       </c>
       <c r="D500" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E500">
         <v>3.211002459763304</v>
@@ -26400,7 +26409,7 @@
         <v>1</v>
       </c>
       <c r="P500" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="501" spans="1:16">
@@ -26414,7 +26423,7 @@
         <v>3.25520473334506</v>
       </c>
       <c r="D501" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E501">
         <v>2.670589787379843</v>
@@ -26450,7 +26459,7 @@
         <v>1</v>
       </c>
       <c r="P501" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="502" spans="1:16">
@@ -26464,7 +26473,7 @@
         <v>2.35659384998981</v>
       </c>
       <c r="D502" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E502">
         <v>2.377701080695644</v>
@@ -26500,7 +26509,7 @@
         <v>1</v>
       </c>
       <c r="P502" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="503" spans="1:16">
@@ -26514,7 +26523,7 @@
         <v>2.318802840630408</v>
       </c>
       <c r="D503" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E503">
         <v>3.220721926473129</v>
@@ -26564,7 +26573,7 @@
         <v>3.264499937619139</v>
       </c>
       <c r="D504" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E504">
         <v>2.680412105589244</v>
@@ -26714,7 +26723,7 @@
         <v>2.968469110715926</v>
       </c>
       <c r="D507" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E507">
         <v>3.65607053595874</v>
@@ -26750,7 +26759,7 @@
         <v>1</v>
       </c>
       <c r="P507" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="508" spans="1:16">
@@ -26764,7 +26773,7 @@
         <v>3.056098677724048</v>
       </c>
       <c r="D508" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E508">
         <v>3.65607053595874</v>
@@ -26800,7 +26809,7 @@
         <v>1</v>
       </c>
       <c r="P508" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="509" spans="1:16">
@@ -26814,7 +26823,7 @@
         <v>3.085552267926261</v>
       </c>
       <c r="D509" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E509">
         <v>3.65607053595874</v>
@@ -26850,7 +26859,7 @@
         <v>1</v>
       </c>
       <c r="P509" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="510" spans="1:16">
@@ -26864,7 +26873,7 @@
         <v>3.115403587495276</v>
       </c>
       <c r="D510" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E510">
         <v>4.899694426383849</v>
@@ -26900,7 +26909,7 @@
         <v>1</v>
       </c>
       <c r="P510" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="511" spans="1:16">
@@ -26914,7 +26923,7 @@
         <v>2.857657467623699</v>
       </c>
       <c r="D511" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E511">
         <v>4.899694426383849</v>
@@ -26950,7 +26959,7 @@
         <v>1</v>
       </c>
       <c r="P511" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="512" spans="1:16">
@@ -26964,7 +26973,7 @@
         <v>4.634833021734408</v>
       </c>
       <c r="D512" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E512">
         <v>3.48240231940969</v>
@@ -27000,7 +27009,7 @@
         <v>1</v>
       </c>
       <c r="P512" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="513" spans="1:16">
@@ -27014,7 +27023,7 @@
         <v>3.013404560606677</v>
       </c>
       <c r="D513" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E513">
         <v>3.707166946903694</v>
@@ -27050,7 +27059,7 @@
         <v>1</v>
       </c>
       <c r="P513" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="514" spans="1:16">
@@ -27064,7 +27073,7 @@
         <v>3.101938488870459</v>
       </c>
       <c r="D514" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E514">
         <v>3.707166946903694</v>
@@ -27100,7 +27109,7 @@
         <v>1</v>
       </c>
       <c r="P514" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="515" spans="1:16">
@@ -27114,7 +27123,7 @@
         <v>3.133031233848563</v>
       </c>
       <c r="D515" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E515">
         <v>3.707166946903694</v>
@@ -27150,7 +27159,7 @@
         <v>1</v>
       </c>
       <c r="P515" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="516" spans="1:16">
@@ -27164,7 +27173,7 @@
         <v>2.923647577997855</v>
       </c>
       <c r="D516" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E516">
         <v>4.966814988327585</v>
@@ -27200,7 +27209,7 @@
         <v>1</v>
       </c>
       <c r="P516" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="517" spans="1:16">
@@ -27214,7 +27223,7 @@
         <v>4.706192777064061</v>
       </c>
       <c r="D517" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E517">
         <v>3.555881671432303</v>
@@ -27250,7 +27259,7 @@
         <v>1</v>
       </c>
       <c r="P517" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="518" spans="1:16">
@@ -27264,7 +27273,7 @@
         <v>3.058294813446018</v>
       </c>
       <c r="D518" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E518">
         <v>3.758211963968808</v>
@@ -27300,7 +27309,7 @@
         <v>1</v>
       </c>
       <c r="P518" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="519" spans="1:16">
@@ -27314,7 +27323,7 @@
         <v>3.147732193339273</v>
       </c>
       <c r="D519" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E519">
         <v>3.758211963968808</v>
@@ -27350,7 +27359,7 @@
         <v>1</v>
       </c>
       <c r="P519" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="520" spans="1:16">
@@ -27364,7 +27373,7 @@
         <v>3.18046244439579</v>
       </c>
       <c r="D520" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E520">
         <v>3.758211963968808</v>
@@ -27400,7 +27409,7 @@
         <v>1</v>
       </c>
       <c r="P520" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="521" spans="1:16">
@@ -27414,7 +27423,7 @@
         <v>3.225680173488445</v>
       </c>
       <c r="D521" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E521">
         <v>5.033868038952384</v>
@@ -27450,7 +27459,7 @@
         <v>1</v>
       </c>
       <c r="P521" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="522" spans="1:16">
@@ -27464,7 +27473,7 @@
         <v>2.989571314085818</v>
       </c>
       <c r="D522" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E522">
         <v>5.033868038952384</v>
@@ -27500,7 +27509,7 @@
         <v>1</v>
       </c>
       <c r="P522" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="523" spans="1:16">
@@ -27514,7 +27523,7 @@
         <v>4.77748075720201</v>
       </c>
       <c r="D523" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E523">
         <v>3.629287116326825</v>
@@ -27550,7 +27559,7 @@
         <v>1</v>
       </c>
       <c r="P523" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="524" spans="1:16">
@@ -27564,7 +27573,7 @@
         <v>3.100990526217007</v>
       </c>
       <c r="D524" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E524">
         <v>5.097643081613452</v>
@@ -27600,7 +27609,7 @@
         <v>1</v>
       </c>
       <c r="P524" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="525" spans="1:16">
@@ -27614,7 +27623,7 @@
         <v>3.19128719089559</v>
       </c>
       <c r="D525" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E525">
         <v>5.097643081613452</v>
@@ -27650,7 +27659,7 @@
         <v>1</v>
       </c>
       <c r="P525" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="526" spans="1:16">
@@ -27664,7 +27673,7 @@
         <v>3.225574895625517</v>
       </c>
       <c r="D526" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E526">
         <v>5.097643081613452</v>
@@ -27700,7 +27709,7 @@
         <v>1</v>
       </c>
       <c r="P526" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="527" spans="1:16">
@@ -27714,7 +27723,7 @@
         <v>3.205781960817575</v>
       </c>
       <c r="D527" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E527">
         <v>5.097643081613452</v>
@@ -27750,7 +27759,7 @@
         <v>1</v>
       </c>
       <c r="P527" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="528" spans="1:16">
@@ -27764,7 +27773,7 @@
         <v>3.27809654539346</v>
       </c>
       <c r="D528" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E528">
         <v>5.097643081613452</v>
@@ -27800,7 +27809,7 @@
         <v>1</v>
       </c>
       <c r="P528" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="529" spans="1:16">
@@ -27814,7 +27823,7 @@
         <v>3.052272250765228</v>
       </c>
       <c r="D529" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E529">
         <v>5.097643081613452</v>
@@ -27850,7 +27859,7 @@
         <v>1</v>
       </c>
       <c r="P529" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="530" spans="1:16">
@@ -27864,7 +27873,7 @@
         <v>4.845283697294303</v>
       </c>
       <c r="D530" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E530">
         <v>3.699104005134728</v>
@@ -27900,7 +27909,7 @@
         <v>1</v>
       </c>
       <c r="P530" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="531" spans="1:16">
@@ -27914,7 +27923,7 @@
         <v>3.135431759672713</v>
       </c>
       <c r="D531" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E531">
         <v>5.149088320265843</v>
@@ -27950,7 +27959,7 @@
         <v>1</v>
       </c>
       <c r="P531" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="532" spans="1:16">
@@ -27964,7 +27973,7 @@
         <v>3.226421581251035</v>
       </c>
       <c r="D532" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E532">
         <v>5.149088320265843</v>
@@ -28000,7 +28009,7 @@
         <v>1</v>
       </c>
       <c r="P532" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="533" spans="1:16">
@@ -28014,7 +28023,7 @@
         <v>3.261965632861735</v>
       </c>
       <c r="D533" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E533">
         <v>5.149088320265843</v>
@@ -28050,7 +28059,7 @@
         <v>1</v>
       </c>
       <c r="P533" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="534" spans="1:16">
@@ -28064,7 +28073,7 @@
         <v>3.248497754763896</v>
       </c>
       <c r="D534" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E534">
         <v>5.149088320265843</v>
@@ -28100,7 +28109,7 @@
         <v>1</v>
       </c>
       <c r="P534" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="535" spans="1:16">
@@ -28114,7 +28123,7 @@
         <v>3.320379116277444</v>
       </c>
       <c r="D535" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E535">
         <v>5.149088320265843</v>
@@ -28150,7 +28159,7 @@
         <v>1</v>
       </c>
       <c r="P535" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="536" spans="1:16">
@@ -28164,7 +28173,7 @@
         <v>3.102851043292947</v>
       </c>
       <c r="D536" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E536">
         <v>5.149088320265843</v>
@@ -28200,7 +28209,7 @@
         <v>1</v>
       </c>
       <c r="P536" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="537" spans="1:16">
@@ -28214,7 +28223,7 @@
         <v>4.899978108914215</v>
       </c>
       <c r="D537" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E537">
         <v>3.755423003238402</v>
@@ -28250,7 +28259,7 @@
         <v>1</v>
       </c>
       <c r="P537" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="538" spans="1:16">
@@ -28264,7 +28273,7 @@
         <v>3.340758667101504</v>
       </c>
       <c r="D538" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E538">
         <v>5.455787317211367</v>
@@ -28300,7 +28309,7 @@
         <v>1</v>
       </c>
       <c r="P538" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="539" spans="1:16">
@@ -28314,7 +28323,7 @@
         <v>3.596337846972439</v>
       </c>
       <c r="D539" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E539">
         <v>5.455787317211367</v>
@@ -28350,7 +28359,7 @@
         <v>1</v>
       </c>
       <c r="P539" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="540" spans="1:16">
@@ -28364,7 +28373,7 @@
         <v>3.478914818069512</v>
       </c>
       <c r="D540" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E540">
         <v>5.455787317211367</v>
@@ -28400,7 +28409,7 @@
         <v>1</v>
       </c>
       <c r="P540" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="541" spans="1:16">
@@ -28414,7 +28423,7 @@
         <v>3.503154774543503</v>
       </c>
       <c r="D541" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E541">
         <v>5.455787317211367</v>
@@ -28450,7 +28459,7 @@
         <v>1</v>
       </c>
       <c r="P541" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="542" spans="1:16">
@@ -28464,7 +28473,7 @@
         <v>3.572453407661722</v>
       </c>
       <c r="D542" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E542">
         <v>5.455787317211367</v>
@@ -28500,7 +28509,7 @@
         <v>1</v>
       </c>
       <c r="P542" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="543" spans="1:16">
@@ -28514,7 +28523,7 @@
         <v>3.404384583447808</v>
       </c>
       <c r="D543" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E543">
         <v>5.455787317211367</v>
@@ -28550,7 +28559,7 @@
         <v>1</v>
       </c>
       <c r="P543" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="544" spans="1:16">
@@ -28564,7 +28573,7 @@
         <v>5.25250104043668</v>
       </c>
       <c r="D544" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E544">
         <v>5.56320240731846</v>
@@ -28600,7 +28609,7 @@
         <v>1</v>
       </c>
       <c r="P544" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="545" spans="1:16">
@@ -28614,7 +28623,7 @@
         <v>3.408744253943432</v>
       </c>
       <c r="D545" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E545">
         <v>5.557338115167074</v>
@@ -28650,7 +28659,7 @@
         <v>1</v>
       </c>
       <c r="P545" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="546" spans="1:16">
@@ -28664,7 +28673,7 @@
         <v>3.550748645676077</v>
       </c>
       <c r="D546" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E546">
         <v>5.557338115167074</v>
@@ -28700,7 +28709,7 @@
         <v>1</v>
       </c>
       <c r="P546" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="547" spans="1:16">
@@ -28714,7 +28723,7 @@
         <v>3.587474005519777</v>
       </c>
       <c r="D547" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E547">
         <v>5.557338115167074</v>
@@ -28750,7 +28759,7 @@
         <v>1</v>
       </c>
       <c r="P547" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="548" spans="1:16">
@@ -28764,7 +28773,7 @@
         <v>3.655917474023632</v>
       </c>
       <c r="D548" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E548">
         <v>5.557338115167074</v>
@@ -28800,7 +28809,7 @@
         <v>1</v>
       </c>
       <c r="P548" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="549" spans="1:16">
@@ -28814,7 +28823,7 @@
         <v>3.504225052174785</v>
       </c>
       <c r="D549" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E549">
         <v>5.557338115167074</v>
@@ -28850,7 +28859,7 @@
         <v>1</v>
       </c>
       <c r="P549" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="550" spans="1:16">
@@ -28864,7 +28873,7 @@
         <v>5.346996730323884</v>
       </c>
       <c r="D550" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E550">
         <v>5.864438002961421</v>
@@ -28900,7 +28909,7 @@
         <v>1</v>
       </c>
       <c r="P550" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="551" spans="1:16">
@@ -28914,7 +28923,7 @@
         <v>5.267444590560391</v>
       </c>
       <c r="D551" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E551">
         <v>5.864438002961421</v>
@@ -28950,7 +28959,7 @@
         <v>1</v>
       </c>
       <c r="P551" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="552" spans="1:16">
@@ -28964,7 +28973,7 @@
         <v>3.796322429340982</v>
       </c>
       <c r="D552" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E552">
         <v>5.685955718590687</v>
@@ -29000,7 +29009,7 @@
         <v>1</v>
       </c>
       <c r="P552" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="553" spans="1:16">
@@ -29014,7 +29023,7 @@
         <v>3.641728676729411</v>
       </c>
       <c r="D553" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E553">
         <v>5.685955718590687</v>
@@ -29050,7 +29059,7 @@
         <v>1</v>
       </c>
       <c r="P553" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="554" spans="1:16">
@@ -29064,7 +29073,7 @@
         <v>3.69426723244667</v>
       </c>
       <c r="D554" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E554">
         <v>5.685955718590687</v>
@@ -29100,7 +29109,7 @@
         <v>1</v>
       </c>
       <c r="P554" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="555" spans="1:16">
@@ -29114,7 +29123,7 @@
         <v>3.761627605342749</v>
       </c>
       <c r="D555" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E555">
         <v>5.685955718590687</v>
@@ -29150,7 +29159,7 @@
         <v>1</v>
       </c>
       <c r="P555" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="556" spans="1:16">
@@ -29164,7 +29173,7 @@
         <v>3.630676464382844</v>
       </c>
       <c r="D556" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E556">
         <v>5.685955718590687</v>
@@ -29200,7 +29209,7 @@
         <v>1</v>
       </c>
       <c r="P556" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="557" spans="1:16">
@@ -29214,7 +29223,7 @@
         <v>5.466678794983334</v>
       </c>
       <c r="D557" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E557">
         <v>5.209318422087254</v>
@@ -29250,7 +29259,7 @@
         <v>1</v>
       </c>
       <c r="P557" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="558" spans="1:16">
@@ -29264,7 +29273,7 @@
         <v>5.390917489847062</v>
       </c>
       <c r="D558" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E558">
         <v>5.209318422087254</v>
@@ -29300,7 +29309,7 @@
         <v>1</v>
       </c>
       <c r="P558" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="559" spans="1:16">
@@ -29314,7 +29323,7 @@
         <v>4.159051079599863</v>
       </c>
       <c r="D559" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E559">
         <v>5.343391662540899</v>
@@ -29350,7 +29359,7 @@
         <v>1</v>
       </c>
       <c r="P559" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="560" spans="1:16">
@@ -29364,7 +29373,7 @@
         <v>4.237780255555339</v>
       </c>
       <c r="D560" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E560">
         <v>5.313343652467495</v>
@@ -29400,7 +29409,7 @@
         <v>1</v>
       </c>
       <c r="P560" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="561" spans="1:16">
@@ -29414,7 +29423,7 @@
         <v>4.283295642394084</v>
       </c>
       <c r="D561" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E561">
         <v>5.313343652467495</v>
@@ -29450,7 +29459,7 @@
         <v>1</v>
       </c>
       <c r="P561" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="562" spans="1:16">
@@ -29500,7 +29509,7 @@
         <v>1</v>
       </c>
       <c r="P562" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="563" spans="1:16">
@@ -29514,7 +29523,7 @@
         <v>4.047954928502808</v>
       </c>
       <c r="D563" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E563">
         <v>5.235960539108905</v>
@@ -29550,7 +29559,7 @@
         <v>1</v>
       </c>
       <c r="P563" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="564" spans="1:16">
@@ -29564,7 +29573,7 @@
         <v>4.137221058995326</v>
       </c>
       <c r="D564" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E564">
         <v>5.202705629828571</v>
@@ -29600,7 +29609,7 @@
         <v>1</v>
       </c>
       <c r="P564" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="565" spans="1:16">
@@ -29614,7 +29623,7 @@
         <v>4.169450720548237</v>
       </c>
       <c r="D565" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E565">
         <v>5.202705629828571</v>
@@ -29650,7 +29659,7 @@
         <v>1</v>
       </c>
       <c r="P565" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="566" spans="1:16">
@@ -29664,7 +29673,7 @@
         <v>6.314817655301979</v>
       </c>
       <c r="D566" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E566">
         <v>6.624319057953503</v>
@@ -29700,7 +29709,7 @@
         <v>1</v>
       </c>
       <c r="P566" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="567" spans="1:16">
@@ -29714,7 +29723,7 @@
         <v>4.059730080999771</v>
       </c>
       <c r="D567" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E567">
         <v>5.117447902330046</v>
@@ -29764,7 +29773,7 @@
         <v>4.081721754571493</v>
       </c>
       <c r="D568" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E568">
         <v>5.117447902330046</v>
@@ -29864,7 +29873,7 @@
         <v>4.030557457706422</v>
       </c>
       <c r="D570" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E570">
         <v>5.085351371462874</v>
@@ -29900,7 +29909,7 @@
         <v>1</v>
       </c>
       <c r="P570" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="571" spans="1:16">
@@ -29914,7 +29923,7 @@
         <v>4.048694889476288</v>
       </c>
       <c r="D571" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E571">
         <v>5.085351371462874</v>
@@ -29950,7 +29959,7 @@
         <v>1</v>
       </c>
       <c r="P571" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="572" spans="1:16">
@@ -30000,7 +30009,7 @@
         <v>1</v>
       </c>
       <c r="P572" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="573" spans="1:16">
@@ -30014,7 +30023,7 @@
         <v>3.737521317704196</v>
       </c>
       <c r="D573" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E573">
         <v>4.762944866631269</v>
@@ -30050,7 +30059,7 @@
         <v>1</v>
       </c>
       <c r="P573" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="574" spans="1:16">
@@ -30064,7 +30073,7 @@
         <v>3.716943268562606</v>
       </c>
       <c r="D574" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E574">
         <v>4.762944866631269</v>
@@ -30100,7 +30109,7 @@
         <v>1</v>
       </c>
       <c r="P574" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="575" spans="1:16">
@@ -30150,7 +30159,7 @@
         <v>1</v>
       </c>
       <c r="P575" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="576" spans="1:16">
@@ -30200,7 +30209,7 @@
         <v>1</v>
       </c>
       <c r="P576" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="577" spans="1:16">
@@ -30214,7 +30223,7 @@
         <v>3.710853293730853</v>
       </c>
       <c r="D577" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E577">
         <v>4.733603965539871</v>
@@ -30250,7 +30259,7 @@
         <v>1</v>
       </c>
       <c r="P577" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="578" spans="1:16">
@@ -30264,7 +30273,7 @@
         <v>3.686751906570006</v>
       </c>
       <c r="D578" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E578">
         <v>4.733603965539871</v>
@@ -30300,7 +30309,7 @@
         <v>1</v>
       </c>
       <c r="P578" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="579" spans="1:16">
@@ -30350,7 +30359,7 @@
         <v>1</v>
       </c>
       <c r="P579" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="580" spans="1:16">
@@ -30400,7 +30409,7 @@
         <v>1</v>
       </c>
       <c r="P580" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="581" spans="1:16">
@@ -30450,7 +30459,7 @@
         <v>1</v>
       </c>
       <c r="P581" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="582" spans="1:16">
@@ -30500,7 +30509,7 @@
         <v>1</v>
       </c>
       <c r="P582" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="583" spans="1:16">
@@ -30550,7 +30559,7 @@
         <v>1</v>
       </c>
       <c r="P583" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="584" spans="1:16">
@@ -30600,7 +30609,7 @@
         <v>1</v>
       </c>
       <c r="P584" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="585" spans="1:16">
@@ -30650,7 +30659,7 @@
         <v>1</v>
       </c>
       <c r="P585" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="586" spans="1:16">
@@ -30700,7 +30709,7 @@
         <v>1</v>
       </c>
       <c r="P586" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="587" spans="1:16">
@@ -30750,7 +30759,7 @@
         <v>1</v>
       </c>
       <c r="P587" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="588" spans="1:16">
@@ -30800,7 +30809,7 @@
         <v>1</v>
       </c>
       <c r="P588" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="589" spans="1:16">
@@ -30850,7 +30859,7 @@
         <v>1</v>
       </c>
       <c r="P589" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="590" spans="1:16">
@@ -30900,7 +30909,7 @@
         <v>1</v>
       </c>
       <c r="P590" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="591" spans="1:16">
@@ -31150,7 +31159,7 @@
         <v>1</v>
       </c>
       <c r="P595" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="596" spans="1:16">
@@ -31200,7 +31209,7 @@
         <v>1</v>
       </c>
       <c r="P596" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="597" spans="1:16">
@@ -31250,7 +31259,7 @@
         <v>1</v>
       </c>
       <c r="P597" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="598" spans="1:16">
@@ -31300,7 +31309,7 @@
         <v>1</v>
       </c>
       <c r="P598" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="599" spans="1:16">
@@ -31350,7 +31359,7 @@
         <v>1</v>
       </c>
       <c r="P599" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="600" spans="1:16">
@@ -31400,7 +31409,7 @@
         <v>1</v>
       </c>
       <c r="P600" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="601" spans="1:16">
@@ -31614,7 +31623,7 @@
         <v>6.312844467716282</v>
       </c>
       <c r="D605" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E605">
         <v>7.044140001633426</v>
@@ -31700,7 +31709,7 @@
         <v>1</v>
       </c>
       <c r="P606" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="607" spans="1:16">
@@ -31750,7 +31759,7 @@
         <v>1</v>
       </c>
       <c r="P607" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="608" spans="1:16">
@@ -31800,7 +31809,7 @@
         <v>1</v>
       </c>
       <c r="P608" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="609" spans="1:16">
@@ -31850,7 +31859,7 @@
         <v>1</v>
       </c>
       <c r="P609" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="610" spans="1:16">
@@ -31900,7 +31909,7 @@
         <v>1</v>
       </c>
       <c r="P610" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="611" spans="1:16">
@@ -31950,7 +31959,7 @@
         <v>1</v>
       </c>
       <c r="P611" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="612" spans="1:16">
@@ -32000,7 +32009,7 @@
         <v>1</v>
       </c>
       <c r="P612" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="613" spans="1:16">
@@ -32050,7 +32059,7 @@
         <v>1</v>
       </c>
       <c r="P613" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="614" spans="1:16">
@@ -32100,7 +32109,7 @@
         <v>1</v>
       </c>
       <c r="P614" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="615" spans="1:16">
@@ -32150,7 +32159,7 @@
         <v>1</v>
       </c>
       <c r="P615" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="616" spans="1:16">
@@ -32200,7 +32209,7 @@
         <v>1</v>
       </c>
       <c r="P616" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="617" spans="1:16">
@@ -32250,7 +32259,7 @@
         <v>1</v>
       </c>
       <c r="P617" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="618" spans="1:16">
@@ -32300,7 +32309,7 @@
         <v>1</v>
       </c>
       <c r="P618" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="619" spans="1:16">
@@ -32350,7 +32359,7 @@
         <v>1</v>
       </c>
       <c r="P619" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="620" spans="1:16">
@@ -32400,7 +32409,7 @@
         <v>1</v>
       </c>
       <c r="P620" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="621" spans="1:16">
@@ -32450,7 +32459,7 @@
         <v>1</v>
       </c>
       <c r="P621" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="622" spans="1:16">
@@ -32464,7 +32473,7 @@
         <v>6.52789956231641</v>
       </c>
       <c r="D622" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E622">
         <v>6.970266187949232</v>
@@ -32500,7 +32509,7 @@
         <v>1</v>
       </c>
       <c r="P622" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="623" spans="1:16">
@@ -32550,7 +32559,7 @@
         <v>1</v>
       </c>
       <c r="P623" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="624" spans="1:16">
@@ -32600,7 +32609,7 @@
         <v>1</v>
       </c>
       <c r="P624" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="625" spans="1:16">
@@ -32650,7 +32659,7 @@
         <v>1</v>
       </c>
       <c r="P625" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="626" spans="1:16">
@@ -32664,7 +32673,7 @@
         <v>2.603543847706</v>
       </c>
       <c r="D626" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E626">
         <v>4.770094008155837</v>
@@ -32700,7 +32709,7 @@
         <v>1</v>
       </c>
       <c r="P626" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="627" spans="1:16">
@@ -32750,7 +32759,7 @@
         <v>1</v>
       </c>
       <c r="P627" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="628" spans="1:16">
@@ -32800,7 +32809,7 @@
         <v>1</v>
       </c>
       <c r="P628" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="629" spans="1:16">
@@ -32850,7 +32859,7 @@
         <v>1</v>
       </c>
       <c r="P629" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="630" spans="1:16">
@@ -32900,7 +32909,7 @@
         <v>1</v>
       </c>
       <c r="P630" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="631" spans="1:16">
@@ -32950,7 +32959,7 @@
         <v>1</v>
       </c>
       <c r="P631" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="632" spans="1:16">
@@ -32964,7 +32973,7 @@
         <v>2.478182256708074</v>
       </c>
       <c r="D632" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E632">
         <v>4.645810796435313</v>
@@ -33000,7 +33009,7 @@
         <v>1</v>
       </c>
       <c r="P632" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="633" spans="1:16">
@@ -33050,7 +33059,7 @@
         <v>1</v>
       </c>
       <c r="P633" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="634" spans="1:16">
@@ -33100,7 +33109,7 @@
         <v>1</v>
       </c>
       <c r="P634" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="635" spans="1:16">
@@ -33150,7 +33159,7 @@
         <v>1</v>
       </c>
       <c r="P635" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="636" spans="1:16">
@@ -33200,7 +33209,7 @@
         <v>1</v>
       </c>
       <c r="P636" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="637" spans="1:16">
@@ -33214,7 +33223,7 @@
         <v>2.30694018299906</v>
       </c>
       <c r="D637" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E637">
         <v>4.476041772822722</v>
@@ -33250,7 +33259,7 @@
         <v>1</v>
       </c>
       <c r="P637" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="638" spans="1:16">
@@ -33264,7 +33273,7 @@
         <v>5.979313720333828</v>
       </c>
       <c r="D638" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E638">
         <v>6.921637837986275</v>
@@ -33300,7 +33309,7 @@
         <v>1</v>
       </c>
       <c r="P638" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="639" spans="1:16">
@@ -33314,7 +33323,7 @@
         <v>6.118014825265853</v>
       </c>
       <c r="D639" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E639">
         <v>6.921637837986275</v>
@@ -33350,7 +33359,7 @@
         <v>1</v>
       </c>
       <c r="P639" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="640" spans="1:16">
@@ -33364,7 +33373,7 @@
         <v>2.180042495856011</v>
       </c>
       <c r="D640" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E640">
         <v>4.350235678687355</v>
@@ -33400,7 +33409,7 @@
         <v>1</v>
       </c>
       <c r="P640" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="641" spans="1:16">
@@ -33450,7 +33459,7 @@
         <v>1</v>
       </c>
       <c r="P641" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="642" spans="1:16">
@@ -33500,7 +33509,7 @@
         <v>1</v>
       </c>
       <c r="P642" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="643" spans="1:16">
@@ -33550,7 +33559,7 @@
         <v>1</v>
       </c>
       <c r="P643" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="644" spans="1:16">
@@ -33564,7 +33573,7 @@
         <v>2.005501953213372</v>
       </c>
       <c r="D644" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E644">
         <v>4.177196560067447</v>
@@ -33600,7 +33609,7 @@
         <v>1</v>
       </c>
       <c r="P644" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="645" spans="1:16">
@@ -33614,7 +33623,7 @@
         <v>6.03048720269387</v>
       </c>
       <c r="D645" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E645">
         <v>7.646218976894719</v>
@@ -33650,7 +33659,7 @@
         <v>1</v>
       </c>
       <c r="P645" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="646" spans="1:16">
@@ -33664,7 +33673,7 @@
         <v>6.160487202693869</v>
       </c>
       <c r="D646" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E646">
         <v>7.646218976894719</v>
@@ -33700,7 +33709,7 @@
         <v>1</v>
       </c>
       <c r="P646" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="647" spans="1:16">
@@ -33764,7 +33773,7 @@
         <v>5.929250610805834</v>
       </c>
       <c r="D648" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E648">
         <v>6.44678700451809</v>
@@ -33814,7 +33823,7 @@
         <v>6.059250610805833</v>
       </c>
       <c r="D649" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E649">
         <v>6.44678700451809</v>
@@ -33900,7 +33909,7 @@
         <v>1</v>
       </c>
       <c r="P650" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="651" spans="1:16">
@@ -33914,7 +33923,7 @@
         <v>6.444007644774246</v>
       </c>
       <c r="D651" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E651">
         <v>5.9080963375586</v>
@@ -33950,7 +33959,7 @@
         <v>1</v>
       </c>
       <c r="P651" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="652" spans="1:16">
@@ -33964,7 +33973,7 @@
         <v>5.977845942063905</v>
       </c>
       <c r="D652" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E652">
         <v>5.9080963375586</v>
@@ -34000,7 +34009,7 @@
         <v>1</v>
       </c>
       <c r="P652" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="653" spans="1:16">
@@ -34064,7 +34073,7 @@
         <v>6.325113724849238</v>
       </c>
       <c r="D654" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E654">
         <v>5.966484401224733</v>
@@ -34114,7 +34123,7 @@
         <v>6.616965483162407</v>
       </c>
       <c r="D655" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E655">
         <v>5.966484401224733</v>
@@ -34350,7 +34359,7 @@
         <v>1</v>
       </c>
       <c r="P659" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="660" spans="1:16">
@@ -34364,7 +34373,7 @@
         <v>6.182411935806901</v>
       </c>
       <c r="D660" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="E660">
         <v>5.820555041914538</v>
@@ -34400,7 +34409,7 @@
         <v>1</v>
       </c>
       <c r="P660" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="661" spans="1:16">
@@ -34414,7 +34423,7 @@
         <v>6.479370608860847</v>
       </c>
       <c r="D661" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="E661">
         <v>5.820555041914538</v>
@@ -34450,7 +34459,7 @@
         <v>1</v>
       </c>
       <c r="P661" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="662" spans="1:16">
@@ -34464,7 +34473,7 @@
         <v>6.247760471854665</v>
       </c>
       <c r="D662" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="E662">
         <v>5.820555041914538</v>
@@ -34500,7 +34509,7 @@
         <v>1</v>
       </c>
       <c r="P662" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="663" spans="1:16">
@@ -34614,7 +34623,7 @@
         <v>6.052746661470383</v>
       </c>
       <c r="D665" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E665">
         <v>5.747828147206722</v>
@@ -34664,7 +34673,7 @@
         <v>6.354345707327784</v>
       </c>
       <c r="D666" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E666">
         <v>5.747828147206722</v>
@@ -34714,7 +34723,7 @@
         <v>6.106229101349317</v>
       </c>
       <c r="D667" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E667">
         <v>5.747828147206722</v>
@@ -34864,7 +34873,7 @@
         <v>5.992378168346487</v>
       </c>
       <c r="D670" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E670">
         <v>5.919638041522585</v>
@@ -34914,7 +34923,7 @@
         <v>6.296137640849427</v>
       </c>
       <c r="D671" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E671">
         <v>5.919638041522585</v>
@@ -34964,7 +34973,7 @@
         <v>6.0403360886604</v>
       </c>
       <c r="D672" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E672">
         <v>5.919638041522585</v>
@@ -35050,7 +35059,7 @@
         <v>1</v>
       </c>
       <c r="P673" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="674" spans="1:16">
@@ -35100,7 +35109,7 @@
         <v>1</v>
       </c>
       <c r="P674" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="675" spans="1:16">
@@ -35114,7 +35123,7 @@
         <v>5.931074248482098</v>
       </c>
       <c r="D675" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E675">
         <v>5.817063063996034</v>
@@ -35150,7 +35159,7 @@
         <v>1</v>
       </c>
       <c r="P675" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="676" spans="1:16">
@@ -35164,7 +35173,7 @@
         <v>6.237027624047666</v>
       </c>
       <c r="D676" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E676">
         <v>5.817063063996034</v>
@@ -35200,7 +35209,7 @@
         <v>1</v>
       </c>
       <c r="P676" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="677" spans="1:16">
@@ -35214,7 +35223,7 @@
         <v>5.973422045250139</v>
       </c>
       <c r="D677" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E677">
         <v>5.817063063996034</v>
@@ -35250,7 +35259,7 @@
         <v>1</v>
       </c>
       <c r="P677" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="678" spans="1:16">
@@ -35364,7 +35373,7 @@
         <v>5.839386641650073</v>
       </c>
       <c r="D680" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E680">
         <v>4.893781158276536</v>
@@ -35414,7 +35423,7 @@
         <v>6.148621271038877</v>
       </c>
       <c r="D681" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E681">
         <v>4.893781158276536</v>
@@ -35464,7 +35473,7 @@
         <v>5.873343803641564</v>
       </c>
       <c r="D682" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E682">
         <v>4.893781158276536</v>
@@ -35564,7 +35573,7 @@
         <v>6.049313264972337</v>
       </c>
       <c r="D684" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E684">
         <v>4.936335249131968</v>
@@ -35614,7 +35623,7 @@
         <v>6.175722584965069</v>
       </c>
       <c r="D685" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E685">
         <v>4.936335249131968</v>
@@ -35664,7 +35673,7 @@
         <v>5.760924613317037</v>
       </c>
       <c r="D686" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E686">
         <v>4.936335249131968</v>
@@ -35814,7 +35823,7 @@
         <v>5.905539797299475</v>
       </c>
       <c r="D689" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E689">
         <v>5.270502414665344</v>
@@ -35864,7 +35873,7 @@
         <v>6.021734035283636</v>
       </c>
       <c r="D690" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E690">
         <v>5.270502414665344</v>
@@ -36014,7 +36023,7 @@
         <v>5.810134805942958</v>
       </c>
       <c r="D693" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E693">
         <v>4.46837075668304</v>
@@ -36064,7 +36073,7 @@
         <v>5.919550534467003</v>
       </c>
       <c r="D694" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E694">
         <v>4.46837075668304</v>
@@ -36114,7 +36123,7 @@
         <v>5.597681787127293</v>
       </c>
       <c r="D695" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E695">
         <v>5.175448484795162</v>
@@ -36164,7 +36173,7 @@
         <v>5.69200276245871</v>
       </c>
       <c r="D696" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E696">
         <v>5.175448484795162</v>
@@ -36250,7 +36259,7 @@
         <v>1</v>
       </c>
       <c r="P697" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="698" spans="1:16">
@@ -36300,7 +36309,7 @@
         <v>1</v>
       </c>
       <c r="P698" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="699" spans="1:16">
@@ -36350,7 +36359,7 @@
         <v>1</v>
       </c>
       <c r="P699" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="700" spans="1:16">
@@ -36400,7 +36409,7 @@
         <v>1</v>
       </c>
       <c r="P700" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="701" spans="1:16">
@@ -36414,7 +36423,7 @@
         <v>10.58920111380781</v>
       </c>
       <c r="D701" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="E701">
         <v>10.63805069137965</v>
@@ -36450,7 +36459,7 @@
         <v>1</v>
       </c>
       <c r="P701" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="702" spans="1:16">
@@ -36500,7 +36509,7 @@
         <v>1</v>
       </c>
       <c r="P702" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="703" spans="1:16">
@@ -36514,7 +36523,7 @@
         <v>13.29070024337744</v>
       </c>
       <c r="D703" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="E703">
         <v>12.1104855745369</v>
@@ -36550,7 +36559,7 @@
         <v>1</v>
       </c>
       <c r="P703" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="704" spans="1:16">
@@ -36600,7 +36609,7 @@
         <v>1</v>
       </c>
       <c r="P704" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="705" spans="1:16">
@@ -36614,7 +36623,7 @@
         <v>13.05967948318782</v>
       </c>
       <c r="D705" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="E705">
         <v>11.87581437344135</v>
@@ -36650,7 +36659,7 @@
         <v>1</v>
       </c>
       <c r="P705" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="706" spans="1:16">
@@ -36700,7 +36709,7 @@
         <v>1</v>
       </c>
       <c r="P706" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="707" spans="1:16">
@@ -36714,7 +36723,7 @@
         <v>12.8170626988293</v>
       </c>
       <c r="D707" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="E707">
         <v>10.97022453374666</v>
@@ -36750,7 +36759,7 @@
         <v>1</v>
       </c>
       <c r="P707" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="708" spans="1:16">
@@ -36800,7 +36809,7 @@
         <v>1</v>
       </c>
       <c r="P708" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="709" spans="1:16">
@@ -36814,7 +36823,7 @@
         <v>12.5987805539735</v>
       </c>
       <c r="D709" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="E709">
         <v>10.73863851098768</v>
@@ -36850,7 +36859,7 @@
         <v>1</v>
       </c>
       <c r="P709" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="710" spans="1:16">
@@ -36900,7 +36909,7 @@
         <v>1</v>
       </c>
       <c r="P710" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="711" spans="1:16">
@@ -36950,7 +36959,7 @@
         <v>1</v>
       </c>
       <c r="P711" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="712" spans="1:16">
@@ -37000,7 +37009,7 @@
         <v>1</v>
       </c>
       <c r="P712" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="713" spans="1:16">
@@ -37014,7 +37023,7 @@
         <v>12.45336310880131</v>
       </c>
       <c r="D713" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="E713">
         <v>10.58435815154991</v>
@@ -37050,7 +37059,7 @@
         <v>1</v>
       </c>
       <c r="P713" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="714" spans="1:16">
@@ -37100,7 +37109,7 @@
         <v>1</v>
       </c>
       <c r="P714" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="715" spans="1:16">
@@ -37150,7 +37159,7 @@
         <v>1</v>
       </c>
       <c r="P715" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="716" spans="1:16">
@@ -37200,7 +37209,7 @@
         <v>1</v>
       </c>
       <c r="P716" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="717" spans="1:16">
@@ -37250,7 +37259,7 @@
         <v>1</v>
       </c>
       <c r="P717" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="718" spans="1:16">
@@ -37300,7 +37309,7 @@
         <v>1</v>
       </c>
       <c r="P718" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="719" spans="1:16">
@@ -37350,7 +37359,7 @@
         <v>1</v>
       </c>
       <c r="P719" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="720" spans="1:16">
@@ -37364,7 +37373,7 @@
         <v>12.29210392935995</v>
       </c>
       <c r="D720" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="E720">
         <v>10.41327053453538</v>
@@ -37400,7 +37409,7 @@
         <v>1</v>
       </c>
       <c r="P720" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="721" spans="1:16">
@@ -37414,7 +37423,7 @@
         <v>9.171282848330055</v>
       </c>
       <c r="D721" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E721">
         <v>6.850968108671186</v>
@@ -37450,7 +37459,7 @@
         <v>1</v>
       </c>
       <c r="P721" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="722" spans="1:16">
@@ -37464,7 +37473,7 @@
         <v>8.830116243154617</v>
       </c>
       <c r="D722" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E722">
         <v>6.850968108671186</v>
@@ -37500,7 +37509,7 @@
         <v>1</v>
       </c>
       <c r="P722" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="723" spans="1:16">
@@ -37664,7 +37673,7 @@
         <v>12.09795277153261</v>
       </c>
       <c r="D726" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="E726">
         <v>10.20728623616326</v>
@@ -37714,7 +37723,7 @@
         <v>8.629829382822578</v>
       </c>
       <c r="D727" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E727">
         <v>7.040051561279032</v>
@@ -37800,7 +37809,7 @@
         <v>1</v>
       </c>
       <c r="P728" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="729" spans="1:16">
@@ -37850,7 +37859,7 @@
         <v>1</v>
       </c>
       <c r="P729" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="730" spans="1:16">
@@ -37900,7 +37909,7 @@
         <v>1</v>
       </c>
       <c r="P730" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="731" spans="1:16">
@@ -37914,7 +37923,7 @@
         <v>11.86477339723001</v>
       </c>
       <c r="D731" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="E731">
         <v>9.95989502640656</v>
@@ -37950,7 +37959,7 @@
         <v>1</v>
       </c>
       <c r="P731" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="732" spans="1:16">
@@ -37964,7 +37973,7 @@
         <v>8.389280908654889</v>
       </c>
       <c r="D732" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E732">
         <v>6.803093216210396</v>
@@ -38000,7 +38009,7 @@
         <v>1</v>
       </c>
       <c r="P732" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="733" spans="1:16">
@@ -38050,7 +38059,7 @@
         <v>1</v>
       </c>
       <c r="P733" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="734" spans="1:16">
@@ -38100,7 +38109,7 @@
         <v>1</v>
       </c>
       <c r="P734" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="735" spans="1:16">
@@ -38150,7 +38159,7 @@
         <v>1</v>
       </c>
       <c r="P735" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="736" spans="1:16">
@@ -38200,7 +38209,7 @@
         <v>1</v>
       </c>
       <c r="P736" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="737" spans="1:16">
@@ -38214,7 +38223,7 @@
         <v>7.721090409497048</v>
       </c>
       <c r="D737" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E737">
         <v>6.845979077114176</v>
@@ -38250,7 +38259,7 @@
         <v>1</v>
       </c>
       <c r="P737" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="738" spans="1:16">
@@ -38300,7 +38309,7 @@
         <v>1</v>
       </c>
       <c r="P738" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="739" spans="1:16">
@@ -38350,7 +38359,7 @@
         <v>1</v>
       </c>
       <c r="P739" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="740" spans="1:16">
@@ -38400,7 +38409,7 @@
         <v>1</v>
       </c>
       <c r="P740" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="741" spans="1:16">
@@ -38414,7 +38423,7 @@
         <v>7.431928747420816</v>
       </c>
       <c r="D741" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="E741">
         <v>6.954602200047407</v>
@@ -38450,7 +38459,7 @@
         <v>1</v>
       </c>
       <c r="P741" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="742" spans="1:16">
@@ -38500,7 +38509,7 @@
         <v>1</v>
       </c>
       <c r="P742" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="743" spans="1:16">
@@ -38550,7 +38559,7 @@
         <v>1</v>
       </c>
       <c r="P743" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="744" spans="1:16">
@@ -38600,7 +38609,7 @@
         <v>1</v>
       </c>
       <c r="P744" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="745" spans="1:16">
@@ -38650,7 +38659,7 @@
         <v>1</v>
       </c>
       <c r="P745" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="746" spans="1:16">
@@ -38664,7 +38673,7 @@
         <v>7.15411432552343</v>
       </c>
       <c r="D746" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E746">
         <v>7.077702572180645</v>
@@ -38700,7 +38709,7 @@
         <v>1</v>
       </c>
       <c r="P746" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="747" spans="1:16">
@@ -38964,7 +38973,7 @@
         <v>6.656074286112602</v>
       </c>
       <c r="D752" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E752">
         <v>7.106777983579878</v>
@@ -39050,7 +39059,7 @@
         <v>1</v>
       </c>
       <c r="P753" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="754" spans="1:16">
@@ -39100,7 +39109,7 @@
         <v>1</v>
       </c>
       <c r="P754" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="755" spans="1:16">
@@ -39150,7 +39159,7 @@
         <v>1</v>
       </c>
       <c r="P755" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="756" spans="1:16">
@@ -39200,7 +39209,7 @@
         <v>1</v>
       </c>
       <c r="P756" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="757" spans="1:16">
@@ -39250,7 +39259,7 @@
         <v>1</v>
       </c>
       <c r="P757" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="758" spans="1:16">
@@ -39300,7 +39309,7 @@
         <v>1</v>
       </c>
       <c r="P758" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="759" spans="1:16">
@@ -39650,7 +39659,7 @@
         <v>1</v>
       </c>
       <c r="P765" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="766" spans="1:16">
@@ -39700,7 +39709,7 @@
         <v>1</v>
       </c>
       <c r="P766" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="767" spans="1:16">
@@ -39714,7 +39723,7 @@
         <v>5.189787984798581</v>
       </c>
       <c r="D767" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E767">
         <v>6.127393152460147</v>
@@ -39750,7 +39759,7 @@
         <v>1</v>
       </c>
       <c r="P767" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="768" spans="1:16">
@@ -39764,7 +39773,7 @@
         <v>5.337615079752425</v>
       </c>
       <c r="D768" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E768">
         <v>6.127393152460147</v>
@@ -39800,7 +39809,7 @@
         <v>1</v>
       </c>
       <c r="P768" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="769" spans="1:16">
@@ -39914,7 +39923,7 @@
         <v>4.573548410677798</v>
       </c>
       <c r="D771" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E771">
         <v>5.983161604764781</v>
@@ -39964,7 +39973,7 @@
         <v>4.718587091269107</v>
       </c>
       <c r="D772" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E772">
         <v>5.983161604764781</v>
@@ -40050,7 +40059,7 @@
         <v>1</v>
       </c>
       <c r="P773" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="774" spans="1:16">
@@ -40100,7 +40109,7 @@
         <v>1</v>
       </c>
       <c r="P774" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="775" spans="1:16">
@@ -40150,7 +40159,7 @@
         <v>1</v>
       </c>
       <c r="P775" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="776" spans="1:16">
@@ -40200,7 +40209,7 @@
         <v>1</v>
       </c>
       <c r="P776" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="777" spans="1:16">
@@ -40450,7 +40459,7 @@
         <v>1</v>
       </c>
       <c r="P781" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="782" spans="1:16">
@@ -40500,7 +40509,7 @@
         <v>1</v>
       </c>
       <c r="P782" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="783" spans="1:16">
@@ -40550,7 +40559,7 @@
         <v>1</v>
       </c>
       <c r="P783" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="784" spans="1:16">
@@ -40950,7 +40959,7 @@
         <v>1</v>
       </c>
       <c r="P791" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="792" spans="1:16">
@@ -41000,7 +41009,7 @@
         <v>1</v>
       </c>
       <c r="P792" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="793" spans="1:16">
@@ -41050,7 +41059,7 @@
         <v>1</v>
       </c>
       <c r="P793" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="794" spans="1:16">
@@ -41100,7 +41109,7 @@
         <v>1</v>
       </c>
       <c r="P794" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="795" spans="1:16">
@@ -41350,7 +41359,7 @@
         <v>1</v>
       </c>
       <c r="P799" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="800" spans="1:16">
@@ -41364,7 +41373,7 @@
         <v>1.03967143846625</v>
       </c>
       <c r="D800" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E800">
         <v>2.609188567947417</v>
@@ -41400,7 +41409,7 @@
         <v>1</v>
       </c>
       <c r="P800" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="801" spans="1:16">
@@ -41414,7 +41423,7 @@
         <v>0.8130094478294367</v>
       </c>
       <c r="D801" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E801">
         <v>2.609188567947417</v>
@@ -41450,7 +41459,7 @@
         <v>1</v>
       </c>
       <c r="P801" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="802" spans="1:16">
@@ -41500,7 +41509,7 @@
         <v>1</v>
       </c>
       <c r="P802" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="803" spans="1:16">
@@ -41514,7 +41523,7 @@
         <v>0.7465491084079581</v>
       </c>
       <c r="D803" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E803">
         <v>2.329329691737918</v>
@@ -41550,7 +41559,7 @@
         <v>1</v>
       </c>
       <c r="P803" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="804" spans="1:16">
@@ -41564,7 +41573,7 @@
         <v>0.5106027000769942</v>
       </c>
       <c r="D804" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E804">
         <v>2.329329691737918</v>
@@ -41600,7 +41609,7 @@
         <v>1</v>
       </c>
       <c r="P804" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="805" spans="1:16">
@@ -41614,7 +41623,7 @@
         <v>0.4893560218813207</v>
       </c>
       <c r="D805" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E805">
         <v>2.083774301434204</v>
@@ -41664,7 +41673,7 @@
         <v>0.2452632261943108</v>
       </c>
       <c r="D806" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E806">
         <v>2.083774301434204</v>
@@ -41714,7 +41723,7 @@
         <v>3.38720643044401</v>
       </c>
       <c r="D807" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E807">
         <v>1.346565161657761</v>
@@ -41764,7 +41773,7 @@
         <v>0.03330516332946587</v>
       </c>
       <c r="D808" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E808">
         <v>1.648359228337185</v>
@@ -41814,7 +41823,7 @@
         <v>-0.2252326821759354</v>
       </c>
       <c r="D809" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E809">
         <v>1.648359228337185</v>
@@ -41864,7 +41873,7 @@
         <v>2.979030594147371</v>
       </c>
       <c r="D810" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E810">
         <v>0.9008321958333205</v>
@@ -41914,7 +41923,7 @@
         <v>-0.3050434949915584</v>
       </c>
       <c r="D811" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E811">
         <v>1.325320464057839</v>
@@ -41950,7 +41959,7 @@
         <v>1</v>
       </c>
       <c r="P811" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="812" spans="1:16">
@@ -41964,7 +41973,7 @@
         <v>-0.5742982663261245</v>
       </c>
       <c r="D812" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E812">
         <v>1.325320464057839</v>
@@ -42000,7 +42009,7 @@
         <v>1</v>
       </c>
       <c r="P812" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="813" spans="1:16">
@@ -42014,7 +42023,7 @@
         <v>2.676200890003035</v>
       </c>
       <c r="D813" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E813">
         <v>0.570138484533139</v>
@@ -42050,7 +42059,7 @@
         <v>1</v>
       </c>
       <c r="P813" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="814" spans="1:16">
@@ -42064,7 +42073,7 @@
         <v>-1.542729235915701</v>
       </c>
       <c r="D814" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E814">
         <v>0.8740710626510406</v>
@@ -42114,7 +42123,7 @@
         <v>-1.06190425457612</v>
       </c>
       <c r="D815" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E815">
         <v>0.8740710626510406</v>
@@ -42164,7 +42173,7 @@
         <v>2.253181308968607</v>
       </c>
       <c r="D816" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E816">
         <v>0.1081959693489338</v>
@@ -42214,7 +42223,7 @@
         <v>-1.645106114375984</v>
       </c>
       <c r="D817" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E817">
         <v>0.7789101756240804</v>
@@ -42264,7 +42273,7 @@
         <v>-1.164732132500994</v>
       </c>
       <c r="D818" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E818">
         <v>0.7789101756240804</v>
@@ -42314,7 +42323,7 @@
         <v>1.705918320624114</v>
       </c>
       <c r="D819" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E819">
         <v>0.01078008499905536</v>
@@ -42364,7 +42373,7 @@
         <v>2.163973614874138</v>
       </c>
       <c r="D820" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E820">
         <v>0.01078008499905536</v>
@@ -42414,7 +42423,7 @@
         <v>2.083749225749141</v>
       </c>
       <c r="D821" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E821">
         <v>-0.02146380625091737</v>
@@ -42464,7 +42473,7 @@
         <v>-1.354990011712744</v>
       </c>
       <c r="D822" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E822">
         <v>1.048577566205335</v>
@@ -42514,7 +42523,7 @@
         <v>-0.8733379853326184</v>
       </c>
       <c r="D823" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E823">
         <v>1.048577566205335</v>
@@ -42564,7 +42573,7 @@
         <v>1.965361355164372</v>
       </c>
       <c r="D824" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E824">
         <v>0.2868376981059342</v>
@@ -42614,7 +42623,7 @@
         <v>2.41677081798775</v>
       </c>
       <c r="D825" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E825">
         <v>0.2868376981059342</v>
@@ -42664,7 +42673,7 @@
         <v>2.335779602159679</v>
       </c>
       <c r="D826" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E826">
         <v>0.246925539825213</v>
@@ -42714,7 +42723,7 @@
         <v>-1.093559587288276</v>
       </c>
       <c r="D827" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E827">
         <v>-1.564638644835625</v>
@@ -42764,7 +42773,7 @@
         <v>-1.266714738768137</v>
       </c>
       <c r="D828" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E828">
         <v>0.4727739583005963</v>
@@ -42800,7 +42809,7 @@
         <v>1</v>
       </c>
       <c r="P828" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="829" spans="1:16">
@@ -42814,7 +42823,7 @@
         <v>-0.7846738345336348</v>
       </c>
       <c r="D829" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E829">
         <v>0.5188966710041001</v>
@@ -42850,7 +42859,7 @@
         <v>1</v>
       </c>
       <c r="P829" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="830" spans="1:16">
@@ -42864,7 +42873,7 @@
         <v>2.044303559603822</v>
       </c>
       <c r="D830" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E830">
         <v>0.3708353146523429</v>
@@ -42900,7 +42909,7 @@
         <v>1</v>
       </c>
       <c r="P830" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="831" spans="1:16">
@@ -42914,7 +42923,7 @@
         <v>2.412466315043719</v>
       </c>
       <c r="D831" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E831">
         <v>0.3285898892453361</v>
@@ -42950,7 +42959,7 @@
         <v>1</v>
       </c>
       <c r="P831" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="832" spans="1:16">
@@ -42964,7 +42973,7 @@
         <v>-1.016717323262487</v>
       </c>
       <c r="D832" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E832">
         <v>-1.725082876878652</v>
@@ -43000,7 +43009,7 @@
         <v>1</v>
       </c>
       <c r="P832" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="833" spans="1:16">
@@ -43014,7 +43023,7 @@
         <v>-1.012419255686936</v>
       </c>
       <c r="D833" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E833">
         <v>0.7130663861460427</v>
@@ -43064,7 +43073,7 @@
         <v>2.271713176632382</v>
       </c>
       <c r="D834" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E834">
         <v>0.563841217205912</v>
@@ -43114,7 +43123,7 @@
         <v>2.633378514442889</v>
       </c>
       <c r="D835" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E835">
         <v>0.563841217205912</v>
@@ -43164,7 +43173,7 @@
         <v>-0.7953570260957719</v>
       </c>
       <c r="D836" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E836">
         <v>-0.6798364854873604</v>
@@ -43214,7 +43223,7 @@
         <v>-1.154980882524804</v>
       </c>
       <c r="D837" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E837">
         <v>0.3632888214250194</v>
@@ -43250,7 +43259,7 @@
         <v>1</v>
       </c>
       <c r="P837" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="838" spans="1:16">
@@ -43264,7 +43273,7 @@
         <v>2.144224144702488</v>
       </c>
       <c r="D838" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E838">
         <v>0.3406232020973725</v>
@@ -43300,7 +43309,7 @@
         <v>1</v>
       </c>
       <c r="P838" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="839" spans="1:16">
@@ -43314,7 +43323,7 @@
         <v>2.509532026282422</v>
       </c>
       <c r="D839" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E839">
         <v>0.3406232020973725</v>
@@ -43350,7 +43359,7 @@
         <v>1</v>
       </c>
       <c r="P839" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="840" spans="1:16">
@@ -43400,7 +43409,7 @@
         <v>1</v>
       </c>
       <c r="P840" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="841" spans="1:16">
@@ -43414,7 +43423,7 @@
         <v>-0.7435135480053319</v>
       </c>
       <c r="D841" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E841">
         <v>0.7484730002152737</v>
@@ -43564,7 +43573,7 @@
         <v>-0.3742444036399846</v>
       </c>
       <c r="D844" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E844">
         <v>1.094154467958163</v>
@@ -43600,7 +43609,7 @@
         <v>1</v>
       </c>
       <c r="P844" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="845" spans="1:16">
@@ -43650,7 +43659,7 @@
         <v>1</v>
       </c>
       <c r="P845" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="846" spans="1:16">
@@ -43700,7 +43709,7 @@
         <v>1</v>
       </c>
       <c r="P846" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="847" spans="1:16">
@@ -43714,7 +43723,7 @@
         <v>-0.2301600625778306</v>
       </c>
       <c r="D847" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E847">
         <v>1.229035183710177</v>
@@ -43750,7 +43759,7 @@
         <v>1</v>
       </c>
       <c r="P847" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="848" spans="1:16">
@@ -43800,7 +43809,7 @@
         <v>1</v>
       </c>
       <c r="P848" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="849" spans="1:16">
@@ -43850,7 +43859,7 @@
         <v>1</v>
       </c>
       <c r="P849" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="850" spans="1:16">
@@ -43864,7 +43873,7 @@
         <v>-0.008911774850371756</v>
       </c>
       <c r="D850" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E850">
         <v>0.5721947646345491</v>
@@ -43900,7 +43909,7 @@
         <v>1</v>
       </c>
       <c r="P850" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="851" spans="1:16">
@@ -43914,7 +43923,7 @@
         <v>-0.1112036199752922</v>
       </c>
       <c r="D851" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E851">
         <v>1.340393087027532</v>
@@ -44064,7 +44073,7 @@
         <v>0.09903988671845454</v>
       </c>
       <c r="D854" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="E854">
         <v>1.106317252320714</v>
@@ -44114,7 +44123,7 @@
         <v>-0.06944114310240224</v>
       </c>
       <c r="D855" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E855">
         <v>1.379487916699293</v>
@@ -44150,7 +44159,7 @@
         <v>1</v>
       </c>
       <c r="P855" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="856" spans="1:16">
@@ -44200,7 +44209,7 @@
         <v>1</v>
       </c>
       <c r="P856" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="857" spans="1:16">
@@ -44250,7 +44259,7 @@
         <v>1</v>
       </c>
       <c r="P857" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="858" spans="1:16">
@@ -44264,7 +44273,7 @@
         <v>0.1369388745414319</v>
       </c>
       <c r="D858" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="E858">
         <v>1.371101739245933</v>
@@ -44300,7 +44309,57 @@
         <v>1</v>
       </c>
       <c r="P858" t="s">
-        <v>243</v>
+        <v>244</v>
+      </c>
+    </row>
+    <row r="859" spans="1:16">
+      <c r="A859" s="1">
+        <v>0</v>
+      </c>
+      <c r="B859" t="s">
+        <v>154</v>
+      </c>
+      <c r="C859">
+        <v>13.70922282990332</v>
+      </c>
+      <c r="D859" t="s">
+        <v>265</v>
+      </c>
+      <c r="E859">
+        <v>12.65888206048432</v>
+      </c>
+      <c r="F859">
+        <v>-1</v>
+      </c>
+      <c r="G859">
+        <v>0.05159077717009667</v>
+      </c>
+      <c r="H859">
+        <v>0.04978111793951567</v>
+      </c>
+      <c r="I859">
+        <v>1.050340769418998</v>
+      </c>
+      <c r="J859">
+        <v>0.8436871790688943</v>
+      </c>
+      <c r="K859">
+        <v>22.45</v>
+      </c>
+      <c r="L859">
+        <v>32.65</v>
+      </c>
+      <c r="M859">
+        <v>22</v>
+      </c>
+      <c r="N859">
+        <v>31.22</v>
+      </c>
+      <c r="O859">
+        <v>1</v>
+      </c>
+      <c r="P859" t="s">
+        <v>346</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-00763-000063.xlsx
+++ b/s60_signal/position-00763-000063.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2589" uniqueCount="347">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2595" uniqueCount="350">
   <si>
     <t>trade_time</t>
   </si>
@@ -481,6 +481,9 @@
     <t>2021-11-24</t>
   </si>
   <si>
+    <t>2021-11-29</t>
+  </si>
+  <si>
     <t>2017-03-17</t>
   </si>
   <si>
@@ -814,6 +817,9 @@
     <t>2021-11-26</t>
   </si>
   <si>
+    <t>2021-11-30</t>
+  </si>
+  <si>
     <t>2017-02-08</t>
   </si>
   <si>
@@ -1055,6 +1061,9 @@
   </si>
   <si>
     <t>2021-11-23</t>
+  </si>
+  <si>
+    <t>2021-11-25</t>
   </si>
 </sst>
 </file>
@@ -1412,7 +1421,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P859"/>
+  <dimension ref="A1:P861"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -1473,7 +1482,7 @@
         <v>8.357775317423281</v>
       </c>
       <c r="D2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E2">
         <v>9.239078272099615</v>
@@ -1509,7 +1518,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -1523,7 +1532,7 @@
         <v>9.433191964550923</v>
       </c>
       <c r="D3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E3">
         <v>9.285575452539577</v>
@@ -1559,7 +1568,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -1573,7 +1582,7 @@
         <v>9.420218808988363</v>
       </c>
       <c r="D4" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E4">
         <v>9.285575452539577</v>
@@ -1609,7 +1618,7 @@
         <v>1</v>
       </c>
       <c r="P4" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -1623,7 +1632,7 @@
         <v>9.27302954676334</v>
       </c>
       <c r="D5" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E5">
         <v>9.285575452539577</v>
@@ -1659,7 +1668,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -1673,7 +1682,7 @@
         <v>8.163141562328137</v>
       </c>
       <c r="D6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E6">
         <v>8.870417830135191</v>
@@ -1709,7 +1718,7 @@
         <v>1</v>
       </c>
       <c r="P6" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -1723,7 +1732,7 @@
         <v>8.167981542028786</v>
       </c>
       <c r="D7" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E7">
         <v>8.870417830135191</v>
@@ -1759,7 +1768,7 @@
         <v>1</v>
       </c>
       <c r="P7" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -1773,7 +1782,7 @@
         <v>9.039124544167011</v>
       </c>
       <c r="D8" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E8">
         <v>9.113918803782131</v>
@@ -1809,7 +1818,7 @@
         <v>1</v>
       </c>
       <c r="P8" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -1823,7 +1832,7 @@
         <v>9.052076876787602</v>
       </c>
       <c r="D9" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E9">
         <v>9.113918803782131</v>
@@ -1859,7 +1868,7 @@
         <v>1</v>
       </c>
       <c r="P9" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -1873,7 +1882,7 @@
         <v>8.972076876787604</v>
       </c>
       <c r="D10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E10">
         <v>9.113918803782131</v>
@@ -1909,7 +1918,7 @@
         <v>1</v>
       </c>
       <c r="P10" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -1923,7 +1932,7 @@
         <v>1.247895028504875</v>
       </c>
       <c r="D11" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E11">
         <v>5.93332434483856</v>
@@ -1959,7 +1968,7 @@
         <v>1</v>
       </c>
       <c r="P11" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -1973,7 +1982,7 @@
         <v>2.464515501370315</v>
       </c>
       <c r="D12" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E12">
         <v>5.93332434483856</v>
@@ -2009,7 +2018,7 @@
         <v>1</v>
       </c>
       <c r="P12" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -2059,7 +2068,7 @@
         <v>1</v>
       </c>
       <c r="P13" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -2073,7 +2082,7 @@
         <v>1.224092499726471</v>
       </c>
       <c r="D14" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E14">
         <v>5.913320521841428</v>
@@ -2109,7 +2118,7 @@
         <v>1</v>
       </c>
       <c r="P14" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -2123,7 +2132,7 @@
         <v>2.442814384300704</v>
       </c>
       <c r="D15" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E15">
         <v>5.913320521841428</v>
@@ -2159,7 +2168,7 @@
         <v>1</v>
       </c>
       <c r="P15" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -2173,7 +2182,7 @@
         <v>8.399951396166678</v>
       </c>
       <c r="D16" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E16">
         <v>7.154665097353277</v>
@@ -2209,7 +2218,7 @@
         <v>1</v>
       </c>
       <c r="P16" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -2223,7 +2232,7 @@
         <v>1.231818368992485</v>
       </c>
       <c r="D17" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E17">
         <v>5.919813400087062</v>
@@ -2259,7 +2268,7 @@
         <v>1</v>
       </c>
       <c r="P17" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -2273,7 +2282,7 @@
         <v>2.449858173427781</v>
       </c>
       <c r="D18" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E18">
         <v>5.919813400087062</v>
@@ -2309,7 +2318,7 @@
         <v>1</v>
       </c>
       <c r="P18" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -2359,7 +2368,7 @@
         <v>1</v>
       </c>
       <c r="P19" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="20" spans="1:16">
@@ -2373,7 +2382,7 @@
         <v>1.145797529921555</v>
       </c>
       <c r="D20" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E20">
         <v>5.847520844331356</v>
@@ -2409,7 +2418,7 @@
         <v>1</v>
       </c>
       <c r="P20" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -2423,7 +2432,7 @@
         <v>2.37143170385038</v>
       </c>
       <c r="D21" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E21">
         <v>5.847520844331356</v>
@@ -2459,7 +2468,7 @@
         <v>1</v>
       </c>
       <c r="P21" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -2473,7 +2482,7 @@
         <v>8.323251570058975</v>
       </c>
       <c r="D22" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E22">
         <v>6.49770468378167</v>
@@ -2509,7 +2518,7 @@
         <v>1</v>
       </c>
       <c r="P22" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="23" spans="1:16">
@@ -2523,7 +2532,7 @@
         <v>8.298928068060523</v>
       </c>
       <c r="D23" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E23">
         <v>6.513844529583032</v>
@@ -2609,7 +2618,7 @@
         <v>1</v>
       </c>
       <c r="P24" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="25" spans="1:16">
@@ -2659,7 +2668,7 @@
         <v>1</v>
       </c>
       <c r="P25" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="26" spans="1:16">
@@ -2673,7 +2682,7 @@
         <v>4.521898732172186</v>
       </c>
       <c r="D26" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E26">
         <v>7.471272137184702</v>
@@ -2709,7 +2718,7 @@
         <v>1</v>
       </c>
       <c r="P26" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="27" spans="1:16">
@@ -2759,7 +2768,7 @@
         <v>1</v>
       </c>
       <c r="P27" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="28" spans="1:16">
@@ -2809,7 +2818,7 @@
         <v>1</v>
       </c>
       <c r="P28" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -2823,7 +2832,7 @@
         <v>10.06347633639325</v>
       </c>
       <c r="D29" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E29">
         <v>8.926863738767604</v>
@@ -2859,7 +2868,7 @@
         <v>1</v>
       </c>
       <c r="P29" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -3023,7 +3032,7 @@
         <v>10.57243502356749</v>
       </c>
       <c r="D33" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E33">
         <v>11.2289160904059</v>
@@ -3073,7 +3082,7 @@
         <v>10.58025171866791</v>
       </c>
       <c r="D34" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E34">
         <v>11.2289160904059</v>
@@ -3123,7 +3132,7 @@
         <v>6.89098969886382</v>
       </c>
       <c r="D35" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E35">
         <v>9.162922766970905</v>
@@ -3159,7 +3168,7 @@
         <v>1</v>
       </c>
       <c r="P35" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -3209,7 +3218,7 @@
         <v>1</v>
       </c>
       <c r="P36" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="37" spans="1:16">
@@ -3259,7 +3268,7 @@
         <v>1</v>
       </c>
       <c r="P37" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="38" spans="1:16">
@@ -3309,7 +3318,7 @@
         <v>1</v>
       </c>
       <c r="P38" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="39" spans="1:16">
@@ -3323,7 +3332,7 @@
         <v>10.57710841036202</v>
       </c>
       <c r="D39" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E39">
         <v>10.91875227586742</v>
@@ -3359,7 +3368,7 @@
         <v>1</v>
       </c>
       <c r="P39" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="40" spans="1:16">
@@ -3373,7 +3382,7 @@
         <v>10.58544939256899</v>
       </c>
       <c r="D40" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E40">
         <v>10.91875227586742</v>
@@ -3409,7 +3418,7 @@
         <v>1</v>
       </c>
       <c r="P40" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="41" spans="1:16">
@@ -3459,7 +3468,7 @@
         <v>1</v>
       </c>
       <c r="P41" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="42" spans="1:16">
@@ -3509,7 +3518,7 @@
         <v>1</v>
       </c>
       <c r="P42" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="43" spans="1:16">
@@ -3559,7 +3568,7 @@
         <v>1</v>
       </c>
       <c r="P43" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="44" spans="1:16">
@@ -3573,7 +3582,7 @@
         <v>10.50706987192051</v>
       </c>
       <c r="D44" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E44">
         <v>9.836117792760128</v>
@@ -3609,7 +3618,7 @@
         <v>1</v>
       </c>
       <c r="P44" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -3773,7 +3782,7 @@
         <v>11.00643298606593</v>
       </c>
       <c r="D48" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E48">
         <v>10.08970532444388</v>
@@ -3859,7 +3868,7 @@
         <v>1</v>
       </c>
       <c r="P49" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="50" spans="1:16">
@@ -3909,7 +3918,7 @@
         <v>1</v>
       </c>
       <c r="P50" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="51" spans="1:16">
@@ -3959,7 +3968,7 @@
         <v>1</v>
       </c>
       <c r="P51" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="52" spans="1:16">
@@ -4009,7 +4018,7 @@
         <v>1</v>
       </c>
       <c r="P52" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="53" spans="1:16">
@@ -4059,7 +4068,7 @@
         <v>1</v>
       </c>
       <c r="P53" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="54" spans="1:16">
@@ -4109,7 +4118,7 @@
         <v>1</v>
       </c>
       <c r="P54" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="55" spans="1:16">
@@ -4123,7 +4132,7 @@
         <v>10.96451987407661</v>
       </c>
       <c r="D55" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E55">
         <v>9.918825279734797</v>
@@ -4159,7 +4168,7 @@
         <v>1</v>
       </c>
       <c r="P55" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="56" spans="1:16">
@@ -4209,7 +4218,7 @@
         <v>1</v>
       </c>
       <c r="P56" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="57" spans="1:16">
@@ -4259,7 +4268,7 @@
         <v>1</v>
       </c>
       <c r="P57" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="58" spans="1:16">
@@ -4309,7 +4318,7 @@
         <v>1</v>
       </c>
       <c r="P58" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="59" spans="1:16">
@@ -4359,7 +4368,7 @@
         <v>1</v>
       </c>
       <c r="P59" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="60" spans="1:16">
@@ -4409,7 +4418,7 @@
         <v>1</v>
       </c>
       <c r="P60" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="61" spans="1:16">
@@ -4459,7 +4468,7 @@
         <v>1</v>
       </c>
       <c r="P61" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="62" spans="1:16">
@@ -4509,7 +4518,7 @@
         <v>1</v>
       </c>
       <c r="P62" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="63" spans="1:16">
@@ -4523,7 +4532,7 @@
         <v>10.70295290100141</v>
       </c>
       <c r="D63" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E63">
         <v>8.905400692050126</v>
@@ -4559,7 +4568,7 @@
         <v>1</v>
       </c>
       <c r="P63" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="64" spans="1:16">
@@ -4573,7 +4582,7 @@
         <v>11.20304517915771</v>
       </c>
       <c r="D64" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E64">
         <v>8.905400692050126</v>
@@ -4609,7 +4618,7 @@
         <v>1</v>
       </c>
       <c r="P64" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="65" spans="1:16">
@@ -4659,7 +4668,7 @@
         <v>1</v>
       </c>
       <c r="P65" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="66" spans="1:16">
@@ -4673,7 +4682,7 @@
         <v>10.69564352718713</v>
       </c>
       <c r="D66" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E66">
         <v>10.68408451836947</v>
@@ -4709,7 +4718,7 @@
         <v>1</v>
       </c>
       <c r="P66" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="67" spans="1:16">
@@ -4723,7 +4732,7 @@
         <v>11.03068966626528</v>
       </c>
       <c r="D67" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E67">
         <v>10.68408451836947</v>
@@ -4759,7 +4768,7 @@
         <v>1</v>
       </c>
       <c r="P67" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="68" spans="1:16">
@@ -4809,7 +4818,7 @@
         <v>1</v>
       </c>
       <c r="P68" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="69" spans="1:16">
@@ -4823,7 +4832,7 @@
         <v>10.52605158161457</v>
       </c>
       <c r="D69" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E69">
         <v>8.71498607743235</v>
@@ -4859,7 +4868,7 @@
         <v>1</v>
       </c>
       <c r="P69" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="70" spans="1:16">
@@ -4873,7 +4882,7 @@
         <v>11.02061569354003</v>
       </c>
       <c r="D70" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E70">
         <v>8.71498607743235</v>
@@ -4909,7 +4918,7 @@
         <v>1</v>
       </c>
       <c r="P70" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="71" spans="1:16">
@@ -4959,7 +4968,7 @@
         <v>1</v>
       </c>
       <c r="P71" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="72" spans="1:16">
@@ -4973,7 +4982,7 @@
         <v>10.52396325368498</v>
       </c>
       <c r="D72" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E72">
         <v>8.806051581614568</v>
@@ -5009,7 +5018,7 @@
         <v>1</v>
       </c>
       <c r="P72" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="73" spans="1:16">
@@ -5023,7 +5032,7 @@
         <v>10.8562453096477</v>
       </c>
       <c r="D73" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E73">
         <v>8.806051581614568</v>
@@ -5059,7 +5068,7 @@
         <v>1</v>
       </c>
       <c r="P73" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="74" spans="1:16">
@@ -5073,7 +5082,7 @@
         <v>10.34525014922946</v>
       </c>
       <c r="D74" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E74">
         <v>8.520373424517821</v>
@@ -5123,7 +5132,7 @@
         <v>10.83416421639288</v>
       </c>
       <c r="D75" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E75">
         <v>8.520373424517821</v>
@@ -5273,7 +5282,7 @@
         <v>10.34849797468624</v>
       </c>
       <c r="D78" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E78">
         <v>8.625250149229462</v>
@@ -5323,7 +5332,7 @@
         <v>10.67795500826794</v>
       </c>
       <c r="D79" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E79">
         <v>8.625250149229462</v>
@@ -5373,7 +5382,7 @@
         <v>10.18864383981015</v>
       </c>
       <c r="D80" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E80">
         <v>8.351804133128983</v>
@@ -5409,7 +5418,7 @@
         <v>1</v>
       </c>
       <c r="P80" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="81" spans="1:16">
@@ -5423,7 +5432,7 @@
         <v>10.67266395980422</v>
       </c>
       <c r="D81" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E81">
         <v>8.351804133128983</v>
@@ -5459,7 +5468,7 @@
         <v>1</v>
       </c>
       <c r="P81" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="82" spans="1:16">
@@ -5509,7 +5518,7 @@
         <v>1</v>
       </c>
       <c r="P82" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="83" spans="1:16">
@@ -5559,7 +5568,7 @@
         <v>1</v>
       </c>
       <c r="P83" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="84" spans="1:16">
@@ -5573,7 +5582,7 @@
         <v>10.19651372648243</v>
       </c>
       <c r="D84" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E84">
         <v>8.468643839810152</v>
@@ -5609,7 +5618,7 @@
         <v>1</v>
       </c>
       <c r="P84" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="85" spans="1:16">
@@ -5623,7 +5632,7 @@
         <v>10.52352378647946</v>
       </c>
       <c r="D85" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E85">
         <v>8.468643839810152</v>
@@ -5659,7 +5668,7 @@
         <v>1</v>
       </c>
       <c r="P85" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="86" spans="1:16">
@@ -5673,7 +5682,7 @@
         <v>-1.278554542763944</v>
       </c>
       <c r="D86" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E86">
         <v>0.01420169243589342</v>
@@ -5709,7 +5718,7 @@
         <v>1</v>
       </c>
       <c r="P86" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="87" spans="1:16">
@@ -5723,7 +5732,7 @@
         <v>-2.406586639852707</v>
       </c>
       <c r="D87" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E87">
         <v>0.01420169243589342</v>
@@ -5759,7 +5768,7 @@
         <v>1</v>
       </c>
       <c r="P87" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="88" spans="1:16">
@@ -5809,7 +5818,7 @@
         <v>1</v>
       </c>
       <c r="P88" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="89" spans="1:16">
@@ -5823,7 +5832,7 @@
         <v>-1.341212522415489</v>
       </c>
       <c r="D89" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E89">
         <v>0.1246199151405953</v>
@@ -5859,7 +5868,7 @@
         <v>1</v>
       </c>
       <c r="P89" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="90" spans="1:16">
@@ -5873,7 +5882,7 @@
         <v>-2.475362406493851</v>
       </c>
       <c r="D90" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E90">
         <v>0.1246199151405953</v>
@@ -5909,7 +5918,7 @@
         <v>1</v>
       </c>
       <c r="P90" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="91" spans="1:16">
@@ -5959,7 +5968,7 @@
         <v>1</v>
       </c>
       <c r="P91" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="92" spans="1:16">
@@ -5973,7 +5982,7 @@
         <v>-2.566016320350375</v>
       </c>
       <c r="D92" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E92">
         <v>0.02954385914472724</v>
@@ -6123,7 +6132,7 @@
         <v>-2.663355023194697</v>
       </c>
       <c r="D95" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E95">
         <v>0.03872013419191234</v>
@@ -6159,7 +6168,7 @@
         <v>1</v>
       </c>
       <c r="P95" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="96" spans="1:16">
@@ -6209,7 +6218,7 @@
         <v>1</v>
       </c>
       <c r="P96" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="97" spans="1:16">
@@ -6259,7 +6268,7 @@
         <v>1</v>
       </c>
       <c r="P97" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="98" spans="1:16">
@@ -6273,7 +6282,7 @@
         <v>-2.748103967913549</v>
       </c>
       <c r="D98" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E98">
         <v>-0.04760949385741853</v>
@@ -6309,7 +6318,7 @@
         <v>1</v>
       </c>
       <c r="P98" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="99" spans="1:16">
@@ -6323,7 +6332,7 @@
         <v>1.170412609918055</v>
       </c>
       <c r="D99" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E99">
         <v>1.469846093587645</v>
@@ -6359,7 +6368,7 @@
         <v>1</v>
       </c>
       <c r="P99" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="100" spans="1:16">
@@ -6373,7 +6382,7 @@
         <v>1.197090465141786</v>
       </c>
       <c r="D100" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E100">
         <v>1.469846093587645</v>
@@ -6409,7 +6418,7 @@
         <v>1</v>
       </c>
       <c r="P100" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="101" spans="1:16">
@@ -6423,7 +6432,7 @@
         <v>-2.807295369205091</v>
       </c>
       <c r="D101" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E101">
         <v>0.3363998775430197</v>
@@ -6459,7 +6468,7 @@
         <v>1</v>
       </c>
       <c r="P101" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="102" spans="1:16">
@@ -6509,7 +6518,7 @@
         <v>1</v>
       </c>
       <c r="P102" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="103" spans="1:16">
@@ -6609,7 +6618,7 @@
         <v>1</v>
       </c>
       <c r="P104" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="105" spans="1:16">
@@ -6623,7 +6632,7 @@
         <v>1.819034812951433</v>
       </c>
       <c r="D105" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E105">
         <v>1.780382458905816</v>
@@ -6659,7 +6668,7 @@
         <v>1</v>
       </c>
       <c r="P105" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="106" spans="1:16">
@@ -6673,7 +6682,7 @@
         <v>1.278232359359254</v>
       </c>
       <c r="D106" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E106">
         <v>1.780382458905816</v>
@@ -6709,7 +6718,7 @@
         <v>1</v>
       </c>
       <c r="P106" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="107" spans="1:16">
@@ -6723,7 +6732,7 @@
         <v>-1.27500579580901</v>
       </c>
       <c r="D107" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E107">
         <v>0.204597470791132</v>
@@ -6759,7 +6768,7 @@
         <v>1</v>
       </c>
       <c r="P107" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="108" spans="1:16">
@@ -6773,7 +6782,7 @@
         <v>-1.164182632644362</v>
       </c>
       <c r="D108" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E108">
         <v>0.204597470791132</v>
@@ -6809,7 +6818,7 @@
         <v>1</v>
       </c>
       <c r="P108" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="109" spans="1:16">
@@ -6859,7 +6868,7 @@
         <v>1</v>
       </c>
       <c r="P109" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="110" spans="1:16">
@@ -6909,7 +6918,7 @@
         <v>1</v>
       </c>
       <c r="P110" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="111" spans="1:16">
@@ -6923,7 +6932,7 @@
         <v>-1.330656541117063</v>
       </c>
       <c r="D111" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E111">
         <v>0.1498300706466971</v>
@@ -6959,7 +6968,7 @@
         <v>1</v>
       </c>
       <c r="P111" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="112" spans="1:16">
@@ -6973,7 +6982,7 @@
         <v>-1.089957636312631</v>
       </c>
       <c r="D112" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E112">
         <v>0.1498300706466971</v>
@@ -7009,7 +7018,7 @@
         <v>1</v>
       </c>
       <c r="P112" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="113" spans="1:16">
@@ -7023,7 +7032,7 @@
         <v>1.663161219313913</v>
       </c>
       <c r="D113" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E113">
         <v>1.394552474924428</v>
@@ -7059,7 +7068,7 @@
         <v>1</v>
       </c>
       <c r="P113" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="114" spans="1:16">
@@ -7073,7 +7082,7 @@
         <v>2.020453841772007</v>
       </c>
       <c r="D114" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E114">
         <v>1.394552474924428</v>
@@ -7109,7 +7118,7 @@
         <v>1</v>
       </c>
       <c r="P114" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="115" spans="1:16">
@@ -7159,7 +7168,7 @@
         <v>1</v>
       </c>
       <c r="P115" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="116" spans="1:16">
@@ -7209,7 +7218,7 @@
         <v>1</v>
       </c>
       <c r="P116" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="117" spans="1:16">
@@ -7259,7 +7268,7 @@
         <v>1</v>
       </c>
       <c r="P117" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="118" spans="1:16">
@@ -7309,7 +7318,7 @@
         <v>1</v>
       </c>
       <c r="P118" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="119" spans="1:16">
@@ -7359,7 +7368,7 @@
         <v>1</v>
       </c>
       <c r="P119" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="120" spans="1:16">
@@ -7409,7 +7418,7 @@
         <v>1</v>
       </c>
       <c r="P120" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="121" spans="1:16">
@@ -7459,7 +7468,7 @@
         <v>1</v>
       </c>
       <c r="P121" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="122" spans="1:16">
@@ -7509,7 +7518,7 @@
         <v>1</v>
       </c>
       <c r="P122" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="123" spans="1:16">
@@ -7559,7 +7568,7 @@
         <v>1</v>
       </c>
       <c r="P123" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="124" spans="1:16">
@@ -7609,7 +7618,7 @@
         <v>1</v>
       </c>
       <c r="P124" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="125" spans="1:16">
@@ -7723,7 +7732,7 @@
         <v>1.583716178161136</v>
       </c>
       <c r="D127" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E127">
         <v>1.731188504841963</v>
@@ -7773,7 +7782,7 @@
         <v>1.943294205912665</v>
       </c>
       <c r="D128" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E128">
         <v>1.731188504841963</v>
@@ -7823,7 +7832,7 @@
         <v>1.440029121201585</v>
       </c>
       <c r="D129" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E129">
         <v>1.731188504841963</v>
@@ -7909,7 +7918,7 @@
         <v>1</v>
       </c>
       <c r="P130" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="131" spans="1:16">
@@ -7959,7 +7968,7 @@
         <v>1</v>
       </c>
       <c r="P131" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="132" spans="1:16">
@@ -8009,7 +8018,7 @@
         <v>1</v>
       </c>
       <c r="P132" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="133" spans="1:16">
@@ -8059,7 +8068,7 @@
         <v>1</v>
       </c>
       <c r="P133" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="134" spans="1:16">
@@ -8109,7 +8118,7 @@
         <v>1</v>
       </c>
       <c r="P134" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="135" spans="1:16">
@@ -8123,7 +8132,7 @@
         <v>-0.8820242128746258</v>
       </c>
       <c r="D135" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E135">
         <v>0.3526024044326252</v>
@@ -8159,7 +8168,7 @@
         <v>1</v>
       </c>
       <c r="P135" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="136" spans="1:16">
@@ -8173,7 +8182,7 @@
         <v>-1.173427909927172</v>
       </c>
       <c r="D136" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E136">
         <v>0.3526024044326252</v>
@@ -8209,7 +8218,7 @@
         <v>1</v>
       </c>
       <c r="P136" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="137" spans="1:16">
@@ -8259,7 +8268,7 @@
         <v>1</v>
       </c>
       <c r="P137" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="138" spans="1:16">
@@ -8309,7 +8318,7 @@
         <v>1</v>
       </c>
       <c r="P138" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="139" spans="1:16">
@@ -8359,7 +8368,7 @@
         <v>1</v>
       </c>
       <c r="P139" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="140" spans="1:16">
@@ -8673,7 +8682,7 @@
         <v>1.916709703800588</v>
       </c>
       <c r="D146" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E146">
         <v>1.625228926806798</v>
@@ -8723,7 +8732,7 @@
         <v>1.775844332123576</v>
       </c>
       <c r="D147" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E147">
         <v>1.625228926806798</v>
@@ -8773,7 +8782,7 @@
         <v>1.706459737440355</v>
       </c>
       <c r="D148" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E148">
         <v>1.625228926806798</v>
@@ -8823,7 +8832,7 @@
         <v>1.898407474064776</v>
       </c>
       <c r="D149" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E149">
         <v>1.579058157468399</v>
@@ -8859,7 +8868,7 @@
         <v>1</v>
       </c>
       <c r="P149" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="150" spans="1:16">
@@ -8873,7 +8882,7 @@
         <v>1.757671173119327</v>
       </c>
       <c r="D150" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E150">
         <v>1.579058157468399</v>
@@ -8909,7 +8918,7 @@
         <v>1</v>
       </c>
       <c r="P150" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="151" spans="1:16">
@@ -8923,7 +8932,7 @@
         <v>1.688493091606606</v>
       </c>
       <c r="D151" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E151">
         <v>1.579058157468399</v>
@@ -8959,7 +8968,7 @@
         <v>1</v>
       </c>
       <c r="P151" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="152" spans="1:16">
@@ -9009,7 +9018,7 @@
         <v>1</v>
       </c>
       <c r="P152" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="153" spans="1:16">
@@ -9059,7 +9068,7 @@
         <v>1</v>
       </c>
       <c r="P153" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="154" spans="1:16">
@@ -9109,7 +9118,7 @@
         <v>1</v>
       </c>
       <c r="P154" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="155" spans="1:16">
@@ -9159,7 +9168,7 @@
         <v>1</v>
       </c>
       <c r="P155" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="156" spans="1:16">
@@ -9209,7 +9218,7 @@
         <v>1</v>
       </c>
       <c r="P156" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="157" spans="1:16">
@@ -9259,7 +9268,7 @@
         <v>1</v>
       </c>
       <c r="P157" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="158" spans="1:16">
@@ -9409,7 +9418,7 @@
         <v>1</v>
       </c>
       <c r="P160" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="161" spans="1:16">
@@ -9459,7 +9468,7 @@
         <v>1</v>
       </c>
       <c r="P161" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="162" spans="1:16">
@@ -9509,7 +9518,7 @@
         <v>1</v>
       </c>
       <c r="P162" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="163" spans="1:16">
@@ -9559,7 +9568,7 @@
         <v>1</v>
       </c>
       <c r="P163" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="164" spans="1:16">
@@ -9573,7 +9582,7 @@
         <v>2.0418888555804</v>
       </c>
       <c r="D164" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E164">
         <v>2.091052252009925</v>
@@ -9623,7 +9632,7 @@
         <v>2.437529947263654</v>
       </c>
       <c r="D165" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E165">
         <v>2.091052252009925</v>
@@ -9673,7 +9682,7 @@
         <v>2.035427646090795</v>
       </c>
       <c r="D166" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E166">
         <v>1.677256780401082</v>
@@ -9709,7 +9718,7 @@
         <v>1</v>
       </c>
       <c r="P166" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="167" spans="1:16">
@@ -9723,7 +9732,7 @@
         <v>2.4319519246827</v>
       </c>
       <c r="D167" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E167">
         <v>1.677256780401082</v>
@@ -9759,7 +9768,7 @@
         <v>1</v>
       </c>
       <c r="P167" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="168" spans="1:16">
@@ -9809,7 +9818,7 @@
         <v>1</v>
       </c>
       <c r="P168" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="169" spans="1:16">
@@ -9859,7 +9868,7 @@
         <v>1</v>
       </c>
       <c r="P169" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="170" spans="1:16">
@@ -9909,7 +9918,7 @@
         <v>1</v>
       </c>
       <c r="P170" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="171" spans="1:16">
@@ -9959,7 +9968,7 @@
         <v>1</v>
       </c>
       <c r="P171" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="172" spans="1:16">
@@ -10009,7 +10018,7 @@
         <v>1</v>
       </c>
       <c r="P172" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="173" spans="1:16">
@@ -10023,7 +10032,7 @@
         <v>2.053037839433713</v>
       </c>
       <c r="D173" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E173">
         <v>2.029053723158555</v>
@@ -10059,7 +10068,7 @@
         <v>1</v>
       </c>
       <c r="P173" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="174" spans="1:16">
@@ -10173,7 +10182,7 @@
         <v>2.072439051471395</v>
       </c>
       <c r="D176" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E176">
         <v>2.198537473651809</v>
@@ -10209,7 +10218,7 @@
         <v>1</v>
       </c>
       <c r="P176" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="177" spans="1:16">
@@ -10223,7 +10232,7 @@
         <v>2.176038435736924</v>
       </c>
       <c r="D177" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E177">
         <v>2.198537473651809</v>
@@ -10259,7 +10268,7 @@
         <v>1</v>
       </c>
       <c r="P177" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="178" spans="1:16">
@@ -10309,7 +10318,7 @@
         <v>1</v>
       </c>
       <c r="P178" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="179" spans="1:16">
@@ -10373,7 +10382,7 @@
         <v>2.199572666349018</v>
       </c>
       <c r="D180" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E180">
         <v>2.369622868222606</v>
@@ -10573,7 +10582,7 @@
         <v>2.441204477380014</v>
       </c>
       <c r="D184" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E184">
         <v>3.019740173907834</v>
@@ -10673,7 +10682,7 @@
         <v>2.450942264059425</v>
       </c>
       <c r="D186" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E186">
         <v>3.396065694761221</v>
@@ -10723,7 +10732,7 @@
         <v>2.93271297523739</v>
       </c>
       <c r="D187" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E187">
         <v>3.396065694761221</v>
@@ -10823,7 +10832,7 @@
         <v>2.613291041571109</v>
       </c>
       <c r="D189" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E189">
         <v>1.747095958240026</v>
@@ -10873,7 +10882,7 @@
         <v>2.94332933323569</v>
       </c>
       <c r="D190" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E190">
         <v>3.513960124909904</v>
@@ -11023,7 +11032,7 @@
         <v>2.630002520413537</v>
       </c>
       <c r="D193" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E193">
         <v>1.763414225815572</v>
@@ -11073,7 +11082,7 @@
         <v>2.960405936825934</v>
       </c>
       <c r="D194" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E194">
         <v>2.688557154970242</v>
@@ -11273,7 +11282,7 @@
         <v>2.642059072099817</v>
       </c>
       <c r="D198" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E198">
         <v>1.775187093932763</v>
@@ -11323,7 +11332,7 @@
         <v>2.972725908969226</v>
       </c>
       <c r="D199" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E199">
         <v>2.375803028433923</v>
@@ -11473,7 +11482,7 @@
         <v>2.666955617984192</v>
       </c>
       <c r="D202" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E202">
         <v>1.799497838737505</v>
@@ -11523,7 +11532,7 @@
         <v>2.998166412998973</v>
       </c>
       <c r="D203" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E203">
         <v>1.736641978102437</v>
@@ -11673,7 +11682,7 @@
         <v>2.973643871143521</v>
       </c>
       <c r="D206" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E206">
         <v>1.818524938691256</v>
@@ -11723,7 +11732,7 @@
         <v>3.018077732744034</v>
       </c>
       <c r="D207" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E207">
         <v>1.759533446033025</v>
@@ -11873,7 +11882,7 @@
         <v>2.990082102112254</v>
       </c>
       <c r="D210" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E210">
         <v>1.83485077149952</v>
@@ -11923,7 +11932,7 @@
         <v>3.03516225313547</v>
       </c>
       <c r="D211" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E211">
         <v>1.779175024575153</v>
@@ -12009,7 +12018,7 @@
         <v>1</v>
       </c>
       <c r="P212" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="213" spans="1:16">
@@ -12059,7 +12068,7 @@
         <v>1</v>
       </c>
       <c r="P213" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="214" spans="1:16">
@@ -12073,7 +12082,7 @@
         <v>3.005496469975766</v>
       </c>
       <c r="D214" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E214">
         <v>1.850159741975929</v>
@@ -12109,7 +12118,7 @@
         <v>1</v>
       </c>
       <c r="P214" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="215" spans="1:16">
@@ -12123,7 +12132,7 @@
         <v>3.051182655974811</v>
       </c>
       <c r="D215" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E215">
         <v>1.797593217971041</v>
@@ -12159,7 +12168,7 @@
         <v>1</v>
       </c>
       <c r="P215" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="216" spans="1:16">
@@ -12273,7 +12282,7 @@
         <v>3.018931533510157</v>
       </c>
       <c r="D218" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E218">
         <v>1.863502941828035</v>
@@ -12323,7 +12332,7 @@
         <v>3.06514593568235</v>
       </c>
       <c r="D219" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E219">
         <v>1.813646396450594</v>
@@ -12473,7 +12482,7 @@
         <v>3.033933076549712</v>
       </c>
       <c r="D222" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E222">
         <v>1.878401910214327</v>
@@ -12523,7 +12532,7 @@
         <v>3.080737282978161</v>
       </c>
       <c r="D223" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E223">
         <v>1.831571317108114</v>
@@ -12573,7 +12582,7 @@
         <v>1.639859271051932</v>
       </c>
       <c r="D224" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E224">
         <v>1.9209216037227</v>
@@ -12723,7 +12732,7 @@
         <v>3.05833801181463</v>
       </c>
       <c r="D227" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E227">
         <v>1.902639974127007</v>
@@ -12773,7 +12782,7 @@
         <v>3.106101728518452</v>
       </c>
       <c r="D228" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E228">
         <v>1.860732085911838</v>
@@ -12859,7 +12868,7 @@
         <v>1</v>
       </c>
       <c r="P229" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="230" spans="1:16">
@@ -12909,7 +12918,7 @@
         <v>1</v>
       </c>
       <c r="P230" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="231" spans="1:16">
@@ -12923,7 +12932,7 @@
         <v>3.085055612872655</v>
       </c>
       <c r="D231" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E231">
         <v>1.929174890733353</v>
@@ -12959,7 +12968,7 @@
         <v>1</v>
       </c>
       <c r="P231" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="232" spans="1:16">
@@ -12973,7 +12982,7 @@
         <v>3.13386976517363</v>
       </c>
       <c r="D232" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E232">
         <v>1.892656193842708</v>
@@ -13009,7 +13018,7 @@
         <v>1</v>
       </c>
       <c r="P232" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="233" spans="1:16">
@@ -13073,7 +13082,7 @@
         <v>3.103034611570727</v>
       </c>
       <c r="D234" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E234">
         <v>1.947030956106994</v>
@@ -13123,7 +13132,7 @@
         <v>3.152555630487182</v>
       </c>
       <c r="D235" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E235">
         <v>1.914138792287073</v>
@@ -13173,7 +13182,7 @@
         <v>1.641725609550694</v>
       </c>
       <c r="D236" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E236">
         <v>1.89319910743864</v>
@@ -13259,7 +13268,7 @@
         <v>1</v>
       </c>
       <c r="P237" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="238" spans="1:16">
@@ -13273,7 +13282,7 @@
         <v>3.11979974827751</v>
       </c>
       <c r="D238" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E238">
         <v>1.963681459400396</v>
@@ -13309,7 +13318,7 @@
         <v>1</v>
       </c>
       <c r="P238" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="239" spans="1:16">
@@ -13323,7 +13332,7 @@
         <v>3.169979909320897</v>
       </c>
       <c r="D239" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E239">
         <v>1.934170981275177</v>
@@ -13359,7 +13368,7 @@
         <v>1</v>
       </c>
       <c r="P239" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="240" spans="1:16">
@@ -13373,7 +13382,7 @@
         <v>1.664480342106565</v>
       </c>
       <c r="D240" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E240">
         <v>2.221652319966786</v>
@@ -13409,7 +13418,7 @@
         <v>1</v>
       </c>
       <c r="P240" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="241" spans="1:16">
@@ -13473,7 +13482,7 @@
         <v>3.136490860930856</v>
       </c>
       <c r="D242" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E242">
         <v>1.980258444787738</v>
@@ -13523,7 +13532,7 @@
         <v>3.187327253753777</v>
       </c>
       <c r="D243" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E243">
         <v>1.954114721009688</v>
@@ -13723,7 +13732,7 @@
         <v>3.154470288152615</v>
       </c>
       <c r="D247" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E247">
         <v>1.998114935754989</v>
@@ -13773,7 +13782,7 @@
         <v>3.206013564438956</v>
       </c>
       <c r="D248" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E248">
         <v>1.975597831484915</v>
@@ -13959,7 +13968,7 @@
         <v>1</v>
       </c>
       <c r="P251" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="252" spans="1:16">
@@ -14009,7 +14018,7 @@
         <v>1</v>
       </c>
       <c r="P252" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="253" spans="1:16">
@@ -14023,7 +14032,7 @@
         <v>3.175183381627829</v>
       </c>
       <c r="D253" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E253">
         <v>2.406837822852639</v>
@@ -14059,7 +14068,7 @@
         <v>1</v>
       </c>
       <c r="P253" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="254" spans="1:16">
@@ -14073,7 +14082,7 @@
         <v>3.227541018854222</v>
       </c>
       <c r="D254" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E254">
         <v>2.000347322662993</v>
@@ -14109,7 +14118,7 @@
         <v>1</v>
       </c>
       <c r="P254" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="255" spans="1:16">
@@ -14159,7 +14168,7 @@
         <v>1</v>
       </c>
       <c r="P255" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="256" spans="1:16">
@@ -14209,7 +14218,7 @@
         <v>1</v>
       </c>
       <c r="P256" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="257" spans="1:16">
@@ -14323,7 +14332,7 @@
         <v>3.194491499183421</v>
       </c>
       <c r="D259" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E259">
         <v>2.42485873257119</v>
@@ -14373,7 +14382,7 @@
         <v>3.247608258980375</v>
       </c>
       <c r="D260" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E260">
         <v>2.023418047742236</v>
@@ -14623,7 +14632,7 @@
         <v>3.213727962726566</v>
       </c>
       <c r="D265" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E265">
         <v>2.442812765211459</v>
@@ -14673,7 +14682,7 @@
         <v>3.26760102792778</v>
       </c>
       <c r="D266" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E266">
         <v>2.046403155463022</v>
@@ -14873,7 +14882,7 @@
         <v>3.233647867837396</v>
       </c>
       <c r="D270" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E270">
         <v>2.461404676648234</v>
@@ -14923,7 +14932,7 @@
         <v>3.288304108795105</v>
       </c>
       <c r="D271" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E271">
         <v>2.070204888236475</v>
@@ -15123,7 +15132,7 @@
         <v>3.249417008017017</v>
       </c>
       <c r="D275" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E275">
         <v>2.476122540815881</v>
@@ -15173,7 +15182,7 @@
         <v>3.304693232263839</v>
       </c>
       <c r="D276" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E276">
         <v>2.089046989066485</v>
@@ -15323,7 +15332,7 @@
         <v>1.914875661806953</v>
       </c>
       <c r="D279" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E279">
         <v>2.109898465499843</v>
@@ -15409,7 +15418,7 @@
         <v>1</v>
       </c>
       <c r="P280" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="281" spans="1:16">
@@ -15423,7 +15432,7 @@
         <v>3.261163134684622</v>
       </c>
       <c r="D281" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E281">
         <v>2.487085592372312</v>
@@ -15459,7 +15468,7 @@
         <v>1</v>
       </c>
       <c r="P281" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="282" spans="1:16">
@@ -15473,7 +15482,7 @@
         <v>3.316901172458547</v>
       </c>
       <c r="D282" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E282">
         <v>2.103082104520595</v>
@@ -15509,7 +15518,7 @@
         <v>1</v>
       </c>
       <c r="P282" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="283" spans="1:16">
@@ -15559,7 +15568,7 @@
         <v>1</v>
       </c>
       <c r="P283" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="284" spans="1:16">
@@ -15609,7 +15618,7 @@
         <v>1</v>
       </c>
       <c r="P284" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="285" spans="1:16">
@@ -15623,7 +15632,7 @@
         <v>1.930296217842372</v>
       </c>
       <c r="D285" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E285">
         <v>2.383746445952788</v>
@@ -15659,7 +15668,7 @@
         <v>1</v>
       </c>
       <c r="P285" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="286" spans="1:16">
@@ -15709,7 +15718,7 @@
         <v>1</v>
       </c>
       <c r="P286" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="287" spans="1:16">
@@ -15723,7 +15732,7 @@
         <v>3.267778188252251</v>
       </c>
       <c r="D287" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E287">
         <v>2.493259642368766</v>
@@ -15759,7 +15768,7 @@
         <v>1</v>
       </c>
       <c r="P287" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="288" spans="1:16">
@@ -15773,7 +15782,7 @@
         <v>3.323776305055329</v>
       </c>
       <c r="D288" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E288">
         <v>2.110986245450121</v>
@@ -15809,7 +15818,7 @@
         <v>1</v>
       </c>
       <c r="P288" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="289" spans="1:16">
@@ -15859,7 +15868,7 @@
         <v>1</v>
       </c>
       <c r="P289" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="290" spans="1:16">
@@ -15909,7 +15918,7 @@
         <v>1</v>
       </c>
       <c r="P290" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="291" spans="1:16">
@@ -15959,7 +15968,7 @@
         <v>1</v>
       </c>
       <c r="P291" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="292" spans="1:16">
@@ -15973,7 +15982,7 @@
         <v>3.278598009747792</v>
       </c>
       <c r="D292" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E292">
         <v>2.503358142431271</v>
@@ -16023,7 +16032,7 @@
         <v>3.335021521242147</v>
       </c>
       <c r="D293" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E293">
         <v>2.123914544980693</v>
@@ -16173,7 +16182,7 @@
         <v>1.953185079463765</v>
       </c>
       <c r="D296" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E296">
         <v>1.673185079463764</v>
@@ -16223,7 +16232,7 @@
         <v>1.838424946780282</v>
       </c>
       <c r="D297" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E297">
         <v>1.673185079463764</v>
@@ -16273,7 +16282,7 @@
         <v>3.286491586851236</v>
       </c>
       <c r="D298" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E298">
         <v>2.510725481061151</v>
@@ -16323,7 +16332,7 @@
         <v>3.343225444112052</v>
       </c>
       <c r="D299" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E299">
         <v>2.133346357622241</v>
@@ -16473,7 +16482,7 @@
         <v>1.963547929404697</v>
       </c>
       <c r="D302" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E302">
         <v>2.040362444937774</v>
@@ -16523,7 +16532,7 @@
         <v>1.849314035194777</v>
       </c>
       <c r="D303" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E303">
         <v>2.040362444937774</v>
@@ -16573,7 +16582,7 @@
         <v>3.287218803551511</v>
       </c>
       <c r="D304" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E304">
         <v>2.511404216648074</v>
@@ -16623,7 +16632,7 @@
         <v>3.34398125223815</v>
       </c>
       <c r="D305" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E305">
         <v>2.134215288346162</v>
@@ -16773,7 +16782,7 @@
         <v>1.964502634406085</v>
       </c>
       <c r="D308" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E308">
         <v>2.034789980466009</v>
@@ -16823,7 +16832,7 @@
         <v>1.850317221309513</v>
       </c>
       <c r="D309" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E309">
         <v>2.034789980466009</v>
@@ -16873,7 +16882,7 @@
         <v>3.309574328279867</v>
       </c>
       <c r="D310" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E310">
         <v>2.532269373061208</v>
@@ -16923,7 +16932,7 @@
         <v>3.367215712126766</v>
       </c>
       <c r="D311" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E311">
         <v>2.160927274303631</v>
@@ -17173,7 +17182,7 @@
         <v>3.386581638751728</v>
       </c>
       <c r="D316" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E316">
         <v>2.183191719551736</v>
@@ -17273,7 +17282,7 @@
         <v>2.018313648949551</v>
       </c>
       <c r="D318" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E318">
         <v>2.020805677582523</v>
@@ -17323,7 +17332,7 @@
         <v>1.906860826435267</v>
       </c>
       <c r="D319" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E319">
         <v>2.020805677582523</v>
@@ -17373,7 +17382,7 @@
         <v>1.784750528729781</v>
       </c>
       <c r="D320" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E320">
         <v>2.020805677582523</v>
@@ -17423,7 +17432,7 @@
         <v>3.376305833526885</v>
       </c>
       <c r="D321" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E321">
         <v>2.171377923742256</v>
@@ -17459,7 +17468,7 @@
         <v>1</v>
       </c>
       <c r="P321" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="322" spans="1:16">
@@ -17509,7 +17518,7 @@
         <v>1</v>
       </c>
       <c r="P322" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="323" spans="1:16">
@@ -17559,7 +17568,7 @@
         <v>1</v>
       </c>
       <c r="P323" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="324" spans="1:16">
@@ -17609,7 +17618,7 @@
         <v>1</v>
       </c>
       <c r="P324" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="325" spans="1:16">
@@ -17623,7 +17632,7 @@
         <v>3.346413966869674</v>
       </c>
       <c r="D325" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E325">
         <v>2.137012109937338</v>
@@ -17659,7 +17668,7 @@
         <v>1</v>
       </c>
       <c r="P325" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="326" spans="1:16">
@@ -17709,7 +17718,7 @@
         <v>1</v>
       </c>
       <c r="P326" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="327" spans="1:16">
@@ -17723,7 +17732,7 @@
         <v>1.853546169841817</v>
       </c>
       <c r="D327" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E327">
         <v>1.909412654865697</v>
@@ -17759,7 +17768,7 @@
         <v>1</v>
       </c>
       <c r="P327" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="328" spans="1:16">
@@ -17773,7 +17782,7 @@
         <v>1.729057523143315</v>
       </c>
       <c r="D328" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E328">
         <v>1.909412654865697</v>
@@ -17809,7 +17818,7 @@
         <v>1</v>
       </c>
       <c r="P328" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="329" spans="1:16">
@@ -17823,7 +17832,7 @@
         <v>1.90213361560998</v>
       </c>
       <c r="D329" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E329">
         <v>1.909412654865697</v>
@@ -17859,7 +17868,7 @@
         <v>1</v>
       </c>
       <c r="P329" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="330" spans="1:16">
@@ -17873,7 +17882,7 @@
         <v>3.335708401471214</v>
       </c>
       <c r="D330" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E330">
         <v>2.124704231296676</v>
@@ -17909,7 +17918,7 @@
         <v>1</v>
       </c>
       <c r="P330" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="331" spans="1:16">
@@ -17959,7 +17968,7 @@
         <v>1</v>
       </c>
       <c r="P331" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="332" spans="1:16">
@@ -17973,7 +17982,7 @@
         <v>1.839336644715903</v>
       </c>
       <c r="D332" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E332">
         <v>2.572020438006287</v>
@@ -18009,7 +18018,7 @@
         <v>1</v>
       </c>
       <c r="P332" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="333" spans="1:16">
@@ -18023,7 +18032,7 @@
         <v>1.714214115855647</v>
       </c>
       <c r="D333" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E333">
         <v>2.572020438006287</v>
@@ -18059,7 +18068,7 @@
         <v>1</v>
       </c>
       <c r="P333" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="334" spans="1:16">
@@ -18073,7 +18082,7 @@
         <v>1.88846993345668</v>
       </c>
       <c r="D334" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E334">
         <v>2.572020438006287</v>
@@ -18109,7 +18118,7 @@
         <v>1</v>
       </c>
       <c r="P334" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="335" spans="1:16">
@@ -18123,7 +18132,7 @@
         <v>3.319807569063805</v>
       </c>
       <c r="D335" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E335">
         <v>2.106423504565129</v>
@@ -18223,7 +18232,7 @@
         <v>1.818231428017253</v>
       </c>
       <c r="D337" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E337">
         <v>2.552327466291189</v>
@@ -18273,7 +18282,7 @@
         <v>1.692167402501294</v>
       </c>
       <c r="D338" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E338">
         <v>2.552327466291189</v>
@@ -18323,7 +18332,7 @@
         <v>1.86817544998933</v>
       </c>
       <c r="D339" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E339">
         <v>2.552327466291189</v>
@@ -18373,7 +18382,7 @@
         <v>3.297653300651016</v>
       </c>
       <c r="D340" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E340">
         <v>2.080953383478715</v>
@@ -18409,7 +18418,7 @@
         <v>1</v>
       </c>
       <c r="P340" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="341" spans="1:16">
@@ -18459,7 +18468,7 @@
         <v>1</v>
       </c>
       <c r="P341" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="342" spans="1:16">
@@ -18473,7 +18482,7 @@
         <v>1.788826009252247</v>
       </c>
       <c r="D342" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E342">
         <v>2.524889696365481</v>
@@ -18509,7 +18518,7 @@
         <v>1</v>
       </c>
       <c r="P342" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="343" spans="1:16">
@@ -18523,7 +18532,7 @@
         <v>1.661450217843427</v>
       </c>
       <c r="D343" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E343">
         <v>2.524889696365481</v>
@@ -18559,7 +18568,7 @@
         <v>1</v>
       </c>
       <c r="P343" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="344" spans="1:16">
@@ -18573,7 +18582,7 @@
         <v>1.839899607409848</v>
       </c>
       <c r="D344" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E344">
         <v>2.524889696365481</v>
@@ -18609,7 +18618,7 @@
         <v>1</v>
       </c>
       <c r="P344" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="345" spans="1:16">
@@ -18623,7 +18632,7 @@
         <v>3.263703117123406</v>
       </c>
       <c r="D345" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E345">
         <v>2.041921840245493</v>
@@ -18723,7 +18732,7 @@
         <v>1.743763841313463</v>
       </c>
       <c r="D347" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E347">
         <v>2.48284284077948</v>
@@ -18773,7 +18782,7 @@
         <v>1.614377841669459</v>
       </c>
       <c r="D348" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E348">
         <v>2.48284284077948</v>
@@ -18823,7 +18832,7 @@
         <v>1.796568452118031</v>
       </c>
       <c r="D349" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E349">
         <v>2.48284284077948</v>
@@ -18873,7 +18882,7 @@
         <v>3.242126022559422</v>
       </c>
       <c r="D350" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E350">
         <v>2.017115279225386</v>
@@ -18909,7 +18918,7 @@
         <v>1</v>
       </c>
       <c r="P350" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="351" spans="1:16">
@@ -18959,7 +18968,7 @@
         <v>1</v>
       </c>
       <c r="P351" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="352" spans="1:16">
@@ -18973,7 +18982,7 @@
         <v>1.715124506916858</v>
       </c>
       <c r="D352" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E352">
         <v>2.456119893071122</v>
@@ -19009,7 +19018,7 @@
         <v>1</v>
       </c>
       <c r="P352" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="353" spans="1:16">
@@ -19023,7 +19032,7 @@
         <v>1.584460916147354</v>
       </c>
       <c r="D353" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E353">
         <v>2.456119893071122</v>
@@ -19059,7 +19068,7 @@
         <v>1</v>
       </c>
       <c r="P353" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="354" spans="1:16">
@@ -19073,7 +19082,7 @@
         <v>1.769029265635051</v>
       </c>
       <c r="D354" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E354">
         <v>2.456119893071122</v>
@@ -19109,7 +19118,7 @@
         <v>1</v>
       </c>
       <c r="P354" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="355" spans="1:16">
@@ -19123,7 +19132,7 @@
         <v>3.218796578894542</v>
       </c>
       <c r="D355" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E355">
         <v>1.990294093169876</v>
@@ -19223,7 +19232,7 @@
         <v>1.684159274947191</v>
       </c>
       <c r="D357" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E357">
         <v>2.427226684058535</v>
@@ -19273,7 +19282,7 @@
         <v>1.552114335539635</v>
       </c>
       <c r="D358" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E358">
         <v>2.427226684058535</v>
@@ -19323,7 +19332,7 @@
         <v>1.739253528325928</v>
       </c>
       <c r="D359" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E359">
         <v>2.427226684058535</v>
@@ -19373,7 +19382,7 @@
         <v>3.223084813618858</v>
       </c>
       <c r="D360" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E360">
         <v>1.995224152499308</v>
@@ -19409,7 +19418,7 @@
         <v>1</v>
       </c>
       <c r="P360" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="361" spans="1:16">
@@ -19423,7 +19432,7 @@
         <v>1.689851060181606</v>
       </c>
       <c r="D361" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E361">
         <v>2.432537606340457</v>
@@ -19459,7 +19468,7 @@
         <v>1</v>
       </c>
       <c r="P361" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="362" spans="1:16">
@@ -19473,7 +19482,7 @@
         <v>1.558060029409038</v>
       </c>
       <c r="D362" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E362">
         <v>2.432537606340457</v>
@@ -19509,7 +19518,7 @@
         <v>1</v>
       </c>
       <c r="P362" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="363" spans="1:16">
@@ -19523,7 +19532,7 @@
         <v>1.5546355793606</v>
       </c>
       <c r="D363" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E363">
         <v>2.429478755941318</v>
@@ -19573,7 +19582,7 @@
         <v>2.749895863416445</v>
       </c>
       <c r="D364" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E364">
         <v>2.144120683335579</v>
@@ -19609,7 +19618,7 @@
         <v>1</v>
       </c>
       <c r="P364" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="365" spans="1:16">
@@ -19623,7 +19632,7 @@
         <v>1.575757316392718</v>
       </c>
       <c r="D365" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E365">
         <v>2.448345503254703</v>
@@ -19659,7 +19668,7 @@
         <v>1</v>
       </c>
       <c r="P365" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="366" spans="1:16">
@@ -19673,7 +19682,7 @@
         <v>1.708690594836302</v>
       </c>
       <c r="D366" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E366">
         <v>1.95524223097577</v>
@@ -19709,7 +19718,7 @@
         <v>1</v>
       </c>
       <c r="P366" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="367" spans="1:16">
@@ -19723,7 +19732,7 @@
         <v>2.776972324350222</v>
       </c>
       <c r="D367" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E367">
         <v>2.170167242074328</v>
@@ -19759,7 +19768,7 @@
         <v>1</v>
       </c>
       <c r="P367" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="368" spans="1:16">
@@ -19773,7 +19782,7 @@
         <v>1.603764011567165</v>
       </c>
       <c r="D368" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E368">
         <v>2.473362159798427</v>
@@ -19809,7 +19818,7 @@
         <v>1</v>
       </c>
       <c r="P368" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="369" spans="1:16">
@@ -19823,7 +19832,7 @@
         <v>1.733308579562596</v>
       </c>
       <c r="D369" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E369">
         <v>2.069952921130998</v>
@@ -19859,7 +19868,7 @@
         <v>1</v>
       </c>
       <c r="P369" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="370" spans="1:16">
@@ -19873,7 +19882,7 @@
         <v>2.804318151096002</v>
       </c>
       <c r="D370" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E370">
         <v>2.196472920808915</v>
@@ -19909,7 +19918,7 @@
         <v>1</v>
       </c>
       <c r="P370" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="371" spans="1:16">
@@ -19923,7 +19932,7 @@
         <v>1.632049326839176</v>
       </c>
       <c r="D371" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E371">
         <v>2.498627690521825</v>
@@ -19959,7 +19968,7 @@
         <v>1</v>
       </c>
       <c r="P371" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="372" spans="1:16">
@@ -19973,7 +19982,7 @@
         <v>1.758171472346181</v>
       </c>
       <c r="D372" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E372">
         <v>2.648741745065742</v>
@@ -20009,7 +20018,7 @@
         <v>1</v>
       </c>
       <c r="P372" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="373" spans="1:16">
@@ -20023,7 +20032,7 @@
         <v>1.836308899819077</v>
       </c>
       <c r="D373" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E373">
         <v>2.387421432319158</v>
@@ -20059,7 +20068,7 @@
         <v>1</v>
       </c>
       <c r="P373" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="374" spans="1:16">
@@ -20109,7 +20118,7 @@
         <v>1</v>
       </c>
       <c r="P374" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="375" spans="1:16">
@@ -20123,7 +20132,7 @@
         <v>1.66686196794393</v>
       </c>
       <c r="D375" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E375">
         <v>2.529723679551338</v>
@@ -20159,7 +20168,7 @@
         <v>1</v>
       </c>
       <c r="P375" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="376" spans="1:16">
@@ -20173,7 +20182,7 @@
         <v>1.844881242140559</v>
       </c>
       <c r="D376" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E376">
         <v>2.529723679551338</v>
@@ -20209,7 +20218,7 @@
         <v>1</v>
       </c>
       <c r="P376" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="377" spans="1:16">
@@ -20223,7 +20232,7 @@
         <v>1.788771907765661</v>
       </c>
       <c r="D377" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E377">
         <v>2.679961622497764</v>
@@ -20259,7 +20268,7 @@
         <v>1</v>
       </c>
       <c r="P377" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="378" spans="1:16">
@@ -20273,7 +20282,7 @@
         <v>1.861508767932467</v>
       </c>
       <c r="D378" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E378">
         <v>2.411732640096055</v>
@@ -20309,7 +20318,7 @@
         <v>1</v>
       </c>
       <c r="P378" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="379" spans="1:16">
@@ -20359,7 +20368,7 @@
         <v>1</v>
       </c>
       <c r="P379" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="380" spans="1:16">
@@ -20373,7 +20382,7 @@
         <v>1.693616991646184</v>
       </c>
       <c r="D380" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E380">
         <v>2.55362229502915</v>
@@ -20409,7 +20418,7 @@
         <v>1</v>
       </c>
       <c r="P380" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="381" spans="1:16">
@@ -20423,7 +20432,7 @@
         <v>1.869509828609061</v>
       </c>
       <c r="D381" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E381">
         <v>2.55362229502915</v>
@@ -20459,7 +20468,7 @@
         <v>1</v>
       </c>
       <c r="P381" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="382" spans="1:16">
@@ -20473,7 +20482,7 @@
         <v>2.574954921244757</v>
       </c>
       <c r="D382" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E382">
         <v>2.17950982860906</v>
@@ -20509,7 +20518,7 @@
         <v>1</v>
       </c>
       <c r="P382" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="383" spans="1:16">
@@ -20523,7 +20532,7 @@
         <v>1.812289668813548</v>
       </c>
       <c r="D383" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E383">
         <v>2.703955451583056</v>
@@ -20559,7 +20568,7 @@
         <v>1</v>
       </c>
       <c r="P383" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="384" spans="1:16">
@@ -20573,7 +20582,7 @@
         <v>1.878354735459471</v>
       </c>
       <c r="D384" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E384">
         <v>2.42798454327702</v>
@@ -20609,7 +20618,7 @@
         <v>1</v>
       </c>
       <c r="P384" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="385" spans="1:16">
@@ -20659,7 +20668,7 @@
         <v>1</v>
       </c>
       <c r="P385" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="386" spans="1:16">
@@ -20673,7 +20682,7 @@
         <v>1.711502571778759</v>
       </c>
       <c r="D386" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E386">
         <v>2.569598382620882</v>
@@ -20709,7 +20718,7 @@
         <v>1</v>
       </c>
       <c r="P386" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="387" spans="1:16">
@@ -20723,7 +20732,7 @@
         <v>1.885973897627895</v>
       </c>
       <c r="D387" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E387">
         <v>2.569598382620882</v>
@@ -20759,7 +20768,7 @@
         <v>1</v>
       </c>
       <c r="P387" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="388" spans="1:16">
@@ -20773,7 +20782,7 @@
         <v>2.591185607841933</v>
       </c>
       <c r="D388" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E388">
         <v>2.195973897627894</v>
@@ -20809,7 +20818,7 @@
         <v>1</v>
       </c>
       <c r="P388" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="389" spans="1:16">
@@ -20823,7 +20832,7 @@
         <v>1.828011157399832</v>
       </c>
       <c r="D389" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E389">
         <v>2.719995188926148</v>
@@ -20859,7 +20868,7 @@
         <v>1</v>
       </c>
       <c r="P389" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="390" spans="1:16">
@@ -20873,7 +20882,7 @@
         <v>1.884937981108568</v>
       </c>
       <c r="D390" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E390">
         <v>2.434335634167709</v>
@@ -20909,7 +20918,7 @@
         <v>1</v>
       </c>
       <c r="P390" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="391" spans="1:16">
@@ -20959,7 +20968,7 @@
         <v>1</v>
       </c>
       <c r="P391" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="392" spans="1:16">
@@ -20973,7 +20982,7 @@
         <v>1.718492088255065</v>
       </c>
       <c r="D392" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E392">
         <v>2.575841687373739</v>
@@ -21009,7 +21018,7 @@
         <v>1</v>
       </c>
       <c r="P392" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="393" spans="1:16">
@@ -21023,7 +21032,7 @@
         <v>1.892407900932305</v>
       </c>
       <c r="D393" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E393">
         <v>2.575841687373739</v>
@@ -21059,7 +21068,7 @@
         <v>1</v>
       </c>
       <c r="P393" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="394" spans="1:16">
@@ -21073,7 +21082,7 @@
         <v>1.834154967256232</v>
       </c>
       <c r="D394" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E394">
         <v>2.726263367403121</v>
@@ -21109,7 +21118,7 @@
         <v>1</v>
       </c>
       <c r="P394" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="395" spans="1:16">
@@ -21123,7 +21132,7 @@
         <v>2.791624887079966</v>
       </c>
       <c r="D395" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E395">
         <v>2.637829766815571</v>
@@ -21159,7 +21168,7 @@
         <v>1</v>
       </c>
       <c r="P395" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="396" spans="1:16">
@@ -21173,7 +21182,7 @@
         <v>1.897004594528006</v>
       </c>
       <c r="D396" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E396">
         <v>2.445976724695786</v>
@@ -21209,7 +21218,7 @@
         <v>1</v>
       </c>
       <c r="P396" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="397" spans="1:16">
@@ -21259,7 +21268,7 @@
         <v>1</v>
       </c>
       <c r="P397" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="398" spans="1:16">
@@ -21273,7 +21282,7 @@
         <v>1.731303366734398</v>
       </c>
       <c r="D398" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E398">
         <v>2.587285213702252</v>
@@ -21309,7 +21318,7 @@
         <v>1</v>
       </c>
       <c r="P398" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="399" spans="1:16">
@@ -21323,7 +21332,7 @@
         <v>1.904200963921582</v>
       </c>
       <c r="D399" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E399">
         <v>2.587285213702252</v>
@@ -21359,7 +21368,7 @@
         <v>1</v>
       </c>
       <c r="P399" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="400" spans="1:16">
@@ -21373,7 +21382,7 @@
         <v>1.845416126631299</v>
       </c>
       <c r="D400" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E400">
         <v>2.737752485469994</v>
@@ -21409,7 +21418,7 @@
         <v>1</v>
       </c>
       <c r="P400" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="401" spans="1:16">
@@ -21423,7 +21432,7 @@
         <v>2.802612496024871</v>
       </c>
       <c r="D401" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E401">
         <v>2.813453713263602</v>
@@ -21459,7 +21468,7 @@
         <v>1</v>
       </c>
       <c r="P401" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="402" spans="1:16">
@@ -21473,7 +21482,7 @@
         <v>1.915149243214803</v>
       </c>
       <c r="D402" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E402">
         <v>2.463481511716044</v>
@@ -21509,7 +21518,7 @@
         <v>1</v>
       </c>
       <c r="P402" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="403" spans="1:16">
@@ -21559,7 +21568,7 @@
         <v>1</v>
       </c>
       <c r="P403" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="404" spans="1:16">
@@ -21573,7 +21582,7 @@
         <v>1.750567773337632</v>
       </c>
       <c r="D404" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E404">
         <v>2.60449292209162</v>
@@ -21609,7 +21618,7 @@
         <v>1</v>
       </c>
       <c r="P404" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="405" spans="1:16">
@@ -21623,7 +21632,7 @@
         <v>1.921934272965604</v>
       </c>
       <c r="D405" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E405">
         <v>2.60449292209162</v>
@@ -21659,7 +21668,7 @@
         <v>1</v>
       </c>
       <c r="P405" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="406" spans="1:16">
@@ -21673,7 +21682,7 @@
         <v>1.862349608592151</v>
       </c>
       <c r="D406" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E406">
         <v>2.75502875046649</v>
@@ -21709,7 +21718,7 @@
         <v>1</v>
       </c>
       <c r="P406" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="407" spans="1:16">
@@ -21723,7 +21732,7 @@
         <v>2.819134638342948</v>
       </c>
       <c r="D407" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E407">
         <v>2.769730713091974</v>
@@ -21759,7 +21768,7 @@
         <v>1</v>
       </c>
       <c r="P407" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="408" spans="1:16">
@@ -21773,7 +21782,7 @@
         <v>1.92753511972947</v>
       </c>
       <c r="D408" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E408">
         <v>2.475430606691152</v>
@@ -21873,7 +21882,7 @@
         <v>1.76371801754653</v>
       </c>
       <c r="D410" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E410">
         <v>2.616239225637646</v>
@@ -21923,7 +21932,7 @@
         <v>1.934039361347697</v>
       </c>
       <c r="D411" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E411">
         <v>2.616239225637646</v>
@@ -21973,7 +21982,7 @@
         <v>1.873908720049794</v>
       </c>
       <c r="D412" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E412">
         <v>2.766821852034614</v>
@@ -22023,7 +22032,7 @@
         <v>2.830412961668017</v>
       </c>
       <c r="D413" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E413">
         <v>2.221708855759843</v>
@@ -22073,7 +22082,7 @@
         <v>1.937685341557977</v>
       </c>
       <c r="D414" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E414">
         <v>2.485222886188172</v>
@@ -22109,7 +22118,7 @@
         <v>1</v>
       </c>
       <c r="P414" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="415" spans="1:16">
@@ -22159,7 +22168,7 @@
         <v>1</v>
       </c>
       <c r="P415" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="416" spans="1:16">
@@ -22173,7 +22182,7 @@
         <v>1.774494638455131</v>
       </c>
       <c r="D416" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E416">
         <v>2.625865317623621</v>
@@ -22209,7 +22218,7 @@
         <v>1</v>
       </c>
       <c r="P416" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="417" spans="1:16">
@@ -22223,7 +22232,7 @@
         <v>1.943959477391676</v>
       </c>
       <c r="D417" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E417">
         <v>2.625865317623621</v>
@@ -22259,7 +22268,7 @@
         <v>1</v>
       </c>
       <c r="P417" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="418" spans="1:16">
@@ -22273,7 +22282,7 @@
         <v>1.883381408179421</v>
       </c>
       <c r="D418" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E418">
         <v>2.776486294984675</v>
@@ -22309,7 +22318,7 @@
         <v>1</v>
       </c>
       <c r="P418" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="419" spans="1:16">
@@ -22323,7 +22332,7 @@
         <v>2.839655544013116</v>
       </c>
       <c r="D419" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E419">
         <v>2.231475567947474</v>
@@ -22359,7 +22368,7 @@
         <v>1</v>
       </c>
       <c r="P419" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="420" spans="1:16">
@@ -22373,7 +22382,7 @@
         <v>1.950149148490695</v>
       </c>
       <c r="D420" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E420">
         <v>2.49724716340538</v>
@@ -22409,7 +22418,7 @@
         <v>1</v>
       </c>
       <c r="P420" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="421" spans="1:16">
@@ -22459,7 +22468,7 @@
         <v>1</v>
       </c>
       <c r="P421" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="422" spans="1:16">
@@ -22473,7 +22482,7 @@
         <v>1.787727622389998</v>
       </c>
       <c r="D422" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E422">
         <v>2.637685527472915</v>
@@ -22509,7 +22518,7 @@
         <v>1</v>
       </c>
       <c r="P422" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="423" spans="1:16">
@@ -22523,7 +22532,7 @@
         <v>1.956140729507283</v>
       </c>
       <c r="D423" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E423">
         <v>2.637685527472915</v>
@@ -22559,7 +22568,7 @@
         <v>1</v>
       </c>
       <c r="P423" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="424" spans="1:16">
@@ -22573,7 +22582,7 @@
         <v>1.895013248150637</v>
       </c>
       <c r="D424" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E424">
         <v>2.788353597303487</v>
@@ -22609,7 +22618,7 @@
         <v>1</v>
       </c>
       <c r="P424" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="425" spans="1:16">
@@ -22623,7 +22632,7 @@
         <v>2.85100482916722</v>
       </c>
       <c r="D425" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E425">
         <v>2.243468450185002</v>
@@ -22659,7 +22668,7 @@
         <v>1</v>
       </c>
       <c r="P425" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="426" spans="1:16">
@@ -22723,7 +22732,7 @@
         <v>1.796280604882195</v>
       </c>
       <c r="D427" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E427">
         <v>2.645325380161676</v>
@@ -22773,7 +22782,7 @@
         <v>1.964013937590256</v>
       </c>
       <c r="D428" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E428">
         <v>2.645325380161676</v>
@@ -22823,7 +22832,7 @@
         <v>1.902531350198938</v>
       </c>
       <c r="D429" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E429">
         <v>2.796023887652364</v>
@@ -22873,7 +22882,7 @@
         <v>2.858340305254835</v>
       </c>
       <c r="D430" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E430">
         <v>2.251219907627515</v>
@@ -22959,7 +22968,7 @@
         <v>1</v>
       </c>
       <c r="P431" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="432" spans="1:16">
@@ -22973,7 +22982,7 @@
         <v>1.81059278070445</v>
       </c>
       <c r="D432" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E432">
         <v>2.658109565682619</v>
@@ -23009,7 +23018,7 @@
         <v>1</v>
       </c>
       <c r="P432" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="433" spans="1:16">
@@ -23023,7 +23032,7 @@
         <v>1.977188609521534</v>
       </c>
       <c r="D433" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E433">
         <v>2.658109565682619</v>
@@ -23059,7 +23068,7 @@
         <v>1</v>
       </c>
       <c r="P433" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="434" spans="1:16">
@@ -23073,7 +23082,7 @@
         <v>1.915111803679711</v>
       </c>
       <c r="D434" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E434">
         <v>2.808859006183351</v>
@@ -23109,7 +23118,7 @@
         <v>1</v>
       </c>
       <c r="P434" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="435" spans="1:16">
@@ -23123,7 +23132,7 @@
         <v>2.870615160675342</v>
       </c>
       <c r="D435" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E435">
         <v>2.26419084751862</v>
@@ -23159,7 +23168,7 @@
         <v>1</v>
       </c>
       <c r="P435" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="436" spans="1:16">
@@ -23209,7 +23218,7 @@
         <v>1</v>
       </c>
       <c r="P436" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="437" spans="1:16">
@@ -23223,7 +23232,7 @@
         <v>1.82632056259726</v>
       </c>
       <c r="D437" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E437">
         <v>2.672158224953424</v>
@@ -23259,7 +23268,7 @@
         <v>1</v>
       </c>
       <c r="P437" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="438" spans="1:16">
@@ -23273,7 +23282,7 @@
         <v>1.991666377906849</v>
       </c>
       <c r="D438" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E438">
         <v>2.672158224953424</v>
@@ -23309,7 +23318,7 @@
         <v>1</v>
       </c>
       <c r="P438" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="439" spans="1:16">
@@ -23323,7 +23332,7 @@
         <v>1.928936579934245</v>
       </c>
       <c r="D439" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E439">
         <v>2.822963636208222</v>
@@ -23359,7 +23368,7 @@
         <v>1</v>
       </c>
       <c r="P439" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="440" spans="1:16">
@@ -23373,7 +23382,7 @@
         <v>2.884104112405478</v>
       </c>
       <c r="D440" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E440">
         <v>2.278444732887671</v>
@@ -23409,7 +23418,7 @@
         <v>1</v>
       </c>
       <c r="P440" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="441" spans="1:16">
@@ -23423,7 +23432,7 @@
         <v>1.850091985515281</v>
       </c>
       <c r="D441" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E441">
         <v>2.693391773538558</v>
@@ -23473,7 +23482,7 @@
         <v>2.013548494377055</v>
       </c>
       <c r="D442" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E442">
         <v>2.693391773538558</v>
@@ -23523,7 +23532,7 @@
         <v>1.949831745274995</v>
       </c>
       <c r="D443" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E443">
         <v>2.844281780604454</v>
@@ -23573,7 +23582,7 @@
         <v>2.90449170287965</v>
       </c>
       <c r="D444" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E444">
         <v>2.29998846611349</v>
@@ -23623,7 +23632,7 @@
         <v>1.883787347386825</v>
       </c>
       <c r="D445" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E445">
         <v>2.723489765815277</v>
@@ -23659,7 +23668,7 @@
         <v>1</v>
       </c>
       <c r="P445" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="446" spans="1:16">
@@ -23673,7 +23682,7 @@
         <v>2.044565814439117</v>
       </c>
       <c r="D446" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E446">
         <v>2.723489765815277</v>
@@ -23709,7 +23718,7 @@
         <v>1</v>
       </c>
       <c r="P446" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="447" spans="1:16">
@@ -23723,7 +23732,7 @@
         <v>2.74752944335815</v>
       </c>
       <c r="D447" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E447">
         <v>2.354565814439116</v>
@@ -23759,7 +23768,7 @@
         <v>1</v>
       </c>
       <c r="P447" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="448" spans="1:16">
@@ -23773,7 +23782,7 @@
         <v>1.979450088272404</v>
       </c>
       <c r="D448" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E448">
         <v>2.874499685200998</v>
@@ -23809,7 +23818,7 @@
         <v>1</v>
       </c>
       <c r="P448" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="449" spans="1:16">
@@ -23823,7 +23832,7 @@
         <v>2.933390571958093</v>
       </c>
       <c r="D449" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E449">
         <v>2.330526136896243</v>
@@ -23859,7 +23868,7 @@
         <v>1</v>
       </c>
       <c r="P449" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="450" spans="1:16">
@@ -23909,7 +23918,7 @@
         <v>1</v>
       </c>
       <c r="P450" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="451" spans="1:16">
@@ -23923,7 +23932,7 @@
         <v>1.920897553279229</v>
       </c>
       <c r="D451" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E451">
         <v>2.756638028018099</v>
@@ -23959,7 +23968,7 @@
         <v>1</v>
       </c>
       <c r="P451" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="452" spans="1:16">
@@ -23973,7 +23982,7 @@
         <v>2.078726573362612</v>
       </c>
       <c r="D452" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E452">
         <v>2.756638028018099</v>
@@ -24009,7 +24018,7 @@
         <v>1</v>
       </c>
       <c r="P452" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="453" spans="1:16">
@@ -24023,7 +24032,7 @@
         <v>2.012070091316616</v>
       </c>
       <c r="D453" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E453">
         <v>2.907780012193474</v>
@@ -24059,7 +24068,7 @@
         <v>1</v>
       </c>
       <c r="P453" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="454" spans="1:16">
@@ -24073,7 +24082,7 @@
         <v>2.965218186264387</v>
       </c>
       <c r="D454" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E454">
         <v>2.364158636661127</v>
@@ -24109,7 +24118,7 @@
         <v>1</v>
       </c>
       <c r="P454" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="455" spans="1:16">
@@ -24123,7 +24132,7 @@
         <v>1.971362962924253</v>
       </c>
       <c r="D455" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E455">
         <v>2.801715671508852</v>
@@ -24173,7 +24182,7 @@
         <v>2.125181090426125</v>
       </c>
       <c r="D456" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E456">
         <v>2.801715671508852</v>
@@ -24223,7 +24232,7 @@
         <v>2.056429365986798</v>
       </c>
       <c r="D457" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E457">
         <v>2.95303724788937</v>
@@ -24273,7 +24282,7 @@
         <v>3.008499907703719</v>
       </c>
       <c r="D458" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E458">
         <v>2.409894784904068</v>
@@ -24323,7 +24332,7 @@
         <v>2.008171638992437</v>
       </c>
       <c r="D459" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E459">
         <v>2.834594595683633</v>
@@ -24359,7 +24368,7 @@
         <v>1</v>
       </c>
       <c r="P459" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="460" spans="1:16">
@@ -24373,7 +24382,7 @@
         <v>2.159064284529219</v>
       </c>
       <c r="D460" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E460">
         <v>2.834594595683633</v>
@@ -24409,7 +24418,7 @@
         <v>1</v>
       </c>
       <c r="P460" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="461" spans="1:16">
@@ -24423,7 +24432,7 @@
         <v>2.088784323242461</v>
       </c>
       <c r="D461" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E461">
         <v>2.986047163793931</v>
@@ -24459,7 +24468,7 @@
         <v>1</v>
       </c>
       <c r="P461" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="462" spans="1:16">
@@ -24473,7 +24482,7 @@
         <v>3.040068914580697</v>
       </c>
       <c r="D462" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E462">
         <v>2.443254012088044</v>
@@ -24509,7 +24518,7 @@
         <v>1</v>
       </c>
       <c r="P462" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="463" spans="1:16">
@@ -24523,7 +24532,7 @@
         <v>2.067700645146257</v>
       </c>
       <c r="D463" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E463">
         <v>2.887768191927794</v>
@@ -24573,7 +24582,7 @@
         <v>2.213862041083626</v>
       </c>
       <c r="D464" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E464">
         <v>2.887768191927794</v>
@@ -24623,7 +24632,7 @@
         <v>2.914425852356924</v>
       </c>
       <c r="D465" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E465">
         <v>2.523862041083625</v>
@@ -24673,7 +24682,7 @@
         <v>2.141110531498665</v>
       </c>
       <c r="D466" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E466">
         <v>3.039432607035081</v>
@@ -24723,7 +24732,7 @@
         <v>3.091124040854972</v>
       </c>
       <c r="D467" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E467">
         <v>2.497204380654495</v>
@@ -24773,7 +24782,7 @@
         <v>2.102053433035913</v>
       </c>
       <c r="D468" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E468">
         <v>2.918453422391508</v>
@@ -24809,7 +24818,7 @@
         <v>1</v>
       </c>
       <c r="P468" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="469" spans="1:16">
@@ -24823,7 +24832,7 @@
         <v>2.245484536222857</v>
       </c>
       <c r="D469" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E469">
         <v>2.918453422391508</v>
@@ -24859,7 +24868,7 @@
         <v>1</v>
       </c>
       <c r="P469" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="470" spans="1:16">
@@ -24873,7 +24882,7 @@
         <v>2.945600090477427</v>
       </c>
       <c r="D470" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E470">
         <v>2.555484536222856</v>
@@ -24909,7 +24918,7 @@
         <v>1</v>
       </c>
       <c r="P470" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="471" spans="1:16">
@@ -24923,7 +24932,7 @@
         <v>2.171306754305586</v>
       </c>
       <c r="D471" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E471">
         <v>3.070240089412991</v>
@@ -24959,7 +24968,7 @@
         <v>1</v>
       </c>
       <c r="P471" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="472" spans="1:16">
@@ -24973,7 +24982,7 @@
         <v>3.120586752176706</v>
       </c>
       <c r="D472" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E472">
         <v>2.528337868136934</v>
@@ -25009,7 +25018,7 @@
         <v>1</v>
       </c>
       <c r="P472" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="473" spans="1:16">
@@ -25023,7 +25032,7 @@
         <v>2.150109762840597</v>
       </c>
       <c r="D473" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E473">
         <v>2.961379183177897</v>
@@ -25059,7 +25068,7 @@
         <v>1</v>
       </c>
       <c r="P473" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="474" spans="1:16">
@@ -25073,7 +25082,7 @@
         <v>2.289721442425034</v>
       </c>
       <c r="D474" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E474">
         <v>2.961379183177897</v>
@@ -25109,7 +25118,7 @@
         <v>1</v>
       </c>
       <c r="P474" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="475" spans="1:16">
@@ -25123,7 +25132,7 @@
         <v>2.989209927132926</v>
       </c>
       <c r="D475" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E475">
         <v>2.599721442425032</v>
@@ -25159,7 +25168,7 @@
         <v>1</v>
       </c>
       <c r="P475" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="476" spans="1:16">
@@ -25173,7 +25182,7 @@
         <v>2.213548439222873</v>
       </c>
       <c r="D476" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E476">
         <v>3.113336869166659</v>
@@ -25209,7 +25218,7 @@
         <v>1</v>
       </c>
       <c r="P476" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="477" spans="1:16">
@@ -25223,7 +25232,7 @@
         <v>3.161802323290331</v>
       </c>
       <c r="D477" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E477">
         <v>2.571890698470007</v>
@@ -25259,7 +25268,7 @@
         <v>1</v>
       </c>
       <c r="P477" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="478" spans="1:16">
@@ -25273,7 +25282,7 @@
         <v>2.189716387261424</v>
       </c>
       <c r="D478" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E478">
         <v>2.99675734235807</v>
@@ -25323,7 +25332,7 @@
         <v>2.326180209388927</v>
       </c>
       <c r="D479" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E479">
         <v>2.99675734235807</v>
@@ -25373,7 +25382,7 @@
         <v>2.248362803037622</v>
       </c>
       <c r="D480" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E480">
         <v>3.148855977188184</v>
@@ -25423,7 +25432,7 @@
         <v>3.19577099405695</v>
       </c>
       <c r="D481" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E481">
         <v>2.607785670068477</v>
@@ -25473,7 +25482,7 @@
         <v>2.215826782258592</v>
       </c>
       <c r="D482" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E482">
         <v>3.020080150700736</v>
@@ -25509,7 +25518,7 @@
         <v>1</v>
       </c>
       <c r="P482" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="483" spans="1:16">
@@ -25523,7 +25532,7 @@
         <v>2.350215400987747</v>
       </c>
       <c r="D483" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E483">
         <v>3.020080150700736</v>
@@ -25559,7 +25568,7 @@
         <v>1</v>
       </c>
       <c r="P483" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="484" spans="1:16">
@@ -25573,7 +25582,7 @@
         <v>2.271313933159689</v>
       </c>
       <c r="D484" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E484">
         <v>3.172271705086001</v>
@@ -25609,7 +25618,7 @@
         <v>1</v>
       </c>
       <c r="P484" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="485" spans="1:16">
@@ -25623,7 +25632,7 @@
         <v>3.218164606848116</v>
       </c>
       <c r="D485" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E485">
         <v>2.631449183446694</v>
@@ -25659,7 +25668,7 @@
         <v>1</v>
       </c>
       <c r="P485" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="486" spans="1:16">
@@ -25709,7 +25718,7 @@
         <v>1</v>
       </c>
       <c r="P486" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="487" spans="1:16">
@@ -25723,7 +25732,7 @@
         <v>2.227304742320833</v>
       </c>
       <c r="D487" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E487">
         <v>3.030332705774125</v>
@@ -25759,7 +25768,7 @@
         <v>1</v>
       </c>
       <c r="P487" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="488" spans="1:16">
@@ -25773,7 +25782,7 @@
         <v>2.360781115113841</v>
       </c>
       <c r="D488" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E488">
         <v>3.030332705774125</v>
@@ -25809,7 +25818,7 @@
         <v>1</v>
       </c>
       <c r="P488" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="489" spans="1:16">
@@ -25823,7 +25832,7 @@
         <v>2.28140310090123</v>
       </c>
       <c r="D489" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E489">
         <v>3.182565106992353</v>
@@ -25859,7 +25868,7 @@
         <v>1</v>
       </c>
       <c r="P489" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="490" spans="1:16">
@@ -25873,7 +25882,7 @@
         <v>3.228008693591889</v>
       </c>
       <c r="D490" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E490">
         <v>2.641851510240944</v>
@@ -25909,7 +25918,7 @@
         <v>1</v>
       </c>
       <c r="P490" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="491" spans="1:16">
@@ -25923,7 +25932,7 @@
         <v>2.326764722017106</v>
       </c>
       <c r="D491" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E491">
         <v>2.338905512271317</v>
@@ -25959,7 +25968,7 @@
         <v>1</v>
       </c>
       <c r="P491" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="492" spans="1:16">
@@ -25973,7 +25982,7 @@
         <v>2.245345573811253</v>
       </c>
       <c r="D492" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E492">
         <v>3.046447469845635</v>
@@ -26009,7 +26018,7 @@
         <v>1</v>
       </c>
       <c r="P492" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="493" spans="1:16">
@@ -26023,7 +26032,7 @@
         <v>2.377388096414631</v>
       </c>
       <c r="D493" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E493">
         <v>3.046447469845635</v>
@@ -26059,7 +26068,7 @@
         <v>1</v>
       </c>
       <c r="P493" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="494" spans="1:16">
@@ -26073,7 +26082,7 @@
         <v>2.297261055983554</v>
       </c>
       <c r="D494" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E494">
         <v>3.198744073311161</v>
@@ -26109,7 +26118,7 @@
         <v>1</v>
       </c>
       <c r="P494" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="495" spans="1:16">
@@ -26123,7 +26132,7 @@
         <v>3.243481435190432</v>
       </c>
       <c r="D495" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E495">
         <v>2.658201682552544</v>
@@ -26159,7 +26168,7 @@
         <v>1</v>
       </c>
       <c r="P495" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="496" spans="1:16">
@@ -26209,7 +26218,7 @@
         <v>1</v>
       </c>
       <c r="P496" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="497" spans="1:16">
@@ -26223,7 +26232,7 @@
         <v>2.301170929293026</v>
       </c>
       <c r="D497" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E497">
         <v>3.202733093853617</v>
@@ -26273,7 +26282,7 @@
         <v>3.247296331820319</v>
       </c>
       <c r="D498" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E498">
         <v>2.662232914952593</v>
@@ -26373,7 +26382,7 @@
         <v>2.309276220482282</v>
       </c>
       <c r="D500" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E500">
         <v>3.211002459763304</v>
@@ -26409,7 +26418,7 @@
         <v>1</v>
       </c>
       <c r="P500" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="501" spans="1:16">
@@ -26423,7 +26432,7 @@
         <v>3.25520473334506</v>
       </c>
       <c r="D501" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E501">
         <v>2.670589787379843</v>
@@ -26459,7 +26468,7 @@
         <v>1</v>
       </c>
       <c r="P501" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="502" spans="1:16">
@@ -26473,7 +26482,7 @@
         <v>2.35659384998981</v>
       </c>
       <c r="D502" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E502">
         <v>2.377701080695644</v>
@@ -26509,7 +26518,7 @@
         <v>1</v>
       </c>
       <c r="P502" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="503" spans="1:16">
@@ -26523,7 +26532,7 @@
         <v>2.318802840630408</v>
       </c>
       <c r="D503" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E503">
         <v>3.220721926473129</v>
@@ -26573,7 +26582,7 @@
         <v>3.264499937619139</v>
       </c>
       <c r="D504" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E504">
         <v>2.680412105589244</v>
@@ -26723,7 +26732,7 @@
         <v>2.968469110715926</v>
       </c>
       <c r="D507" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E507">
         <v>3.65607053595874</v>
@@ -26759,7 +26768,7 @@
         <v>1</v>
       </c>
       <c r="P507" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="508" spans="1:16">
@@ -26773,7 +26782,7 @@
         <v>3.056098677724048</v>
       </c>
       <c r="D508" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E508">
         <v>3.65607053595874</v>
@@ -26809,7 +26818,7 @@
         <v>1</v>
       </c>
       <c r="P508" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="509" spans="1:16">
@@ -26823,7 +26832,7 @@
         <v>3.085552267926261</v>
       </c>
       <c r="D509" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E509">
         <v>3.65607053595874</v>
@@ -26859,7 +26868,7 @@
         <v>1</v>
       </c>
       <c r="P509" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="510" spans="1:16">
@@ -26873,7 +26882,7 @@
         <v>3.115403587495276</v>
       </c>
       <c r="D510" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E510">
         <v>4.899694426383849</v>
@@ -26909,7 +26918,7 @@
         <v>1</v>
       </c>
       <c r="P510" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="511" spans="1:16">
@@ -26923,7 +26932,7 @@
         <v>2.857657467623699</v>
       </c>
       <c r="D511" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E511">
         <v>4.899694426383849</v>
@@ -26959,7 +26968,7 @@
         <v>1</v>
       </c>
       <c r="P511" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="512" spans="1:16">
@@ -26973,7 +26982,7 @@
         <v>4.634833021734408</v>
       </c>
       <c r="D512" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E512">
         <v>3.48240231940969</v>
@@ -27009,7 +27018,7 @@
         <v>1</v>
       </c>
       <c r="P512" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="513" spans="1:16">
@@ -27023,7 +27032,7 @@
         <v>3.013404560606677</v>
       </c>
       <c r="D513" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E513">
         <v>3.707166946903694</v>
@@ -27059,7 +27068,7 @@
         <v>1</v>
       </c>
       <c r="P513" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="514" spans="1:16">
@@ -27073,7 +27082,7 @@
         <v>3.101938488870459</v>
       </c>
       <c r="D514" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E514">
         <v>3.707166946903694</v>
@@ -27109,7 +27118,7 @@
         <v>1</v>
       </c>
       <c r="P514" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="515" spans="1:16">
@@ -27123,7 +27132,7 @@
         <v>3.133031233848563</v>
       </c>
       <c r="D515" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E515">
         <v>3.707166946903694</v>
@@ -27159,7 +27168,7 @@
         <v>1</v>
       </c>
       <c r="P515" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="516" spans="1:16">
@@ -27173,7 +27182,7 @@
         <v>2.923647577997855</v>
       </c>
       <c r="D516" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E516">
         <v>4.966814988327585</v>
@@ -27209,7 +27218,7 @@
         <v>1</v>
       </c>
       <c r="P516" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="517" spans="1:16">
@@ -27223,7 +27232,7 @@
         <v>4.706192777064061</v>
       </c>
       <c r="D517" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E517">
         <v>3.555881671432303</v>
@@ -27259,7 +27268,7 @@
         <v>1</v>
       </c>
       <c r="P517" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="518" spans="1:16">
@@ -27273,7 +27282,7 @@
         <v>3.058294813446018</v>
       </c>
       <c r="D518" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E518">
         <v>3.758211963968808</v>
@@ -27309,7 +27318,7 @@
         <v>1</v>
       </c>
       <c r="P518" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="519" spans="1:16">
@@ -27323,7 +27332,7 @@
         <v>3.147732193339273</v>
       </c>
       <c r="D519" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E519">
         <v>3.758211963968808</v>
@@ -27359,7 +27368,7 @@
         <v>1</v>
       </c>
       <c r="P519" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="520" spans="1:16">
@@ -27373,7 +27382,7 @@
         <v>3.18046244439579</v>
       </c>
       <c r="D520" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E520">
         <v>3.758211963968808</v>
@@ -27409,7 +27418,7 @@
         <v>1</v>
       </c>
       <c r="P520" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="521" spans="1:16">
@@ -27423,7 +27432,7 @@
         <v>3.225680173488445</v>
       </c>
       <c r="D521" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E521">
         <v>5.033868038952384</v>
@@ -27459,7 +27468,7 @@
         <v>1</v>
       </c>
       <c r="P521" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="522" spans="1:16">
@@ -27473,7 +27482,7 @@
         <v>2.989571314085818</v>
       </c>
       <c r="D522" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E522">
         <v>5.033868038952384</v>
@@ -27509,7 +27518,7 @@
         <v>1</v>
       </c>
       <c r="P522" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="523" spans="1:16">
@@ -27523,7 +27532,7 @@
         <v>4.77748075720201</v>
       </c>
       <c r="D523" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E523">
         <v>3.629287116326825</v>
@@ -27559,7 +27568,7 @@
         <v>1</v>
       </c>
       <c r="P523" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="524" spans="1:16">
@@ -27573,7 +27582,7 @@
         <v>3.100990526217007</v>
       </c>
       <c r="D524" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E524">
         <v>5.097643081613452</v>
@@ -27609,7 +27618,7 @@
         <v>1</v>
       </c>
       <c r="P524" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="525" spans="1:16">
@@ -27623,7 +27632,7 @@
         <v>3.19128719089559</v>
       </c>
       <c r="D525" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E525">
         <v>5.097643081613452</v>
@@ -27659,7 +27668,7 @@
         <v>1</v>
       </c>
       <c r="P525" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="526" spans="1:16">
@@ -27673,7 +27682,7 @@
         <v>3.225574895625517</v>
       </c>
       <c r="D526" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E526">
         <v>5.097643081613452</v>
@@ -27709,7 +27718,7 @@
         <v>1</v>
       </c>
       <c r="P526" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="527" spans="1:16">
@@ -27723,7 +27732,7 @@
         <v>3.205781960817575</v>
       </c>
       <c r="D527" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E527">
         <v>5.097643081613452</v>
@@ -27759,7 +27768,7 @@
         <v>1</v>
       </c>
       <c r="P527" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="528" spans="1:16">
@@ -27773,7 +27782,7 @@
         <v>3.27809654539346</v>
       </c>
       <c r="D528" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E528">
         <v>5.097643081613452</v>
@@ -27809,7 +27818,7 @@
         <v>1</v>
       </c>
       <c r="P528" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="529" spans="1:16">
@@ -27823,7 +27832,7 @@
         <v>3.052272250765228</v>
       </c>
       <c r="D529" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E529">
         <v>5.097643081613452</v>
@@ -27859,7 +27868,7 @@
         <v>1</v>
       </c>
       <c r="P529" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="530" spans="1:16">
@@ -27873,7 +27882,7 @@
         <v>4.845283697294303</v>
       </c>
       <c r="D530" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E530">
         <v>3.699104005134728</v>
@@ -27909,7 +27918,7 @@
         <v>1</v>
       </c>
       <c r="P530" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="531" spans="1:16">
@@ -27923,7 +27932,7 @@
         <v>3.135431759672713</v>
       </c>
       <c r="D531" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E531">
         <v>5.149088320265843</v>
@@ -27959,7 +27968,7 @@
         <v>1</v>
       </c>
       <c r="P531" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="532" spans="1:16">
@@ -27973,7 +27982,7 @@
         <v>3.226421581251035</v>
       </c>
       <c r="D532" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E532">
         <v>5.149088320265843</v>
@@ -28009,7 +28018,7 @@
         <v>1</v>
       </c>
       <c r="P532" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="533" spans="1:16">
@@ -28023,7 +28032,7 @@
         <v>3.261965632861735</v>
       </c>
       <c r="D533" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E533">
         <v>5.149088320265843</v>
@@ -28059,7 +28068,7 @@
         <v>1</v>
       </c>
       <c r="P533" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="534" spans="1:16">
@@ -28073,7 +28082,7 @@
         <v>3.248497754763896</v>
       </c>
       <c r="D534" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E534">
         <v>5.149088320265843</v>
@@ -28109,7 +28118,7 @@
         <v>1</v>
       </c>
       <c r="P534" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="535" spans="1:16">
@@ -28123,7 +28132,7 @@
         <v>3.320379116277444</v>
       </c>
       <c r="D535" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E535">
         <v>5.149088320265843</v>
@@ -28159,7 +28168,7 @@
         <v>1</v>
       </c>
       <c r="P535" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="536" spans="1:16">
@@ -28173,7 +28182,7 @@
         <v>3.102851043292947</v>
       </c>
       <c r="D536" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E536">
         <v>5.149088320265843</v>
@@ -28209,7 +28218,7 @@
         <v>1</v>
       </c>
       <c r="P536" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="537" spans="1:16">
@@ -28223,7 +28232,7 @@
         <v>4.899978108914215</v>
       </c>
       <c r="D537" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E537">
         <v>3.755423003238402</v>
@@ -28259,7 +28268,7 @@
         <v>1</v>
       </c>
       <c r="P537" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="538" spans="1:16">
@@ -28273,7 +28282,7 @@
         <v>3.340758667101504</v>
       </c>
       <c r="D538" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E538">
         <v>5.455787317211367</v>
@@ -28309,7 +28318,7 @@
         <v>1</v>
       </c>
       <c r="P538" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="539" spans="1:16">
@@ -28323,7 +28332,7 @@
         <v>3.596337846972439</v>
       </c>
       <c r="D539" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E539">
         <v>5.455787317211367</v>
@@ -28359,7 +28368,7 @@
         <v>1</v>
       </c>
       <c r="P539" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="540" spans="1:16">
@@ -28373,7 +28382,7 @@
         <v>3.478914818069512</v>
       </c>
       <c r="D540" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E540">
         <v>5.455787317211367</v>
@@ -28409,7 +28418,7 @@
         <v>1</v>
       </c>
       <c r="P540" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="541" spans="1:16">
@@ -28423,7 +28432,7 @@
         <v>3.503154774543503</v>
       </c>
       <c r="D541" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E541">
         <v>5.455787317211367</v>
@@ -28459,7 +28468,7 @@
         <v>1</v>
       </c>
       <c r="P541" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="542" spans="1:16">
@@ -28473,7 +28482,7 @@
         <v>3.572453407661722</v>
       </c>
       <c r="D542" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E542">
         <v>5.455787317211367</v>
@@ -28509,7 +28518,7 @@
         <v>1</v>
       </c>
       <c r="P542" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="543" spans="1:16">
@@ -28523,7 +28532,7 @@
         <v>3.404384583447808</v>
       </c>
       <c r="D543" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E543">
         <v>5.455787317211367</v>
@@ -28559,7 +28568,7 @@
         <v>1</v>
       </c>
       <c r="P543" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="544" spans="1:16">
@@ -28573,7 +28582,7 @@
         <v>5.25250104043668</v>
       </c>
       <c r="D544" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E544">
         <v>5.56320240731846</v>
@@ -28609,7 +28618,7 @@
         <v>1</v>
       </c>
       <c r="P544" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="545" spans="1:16">
@@ -28623,7 +28632,7 @@
         <v>3.408744253943432</v>
       </c>
       <c r="D545" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E545">
         <v>5.557338115167074</v>
@@ -28659,7 +28668,7 @@
         <v>1</v>
       </c>
       <c r="P545" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="546" spans="1:16">
@@ -28673,7 +28682,7 @@
         <v>3.550748645676077</v>
       </c>
       <c r="D546" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E546">
         <v>5.557338115167074</v>
@@ -28709,7 +28718,7 @@
         <v>1</v>
       </c>
       <c r="P546" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="547" spans="1:16">
@@ -28723,7 +28732,7 @@
         <v>3.587474005519777</v>
       </c>
       <c r="D547" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E547">
         <v>5.557338115167074</v>
@@ -28759,7 +28768,7 @@
         <v>1</v>
       </c>
       <c r="P547" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="548" spans="1:16">
@@ -28773,7 +28782,7 @@
         <v>3.655917474023632</v>
       </c>
       <c r="D548" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E548">
         <v>5.557338115167074</v>
@@ -28809,7 +28818,7 @@
         <v>1</v>
       </c>
       <c r="P548" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="549" spans="1:16">
@@ -28823,7 +28832,7 @@
         <v>3.504225052174785</v>
       </c>
       <c r="D549" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E549">
         <v>5.557338115167074</v>
@@ -28859,7 +28868,7 @@
         <v>1</v>
       </c>
       <c r="P549" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="550" spans="1:16">
@@ -28873,7 +28882,7 @@
         <v>5.346996730323884</v>
       </c>
       <c r="D550" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E550">
         <v>5.864438002961421</v>
@@ -28909,7 +28918,7 @@
         <v>1</v>
       </c>
       <c r="P550" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="551" spans="1:16">
@@ -28923,7 +28932,7 @@
         <v>5.267444590560391</v>
       </c>
       <c r="D551" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E551">
         <v>5.864438002961421</v>
@@ -28959,7 +28968,7 @@
         <v>1</v>
       </c>
       <c r="P551" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="552" spans="1:16">
@@ -28973,7 +28982,7 @@
         <v>3.796322429340982</v>
       </c>
       <c r="D552" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E552">
         <v>5.685955718590687</v>
@@ -29009,7 +29018,7 @@
         <v>1</v>
       </c>
       <c r="P552" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="553" spans="1:16">
@@ -29023,7 +29032,7 @@
         <v>3.641728676729411</v>
       </c>
       <c r="D553" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E553">
         <v>5.685955718590687</v>
@@ -29059,7 +29068,7 @@
         <v>1</v>
       </c>
       <c r="P553" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="554" spans="1:16">
@@ -29073,7 +29082,7 @@
         <v>3.69426723244667</v>
       </c>
       <c r="D554" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E554">
         <v>5.685955718590687</v>
@@ -29109,7 +29118,7 @@
         <v>1</v>
       </c>
       <c r="P554" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="555" spans="1:16">
@@ -29123,7 +29132,7 @@
         <v>3.761627605342749</v>
       </c>
       <c r="D555" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E555">
         <v>5.685955718590687</v>
@@ -29159,7 +29168,7 @@
         <v>1</v>
       </c>
       <c r="P555" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="556" spans="1:16">
@@ -29173,7 +29182,7 @@
         <v>3.630676464382844</v>
       </c>
       <c r="D556" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E556">
         <v>5.685955718590687</v>
@@ -29209,7 +29218,7 @@
         <v>1</v>
       </c>
       <c r="P556" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="557" spans="1:16">
@@ -29223,7 +29232,7 @@
         <v>5.466678794983334</v>
       </c>
       <c r="D557" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E557">
         <v>5.209318422087254</v>
@@ -29259,7 +29268,7 @@
         <v>1</v>
       </c>
       <c r="P557" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="558" spans="1:16">
@@ -29273,7 +29282,7 @@
         <v>5.390917489847062</v>
       </c>
       <c r="D558" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E558">
         <v>5.209318422087254</v>
@@ -29309,7 +29318,7 @@
         <v>1</v>
       </c>
       <c r="P558" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="559" spans="1:16">
@@ -29323,7 +29332,7 @@
         <v>4.159051079599863</v>
       </c>
       <c r="D559" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E559">
         <v>5.343391662540899</v>
@@ -29359,7 +29368,7 @@
         <v>1</v>
       </c>
       <c r="P559" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="560" spans="1:16">
@@ -29373,7 +29382,7 @@
         <v>4.237780255555339</v>
       </c>
       <c r="D560" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E560">
         <v>5.313343652467495</v>
@@ -29409,7 +29418,7 @@
         <v>1</v>
       </c>
       <c r="P560" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="561" spans="1:16">
@@ -29423,7 +29432,7 @@
         <v>4.283295642394084</v>
       </c>
       <c r="D561" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E561">
         <v>5.313343652467495</v>
@@ -29459,7 +29468,7 @@
         <v>1</v>
       </c>
       <c r="P561" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="562" spans="1:16">
@@ -29509,7 +29518,7 @@
         <v>1</v>
       </c>
       <c r="P562" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="563" spans="1:16">
@@ -29523,7 +29532,7 @@
         <v>4.047954928502808</v>
       </c>
       <c r="D563" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E563">
         <v>5.235960539108905</v>
@@ -29559,7 +29568,7 @@
         <v>1</v>
       </c>
       <c r="P563" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="564" spans="1:16">
@@ -29573,7 +29582,7 @@
         <v>4.137221058995326</v>
       </c>
       <c r="D564" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E564">
         <v>5.202705629828571</v>
@@ -29609,7 +29618,7 @@
         <v>1</v>
       </c>
       <c r="P564" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="565" spans="1:16">
@@ -29623,7 +29632,7 @@
         <v>4.169450720548237</v>
       </c>
       <c r="D565" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E565">
         <v>5.202705629828571</v>
@@ -29659,7 +29668,7 @@
         <v>1</v>
       </c>
       <c r="P565" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="566" spans="1:16">
@@ -29673,7 +29682,7 @@
         <v>6.314817655301979</v>
       </c>
       <c r="D566" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E566">
         <v>6.624319057953503</v>
@@ -29709,7 +29718,7 @@
         <v>1</v>
       </c>
       <c r="P566" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="567" spans="1:16">
@@ -29723,7 +29732,7 @@
         <v>4.059730080999771</v>
       </c>
       <c r="D567" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E567">
         <v>5.117447902330046</v>
@@ -29773,7 +29782,7 @@
         <v>4.081721754571493</v>
       </c>
       <c r="D568" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E568">
         <v>5.117447902330046</v>
@@ -29873,7 +29882,7 @@
         <v>4.030557457706422</v>
       </c>
       <c r="D570" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E570">
         <v>5.085351371462874</v>
@@ -29909,7 +29918,7 @@
         <v>1</v>
       </c>
       <c r="P570" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="571" spans="1:16">
@@ -29923,7 +29932,7 @@
         <v>4.048694889476288</v>
       </c>
       <c r="D571" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E571">
         <v>5.085351371462874</v>
@@ -29959,7 +29968,7 @@
         <v>1</v>
       </c>
       <c r="P571" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="572" spans="1:16">
@@ -30009,7 +30018,7 @@
         <v>1</v>
       </c>
       <c r="P572" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="573" spans="1:16">
@@ -30023,7 +30032,7 @@
         <v>3.737521317704196</v>
       </c>
       <c r="D573" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E573">
         <v>4.762944866631269</v>
@@ -30059,7 +30068,7 @@
         <v>1</v>
       </c>
       <c r="P573" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="574" spans="1:16">
@@ -30073,7 +30082,7 @@
         <v>3.716943268562606</v>
       </c>
       <c r="D574" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E574">
         <v>4.762944866631269</v>
@@ -30109,7 +30118,7 @@
         <v>1</v>
       </c>
       <c r="P574" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="575" spans="1:16">
@@ -30159,7 +30168,7 @@
         <v>1</v>
       </c>
       <c r="P575" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="576" spans="1:16">
@@ -30209,7 +30218,7 @@
         <v>1</v>
       </c>
       <c r="P576" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="577" spans="1:16">
@@ -30223,7 +30232,7 @@
         <v>3.710853293730853</v>
       </c>
       <c r="D577" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E577">
         <v>4.733603965539871</v>
@@ -30259,7 +30268,7 @@
         <v>1</v>
       </c>
       <c r="P577" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="578" spans="1:16">
@@ -30273,7 +30282,7 @@
         <v>3.686751906570006</v>
       </c>
       <c r="D578" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E578">
         <v>4.733603965539871</v>
@@ -30309,7 +30318,7 @@
         <v>1</v>
       </c>
       <c r="P578" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="579" spans="1:16">
@@ -30359,7 +30368,7 @@
         <v>1</v>
       </c>
       <c r="P579" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="580" spans="1:16">
@@ -30409,7 +30418,7 @@
         <v>1</v>
       </c>
       <c r="P580" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="581" spans="1:16">
@@ -30459,7 +30468,7 @@
         <v>1</v>
       </c>
       <c r="P581" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="582" spans="1:16">
@@ -30509,7 +30518,7 @@
         <v>1</v>
       </c>
       <c r="P582" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="583" spans="1:16">
@@ -30559,7 +30568,7 @@
         <v>1</v>
       </c>
       <c r="P583" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="584" spans="1:16">
@@ -30609,7 +30618,7 @@
         <v>1</v>
       </c>
       <c r="P584" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="585" spans="1:16">
@@ -30659,7 +30668,7 @@
         <v>1</v>
       </c>
       <c r="P585" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="586" spans="1:16">
@@ -30709,7 +30718,7 @@
         <v>1</v>
       </c>
       <c r="P586" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="587" spans="1:16">
@@ -30759,7 +30768,7 @@
         <v>1</v>
       </c>
       <c r="P587" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="588" spans="1:16">
@@ -30809,7 +30818,7 @@
         <v>1</v>
       </c>
       <c r="P588" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="589" spans="1:16">
@@ -30859,7 +30868,7 @@
         <v>1</v>
       </c>
       <c r="P589" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="590" spans="1:16">
@@ -30909,7 +30918,7 @@
         <v>1</v>
       </c>
       <c r="P590" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="591" spans="1:16">
@@ -31159,7 +31168,7 @@
         <v>1</v>
       </c>
       <c r="P595" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="596" spans="1:16">
@@ -31209,7 +31218,7 @@
         <v>1</v>
       </c>
       <c r="P596" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="597" spans="1:16">
@@ -31259,7 +31268,7 @@
         <v>1</v>
       </c>
       <c r="P597" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="598" spans="1:16">
@@ -31309,7 +31318,7 @@
         <v>1</v>
       </c>
       <c r="P598" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="599" spans="1:16">
@@ -31359,7 +31368,7 @@
         <v>1</v>
       </c>
       <c r="P599" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="600" spans="1:16">
@@ -31409,7 +31418,7 @@
         <v>1</v>
       </c>
       <c r="P600" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="601" spans="1:16">
@@ -31623,7 +31632,7 @@
         <v>6.312844467716282</v>
       </c>
       <c r="D605" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E605">
         <v>7.044140001633426</v>
@@ -31709,7 +31718,7 @@
         <v>1</v>
       </c>
       <c r="P606" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="607" spans="1:16">
@@ -31759,7 +31768,7 @@
         <v>1</v>
       </c>
       <c r="P607" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="608" spans="1:16">
@@ -31809,7 +31818,7 @@
         <v>1</v>
       </c>
       <c r="P608" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="609" spans="1:16">
@@ -31859,7 +31868,7 @@
         <v>1</v>
       </c>
       <c r="P609" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="610" spans="1:16">
@@ -31909,7 +31918,7 @@
         <v>1</v>
       </c>
       <c r="P610" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="611" spans="1:16">
@@ -31959,7 +31968,7 @@
         <v>1</v>
       </c>
       <c r="P611" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="612" spans="1:16">
@@ -32009,7 +32018,7 @@
         <v>1</v>
       </c>
       <c r="P612" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="613" spans="1:16">
@@ -32059,7 +32068,7 @@
         <v>1</v>
       </c>
       <c r="P613" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="614" spans="1:16">
@@ -32109,7 +32118,7 @@
         <v>1</v>
       </c>
       <c r="P614" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="615" spans="1:16">
@@ -32159,7 +32168,7 @@
         <v>1</v>
       </c>
       <c r="P615" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="616" spans="1:16">
@@ -32209,7 +32218,7 @@
         <v>1</v>
       </c>
       <c r="P616" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="617" spans="1:16">
@@ -32259,7 +32268,7 @@
         <v>1</v>
       </c>
       <c r="P617" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="618" spans="1:16">
@@ -32309,7 +32318,7 @@
         <v>1</v>
       </c>
       <c r="P618" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="619" spans="1:16">
@@ -32359,7 +32368,7 @@
         <v>1</v>
       </c>
       <c r="P619" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="620" spans="1:16">
@@ -32409,7 +32418,7 @@
         <v>1</v>
       </c>
       <c r="P620" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="621" spans="1:16">
@@ -32459,7 +32468,7 @@
         <v>1</v>
       </c>
       <c r="P621" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="622" spans="1:16">
@@ -32473,7 +32482,7 @@
         <v>6.52789956231641</v>
       </c>
       <c r="D622" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E622">
         <v>6.970266187949232</v>
@@ -32509,7 +32518,7 @@
         <v>1</v>
       </c>
       <c r="P622" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="623" spans="1:16">
@@ -32559,7 +32568,7 @@
         <v>1</v>
       </c>
       <c r="P623" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="624" spans="1:16">
@@ -32609,7 +32618,7 @@
         <v>1</v>
       </c>
       <c r="P624" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="625" spans="1:16">
@@ -32659,7 +32668,7 @@
         <v>1</v>
       </c>
       <c r="P625" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="626" spans="1:16">
@@ -32673,7 +32682,7 @@
         <v>2.603543847706</v>
       </c>
       <c r="D626" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E626">
         <v>4.770094008155837</v>
@@ -32709,7 +32718,7 @@
         <v>1</v>
       </c>
       <c r="P626" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="627" spans="1:16">
@@ -32759,7 +32768,7 @@
         <v>1</v>
       </c>
       <c r="P627" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="628" spans="1:16">
@@ -32809,7 +32818,7 @@
         <v>1</v>
       </c>
       <c r="P628" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="629" spans="1:16">
@@ -32859,7 +32868,7 @@
         <v>1</v>
       </c>
       <c r="P629" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="630" spans="1:16">
@@ -32909,7 +32918,7 @@
         <v>1</v>
       </c>
       <c r="P630" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="631" spans="1:16">
@@ -32959,7 +32968,7 @@
         <v>1</v>
       </c>
       <c r="P631" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="632" spans="1:16">
@@ -32973,7 +32982,7 @@
         <v>2.478182256708074</v>
       </c>
       <c r="D632" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E632">
         <v>4.645810796435313</v>
@@ -33009,7 +33018,7 @@
         <v>1</v>
       </c>
       <c r="P632" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="633" spans="1:16">
@@ -33059,7 +33068,7 @@
         <v>1</v>
       </c>
       <c r="P633" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="634" spans="1:16">
@@ -33109,7 +33118,7 @@
         <v>1</v>
       </c>
       <c r="P634" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="635" spans="1:16">
@@ -33159,7 +33168,7 @@
         <v>1</v>
       </c>
       <c r="P635" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="636" spans="1:16">
@@ -33209,7 +33218,7 @@
         <v>1</v>
       </c>
       <c r="P636" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="637" spans="1:16">
@@ -33223,7 +33232,7 @@
         <v>2.30694018299906</v>
       </c>
       <c r="D637" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E637">
         <v>4.476041772822722</v>
@@ -33259,7 +33268,7 @@
         <v>1</v>
       </c>
       <c r="P637" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="638" spans="1:16">
@@ -33273,7 +33282,7 @@
         <v>5.979313720333828</v>
       </c>
       <c r="D638" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E638">
         <v>6.921637837986275</v>
@@ -33309,7 +33318,7 @@
         <v>1</v>
       </c>
       <c r="P638" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="639" spans="1:16">
@@ -33323,7 +33332,7 @@
         <v>6.118014825265853</v>
       </c>
       <c r="D639" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E639">
         <v>6.921637837986275</v>
@@ -33359,7 +33368,7 @@
         <v>1</v>
       </c>
       <c r="P639" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="640" spans="1:16">
@@ -33373,7 +33382,7 @@
         <v>2.180042495856011</v>
       </c>
       <c r="D640" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E640">
         <v>4.350235678687355</v>
@@ -33409,7 +33418,7 @@
         <v>1</v>
       </c>
       <c r="P640" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="641" spans="1:16">
@@ -33459,7 +33468,7 @@
         <v>1</v>
       </c>
       <c r="P641" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="642" spans="1:16">
@@ -33509,7 +33518,7 @@
         <v>1</v>
       </c>
       <c r="P642" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="643" spans="1:16">
@@ -33559,7 +33568,7 @@
         <v>1</v>
       </c>
       <c r="P643" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="644" spans="1:16">
@@ -33573,7 +33582,7 @@
         <v>2.005501953213372</v>
       </c>
       <c r="D644" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E644">
         <v>4.177196560067447</v>
@@ -33609,7 +33618,7 @@
         <v>1</v>
       </c>
       <c r="P644" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="645" spans="1:16">
@@ -33623,7 +33632,7 @@
         <v>6.03048720269387</v>
       </c>
       <c r="D645" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E645">
         <v>7.646218976894719</v>
@@ -33659,7 +33668,7 @@
         <v>1</v>
       </c>
       <c r="P645" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="646" spans="1:16">
@@ -33673,7 +33682,7 @@
         <v>6.160487202693869</v>
       </c>
       <c r="D646" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E646">
         <v>7.646218976894719</v>
@@ -33709,7 +33718,7 @@
         <v>1</v>
       </c>
       <c r="P646" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="647" spans="1:16">
@@ -33773,7 +33782,7 @@
         <v>5.929250610805834</v>
       </c>
       <c r="D648" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E648">
         <v>6.44678700451809</v>
@@ -33823,7 +33832,7 @@
         <v>6.059250610805833</v>
       </c>
       <c r="D649" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E649">
         <v>6.44678700451809</v>
@@ -33909,7 +33918,7 @@
         <v>1</v>
       </c>
       <c r="P650" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="651" spans="1:16">
@@ -33923,7 +33932,7 @@
         <v>6.444007644774246</v>
       </c>
       <c r="D651" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E651">
         <v>5.9080963375586</v>
@@ -33959,7 +33968,7 @@
         <v>1</v>
       </c>
       <c r="P651" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="652" spans="1:16">
@@ -33973,7 +33982,7 @@
         <v>5.977845942063905</v>
       </c>
       <c r="D652" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E652">
         <v>5.9080963375586</v>
@@ -34009,7 +34018,7 @@
         <v>1</v>
       </c>
       <c r="P652" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="653" spans="1:16">
@@ -34073,7 +34082,7 @@
         <v>6.325113724849238</v>
       </c>
       <c r="D654" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="E654">
         <v>5.966484401224733</v>
@@ -34123,7 +34132,7 @@
         <v>6.616965483162407</v>
       </c>
       <c r="D655" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="E655">
         <v>5.966484401224733</v>
@@ -34359,7 +34368,7 @@
         <v>1</v>
       </c>
       <c r="P659" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="660" spans="1:16">
@@ -34373,7 +34382,7 @@
         <v>6.182411935806901</v>
       </c>
       <c r="D660" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E660">
         <v>5.820555041914538</v>
@@ -34409,7 +34418,7 @@
         <v>1</v>
       </c>
       <c r="P660" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="661" spans="1:16">
@@ -34423,7 +34432,7 @@
         <v>6.479370608860847</v>
       </c>
       <c r="D661" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E661">
         <v>5.820555041914538</v>
@@ -34459,7 +34468,7 @@
         <v>1</v>
       </c>
       <c r="P661" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="662" spans="1:16">
@@ -34473,7 +34482,7 @@
         <v>6.247760471854665</v>
       </c>
       <c r="D662" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E662">
         <v>5.820555041914538</v>
@@ -34509,7 +34518,7 @@
         <v>1</v>
       </c>
       <c r="P662" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="663" spans="1:16">
@@ -34623,7 +34632,7 @@
         <v>6.052746661470383</v>
       </c>
       <c r="D665" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E665">
         <v>5.747828147206722</v>
@@ -34673,7 +34682,7 @@
         <v>6.354345707327784</v>
       </c>
       <c r="D666" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E666">
         <v>5.747828147206722</v>
@@ -34723,7 +34732,7 @@
         <v>6.106229101349317</v>
       </c>
       <c r="D667" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E667">
         <v>5.747828147206722</v>
@@ -34873,7 +34882,7 @@
         <v>5.992378168346487</v>
       </c>
       <c r="D670" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E670">
         <v>5.919638041522585</v>
@@ -34923,7 +34932,7 @@
         <v>6.296137640849427</v>
       </c>
       <c r="D671" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E671">
         <v>5.919638041522585</v>
@@ -34973,7 +34982,7 @@
         <v>6.0403360886604</v>
       </c>
       <c r="D672" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E672">
         <v>5.919638041522585</v>
@@ -35059,7 +35068,7 @@
         <v>1</v>
       </c>
       <c r="P673" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="674" spans="1:16">
@@ -35109,7 +35118,7 @@
         <v>1</v>
       </c>
       <c r="P674" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="675" spans="1:16">
@@ -35123,7 +35132,7 @@
         <v>5.931074248482098</v>
       </c>
       <c r="D675" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E675">
         <v>5.817063063996034</v>
@@ -35159,7 +35168,7 @@
         <v>1</v>
       </c>
       <c r="P675" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="676" spans="1:16">
@@ -35173,7 +35182,7 @@
         <v>6.237027624047666</v>
       </c>
       <c r="D676" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E676">
         <v>5.817063063996034</v>
@@ -35209,7 +35218,7 @@
         <v>1</v>
       </c>
       <c r="P676" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="677" spans="1:16">
@@ -35223,7 +35232,7 @@
         <v>5.973422045250139</v>
       </c>
       <c r="D677" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E677">
         <v>5.817063063996034</v>
@@ -35259,7 +35268,7 @@
         <v>1</v>
       </c>
       <c r="P677" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="678" spans="1:16">
@@ -35373,7 +35382,7 @@
         <v>5.839386641650073</v>
       </c>
       <c r="D680" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E680">
         <v>4.893781158276536</v>
@@ -35423,7 +35432,7 @@
         <v>6.148621271038877</v>
       </c>
       <c r="D681" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E681">
         <v>4.893781158276536</v>
@@ -35473,7 +35482,7 @@
         <v>5.873343803641564</v>
       </c>
       <c r="D682" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E682">
         <v>4.893781158276536</v>
@@ -35573,7 +35582,7 @@
         <v>6.049313264972337</v>
       </c>
       <c r="D684" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E684">
         <v>4.936335249131968</v>
@@ -35623,7 +35632,7 @@
         <v>6.175722584965069</v>
       </c>
       <c r="D685" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E685">
         <v>4.936335249131968</v>
@@ -35673,7 +35682,7 @@
         <v>5.760924613317037</v>
       </c>
       <c r="D686" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E686">
         <v>4.936335249131968</v>
@@ -35823,7 +35832,7 @@
         <v>5.905539797299475</v>
       </c>
       <c r="D689" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E689">
         <v>5.270502414665344</v>
@@ -35873,7 +35882,7 @@
         <v>6.021734035283636</v>
       </c>
       <c r="D690" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E690">
         <v>5.270502414665344</v>
@@ -36023,7 +36032,7 @@
         <v>5.810134805942958</v>
       </c>
       <c r="D693" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E693">
         <v>4.46837075668304</v>
@@ -36073,7 +36082,7 @@
         <v>5.919550534467003</v>
       </c>
       <c r="D694" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E694">
         <v>4.46837075668304</v>
@@ -36123,7 +36132,7 @@
         <v>5.597681787127293</v>
       </c>
       <c r="D695" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="E695">
         <v>5.175448484795162</v>
@@ -36173,7 +36182,7 @@
         <v>5.69200276245871</v>
       </c>
       <c r="D696" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="E696">
         <v>5.175448484795162</v>
@@ -36259,7 +36268,7 @@
         <v>1</v>
       </c>
       <c r="P697" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="698" spans="1:16">
@@ -36309,7 +36318,7 @@
         <v>1</v>
       </c>
       <c r="P698" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="699" spans="1:16">
@@ -36359,7 +36368,7 @@
         <v>1</v>
       </c>
       <c r="P699" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="700" spans="1:16">
@@ -36409,7 +36418,7 @@
         <v>1</v>
       </c>
       <c r="P700" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="701" spans="1:16">
@@ -36423,7 +36432,7 @@
         <v>10.58920111380781</v>
       </c>
       <c r="D701" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="E701">
         <v>10.63805069137965</v>
@@ -36459,7 +36468,7 @@
         <v>1</v>
       </c>
       <c r="P701" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="702" spans="1:16">
@@ -36509,7 +36518,7 @@
         <v>1</v>
       </c>
       <c r="P702" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="703" spans="1:16">
@@ -36523,7 +36532,7 @@
         <v>13.29070024337744</v>
       </c>
       <c r="D703" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="E703">
         <v>12.1104855745369</v>
@@ -36559,7 +36568,7 @@
         <v>1</v>
       </c>
       <c r="P703" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="704" spans="1:16">
@@ -36609,7 +36618,7 @@
         <v>1</v>
       </c>
       <c r="P704" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="705" spans="1:16">
@@ -36623,7 +36632,7 @@
         <v>13.05967948318782</v>
       </c>
       <c r="D705" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="E705">
         <v>11.87581437344135</v>
@@ -36659,7 +36668,7 @@
         <v>1</v>
       </c>
       <c r="P705" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="706" spans="1:16">
@@ -36709,7 +36718,7 @@
         <v>1</v>
       </c>
       <c r="P706" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="707" spans="1:16">
@@ -36723,7 +36732,7 @@
         <v>12.8170626988293</v>
       </c>
       <c r="D707" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E707">
         <v>10.97022453374666</v>
@@ -36759,7 +36768,7 @@
         <v>1</v>
       </c>
       <c r="P707" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="708" spans="1:16">
@@ -36809,7 +36818,7 @@
         <v>1</v>
       </c>
       <c r="P708" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="709" spans="1:16">
@@ -36823,7 +36832,7 @@
         <v>12.5987805539735</v>
       </c>
       <c r="D709" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E709">
         <v>10.73863851098768</v>
@@ -36859,7 +36868,7 @@
         <v>1</v>
       </c>
       <c r="P709" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="710" spans="1:16">
@@ -36909,7 +36918,7 @@
         <v>1</v>
       </c>
       <c r="P710" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="711" spans="1:16">
@@ -36959,7 +36968,7 @@
         <v>1</v>
       </c>
       <c r="P711" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="712" spans="1:16">
@@ -37009,7 +37018,7 @@
         <v>1</v>
       </c>
       <c r="P712" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="713" spans="1:16">
@@ -37023,7 +37032,7 @@
         <v>12.45336310880131</v>
       </c>
       <c r="D713" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E713">
         <v>10.58435815154991</v>
@@ -37059,7 +37068,7 @@
         <v>1</v>
       </c>
       <c r="P713" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="714" spans="1:16">
@@ -37109,7 +37118,7 @@
         <v>1</v>
       </c>
       <c r="P714" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="715" spans="1:16">
@@ -37159,7 +37168,7 @@
         <v>1</v>
       </c>
       <c r="P715" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="716" spans="1:16">
@@ -37209,7 +37218,7 @@
         <v>1</v>
       </c>
       <c r="P716" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="717" spans="1:16">
@@ -37259,7 +37268,7 @@
         <v>1</v>
       </c>
       <c r="P717" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="718" spans="1:16">
@@ -37309,7 +37318,7 @@
         <v>1</v>
       </c>
       <c r="P718" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="719" spans="1:16">
@@ -37359,7 +37368,7 @@
         <v>1</v>
       </c>
       <c r="P719" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="720" spans="1:16">
@@ -37373,7 +37382,7 @@
         <v>12.29210392935995</v>
       </c>
       <c r="D720" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E720">
         <v>10.41327053453538</v>
@@ -37409,7 +37418,7 @@
         <v>1</v>
       </c>
       <c r="P720" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="721" spans="1:16">
@@ -37423,7 +37432,7 @@
         <v>9.171282848330055</v>
       </c>
       <c r="D721" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E721">
         <v>6.850968108671186</v>
@@ -37459,7 +37468,7 @@
         <v>1</v>
       </c>
       <c r="P721" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="722" spans="1:16">
@@ -37473,7 +37482,7 @@
         <v>8.830116243154617</v>
       </c>
       <c r="D722" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E722">
         <v>6.850968108671186</v>
@@ -37509,7 +37518,7 @@
         <v>1</v>
       </c>
       <c r="P722" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="723" spans="1:16">
@@ -37673,7 +37682,7 @@
         <v>12.09795277153261</v>
       </c>
       <c r="D726" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E726">
         <v>10.20728623616326</v>
@@ -37723,7 +37732,7 @@
         <v>8.629829382822578</v>
       </c>
       <c r="D727" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E727">
         <v>7.040051561279032</v>
@@ -37809,7 +37818,7 @@
         <v>1</v>
       </c>
       <c r="P728" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="729" spans="1:16">
@@ -37859,7 +37868,7 @@
         <v>1</v>
       </c>
       <c r="P729" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="730" spans="1:16">
@@ -37909,7 +37918,7 @@
         <v>1</v>
       </c>
       <c r="P730" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="731" spans="1:16">
@@ -37923,7 +37932,7 @@
         <v>11.86477339723001</v>
       </c>
       <c r="D731" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E731">
         <v>9.95989502640656</v>
@@ -37959,7 +37968,7 @@
         <v>1</v>
       </c>
       <c r="P731" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="732" spans="1:16">
@@ -37973,7 +37982,7 @@
         <v>8.389280908654889</v>
       </c>
       <c r="D732" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E732">
         <v>6.803093216210396</v>
@@ -38009,7 +38018,7 @@
         <v>1</v>
       </c>
       <c r="P732" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="733" spans="1:16">
@@ -38059,7 +38068,7 @@
         <v>1</v>
       </c>
       <c r="P733" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="734" spans="1:16">
@@ -38109,7 +38118,7 @@
         <v>1</v>
       </c>
       <c r="P734" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="735" spans="1:16">
@@ -38159,7 +38168,7 @@
         <v>1</v>
       </c>
       <c r="P735" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="736" spans="1:16">
@@ -38209,7 +38218,7 @@
         <v>1</v>
       </c>
       <c r="P736" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="737" spans="1:16">
@@ -38223,7 +38232,7 @@
         <v>7.721090409497048</v>
       </c>
       <c r="D737" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="E737">
         <v>6.845979077114176</v>
@@ -38259,7 +38268,7 @@
         <v>1</v>
       </c>
       <c r="P737" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="738" spans="1:16">
@@ -38309,7 +38318,7 @@
         <v>1</v>
       </c>
       <c r="P738" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="739" spans="1:16">
@@ -38359,7 +38368,7 @@
         <v>1</v>
       </c>
       <c r="P739" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="740" spans="1:16">
@@ -38409,7 +38418,7 @@
         <v>1</v>
       </c>
       <c r="P740" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="741" spans="1:16">
@@ -38423,7 +38432,7 @@
         <v>7.431928747420816</v>
       </c>
       <c r="D741" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E741">
         <v>6.954602200047407</v>
@@ -38459,7 +38468,7 @@
         <v>1</v>
       </c>
       <c r="P741" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="742" spans="1:16">
@@ -38509,7 +38518,7 @@
         <v>1</v>
       </c>
       <c r="P742" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="743" spans="1:16">
@@ -38559,7 +38568,7 @@
         <v>1</v>
       </c>
       <c r="P743" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="744" spans="1:16">
@@ -38609,7 +38618,7 @@
         <v>1</v>
       </c>
       <c r="P744" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="745" spans="1:16">
@@ -38659,7 +38668,7 @@
         <v>1</v>
       </c>
       <c r="P745" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="746" spans="1:16">
@@ -38673,7 +38682,7 @@
         <v>7.15411432552343</v>
       </c>
       <c r="D746" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E746">
         <v>7.077702572180645</v>
@@ -38709,7 +38718,7 @@
         <v>1</v>
       </c>
       <c r="P746" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="747" spans="1:16">
@@ -38973,7 +38982,7 @@
         <v>6.656074286112602</v>
       </c>
       <c r="D752" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E752">
         <v>7.106777983579878</v>
@@ -39059,7 +39068,7 @@
         <v>1</v>
       </c>
       <c r="P753" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="754" spans="1:16">
@@ -39109,7 +39118,7 @@
         <v>1</v>
       </c>
       <c r="P754" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="755" spans="1:16">
@@ -39159,7 +39168,7 @@
         <v>1</v>
       </c>
       <c r="P755" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="756" spans="1:16">
@@ -39209,7 +39218,7 @@
         <v>1</v>
       </c>
       <c r="P756" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="757" spans="1:16">
@@ -39259,7 +39268,7 @@
         <v>1</v>
       </c>
       <c r="P757" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="758" spans="1:16">
@@ -39309,7 +39318,7 @@
         <v>1</v>
       </c>
       <c r="P758" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="759" spans="1:16">
@@ -39659,7 +39668,7 @@
         <v>1</v>
       </c>
       <c r="P765" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="766" spans="1:16">
@@ -39709,7 +39718,7 @@
         <v>1</v>
       </c>
       <c r="P766" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="767" spans="1:16">
@@ -39723,7 +39732,7 @@
         <v>5.189787984798581</v>
       </c>
       <c r="D767" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E767">
         <v>6.127393152460147</v>
@@ -39759,7 +39768,7 @@
         <v>1</v>
       </c>
       <c r="P767" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="768" spans="1:16">
@@ -39773,7 +39782,7 @@
         <v>5.337615079752425</v>
       </c>
       <c r="D768" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E768">
         <v>6.127393152460147</v>
@@ -39809,7 +39818,7 @@
         <v>1</v>
       </c>
       <c r="P768" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="769" spans="1:16">
@@ -39923,7 +39932,7 @@
         <v>4.573548410677798</v>
       </c>
       <c r="D771" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E771">
         <v>5.983161604764781</v>
@@ -39973,7 +39982,7 @@
         <v>4.718587091269107</v>
       </c>
       <c r="D772" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E772">
         <v>5.983161604764781</v>
@@ -40059,7 +40068,7 @@
         <v>1</v>
       </c>
       <c r="P773" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="774" spans="1:16">
@@ -40109,7 +40118,7 @@
         <v>1</v>
       </c>
       <c r="P774" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="775" spans="1:16">
@@ -40159,7 +40168,7 @@
         <v>1</v>
       </c>
       <c r="P775" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="776" spans="1:16">
@@ -40209,7 +40218,7 @@
         <v>1</v>
       </c>
       <c r="P776" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="777" spans="1:16">
@@ -40459,7 +40468,7 @@
         <v>1</v>
       </c>
       <c r="P781" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="782" spans="1:16">
@@ -40509,7 +40518,7 @@
         <v>1</v>
       </c>
       <c r="P782" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="783" spans="1:16">
@@ -40559,7 +40568,7 @@
         <v>1</v>
       </c>
       <c r="P783" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="784" spans="1:16">
@@ -40959,7 +40968,7 @@
         <v>1</v>
       </c>
       <c r="P791" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="792" spans="1:16">
@@ -41009,7 +41018,7 @@
         <v>1</v>
       </c>
       <c r="P792" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="793" spans="1:16">
@@ -41059,7 +41068,7 @@
         <v>1</v>
       </c>
       <c r="P793" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="794" spans="1:16">
@@ -41109,7 +41118,7 @@
         <v>1</v>
       </c>
       <c r="P794" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="795" spans="1:16">
@@ -41359,7 +41368,7 @@
         <v>1</v>
       </c>
       <c r="P799" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="800" spans="1:16">
@@ -41373,7 +41382,7 @@
         <v>1.03967143846625</v>
       </c>
       <c r="D800" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E800">
         <v>2.609188567947417</v>
@@ -41409,7 +41418,7 @@
         <v>1</v>
       </c>
       <c r="P800" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="801" spans="1:16">
@@ -41423,7 +41432,7 @@
         <v>0.8130094478294367</v>
       </c>
       <c r="D801" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E801">
         <v>2.609188567947417</v>
@@ -41459,7 +41468,7 @@
         <v>1</v>
       </c>
       <c r="P801" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="802" spans="1:16">
@@ -41509,7 +41518,7 @@
         <v>1</v>
       </c>
       <c r="P802" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="803" spans="1:16">
@@ -41523,7 +41532,7 @@
         <v>0.7465491084079581</v>
       </c>
       <c r="D803" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E803">
         <v>2.329329691737918</v>
@@ -41559,7 +41568,7 @@
         <v>1</v>
       </c>
       <c r="P803" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="804" spans="1:16">
@@ -41573,7 +41582,7 @@
         <v>0.5106027000769942</v>
       </c>
       <c r="D804" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E804">
         <v>2.329329691737918</v>
@@ -41609,7 +41618,7 @@
         <v>1</v>
       </c>
       <c r="P804" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="805" spans="1:16">
@@ -41623,7 +41632,7 @@
         <v>0.4893560218813207</v>
       </c>
       <c r="D805" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E805">
         <v>2.083774301434204</v>
@@ -41673,7 +41682,7 @@
         <v>0.2452632261943108</v>
       </c>
       <c r="D806" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E806">
         <v>2.083774301434204</v>
@@ -41723,7 +41732,7 @@
         <v>3.38720643044401</v>
       </c>
       <c r="D807" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E807">
         <v>1.346565161657761</v>
@@ -41773,7 +41782,7 @@
         <v>0.03330516332946587</v>
       </c>
       <c r="D808" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E808">
         <v>1.648359228337185</v>
@@ -41823,7 +41832,7 @@
         <v>-0.2252326821759354</v>
       </c>
       <c r="D809" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E809">
         <v>1.648359228337185</v>
@@ -41873,7 +41882,7 @@
         <v>2.979030594147371</v>
       </c>
       <c r="D810" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E810">
         <v>0.9008321958333205</v>
@@ -41923,7 +41932,7 @@
         <v>-0.3050434949915584</v>
       </c>
       <c r="D811" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E811">
         <v>1.325320464057839</v>
@@ -41959,7 +41968,7 @@
         <v>1</v>
       </c>
       <c r="P811" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="812" spans="1:16">
@@ -41973,7 +41982,7 @@
         <v>-0.5742982663261245</v>
       </c>
       <c r="D812" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E812">
         <v>1.325320464057839</v>
@@ -42009,7 +42018,7 @@
         <v>1</v>
       </c>
       <c r="P812" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="813" spans="1:16">
@@ -42023,7 +42032,7 @@
         <v>2.676200890003035</v>
       </c>
       <c r="D813" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E813">
         <v>0.570138484533139</v>
@@ -42059,7 +42068,7 @@
         <v>1</v>
       </c>
       <c r="P813" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="814" spans="1:16">
@@ -42073,7 +42082,7 @@
         <v>-1.542729235915701</v>
       </c>
       <c r="D814" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E814">
         <v>0.8740710626510406</v>
@@ -42123,7 +42132,7 @@
         <v>-1.06190425457612</v>
       </c>
       <c r="D815" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E815">
         <v>0.8740710626510406</v>
@@ -42173,7 +42182,7 @@
         <v>2.253181308968607</v>
       </c>
       <c r="D816" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E816">
         <v>0.1081959693489338</v>
@@ -42223,7 +42232,7 @@
         <v>-1.645106114375984</v>
       </c>
       <c r="D817" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E817">
         <v>0.7789101756240804</v>
@@ -42273,7 +42282,7 @@
         <v>-1.164732132500994</v>
       </c>
       <c r="D818" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E818">
         <v>0.7789101756240804</v>
@@ -42323,7 +42332,7 @@
         <v>1.705918320624114</v>
       </c>
       <c r="D819" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E819">
         <v>0.01078008499905536</v>
@@ -42373,7 +42382,7 @@
         <v>2.163973614874138</v>
       </c>
       <c r="D820" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E820">
         <v>0.01078008499905536</v>
@@ -42423,7 +42432,7 @@
         <v>2.083749225749141</v>
       </c>
       <c r="D821" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E821">
         <v>-0.02146380625091737</v>
@@ -42473,7 +42482,7 @@
         <v>-1.354990011712744</v>
       </c>
       <c r="D822" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E822">
         <v>1.048577566205335</v>
@@ -42523,7 +42532,7 @@
         <v>-0.8733379853326184</v>
       </c>
       <c r="D823" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E823">
         <v>1.048577566205335</v>
@@ -42573,7 +42582,7 @@
         <v>1.965361355164372</v>
       </c>
       <c r="D824" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E824">
         <v>0.2868376981059342</v>
@@ -42623,7 +42632,7 @@
         <v>2.41677081798775</v>
       </c>
       <c r="D825" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E825">
         <v>0.2868376981059342</v>
@@ -42673,7 +42682,7 @@
         <v>2.335779602159679</v>
       </c>
       <c r="D826" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E826">
         <v>0.246925539825213</v>
@@ -42723,7 +42732,7 @@
         <v>-1.093559587288276</v>
       </c>
       <c r="D827" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E827">
         <v>-1.564638644835625</v>
@@ -42773,7 +42782,7 @@
         <v>-1.266714738768137</v>
       </c>
       <c r="D828" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E828">
         <v>0.4727739583005963</v>
@@ -42809,7 +42818,7 @@
         <v>1</v>
       </c>
       <c r="P828" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="829" spans="1:16">
@@ -42823,7 +42832,7 @@
         <v>-0.7846738345336348</v>
       </c>
       <c r="D829" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E829">
         <v>0.5188966710041001</v>
@@ -42859,7 +42868,7 @@
         <v>1</v>
       </c>
       <c r="P829" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="830" spans="1:16">
@@ -42873,7 +42882,7 @@
         <v>2.044303559603822</v>
       </c>
       <c r="D830" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E830">
         <v>0.3708353146523429</v>
@@ -42909,7 +42918,7 @@
         <v>1</v>
       </c>
       <c r="P830" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="831" spans="1:16">
@@ -42923,7 +42932,7 @@
         <v>2.412466315043719</v>
       </c>
       <c r="D831" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E831">
         <v>0.3285898892453361</v>
@@ -42959,7 +42968,7 @@
         <v>1</v>
       </c>
       <c r="P831" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="832" spans="1:16">
@@ -42973,7 +42982,7 @@
         <v>-1.016717323262487</v>
       </c>
       <c r="D832" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E832">
         <v>-1.725082876878652</v>
@@ -43009,7 +43018,7 @@
         <v>1</v>
       </c>
       <c r="P832" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="833" spans="1:16">
@@ -43023,7 +43032,7 @@
         <v>-1.012419255686936</v>
       </c>
       <c r="D833" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E833">
         <v>0.7130663861460427</v>
@@ -43073,7 +43082,7 @@
         <v>2.271713176632382</v>
       </c>
       <c r="D834" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E834">
         <v>0.563841217205912</v>
@@ -43123,7 +43132,7 @@
         <v>2.633378514442889</v>
       </c>
       <c r="D835" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E835">
         <v>0.563841217205912</v>
@@ -43173,7 +43182,7 @@
         <v>-0.7953570260957719</v>
       </c>
       <c r="D836" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E836">
         <v>-0.6798364854873604</v>
@@ -43223,7 +43232,7 @@
         <v>-1.154980882524804</v>
       </c>
       <c r="D837" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E837">
         <v>0.3632888214250194</v>
@@ -43259,7 +43268,7 @@
         <v>1</v>
       </c>
       <c r="P837" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="838" spans="1:16">
@@ -43273,7 +43282,7 @@
         <v>2.144224144702488</v>
       </c>
       <c r="D838" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E838">
         <v>0.3406232020973725</v>
@@ -43309,7 +43318,7 @@
         <v>1</v>
       </c>
       <c r="P838" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="839" spans="1:16">
@@ -43323,7 +43332,7 @@
         <v>2.509532026282422</v>
       </c>
       <c r="D839" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E839">
         <v>0.3406232020973725</v>
@@ -43359,7 +43368,7 @@
         <v>1</v>
       </c>
       <c r="P839" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="840" spans="1:16">
@@ -43409,7 +43418,7 @@
         <v>1</v>
       </c>
       <c r="P840" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="841" spans="1:16">
@@ -43423,7 +43432,7 @@
         <v>-0.7435135480053319</v>
       </c>
       <c r="D841" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E841">
         <v>0.7484730002152737</v>
@@ -43573,7 +43582,7 @@
         <v>-0.3742444036399846</v>
       </c>
       <c r="D844" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E844">
         <v>1.094154467958163</v>
@@ -43609,7 +43618,7 @@
         <v>1</v>
       </c>
       <c r="P844" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="845" spans="1:16">
@@ -43659,7 +43668,7 @@
         <v>1</v>
       </c>
       <c r="P845" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="846" spans="1:16">
@@ -43709,7 +43718,7 @@
         <v>1</v>
       </c>
       <c r="P846" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="847" spans="1:16">
@@ -43723,7 +43732,7 @@
         <v>-0.2301600625778306</v>
       </c>
       <c r="D847" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E847">
         <v>1.229035183710177</v>
@@ -43759,7 +43768,7 @@
         <v>1</v>
       </c>
       <c r="P847" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="848" spans="1:16">
@@ -43809,7 +43818,7 @@
         <v>1</v>
       </c>
       <c r="P848" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="849" spans="1:16">
@@ -43859,7 +43868,7 @@
         <v>1</v>
       </c>
       <c r="P849" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="850" spans="1:16">
@@ -43873,7 +43882,7 @@
         <v>-0.008911774850371756</v>
       </c>
       <c r="D850" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="E850">
         <v>0.5721947646345491</v>
@@ -43909,7 +43918,7 @@
         <v>1</v>
       </c>
       <c r="P850" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="851" spans="1:16">
@@ -43923,7 +43932,7 @@
         <v>-0.1112036199752922</v>
       </c>
       <c r="D851" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E851">
         <v>1.340393087027532</v>
@@ -44073,7 +44082,7 @@
         <v>0.09903988671845454</v>
       </c>
       <c r="D854" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="E854">
         <v>1.106317252320714</v>
@@ -44123,7 +44132,7 @@
         <v>-0.06944114310240224</v>
       </c>
       <c r="D855" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E855">
         <v>1.379487916699293</v>
@@ -44159,7 +44168,7 @@
         <v>1</v>
       </c>
       <c r="P855" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="856" spans="1:16">
@@ -44209,7 +44218,7 @@
         <v>1</v>
       </c>
       <c r="P856" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="857" spans="1:16">
@@ -44259,7 +44268,7 @@
         <v>1</v>
       </c>
       <c r="P857" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="858" spans="1:16">
@@ -44273,7 +44282,7 @@
         <v>0.1369388745414319</v>
       </c>
       <c r="D858" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E858">
         <v>1.371101739245933</v>
@@ -44309,7 +44318,7 @@
         <v>1</v>
       </c>
       <c r="P858" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="859" spans="1:16">
@@ -44323,7 +44332,7 @@
         <v>13.70922282990332</v>
       </c>
       <c r="D859" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E859">
         <v>12.65888206048432</v>
@@ -44359,7 +44368,107 @@
         <v>1</v>
       </c>
       <c r="P859" t="s">
-        <v>346</v>
+        <v>348</v>
+      </c>
+    </row>
+    <row r="860" spans="1:16">
+      <c r="A860" s="1">
+        <v>1</v>
+      </c>
+      <c r="B860" t="s">
+        <v>155</v>
+      </c>
+      <c r="C860">
+        <v>12.5976194962981</v>
+      </c>
+      <c r="D860" t="s">
+        <v>267</v>
+      </c>
+      <c r="E860">
+        <v>12.83601616269289</v>
+      </c>
+      <c r="F860">
+        <v>1</v>
+      </c>
+      <c r="G860">
+        <v>0.0493823805037019</v>
+      </c>
+      <c r="H860">
+        <v>0.04852398383730711</v>
+      </c>
+      <c r="I860">
+        <v>0.2383966663947845</v>
+      </c>
+      <c r="J860">
+        <v>0.8436871790688943</v>
+      </c>
+      <c r="K860">
+        <v>21.8</v>
+      </c>
+      <c r="L860">
+        <v>30.99</v>
+      </c>
+      <c r="M860">
+        <v>21.15</v>
+      </c>
+      <c r="N860">
+        <v>30.68</v>
+      </c>
+      <c r="O860">
+        <v>1</v>
+      </c>
+      <c r="P860" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="861" spans="1:16">
+      <c r="A861" s="1">
+        <v>0</v>
+      </c>
+      <c r="B861" t="s">
+        <v>155</v>
+      </c>
+      <c r="C861">
+        <v>12.45873056517934</v>
+      </c>
+      <c r="D861" t="s">
+        <v>267</v>
+      </c>
+      <c r="E861">
+        <v>12.70126841530015</v>
+      </c>
+      <c r="F861">
+        <v>1</v>
+      </c>
+      <c r="G861">
+        <v>0.04952126943482065</v>
+      </c>
+      <c r="H861">
+        <v>0.04865873158469985</v>
+      </c>
+      <c r="I861">
+        <v>0.2425378501208044</v>
+      </c>
+      <c r="J861">
+        <v>0.8500582309550758</v>
+      </c>
+      <c r="K861">
+        <v>21.8</v>
+      </c>
+      <c r="L861">
+        <v>30.99</v>
+      </c>
+      <c r="M861">
+        <v>21.15</v>
+      </c>
+      <c r="N861">
+        <v>30.68</v>
+      </c>
+      <c r="O861">
+        <v>1</v>
+      </c>
+      <c r="P861" t="s">
+        <v>349</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-00763-000063.xlsx
+++ b/s60_signal/position-00763-000063.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2595" uniqueCount="350">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2601" uniqueCount="351">
   <si>
     <t>trade_time</t>
   </si>
@@ -817,6 +817,9 @@
     <t>2021-11-26</t>
   </si>
   <si>
+    <t>2021-12-01</t>
+  </si>
+  <si>
     <t>2021-11-30</t>
   </si>
   <si>
@@ -1421,7 +1424,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P861"/>
+  <dimension ref="A1:P863"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -1518,7 +1521,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -1568,7 +1571,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -1618,7 +1621,7 @@
         <v>1</v>
       </c>
       <c r="P4" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -1668,7 +1671,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -1718,7 +1721,7 @@
         <v>1</v>
       </c>
       <c r="P6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -1768,7 +1771,7 @@
         <v>1</v>
       </c>
       <c r="P7" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -1818,7 +1821,7 @@
         <v>1</v>
       </c>
       <c r="P8" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -1868,7 +1871,7 @@
         <v>1</v>
       </c>
       <c r="P9" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -1918,7 +1921,7 @@
         <v>1</v>
       </c>
       <c r="P10" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -1968,7 +1971,7 @@
         <v>1</v>
       </c>
       <c r="P11" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -2018,7 +2021,7 @@
         <v>1</v>
       </c>
       <c r="P12" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -2068,7 +2071,7 @@
         <v>1</v>
       </c>
       <c r="P13" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -2118,7 +2121,7 @@
         <v>1</v>
       </c>
       <c r="P14" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -2168,7 +2171,7 @@
         <v>1</v>
       </c>
       <c r="P15" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -2218,7 +2221,7 @@
         <v>1</v>
       </c>
       <c r="P16" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -2268,7 +2271,7 @@
         <v>1</v>
       </c>
       <c r="P17" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -2318,7 +2321,7 @@
         <v>1</v>
       </c>
       <c r="P18" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -2368,7 +2371,7 @@
         <v>1</v>
       </c>
       <c r="P19" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="20" spans="1:16">
@@ -2418,7 +2421,7 @@
         <v>1</v>
       </c>
       <c r="P20" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -2468,7 +2471,7 @@
         <v>1</v>
       </c>
       <c r="P21" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -2518,7 +2521,7 @@
         <v>1</v>
       </c>
       <c r="P22" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="23" spans="1:16">
@@ -2618,7 +2621,7 @@
         <v>1</v>
       </c>
       <c r="P24" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="25" spans="1:16">
@@ -2668,7 +2671,7 @@
         <v>1</v>
       </c>
       <c r="P25" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="26" spans="1:16">
@@ -2718,7 +2721,7 @@
         <v>1</v>
       </c>
       <c r="P26" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="27" spans="1:16">
@@ -2768,7 +2771,7 @@
         <v>1</v>
       </c>
       <c r="P27" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="28" spans="1:16">
@@ -2818,7 +2821,7 @@
         <v>1</v>
       </c>
       <c r="P28" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -2868,7 +2871,7 @@
         <v>1</v>
       </c>
       <c r="P29" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -3168,7 +3171,7 @@
         <v>1</v>
       </c>
       <c r="P35" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -3218,7 +3221,7 @@
         <v>1</v>
       </c>
       <c r="P36" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="37" spans="1:16">
@@ -3268,7 +3271,7 @@
         <v>1</v>
       </c>
       <c r="P37" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="38" spans="1:16">
@@ -3318,7 +3321,7 @@
         <v>1</v>
       </c>
       <c r="P38" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="39" spans="1:16">
@@ -3368,7 +3371,7 @@
         <v>1</v>
       </c>
       <c r="P39" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="40" spans="1:16">
@@ -3418,7 +3421,7 @@
         <v>1</v>
       </c>
       <c r="P40" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="41" spans="1:16">
@@ -3468,7 +3471,7 @@
         <v>1</v>
       </c>
       <c r="P41" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="42" spans="1:16">
@@ -3518,7 +3521,7 @@
         <v>1</v>
       </c>
       <c r="P42" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="43" spans="1:16">
@@ -3568,7 +3571,7 @@
         <v>1</v>
       </c>
       <c r="P43" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="44" spans="1:16">
@@ -3618,7 +3621,7 @@
         <v>1</v>
       </c>
       <c r="P44" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -3868,7 +3871,7 @@
         <v>1</v>
       </c>
       <c r="P49" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="50" spans="1:16">
@@ -3918,7 +3921,7 @@
         <v>1</v>
       </c>
       <c r="P50" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="51" spans="1:16">
@@ -3968,7 +3971,7 @@
         <v>1</v>
       </c>
       <c r="P51" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="52" spans="1:16">
@@ -4018,7 +4021,7 @@
         <v>1</v>
       </c>
       <c r="P52" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="53" spans="1:16">
@@ -4068,7 +4071,7 @@
         <v>1</v>
       </c>
       <c r="P53" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="54" spans="1:16">
@@ -4118,7 +4121,7 @@
         <v>1</v>
       </c>
       <c r="P54" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="55" spans="1:16">
@@ -4168,7 +4171,7 @@
         <v>1</v>
       </c>
       <c r="P55" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="56" spans="1:16">
@@ -4518,7 +4521,7 @@
         <v>1</v>
       </c>
       <c r="P62" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="63" spans="1:16">
@@ -4568,7 +4571,7 @@
         <v>1</v>
       </c>
       <c r="P63" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="64" spans="1:16">
@@ -4618,7 +4621,7 @@
         <v>1</v>
       </c>
       <c r="P64" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="65" spans="1:16">
@@ -4668,7 +4671,7 @@
         <v>1</v>
       </c>
       <c r="P65" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="66" spans="1:16">
@@ -4718,7 +4721,7 @@
         <v>1</v>
       </c>
       <c r="P66" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="67" spans="1:16">
@@ -4768,7 +4771,7 @@
         <v>1</v>
       </c>
       <c r="P67" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="68" spans="1:16">
@@ -4818,7 +4821,7 @@
         <v>1</v>
       </c>
       <c r="P68" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="69" spans="1:16">
@@ -4868,7 +4871,7 @@
         <v>1</v>
       </c>
       <c r="P69" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="70" spans="1:16">
@@ -4918,7 +4921,7 @@
         <v>1</v>
       </c>
       <c r="P70" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="71" spans="1:16">
@@ -4968,7 +4971,7 @@
         <v>1</v>
       </c>
       <c r="P71" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="72" spans="1:16">
@@ -5018,7 +5021,7 @@
         <v>1</v>
       </c>
       <c r="P72" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="73" spans="1:16">
@@ -5068,7 +5071,7 @@
         <v>1</v>
       </c>
       <c r="P73" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="74" spans="1:16">
@@ -5718,7 +5721,7 @@
         <v>1</v>
       </c>
       <c r="P86" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="87" spans="1:16">
@@ -5768,7 +5771,7 @@
         <v>1</v>
       </c>
       <c r="P87" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="88" spans="1:16">
@@ -5818,7 +5821,7 @@
         <v>1</v>
       </c>
       <c r="P88" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="89" spans="1:16">
@@ -5868,7 +5871,7 @@
         <v>1</v>
       </c>
       <c r="P89" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="90" spans="1:16">
@@ -5918,7 +5921,7 @@
         <v>1</v>
       </c>
       <c r="P90" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="91" spans="1:16">
@@ -5968,7 +5971,7 @@
         <v>1</v>
       </c>
       <c r="P91" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="92" spans="1:16">
@@ -6168,7 +6171,7 @@
         <v>1</v>
       </c>
       <c r="P95" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="96" spans="1:16">
@@ -6218,7 +6221,7 @@
         <v>1</v>
       </c>
       <c r="P96" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="97" spans="1:16">
@@ -6268,7 +6271,7 @@
         <v>1</v>
       </c>
       <c r="P97" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="98" spans="1:16">
@@ -6318,7 +6321,7 @@
         <v>1</v>
       </c>
       <c r="P98" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="99" spans="1:16">
@@ -6368,7 +6371,7 @@
         <v>1</v>
       </c>
       <c r="P99" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="100" spans="1:16">
@@ -6418,7 +6421,7 @@
         <v>1</v>
       </c>
       <c r="P100" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="101" spans="1:16">
@@ -6468,7 +6471,7 @@
         <v>1</v>
       </c>
       <c r="P101" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="102" spans="1:16">
@@ -6518,7 +6521,7 @@
         <v>1</v>
       </c>
       <c r="P102" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="103" spans="1:16">
@@ -6618,7 +6621,7 @@
         <v>1</v>
       </c>
       <c r="P104" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="105" spans="1:16">
@@ -6668,7 +6671,7 @@
         <v>1</v>
       </c>
       <c r="P105" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="106" spans="1:16">
@@ -6718,7 +6721,7 @@
         <v>1</v>
       </c>
       <c r="P106" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="107" spans="1:16">
@@ -6768,7 +6771,7 @@
         <v>1</v>
       </c>
       <c r="P107" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="108" spans="1:16">
@@ -6818,7 +6821,7 @@
         <v>1</v>
       </c>
       <c r="P108" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="109" spans="1:16">
@@ -6868,7 +6871,7 @@
         <v>1</v>
       </c>
       <c r="P109" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="110" spans="1:16">
@@ -6918,7 +6921,7 @@
         <v>1</v>
       </c>
       <c r="P110" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="111" spans="1:16">
@@ -6968,7 +6971,7 @@
         <v>1</v>
       </c>
       <c r="P111" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="112" spans="1:16">
@@ -7018,7 +7021,7 @@
         <v>1</v>
       </c>
       <c r="P112" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="113" spans="1:16">
@@ -7068,7 +7071,7 @@
         <v>1</v>
       </c>
       <c r="P113" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="114" spans="1:16">
@@ -7118,7 +7121,7 @@
         <v>1</v>
       </c>
       <c r="P114" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="115" spans="1:16">
@@ -7168,7 +7171,7 @@
         <v>1</v>
       </c>
       <c r="P115" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="116" spans="1:16">
@@ -7218,7 +7221,7 @@
         <v>1</v>
       </c>
       <c r="P116" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="117" spans="1:16">
@@ -7268,7 +7271,7 @@
         <v>1</v>
       </c>
       <c r="P117" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="118" spans="1:16">
@@ -7318,7 +7321,7 @@
         <v>1</v>
       </c>
       <c r="P118" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="119" spans="1:16">
@@ -7368,7 +7371,7 @@
         <v>1</v>
       </c>
       <c r="P119" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="120" spans="1:16">
@@ -8868,7 +8871,7 @@
         <v>1</v>
       </c>
       <c r="P149" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="150" spans="1:16">
@@ -8918,7 +8921,7 @@
         <v>1</v>
       </c>
       <c r="P150" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="151" spans="1:16">
@@ -8968,7 +8971,7 @@
         <v>1</v>
       </c>
       <c r="P151" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="152" spans="1:16">
@@ -9018,7 +9021,7 @@
         <v>1</v>
       </c>
       <c r="P152" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="153" spans="1:16">
@@ -9068,7 +9071,7 @@
         <v>1</v>
       </c>
       <c r="P153" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="154" spans="1:16">
@@ -9118,7 +9121,7 @@
         <v>1</v>
       </c>
       <c r="P154" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="155" spans="1:16">
@@ -9168,7 +9171,7 @@
         <v>1</v>
       </c>
       <c r="P155" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="156" spans="1:16">
@@ -9218,7 +9221,7 @@
         <v>1</v>
       </c>
       <c r="P156" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="157" spans="1:16">
@@ -9268,7 +9271,7 @@
         <v>1</v>
       </c>
       <c r="P157" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="158" spans="1:16">
@@ -9418,7 +9421,7 @@
         <v>1</v>
       </c>
       <c r="P160" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="161" spans="1:16">
@@ -9468,7 +9471,7 @@
         <v>1</v>
       </c>
       <c r="P161" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="162" spans="1:16">
@@ -9518,7 +9521,7 @@
         <v>1</v>
       </c>
       <c r="P162" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="163" spans="1:16">
@@ -9568,7 +9571,7 @@
         <v>1</v>
       </c>
       <c r="P163" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="164" spans="1:16">
@@ -9718,7 +9721,7 @@
         <v>1</v>
       </c>
       <c r="P166" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="167" spans="1:16">
@@ -9768,7 +9771,7 @@
         <v>1</v>
       </c>
       <c r="P167" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="168" spans="1:16">
@@ -9818,7 +9821,7 @@
         <v>1</v>
       </c>
       <c r="P168" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="169" spans="1:16">
@@ -9868,7 +9871,7 @@
         <v>1</v>
       </c>
       <c r="P169" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="170" spans="1:16">
@@ -10318,7 +10321,7 @@
         <v>1</v>
       </c>
       <c r="P178" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="179" spans="1:16">
@@ -17918,7 +17921,7 @@
         <v>1</v>
       </c>
       <c r="P330" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="331" spans="1:16">
@@ -17968,7 +17971,7 @@
         <v>1</v>
       </c>
       <c r="P331" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="332" spans="1:16">
@@ -18018,7 +18021,7 @@
         <v>1</v>
       </c>
       <c r="P332" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="333" spans="1:16">
@@ -18068,7 +18071,7 @@
         <v>1</v>
       </c>
       <c r="P333" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="334" spans="1:16">
@@ -18118,7 +18121,7 @@
         <v>1</v>
       </c>
       <c r="P334" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="335" spans="1:16">
@@ -20918,7 +20921,7 @@
         <v>1</v>
       </c>
       <c r="P390" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="391" spans="1:16">
@@ -20968,7 +20971,7 @@
         <v>1</v>
       </c>
       <c r="P391" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="392" spans="1:16">
@@ -21018,7 +21021,7 @@
         <v>1</v>
       </c>
       <c r="P392" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="393" spans="1:16">
@@ -21068,7 +21071,7 @@
         <v>1</v>
       </c>
       <c r="P393" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="394" spans="1:16">
@@ -21118,7 +21121,7 @@
         <v>1</v>
       </c>
       <c r="P394" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="395" spans="1:16">
@@ -21168,7 +21171,7 @@
         <v>1</v>
       </c>
       <c r="P395" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="396" spans="1:16">
@@ -21218,7 +21221,7 @@
         <v>1</v>
       </c>
       <c r="P396" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="397" spans="1:16">
@@ -21268,7 +21271,7 @@
         <v>1</v>
       </c>
       <c r="P397" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="398" spans="1:16">
@@ -21318,7 +21321,7 @@
         <v>1</v>
       </c>
       <c r="P398" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="399" spans="1:16">
@@ -21368,7 +21371,7 @@
         <v>1</v>
       </c>
       <c r="P399" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="400" spans="1:16">
@@ -21418,7 +21421,7 @@
         <v>1</v>
       </c>
       <c r="P400" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="401" spans="1:16">
@@ -21468,7 +21471,7 @@
         <v>1</v>
       </c>
       <c r="P401" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="402" spans="1:16">
@@ -21518,7 +21521,7 @@
         <v>1</v>
       </c>
       <c r="P402" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="403" spans="1:16">
@@ -21568,7 +21571,7 @@
         <v>1</v>
       </c>
       <c r="P403" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="404" spans="1:16">
@@ -21618,7 +21621,7 @@
         <v>1</v>
       </c>
       <c r="P404" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="405" spans="1:16">
@@ -21668,7 +21671,7 @@
         <v>1</v>
       </c>
       <c r="P405" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="406" spans="1:16">
@@ -21718,7 +21721,7 @@
         <v>1</v>
       </c>
       <c r="P406" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="407" spans="1:16">
@@ -21768,7 +21771,7 @@
         <v>1</v>
       </c>
       <c r="P407" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="408" spans="1:16">
@@ -22418,7 +22421,7 @@
         <v>1</v>
       </c>
       <c r="P420" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="421" spans="1:16">
@@ -22468,7 +22471,7 @@
         <v>1</v>
       </c>
       <c r="P421" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="422" spans="1:16">
@@ -22518,7 +22521,7 @@
         <v>1</v>
       </c>
       <c r="P422" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="423" spans="1:16">
@@ -22568,7 +22571,7 @@
         <v>1</v>
       </c>
       <c r="P423" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="424" spans="1:16">
@@ -22618,7 +22621,7 @@
         <v>1</v>
       </c>
       <c r="P424" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="425" spans="1:16">
@@ -22668,7 +22671,7 @@
         <v>1</v>
       </c>
       <c r="P425" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="426" spans="1:16">
@@ -23668,7 +23671,7 @@
         <v>1</v>
       </c>
       <c r="P445" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="446" spans="1:16">
@@ -23718,7 +23721,7 @@
         <v>1</v>
       </c>
       <c r="P446" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="447" spans="1:16">
@@ -23768,7 +23771,7 @@
         <v>1</v>
       </c>
       <c r="P447" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="448" spans="1:16">
@@ -23818,7 +23821,7 @@
         <v>1</v>
       </c>
       <c r="P448" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="449" spans="1:16">
@@ -23868,7 +23871,7 @@
         <v>1</v>
       </c>
       <c r="P449" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="450" spans="1:16">
@@ -23918,7 +23921,7 @@
         <v>1</v>
       </c>
       <c r="P450" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="451" spans="1:16">
@@ -23968,7 +23971,7 @@
         <v>1</v>
       </c>
       <c r="P451" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="452" spans="1:16">
@@ -24018,7 +24021,7 @@
         <v>1</v>
       </c>
       <c r="P452" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="453" spans="1:16">
@@ -24068,7 +24071,7 @@
         <v>1</v>
       </c>
       <c r="P453" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="454" spans="1:16">
@@ -24118,7 +24121,7 @@
         <v>1</v>
       </c>
       <c r="P454" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="455" spans="1:16">
@@ -27318,7 +27321,7 @@
         <v>1</v>
       </c>
       <c r="P518" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="519" spans="1:16">
@@ -27368,7 +27371,7 @@
         <v>1</v>
       </c>
       <c r="P519" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="520" spans="1:16">
@@ -27418,7 +27421,7 @@
         <v>1</v>
       </c>
       <c r="P520" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="521" spans="1:16">
@@ -27468,7 +27471,7 @@
         <v>1</v>
       </c>
       <c r="P521" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="522" spans="1:16">
@@ -27518,7 +27521,7 @@
         <v>1</v>
       </c>
       <c r="P522" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="523" spans="1:16">
@@ -27568,7 +27571,7 @@
         <v>1</v>
       </c>
       <c r="P523" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="524" spans="1:16">
@@ -27618,7 +27621,7 @@
         <v>1</v>
       </c>
       <c r="P524" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="525" spans="1:16">
@@ -27668,7 +27671,7 @@
         <v>1</v>
       </c>
       <c r="P525" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="526" spans="1:16">
@@ -27718,7 +27721,7 @@
         <v>1</v>
       </c>
       <c r="P526" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="527" spans="1:16">
@@ -27768,7 +27771,7 @@
         <v>1</v>
       </c>
       <c r="P527" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="528" spans="1:16">
@@ -27818,7 +27821,7 @@
         <v>1</v>
       </c>
       <c r="P528" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="529" spans="1:16">
@@ -27868,7 +27871,7 @@
         <v>1</v>
       </c>
       <c r="P529" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="530" spans="1:16">
@@ -27918,7 +27921,7 @@
         <v>1</v>
       </c>
       <c r="P530" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="531" spans="1:16">
@@ -27968,7 +27971,7 @@
         <v>1</v>
       </c>
       <c r="P531" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="532" spans="1:16">
@@ -28018,7 +28021,7 @@
         <v>1</v>
       </c>
       <c r="P532" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="533" spans="1:16">
@@ -28068,7 +28071,7 @@
         <v>1</v>
       </c>
       <c r="P533" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="534" spans="1:16">
@@ -28118,7 +28121,7 @@
         <v>1</v>
       </c>
       <c r="P534" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="535" spans="1:16">
@@ -28168,7 +28171,7 @@
         <v>1</v>
       </c>
       <c r="P535" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="536" spans="1:16">
@@ -28218,7 +28221,7 @@
         <v>1</v>
       </c>
       <c r="P536" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="537" spans="1:16">
@@ -28268,7 +28271,7 @@
         <v>1</v>
       </c>
       <c r="P537" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="538" spans="1:16">
@@ -28318,7 +28321,7 @@
         <v>1</v>
       </c>
       <c r="P538" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="539" spans="1:16">
@@ -28368,7 +28371,7 @@
         <v>1</v>
       </c>
       <c r="P539" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="540" spans="1:16">
@@ -28418,7 +28421,7 @@
         <v>1</v>
       </c>
       <c r="P540" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="541" spans="1:16">
@@ -28468,7 +28471,7 @@
         <v>1</v>
       </c>
       <c r="P541" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="542" spans="1:16">
@@ -28518,7 +28521,7 @@
         <v>1</v>
       </c>
       <c r="P542" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="543" spans="1:16">
@@ -28568,7 +28571,7 @@
         <v>1</v>
       </c>
       <c r="P543" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="544" spans="1:16">
@@ -28618,7 +28621,7 @@
         <v>1</v>
       </c>
       <c r="P544" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="545" spans="1:16">
@@ -28668,7 +28671,7 @@
         <v>1</v>
       </c>
       <c r="P545" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="546" spans="1:16">
@@ -28718,7 +28721,7 @@
         <v>1</v>
       </c>
       <c r="P546" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="547" spans="1:16">
@@ -28768,7 +28771,7 @@
         <v>1</v>
       </c>
       <c r="P547" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="548" spans="1:16">
@@ -28818,7 +28821,7 @@
         <v>1</v>
       </c>
       <c r="P548" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="549" spans="1:16">
@@ -28868,7 +28871,7 @@
         <v>1</v>
       </c>
       <c r="P549" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="550" spans="1:16">
@@ -28918,7 +28921,7 @@
         <v>1</v>
       </c>
       <c r="P550" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="551" spans="1:16">
@@ -28968,7 +28971,7 @@
         <v>1</v>
       </c>
       <c r="P551" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="552" spans="1:16">
@@ -29018,7 +29021,7 @@
         <v>1</v>
       </c>
       <c r="P552" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="553" spans="1:16">
@@ -29068,7 +29071,7 @@
         <v>1</v>
       </c>
       <c r="P553" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="554" spans="1:16">
@@ -29118,7 +29121,7 @@
         <v>1</v>
       </c>
       <c r="P554" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="555" spans="1:16">
@@ -29168,7 +29171,7 @@
         <v>1</v>
       </c>
       <c r="P555" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="556" spans="1:16">
@@ -29218,7 +29221,7 @@
         <v>1</v>
       </c>
       <c r="P556" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="557" spans="1:16">
@@ -29268,7 +29271,7 @@
         <v>1</v>
       </c>
       <c r="P557" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="558" spans="1:16">
@@ -29318,7 +29321,7 @@
         <v>1</v>
       </c>
       <c r="P558" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="559" spans="1:16">
@@ -29568,7 +29571,7 @@
         <v>1</v>
       </c>
       <c r="P563" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="564" spans="1:16">
@@ -29618,7 +29621,7 @@
         <v>1</v>
       </c>
       <c r="P564" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="565" spans="1:16">
@@ -29668,7 +29671,7 @@
         <v>1</v>
       </c>
       <c r="P565" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="566" spans="1:16">
@@ -29718,7 +29721,7 @@
         <v>1</v>
       </c>
       <c r="P566" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="567" spans="1:16">
@@ -30268,7 +30271,7 @@
         <v>1</v>
       </c>
       <c r="P577" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="578" spans="1:16">
@@ -30318,7 +30321,7 @@
         <v>1</v>
       </c>
       <c r="P578" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="579" spans="1:16">
@@ -30368,7 +30371,7 @@
         <v>1</v>
       </c>
       <c r="P579" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="580" spans="1:16">
@@ -30418,7 +30421,7 @@
         <v>1</v>
       </c>
       <c r="P580" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="581" spans="1:16">
@@ -30468,7 +30471,7 @@
         <v>1</v>
       </c>
       <c r="P581" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="582" spans="1:16">
@@ -30518,7 +30521,7 @@
         <v>1</v>
       </c>
       <c r="P582" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="583" spans="1:16">
@@ -30568,7 +30571,7 @@
         <v>1</v>
       </c>
       <c r="P583" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="584" spans="1:16">
@@ -30618,7 +30621,7 @@
         <v>1</v>
       </c>
       <c r="P584" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="585" spans="1:16">
@@ -30668,7 +30671,7 @@
         <v>1</v>
       </c>
       <c r="P585" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="586" spans="1:16">
@@ -30718,7 +30721,7 @@
         <v>1</v>
       </c>
       <c r="P586" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="587" spans="1:16">
@@ -30768,7 +30771,7 @@
         <v>1</v>
       </c>
       <c r="P587" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="588" spans="1:16">
@@ -30818,7 +30821,7 @@
         <v>1</v>
       </c>
       <c r="P588" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="589" spans="1:16">
@@ -30868,7 +30871,7 @@
         <v>1</v>
       </c>
       <c r="P589" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="590" spans="1:16">
@@ -30918,7 +30921,7 @@
         <v>1</v>
       </c>
       <c r="P590" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="591" spans="1:16">
@@ -31168,7 +31171,7 @@
         <v>1</v>
       </c>
       <c r="P595" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="596" spans="1:16">
@@ -31218,7 +31221,7 @@
         <v>1</v>
       </c>
       <c r="P596" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="597" spans="1:16">
@@ -31268,7 +31271,7 @@
         <v>1</v>
       </c>
       <c r="P597" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="598" spans="1:16">
@@ -31318,7 +31321,7 @@
         <v>1</v>
       </c>
       <c r="P598" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="599" spans="1:16">
@@ -31368,7 +31371,7 @@
         <v>1</v>
       </c>
       <c r="P599" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="600" spans="1:16">
@@ -31418,7 +31421,7 @@
         <v>1</v>
       </c>
       <c r="P600" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="601" spans="1:16">
@@ -31718,7 +31721,7 @@
         <v>1</v>
       </c>
       <c r="P606" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="607" spans="1:16">
@@ -31768,7 +31771,7 @@
         <v>1</v>
       </c>
       <c r="P607" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="608" spans="1:16">
@@ -31818,7 +31821,7 @@
         <v>1</v>
       </c>
       <c r="P608" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="609" spans="1:16">
@@ -31868,7 +31871,7 @@
         <v>1</v>
       </c>
       <c r="P609" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="610" spans="1:16">
@@ -31918,7 +31921,7 @@
         <v>1</v>
       </c>
       <c r="P610" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="611" spans="1:16">
@@ -32568,7 +32571,7 @@
         <v>1</v>
       </c>
       <c r="P623" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="624" spans="1:16">
@@ -32618,7 +32621,7 @@
         <v>1</v>
       </c>
       <c r="P624" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="625" spans="1:16">
@@ -32668,7 +32671,7 @@
         <v>1</v>
       </c>
       <c r="P625" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="626" spans="1:16">
@@ -32718,7 +32721,7 @@
         <v>1</v>
       </c>
       <c r="P626" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="627" spans="1:16">
@@ -32768,7 +32771,7 @@
         <v>1</v>
       </c>
       <c r="P627" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="628" spans="1:16">
@@ -32818,7 +32821,7 @@
         <v>1</v>
       </c>
       <c r="P628" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="629" spans="1:16">
@@ -32868,7 +32871,7 @@
         <v>1</v>
       </c>
       <c r="P629" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="630" spans="1:16">
@@ -32918,7 +32921,7 @@
         <v>1</v>
       </c>
       <c r="P630" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="631" spans="1:16">
@@ -32968,7 +32971,7 @@
         <v>1</v>
       </c>
       <c r="P631" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="632" spans="1:16">
@@ -33018,7 +33021,7 @@
         <v>1</v>
       </c>
       <c r="P632" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="633" spans="1:16">
@@ -33068,7 +33071,7 @@
         <v>1</v>
       </c>
       <c r="P633" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="634" spans="1:16">
@@ -33118,7 +33121,7 @@
         <v>1</v>
       </c>
       <c r="P634" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="635" spans="1:16">
@@ -33168,7 +33171,7 @@
         <v>1</v>
       </c>
       <c r="P635" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="636" spans="1:16">
@@ -33218,7 +33221,7 @@
         <v>1</v>
       </c>
       <c r="P636" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="637" spans="1:16">
@@ -33268,7 +33271,7 @@
         <v>1</v>
       </c>
       <c r="P637" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="638" spans="1:16">
@@ -33318,7 +33321,7 @@
         <v>1</v>
       </c>
       <c r="P638" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="639" spans="1:16">
@@ -33368,7 +33371,7 @@
         <v>1</v>
       </c>
       <c r="P639" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="640" spans="1:16">
@@ -33418,7 +33421,7 @@
         <v>1</v>
       </c>
       <c r="P640" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="641" spans="1:16">
@@ -33468,7 +33471,7 @@
         <v>1</v>
       </c>
       <c r="P641" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="642" spans="1:16">
@@ -33518,7 +33521,7 @@
         <v>1</v>
       </c>
       <c r="P642" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="643" spans="1:16">
@@ -33568,7 +33571,7 @@
         <v>1</v>
       </c>
       <c r="P643" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="644" spans="1:16">
@@ -33618,7 +33621,7 @@
         <v>1</v>
       </c>
       <c r="P644" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="645" spans="1:16">
@@ -33668,7 +33671,7 @@
         <v>1</v>
       </c>
       <c r="P645" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="646" spans="1:16">
@@ -33718,7 +33721,7 @@
         <v>1</v>
       </c>
       <c r="P646" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="647" spans="1:16">
@@ -33918,7 +33921,7 @@
         <v>1</v>
       </c>
       <c r="P650" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="651" spans="1:16">
@@ -33968,7 +33971,7 @@
         <v>1</v>
       </c>
       <c r="P651" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="652" spans="1:16">
@@ -34018,7 +34021,7 @@
         <v>1</v>
       </c>
       <c r="P652" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="653" spans="1:16">
@@ -34368,7 +34371,7 @@
         <v>1</v>
       </c>
       <c r="P659" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="660" spans="1:16">
@@ -34418,7 +34421,7 @@
         <v>1</v>
       </c>
       <c r="P660" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="661" spans="1:16">
@@ -34468,7 +34471,7 @@
         <v>1</v>
       </c>
       <c r="P661" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="662" spans="1:16">
@@ -34518,7 +34521,7 @@
         <v>1</v>
       </c>
       <c r="P662" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="663" spans="1:16">
@@ -36268,7 +36271,7 @@
         <v>1</v>
       </c>
       <c r="P697" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="698" spans="1:16">
@@ -36318,7 +36321,7 @@
         <v>1</v>
       </c>
       <c r="P698" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="699" spans="1:16">
@@ -36368,7 +36371,7 @@
         <v>1</v>
       </c>
       <c r="P699" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="700" spans="1:16">
@@ -36418,7 +36421,7 @@
         <v>1</v>
       </c>
       <c r="P700" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="701" spans="1:16">
@@ -36468,7 +36471,7 @@
         <v>1</v>
       </c>
       <c r="P701" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="702" spans="1:16">
@@ -36518,7 +36521,7 @@
         <v>1</v>
       </c>
       <c r="P702" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="703" spans="1:16">
@@ -36568,7 +36571,7 @@
         <v>1</v>
       </c>
       <c r="P703" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="704" spans="1:16">
@@ -36618,7 +36621,7 @@
         <v>1</v>
       </c>
       <c r="P704" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="705" spans="1:16">
@@ -36668,7 +36671,7 @@
         <v>1</v>
       </c>
       <c r="P705" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="706" spans="1:16">
@@ -36718,7 +36721,7 @@
         <v>1</v>
       </c>
       <c r="P706" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="707" spans="1:16">
@@ -36768,7 +36771,7 @@
         <v>1</v>
       </c>
       <c r="P707" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="708" spans="1:16">
@@ -36818,7 +36821,7 @@
         <v>1</v>
       </c>
       <c r="P708" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="709" spans="1:16">
@@ -36868,7 +36871,7 @@
         <v>1</v>
       </c>
       <c r="P709" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="710" spans="1:16">
@@ -36918,7 +36921,7 @@
         <v>1</v>
       </c>
       <c r="P710" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="711" spans="1:16">
@@ -36968,7 +36971,7 @@
         <v>1</v>
       </c>
       <c r="P711" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="712" spans="1:16">
@@ -37018,7 +37021,7 @@
         <v>1</v>
       </c>
       <c r="P712" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="713" spans="1:16">
@@ -37068,7 +37071,7 @@
         <v>1</v>
       </c>
       <c r="P713" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="714" spans="1:16">
@@ -37118,7 +37121,7 @@
         <v>1</v>
       </c>
       <c r="P714" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="715" spans="1:16">
@@ -37168,7 +37171,7 @@
         <v>1</v>
       </c>
       <c r="P715" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="716" spans="1:16">
@@ -37218,7 +37221,7 @@
         <v>1</v>
       </c>
       <c r="P716" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="717" spans="1:16">
@@ -37268,7 +37271,7 @@
         <v>1</v>
       </c>
       <c r="P717" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="718" spans="1:16">
@@ -37318,7 +37321,7 @@
         <v>1</v>
       </c>
       <c r="P718" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="719" spans="1:16">
@@ -37368,7 +37371,7 @@
         <v>1</v>
       </c>
       <c r="P719" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="720" spans="1:16">
@@ -37418,7 +37421,7 @@
         <v>1</v>
       </c>
       <c r="P720" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="721" spans="1:16">
@@ -37468,7 +37471,7 @@
         <v>1</v>
       </c>
       <c r="P721" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="722" spans="1:16">
@@ -37518,7 +37521,7 @@
         <v>1</v>
       </c>
       <c r="P722" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="723" spans="1:16">
@@ -37818,7 +37821,7 @@
         <v>1</v>
       </c>
       <c r="P728" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="729" spans="1:16">
@@ -37868,7 +37871,7 @@
         <v>1</v>
       </c>
       <c r="P729" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="730" spans="1:16">
@@ -37918,7 +37921,7 @@
         <v>1</v>
       </c>
       <c r="P730" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="731" spans="1:16">
@@ -37968,7 +37971,7 @@
         <v>1</v>
       </c>
       <c r="P731" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="732" spans="1:16">
@@ -38018,7 +38021,7 @@
         <v>1</v>
       </c>
       <c r="P732" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="733" spans="1:16">
@@ -38068,7 +38071,7 @@
         <v>1</v>
       </c>
       <c r="P733" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="734" spans="1:16">
@@ -38118,7 +38121,7 @@
         <v>1</v>
       </c>
       <c r="P734" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="735" spans="1:16">
@@ -38168,7 +38171,7 @@
         <v>1</v>
       </c>
       <c r="P735" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="736" spans="1:16">
@@ -38218,7 +38221,7 @@
         <v>1</v>
       </c>
       <c r="P736" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="737" spans="1:16">
@@ -38268,7 +38271,7 @@
         <v>1</v>
       </c>
       <c r="P737" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="738" spans="1:16">
@@ -38318,7 +38321,7 @@
         <v>1</v>
       </c>
       <c r="P738" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="739" spans="1:16">
@@ -38368,7 +38371,7 @@
         <v>1</v>
       </c>
       <c r="P739" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="740" spans="1:16">
@@ -38418,7 +38421,7 @@
         <v>1</v>
       </c>
       <c r="P740" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="741" spans="1:16">
@@ -38468,7 +38471,7 @@
         <v>1</v>
       </c>
       <c r="P741" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="742" spans="1:16">
@@ -38518,7 +38521,7 @@
         <v>1</v>
       </c>
       <c r="P742" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="743" spans="1:16">
@@ -38568,7 +38571,7 @@
         <v>1</v>
       </c>
       <c r="P743" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="744" spans="1:16">
@@ -38618,7 +38621,7 @@
         <v>1</v>
       </c>
       <c r="P744" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="745" spans="1:16">
@@ -38668,7 +38671,7 @@
         <v>1</v>
       </c>
       <c r="P745" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="746" spans="1:16">
@@ -38718,7 +38721,7 @@
         <v>1</v>
       </c>
       <c r="P746" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="747" spans="1:16">
@@ -39068,7 +39071,7 @@
         <v>1</v>
       </c>
       <c r="P753" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="754" spans="1:16">
@@ -39118,7 +39121,7 @@
         <v>1</v>
       </c>
       <c r="P754" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="755" spans="1:16">
@@ -39168,7 +39171,7 @@
         <v>1</v>
       </c>
       <c r="P755" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="756" spans="1:16">
@@ -39218,7 +39221,7 @@
         <v>1</v>
       </c>
       <c r="P756" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="757" spans="1:16">
@@ -39268,7 +39271,7 @@
         <v>1</v>
       </c>
       <c r="P757" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="758" spans="1:16">
@@ -39318,7 +39321,7 @@
         <v>1</v>
       </c>
       <c r="P758" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="759" spans="1:16">
@@ -39668,7 +39671,7 @@
         <v>1</v>
       </c>
       <c r="P765" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="766" spans="1:16">
@@ -39718,7 +39721,7 @@
         <v>1</v>
       </c>
       <c r="P766" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="767" spans="1:16">
@@ -39768,7 +39771,7 @@
         <v>1</v>
       </c>
       <c r="P767" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="768" spans="1:16">
@@ -39818,7 +39821,7 @@
         <v>1</v>
       </c>
       <c r="P768" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="769" spans="1:16">
@@ -40068,7 +40071,7 @@
         <v>1</v>
       </c>
       <c r="P773" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="774" spans="1:16">
@@ -40118,7 +40121,7 @@
         <v>1</v>
       </c>
       <c r="P774" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="775" spans="1:16">
@@ -40168,7 +40171,7 @@
         <v>1</v>
       </c>
       <c r="P775" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="776" spans="1:16">
@@ -40218,7 +40221,7 @@
         <v>1</v>
       </c>
       <c r="P776" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="777" spans="1:16">
@@ -40468,7 +40471,7 @@
         <v>1</v>
       </c>
       <c r="P781" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="782" spans="1:16">
@@ -40518,7 +40521,7 @@
         <v>1</v>
       </c>
       <c r="P782" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="783" spans="1:16">
@@ -40568,7 +40571,7 @@
         <v>1</v>
       </c>
       <c r="P783" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="784" spans="1:16">
@@ -40968,7 +40971,7 @@
         <v>1</v>
       </c>
       <c r="P791" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="792" spans="1:16">
@@ -41018,7 +41021,7 @@
         <v>1</v>
       </c>
       <c r="P792" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="793" spans="1:16">
@@ -41068,7 +41071,7 @@
         <v>1</v>
       </c>
       <c r="P793" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="794" spans="1:16">
@@ -41118,7 +41121,7 @@
         <v>1</v>
       </c>
       <c r="P794" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="795" spans="1:16">
@@ -41368,7 +41371,7 @@
         <v>1</v>
       </c>
       <c r="P799" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="800" spans="1:16">
@@ -41418,7 +41421,7 @@
         <v>1</v>
       </c>
       <c r="P800" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="801" spans="1:16">
@@ -41468,7 +41471,7 @@
         <v>1</v>
       </c>
       <c r="P801" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="802" spans="1:16">
@@ -41518,7 +41521,7 @@
         <v>1</v>
       </c>
       <c r="P802" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="803" spans="1:16">
@@ -41568,7 +41571,7 @@
         <v>1</v>
       </c>
       <c r="P803" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="804" spans="1:16">
@@ -41618,7 +41621,7 @@
         <v>1</v>
       </c>
       <c r="P804" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="805" spans="1:16">
@@ -41968,7 +41971,7 @@
         <v>1</v>
       </c>
       <c r="P811" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="812" spans="1:16">
@@ -42018,7 +42021,7 @@
         <v>1</v>
       </c>
       <c r="P812" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="813" spans="1:16">
@@ -42068,7 +42071,7 @@
         <v>1</v>
       </c>
       <c r="P813" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="814" spans="1:16">
@@ -43618,7 +43621,7 @@
         <v>1</v>
       </c>
       <c r="P844" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="845" spans="1:16">
@@ -43668,7 +43671,7 @@
         <v>1</v>
       </c>
       <c r="P845" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="846" spans="1:16">
@@ -43718,7 +43721,7 @@
         <v>1</v>
       </c>
       <c r="P846" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="847" spans="1:16">
@@ -43768,7 +43771,7 @@
         <v>1</v>
       </c>
       <c r="P847" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="848" spans="1:16">
@@ -43818,7 +43821,7 @@
         <v>1</v>
       </c>
       <c r="P848" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="849" spans="1:16">
@@ -43868,7 +43871,7 @@
         <v>1</v>
       </c>
       <c r="P849" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="850" spans="1:16">
@@ -43918,7 +43921,7 @@
         <v>1</v>
       </c>
       <c r="P850" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="851" spans="1:16">
@@ -44368,7 +44371,7 @@
         <v>1</v>
       </c>
       <c r="P859" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="860" spans="1:16">
@@ -44385,7 +44388,7 @@
         <v>267</v>
       </c>
       <c r="E860">
-        <v>12.83601616269289</v>
+        <v>13.05601616269288</v>
       </c>
       <c r="F860">
         <v>1</v>
@@ -44394,10 +44397,10 @@
         <v>0.0493823805037019</v>
       </c>
       <c r="H860">
-        <v>0.04852398383730711</v>
+        <v>0.04874398383730711</v>
       </c>
       <c r="I860">
-        <v>0.2383966663947845</v>
+        <v>0.4583966663947834</v>
       </c>
       <c r="J860">
         <v>0.8436871790688943</v>
@@ -44412,13 +44415,13 @@
         <v>21.15</v>
       </c>
       <c r="N860">
-        <v>30.68</v>
+        <v>30.9</v>
       </c>
       <c r="O860">
         <v>1</v>
       </c>
       <c r="P860" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="861" spans="1:16">
@@ -44429,28 +44432,28 @@
         <v>155</v>
       </c>
       <c r="C861">
-        <v>12.45873056517934</v>
+        <v>12.51796460063045</v>
       </c>
       <c r="D861" t="s">
         <v>267</v>
       </c>
       <c r="E861">
-        <v>12.70126841530015</v>
+        <v>12.97873629831807</v>
       </c>
       <c r="F861">
         <v>1</v>
       </c>
       <c r="G861">
-        <v>0.04952126943482065</v>
+        <v>0.04946203539936955</v>
       </c>
       <c r="H861">
-        <v>0.04865873158469985</v>
+        <v>0.04882126370168193</v>
       </c>
       <c r="I861">
-        <v>0.2425378501208044</v>
+        <v>0.4607716976876262</v>
       </c>
       <c r="J861">
-        <v>0.8500582309550758</v>
+        <v>0.8473410733655758</v>
       </c>
       <c r="K861">
         <v>21.8</v>
@@ -44462,13 +44465,113 @@
         <v>21.15</v>
       </c>
       <c r="N861">
+        <v>30.9</v>
+      </c>
+      <c r="O861">
+        <v>1</v>
+      </c>
+      <c r="P861" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="862" spans="1:16">
+      <c r="A862" s="1">
+        <v>0</v>
+      </c>
+      <c r="B862" t="s">
+        <v>155</v>
+      </c>
+      <c r="C862">
+        <v>12.45873056517934</v>
+      </c>
+      <c r="D862" t="s">
+        <v>268</v>
+      </c>
+      <c r="E862">
+        <v>12.70126841530015</v>
+      </c>
+      <c r="F862">
+        <v>1</v>
+      </c>
+      <c r="G862">
+        <v>0.04952126943482065</v>
+      </c>
+      <c r="H862">
+        <v>0.04865873158469985</v>
+      </c>
+      <c r="I862">
+        <v>0.2425378501208044</v>
+      </c>
+      <c r="J862">
+        <v>0.8500582309550758</v>
+      </c>
+      <c r="K862">
+        <v>21.8</v>
+      </c>
+      <c r="L862">
+        <v>30.99</v>
+      </c>
+      <c r="M862">
+        <v>21.15</v>
+      </c>
+      <c r="N862">
         <v>30.68</v>
       </c>
-      <c r="O861">
-        <v>1</v>
-      </c>
-      <c r="P861" t="s">
-        <v>349</v>
+      <c r="O862">
+        <v>1</v>
+      </c>
+      <c r="P862" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="863" spans="1:16">
+      <c r="A863" s="1">
+        <v>0</v>
+      </c>
+      <c r="B863" t="s">
+        <v>155</v>
+      </c>
+      <c r="C863">
+        <v>12.42436853267676</v>
+      </c>
+      <c r="D863" t="s">
+        <v>268</v>
+      </c>
+      <c r="E863">
+        <v>12.66793093881254</v>
+      </c>
+      <c r="F863">
+        <v>1</v>
+      </c>
+      <c r="G863">
+        <v>0.04955563146732324</v>
+      </c>
+      <c r="H863">
+        <v>0.04869206906118746</v>
+      </c>
+      <c r="I863">
+        <v>0.2435624061357871</v>
+      </c>
+      <c r="J863">
+        <v>0.8516344709781304</v>
+      </c>
+      <c r="K863">
+        <v>21.8</v>
+      </c>
+      <c r="L863">
+        <v>30.99</v>
+      </c>
+      <c r="M863">
+        <v>21.15</v>
+      </c>
+      <c r="N863">
+        <v>30.68</v>
+      </c>
+      <c r="O863">
+        <v>1</v>
+      </c>
+      <c r="P863" t="s">
+        <v>266</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-00763-000063.xlsx
+++ b/s60_signal/position-00763-000063.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2601" uniqueCount="351">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2598" uniqueCount="351">
   <si>
     <t>trade_time</t>
   </si>
@@ -484,6 +484,9 @@
     <t>2021-11-29</t>
   </si>
   <si>
+    <t>2021-12-01</t>
+  </si>
+  <si>
     <t>2017-03-17</t>
   </si>
   <si>
@@ -817,10 +820,10 @@
     <t>2021-11-26</t>
   </si>
   <si>
-    <t>2021-12-01</t>
+    <t>2021-11-30</t>
   </si>
   <si>
-    <t>2021-11-30</t>
+    <t>2021-12-02</t>
   </si>
   <si>
     <t>2017-02-08</t>
@@ -1064,9 +1067,6 @@
   </si>
   <si>
     <t>2021-11-23</t>
-  </si>
-  <si>
-    <t>2021-11-25</t>
   </si>
 </sst>
 </file>
@@ -1424,7 +1424,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P863"/>
+  <dimension ref="A1:P862"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -1485,7 +1485,7 @@
         <v>8.357775317423281</v>
       </c>
       <c r="D2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E2">
         <v>9.239078272099615</v>
@@ -1521,7 +1521,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -1535,7 +1535,7 @@
         <v>9.433191964550923</v>
       </c>
       <c r="D3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E3">
         <v>9.285575452539577</v>
@@ -1571,7 +1571,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -1585,7 +1585,7 @@
         <v>9.420218808988363</v>
       </c>
       <c r="D4" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E4">
         <v>9.285575452539577</v>
@@ -1621,7 +1621,7 @@
         <v>1</v>
       </c>
       <c r="P4" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -1635,7 +1635,7 @@
         <v>9.27302954676334</v>
       </c>
       <c r="D5" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E5">
         <v>9.285575452539577</v>
@@ -1671,7 +1671,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -1685,7 +1685,7 @@
         <v>8.163141562328137</v>
       </c>
       <c r="D6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E6">
         <v>8.870417830135191</v>
@@ -1721,7 +1721,7 @@
         <v>1</v>
       </c>
       <c r="P6" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -1735,7 +1735,7 @@
         <v>8.167981542028786</v>
       </c>
       <c r="D7" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E7">
         <v>8.870417830135191</v>
@@ -1771,7 +1771,7 @@
         <v>1</v>
       </c>
       <c r="P7" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -1785,7 +1785,7 @@
         <v>9.039124544167011</v>
       </c>
       <c r="D8" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E8">
         <v>9.113918803782131</v>
@@ -1821,7 +1821,7 @@
         <v>1</v>
       </c>
       <c r="P8" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -1835,7 +1835,7 @@
         <v>9.052076876787602</v>
       </c>
       <c r="D9" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E9">
         <v>9.113918803782131</v>
@@ -1871,7 +1871,7 @@
         <v>1</v>
       </c>
       <c r="P9" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -1885,7 +1885,7 @@
         <v>8.972076876787604</v>
       </c>
       <c r="D10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E10">
         <v>9.113918803782131</v>
@@ -1921,7 +1921,7 @@
         <v>1</v>
       </c>
       <c r="P10" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -1935,7 +1935,7 @@
         <v>1.247895028504875</v>
       </c>
       <c r="D11" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E11">
         <v>5.93332434483856</v>
@@ -1971,7 +1971,7 @@
         <v>1</v>
       </c>
       <c r="P11" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -1985,7 +1985,7 @@
         <v>2.464515501370315</v>
       </c>
       <c r="D12" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E12">
         <v>5.93332434483856</v>
@@ -2021,7 +2021,7 @@
         <v>1</v>
       </c>
       <c r="P12" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -2071,7 +2071,7 @@
         <v>1</v>
       </c>
       <c r="P13" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -2085,7 +2085,7 @@
         <v>1.224092499726471</v>
       </c>
       <c r="D14" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E14">
         <v>5.913320521841428</v>
@@ -2121,7 +2121,7 @@
         <v>1</v>
       </c>
       <c r="P14" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -2135,7 +2135,7 @@
         <v>2.442814384300704</v>
       </c>
       <c r="D15" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E15">
         <v>5.913320521841428</v>
@@ -2171,7 +2171,7 @@
         <v>1</v>
       </c>
       <c r="P15" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -2185,7 +2185,7 @@
         <v>8.399951396166678</v>
       </c>
       <c r="D16" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E16">
         <v>7.154665097353277</v>
@@ -2221,7 +2221,7 @@
         <v>1</v>
       </c>
       <c r="P16" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -2235,7 +2235,7 @@
         <v>1.231818368992485</v>
       </c>
       <c r="D17" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E17">
         <v>5.919813400087062</v>
@@ -2271,7 +2271,7 @@
         <v>1</v>
       </c>
       <c r="P17" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -2285,7 +2285,7 @@
         <v>2.449858173427781</v>
       </c>
       <c r="D18" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E18">
         <v>5.919813400087062</v>
@@ -2321,7 +2321,7 @@
         <v>1</v>
       </c>
       <c r="P18" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -2371,7 +2371,7 @@
         <v>1</v>
       </c>
       <c r="P19" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="20" spans="1:16">
@@ -2385,7 +2385,7 @@
         <v>1.145797529921555</v>
       </c>
       <c r="D20" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E20">
         <v>5.847520844331356</v>
@@ -2421,7 +2421,7 @@
         <v>1</v>
       </c>
       <c r="P20" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -2435,7 +2435,7 @@
         <v>2.37143170385038</v>
       </c>
       <c r="D21" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E21">
         <v>5.847520844331356</v>
@@ -2471,7 +2471,7 @@
         <v>1</v>
       </c>
       <c r="P21" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -2485,7 +2485,7 @@
         <v>8.323251570058975</v>
       </c>
       <c r="D22" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E22">
         <v>6.49770468378167</v>
@@ -2521,7 +2521,7 @@
         <v>1</v>
       </c>
       <c r="P22" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="23" spans="1:16">
@@ -2535,7 +2535,7 @@
         <v>8.298928068060523</v>
       </c>
       <c r="D23" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E23">
         <v>6.513844529583032</v>
@@ -2621,7 +2621,7 @@
         <v>1</v>
       </c>
       <c r="P24" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="25" spans="1:16">
@@ -2671,7 +2671,7 @@
         <v>1</v>
       </c>
       <c r="P25" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="26" spans="1:16">
@@ -2685,7 +2685,7 @@
         <v>4.521898732172186</v>
       </c>
       <c r="D26" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E26">
         <v>7.471272137184702</v>
@@ -2721,7 +2721,7 @@
         <v>1</v>
       </c>
       <c r="P26" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="27" spans="1:16">
@@ -2771,7 +2771,7 @@
         <v>1</v>
       </c>
       <c r="P27" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="28" spans="1:16">
@@ -2821,7 +2821,7 @@
         <v>1</v>
       </c>
       <c r="P28" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -2835,7 +2835,7 @@
         <v>10.06347633639325</v>
       </c>
       <c r="D29" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E29">
         <v>8.926863738767604</v>
@@ -2871,7 +2871,7 @@
         <v>1</v>
       </c>
       <c r="P29" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -3035,7 +3035,7 @@
         <v>10.57243502356749</v>
       </c>
       <c r="D33" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E33">
         <v>11.2289160904059</v>
@@ -3085,7 +3085,7 @@
         <v>10.58025171866791</v>
       </c>
       <c r="D34" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E34">
         <v>11.2289160904059</v>
@@ -3135,7 +3135,7 @@
         <v>6.89098969886382</v>
       </c>
       <c r="D35" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E35">
         <v>9.162922766970905</v>
@@ -3171,7 +3171,7 @@
         <v>1</v>
       </c>
       <c r="P35" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -3221,7 +3221,7 @@
         <v>1</v>
       </c>
       <c r="P36" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="37" spans="1:16">
@@ -3271,7 +3271,7 @@
         <v>1</v>
       </c>
       <c r="P37" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="38" spans="1:16">
@@ -3321,7 +3321,7 @@
         <v>1</v>
       </c>
       <c r="P38" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="39" spans="1:16">
@@ -3335,7 +3335,7 @@
         <v>10.57710841036202</v>
       </c>
       <c r="D39" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E39">
         <v>10.91875227586742</v>
@@ -3371,7 +3371,7 @@
         <v>1</v>
       </c>
       <c r="P39" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="40" spans="1:16">
@@ -3385,7 +3385,7 @@
         <v>10.58544939256899</v>
       </c>
       <c r="D40" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E40">
         <v>10.91875227586742</v>
@@ -3421,7 +3421,7 @@
         <v>1</v>
       </c>
       <c r="P40" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="41" spans="1:16">
@@ -3471,7 +3471,7 @@
         <v>1</v>
       </c>
       <c r="P41" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="42" spans="1:16">
@@ -3521,7 +3521,7 @@
         <v>1</v>
       </c>
       <c r="P42" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="43" spans="1:16">
@@ -3571,7 +3571,7 @@
         <v>1</v>
       </c>
       <c r="P43" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="44" spans="1:16">
@@ -3585,7 +3585,7 @@
         <v>10.50706987192051</v>
       </c>
       <c r="D44" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E44">
         <v>9.836117792760128</v>
@@ -3621,7 +3621,7 @@
         <v>1</v>
       </c>
       <c r="P44" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -3785,7 +3785,7 @@
         <v>11.00643298606593</v>
       </c>
       <c r="D48" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E48">
         <v>10.08970532444388</v>
@@ -3871,7 +3871,7 @@
         <v>1</v>
       </c>
       <c r="P49" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="50" spans="1:16">
@@ -3921,7 +3921,7 @@
         <v>1</v>
       </c>
       <c r="P50" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="51" spans="1:16">
@@ -3971,7 +3971,7 @@
         <v>1</v>
       </c>
       <c r="P51" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="52" spans="1:16">
@@ -4021,7 +4021,7 @@
         <v>1</v>
       </c>
       <c r="P52" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="53" spans="1:16">
@@ -4071,7 +4071,7 @@
         <v>1</v>
       </c>
       <c r="P53" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="54" spans="1:16">
@@ -4121,7 +4121,7 @@
         <v>1</v>
       </c>
       <c r="P54" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="55" spans="1:16">
@@ -4135,7 +4135,7 @@
         <v>10.96451987407661</v>
       </c>
       <c r="D55" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E55">
         <v>9.918825279734797</v>
@@ -4171,7 +4171,7 @@
         <v>1</v>
       </c>
       <c r="P55" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="56" spans="1:16">
@@ -4221,7 +4221,7 @@
         <v>1</v>
       </c>
       <c r="P56" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="57" spans="1:16">
@@ -4271,7 +4271,7 @@
         <v>1</v>
       </c>
       <c r="P57" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="58" spans="1:16">
@@ -4321,7 +4321,7 @@
         <v>1</v>
       </c>
       <c r="P58" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="59" spans="1:16">
@@ -4371,7 +4371,7 @@
         <v>1</v>
       </c>
       <c r="P59" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="60" spans="1:16">
@@ -4421,7 +4421,7 @@
         <v>1</v>
       </c>
       <c r="P60" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="61" spans="1:16">
@@ -4471,7 +4471,7 @@
         <v>1</v>
       </c>
       <c r="P61" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="62" spans="1:16">
@@ -4521,7 +4521,7 @@
         <v>1</v>
       </c>
       <c r="P62" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="63" spans="1:16">
@@ -4535,7 +4535,7 @@
         <v>10.70295290100141</v>
       </c>
       <c r="D63" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E63">
         <v>8.905400692050126</v>
@@ -4571,7 +4571,7 @@
         <v>1</v>
       </c>
       <c r="P63" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="64" spans="1:16">
@@ -4585,7 +4585,7 @@
         <v>11.20304517915771</v>
       </c>
       <c r="D64" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E64">
         <v>8.905400692050126</v>
@@ -4621,7 +4621,7 @@
         <v>1</v>
       </c>
       <c r="P64" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="65" spans="1:16">
@@ -4671,7 +4671,7 @@
         <v>1</v>
       </c>
       <c r="P65" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="66" spans="1:16">
@@ -4685,7 +4685,7 @@
         <v>10.69564352718713</v>
       </c>
       <c r="D66" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E66">
         <v>10.68408451836947</v>
@@ -4721,7 +4721,7 @@
         <v>1</v>
       </c>
       <c r="P66" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="67" spans="1:16">
@@ -4735,7 +4735,7 @@
         <v>11.03068966626528</v>
       </c>
       <c r="D67" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E67">
         <v>10.68408451836947</v>
@@ -4771,7 +4771,7 @@
         <v>1</v>
       </c>
       <c r="P67" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="68" spans="1:16">
@@ -4821,7 +4821,7 @@
         <v>1</v>
       </c>
       <c r="P68" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="69" spans="1:16">
@@ -4835,7 +4835,7 @@
         <v>10.52605158161457</v>
       </c>
       <c r="D69" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E69">
         <v>8.71498607743235</v>
@@ -4871,7 +4871,7 @@
         <v>1</v>
       </c>
       <c r="P69" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="70" spans="1:16">
@@ -4885,7 +4885,7 @@
         <v>11.02061569354003</v>
       </c>
       <c r="D70" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E70">
         <v>8.71498607743235</v>
@@ -4921,7 +4921,7 @@
         <v>1</v>
       </c>
       <c r="P70" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="71" spans="1:16">
@@ -4971,7 +4971,7 @@
         <v>1</v>
       </c>
       <c r="P71" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="72" spans="1:16">
@@ -4985,7 +4985,7 @@
         <v>10.52396325368498</v>
       </c>
       <c r="D72" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E72">
         <v>8.806051581614568</v>
@@ -5021,7 +5021,7 @@
         <v>1</v>
       </c>
       <c r="P72" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="73" spans="1:16">
@@ -5035,7 +5035,7 @@
         <v>10.8562453096477</v>
       </c>
       <c r="D73" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E73">
         <v>8.806051581614568</v>
@@ -5071,7 +5071,7 @@
         <v>1</v>
       </c>
       <c r="P73" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="74" spans="1:16">
@@ -5085,7 +5085,7 @@
         <v>10.34525014922946</v>
       </c>
       <c r="D74" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E74">
         <v>8.520373424517821</v>
@@ -5135,7 +5135,7 @@
         <v>10.83416421639288</v>
       </c>
       <c r="D75" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E75">
         <v>8.520373424517821</v>
@@ -5285,7 +5285,7 @@
         <v>10.34849797468624</v>
       </c>
       <c r="D78" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E78">
         <v>8.625250149229462</v>
@@ -5335,7 +5335,7 @@
         <v>10.67795500826794</v>
       </c>
       <c r="D79" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E79">
         <v>8.625250149229462</v>
@@ -5385,7 +5385,7 @@
         <v>10.18864383981015</v>
       </c>
       <c r="D80" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E80">
         <v>8.351804133128983</v>
@@ -5421,7 +5421,7 @@
         <v>1</v>
       </c>
       <c r="P80" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="81" spans="1:16">
@@ -5435,7 +5435,7 @@
         <v>10.67266395980422</v>
       </c>
       <c r="D81" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E81">
         <v>8.351804133128983</v>
@@ -5471,7 +5471,7 @@
         <v>1</v>
       </c>
       <c r="P81" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="82" spans="1:16">
@@ -5521,7 +5521,7 @@
         <v>1</v>
       </c>
       <c r="P82" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="83" spans="1:16">
@@ -5571,7 +5571,7 @@
         <v>1</v>
       </c>
       <c r="P83" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="84" spans="1:16">
@@ -5585,7 +5585,7 @@
         <v>10.19651372648243</v>
       </c>
       <c r="D84" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E84">
         <v>8.468643839810152</v>
@@ -5621,7 +5621,7 @@
         <v>1</v>
       </c>
       <c r="P84" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="85" spans="1:16">
@@ -5635,7 +5635,7 @@
         <v>10.52352378647946</v>
       </c>
       <c r="D85" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E85">
         <v>8.468643839810152</v>
@@ -5671,7 +5671,7 @@
         <v>1</v>
       </c>
       <c r="P85" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="86" spans="1:16">
@@ -5685,7 +5685,7 @@
         <v>-1.278554542763944</v>
       </c>
       <c r="D86" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E86">
         <v>0.01420169243589342</v>
@@ -5721,7 +5721,7 @@
         <v>1</v>
       </c>
       <c r="P86" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="87" spans="1:16">
@@ -5735,7 +5735,7 @@
         <v>-2.406586639852707</v>
       </c>
       <c r="D87" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E87">
         <v>0.01420169243589342</v>
@@ -5771,7 +5771,7 @@
         <v>1</v>
       </c>
       <c r="P87" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="88" spans="1:16">
@@ -5821,7 +5821,7 @@
         <v>1</v>
       </c>
       <c r="P88" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="89" spans="1:16">
@@ -5835,7 +5835,7 @@
         <v>-1.341212522415489</v>
       </c>
       <c r="D89" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E89">
         <v>0.1246199151405953</v>
@@ -5871,7 +5871,7 @@
         <v>1</v>
       </c>
       <c r="P89" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="90" spans="1:16">
@@ -5885,7 +5885,7 @@
         <v>-2.475362406493851</v>
       </c>
       <c r="D90" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E90">
         <v>0.1246199151405953</v>
@@ -5921,7 +5921,7 @@
         <v>1</v>
       </c>
       <c r="P90" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="91" spans="1:16">
@@ -5971,7 +5971,7 @@
         <v>1</v>
       </c>
       <c r="P91" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="92" spans="1:16">
@@ -5985,7 +5985,7 @@
         <v>-2.566016320350375</v>
       </c>
       <c r="D92" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E92">
         <v>0.02954385914472724</v>
@@ -6135,7 +6135,7 @@
         <v>-2.663355023194697</v>
       </c>
       <c r="D95" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E95">
         <v>0.03872013419191234</v>
@@ -6171,7 +6171,7 @@
         <v>1</v>
       </c>
       <c r="P95" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="96" spans="1:16">
@@ -6221,7 +6221,7 @@
         <v>1</v>
       </c>
       <c r="P96" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="97" spans="1:16">
@@ -6271,7 +6271,7 @@
         <v>1</v>
       </c>
       <c r="P97" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="98" spans="1:16">
@@ -6285,7 +6285,7 @@
         <v>-2.748103967913549</v>
       </c>
       <c r="D98" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E98">
         <v>-0.04760949385741853</v>
@@ -6321,7 +6321,7 @@
         <v>1</v>
       </c>
       <c r="P98" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="99" spans="1:16">
@@ -6335,7 +6335,7 @@
         <v>1.170412609918055</v>
       </c>
       <c r="D99" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E99">
         <v>1.469846093587645</v>
@@ -6371,7 +6371,7 @@
         <v>1</v>
       </c>
       <c r="P99" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="100" spans="1:16">
@@ -6385,7 +6385,7 @@
         <v>1.197090465141786</v>
       </c>
       <c r="D100" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E100">
         <v>1.469846093587645</v>
@@ -6421,7 +6421,7 @@
         <v>1</v>
       </c>
       <c r="P100" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="101" spans="1:16">
@@ -6435,7 +6435,7 @@
         <v>-2.807295369205091</v>
       </c>
       <c r="D101" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E101">
         <v>0.3363998775430197</v>
@@ -6471,7 +6471,7 @@
         <v>1</v>
       </c>
       <c r="P101" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="102" spans="1:16">
@@ -6521,7 +6521,7 @@
         <v>1</v>
       </c>
       <c r="P102" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="103" spans="1:16">
@@ -6621,7 +6621,7 @@
         <v>1</v>
       </c>
       <c r="P104" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="105" spans="1:16">
@@ -6635,7 +6635,7 @@
         <v>1.819034812951433</v>
       </c>
       <c r="D105" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E105">
         <v>1.780382458905816</v>
@@ -6671,7 +6671,7 @@
         <v>1</v>
       </c>
       <c r="P105" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="106" spans="1:16">
@@ -6685,7 +6685,7 @@
         <v>1.278232359359254</v>
       </c>
       <c r="D106" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E106">
         <v>1.780382458905816</v>
@@ -6721,7 +6721,7 @@
         <v>1</v>
       </c>
       <c r="P106" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="107" spans="1:16">
@@ -6735,7 +6735,7 @@
         <v>-1.27500579580901</v>
       </c>
       <c r="D107" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E107">
         <v>0.204597470791132</v>
@@ -6771,7 +6771,7 @@
         <v>1</v>
       </c>
       <c r="P107" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="108" spans="1:16">
@@ -6785,7 +6785,7 @@
         <v>-1.164182632644362</v>
       </c>
       <c r="D108" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E108">
         <v>0.204597470791132</v>
@@ -6821,7 +6821,7 @@
         <v>1</v>
       </c>
       <c r="P108" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="109" spans="1:16">
@@ -6871,7 +6871,7 @@
         <v>1</v>
       </c>
       <c r="P109" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="110" spans="1:16">
@@ -6921,7 +6921,7 @@
         <v>1</v>
       </c>
       <c r="P110" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="111" spans="1:16">
@@ -6935,7 +6935,7 @@
         <v>-1.330656541117063</v>
       </c>
       <c r="D111" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E111">
         <v>0.1498300706466971</v>
@@ -6971,7 +6971,7 @@
         <v>1</v>
       </c>
       <c r="P111" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="112" spans="1:16">
@@ -6985,7 +6985,7 @@
         <v>-1.089957636312631</v>
       </c>
       <c r="D112" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E112">
         <v>0.1498300706466971</v>
@@ -7021,7 +7021,7 @@
         <v>1</v>
       </c>
       <c r="P112" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="113" spans="1:16">
@@ -7035,7 +7035,7 @@
         <v>1.663161219313913</v>
       </c>
       <c r="D113" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E113">
         <v>1.394552474924428</v>
@@ -7071,7 +7071,7 @@
         <v>1</v>
       </c>
       <c r="P113" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="114" spans="1:16">
@@ -7085,7 +7085,7 @@
         <v>2.020453841772007</v>
       </c>
       <c r="D114" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E114">
         <v>1.394552474924428</v>
@@ -7121,7 +7121,7 @@
         <v>1</v>
       </c>
       <c r="P114" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="115" spans="1:16">
@@ -7171,7 +7171,7 @@
         <v>1</v>
       </c>
       <c r="P115" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="116" spans="1:16">
@@ -7221,7 +7221,7 @@
         <v>1</v>
       </c>
       <c r="P116" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="117" spans="1:16">
@@ -7271,7 +7271,7 @@
         <v>1</v>
       </c>
       <c r="P117" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="118" spans="1:16">
@@ -7321,7 +7321,7 @@
         <v>1</v>
       </c>
       <c r="P118" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="119" spans="1:16">
@@ -7371,7 +7371,7 @@
         <v>1</v>
       </c>
       <c r="P119" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="120" spans="1:16">
@@ -7421,7 +7421,7 @@
         <v>1</v>
       </c>
       <c r="P120" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="121" spans="1:16">
@@ -7471,7 +7471,7 @@
         <v>1</v>
       </c>
       <c r="P121" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="122" spans="1:16">
@@ -7521,7 +7521,7 @@
         <v>1</v>
       </c>
       <c r="P122" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="123" spans="1:16">
@@ -7571,7 +7571,7 @@
         <v>1</v>
       </c>
       <c r="P123" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="124" spans="1:16">
@@ -7621,7 +7621,7 @@
         <v>1</v>
       </c>
       <c r="P124" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="125" spans="1:16">
@@ -7735,7 +7735,7 @@
         <v>1.583716178161136</v>
       </c>
       <c r="D127" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E127">
         <v>1.731188504841963</v>
@@ -7785,7 +7785,7 @@
         <v>1.943294205912665</v>
       </c>
       <c r="D128" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E128">
         <v>1.731188504841963</v>
@@ -7835,7 +7835,7 @@
         <v>1.440029121201585</v>
       </c>
       <c r="D129" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E129">
         <v>1.731188504841963</v>
@@ -7921,7 +7921,7 @@
         <v>1</v>
       </c>
       <c r="P130" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="131" spans="1:16">
@@ -7971,7 +7971,7 @@
         <v>1</v>
       </c>
       <c r="P131" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="132" spans="1:16">
@@ -8021,7 +8021,7 @@
         <v>1</v>
       </c>
       <c r="P132" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="133" spans="1:16">
@@ -8071,7 +8071,7 @@
         <v>1</v>
       </c>
       <c r="P133" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="134" spans="1:16">
@@ -8121,7 +8121,7 @@
         <v>1</v>
       </c>
       <c r="P134" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="135" spans="1:16">
@@ -8135,7 +8135,7 @@
         <v>-0.8820242128746258</v>
       </c>
       <c r="D135" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E135">
         <v>0.3526024044326252</v>
@@ -8171,7 +8171,7 @@
         <v>1</v>
       </c>
       <c r="P135" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="136" spans="1:16">
@@ -8185,7 +8185,7 @@
         <v>-1.173427909927172</v>
       </c>
       <c r="D136" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E136">
         <v>0.3526024044326252</v>
@@ -8221,7 +8221,7 @@
         <v>1</v>
       </c>
       <c r="P136" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="137" spans="1:16">
@@ -8271,7 +8271,7 @@
         <v>1</v>
       </c>
       <c r="P137" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="138" spans="1:16">
@@ -8321,7 +8321,7 @@
         <v>1</v>
       </c>
       <c r="P138" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="139" spans="1:16">
@@ -8371,7 +8371,7 @@
         <v>1</v>
       </c>
       <c r="P139" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="140" spans="1:16">
@@ -8685,7 +8685,7 @@
         <v>1.916709703800588</v>
       </c>
       <c r="D146" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E146">
         <v>1.625228926806798</v>
@@ -8735,7 +8735,7 @@
         <v>1.775844332123576</v>
       </c>
       <c r="D147" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E147">
         <v>1.625228926806798</v>
@@ -8785,7 +8785,7 @@
         <v>1.706459737440355</v>
       </c>
       <c r="D148" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E148">
         <v>1.625228926806798</v>
@@ -8835,7 +8835,7 @@
         <v>1.898407474064776</v>
       </c>
       <c r="D149" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E149">
         <v>1.579058157468399</v>
@@ -8871,7 +8871,7 @@
         <v>1</v>
       </c>
       <c r="P149" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="150" spans="1:16">
@@ -8885,7 +8885,7 @@
         <v>1.757671173119327</v>
       </c>
       <c r="D150" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E150">
         <v>1.579058157468399</v>
@@ -8921,7 +8921,7 @@
         <v>1</v>
       </c>
       <c r="P150" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="151" spans="1:16">
@@ -8935,7 +8935,7 @@
         <v>1.688493091606606</v>
       </c>
       <c r="D151" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E151">
         <v>1.579058157468399</v>
@@ -8971,7 +8971,7 @@
         <v>1</v>
       </c>
       <c r="P151" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="152" spans="1:16">
@@ -9021,7 +9021,7 @@
         <v>1</v>
       </c>
       <c r="P152" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="153" spans="1:16">
@@ -9071,7 +9071,7 @@
         <v>1</v>
       </c>
       <c r="P153" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="154" spans="1:16">
@@ -9121,7 +9121,7 @@
         <v>1</v>
       </c>
       <c r="P154" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="155" spans="1:16">
@@ -9171,7 +9171,7 @@
         <v>1</v>
       </c>
       <c r="P155" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="156" spans="1:16">
@@ -9221,7 +9221,7 @@
         <v>1</v>
       </c>
       <c r="P156" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="157" spans="1:16">
@@ -9271,7 +9271,7 @@
         <v>1</v>
       </c>
       <c r="P157" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="158" spans="1:16">
@@ -9421,7 +9421,7 @@
         <v>1</v>
       </c>
       <c r="P160" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="161" spans="1:16">
@@ -9471,7 +9471,7 @@
         <v>1</v>
       </c>
       <c r="P161" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="162" spans="1:16">
@@ -9521,7 +9521,7 @@
         <v>1</v>
       </c>
       <c r="P162" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="163" spans="1:16">
@@ -9571,7 +9571,7 @@
         <v>1</v>
       </c>
       <c r="P163" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="164" spans="1:16">
@@ -9585,7 +9585,7 @@
         <v>2.0418888555804</v>
       </c>
       <c r="D164" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E164">
         <v>2.091052252009925</v>
@@ -9635,7 +9635,7 @@
         <v>2.437529947263654</v>
       </c>
       <c r="D165" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E165">
         <v>2.091052252009925</v>
@@ -9685,7 +9685,7 @@
         <v>2.035427646090795</v>
       </c>
       <c r="D166" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E166">
         <v>1.677256780401082</v>
@@ -9721,7 +9721,7 @@
         <v>1</v>
       </c>
       <c r="P166" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="167" spans="1:16">
@@ -9735,7 +9735,7 @@
         <v>2.4319519246827</v>
       </c>
       <c r="D167" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E167">
         <v>1.677256780401082</v>
@@ -9771,7 +9771,7 @@
         <v>1</v>
       </c>
       <c r="P167" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="168" spans="1:16">
@@ -9821,7 +9821,7 @@
         <v>1</v>
       </c>
       <c r="P168" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="169" spans="1:16">
@@ -9871,7 +9871,7 @@
         <v>1</v>
       </c>
       <c r="P169" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="170" spans="1:16">
@@ -9921,7 +9921,7 @@
         <v>1</v>
       </c>
       <c r="P170" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="171" spans="1:16">
@@ -9971,7 +9971,7 @@
         <v>1</v>
       </c>
       <c r="P171" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="172" spans="1:16">
@@ -10021,7 +10021,7 @@
         <v>1</v>
       </c>
       <c r="P172" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="173" spans="1:16">
@@ -10035,7 +10035,7 @@
         <v>2.053037839433713</v>
       </c>
       <c r="D173" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E173">
         <v>2.029053723158555</v>
@@ -10071,7 +10071,7 @@
         <v>1</v>
       </c>
       <c r="P173" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="174" spans="1:16">
@@ -10185,7 +10185,7 @@
         <v>2.072439051471395</v>
       </c>
       <c r="D176" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E176">
         <v>2.198537473651809</v>
@@ -10221,7 +10221,7 @@
         <v>1</v>
       </c>
       <c r="P176" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="177" spans="1:16">
@@ -10235,7 +10235,7 @@
         <v>2.176038435736924</v>
       </c>
       <c r="D177" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E177">
         <v>2.198537473651809</v>
@@ -10271,7 +10271,7 @@
         <v>1</v>
       </c>
       <c r="P177" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="178" spans="1:16">
@@ -10321,7 +10321,7 @@
         <v>1</v>
       </c>
       <c r="P178" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="179" spans="1:16">
@@ -10385,7 +10385,7 @@
         <v>2.199572666349018</v>
       </c>
       <c r="D180" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E180">
         <v>2.369622868222606</v>
@@ -10585,7 +10585,7 @@
         <v>2.441204477380014</v>
       </c>
       <c r="D184" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E184">
         <v>3.019740173907834</v>
@@ -10685,7 +10685,7 @@
         <v>2.450942264059425</v>
       </c>
       <c r="D186" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E186">
         <v>3.396065694761221</v>
@@ -10735,7 +10735,7 @@
         <v>2.93271297523739</v>
       </c>
       <c r="D187" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E187">
         <v>3.396065694761221</v>
@@ -10835,7 +10835,7 @@
         <v>2.613291041571109</v>
       </c>
       <c r="D189" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E189">
         <v>1.747095958240026</v>
@@ -10885,7 +10885,7 @@
         <v>2.94332933323569</v>
       </c>
       <c r="D190" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E190">
         <v>3.513960124909904</v>
@@ -11035,7 +11035,7 @@
         <v>2.630002520413537</v>
       </c>
       <c r="D193" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E193">
         <v>1.763414225815572</v>
@@ -11085,7 +11085,7 @@
         <v>2.960405936825934</v>
       </c>
       <c r="D194" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E194">
         <v>2.688557154970242</v>
@@ -11285,7 +11285,7 @@
         <v>2.642059072099817</v>
       </c>
       <c r="D198" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E198">
         <v>1.775187093932763</v>
@@ -11335,7 +11335,7 @@
         <v>2.972725908969226</v>
       </c>
       <c r="D199" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E199">
         <v>2.375803028433923</v>
@@ -11485,7 +11485,7 @@
         <v>2.666955617984192</v>
       </c>
       <c r="D202" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E202">
         <v>1.799497838737505</v>
@@ -11535,7 +11535,7 @@
         <v>2.998166412998973</v>
       </c>
       <c r="D203" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E203">
         <v>1.736641978102437</v>
@@ -11685,7 +11685,7 @@
         <v>2.973643871143521</v>
       </c>
       <c r="D206" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E206">
         <v>1.818524938691256</v>
@@ -11735,7 +11735,7 @@
         <v>3.018077732744034</v>
       </c>
       <c r="D207" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E207">
         <v>1.759533446033025</v>
@@ -11885,7 +11885,7 @@
         <v>2.990082102112254</v>
       </c>
       <c r="D210" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E210">
         <v>1.83485077149952</v>
@@ -11935,7 +11935,7 @@
         <v>3.03516225313547</v>
       </c>
       <c r="D211" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E211">
         <v>1.779175024575153</v>
@@ -12021,7 +12021,7 @@
         <v>1</v>
       </c>
       <c r="P212" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="213" spans="1:16">
@@ -12071,7 +12071,7 @@
         <v>1</v>
       </c>
       <c r="P213" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="214" spans="1:16">
@@ -12085,7 +12085,7 @@
         <v>3.005496469975766</v>
       </c>
       <c r="D214" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E214">
         <v>1.850159741975929</v>
@@ -12121,7 +12121,7 @@
         <v>1</v>
       </c>
       <c r="P214" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="215" spans="1:16">
@@ -12135,7 +12135,7 @@
         <v>3.051182655974811</v>
       </c>
       <c r="D215" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E215">
         <v>1.797593217971041</v>
@@ -12171,7 +12171,7 @@
         <v>1</v>
       </c>
       <c r="P215" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="216" spans="1:16">
@@ -12285,7 +12285,7 @@
         <v>3.018931533510157</v>
       </c>
       <c r="D218" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E218">
         <v>1.863502941828035</v>
@@ -12335,7 +12335,7 @@
         <v>3.06514593568235</v>
       </c>
       <c r="D219" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E219">
         <v>1.813646396450594</v>
@@ -12485,7 +12485,7 @@
         <v>3.033933076549712</v>
       </c>
       <c r="D222" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E222">
         <v>1.878401910214327</v>
@@ -12535,7 +12535,7 @@
         <v>3.080737282978161</v>
       </c>
       <c r="D223" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E223">
         <v>1.831571317108114</v>
@@ -12585,7 +12585,7 @@
         <v>1.639859271051932</v>
       </c>
       <c r="D224" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E224">
         <v>1.9209216037227</v>
@@ -12735,7 +12735,7 @@
         <v>3.05833801181463</v>
       </c>
       <c r="D227" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E227">
         <v>1.902639974127007</v>
@@ -12785,7 +12785,7 @@
         <v>3.106101728518452</v>
       </c>
       <c r="D228" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E228">
         <v>1.860732085911838</v>
@@ -12871,7 +12871,7 @@
         <v>1</v>
       </c>
       <c r="P229" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="230" spans="1:16">
@@ -12921,7 +12921,7 @@
         <v>1</v>
       </c>
       <c r="P230" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="231" spans="1:16">
@@ -12935,7 +12935,7 @@
         <v>3.085055612872655</v>
       </c>
       <c r="D231" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E231">
         <v>1.929174890733353</v>
@@ -12971,7 +12971,7 @@
         <v>1</v>
       </c>
       <c r="P231" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="232" spans="1:16">
@@ -12985,7 +12985,7 @@
         <v>3.13386976517363</v>
       </c>
       <c r="D232" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E232">
         <v>1.892656193842708</v>
@@ -13021,7 +13021,7 @@
         <v>1</v>
       </c>
       <c r="P232" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="233" spans="1:16">
@@ -13085,7 +13085,7 @@
         <v>3.103034611570727</v>
       </c>
       <c r="D234" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E234">
         <v>1.947030956106994</v>
@@ -13135,7 +13135,7 @@
         <v>3.152555630487182</v>
       </c>
       <c r="D235" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E235">
         <v>1.914138792287073</v>
@@ -13185,7 +13185,7 @@
         <v>1.641725609550694</v>
       </c>
       <c r="D236" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E236">
         <v>1.89319910743864</v>
@@ -13271,7 +13271,7 @@
         <v>1</v>
       </c>
       <c r="P237" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="238" spans="1:16">
@@ -13285,7 +13285,7 @@
         <v>3.11979974827751</v>
       </c>
       <c r="D238" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E238">
         <v>1.963681459400396</v>
@@ -13321,7 +13321,7 @@
         <v>1</v>
       </c>
       <c r="P238" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="239" spans="1:16">
@@ -13335,7 +13335,7 @@
         <v>3.169979909320897</v>
       </c>
       <c r="D239" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E239">
         <v>1.934170981275177</v>
@@ -13371,7 +13371,7 @@
         <v>1</v>
       </c>
       <c r="P239" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="240" spans="1:16">
@@ -13385,7 +13385,7 @@
         <v>1.664480342106565</v>
       </c>
       <c r="D240" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E240">
         <v>2.221652319966786</v>
@@ -13421,7 +13421,7 @@
         <v>1</v>
       </c>
       <c r="P240" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="241" spans="1:16">
@@ -13485,7 +13485,7 @@
         <v>3.136490860930856</v>
       </c>
       <c r="D242" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E242">
         <v>1.980258444787738</v>
@@ -13535,7 +13535,7 @@
         <v>3.187327253753777</v>
       </c>
       <c r="D243" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E243">
         <v>1.954114721009688</v>
@@ -13735,7 +13735,7 @@
         <v>3.154470288152615</v>
       </c>
       <c r="D247" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E247">
         <v>1.998114935754989</v>
@@ -13785,7 +13785,7 @@
         <v>3.206013564438956</v>
       </c>
       <c r="D248" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E248">
         <v>1.975597831484915</v>
@@ -13971,7 +13971,7 @@
         <v>1</v>
       </c>
       <c r="P251" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="252" spans="1:16">
@@ -14021,7 +14021,7 @@
         <v>1</v>
       </c>
       <c r="P252" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="253" spans="1:16">
@@ -14035,7 +14035,7 @@
         <v>3.175183381627829</v>
       </c>
       <c r="D253" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E253">
         <v>2.406837822852639</v>
@@ -14071,7 +14071,7 @@
         <v>1</v>
       </c>
       <c r="P253" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="254" spans="1:16">
@@ -14085,7 +14085,7 @@
         <v>3.227541018854222</v>
       </c>
       <c r="D254" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E254">
         <v>2.000347322662993</v>
@@ -14121,7 +14121,7 @@
         <v>1</v>
       </c>
       <c r="P254" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="255" spans="1:16">
@@ -14171,7 +14171,7 @@
         <v>1</v>
       </c>
       <c r="P255" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="256" spans="1:16">
@@ -14221,7 +14221,7 @@
         <v>1</v>
       </c>
       <c r="P256" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="257" spans="1:16">
@@ -14335,7 +14335,7 @@
         <v>3.194491499183421</v>
       </c>
       <c r="D259" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E259">
         <v>2.42485873257119</v>
@@ -14385,7 +14385,7 @@
         <v>3.247608258980375</v>
       </c>
       <c r="D260" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E260">
         <v>2.023418047742236</v>
@@ -14635,7 +14635,7 @@
         <v>3.213727962726566</v>
       </c>
       <c r="D265" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E265">
         <v>2.442812765211459</v>
@@ -14685,7 +14685,7 @@
         <v>3.26760102792778</v>
       </c>
       <c r="D266" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E266">
         <v>2.046403155463022</v>
@@ -14885,7 +14885,7 @@
         <v>3.233647867837396</v>
       </c>
       <c r="D270" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E270">
         <v>2.461404676648234</v>
@@ -14935,7 +14935,7 @@
         <v>3.288304108795105</v>
       </c>
       <c r="D271" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E271">
         <v>2.070204888236475</v>
@@ -15135,7 +15135,7 @@
         <v>3.249417008017017</v>
       </c>
       <c r="D275" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E275">
         <v>2.476122540815881</v>
@@ -15185,7 +15185,7 @@
         <v>3.304693232263839</v>
       </c>
       <c r="D276" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E276">
         <v>2.089046989066485</v>
@@ -15335,7 +15335,7 @@
         <v>1.914875661806953</v>
       </c>
       <c r="D279" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E279">
         <v>2.109898465499843</v>
@@ -15421,7 +15421,7 @@
         <v>1</v>
       </c>
       <c r="P280" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="281" spans="1:16">
@@ -15435,7 +15435,7 @@
         <v>3.261163134684622</v>
       </c>
       <c r="D281" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E281">
         <v>2.487085592372312</v>
@@ -15471,7 +15471,7 @@
         <v>1</v>
       </c>
       <c r="P281" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="282" spans="1:16">
@@ -15485,7 +15485,7 @@
         <v>3.316901172458547</v>
       </c>
       <c r="D282" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E282">
         <v>2.103082104520595</v>
@@ -15521,7 +15521,7 @@
         <v>1</v>
       </c>
       <c r="P282" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="283" spans="1:16">
@@ -15571,7 +15571,7 @@
         <v>1</v>
       </c>
       <c r="P283" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="284" spans="1:16">
@@ -15621,7 +15621,7 @@
         <v>1</v>
       </c>
       <c r="P284" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="285" spans="1:16">
@@ -15635,7 +15635,7 @@
         <v>1.930296217842372</v>
       </c>
       <c r="D285" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E285">
         <v>2.383746445952788</v>
@@ -15671,7 +15671,7 @@
         <v>1</v>
       </c>
       <c r="P285" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="286" spans="1:16">
@@ -15721,7 +15721,7 @@
         <v>1</v>
       </c>
       <c r="P286" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="287" spans="1:16">
@@ -15735,7 +15735,7 @@
         <v>3.267778188252251</v>
       </c>
       <c r="D287" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E287">
         <v>2.493259642368766</v>
@@ -15771,7 +15771,7 @@
         <v>1</v>
       </c>
       <c r="P287" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="288" spans="1:16">
@@ -15785,7 +15785,7 @@
         <v>3.323776305055329</v>
       </c>
       <c r="D288" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E288">
         <v>2.110986245450121</v>
@@ -15821,7 +15821,7 @@
         <v>1</v>
       </c>
       <c r="P288" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="289" spans="1:16">
@@ -15871,7 +15871,7 @@
         <v>1</v>
       </c>
       <c r="P289" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="290" spans="1:16">
@@ -15921,7 +15921,7 @@
         <v>1</v>
       </c>
       <c r="P290" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="291" spans="1:16">
@@ -15971,7 +15971,7 @@
         <v>1</v>
       </c>
       <c r="P291" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="292" spans="1:16">
@@ -15985,7 +15985,7 @@
         <v>3.278598009747792</v>
       </c>
       <c r="D292" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E292">
         <v>2.503358142431271</v>
@@ -16035,7 +16035,7 @@
         <v>3.335021521242147</v>
       </c>
       <c r="D293" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E293">
         <v>2.123914544980693</v>
@@ -16185,7 +16185,7 @@
         <v>1.953185079463765</v>
       </c>
       <c r="D296" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E296">
         <v>1.673185079463764</v>
@@ -16235,7 +16235,7 @@
         <v>1.838424946780282</v>
       </c>
       <c r="D297" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E297">
         <v>1.673185079463764</v>
@@ -16285,7 +16285,7 @@
         <v>3.286491586851236</v>
       </c>
       <c r="D298" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E298">
         <v>2.510725481061151</v>
@@ -16335,7 +16335,7 @@
         <v>3.343225444112052</v>
       </c>
       <c r="D299" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E299">
         <v>2.133346357622241</v>
@@ -16485,7 +16485,7 @@
         <v>1.963547929404697</v>
       </c>
       <c r="D302" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E302">
         <v>2.040362444937774</v>
@@ -16535,7 +16535,7 @@
         <v>1.849314035194777</v>
       </c>
       <c r="D303" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E303">
         <v>2.040362444937774</v>
@@ -16585,7 +16585,7 @@
         <v>3.287218803551511</v>
       </c>
       <c r="D304" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E304">
         <v>2.511404216648074</v>
@@ -16635,7 +16635,7 @@
         <v>3.34398125223815</v>
       </c>
       <c r="D305" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E305">
         <v>2.134215288346162</v>
@@ -16785,7 +16785,7 @@
         <v>1.964502634406085</v>
       </c>
       <c r="D308" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E308">
         <v>2.034789980466009</v>
@@ -16835,7 +16835,7 @@
         <v>1.850317221309513</v>
       </c>
       <c r="D309" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E309">
         <v>2.034789980466009</v>
@@ -16885,7 +16885,7 @@
         <v>3.309574328279867</v>
       </c>
       <c r="D310" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E310">
         <v>2.532269373061208</v>
@@ -16935,7 +16935,7 @@
         <v>3.367215712126766</v>
       </c>
       <c r="D311" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E311">
         <v>2.160927274303631</v>
@@ -17185,7 +17185,7 @@
         <v>3.386581638751728</v>
       </c>
       <c r="D316" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E316">
         <v>2.183191719551736</v>
@@ -17285,7 +17285,7 @@
         <v>2.018313648949551</v>
       </c>
       <c r="D318" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E318">
         <v>2.020805677582523</v>
@@ -17335,7 +17335,7 @@
         <v>1.906860826435267</v>
       </c>
       <c r="D319" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E319">
         <v>2.020805677582523</v>
@@ -17385,7 +17385,7 @@
         <v>1.784750528729781</v>
       </c>
       <c r="D320" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E320">
         <v>2.020805677582523</v>
@@ -17435,7 +17435,7 @@
         <v>3.376305833526885</v>
       </c>
       <c r="D321" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E321">
         <v>2.171377923742256</v>
@@ -17471,7 +17471,7 @@
         <v>1</v>
       </c>
       <c r="P321" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="322" spans="1:16">
@@ -17521,7 +17521,7 @@
         <v>1</v>
       </c>
       <c r="P322" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="323" spans="1:16">
@@ -17571,7 +17571,7 @@
         <v>1</v>
       </c>
       <c r="P323" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="324" spans="1:16">
@@ -17621,7 +17621,7 @@
         <v>1</v>
       </c>
       <c r="P324" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="325" spans="1:16">
@@ -17635,7 +17635,7 @@
         <v>3.346413966869674</v>
       </c>
       <c r="D325" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E325">
         <v>2.137012109937338</v>
@@ -17671,7 +17671,7 @@
         <v>1</v>
       </c>
       <c r="P325" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="326" spans="1:16">
@@ -17721,7 +17721,7 @@
         <v>1</v>
       </c>
       <c r="P326" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="327" spans="1:16">
@@ -17735,7 +17735,7 @@
         <v>1.853546169841817</v>
       </c>
       <c r="D327" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E327">
         <v>1.909412654865697</v>
@@ -17771,7 +17771,7 @@
         <v>1</v>
       </c>
       <c r="P327" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="328" spans="1:16">
@@ -17785,7 +17785,7 @@
         <v>1.729057523143315</v>
       </c>
       <c r="D328" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E328">
         <v>1.909412654865697</v>
@@ -17821,7 +17821,7 @@
         <v>1</v>
       </c>
       <c r="P328" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="329" spans="1:16">
@@ -17835,7 +17835,7 @@
         <v>1.90213361560998</v>
       </c>
       <c r="D329" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E329">
         <v>1.909412654865697</v>
@@ -17871,7 +17871,7 @@
         <v>1</v>
       </c>
       <c r="P329" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="330" spans="1:16">
@@ -17885,7 +17885,7 @@
         <v>3.335708401471214</v>
       </c>
       <c r="D330" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E330">
         <v>2.124704231296676</v>
@@ -17921,7 +17921,7 @@
         <v>1</v>
       </c>
       <c r="P330" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="331" spans="1:16">
@@ -17971,7 +17971,7 @@
         <v>1</v>
       </c>
       <c r="P331" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="332" spans="1:16">
@@ -17985,7 +17985,7 @@
         <v>1.839336644715903</v>
       </c>
       <c r="D332" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E332">
         <v>2.572020438006287</v>
@@ -18021,7 +18021,7 @@
         <v>1</v>
       </c>
       <c r="P332" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="333" spans="1:16">
@@ -18035,7 +18035,7 @@
         <v>1.714214115855647</v>
       </c>
       <c r="D333" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E333">
         <v>2.572020438006287</v>
@@ -18071,7 +18071,7 @@
         <v>1</v>
       </c>
       <c r="P333" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="334" spans="1:16">
@@ -18085,7 +18085,7 @@
         <v>1.88846993345668</v>
       </c>
       <c r="D334" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E334">
         <v>2.572020438006287</v>
@@ -18121,7 +18121,7 @@
         <v>1</v>
       </c>
       <c r="P334" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="335" spans="1:16">
@@ -18135,7 +18135,7 @@
         <v>3.319807569063805</v>
       </c>
       <c r="D335" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E335">
         <v>2.106423504565129</v>
@@ -18235,7 +18235,7 @@
         <v>1.818231428017253</v>
       </c>
       <c r="D337" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E337">
         <v>2.552327466291189</v>
@@ -18285,7 +18285,7 @@
         <v>1.692167402501294</v>
       </c>
       <c r="D338" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E338">
         <v>2.552327466291189</v>
@@ -18335,7 +18335,7 @@
         <v>1.86817544998933</v>
       </c>
       <c r="D339" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E339">
         <v>2.552327466291189</v>
@@ -18385,7 +18385,7 @@
         <v>3.297653300651016</v>
       </c>
       <c r="D340" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E340">
         <v>2.080953383478715</v>
@@ -18421,7 +18421,7 @@
         <v>1</v>
       </c>
       <c r="P340" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="341" spans="1:16">
@@ -18471,7 +18471,7 @@
         <v>1</v>
       </c>
       <c r="P341" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="342" spans="1:16">
@@ -18485,7 +18485,7 @@
         <v>1.788826009252247</v>
       </c>
       <c r="D342" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E342">
         <v>2.524889696365481</v>
@@ -18521,7 +18521,7 @@
         <v>1</v>
       </c>
       <c r="P342" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="343" spans="1:16">
@@ -18535,7 +18535,7 @@
         <v>1.661450217843427</v>
       </c>
       <c r="D343" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E343">
         <v>2.524889696365481</v>
@@ -18571,7 +18571,7 @@
         <v>1</v>
       </c>
       <c r="P343" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="344" spans="1:16">
@@ -18585,7 +18585,7 @@
         <v>1.839899607409848</v>
       </c>
       <c r="D344" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E344">
         <v>2.524889696365481</v>
@@ -18621,7 +18621,7 @@
         <v>1</v>
       </c>
       <c r="P344" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="345" spans="1:16">
@@ -18635,7 +18635,7 @@
         <v>3.263703117123406</v>
       </c>
       <c r="D345" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E345">
         <v>2.041921840245493</v>
@@ -18735,7 +18735,7 @@
         <v>1.743763841313463</v>
       </c>
       <c r="D347" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E347">
         <v>2.48284284077948</v>
@@ -18785,7 +18785,7 @@
         <v>1.614377841669459</v>
       </c>
       <c r="D348" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E348">
         <v>2.48284284077948</v>
@@ -18835,7 +18835,7 @@
         <v>1.796568452118031</v>
       </c>
       <c r="D349" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E349">
         <v>2.48284284077948</v>
@@ -18885,7 +18885,7 @@
         <v>3.242126022559422</v>
       </c>
       <c r="D350" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E350">
         <v>2.017115279225386</v>
@@ -18921,7 +18921,7 @@
         <v>1</v>
       </c>
       <c r="P350" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="351" spans="1:16">
@@ -18971,7 +18971,7 @@
         <v>1</v>
       </c>
       <c r="P351" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="352" spans="1:16">
@@ -18985,7 +18985,7 @@
         <v>1.715124506916858</v>
       </c>
       <c r="D352" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E352">
         <v>2.456119893071122</v>
@@ -19021,7 +19021,7 @@
         <v>1</v>
       </c>
       <c r="P352" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="353" spans="1:16">
@@ -19035,7 +19035,7 @@
         <v>1.584460916147354</v>
       </c>
       <c r="D353" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E353">
         <v>2.456119893071122</v>
@@ -19071,7 +19071,7 @@
         <v>1</v>
       </c>
       <c r="P353" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="354" spans="1:16">
@@ -19085,7 +19085,7 @@
         <v>1.769029265635051</v>
       </c>
       <c r="D354" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E354">
         <v>2.456119893071122</v>
@@ -19121,7 +19121,7 @@
         <v>1</v>
       </c>
       <c r="P354" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="355" spans="1:16">
@@ -19135,7 +19135,7 @@
         <v>3.218796578894542</v>
       </c>
       <c r="D355" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E355">
         <v>1.990294093169876</v>
@@ -19235,7 +19235,7 @@
         <v>1.684159274947191</v>
       </c>
       <c r="D357" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E357">
         <v>2.427226684058535</v>
@@ -19285,7 +19285,7 @@
         <v>1.552114335539635</v>
       </c>
       <c r="D358" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E358">
         <v>2.427226684058535</v>
@@ -19335,7 +19335,7 @@
         <v>1.739253528325928</v>
       </c>
       <c r="D359" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E359">
         <v>2.427226684058535</v>
@@ -19385,7 +19385,7 @@
         <v>3.223084813618858</v>
       </c>
       <c r="D360" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E360">
         <v>1.995224152499308</v>
@@ -19421,7 +19421,7 @@
         <v>1</v>
       </c>
       <c r="P360" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="361" spans="1:16">
@@ -19435,7 +19435,7 @@
         <v>1.689851060181606</v>
       </c>
       <c r="D361" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E361">
         <v>2.432537606340457</v>
@@ -19471,7 +19471,7 @@
         <v>1</v>
       </c>
       <c r="P361" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="362" spans="1:16">
@@ -19485,7 +19485,7 @@
         <v>1.558060029409038</v>
       </c>
       <c r="D362" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E362">
         <v>2.432537606340457</v>
@@ -19521,7 +19521,7 @@
         <v>1</v>
       </c>
       <c r="P362" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="363" spans="1:16">
@@ -19535,7 +19535,7 @@
         <v>1.5546355793606</v>
       </c>
       <c r="D363" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E363">
         <v>2.429478755941318</v>
@@ -19585,7 +19585,7 @@
         <v>2.749895863416445</v>
       </c>
       <c r="D364" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E364">
         <v>2.144120683335579</v>
@@ -19621,7 +19621,7 @@
         <v>1</v>
       </c>
       <c r="P364" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="365" spans="1:16">
@@ -19635,7 +19635,7 @@
         <v>1.575757316392718</v>
       </c>
       <c r="D365" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E365">
         <v>2.448345503254703</v>
@@ -19671,7 +19671,7 @@
         <v>1</v>
       </c>
       <c r="P365" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="366" spans="1:16">
@@ -19685,7 +19685,7 @@
         <v>1.708690594836302</v>
       </c>
       <c r="D366" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E366">
         <v>1.95524223097577</v>
@@ -19721,7 +19721,7 @@
         <v>1</v>
       </c>
       <c r="P366" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="367" spans="1:16">
@@ -19735,7 +19735,7 @@
         <v>2.776972324350222</v>
       </c>
       <c r="D367" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E367">
         <v>2.170167242074328</v>
@@ -19771,7 +19771,7 @@
         <v>1</v>
       </c>
       <c r="P367" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="368" spans="1:16">
@@ -19785,7 +19785,7 @@
         <v>1.603764011567165</v>
       </c>
       <c r="D368" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E368">
         <v>2.473362159798427</v>
@@ -19821,7 +19821,7 @@
         <v>1</v>
       </c>
       <c r="P368" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="369" spans="1:16">
@@ -19835,7 +19835,7 @@
         <v>1.733308579562596</v>
       </c>
       <c r="D369" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E369">
         <v>2.069952921130998</v>
@@ -19871,7 +19871,7 @@
         <v>1</v>
       </c>
       <c r="P369" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="370" spans="1:16">
@@ -19885,7 +19885,7 @@
         <v>2.804318151096002</v>
       </c>
       <c r="D370" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E370">
         <v>2.196472920808915</v>
@@ -19921,7 +19921,7 @@
         <v>1</v>
       </c>
       <c r="P370" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="371" spans="1:16">
@@ -19935,7 +19935,7 @@
         <v>1.632049326839176</v>
       </c>
       <c r="D371" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E371">
         <v>2.498627690521825</v>
@@ -19971,7 +19971,7 @@
         <v>1</v>
       </c>
       <c r="P371" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="372" spans="1:16">
@@ -19985,7 +19985,7 @@
         <v>1.758171472346181</v>
       </c>
       <c r="D372" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E372">
         <v>2.648741745065742</v>
@@ -20021,7 +20021,7 @@
         <v>1</v>
       </c>
       <c r="P372" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="373" spans="1:16">
@@ -20035,7 +20035,7 @@
         <v>1.836308899819077</v>
       </c>
       <c r="D373" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E373">
         <v>2.387421432319158</v>
@@ -20071,7 +20071,7 @@
         <v>1</v>
       </c>
       <c r="P373" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="374" spans="1:16">
@@ -20121,7 +20121,7 @@
         <v>1</v>
       </c>
       <c r="P374" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="375" spans="1:16">
@@ -20135,7 +20135,7 @@
         <v>1.66686196794393</v>
       </c>
       <c r="D375" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E375">
         <v>2.529723679551338</v>
@@ -20171,7 +20171,7 @@
         <v>1</v>
       </c>
       <c r="P375" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="376" spans="1:16">
@@ -20185,7 +20185,7 @@
         <v>1.844881242140559</v>
       </c>
       <c r="D376" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E376">
         <v>2.529723679551338</v>
@@ -20221,7 +20221,7 @@
         <v>1</v>
       </c>
       <c r="P376" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="377" spans="1:16">
@@ -20235,7 +20235,7 @@
         <v>1.788771907765661</v>
       </c>
       <c r="D377" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E377">
         <v>2.679961622497764</v>
@@ -20271,7 +20271,7 @@
         <v>1</v>
       </c>
       <c r="P377" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="378" spans="1:16">
@@ -20285,7 +20285,7 @@
         <v>1.861508767932467</v>
       </c>
       <c r="D378" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E378">
         <v>2.411732640096055</v>
@@ -20321,7 +20321,7 @@
         <v>1</v>
       </c>
       <c r="P378" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="379" spans="1:16">
@@ -20371,7 +20371,7 @@
         <v>1</v>
       </c>
       <c r="P379" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="380" spans="1:16">
@@ -20385,7 +20385,7 @@
         <v>1.693616991646184</v>
       </c>
       <c r="D380" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E380">
         <v>2.55362229502915</v>
@@ -20421,7 +20421,7 @@
         <v>1</v>
       </c>
       <c r="P380" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="381" spans="1:16">
@@ -20435,7 +20435,7 @@
         <v>1.869509828609061</v>
       </c>
       <c r="D381" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E381">
         <v>2.55362229502915</v>
@@ -20471,7 +20471,7 @@
         <v>1</v>
       </c>
       <c r="P381" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="382" spans="1:16">
@@ -20485,7 +20485,7 @@
         <v>2.574954921244757</v>
       </c>
       <c r="D382" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E382">
         <v>2.17950982860906</v>
@@ -20521,7 +20521,7 @@
         <v>1</v>
       </c>
       <c r="P382" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="383" spans="1:16">
@@ -20535,7 +20535,7 @@
         <v>1.812289668813548</v>
       </c>
       <c r="D383" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E383">
         <v>2.703955451583056</v>
@@ -20571,7 +20571,7 @@
         <v>1</v>
       </c>
       <c r="P383" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="384" spans="1:16">
@@ -20585,7 +20585,7 @@
         <v>1.878354735459471</v>
       </c>
       <c r="D384" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E384">
         <v>2.42798454327702</v>
@@ -20621,7 +20621,7 @@
         <v>1</v>
       </c>
       <c r="P384" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="385" spans="1:16">
@@ -20671,7 +20671,7 @@
         <v>1</v>
       </c>
       <c r="P385" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="386" spans="1:16">
@@ -20685,7 +20685,7 @@
         <v>1.711502571778759</v>
       </c>
       <c r="D386" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E386">
         <v>2.569598382620882</v>
@@ -20721,7 +20721,7 @@
         <v>1</v>
       </c>
       <c r="P386" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="387" spans="1:16">
@@ -20735,7 +20735,7 @@
         <v>1.885973897627895</v>
       </c>
       <c r="D387" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E387">
         <v>2.569598382620882</v>
@@ -20771,7 +20771,7 @@
         <v>1</v>
       </c>
       <c r="P387" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="388" spans="1:16">
@@ -20785,7 +20785,7 @@
         <v>2.591185607841933</v>
       </c>
       <c r="D388" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E388">
         <v>2.195973897627894</v>
@@ -20821,7 +20821,7 @@
         <v>1</v>
       </c>
       <c r="P388" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="389" spans="1:16">
@@ -20835,7 +20835,7 @@
         <v>1.828011157399832</v>
       </c>
       <c r="D389" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E389">
         <v>2.719995188926148</v>
@@ -20871,7 +20871,7 @@
         <v>1</v>
       </c>
       <c r="P389" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="390" spans="1:16">
@@ -20885,7 +20885,7 @@
         <v>1.884937981108568</v>
       </c>
       <c r="D390" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E390">
         <v>2.434335634167709</v>
@@ -20921,7 +20921,7 @@
         <v>1</v>
       </c>
       <c r="P390" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="391" spans="1:16">
@@ -20971,7 +20971,7 @@
         <v>1</v>
       </c>
       <c r="P391" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="392" spans="1:16">
@@ -20985,7 +20985,7 @@
         <v>1.718492088255065</v>
       </c>
       <c r="D392" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E392">
         <v>2.575841687373739</v>
@@ -21021,7 +21021,7 @@
         <v>1</v>
       </c>
       <c r="P392" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="393" spans="1:16">
@@ -21035,7 +21035,7 @@
         <v>1.892407900932305</v>
       </c>
       <c r="D393" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E393">
         <v>2.575841687373739</v>
@@ -21071,7 +21071,7 @@
         <v>1</v>
       </c>
       <c r="P393" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="394" spans="1:16">
@@ -21085,7 +21085,7 @@
         <v>1.834154967256232</v>
       </c>
       <c r="D394" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E394">
         <v>2.726263367403121</v>
@@ -21121,7 +21121,7 @@
         <v>1</v>
       </c>
       <c r="P394" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="395" spans="1:16">
@@ -21135,7 +21135,7 @@
         <v>2.791624887079966</v>
       </c>
       <c r="D395" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E395">
         <v>2.637829766815571</v>
@@ -21171,7 +21171,7 @@
         <v>1</v>
       </c>
       <c r="P395" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="396" spans="1:16">
@@ -21185,7 +21185,7 @@
         <v>1.897004594528006</v>
       </c>
       <c r="D396" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E396">
         <v>2.445976724695786</v>
@@ -21221,7 +21221,7 @@
         <v>1</v>
       </c>
       <c r="P396" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="397" spans="1:16">
@@ -21271,7 +21271,7 @@
         <v>1</v>
       </c>
       <c r="P397" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="398" spans="1:16">
@@ -21285,7 +21285,7 @@
         <v>1.731303366734398</v>
       </c>
       <c r="D398" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E398">
         <v>2.587285213702252</v>
@@ -21321,7 +21321,7 @@
         <v>1</v>
       </c>
       <c r="P398" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="399" spans="1:16">
@@ -21335,7 +21335,7 @@
         <v>1.904200963921582</v>
       </c>
       <c r="D399" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E399">
         <v>2.587285213702252</v>
@@ -21371,7 +21371,7 @@
         <v>1</v>
       </c>
       <c r="P399" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="400" spans="1:16">
@@ -21385,7 +21385,7 @@
         <v>1.845416126631299</v>
       </c>
       <c r="D400" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E400">
         <v>2.737752485469994</v>
@@ -21421,7 +21421,7 @@
         <v>1</v>
       </c>
       <c r="P400" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="401" spans="1:16">
@@ -21435,7 +21435,7 @@
         <v>2.802612496024871</v>
       </c>
       <c r="D401" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E401">
         <v>2.813453713263602</v>
@@ -21471,7 +21471,7 @@
         <v>1</v>
       </c>
       <c r="P401" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="402" spans="1:16">
@@ -21485,7 +21485,7 @@
         <v>1.915149243214803</v>
       </c>
       <c r="D402" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E402">
         <v>2.463481511716044</v>
@@ -21521,7 +21521,7 @@
         <v>1</v>
       </c>
       <c r="P402" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="403" spans="1:16">
@@ -21571,7 +21571,7 @@
         <v>1</v>
       </c>
       <c r="P403" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="404" spans="1:16">
@@ -21585,7 +21585,7 @@
         <v>1.750567773337632</v>
       </c>
       <c r="D404" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E404">
         <v>2.60449292209162</v>
@@ -21621,7 +21621,7 @@
         <v>1</v>
       </c>
       <c r="P404" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="405" spans="1:16">
@@ -21635,7 +21635,7 @@
         <v>1.921934272965604</v>
       </c>
       <c r="D405" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E405">
         <v>2.60449292209162</v>
@@ -21671,7 +21671,7 @@
         <v>1</v>
       </c>
       <c r="P405" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="406" spans="1:16">
@@ -21685,7 +21685,7 @@
         <v>1.862349608592151</v>
       </c>
       <c r="D406" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E406">
         <v>2.75502875046649</v>
@@ -21721,7 +21721,7 @@
         <v>1</v>
       </c>
       <c r="P406" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="407" spans="1:16">
@@ -21735,7 +21735,7 @@
         <v>2.819134638342948</v>
       </c>
       <c r="D407" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E407">
         <v>2.769730713091974</v>
@@ -21771,7 +21771,7 @@
         <v>1</v>
       </c>
       <c r="P407" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="408" spans="1:16">
@@ -21785,7 +21785,7 @@
         <v>1.92753511972947</v>
       </c>
       <c r="D408" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E408">
         <v>2.475430606691152</v>
@@ -21885,7 +21885,7 @@
         <v>1.76371801754653</v>
       </c>
       <c r="D410" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E410">
         <v>2.616239225637646</v>
@@ -21935,7 +21935,7 @@
         <v>1.934039361347697</v>
       </c>
       <c r="D411" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E411">
         <v>2.616239225637646</v>
@@ -21985,7 +21985,7 @@
         <v>1.873908720049794</v>
       </c>
       <c r="D412" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E412">
         <v>2.766821852034614</v>
@@ -22035,7 +22035,7 @@
         <v>2.830412961668017</v>
       </c>
       <c r="D413" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E413">
         <v>2.221708855759843</v>
@@ -22085,7 +22085,7 @@
         <v>1.937685341557977</v>
       </c>
       <c r="D414" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E414">
         <v>2.485222886188172</v>
@@ -22121,7 +22121,7 @@
         <v>1</v>
       </c>
       <c r="P414" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="415" spans="1:16">
@@ -22171,7 +22171,7 @@
         <v>1</v>
       </c>
       <c r="P415" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="416" spans="1:16">
@@ -22185,7 +22185,7 @@
         <v>1.774494638455131</v>
       </c>
       <c r="D416" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E416">
         <v>2.625865317623621</v>
@@ -22221,7 +22221,7 @@
         <v>1</v>
       </c>
       <c r="P416" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="417" spans="1:16">
@@ -22235,7 +22235,7 @@
         <v>1.943959477391676</v>
       </c>
       <c r="D417" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E417">
         <v>2.625865317623621</v>
@@ -22271,7 +22271,7 @@
         <v>1</v>
       </c>
       <c r="P417" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="418" spans="1:16">
@@ -22285,7 +22285,7 @@
         <v>1.883381408179421</v>
       </c>
       <c r="D418" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E418">
         <v>2.776486294984675</v>
@@ -22321,7 +22321,7 @@
         <v>1</v>
       </c>
       <c r="P418" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="419" spans="1:16">
@@ -22335,7 +22335,7 @@
         <v>2.839655544013116</v>
       </c>
       <c r="D419" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E419">
         <v>2.231475567947474</v>
@@ -22371,7 +22371,7 @@
         <v>1</v>
       </c>
       <c r="P419" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="420" spans="1:16">
@@ -22385,7 +22385,7 @@
         <v>1.950149148490695</v>
       </c>
       <c r="D420" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E420">
         <v>2.49724716340538</v>
@@ -22421,7 +22421,7 @@
         <v>1</v>
       </c>
       <c r="P420" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="421" spans="1:16">
@@ -22471,7 +22471,7 @@
         <v>1</v>
       </c>
       <c r="P421" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="422" spans="1:16">
@@ -22485,7 +22485,7 @@
         <v>1.787727622389998</v>
       </c>
       <c r="D422" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E422">
         <v>2.637685527472915</v>
@@ -22521,7 +22521,7 @@
         <v>1</v>
       </c>
       <c r="P422" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="423" spans="1:16">
@@ -22535,7 +22535,7 @@
         <v>1.956140729507283</v>
       </c>
       <c r="D423" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E423">
         <v>2.637685527472915</v>
@@ -22571,7 +22571,7 @@
         <v>1</v>
       </c>
       <c r="P423" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="424" spans="1:16">
@@ -22585,7 +22585,7 @@
         <v>1.895013248150637</v>
       </c>
       <c r="D424" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E424">
         <v>2.788353597303487</v>
@@ -22621,7 +22621,7 @@
         <v>1</v>
       </c>
       <c r="P424" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="425" spans="1:16">
@@ -22635,7 +22635,7 @@
         <v>2.85100482916722</v>
       </c>
       <c r="D425" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E425">
         <v>2.243468450185002</v>
@@ -22671,7 +22671,7 @@
         <v>1</v>
       </c>
       <c r="P425" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="426" spans="1:16">
@@ -22735,7 +22735,7 @@
         <v>1.796280604882195</v>
       </c>
       <c r="D427" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E427">
         <v>2.645325380161676</v>
@@ -22785,7 +22785,7 @@
         <v>1.964013937590256</v>
       </c>
       <c r="D428" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E428">
         <v>2.645325380161676</v>
@@ -22835,7 +22835,7 @@
         <v>1.902531350198938</v>
       </c>
       <c r="D429" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E429">
         <v>2.796023887652364</v>
@@ -22885,7 +22885,7 @@
         <v>2.858340305254835</v>
       </c>
       <c r="D430" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E430">
         <v>2.251219907627515</v>
@@ -22971,7 +22971,7 @@
         <v>1</v>
       </c>
       <c r="P431" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="432" spans="1:16">
@@ -22985,7 +22985,7 @@
         <v>1.81059278070445</v>
       </c>
       <c r="D432" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E432">
         <v>2.658109565682619</v>
@@ -23021,7 +23021,7 @@
         <v>1</v>
       </c>
       <c r="P432" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="433" spans="1:16">
@@ -23035,7 +23035,7 @@
         <v>1.977188609521534</v>
       </c>
       <c r="D433" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E433">
         <v>2.658109565682619</v>
@@ -23071,7 +23071,7 @@
         <v>1</v>
       </c>
       <c r="P433" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="434" spans="1:16">
@@ -23085,7 +23085,7 @@
         <v>1.915111803679711</v>
       </c>
       <c r="D434" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E434">
         <v>2.808859006183351</v>
@@ -23121,7 +23121,7 @@
         <v>1</v>
       </c>
       <c r="P434" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="435" spans="1:16">
@@ -23135,7 +23135,7 @@
         <v>2.870615160675342</v>
       </c>
       <c r="D435" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E435">
         <v>2.26419084751862</v>
@@ -23171,7 +23171,7 @@
         <v>1</v>
       </c>
       <c r="P435" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="436" spans="1:16">
@@ -23221,7 +23221,7 @@
         <v>1</v>
       </c>
       <c r="P436" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="437" spans="1:16">
@@ -23235,7 +23235,7 @@
         <v>1.82632056259726</v>
       </c>
       <c r="D437" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E437">
         <v>2.672158224953424</v>
@@ -23271,7 +23271,7 @@
         <v>1</v>
       </c>
       <c r="P437" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="438" spans="1:16">
@@ -23285,7 +23285,7 @@
         <v>1.991666377906849</v>
       </c>
       <c r="D438" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E438">
         <v>2.672158224953424</v>
@@ -23321,7 +23321,7 @@
         <v>1</v>
       </c>
       <c r="P438" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="439" spans="1:16">
@@ -23335,7 +23335,7 @@
         <v>1.928936579934245</v>
       </c>
       <c r="D439" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E439">
         <v>2.822963636208222</v>
@@ -23371,7 +23371,7 @@
         <v>1</v>
       </c>
       <c r="P439" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="440" spans="1:16">
@@ -23385,7 +23385,7 @@
         <v>2.884104112405478</v>
       </c>
       <c r="D440" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E440">
         <v>2.278444732887671</v>
@@ -23421,7 +23421,7 @@
         <v>1</v>
       </c>
       <c r="P440" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="441" spans="1:16">
@@ -23435,7 +23435,7 @@
         <v>1.850091985515281</v>
       </c>
       <c r="D441" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E441">
         <v>2.693391773538558</v>
@@ -23485,7 +23485,7 @@
         <v>2.013548494377055</v>
       </c>
       <c r="D442" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E442">
         <v>2.693391773538558</v>
@@ -23535,7 +23535,7 @@
         <v>1.949831745274995</v>
       </c>
       <c r="D443" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E443">
         <v>2.844281780604454</v>
@@ -23585,7 +23585,7 @@
         <v>2.90449170287965</v>
       </c>
       <c r="D444" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E444">
         <v>2.29998846611349</v>
@@ -23635,7 +23635,7 @@
         <v>1.883787347386825</v>
       </c>
       <c r="D445" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E445">
         <v>2.723489765815277</v>
@@ -23671,7 +23671,7 @@
         <v>1</v>
       </c>
       <c r="P445" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="446" spans="1:16">
@@ -23685,7 +23685,7 @@
         <v>2.044565814439117</v>
       </c>
       <c r="D446" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E446">
         <v>2.723489765815277</v>
@@ -23721,7 +23721,7 @@
         <v>1</v>
       </c>
       <c r="P446" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="447" spans="1:16">
@@ -23735,7 +23735,7 @@
         <v>2.74752944335815</v>
       </c>
       <c r="D447" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E447">
         <v>2.354565814439116</v>
@@ -23771,7 +23771,7 @@
         <v>1</v>
       </c>
       <c r="P447" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="448" spans="1:16">
@@ -23785,7 +23785,7 @@
         <v>1.979450088272404</v>
       </c>
       <c r="D448" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E448">
         <v>2.874499685200998</v>
@@ -23821,7 +23821,7 @@
         <v>1</v>
       </c>
       <c r="P448" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="449" spans="1:16">
@@ -23835,7 +23835,7 @@
         <v>2.933390571958093</v>
       </c>
       <c r="D449" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E449">
         <v>2.330526136896243</v>
@@ -23871,7 +23871,7 @@
         <v>1</v>
       </c>
       <c r="P449" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="450" spans="1:16">
@@ -23921,7 +23921,7 @@
         <v>1</v>
       </c>
       <c r="P450" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="451" spans="1:16">
@@ -23935,7 +23935,7 @@
         <v>1.920897553279229</v>
       </c>
       <c r="D451" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E451">
         <v>2.756638028018099</v>
@@ -23971,7 +23971,7 @@
         <v>1</v>
       </c>
       <c r="P451" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="452" spans="1:16">
@@ -23985,7 +23985,7 @@
         <v>2.078726573362612</v>
       </c>
       <c r="D452" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E452">
         <v>2.756638028018099</v>
@@ -24021,7 +24021,7 @@
         <v>1</v>
       </c>
       <c r="P452" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="453" spans="1:16">
@@ -24035,7 +24035,7 @@
         <v>2.012070091316616</v>
       </c>
       <c r="D453" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E453">
         <v>2.907780012193474</v>
@@ -24071,7 +24071,7 @@
         <v>1</v>
       </c>
       <c r="P453" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="454" spans="1:16">
@@ -24085,7 +24085,7 @@
         <v>2.965218186264387</v>
       </c>
       <c r="D454" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E454">
         <v>2.364158636661127</v>
@@ -24121,7 +24121,7 @@
         <v>1</v>
       </c>
       <c r="P454" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="455" spans="1:16">
@@ -24135,7 +24135,7 @@
         <v>1.971362962924253</v>
       </c>
       <c r="D455" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E455">
         <v>2.801715671508852</v>
@@ -24185,7 +24185,7 @@
         <v>2.125181090426125</v>
       </c>
       <c r="D456" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E456">
         <v>2.801715671508852</v>
@@ -24235,7 +24235,7 @@
         <v>2.056429365986798</v>
       </c>
       <c r="D457" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E457">
         <v>2.95303724788937</v>
@@ -24285,7 +24285,7 @@
         <v>3.008499907703719</v>
       </c>
       <c r="D458" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E458">
         <v>2.409894784904068</v>
@@ -24335,7 +24335,7 @@
         <v>2.008171638992437</v>
       </c>
       <c r="D459" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E459">
         <v>2.834594595683633</v>
@@ -24371,7 +24371,7 @@
         <v>1</v>
       </c>
       <c r="P459" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="460" spans="1:16">
@@ -24385,7 +24385,7 @@
         <v>2.159064284529219</v>
       </c>
       <c r="D460" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E460">
         <v>2.834594595683633</v>
@@ -24421,7 +24421,7 @@
         <v>1</v>
       </c>
       <c r="P460" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="461" spans="1:16">
@@ -24435,7 +24435,7 @@
         <v>2.088784323242461</v>
       </c>
       <c r="D461" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E461">
         <v>2.986047163793931</v>
@@ -24471,7 +24471,7 @@
         <v>1</v>
       </c>
       <c r="P461" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="462" spans="1:16">
@@ -24485,7 +24485,7 @@
         <v>3.040068914580697</v>
       </c>
       <c r="D462" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E462">
         <v>2.443254012088044</v>
@@ -24521,7 +24521,7 @@
         <v>1</v>
       </c>
       <c r="P462" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="463" spans="1:16">
@@ -24535,7 +24535,7 @@
         <v>2.067700645146257</v>
       </c>
       <c r="D463" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E463">
         <v>2.887768191927794</v>
@@ -24585,7 +24585,7 @@
         <v>2.213862041083626</v>
       </c>
       <c r="D464" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E464">
         <v>2.887768191927794</v>
@@ -24635,7 +24635,7 @@
         <v>2.914425852356924</v>
       </c>
       <c r="D465" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E465">
         <v>2.523862041083625</v>
@@ -24685,7 +24685,7 @@
         <v>2.141110531498665</v>
       </c>
       <c r="D466" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E466">
         <v>3.039432607035081</v>
@@ -24735,7 +24735,7 @@
         <v>3.091124040854972</v>
       </c>
       <c r="D467" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E467">
         <v>2.497204380654495</v>
@@ -24785,7 +24785,7 @@
         <v>2.102053433035913</v>
       </c>
       <c r="D468" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E468">
         <v>2.918453422391508</v>
@@ -24821,7 +24821,7 @@
         <v>1</v>
       </c>
       <c r="P468" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="469" spans="1:16">
@@ -24835,7 +24835,7 @@
         <v>2.245484536222857</v>
       </c>
       <c r="D469" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E469">
         <v>2.918453422391508</v>
@@ -24871,7 +24871,7 @@
         <v>1</v>
       </c>
       <c r="P469" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="470" spans="1:16">
@@ -24885,7 +24885,7 @@
         <v>2.945600090477427</v>
       </c>
       <c r="D470" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E470">
         <v>2.555484536222856</v>
@@ -24921,7 +24921,7 @@
         <v>1</v>
       </c>
       <c r="P470" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="471" spans="1:16">
@@ -24935,7 +24935,7 @@
         <v>2.171306754305586</v>
       </c>
       <c r="D471" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E471">
         <v>3.070240089412991</v>
@@ -24971,7 +24971,7 @@
         <v>1</v>
       </c>
       <c r="P471" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="472" spans="1:16">
@@ -24985,7 +24985,7 @@
         <v>3.120586752176706</v>
       </c>
       <c r="D472" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E472">
         <v>2.528337868136934</v>
@@ -25021,7 +25021,7 @@
         <v>1</v>
       </c>
       <c r="P472" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="473" spans="1:16">
@@ -25035,7 +25035,7 @@
         <v>2.150109762840597</v>
       </c>
       <c r="D473" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E473">
         <v>2.961379183177897</v>
@@ -25071,7 +25071,7 @@
         <v>1</v>
       </c>
       <c r="P473" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="474" spans="1:16">
@@ -25085,7 +25085,7 @@
         <v>2.289721442425034</v>
       </c>
       <c r="D474" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E474">
         <v>2.961379183177897</v>
@@ -25121,7 +25121,7 @@
         <v>1</v>
       </c>
       <c r="P474" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="475" spans="1:16">
@@ -25135,7 +25135,7 @@
         <v>2.989209927132926</v>
       </c>
       <c r="D475" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E475">
         <v>2.599721442425032</v>
@@ -25171,7 +25171,7 @@
         <v>1</v>
       </c>
       <c r="P475" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="476" spans="1:16">
@@ -25185,7 +25185,7 @@
         <v>2.213548439222873</v>
       </c>
       <c r="D476" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E476">
         <v>3.113336869166659</v>
@@ -25221,7 +25221,7 @@
         <v>1</v>
       </c>
       <c r="P476" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="477" spans="1:16">
@@ -25235,7 +25235,7 @@
         <v>3.161802323290331</v>
       </c>
       <c r="D477" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E477">
         <v>2.571890698470007</v>
@@ -25271,7 +25271,7 @@
         <v>1</v>
       </c>
       <c r="P477" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="478" spans="1:16">
@@ -25285,7 +25285,7 @@
         <v>2.189716387261424</v>
       </c>
       <c r="D478" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E478">
         <v>2.99675734235807</v>
@@ -25335,7 +25335,7 @@
         <v>2.326180209388927</v>
       </c>
       <c r="D479" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E479">
         <v>2.99675734235807</v>
@@ -25385,7 +25385,7 @@
         <v>2.248362803037622</v>
       </c>
       <c r="D480" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E480">
         <v>3.148855977188184</v>
@@ -25435,7 +25435,7 @@
         <v>3.19577099405695</v>
       </c>
       <c r="D481" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E481">
         <v>2.607785670068477</v>
@@ -25485,7 +25485,7 @@
         <v>2.215826782258592</v>
       </c>
       <c r="D482" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E482">
         <v>3.020080150700736</v>
@@ -25521,7 +25521,7 @@
         <v>1</v>
       </c>
       <c r="P482" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="483" spans="1:16">
@@ -25535,7 +25535,7 @@
         <v>2.350215400987747</v>
       </c>
       <c r="D483" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E483">
         <v>3.020080150700736</v>
@@ -25571,7 +25571,7 @@
         <v>1</v>
       </c>
       <c r="P483" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="484" spans="1:16">
@@ -25585,7 +25585,7 @@
         <v>2.271313933159689</v>
       </c>
       <c r="D484" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E484">
         <v>3.172271705086001</v>
@@ -25621,7 +25621,7 @@
         <v>1</v>
       </c>
       <c r="P484" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="485" spans="1:16">
@@ -25635,7 +25635,7 @@
         <v>3.218164606848116</v>
       </c>
       <c r="D485" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E485">
         <v>2.631449183446694</v>
@@ -25671,7 +25671,7 @@
         <v>1</v>
       </c>
       <c r="P485" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="486" spans="1:16">
@@ -25721,7 +25721,7 @@
         <v>1</v>
       </c>
       <c r="P486" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="487" spans="1:16">
@@ -25735,7 +25735,7 @@
         <v>2.227304742320833</v>
       </c>
       <c r="D487" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E487">
         <v>3.030332705774125</v>
@@ -25771,7 +25771,7 @@
         <v>1</v>
       </c>
       <c r="P487" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="488" spans="1:16">
@@ -25785,7 +25785,7 @@
         <v>2.360781115113841</v>
       </c>
       <c r="D488" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E488">
         <v>3.030332705774125</v>
@@ -25821,7 +25821,7 @@
         <v>1</v>
       </c>
       <c r="P488" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="489" spans="1:16">
@@ -25835,7 +25835,7 @@
         <v>2.28140310090123</v>
       </c>
       <c r="D489" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E489">
         <v>3.182565106992353</v>
@@ -25871,7 +25871,7 @@
         <v>1</v>
       </c>
       <c r="P489" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="490" spans="1:16">
@@ -25885,7 +25885,7 @@
         <v>3.228008693591889</v>
       </c>
       <c r="D490" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E490">
         <v>2.641851510240944</v>
@@ -25921,7 +25921,7 @@
         <v>1</v>
       </c>
       <c r="P490" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="491" spans="1:16">
@@ -25935,7 +25935,7 @@
         <v>2.326764722017106</v>
       </c>
       <c r="D491" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E491">
         <v>2.338905512271317</v>
@@ -25971,7 +25971,7 @@
         <v>1</v>
       </c>
       <c r="P491" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="492" spans="1:16">
@@ -25985,7 +25985,7 @@
         <v>2.245345573811253</v>
       </c>
       <c r="D492" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E492">
         <v>3.046447469845635</v>
@@ -26021,7 +26021,7 @@
         <v>1</v>
       </c>
       <c r="P492" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="493" spans="1:16">
@@ -26035,7 +26035,7 @@
         <v>2.377388096414631</v>
       </c>
       <c r="D493" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E493">
         <v>3.046447469845635</v>
@@ -26071,7 +26071,7 @@
         <v>1</v>
       </c>
       <c r="P493" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="494" spans="1:16">
@@ -26085,7 +26085,7 @@
         <v>2.297261055983554</v>
       </c>
       <c r="D494" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E494">
         <v>3.198744073311161</v>
@@ -26121,7 +26121,7 @@
         <v>1</v>
       </c>
       <c r="P494" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="495" spans="1:16">
@@ -26135,7 +26135,7 @@
         <v>3.243481435190432</v>
       </c>
       <c r="D495" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E495">
         <v>2.658201682552544</v>
@@ -26171,7 +26171,7 @@
         <v>1</v>
       </c>
       <c r="P495" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="496" spans="1:16">
@@ -26221,7 +26221,7 @@
         <v>1</v>
       </c>
       <c r="P496" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="497" spans="1:16">
@@ -26235,7 +26235,7 @@
         <v>2.301170929293026</v>
       </c>
       <c r="D497" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E497">
         <v>3.202733093853617</v>
@@ -26285,7 +26285,7 @@
         <v>3.247296331820319</v>
       </c>
       <c r="D498" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E498">
         <v>2.662232914952593</v>
@@ -26385,7 +26385,7 @@
         <v>2.309276220482282</v>
       </c>
       <c r="D500" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E500">
         <v>3.211002459763304</v>
@@ -26421,7 +26421,7 @@
         <v>1</v>
       </c>
       <c r="P500" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="501" spans="1:16">
@@ -26435,7 +26435,7 @@
         <v>3.25520473334506</v>
       </c>
       <c r="D501" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E501">
         <v>2.670589787379843</v>
@@ -26471,7 +26471,7 @@
         <v>1</v>
       </c>
       <c r="P501" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="502" spans="1:16">
@@ -26485,7 +26485,7 @@
         <v>2.35659384998981</v>
       </c>
       <c r="D502" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E502">
         <v>2.377701080695644</v>
@@ -26521,7 +26521,7 @@
         <v>1</v>
       </c>
       <c r="P502" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="503" spans="1:16">
@@ -26535,7 +26535,7 @@
         <v>2.318802840630408</v>
       </c>
       <c r="D503" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E503">
         <v>3.220721926473129</v>
@@ -26585,7 +26585,7 @@
         <v>3.264499937619139</v>
       </c>
       <c r="D504" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E504">
         <v>2.680412105589244</v>
@@ -26735,7 +26735,7 @@
         <v>2.968469110715926</v>
       </c>
       <c r="D507" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E507">
         <v>3.65607053595874</v>
@@ -26771,7 +26771,7 @@
         <v>1</v>
       </c>
       <c r="P507" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="508" spans="1:16">
@@ -26785,7 +26785,7 @@
         <v>3.056098677724048</v>
       </c>
       <c r="D508" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E508">
         <v>3.65607053595874</v>
@@ -26821,7 +26821,7 @@
         <v>1</v>
       </c>
       <c r="P508" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="509" spans="1:16">
@@ -26835,7 +26835,7 @@
         <v>3.085552267926261</v>
       </c>
       <c r="D509" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E509">
         <v>3.65607053595874</v>
@@ -26871,7 +26871,7 @@
         <v>1</v>
       </c>
       <c r="P509" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="510" spans="1:16">
@@ -26885,7 +26885,7 @@
         <v>3.115403587495276</v>
       </c>
       <c r="D510" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E510">
         <v>4.899694426383849</v>
@@ -26921,7 +26921,7 @@
         <v>1</v>
       </c>
       <c r="P510" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="511" spans="1:16">
@@ -26935,7 +26935,7 @@
         <v>2.857657467623699</v>
       </c>
       <c r="D511" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E511">
         <v>4.899694426383849</v>
@@ -26971,7 +26971,7 @@
         <v>1</v>
       </c>
       <c r="P511" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="512" spans="1:16">
@@ -26985,7 +26985,7 @@
         <v>4.634833021734408</v>
       </c>
       <c r="D512" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E512">
         <v>3.48240231940969</v>
@@ -27021,7 +27021,7 @@
         <v>1</v>
       </c>
       <c r="P512" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="513" spans="1:16">
@@ -27035,7 +27035,7 @@
         <v>3.013404560606677</v>
       </c>
       <c r="D513" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E513">
         <v>3.707166946903694</v>
@@ -27071,7 +27071,7 @@
         <v>1</v>
       </c>
       <c r="P513" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="514" spans="1:16">
@@ -27085,7 +27085,7 @@
         <v>3.101938488870459</v>
       </c>
       <c r="D514" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E514">
         <v>3.707166946903694</v>
@@ -27121,7 +27121,7 @@
         <v>1</v>
       </c>
       <c r="P514" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="515" spans="1:16">
@@ -27135,7 +27135,7 @@
         <v>3.133031233848563</v>
       </c>
       <c r="D515" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E515">
         <v>3.707166946903694</v>
@@ -27171,7 +27171,7 @@
         <v>1</v>
       </c>
       <c r="P515" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="516" spans="1:16">
@@ -27185,7 +27185,7 @@
         <v>2.923647577997855</v>
       </c>
       <c r="D516" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E516">
         <v>4.966814988327585</v>
@@ -27221,7 +27221,7 @@
         <v>1</v>
       </c>
       <c r="P516" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="517" spans="1:16">
@@ -27235,7 +27235,7 @@
         <v>4.706192777064061</v>
       </c>
       <c r="D517" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E517">
         <v>3.555881671432303</v>
@@ -27271,7 +27271,7 @@
         <v>1</v>
       </c>
       <c r="P517" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="518" spans="1:16">
@@ -27285,7 +27285,7 @@
         <v>3.058294813446018</v>
       </c>
       <c r="D518" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E518">
         <v>3.758211963968808</v>
@@ -27321,7 +27321,7 @@
         <v>1</v>
       </c>
       <c r="P518" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="519" spans="1:16">
@@ -27335,7 +27335,7 @@
         <v>3.147732193339273</v>
       </c>
       <c r="D519" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E519">
         <v>3.758211963968808</v>
@@ -27371,7 +27371,7 @@
         <v>1</v>
       </c>
       <c r="P519" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="520" spans="1:16">
@@ -27385,7 +27385,7 @@
         <v>3.18046244439579</v>
       </c>
       <c r="D520" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E520">
         <v>3.758211963968808</v>
@@ -27421,7 +27421,7 @@
         <v>1</v>
       </c>
       <c r="P520" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="521" spans="1:16">
@@ -27435,7 +27435,7 @@
         <v>3.225680173488445</v>
       </c>
       <c r="D521" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E521">
         <v>5.033868038952384</v>
@@ -27471,7 +27471,7 @@
         <v>1</v>
       </c>
       <c r="P521" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="522" spans="1:16">
@@ -27485,7 +27485,7 @@
         <v>2.989571314085818</v>
       </c>
       <c r="D522" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E522">
         <v>5.033868038952384</v>
@@ -27521,7 +27521,7 @@
         <v>1</v>
       </c>
       <c r="P522" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="523" spans="1:16">
@@ -27535,7 +27535,7 @@
         <v>4.77748075720201</v>
       </c>
       <c r="D523" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E523">
         <v>3.629287116326825</v>
@@ -27571,7 +27571,7 @@
         <v>1</v>
       </c>
       <c r="P523" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="524" spans="1:16">
@@ -27585,7 +27585,7 @@
         <v>3.100990526217007</v>
       </c>
       <c r="D524" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E524">
         <v>5.097643081613452</v>
@@ -27621,7 +27621,7 @@
         <v>1</v>
       </c>
       <c r="P524" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="525" spans="1:16">
@@ -27635,7 +27635,7 @@
         <v>3.19128719089559</v>
       </c>
       <c r="D525" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E525">
         <v>5.097643081613452</v>
@@ -27671,7 +27671,7 @@
         <v>1</v>
       </c>
       <c r="P525" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="526" spans="1:16">
@@ -27685,7 +27685,7 @@
         <v>3.225574895625517</v>
       </c>
       <c r="D526" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E526">
         <v>5.097643081613452</v>
@@ -27721,7 +27721,7 @@
         <v>1</v>
       </c>
       <c r="P526" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="527" spans="1:16">
@@ -27735,7 +27735,7 @@
         <v>3.205781960817575</v>
       </c>
       <c r="D527" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E527">
         <v>5.097643081613452</v>
@@ -27771,7 +27771,7 @@
         <v>1</v>
       </c>
       <c r="P527" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="528" spans="1:16">
@@ -27785,7 +27785,7 @@
         <v>3.27809654539346</v>
       </c>
       <c r="D528" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E528">
         <v>5.097643081613452</v>
@@ -27821,7 +27821,7 @@
         <v>1</v>
       </c>
       <c r="P528" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="529" spans="1:16">
@@ -27835,7 +27835,7 @@
         <v>3.052272250765228</v>
       </c>
       <c r="D529" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E529">
         <v>5.097643081613452</v>
@@ -27871,7 +27871,7 @@
         <v>1</v>
       </c>
       <c r="P529" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="530" spans="1:16">
@@ -27885,7 +27885,7 @@
         <v>4.845283697294303</v>
       </c>
       <c r="D530" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E530">
         <v>3.699104005134728</v>
@@ -27921,7 +27921,7 @@
         <v>1</v>
       </c>
       <c r="P530" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="531" spans="1:16">
@@ -27935,7 +27935,7 @@
         <v>3.135431759672713</v>
       </c>
       <c r="D531" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E531">
         <v>5.149088320265843</v>
@@ -27971,7 +27971,7 @@
         <v>1</v>
       </c>
       <c r="P531" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="532" spans="1:16">
@@ -27985,7 +27985,7 @@
         <v>3.226421581251035</v>
       </c>
       <c r="D532" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E532">
         <v>5.149088320265843</v>
@@ -28021,7 +28021,7 @@
         <v>1</v>
       </c>
       <c r="P532" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="533" spans="1:16">
@@ -28035,7 +28035,7 @@
         <v>3.261965632861735</v>
       </c>
       <c r="D533" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E533">
         <v>5.149088320265843</v>
@@ -28071,7 +28071,7 @@
         <v>1</v>
       </c>
       <c r="P533" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="534" spans="1:16">
@@ -28085,7 +28085,7 @@
         <v>3.248497754763896</v>
       </c>
       <c r="D534" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E534">
         <v>5.149088320265843</v>
@@ -28121,7 +28121,7 @@
         <v>1</v>
       </c>
       <c r="P534" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="535" spans="1:16">
@@ -28135,7 +28135,7 @@
         <v>3.320379116277444</v>
       </c>
       <c r="D535" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E535">
         <v>5.149088320265843</v>
@@ -28171,7 +28171,7 @@
         <v>1</v>
       </c>
       <c r="P535" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="536" spans="1:16">
@@ -28185,7 +28185,7 @@
         <v>3.102851043292947</v>
       </c>
       <c r="D536" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E536">
         <v>5.149088320265843</v>
@@ -28221,7 +28221,7 @@
         <v>1</v>
       </c>
       <c r="P536" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="537" spans="1:16">
@@ -28235,7 +28235,7 @@
         <v>4.899978108914215</v>
       </c>
       <c r="D537" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E537">
         <v>3.755423003238402</v>
@@ -28271,7 +28271,7 @@
         <v>1</v>
       </c>
       <c r="P537" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="538" spans="1:16">
@@ -28285,7 +28285,7 @@
         <v>3.340758667101504</v>
       </c>
       <c r="D538" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E538">
         <v>5.455787317211367</v>
@@ -28321,7 +28321,7 @@
         <v>1</v>
       </c>
       <c r="P538" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="539" spans="1:16">
@@ -28335,7 +28335,7 @@
         <v>3.596337846972439</v>
       </c>
       <c r="D539" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E539">
         <v>5.455787317211367</v>
@@ -28371,7 +28371,7 @@
         <v>1</v>
       </c>
       <c r="P539" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="540" spans="1:16">
@@ -28385,7 +28385,7 @@
         <v>3.478914818069512</v>
       </c>
       <c r="D540" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E540">
         <v>5.455787317211367</v>
@@ -28421,7 +28421,7 @@
         <v>1</v>
       </c>
       <c r="P540" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="541" spans="1:16">
@@ -28435,7 +28435,7 @@
         <v>3.503154774543503</v>
       </c>
       <c r="D541" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E541">
         <v>5.455787317211367</v>
@@ -28471,7 +28471,7 @@
         <v>1</v>
       </c>
       <c r="P541" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="542" spans="1:16">
@@ -28485,7 +28485,7 @@
         <v>3.572453407661722</v>
       </c>
       <c r="D542" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E542">
         <v>5.455787317211367</v>
@@ -28521,7 +28521,7 @@
         <v>1</v>
       </c>
       <c r="P542" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="543" spans="1:16">
@@ -28535,7 +28535,7 @@
         <v>3.404384583447808</v>
       </c>
       <c r="D543" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E543">
         <v>5.455787317211367</v>
@@ -28571,7 +28571,7 @@
         <v>1</v>
       </c>
       <c r="P543" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="544" spans="1:16">
@@ -28585,7 +28585,7 @@
         <v>5.25250104043668</v>
       </c>
       <c r="D544" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E544">
         <v>5.56320240731846</v>
@@ -28621,7 +28621,7 @@
         <v>1</v>
       </c>
       <c r="P544" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="545" spans="1:16">
@@ -28635,7 +28635,7 @@
         <v>3.408744253943432</v>
       </c>
       <c r="D545" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E545">
         <v>5.557338115167074</v>
@@ -28671,7 +28671,7 @@
         <v>1</v>
       </c>
       <c r="P545" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="546" spans="1:16">
@@ -28685,7 +28685,7 @@
         <v>3.550748645676077</v>
       </c>
       <c r="D546" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E546">
         <v>5.557338115167074</v>
@@ -28721,7 +28721,7 @@
         <v>1</v>
       </c>
       <c r="P546" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="547" spans="1:16">
@@ -28735,7 +28735,7 @@
         <v>3.587474005519777</v>
       </c>
       <c r="D547" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E547">
         <v>5.557338115167074</v>
@@ -28771,7 +28771,7 @@
         <v>1</v>
       </c>
       <c r="P547" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="548" spans="1:16">
@@ -28785,7 +28785,7 @@
         <v>3.655917474023632</v>
       </c>
       <c r="D548" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E548">
         <v>5.557338115167074</v>
@@ -28821,7 +28821,7 @@
         <v>1</v>
       </c>
       <c r="P548" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="549" spans="1:16">
@@ -28835,7 +28835,7 @@
         <v>3.504225052174785</v>
       </c>
       <c r="D549" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E549">
         <v>5.557338115167074</v>
@@ -28871,7 +28871,7 @@
         <v>1</v>
       </c>
       <c r="P549" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="550" spans="1:16">
@@ -28885,7 +28885,7 @@
         <v>5.346996730323884</v>
       </c>
       <c r="D550" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E550">
         <v>5.864438002961421</v>
@@ -28921,7 +28921,7 @@
         <v>1</v>
       </c>
       <c r="P550" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="551" spans="1:16">
@@ -28935,7 +28935,7 @@
         <v>5.267444590560391</v>
       </c>
       <c r="D551" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E551">
         <v>5.864438002961421</v>
@@ -28971,7 +28971,7 @@
         <v>1</v>
       </c>
       <c r="P551" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="552" spans="1:16">
@@ -28985,7 +28985,7 @@
         <v>3.796322429340982</v>
       </c>
       <c r="D552" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E552">
         <v>5.685955718590687</v>
@@ -29021,7 +29021,7 @@
         <v>1</v>
       </c>
       <c r="P552" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="553" spans="1:16">
@@ -29035,7 +29035,7 @@
         <v>3.641728676729411</v>
       </c>
       <c r="D553" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E553">
         <v>5.685955718590687</v>
@@ -29071,7 +29071,7 @@
         <v>1</v>
       </c>
       <c r="P553" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="554" spans="1:16">
@@ -29085,7 +29085,7 @@
         <v>3.69426723244667</v>
       </c>
       <c r="D554" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E554">
         <v>5.685955718590687</v>
@@ -29121,7 +29121,7 @@
         <v>1</v>
       </c>
       <c r="P554" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="555" spans="1:16">
@@ -29135,7 +29135,7 @@
         <v>3.761627605342749</v>
       </c>
       <c r="D555" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E555">
         <v>5.685955718590687</v>
@@ -29171,7 +29171,7 @@
         <v>1</v>
       </c>
       <c r="P555" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="556" spans="1:16">
@@ -29185,7 +29185,7 @@
         <v>3.630676464382844</v>
       </c>
       <c r="D556" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E556">
         <v>5.685955718590687</v>
@@ -29221,7 +29221,7 @@
         <v>1</v>
       </c>
       <c r="P556" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="557" spans="1:16">
@@ -29235,7 +29235,7 @@
         <v>5.466678794983334</v>
       </c>
       <c r="D557" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E557">
         <v>5.209318422087254</v>
@@ -29271,7 +29271,7 @@
         <v>1</v>
       </c>
       <c r="P557" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="558" spans="1:16">
@@ -29285,7 +29285,7 @@
         <v>5.390917489847062</v>
       </c>
       <c r="D558" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E558">
         <v>5.209318422087254</v>
@@ -29321,7 +29321,7 @@
         <v>1</v>
       </c>
       <c r="P558" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="559" spans="1:16">
@@ -29335,7 +29335,7 @@
         <v>4.159051079599863</v>
       </c>
       <c r="D559" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E559">
         <v>5.343391662540899</v>
@@ -29371,7 +29371,7 @@
         <v>1</v>
       </c>
       <c r="P559" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="560" spans="1:16">
@@ -29385,7 +29385,7 @@
         <v>4.237780255555339</v>
       </c>
       <c r="D560" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E560">
         <v>5.313343652467495</v>
@@ -29421,7 +29421,7 @@
         <v>1</v>
       </c>
       <c r="P560" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="561" spans="1:16">
@@ -29435,7 +29435,7 @@
         <v>4.283295642394084</v>
       </c>
       <c r="D561" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E561">
         <v>5.313343652467495</v>
@@ -29471,7 +29471,7 @@
         <v>1</v>
       </c>
       <c r="P561" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="562" spans="1:16">
@@ -29521,7 +29521,7 @@
         <v>1</v>
       </c>
       <c r="P562" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="563" spans="1:16">
@@ -29535,7 +29535,7 @@
         <v>4.047954928502808</v>
       </c>
       <c r="D563" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E563">
         <v>5.235960539108905</v>
@@ -29571,7 +29571,7 @@
         <v>1</v>
       </c>
       <c r="P563" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="564" spans="1:16">
@@ -29585,7 +29585,7 @@
         <v>4.137221058995326</v>
       </c>
       <c r="D564" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E564">
         <v>5.202705629828571</v>
@@ -29621,7 +29621,7 @@
         <v>1</v>
       </c>
       <c r="P564" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="565" spans="1:16">
@@ -29635,7 +29635,7 @@
         <v>4.169450720548237</v>
       </c>
       <c r="D565" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E565">
         <v>5.202705629828571</v>
@@ -29671,7 +29671,7 @@
         <v>1</v>
       </c>
       <c r="P565" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="566" spans="1:16">
@@ -29685,7 +29685,7 @@
         <v>6.314817655301979</v>
       </c>
       <c r="D566" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E566">
         <v>6.624319057953503</v>
@@ -29721,7 +29721,7 @@
         <v>1</v>
       </c>
       <c r="P566" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="567" spans="1:16">
@@ -29735,7 +29735,7 @@
         <v>4.059730080999771</v>
       </c>
       <c r="D567" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E567">
         <v>5.117447902330046</v>
@@ -29785,7 +29785,7 @@
         <v>4.081721754571493</v>
       </c>
       <c r="D568" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E568">
         <v>5.117447902330046</v>
@@ -29885,7 +29885,7 @@
         <v>4.030557457706422</v>
       </c>
       <c r="D570" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E570">
         <v>5.085351371462874</v>
@@ -29921,7 +29921,7 @@
         <v>1</v>
       </c>
       <c r="P570" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="571" spans="1:16">
@@ -29935,7 +29935,7 @@
         <v>4.048694889476288</v>
       </c>
       <c r="D571" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E571">
         <v>5.085351371462874</v>
@@ -29971,7 +29971,7 @@
         <v>1</v>
       </c>
       <c r="P571" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="572" spans="1:16">
@@ -30021,7 +30021,7 @@
         <v>1</v>
       </c>
       <c r="P572" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="573" spans="1:16">
@@ -30035,7 +30035,7 @@
         <v>3.737521317704196</v>
       </c>
       <c r="D573" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E573">
         <v>4.762944866631269</v>
@@ -30071,7 +30071,7 @@
         <v>1</v>
       </c>
       <c r="P573" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="574" spans="1:16">
@@ -30085,7 +30085,7 @@
         <v>3.716943268562606</v>
       </c>
       <c r="D574" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E574">
         <v>4.762944866631269</v>
@@ -30121,7 +30121,7 @@
         <v>1</v>
       </c>
       <c r="P574" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="575" spans="1:16">
@@ -30171,7 +30171,7 @@
         <v>1</v>
       </c>
       <c r="P575" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="576" spans="1:16">
@@ -30221,7 +30221,7 @@
         <v>1</v>
       </c>
       <c r="P576" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="577" spans="1:16">
@@ -30235,7 +30235,7 @@
         <v>3.710853293730853</v>
       </c>
       <c r="D577" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E577">
         <v>4.733603965539871</v>
@@ -30271,7 +30271,7 @@
         <v>1</v>
       </c>
       <c r="P577" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="578" spans="1:16">
@@ -30285,7 +30285,7 @@
         <v>3.686751906570006</v>
       </c>
       <c r="D578" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E578">
         <v>4.733603965539871</v>
@@ -30321,7 +30321,7 @@
         <v>1</v>
       </c>
       <c r="P578" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="579" spans="1:16">
@@ -30371,7 +30371,7 @@
         <v>1</v>
       </c>
       <c r="P579" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="580" spans="1:16">
@@ -30421,7 +30421,7 @@
         <v>1</v>
       </c>
       <c r="P580" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="581" spans="1:16">
@@ -30471,7 +30471,7 @@
         <v>1</v>
       </c>
       <c r="P581" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="582" spans="1:16">
@@ -30521,7 +30521,7 @@
         <v>1</v>
       </c>
       <c r="P582" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="583" spans="1:16">
@@ -30571,7 +30571,7 @@
         <v>1</v>
       </c>
       <c r="P583" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="584" spans="1:16">
@@ -30621,7 +30621,7 @@
         <v>1</v>
       </c>
       <c r="P584" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="585" spans="1:16">
@@ -30671,7 +30671,7 @@
         <v>1</v>
       </c>
       <c r="P585" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="586" spans="1:16">
@@ -30721,7 +30721,7 @@
         <v>1</v>
       </c>
       <c r="P586" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="587" spans="1:16">
@@ -30771,7 +30771,7 @@
         <v>1</v>
       </c>
       <c r="P587" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="588" spans="1:16">
@@ -30821,7 +30821,7 @@
         <v>1</v>
       </c>
       <c r="P588" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="589" spans="1:16">
@@ -30871,7 +30871,7 @@
         <v>1</v>
       </c>
       <c r="P589" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="590" spans="1:16">
@@ -30921,7 +30921,7 @@
         <v>1</v>
       </c>
       <c r="P590" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="591" spans="1:16">
@@ -31171,7 +31171,7 @@
         <v>1</v>
       </c>
       <c r="P595" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="596" spans="1:16">
@@ -31221,7 +31221,7 @@
         <v>1</v>
       </c>
       <c r="P596" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="597" spans="1:16">
@@ -31271,7 +31271,7 @@
         <v>1</v>
       </c>
       <c r="P597" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="598" spans="1:16">
@@ -31321,7 +31321,7 @@
         <v>1</v>
       </c>
       <c r="P598" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="599" spans="1:16">
@@ -31371,7 +31371,7 @@
         <v>1</v>
       </c>
       <c r="P599" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="600" spans="1:16">
@@ -31421,7 +31421,7 @@
         <v>1</v>
       </c>
       <c r="P600" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="601" spans="1:16">
@@ -31635,7 +31635,7 @@
         <v>6.312844467716282</v>
       </c>
       <c r="D605" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E605">
         <v>7.044140001633426</v>
@@ -31721,7 +31721,7 @@
         <v>1</v>
       </c>
       <c r="P606" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="607" spans="1:16">
@@ -31771,7 +31771,7 @@
         <v>1</v>
       </c>
       <c r="P607" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="608" spans="1:16">
@@ -31821,7 +31821,7 @@
         <v>1</v>
       </c>
       <c r="P608" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="609" spans="1:16">
@@ -31871,7 +31871,7 @@
         <v>1</v>
       </c>
       <c r="P609" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="610" spans="1:16">
@@ -31921,7 +31921,7 @@
         <v>1</v>
       </c>
       <c r="P610" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="611" spans="1:16">
@@ -31971,7 +31971,7 @@
         <v>1</v>
       </c>
       <c r="P611" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="612" spans="1:16">
@@ -32021,7 +32021,7 @@
         <v>1</v>
       </c>
       <c r="P612" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="613" spans="1:16">
@@ -32071,7 +32071,7 @@
         <v>1</v>
       </c>
       <c r="P613" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="614" spans="1:16">
@@ -32121,7 +32121,7 @@
         <v>1</v>
       </c>
       <c r="P614" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="615" spans="1:16">
@@ -32171,7 +32171,7 @@
         <v>1</v>
       </c>
       <c r="P615" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="616" spans="1:16">
@@ -32221,7 +32221,7 @@
         <v>1</v>
       </c>
       <c r="P616" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="617" spans="1:16">
@@ -32271,7 +32271,7 @@
         <v>1</v>
       </c>
       <c r="P617" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="618" spans="1:16">
@@ -32321,7 +32321,7 @@
         <v>1</v>
       </c>
       <c r="P618" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="619" spans="1:16">
@@ -32371,7 +32371,7 @@
         <v>1</v>
       </c>
       <c r="P619" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="620" spans="1:16">
@@ -32421,7 +32421,7 @@
         <v>1</v>
       </c>
       <c r="P620" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="621" spans="1:16">
@@ -32471,7 +32471,7 @@
         <v>1</v>
       </c>
       <c r="P621" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="622" spans="1:16">
@@ -32485,7 +32485,7 @@
         <v>6.52789956231641</v>
       </c>
       <c r="D622" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E622">
         <v>6.970266187949232</v>
@@ -32521,7 +32521,7 @@
         <v>1</v>
       </c>
       <c r="P622" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="623" spans="1:16">
@@ -32571,7 +32571,7 @@
         <v>1</v>
       </c>
       <c r="P623" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="624" spans="1:16">
@@ -32621,7 +32621,7 @@
         <v>1</v>
       </c>
       <c r="P624" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="625" spans="1:16">
@@ -32671,7 +32671,7 @@
         <v>1</v>
       </c>
       <c r="P625" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="626" spans="1:16">
@@ -32685,7 +32685,7 @@
         <v>2.603543847706</v>
       </c>
       <c r="D626" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E626">
         <v>4.770094008155837</v>
@@ -32721,7 +32721,7 @@
         <v>1</v>
       </c>
       <c r="P626" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="627" spans="1:16">
@@ -32771,7 +32771,7 @@
         <v>1</v>
       </c>
       <c r="P627" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="628" spans="1:16">
@@ -32821,7 +32821,7 @@
         <v>1</v>
       </c>
       <c r="P628" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="629" spans="1:16">
@@ -32871,7 +32871,7 @@
         <v>1</v>
       </c>
       <c r="P629" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="630" spans="1:16">
@@ -32921,7 +32921,7 @@
         <v>1</v>
       </c>
       <c r="P630" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="631" spans="1:16">
@@ -32971,7 +32971,7 @@
         <v>1</v>
       </c>
       <c r="P631" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="632" spans="1:16">
@@ -32985,7 +32985,7 @@
         <v>2.478182256708074</v>
       </c>
       <c r="D632" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E632">
         <v>4.645810796435313</v>
@@ -33021,7 +33021,7 @@
         <v>1</v>
       </c>
       <c r="P632" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="633" spans="1:16">
@@ -33071,7 +33071,7 @@
         <v>1</v>
       </c>
       <c r="P633" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="634" spans="1:16">
@@ -33121,7 +33121,7 @@
         <v>1</v>
       </c>
       <c r="P634" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="635" spans="1:16">
@@ -33171,7 +33171,7 @@
         <v>1</v>
       </c>
       <c r="P635" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="636" spans="1:16">
@@ -33221,7 +33221,7 @@
         <v>1</v>
       </c>
       <c r="P636" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="637" spans="1:16">
@@ -33235,7 +33235,7 @@
         <v>2.30694018299906</v>
       </c>
       <c r="D637" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E637">
         <v>4.476041772822722</v>
@@ -33271,7 +33271,7 @@
         <v>1</v>
       </c>
       <c r="P637" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="638" spans="1:16">
@@ -33285,7 +33285,7 @@
         <v>5.979313720333828</v>
       </c>
       <c r="D638" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E638">
         <v>6.921637837986275</v>
@@ -33321,7 +33321,7 @@
         <v>1</v>
       </c>
       <c r="P638" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="639" spans="1:16">
@@ -33335,7 +33335,7 @@
         <v>6.118014825265853</v>
       </c>
       <c r="D639" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E639">
         <v>6.921637837986275</v>
@@ -33371,7 +33371,7 @@
         <v>1</v>
       </c>
       <c r="P639" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="640" spans="1:16">
@@ -33385,7 +33385,7 @@
         <v>2.180042495856011</v>
       </c>
       <c r="D640" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E640">
         <v>4.350235678687355</v>
@@ -33421,7 +33421,7 @@
         <v>1</v>
       </c>
       <c r="P640" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="641" spans="1:16">
@@ -33471,7 +33471,7 @@
         <v>1</v>
       </c>
       <c r="P641" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="642" spans="1:16">
@@ -33521,7 +33521,7 @@
         <v>1</v>
       </c>
       <c r="P642" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="643" spans="1:16">
@@ -33571,7 +33571,7 @@
         <v>1</v>
       </c>
       <c r="P643" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="644" spans="1:16">
@@ -33585,7 +33585,7 @@
         <v>2.005501953213372</v>
       </c>
       <c r="D644" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E644">
         <v>4.177196560067447</v>
@@ -33621,7 +33621,7 @@
         <v>1</v>
       </c>
       <c r="P644" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="645" spans="1:16">
@@ -33635,7 +33635,7 @@
         <v>6.03048720269387</v>
       </c>
       <c r="D645" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E645">
         <v>7.646218976894719</v>
@@ -33671,7 +33671,7 @@
         <v>1</v>
       </c>
       <c r="P645" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="646" spans="1:16">
@@ -33685,7 +33685,7 @@
         <v>6.160487202693869</v>
       </c>
       <c r="D646" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E646">
         <v>7.646218976894719</v>
@@ -33721,7 +33721,7 @@
         <v>1</v>
       </c>
       <c r="P646" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="647" spans="1:16">
@@ -33785,7 +33785,7 @@
         <v>5.929250610805834</v>
       </c>
       <c r="D648" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E648">
         <v>6.44678700451809</v>
@@ -33835,7 +33835,7 @@
         <v>6.059250610805833</v>
       </c>
       <c r="D649" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E649">
         <v>6.44678700451809</v>
@@ -33921,7 +33921,7 @@
         <v>1</v>
       </c>
       <c r="P650" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="651" spans="1:16">
@@ -33935,7 +33935,7 @@
         <v>6.444007644774246</v>
       </c>
       <c r="D651" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="E651">
         <v>5.9080963375586</v>
@@ -33971,7 +33971,7 @@
         <v>1</v>
       </c>
       <c r="P651" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="652" spans="1:16">
@@ -33985,7 +33985,7 @@
         <v>5.977845942063905</v>
       </c>
       <c r="D652" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="E652">
         <v>5.9080963375586</v>
@@ -34021,7 +34021,7 @@
         <v>1</v>
       </c>
       <c r="P652" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="653" spans="1:16">
@@ -34085,7 +34085,7 @@
         <v>6.325113724849238</v>
       </c>
       <c r="D654" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E654">
         <v>5.966484401224733</v>
@@ -34135,7 +34135,7 @@
         <v>6.616965483162407</v>
       </c>
       <c r="D655" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E655">
         <v>5.966484401224733</v>
@@ -34371,7 +34371,7 @@
         <v>1</v>
       </c>
       <c r="P659" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="660" spans="1:16">
@@ -34385,7 +34385,7 @@
         <v>6.182411935806901</v>
       </c>
       <c r="D660" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E660">
         <v>5.820555041914538</v>
@@ -34421,7 +34421,7 @@
         <v>1</v>
       </c>
       <c r="P660" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="661" spans="1:16">
@@ -34435,7 +34435,7 @@
         <v>6.479370608860847</v>
       </c>
       <c r="D661" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E661">
         <v>5.820555041914538</v>
@@ -34471,7 +34471,7 @@
         <v>1</v>
       </c>
       <c r="P661" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="662" spans="1:16">
@@ -34485,7 +34485,7 @@
         <v>6.247760471854665</v>
       </c>
       <c r="D662" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E662">
         <v>5.820555041914538</v>
@@ -34521,7 +34521,7 @@
         <v>1</v>
       </c>
       <c r="P662" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="663" spans="1:16">
@@ -34635,7 +34635,7 @@
         <v>6.052746661470383</v>
       </c>
       <c r="D665" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E665">
         <v>5.747828147206722</v>
@@ -34685,7 +34685,7 @@
         <v>6.354345707327784</v>
       </c>
       <c r="D666" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E666">
         <v>5.747828147206722</v>
@@ -34735,7 +34735,7 @@
         <v>6.106229101349317</v>
       </c>
       <c r="D667" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E667">
         <v>5.747828147206722</v>
@@ -34885,7 +34885,7 @@
         <v>5.992378168346487</v>
       </c>
       <c r="D670" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E670">
         <v>5.919638041522585</v>
@@ -34935,7 +34935,7 @@
         <v>6.296137640849427</v>
       </c>
       <c r="D671" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E671">
         <v>5.919638041522585</v>
@@ -34985,7 +34985,7 @@
         <v>6.0403360886604</v>
       </c>
       <c r="D672" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E672">
         <v>5.919638041522585</v>
@@ -35071,7 +35071,7 @@
         <v>1</v>
       </c>
       <c r="P673" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="674" spans="1:16">
@@ -35121,7 +35121,7 @@
         <v>1</v>
       </c>
       <c r="P674" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="675" spans="1:16">
@@ -35135,7 +35135,7 @@
         <v>5.931074248482098</v>
       </c>
       <c r="D675" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E675">
         <v>5.817063063996034</v>
@@ -35171,7 +35171,7 @@
         <v>1</v>
       </c>
       <c r="P675" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="676" spans="1:16">
@@ -35185,7 +35185,7 @@
         <v>6.237027624047666</v>
       </c>
       <c r="D676" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E676">
         <v>5.817063063996034</v>
@@ -35221,7 +35221,7 @@
         <v>1</v>
       </c>
       <c r="P676" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="677" spans="1:16">
@@ -35235,7 +35235,7 @@
         <v>5.973422045250139</v>
       </c>
       <c r="D677" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E677">
         <v>5.817063063996034</v>
@@ -35271,7 +35271,7 @@
         <v>1</v>
       </c>
       <c r="P677" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="678" spans="1:16">
@@ -35385,7 +35385,7 @@
         <v>5.839386641650073</v>
       </c>
       <c r="D680" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E680">
         <v>4.893781158276536</v>
@@ -35435,7 +35435,7 @@
         <v>6.148621271038877</v>
       </c>
       <c r="D681" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E681">
         <v>4.893781158276536</v>
@@ -35485,7 +35485,7 @@
         <v>5.873343803641564</v>
       </c>
       <c r="D682" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E682">
         <v>4.893781158276536</v>
@@ -35585,7 +35585,7 @@
         <v>6.049313264972337</v>
       </c>
       <c r="D684" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E684">
         <v>4.936335249131968</v>
@@ -35635,7 +35635,7 @@
         <v>6.175722584965069</v>
       </c>
       <c r="D685" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E685">
         <v>4.936335249131968</v>
@@ -35685,7 +35685,7 @@
         <v>5.760924613317037</v>
       </c>
       <c r="D686" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E686">
         <v>4.936335249131968</v>
@@ -35835,7 +35835,7 @@
         <v>5.905539797299475</v>
       </c>
       <c r="D689" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E689">
         <v>5.270502414665344</v>
@@ -35885,7 +35885,7 @@
         <v>6.021734035283636</v>
       </c>
       <c r="D690" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E690">
         <v>5.270502414665344</v>
@@ -36035,7 +36035,7 @@
         <v>5.810134805942958</v>
       </c>
       <c r="D693" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="E693">
         <v>4.46837075668304</v>
@@ -36085,7 +36085,7 @@
         <v>5.919550534467003</v>
       </c>
       <c r="D694" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="E694">
         <v>4.46837075668304</v>
@@ -36135,7 +36135,7 @@
         <v>5.597681787127293</v>
       </c>
       <c r="D695" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="E695">
         <v>5.175448484795162</v>
@@ -36185,7 +36185,7 @@
         <v>5.69200276245871</v>
       </c>
       <c r="D696" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="E696">
         <v>5.175448484795162</v>
@@ -36271,7 +36271,7 @@
         <v>1</v>
       </c>
       <c r="P697" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="698" spans="1:16">
@@ -36321,7 +36321,7 @@
         <v>1</v>
       </c>
       <c r="P698" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="699" spans="1:16">
@@ -36371,7 +36371,7 @@
         <v>1</v>
       </c>
       <c r="P699" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="700" spans="1:16">
@@ -36421,7 +36421,7 @@
         <v>1</v>
       </c>
       <c r="P700" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="701" spans="1:16">
@@ -36435,7 +36435,7 @@
         <v>10.58920111380781</v>
       </c>
       <c r="D701" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="E701">
         <v>10.63805069137965</v>
@@ -36471,7 +36471,7 @@
         <v>1</v>
       </c>
       <c r="P701" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="702" spans="1:16">
@@ -36521,7 +36521,7 @@
         <v>1</v>
       </c>
       <c r="P702" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="703" spans="1:16">
@@ -36535,7 +36535,7 @@
         <v>13.29070024337744</v>
       </c>
       <c r="D703" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E703">
         <v>12.1104855745369</v>
@@ -36571,7 +36571,7 @@
         <v>1</v>
       </c>
       <c r="P703" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="704" spans="1:16">
@@ -36621,7 +36621,7 @@
         <v>1</v>
       </c>
       <c r="P704" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="705" spans="1:16">
@@ -36635,7 +36635,7 @@
         <v>13.05967948318782</v>
       </c>
       <c r="D705" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E705">
         <v>11.87581437344135</v>
@@ -36671,7 +36671,7 @@
         <v>1</v>
       </c>
       <c r="P705" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="706" spans="1:16">
@@ -36721,7 +36721,7 @@
         <v>1</v>
       </c>
       <c r="P706" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="707" spans="1:16">
@@ -36735,7 +36735,7 @@
         <v>12.8170626988293</v>
       </c>
       <c r="D707" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E707">
         <v>10.97022453374666</v>
@@ -36771,7 +36771,7 @@
         <v>1</v>
       </c>
       <c r="P707" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="708" spans="1:16">
@@ -36821,7 +36821,7 @@
         <v>1</v>
       </c>
       <c r="P708" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="709" spans="1:16">
@@ -36835,7 +36835,7 @@
         <v>12.5987805539735</v>
       </c>
       <c r="D709" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E709">
         <v>10.73863851098768</v>
@@ -36871,7 +36871,7 @@
         <v>1</v>
       </c>
       <c r="P709" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="710" spans="1:16">
@@ -36921,7 +36921,7 @@
         <v>1</v>
       </c>
       <c r="P710" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="711" spans="1:16">
@@ -36971,7 +36971,7 @@
         <v>1</v>
       </c>
       <c r="P711" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="712" spans="1:16">
@@ -37021,7 +37021,7 @@
         <v>1</v>
       </c>
       <c r="P712" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="713" spans="1:16">
@@ -37035,7 +37035,7 @@
         <v>12.45336310880131</v>
       </c>
       <c r="D713" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E713">
         <v>10.58435815154991</v>
@@ -37071,7 +37071,7 @@
         <v>1</v>
       </c>
       <c r="P713" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="714" spans="1:16">
@@ -37121,7 +37121,7 @@
         <v>1</v>
       </c>
       <c r="P714" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="715" spans="1:16">
@@ -37171,7 +37171,7 @@
         <v>1</v>
       </c>
       <c r="P715" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="716" spans="1:16">
@@ -37221,7 +37221,7 @@
         <v>1</v>
       </c>
       <c r="P716" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="717" spans="1:16">
@@ -37271,7 +37271,7 @@
         <v>1</v>
       </c>
       <c r="P717" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="718" spans="1:16">
@@ -37321,7 +37321,7 @@
         <v>1</v>
       </c>
       <c r="P718" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="719" spans="1:16">
@@ -37371,7 +37371,7 @@
         <v>1</v>
       </c>
       <c r="P719" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="720" spans="1:16">
@@ -37385,7 +37385,7 @@
         <v>12.29210392935995</v>
       </c>
       <c r="D720" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E720">
         <v>10.41327053453538</v>
@@ -37421,7 +37421,7 @@
         <v>1</v>
       </c>
       <c r="P720" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="721" spans="1:16">
@@ -37435,7 +37435,7 @@
         <v>9.171282848330055</v>
       </c>
       <c r="D721" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E721">
         <v>6.850968108671186</v>
@@ -37471,7 +37471,7 @@
         <v>1</v>
       </c>
       <c r="P721" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="722" spans="1:16">
@@ -37485,7 +37485,7 @@
         <v>8.830116243154617</v>
       </c>
       <c r="D722" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E722">
         <v>6.850968108671186</v>
@@ -37521,7 +37521,7 @@
         <v>1</v>
       </c>
       <c r="P722" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="723" spans="1:16">
@@ -37685,7 +37685,7 @@
         <v>12.09795277153261</v>
       </c>
       <c r="D726" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E726">
         <v>10.20728623616326</v>
@@ -37735,7 +37735,7 @@
         <v>8.629829382822578</v>
       </c>
       <c r="D727" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E727">
         <v>7.040051561279032</v>
@@ -37821,7 +37821,7 @@
         <v>1</v>
       </c>
       <c r="P728" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="729" spans="1:16">
@@ -37871,7 +37871,7 @@
         <v>1</v>
       </c>
       <c r="P729" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="730" spans="1:16">
@@ -37921,7 +37921,7 @@
         <v>1</v>
       </c>
       <c r="P730" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="731" spans="1:16">
@@ -37935,7 +37935,7 @@
         <v>11.86477339723001</v>
       </c>
       <c r="D731" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E731">
         <v>9.95989502640656</v>
@@ -37971,7 +37971,7 @@
         <v>1</v>
       </c>
       <c r="P731" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="732" spans="1:16">
@@ -37985,7 +37985,7 @@
         <v>8.389280908654889</v>
       </c>
       <c r="D732" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="E732">
         <v>6.803093216210396</v>
@@ -38021,7 +38021,7 @@
         <v>1</v>
       </c>
       <c r="P732" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="733" spans="1:16">
@@ -38071,7 +38071,7 @@
         <v>1</v>
       </c>
       <c r="P733" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="734" spans="1:16">
@@ -38121,7 +38121,7 @@
         <v>1</v>
       </c>
       <c r="P734" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="735" spans="1:16">
@@ -38171,7 +38171,7 @@
         <v>1</v>
       </c>
       <c r="P735" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="736" spans="1:16">
@@ -38221,7 +38221,7 @@
         <v>1</v>
       </c>
       <c r="P736" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="737" spans="1:16">
@@ -38235,7 +38235,7 @@
         <v>7.721090409497048</v>
       </c>
       <c r="D737" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E737">
         <v>6.845979077114176</v>
@@ -38271,7 +38271,7 @@
         <v>1</v>
       </c>
       <c r="P737" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="738" spans="1:16">
@@ -38321,7 +38321,7 @@
         <v>1</v>
       </c>
       <c r="P738" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="739" spans="1:16">
@@ -38371,7 +38371,7 @@
         <v>1</v>
       </c>
       <c r="P739" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="740" spans="1:16">
@@ -38421,7 +38421,7 @@
         <v>1</v>
       </c>
       <c r="P740" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="741" spans="1:16">
@@ -38435,7 +38435,7 @@
         <v>7.431928747420816</v>
       </c>
       <c r="D741" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E741">
         <v>6.954602200047407</v>
@@ -38471,7 +38471,7 @@
         <v>1</v>
       </c>
       <c r="P741" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="742" spans="1:16">
@@ -38521,7 +38521,7 @@
         <v>1</v>
       </c>
       <c r="P742" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="743" spans="1:16">
@@ -38571,7 +38571,7 @@
         <v>1</v>
       </c>
       <c r="P743" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="744" spans="1:16">
@@ -38621,7 +38621,7 @@
         <v>1</v>
       </c>
       <c r="P744" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="745" spans="1:16">
@@ -38671,7 +38671,7 @@
         <v>1</v>
       </c>
       <c r="P745" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="746" spans="1:16">
@@ -38685,7 +38685,7 @@
         <v>7.15411432552343</v>
       </c>
       <c r="D746" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E746">
         <v>7.077702572180645</v>
@@ -38721,7 +38721,7 @@
         <v>1</v>
       </c>
       <c r="P746" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="747" spans="1:16">
@@ -38985,7 +38985,7 @@
         <v>6.656074286112602</v>
       </c>
       <c r="D752" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E752">
         <v>7.106777983579878</v>
@@ -39071,7 +39071,7 @@
         <v>1</v>
       </c>
       <c r="P753" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="754" spans="1:16">
@@ -39121,7 +39121,7 @@
         <v>1</v>
       </c>
       <c r="P754" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="755" spans="1:16">
@@ -39171,7 +39171,7 @@
         <v>1</v>
       </c>
       <c r="P755" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="756" spans="1:16">
@@ -39221,7 +39221,7 @@
         <v>1</v>
       </c>
       <c r="P756" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="757" spans="1:16">
@@ -39271,7 +39271,7 @@
         <v>1</v>
       </c>
       <c r="P757" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="758" spans="1:16">
@@ -39321,7 +39321,7 @@
         <v>1</v>
       </c>
       <c r="P758" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="759" spans="1:16">
@@ -39671,7 +39671,7 @@
         <v>1</v>
       </c>
       <c r="P765" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="766" spans="1:16">
@@ -39721,7 +39721,7 @@
         <v>1</v>
       </c>
       <c r="P766" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="767" spans="1:16">
@@ -39735,7 +39735,7 @@
         <v>5.189787984798581</v>
       </c>
       <c r="D767" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E767">
         <v>6.127393152460147</v>
@@ -39771,7 +39771,7 @@
         <v>1</v>
       </c>
       <c r="P767" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="768" spans="1:16">
@@ -39785,7 +39785,7 @@
         <v>5.337615079752425</v>
       </c>
       <c r="D768" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E768">
         <v>6.127393152460147</v>
@@ -39821,7 +39821,7 @@
         <v>1</v>
       </c>
       <c r="P768" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="769" spans="1:16">
@@ -39935,7 +39935,7 @@
         <v>4.573548410677798</v>
       </c>
       <c r="D771" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E771">
         <v>5.983161604764781</v>
@@ -39985,7 +39985,7 @@
         <v>4.718587091269107</v>
       </c>
       <c r="D772" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E772">
         <v>5.983161604764781</v>
@@ -40071,7 +40071,7 @@
         <v>1</v>
       </c>
       <c r="P773" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="774" spans="1:16">
@@ -40121,7 +40121,7 @@
         <v>1</v>
       </c>
       <c r="P774" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="775" spans="1:16">
@@ -40171,7 +40171,7 @@
         <v>1</v>
       </c>
       <c r="P775" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="776" spans="1:16">
@@ -40221,7 +40221,7 @@
         <v>1</v>
       </c>
       <c r="P776" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="777" spans="1:16">
@@ -40471,7 +40471,7 @@
         <v>1</v>
       </c>
       <c r="P781" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="782" spans="1:16">
@@ -40521,7 +40521,7 @@
         <v>1</v>
       </c>
       <c r="P782" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="783" spans="1:16">
@@ -40571,7 +40571,7 @@
         <v>1</v>
       </c>
       <c r="P783" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="784" spans="1:16">
@@ -40971,7 +40971,7 @@
         <v>1</v>
       </c>
       <c r="P791" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="792" spans="1:16">
@@ -41021,7 +41021,7 @@
         <v>1</v>
       </c>
       <c r="P792" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="793" spans="1:16">
@@ -41071,7 +41071,7 @@
         <v>1</v>
       </c>
       <c r="P793" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="794" spans="1:16">
@@ -41121,7 +41121,7 @@
         <v>1</v>
       </c>
       <c r="P794" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="795" spans="1:16">
@@ -41371,7 +41371,7 @@
         <v>1</v>
       </c>
       <c r="P799" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="800" spans="1:16">
@@ -41385,7 +41385,7 @@
         <v>1.03967143846625</v>
       </c>
       <c r="D800" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E800">
         <v>2.609188567947417</v>
@@ -41421,7 +41421,7 @@
         <v>1</v>
       </c>
       <c r="P800" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="801" spans="1:16">
@@ -41435,7 +41435,7 @@
         <v>0.8130094478294367</v>
       </c>
       <c r="D801" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E801">
         <v>2.609188567947417</v>
@@ -41471,7 +41471,7 @@
         <v>1</v>
       </c>
       <c r="P801" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="802" spans="1:16">
@@ -41521,7 +41521,7 @@
         <v>1</v>
       </c>
       <c r="P802" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="803" spans="1:16">
@@ -41535,7 +41535,7 @@
         <v>0.7465491084079581</v>
       </c>
       <c r="D803" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E803">
         <v>2.329329691737918</v>
@@ -41571,7 +41571,7 @@
         <v>1</v>
       </c>
       <c r="P803" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="804" spans="1:16">
@@ -41585,7 +41585,7 @@
         <v>0.5106027000769942</v>
       </c>
       <c r="D804" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E804">
         <v>2.329329691737918</v>
@@ -41621,7 +41621,7 @@
         <v>1</v>
       </c>
       <c r="P804" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="805" spans="1:16">
@@ -41635,7 +41635,7 @@
         <v>0.4893560218813207</v>
       </c>
       <c r="D805" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E805">
         <v>2.083774301434204</v>
@@ -41685,7 +41685,7 @@
         <v>0.2452632261943108</v>
       </c>
       <c r="D806" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E806">
         <v>2.083774301434204</v>
@@ -41735,7 +41735,7 @@
         <v>3.38720643044401</v>
       </c>
       <c r="D807" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E807">
         <v>1.346565161657761</v>
@@ -41785,7 +41785,7 @@
         <v>0.03330516332946587</v>
       </c>
       <c r="D808" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E808">
         <v>1.648359228337185</v>
@@ -41835,7 +41835,7 @@
         <v>-0.2252326821759354</v>
       </c>
       <c r="D809" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E809">
         <v>1.648359228337185</v>
@@ -41885,7 +41885,7 @@
         <v>2.979030594147371</v>
       </c>
       <c r="D810" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E810">
         <v>0.9008321958333205</v>
@@ -41935,7 +41935,7 @@
         <v>-0.3050434949915584</v>
       </c>
       <c r="D811" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E811">
         <v>1.325320464057839</v>
@@ -41971,7 +41971,7 @@
         <v>1</v>
       </c>
       <c r="P811" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="812" spans="1:16">
@@ -41985,7 +41985,7 @@
         <v>-0.5742982663261245</v>
       </c>
       <c r="D812" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E812">
         <v>1.325320464057839</v>
@@ -42021,7 +42021,7 @@
         <v>1</v>
       </c>
       <c r="P812" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="813" spans="1:16">
@@ -42035,7 +42035,7 @@
         <v>2.676200890003035</v>
       </c>
       <c r="D813" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E813">
         <v>0.570138484533139</v>
@@ -42071,7 +42071,7 @@
         <v>1</v>
       </c>
       <c r="P813" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="814" spans="1:16">
@@ -42085,7 +42085,7 @@
         <v>-1.542729235915701</v>
       </c>
       <c r="D814" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E814">
         <v>0.8740710626510406</v>
@@ -42135,7 +42135,7 @@
         <v>-1.06190425457612</v>
       </c>
       <c r="D815" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E815">
         <v>0.8740710626510406</v>
@@ -42185,7 +42185,7 @@
         <v>2.253181308968607</v>
       </c>
       <c r="D816" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E816">
         <v>0.1081959693489338</v>
@@ -42235,7 +42235,7 @@
         <v>-1.645106114375984</v>
       </c>
       <c r="D817" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E817">
         <v>0.7789101756240804</v>
@@ -42285,7 +42285,7 @@
         <v>-1.164732132500994</v>
       </c>
       <c r="D818" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E818">
         <v>0.7789101756240804</v>
@@ -42335,7 +42335,7 @@
         <v>1.705918320624114</v>
       </c>
       <c r="D819" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E819">
         <v>0.01078008499905536</v>
@@ -42385,7 +42385,7 @@
         <v>2.163973614874138</v>
       </c>
       <c r="D820" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E820">
         <v>0.01078008499905536</v>
@@ -42435,7 +42435,7 @@
         <v>2.083749225749141</v>
       </c>
       <c r="D821" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E821">
         <v>-0.02146380625091737</v>
@@ -42485,7 +42485,7 @@
         <v>-1.354990011712744</v>
       </c>
       <c r="D822" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E822">
         <v>1.048577566205335</v>
@@ -42535,7 +42535,7 @@
         <v>-0.8733379853326184</v>
       </c>
       <c r="D823" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E823">
         <v>1.048577566205335</v>
@@ -42585,7 +42585,7 @@
         <v>1.965361355164372</v>
       </c>
       <c r="D824" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E824">
         <v>0.2868376981059342</v>
@@ -42635,7 +42635,7 @@
         <v>2.41677081798775</v>
       </c>
       <c r="D825" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E825">
         <v>0.2868376981059342</v>
@@ -42685,7 +42685,7 @@
         <v>2.335779602159679</v>
       </c>
       <c r="D826" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E826">
         <v>0.246925539825213</v>
@@ -42735,7 +42735,7 @@
         <v>-1.093559587288276</v>
       </c>
       <c r="D827" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E827">
         <v>-1.564638644835625</v>
@@ -42785,7 +42785,7 @@
         <v>-1.266714738768137</v>
       </c>
       <c r="D828" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E828">
         <v>0.4727739583005963</v>
@@ -42821,7 +42821,7 @@
         <v>1</v>
       </c>
       <c r="P828" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="829" spans="1:16">
@@ -42835,7 +42835,7 @@
         <v>-0.7846738345336348</v>
       </c>
       <c r="D829" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E829">
         <v>0.5188966710041001</v>
@@ -42871,7 +42871,7 @@
         <v>1</v>
       </c>
       <c r="P829" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="830" spans="1:16">
@@ -42885,7 +42885,7 @@
         <v>2.044303559603822</v>
       </c>
       <c r="D830" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E830">
         <v>0.3708353146523429</v>
@@ -42921,7 +42921,7 @@
         <v>1</v>
       </c>
       <c r="P830" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="831" spans="1:16">
@@ -42935,7 +42935,7 @@
         <v>2.412466315043719</v>
       </c>
       <c r="D831" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E831">
         <v>0.3285898892453361</v>
@@ -42971,7 +42971,7 @@
         <v>1</v>
       </c>
       <c r="P831" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="832" spans="1:16">
@@ -42985,7 +42985,7 @@
         <v>-1.016717323262487</v>
       </c>
       <c r="D832" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E832">
         <v>-1.725082876878652</v>
@@ -43021,7 +43021,7 @@
         <v>1</v>
       </c>
       <c r="P832" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="833" spans="1:16">
@@ -43035,7 +43035,7 @@
         <v>-1.012419255686936</v>
       </c>
       <c r="D833" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E833">
         <v>0.7130663861460427</v>
@@ -43085,7 +43085,7 @@
         <v>2.271713176632382</v>
       </c>
       <c r="D834" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E834">
         <v>0.563841217205912</v>
@@ -43135,7 +43135,7 @@
         <v>2.633378514442889</v>
       </c>
       <c r="D835" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E835">
         <v>0.563841217205912</v>
@@ -43185,7 +43185,7 @@
         <v>-0.7953570260957719</v>
       </c>
       <c r="D836" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E836">
         <v>-0.6798364854873604</v>
@@ -43235,7 +43235,7 @@
         <v>-1.154980882524804</v>
       </c>
       <c r="D837" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E837">
         <v>0.3632888214250194</v>
@@ -43271,7 +43271,7 @@
         <v>1</v>
       </c>
       <c r="P837" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="838" spans="1:16">
@@ -43285,7 +43285,7 @@
         <v>2.144224144702488</v>
       </c>
       <c r="D838" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="E838">
         <v>0.3406232020973725</v>
@@ -43321,7 +43321,7 @@
         <v>1</v>
       </c>
       <c r="P838" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="839" spans="1:16">
@@ -43335,7 +43335,7 @@
         <v>2.509532026282422</v>
       </c>
       <c r="D839" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="E839">
         <v>0.3406232020973725</v>
@@ -43371,7 +43371,7 @@
         <v>1</v>
       </c>
       <c r="P839" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="840" spans="1:16">
@@ -43421,7 +43421,7 @@
         <v>1</v>
       </c>
       <c r="P840" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="841" spans="1:16">
@@ -43435,7 +43435,7 @@
         <v>-0.7435135480053319</v>
       </c>
       <c r="D841" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E841">
         <v>0.7484730002152737</v>
@@ -43585,7 +43585,7 @@
         <v>-0.3742444036399846</v>
       </c>
       <c r="D844" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E844">
         <v>1.094154467958163</v>
@@ -43621,7 +43621,7 @@
         <v>1</v>
       </c>
       <c r="P844" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="845" spans="1:16">
@@ -43671,7 +43671,7 @@
         <v>1</v>
       </c>
       <c r="P845" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="846" spans="1:16">
@@ -43721,7 +43721,7 @@
         <v>1</v>
       </c>
       <c r="P846" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="847" spans="1:16">
@@ -43735,7 +43735,7 @@
         <v>-0.2301600625778306</v>
       </c>
       <c r="D847" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E847">
         <v>1.229035183710177</v>
@@ -43771,7 +43771,7 @@
         <v>1</v>
       </c>
       <c r="P847" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="848" spans="1:16">
@@ -43821,7 +43821,7 @@
         <v>1</v>
       </c>
       <c r="P848" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="849" spans="1:16">
@@ -43871,7 +43871,7 @@
         <v>1</v>
       </c>
       <c r="P849" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="850" spans="1:16">
@@ -43885,7 +43885,7 @@
         <v>-0.008911774850371756</v>
       </c>
       <c r="D850" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="E850">
         <v>0.5721947646345491</v>
@@ -43921,7 +43921,7 @@
         <v>1</v>
       </c>
       <c r="P850" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="851" spans="1:16">
@@ -43935,7 +43935,7 @@
         <v>-0.1112036199752922</v>
       </c>
       <c r="D851" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E851">
         <v>1.340393087027532</v>
@@ -44085,7 +44085,7 @@
         <v>0.09903988671845454</v>
       </c>
       <c r="D854" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E854">
         <v>1.106317252320714</v>
@@ -44135,7 +44135,7 @@
         <v>-0.06944114310240224</v>
       </c>
       <c r="D855" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E855">
         <v>1.379487916699293</v>
@@ -44171,7 +44171,7 @@
         <v>1</v>
       </c>
       <c r="P855" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="856" spans="1:16">
@@ -44221,7 +44221,7 @@
         <v>1</v>
       </c>
       <c r="P856" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="857" spans="1:16">
@@ -44271,7 +44271,7 @@
         <v>1</v>
       </c>
       <c r="P857" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="858" spans="1:16">
@@ -44285,7 +44285,7 @@
         <v>0.1369388745414319</v>
       </c>
       <c r="D858" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E858">
         <v>1.371101739245933</v>
@@ -44321,7 +44321,7 @@
         <v>1</v>
       </c>
       <c r="P858" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="859" spans="1:16">
@@ -44335,7 +44335,7 @@
         <v>13.70922282990332</v>
       </c>
       <c r="D859" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="E859">
         <v>12.65888206048432</v>
@@ -44371,39 +44371,39 @@
         <v>1</v>
       </c>
       <c r="P859" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="860" spans="1:16">
       <c r="A860" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B860" t="s">
         <v>155</v>
       </c>
       <c r="C860">
-        <v>12.5976194962981</v>
+        <v>12.51796460063045</v>
       </c>
       <c r="D860" t="s">
-        <v>267</v>
+        <v>156</v>
       </c>
       <c r="E860">
-        <v>13.05601616269288</v>
+        <v>12.97873629831807</v>
       </c>
       <c r="F860">
         <v>1</v>
       </c>
       <c r="G860">
-        <v>0.0493823805037019</v>
+        <v>0.04946203539936955</v>
       </c>
       <c r="H860">
-        <v>0.04874398383730711</v>
+        <v>0.04882126370168193</v>
       </c>
       <c r="I860">
-        <v>0.4583966663947834</v>
+        <v>0.4607716976876262</v>
       </c>
       <c r="J860">
-        <v>0.8436871790688943</v>
+        <v>0.8473410733655758</v>
       </c>
       <c r="K860">
         <v>21.8</v>
@@ -44421,7 +44421,7 @@
         <v>1</v>
       </c>
       <c r="P860" t="s">
-        <v>349</v>
+        <v>154</v>
       </c>
     </row>
     <row r="861" spans="1:16">
@@ -44432,28 +44432,28 @@
         <v>155</v>
       </c>
       <c r="C861">
-        <v>12.51796460063045</v>
+        <v>12.42436853267676</v>
       </c>
       <c r="D861" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E861">
-        <v>12.97873629831807</v>
+        <v>12.66793093881254</v>
       </c>
       <c r="F861">
         <v>1</v>
       </c>
       <c r="G861">
-        <v>0.04946203539936955</v>
+        <v>0.04955563146732324</v>
       </c>
       <c r="H861">
-        <v>0.04882126370168193</v>
+        <v>0.04869206906118746</v>
       </c>
       <c r="I861">
-        <v>0.4607716976876262</v>
+        <v>0.2435624061357871</v>
       </c>
       <c r="J861">
-        <v>0.8473410733655758</v>
+        <v>0.8516344709781304</v>
       </c>
       <c r="K861">
         <v>21.8</v>
@@ -44465,113 +44465,63 @@
         <v>21.15</v>
       </c>
       <c r="N861">
-        <v>30.9</v>
+        <v>30.68</v>
       </c>
       <c r="O861">
         <v>1</v>
       </c>
       <c r="P861" t="s">
-        <v>154</v>
+        <v>267</v>
       </c>
     </row>
     <row r="862" spans="1:16">
       <c r="A862" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B862" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C862">
-        <v>12.45873056517934</v>
+        <v>12.88793093881254</v>
       </c>
       <c r="D862" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E862">
-        <v>12.70126841530015</v>
+        <v>12.82342128010598</v>
       </c>
       <c r="F862">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G862">
-        <v>0.04952126943482065</v>
+        <v>0.04891206906118745</v>
       </c>
       <c r="H862">
-        <v>0.04865873158469985</v>
+        <v>0.04833657871989402</v>
       </c>
       <c r="I862">
-        <v>0.2425378501208044</v>
+        <v>0.06450965870656233</v>
       </c>
       <c r="J862">
-        <v>0.8500582309550758</v>
+        <v>0.8516344709781304</v>
       </c>
       <c r="K862">
-        <v>21.8</v>
+        <v>21.15</v>
       </c>
       <c r="L862">
-        <v>30.99</v>
+        <v>30.9</v>
       </c>
       <c r="M862">
-        <v>21.15</v>
+        <v>20.85</v>
       </c>
       <c r="N862">
-        <v>30.68</v>
+        <v>30.58</v>
       </c>
       <c r="O862">
         <v>1</v>
       </c>
       <c r="P862" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="863" spans="1:16">
-      <c r="A863" s="1">
-        <v>0</v>
-      </c>
-      <c r="B863" t="s">
-        <v>155</v>
-      </c>
-      <c r="C863">
-        <v>12.42436853267676</v>
-      </c>
-      <c r="D863" t="s">
-        <v>268</v>
-      </c>
-      <c r="E863">
-        <v>12.66793093881254</v>
-      </c>
-      <c r="F863">
-        <v>1</v>
-      </c>
-      <c r="G863">
-        <v>0.04955563146732324</v>
-      </c>
-      <c r="H863">
-        <v>0.04869206906118746</v>
-      </c>
-      <c r="I863">
-        <v>0.2435624061357871</v>
-      </c>
-      <c r="J863">
-        <v>0.8516344709781304</v>
-      </c>
-      <c r="K863">
-        <v>21.8</v>
-      </c>
-      <c r="L863">
-        <v>30.99</v>
-      </c>
-      <c r="M863">
-        <v>21.15</v>
-      </c>
-      <c r="N863">
-        <v>30.68</v>
-      </c>
-      <c r="O863">
-        <v>1</v>
-      </c>
-      <c r="P863" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-00763-000063.xlsx
+++ b/s60_signal/position-00763-000063.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2598" uniqueCount="351">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2592" uniqueCount="348">
   <si>
     <t>trade_time</t>
   </si>
@@ -478,13 +478,7 @@
     <t>2021-03-19</t>
   </si>
   <si>
-    <t>2021-11-24</t>
-  </si>
-  <si>
-    <t>2021-11-29</t>
-  </si>
-  <si>
-    <t>2021-12-01</t>
+    <t>2021-11-26</t>
   </si>
   <si>
     <t>2017-03-17</t>
@@ -817,13 +811,7 @@
     <t>2021-03-26</t>
   </si>
   <si>
-    <t>2021-11-26</t>
-  </si>
-  <si>
-    <t>2021-11-30</t>
-  </si>
-  <si>
-    <t>2021-12-02</t>
+    <t>2021-12-03</t>
   </si>
   <si>
     <t>2017-02-08</t>
@@ -1067,6 +1055,9 @@
   </si>
   <si>
     <t>2021-11-23</t>
+  </si>
+  <si>
+    <t>2021-11-24</t>
   </si>
 </sst>
 </file>
@@ -1424,7 +1415,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P862"/>
+  <dimension ref="A1:P860"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -1485,7 +1476,7 @@
         <v>8.357775317423281</v>
       </c>
       <c r="D2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E2">
         <v>9.239078272099615</v>
@@ -1521,7 +1512,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -1535,7 +1526,7 @@
         <v>9.433191964550923</v>
       </c>
       <c r="D3" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="E3">
         <v>9.285575452539577</v>
@@ -1571,7 +1562,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -1585,7 +1576,7 @@
         <v>9.420218808988363</v>
       </c>
       <c r="D4" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="E4">
         <v>9.285575452539577</v>
@@ -1621,7 +1612,7 @@
         <v>1</v>
       </c>
       <c r="P4" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -1635,7 +1626,7 @@
         <v>9.27302954676334</v>
       </c>
       <c r="D5" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="E5">
         <v>9.285575452539577</v>
@@ -1671,7 +1662,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -1685,7 +1676,7 @@
         <v>8.163141562328137</v>
       </c>
       <c r="D6" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E6">
         <v>8.870417830135191</v>
@@ -1721,7 +1712,7 @@
         <v>1</v>
       </c>
       <c r="P6" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -1735,7 +1726,7 @@
         <v>8.167981542028786</v>
       </c>
       <c r="D7" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E7">
         <v>8.870417830135191</v>
@@ -1771,7 +1762,7 @@
         <v>1</v>
       </c>
       <c r="P7" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -1785,7 +1776,7 @@
         <v>9.039124544167011</v>
       </c>
       <c r="D8" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="E8">
         <v>9.113918803782131</v>
@@ -1821,7 +1812,7 @@
         <v>1</v>
       </c>
       <c r="P8" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -1835,7 +1826,7 @@
         <v>9.052076876787602</v>
       </c>
       <c r="D9" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="E9">
         <v>9.113918803782131</v>
@@ -1871,7 +1862,7 @@
         <v>1</v>
       </c>
       <c r="P9" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -1885,7 +1876,7 @@
         <v>8.972076876787604</v>
       </c>
       <c r="D10" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="E10">
         <v>9.113918803782131</v>
@@ -1921,7 +1912,7 @@
         <v>1</v>
       </c>
       <c r="P10" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -1935,7 +1926,7 @@
         <v>1.247895028504875</v>
       </c>
       <c r="D11" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="E11">
         <v>5.93332434483856</v>
@@ -1971,7 +1962,7 @@
         <v>1</v>
       </c>
       <c r="P11" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -1985,7 +1976,7 @@
         <v>2.464515501370315</v>
       </c>
       <c r="D12" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="E12">
         <v>5.93332434483856</v>
@@ -2021,7 +2012,7 @@
         <v>1</v>
       </c>
       <c r="P12" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -2071,7 +2062,7 @@
         <v>1</v>
       </c>
       <c r="P13" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -2085,7 +2076,7 @@
         <v>1.224092499726471</v>
       </c>
       <c r="D14" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="E14">
         <v>5.913320521841428</v>
@@ -2121,7 +2112,7 @@
         <v>1</v>
       </c>
       <c r="P14" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -2135,7 +2126,7 @@
         <v>2.442814384300704</v>
       </c>
       <c r="D15" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="E15">
         <v>5.913320521841428</v>
@@ -2171,7 +2162,7 @@
         <v>1</v>
       </c>
       <c r="P15" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -2185,7 +2176,7 @@
         <v>8.399951396166678</v>
       </c>
       <c r="D16" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="E16">
         <v>7.154665097353277</v>
@@ -2221,7 +2212,7 @@
         <v>1</v>
       </c>
       <c r="P16" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -2235,7 +2226,7 @@
         <v>1.231818368992485</v>
       </c>
       <c r="D17" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="E17">
         <v>5.919813400087062</v>
@@ -2271,7 +2262,7 @@
         <v>1</v>
       </c>
       <c r="P17" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -2285,7 +2276,7 @@
         <v>2.449858173427781</v>
       </c>
       <c r="D18" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="E18">
         <v>5.919813400087062</v>
@@ -2321,7 +2312,7 @@
         <v>1</v>
       </c>
       <c r="P18" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -2371,7 +2362,7 @@
         <v>1</v>
       </c>
       <c r="P19" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
     </row>
     <row r="20" spans="1:16">
@@ -2385,7 +2376,7 @@
         <v>1.145797529921555</v>
       </c>
       <c r="D20" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="E20">
         <v>5.847520844331356</v>
@@ -2421,7 +2412,7 @@
         <v>1</v>
       </c>
       <c r="P20" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -2435,7 +2426,7 @@
         <v>2.37143170385038</v>
       </c>
       <c r="D21" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="E21">
         <v>5.847520844331356</v>
@@ -2471,7 +2462,7 @@
         <v>1</v>
       </c>
       <c r="P21" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -2485,7 +2476,7 @@
         <v>8.323251570058975</v>
       </c>
       <c r="D22" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="E22">
         <v>6.49770468378167</v>
@@ -2521,7 +2512,7 @@
         <v>1</v>
       </c>
       <c r="P22" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
     </row>
     <row r="23" spans="1:16">
@@ -2535,7 +2526,7 @@
         <v>8.298928068060523</v>
       </c>
       <c r="D23" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="E23">
         <v>6.513844529583032</v>
@@ -2621,7 +2612,7 @@
         <v>1</v>
       </c>
       <c r="P24" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
     </row>
     <row r="25" spans="1:16">
@@ -2671,7 +2662,7 @@
         <v>1</v>
       </c>
       <c r="P25" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
     </row>
     <row r="26" spans="1:16">
@@ -2685,7 +2676,7 @@
         <v>4.521898732172186</v>
       </c>
       <c r="D26" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="E26">
         <v>7.471272137184702</v>
@@ -2721,7 +2712,7 @@
         <v>1</v>
       </c>
       <c r="P26" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
     </row>
     <row r="27" spans="1:16">
@@ -2771,7 +2762,7 @@
         <v>1</v>
       </c>
       <c r="P27" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
     </row>
     <row r="28" spans="1:16">
@@ -2821,7 +2812,7 @@
         <v>1</v>
       </c>
       <c r="P28" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -2835,7 +2826,7 @@
         <v>10.06347633639325</v>
       </c>
       <c r="D29" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="E29">
         <v>8.926863738767604</v>
@@ -2871,7 +2862,7 @@
         <v>1</v>
       </c>
       <c r="P29" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -3035,7 +3026,7 @@
         <v>10.57243502356749</v>
       </c>
       <c r="D33" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="E33">
         <v>11.2289160904059</v>
@@ -3085,7 +3076,7 @@
         <v>10.58025171866791</v>
       </c>
       <c r="D34" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="E34">
         <v>11.2289160904059</v>
@@ -3135,7 +3126,7 @@
         <v>6.89098969886382</v>
       </c>
       <c r="D35" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="E35">
         <v>9.162922766970905</v>
@@ -3171,7 +3162,7 @@
         <v>1</v>
       </c>
       <c r="P35" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -3221,7 +3212,7 @@
         <v>1</v>
       </c>
       <c r="P36" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
     </row>
     <row r="37" spans="1:16">
@@ -3271,7 +3262,7 @@
         <v>1</v>
       </c>
       <c r="P37" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
     </row>
     <row r="38" spans="1:16">
@@ -3321,7 +3312,7 @@
         <v>1</v>
       </c>
       <c r="P38" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
     </row>
     <row r="39" spans="1:16">
@@ -3335,7 +3326,7 @@
         <v>10.57710841036202</v>
       </c>
       <c r="D39" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="E39">
         <v>10.91875227586742</v>
@@ -3371,7 +3362,7 @@
         <v>1</v>
       </c>
       <c r="P39" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
     </row>
     <row r="40" spans="1:16">
@@ -3385,7 +3376,7 @@
         <v>10.58544939256899</v>
       </c>
       <c r="D40" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="E40">
         <v>10.91875227586742</v>
@@ -3421,7 +3412,7 @@
         <v>1</v>
       </c>
       <c r="P40" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
     </row>
     <row r="41" spans="1:16">
@@ -3471,7 +3462,7 @@
         <v>1</v>
       </c>
       <c r="P41" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
     </row>
     <row r="42" spans="1:16">
@@ -3521,7 +3512,7 @@
         <v>1</v>
       </c>
       <c r="P42" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
     </row>
     <row r="43" spans="1:16">
@@ -3571,7 +3562,7 @@
         <v>1</v>
       </c>
       <c r="P43" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
     </row>
     <row r="44" spans="1:16">
@@ -3585,7 +3576,7 @@
         <v>10.50706987192051</v>
       </c>
       <c r="D44" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="E44">
         <v>9.836117792760128</v>
@@ -3621,7 +3612,7 @@
         <v>1</v>
       </c>
       <c r="P44" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -3785,7 +3776,7 @@
         <v>11.00643298606593</v>
       </c>
       <c r="D48" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="E48">
         <v>10.08970532444388</v>
@@ -3871,7 +3862,7 @@
         <v>1</v>
       </c>
       <c r="P49" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
     </row>
     <row r="50" spans="1:16">
@@ -3921,7 +3912,7 @@
         <v>1</v>
       </c>
       <c r="P50" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
     </row>
     <row r="51" spans="1:16">
@@ -3971,7 +3962,7 @@
         <v>1</v>
       </c>
       <c r="P51" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
     </row>
     <row r="52" spans="1:16">
@@ -4021,7 +4012,7 @@
         <v>1</v>
       </c>
       <c r="P52" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
     </row>
     <row r="53" spans="1:16">
@@ -4071,7 +4062,7 @@
         <v>1</v>
       </c>
       <c r="P53" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
     </row>
     <row r="54" spans="1:16">
@@ -4121,7 +4112,7 @@
         <v>1</v>
       </c>
       <c r="P54" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
     </row>
     <row r="55" spans="1:16">
@@ -4135,7 +4126,7 @@
         <v>10.96451987407661</v>
       </c>
       <c r="D55" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="E55">
         <v>9.918825279734797</v>
@@ -4171,7 +4162,7 @@
         <v>1</v>
       </c>
       <c r="P55" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
     </row>
     <row r="56" spans="1:16">
@@ -4221,7 +4212,7 @@
         <v>1</v>
       </c>
       <c r="P56" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="57" spans="1:16">
@@ -4271,7 +4262,7 @@
         <v>1</v>
       </c>
       <c r="P57" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="58" spans="1:16">
@@ -4321,7 +4312,7 @@
         <v>1</v>
       </c>
       <c r="P58" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="59" spans="1:16">
@@ -4371,7 +4362,7 @@
         <v>1</v>
       </c>
       <c r="P59" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="60" spans="1:16">
@@ -4421,7 +4412,7 @@
         <v>1</v>
       </c>
       <c r="P60" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="61" spans="1:16">
@@ -4471,7 +4462,7 @@
         <v>1</v>
       </c>
       <c r="P61" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="62" spans="1:16">
@@ -4521,7 +4512,7 @@
         <v>1</v>
       </c>
       <c r="P62" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
     </row>
     <row r="63" spans="1:16">
@@ -4535,7 +4526,7 @@
         <v>10.70295290100141</v>
       </c>
       <c r="D63" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="E63">
         <v>8.905400692050126</v>
@@ -4571,7 +4562,7 @@
         <v>1</v>
       </c>
       <c r="P63" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
     </row>
     <row r="64" spans="1:16">
@@ -4585,7 +4576,7 @@
         <v>11.20304517915771</v>
       </c>
       <c r="D64" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="E64">
         <v>8.905400692050126</v>
@@ -4621,7 +4612,7 @@
         <v>1</v>
       </c>
       <c r="P64" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
     </row>
     <row r="65" spans="1:16">
@@ -4671,7 +4662,7 @@
         <v>1</v>
       </c>
       <c r="P65" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
     </row>
     <row r="66" spans="1:16">
@@ -4685,7 +4676,7 @@
         <v>10.69564352718713</v>
       </c>
       <c r="D66" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E66">
         <v>10.68408451836947</v>
@@ -4721,7 +4712,7 @@
         <v>1</v>
       </c>
       <c r="P66" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
     </row>
     <row r="67" spans="1:16">
@@ -4735,7 +4726,7 @@
         <v>11.03068966626528</v>
       </c>
       <c r="D67" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E67">
         <v>10.68408451836947</v>
@@ -4771,7 +4762,7 @@
         <v>1</v>
       </c>
       <c r="P67" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
     </row>
     <row r="68" spans="1:16">
@@ -4821,7 +4812,7 @@
         <v>1</v>
       </c>
       <c r="P68" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
     </row>
     <row r="69" spans="1:16">
@@ -4835,7 +4826,7 @@
         <v>10.52605158161457</v>
       </c>
       <c r="D69" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="E69">
         <v>8.71498607743235</v>
@@ -4871,7 +4862,7 @@
         <v>1</v>
       </c>
       <c r="P69" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
     </row>
     <row r="70" spans="1:16">
@@ -4885,7 +4876,7 @@
         <v>11.02061569354003</v>
       </c>
       <c r="D70" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="E70">
         <v>8.71498607743235</v>
@@ -4921,7 +4912,7 @@
         <v>1</v>
       </c>
       <c r="P70" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
     </row>
     <row r="71" spans="1:16">
@@ -4971,7 +4962,7 @@
         <v>1</v>
       </c>
       <c r="P71" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
     </row>
     <row r="72" spans="1:16">
@@ -4985,7 +4976,7 @@
         <v>10.52396325368498</v>
       </c>
       <c r="D72" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="E72">
         <v>8.806051581614568</v>
@@ -5021,7 +5012,7 @@
         <v>1</v>
       </c>
       <c r="P72" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
     </row>
     <row r="73" spans="1:16">
@@ -5035,7 +5026,7 @@
         <v>10.8562453096477</v>
       </c>
       <c r="D73" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="E73">
         <v>8.806051581614568</v>
@@ -5071,7 +5062,7 @@
         <v>1</v>
       </c>
       <c r="P73" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
     </row>
     <row r="74" spans="1:16">
@@ -5085,7 +5076,7 @@
         <v>10.34525014922946</v>
       </c>
       <c r="D74" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="E74">
         <v>8.520373424517821</v>
@@ -5135,7 +5126,7 @@
         <v>10.83416421639288</v>
       </c>
       <c r="D75" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="E75">
         <v>8.520373424517821</v>
@@ -5285,7 +5276,7 @@
         <v>10.34849797468624</v>
       </c>
       <c r="D78" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="E78">
         <v>8.625250149229462</v>
@@ -5335,7 +5326,7 @@
         <v>10.67795500826794</v>
       </c>
       <c r="D79" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="E79">
         <v>8.625250149229462</v>
@@ -5385,7 +5376,7 @@
         <v>10.18864383981015</v>
       </c>
       <c r="D80" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="E80">
         <v>8.351804133128983</v>
@@ -5421,7 +5412,7 @@
         <v>1</v>
       </c>
       <c r="P80" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="81" spans="1:16">
@@ -5435,7 +5426,7 @@
         <v>10.67266395980422</v>
       </c>
       <c r="D81" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="E81">
         <v>8.351804133128983</v>
@@ -5471,7 +5462,7 @@
         <v>1</v>
       </c>
       <c r="P81" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="82" spans="1:16">
@@ -5521,7 +5512,7 @@
         <v>1</v>
       </c>
       <c r="P82" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="83" spans="1:16">
@@ -5571,7 +5562,7 @@
         <v>1</v>
       </c>
       <c r="P83" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="84" spans="1:16">
@@ -5585,7 +5576,7 @@
         <v>10.19651372648243</v>
       </c>
       <c r="D84" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="E84">
         <v>8.468643839810152</v>
@@ -5621,7 +5612,7 @@
         <v>1</v>
       </c>
       <c r="P84" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="85" spans="1:16">
@@ -5635,7 +5626,7 @@
         <v>10.52352378647946</v>
       </c>
       <c r="D85" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="E85">
         <v>8.468643839810152</v>
@@ -5671,7 +5662,7 @@
         <v>1</v>
       </c>
       <c r="P85" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="86" spans="1:16">
@@ -5685,7 +5676,7 @@
         <v>-1.278554542763944</v>
       </c>
       <c r="D86" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="E86">
         <v>0.01420169243589342</v>
@@ -5721,7 +5712,7 @@
         <v>1</v>
       </c>
       <c r="P86" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
     </row>
     <row r="87" spans="1:16">
@@ -5735,7 +5726,7 @@
         <v>-2.406586639852707</v>
       </c>
       <c r="D87" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="E87">
         <v>0.01420169243589342</v>
@@ -5771,7 +5762,7 @@
         <v>1</v>
       </c>
       <c r="P87" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
     </row>
     <row r="88" spans="1:16">
@@ -5821,7 +5812,7 @@
         <v>1</v>
       </c>
       <c r="P88" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
     </row>
     <row r="89" spans="1:16">
@@ -5835,7 +5826,7 @@
         <v>-1.341212522415489</v>
       </c>
       <c r="D89" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E89">
         <v>0.1246199151405953</v>
@@ -5871,7 +5862,7 @@
         <v>1</v>
       </c>
       <c r="P89" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
     </row>
     <row r="90" spans="1:16">
@@ -5885,7 +5876,7 @@
         <v>-2.475362406493851</v>
       </c>
       <c r="D90" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E90">
         <v>0.1246199151405953</v>
@@ -5921,7 +5912,7 @@
         <v>1</v>
       </c>
       <c r="P90" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
     </row>
     <row r="91" spans="1:16">
@@ -5971,7 +5962,7 @@
         <v>1</v>
       </c>
       <c r="P91" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
     </row>
     <row r="92" spans="1:16">
@@ -5985,7 +5976,7 @@
         <v>-2.566016320350375</v>
       </c>
       <c r="D92" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E92">
         <v>0.02954385914472724</v>
@@ -6135,7 +6126,7 @@
         <v>-2.663355023194697</v>
       </c>
       <c r="D95" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="E95">
         <v>0.03872013419191234</v>
@@ -6171,7 +6162,7 @@
         <v>1</v>
       </c>
       <c r="P95" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
     </row>
     <row r="96" spans="1:16">
@@ -6221,7 +6212,7 @@
         <v>1</v>
       </c>
       <c r="P96" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
     </row>
     <row r="97" spans="1:16">
@@ -6271,7 +6262,7 @@
         <v>1</v>
       </c>
       <c r="P97" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
     </row>
     <row r="98" spans="1:16">
@@ -6285,7 +6276,7 @@
         <v>-2.748103967913549</v>
       </c>
       <c r="D98" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="E98">
         <v>-0.04760949385741853</v>
@@ -6321,7 +6312,7 @@
         <v>1</v>
       </c>
       <c r="P98" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
     </row>
     <row r="99" spans="1:16">
@@ -6335,7 +6326,7 @@
         <v>1.170412609918055</v>
       </c>
       <c r="D99" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="E99">
         <v>1.469846093587645</v>
@@ -6371,7 +6362,7 @@
         <v>1</v>
       </c>
       <c r="P99" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
     </row>
     <row r="100" spans="1:16">
@@ -6385,7 +6376,7 @@
         <v>1.197090465141786</v>
       </c>
       <c r="D100" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="E100">
         <v>1.469846093587645</v>
@@ -6421,7 +6412,7 @@
         <v>1</v>
       </c>
       <c r="P100" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
     </row>
     <row r="101" spans="1:16">
@@ -6435,7 +6426,7 @@
         <v>-2.807295369205091</v>
       </c>
       <c r="D101" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="E101">
         <v>0.3363998775430197</v>
@@ -6471,7 +6462,7 @@
         <v>1</v>
       </c>
       <c r="P101" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
     </row>
     <row r="102" spans="1:16">
@@ -6521,7 +6512,7 @@
         <v>1</v>
       </c>
       <c r="P102" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
     </row>
     <row r="103" spans="1:16">
@@ -6621,7 +6612,7 @@
         <v>1</v>
       </c>
       <c r="P104" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
     </row>
     <row r="105" spans="1:16">
@@ -6635,7 +6626,7 @@
         <v>1.819034812951433</v>
       </c>
       <c r="D105" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="E105">
         <v>1.780382458905816</v>
@@ -6671,7 +6662,7 @@
         <v>1</v>
       </c>
       <c r="P105" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
     </row>
     <row r="106" spans="1:16">
@@ -6685,7 +6676,7 @@
         <v>1.278232359359254</v>
       </c>
       <c r="D106" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="E106">
         <v>1.780382458905816</v>
@@ -6721,7 +6712,7 @@
         <v>1</v>
       </c>
       <c r="P106" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
     </row>
     <row r="107" spans="1:16">
@@ -6735,7 +6726,7 @@
         <v>-1.27500579580901</v>
       </c>
       <c r="D107" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="E107">
         <v>0.204597470791132</v>
@@ -6771,7 +6762,7 @@
         <v>1</v>
       </c>
       <c r="P107" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
     </row>
     <row r="108" spans="1:16">
@@ -6785,7 +6776,7 @@
         <v>-1.164182632644362</v>
       </c>
       <c r="D108" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="E108">
         <v>0.204597470791132</v>
@@ -6821,7 +6812,7 @@
         <v>1</v>
       </c>
       <c r="P108" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
     </row>
     <row r="109" spans="1:16">
@@ -6871,7 +6862,7 @@
         <v>1</v>
       </c>
       <c r="P109" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
     </row>
     <row r="110" spans="1:16">
@@ -6921,7 +6912,7 @@
         <v>1</v>
       </c>
       <c r="P110" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
     </row>
     <row r="111" spans="1:16">
@@ -6935,7 +6926,7 @@
         <v>-1.330656541117063</v>
       </c>
       <c r="D111" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="E111">
         <v>0.1498300706466971</v>
@@ -6971,7 +6962,7 @@
         <v>1</v>
       </c>
       <c r="P111" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
     </row>
     <row r="112" spans="1:16">
@@ -6985,7 +6976,7 @@
         <v>-1.089957636312631</v>
       </c>
       <c r="D112" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="E112">
         <v>0.1498300706466971</v>
@@ -7021,7 +7012,7 @@
         <v>1</v>
       </c>
       <c r="P112" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
     </row>
     <row r="113" spans="1:16">
@@ -7035,7 +7026,7 @@
         <v>1.663161219313913</v>
       </c>
       <c r="D113" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="E113">
         <v>1.394552474924428</v>
@@ -7071,7 +7062,7 @@
         <v>1</v>
       </c>
       <c r="P113" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
     </row>
     <row r="114" spans="1:16">
@@ -7085,7 +7076,7 @@
         <v>2.020453841772007</v>
       </c>
       <c r="D114" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="E114">
         <v>1.394552474924428</v>
@@ -7121,7 +7112,7 @@
         <v>1</v>
       </c>
       <c r="P114" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
     </row>
     <row r="115" spans="1:16">
@@ -7171,7 +7162,7 @@
         <v>1</v>
       </c>
       <c r="P115" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
     </row>
     <row r="116" spans="1:16">
@@ -7221,7 +7212,7 @@
         <v>1</v>
       </c>
       <c r="P116" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
     </row>
     <row r="117" spans="1:16">
@@ -7271,7 +7262,7 @@
         <v>1</v>
       </c>
       <c r="P117" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
     </row>
     <row r="118" spans="1:16">
@@ -7321,7 +7312,7 @@
         <v>1</v>
       </c>
       <c r="P118" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
     </row>
     <row r="119" spans="1:16">
@@ -7371,7 +7362,7 @@
         <v>1</v>
       </c>
       <c r="P119" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
     </row>
     <row r="120" spans="1:16">
@@ -7421,7 +7412,7 @@
         <v>1</v>
       </c>
       <c r="P120" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="121" spans="1:16">
@@ -7471,7 +7462,7 @@
         <v>1</v>
       </c>
       <c r="P121" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="122" spans="1:16">
@@ -7521,7 +7512,7 @@
         <v>1</v>
       </c>
       <c r="P122" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="123" spans="1:16">
@@ -7571,7 +7562,7 @@
         <v>1</v>
       </c>
       <c r="P123" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="124" spans="1:16">
@@ -7621,7 +7612,7 @@
         <v>1</v>
       </c>
       <c r="P124" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="125" spans="1:16">
@@ -7735,7 +7726,7 @@
         <v>1.583716178161136</v>
       </c>
       <c r="D127" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="E127">
         <v>1.731188504841963</v>
@@ -7785,7 +7776,7 @@
         <v>1.943294205912665</v>
       </c>
       <c r="D128" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="E128">
         <v>1.731188504841963</v>
@@ -7835,7 +7826,7 @@
         <v>1.440029121201585</v>
       </c>
       <c r="D129" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="E129">
         <v>1.731188504841963</v>
@@ -7921,7 +7912,7 @@
         <v>1</v>
       </c>
       <c r="P130" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="131" spans="1:16">
@@ -7971,7 +7962,7 @@
         <v>1</v>
       </c>
       <c r="P131" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="132" spans="1:16">
@@ -8021,7 +8012,7 @@
         <v>1</v>
       </c>
       <c r="P132" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="133" spans="1:16">
@@ -8071,7 +8062,7 @@
         <v>1</v>
       </c>
       <c r="P133" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="134" spans="1:16">
@@ -8121,7 +8112,7 @@
         <v>1</v>
       </c>
       <c r="P134" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="135" spans="1:16">
@@ -8135,7 +8126,7 @@
         <v>-0.8820242128746258</v>
       </c>
       <c r="D135" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="E135">
         <v>0.3526024044326252</v>
@@ -8171,7 +8162,7 @@
         <v>1</v>
       </c>
       <c r="P135" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="136" spans="1:16">
@@ -8185,7 +8176,7 @@
         <v>-1.173427909927172</v>
       </c>
       <c r="D136" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="E136">
         <v>0.3526024044326252</v>
@@ -8221,7 +8212,7 @@
         <v>1</v>
       </c>
       <c r="P136" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="137" spans="1:16">
@@ -8271,7 +8262,7 @@
         <v>1</v>
       </c>
       <c r="P137" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="138" spans="1:16">
@@ -8321,7 +8312,7 @@
         <v>1</v>
       </c>
       <c r="P138" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="139" spans="1:16">
@@ -8371,7 +8362,7 @@
         <v>1</v>
       </c>
       <c r="P139" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="140" spans="1:16">
@@ -8685,7 +8676,7 @@
         <v>1.916709703800588</v>
       </c>
       <c r="D146" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="E146">
         <v>1.625228926806798</v>
@@ -8735,7 +8726,7 @@
         <v>1.775844332123576</v>
       </c>
       <c r="D147" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="E147">
         <v>1.625228926806798</v>
@@ -8785,7 +8776,7 @@
         <v>1.706459737440355</v>
       </c>
       <c r="D148" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="E148">
         <v>1.625228926806798</v>
@@ -8835,7 +8826,7 @@
         <v>1.898407474064776</v>
       </c>
       <c r="D149" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="E149">
         <v>1.579058157468399</v>
@@ -8871,7 +8862,7 @@
         <v>1</v>
       </c>
       <c r="P149" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
     </row>
     <row r="150" spans="1:16">
@@ -8885,7 +8876,7 @@
         <v>1.757671173119327</v>
       </c>
       <c r="D150" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="E150">
         <v>1.579058157468399</v>
@@ -8921,7 +8912,7 @@
         <v>1</v>
       </c>
       <c r="P150" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
     </row>
     <row r="151" spans="1:16">
@@ -8935,7 +8926,7 @@
         <v>1.688493091606606</v>
       </c>
       <c r="D151" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="E151">
         <v>1.579058157468399</v>
@@ -8971,7 +8962,7 @@
         <v>1</v>
       </c>
       <c r="P151" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
     </row>
     <row r="152" spans="1:16">
@@ -9021,7 +9012,7 @@
         <v>1</v>
       </c>
       <c r="P152" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
     </row>
     <row r="153" spans="1:16">
@@ -9071,7 +9062,7 @@
         <v>1</v>
       </c>
       <c r="P153" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
     </row>
     <row r="154" spans="1:16">
@@ -9121,7 +9112,7 @@
         <v>1</v>
       </c>
       <c r="P154" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
     </row>
     <row r="155" spans="1:16">
@@ -9171,7 +9162,7 @@
         <v>1</v>
       </c>
       <c r="P155" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
     </row>
     <row r="156" spans="1:16">
@@ -9221,7 +9212,7 @@
         <v>1</v>
       </c>
       <c r="P156" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
     </row>
     <row r="157" spans="1:16">
@@ -9271,7 +9262,7 @@
         <v>1</v>
       </c>
       <c r="P157" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
     </row>
     <row r="158" spans="1:16">
@@ -9421,7 +9412,7 @@
         <v>1</v>
       </c>
       <c r="P160" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
     </row>
     <row r="161" spans="1:16">
@@ -9471,7 +9462,7 @@
         <v>1</v>
       </c>
       <c r="P161" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
     </row>
     <row r="162" spans="1:16">
@@ -9521,7 +9512,7 @@
         <v>1</v>
       </c>
       <c r="P162" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
     </row>
     <row r="163" spans="1:16">
@@ -9571,7 +9562,7 @@
         <v>1</v>
       </c>
       <c r="P163" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
     </row>
     <row r="164" spans="1:16">
@@ -9585,7 +9576,7 @@
         <v>2.0418888555804</v>
       </c>
       <c r="D164" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="E164">
         <v>2.091052252009925</v>
@@ -9635,7 +9626,7 @@
         <v>2.437529947263654</v>
       </c>
       <c r="D165" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="E165">
         <v>2.091052252009925</v>
@@ -9685,7 +9676,7 @@
         <v>2.035427646090795</v>
       </c>
       <c r="D166" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="E166">
         <v>1.677256780401082</v>
@@ -9721,7 +9712,7 @@
         <v>1</v>
       </c>
       <c r="P166" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
     </row>
     <row r="167" spans="1:16">
@@ -9735,7 +9726,7 @@
         <v>2.4319519246827</v>
       </c>
       <c r="D167" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="E167">
         <v>1.677256780401082</v>
@@ -9771,7 +9762,7 @@
         <v>1</v>
       </c>
       <c r="P167" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
     </row>
     <row r="168" spans="1:16">
@@ -9821,7 +9812,7 @@
         <v>1</v>
       </c>
       <c r="P168" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
     </row>
     <row r="169" spans="1:16">
@@ -9871,7 +9862,7 @@
         <v>1</v>
       </c>
       <c r="P169" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
     </row>
     <row r="170" spans="1:16">
@@ -9921,7 +9912,7 @@
         <v>1</v>
       </c>
       <c r="P170" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="171" spans="1:16">
@@ -9971,7 +9962,7 @@
         <v>1</v>
       </c>
       <c r="P171" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="172" spans="1:16">
@@ -10021,7 +10012,7 @@
         <v>1</v>
       </c>
       <c r="P172" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="173" spans="1:16">
@@ -10035,7 +10026,7 @@
         <v>2.053037839433713</v>
       </c>
       <c r="D173" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="E173">
         <v>2.029053723158555</v>
@@ -10071,7 +10062,7 @@
         <v>1</v>
       </c>
       <c r="P173" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="174" spans="1:16">
@@ -10185,7 +10176,7 @@
         <v>2.072439051471395</v>
       </c>
       <c r="D176" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="E176">
         <v>2.198537473651809</v>
@@ -10221,7 +10212,7 @@
         <v>1</v>
       </c>
       <c r="P176" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
     </row>
     <row r="177" spans="1:16">
@@ -10235,7 +10226,7 @@
         <v>2.176038435736924</v>
       </c>
       <c r="D177" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="E177">
         <v>2.198537473651809</v>
@@ -10271,7 +10262,7 @@
         <v>1</v>
       </c>
       <c r="P177" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
     </row>
     <row r="178" spans="1:16">
@@ -10321,7 +10312,7 @@
         <v>1</v>
       </c>
       <c r="P178" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
     </row>
     <row r="179" spans="1:16">
@@ -10385,7 +10376,7 @@
         <v>2.199572666349018</v>
       </c>
       <c r="D180" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="E180">
         <v>2.369622868222606</v>
@@ -10585,7 +10576,7 @@
         <v>2.441204477380014</v>
       </c>
       <c r="D184" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="E184">
         <v>3.019740173907834</v>
@@ -10685,7 +10676,7 @@
         <v>2.450942264059425</v>
       </c>
       <c r="D186" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="E186">
         <v>3.396065694761221</v>
@@ -10735,7 +10726,7 @@
         <v>2.93271297523739</v>
       </c>
       <c r="D187" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="E187">
         <v>3.396065694761221</v>
@@ -10835,7 +10826,7 @@
         <v>2.613291041571109</v>
       </c>
       <c r="D189" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="E189">
         <v>1.747095958240026</v>
@@ -10885,7 +10876,7 @@
         <v>2.94332933323569</v>
       </c>
       <c r="D190" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="E190">
         <v>3.513960124909904</v>
@@ -11035,7 +11026,7 @@
         <v>2.630002520413537</v>
       </c>
       <c r="D193" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="E193">
         <v>1.763414225815572</v>
@@ -11085,7 +11076,7 @@
         <v>2.960405936825934</v>
       </c>
       <c r="D194" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="E194">
         <v>2.688557154970242</v>
@@ -11285,7 +11276,7 @@
         <v>2.642059072099817</v>
       </c>
       <c r="D198" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="E198">
         <v>1.775187093932763</v>
@@ -11335,7 +11326,7 @@
         <v>2.972725908969226</v>
       </c>
       <c r="D199" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="E199">
         <v>2.375803028433923</v>
@@ -11485,7 +11476,7 @@
         <v>2.666955617984192</v>
       </c>
       <c r="D202" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="E202">
         <v>1.799497838737505</v>
@@ -11535,7 +11526,7 @@
         <v>2.998166412998973</v>
       </c>
       <c r="D203" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="E203">
         <v>1.736641978102437</v>
@@ -11685,7 +11676,7 @@
         <v>2.973643871143521</v>
       </c>
       <c r="D206" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="E206">
         <v>1.818524938691256</v>
@@ -11735,7 +11726,7 @@
         <v>3.018077732744034</v>
       </c>
       <c r="D207" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="E207">
         <v>1.759533446033025</v>
@@ -11885,7 +11876,7 @@
         <v>2.990082102112254</v>
       </c>
       <c r="D210" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="E210">
         <v>1.83485077149952</v>
@@ -11935,7 +11926,7 @@
         <v>3.03516225313547</v>
       </c>
       <c r="D211" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="E211">
         <v>1.779175024575153</v>
@@ -12021,7 +12012,7 @@
         <v>1</v>
       </c>
       <c r="P212" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="213" spans="1:16">
@@ -12071,7 +12062,7 @@
         <v>1</v>
       </c>
       <c r="P213" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="214" spans="1:16">
@@ -12085,7 +12076,7 @@
         <v>3.005496469975766</v>
       </c>
       <c r="D214" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="E214">
         <v>1.850159741975929</v>
@@ -12121,7 +12112,7 @@
         <v>1</v>
       </c>
       <c r="P214" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="215" spans="1:16">
@@ -12135,7 +12126,7 @@
         <v>3.051182655974811</v>
       </c>
       <c r="D215" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="E215">
         <v>1.797593217971041</v>
@@ -12171,7 +12162,7 @@
         <v>1</v>
       </c>
       <c r="P215" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="216" spans="1:16">
@@ -12285,7 +12276,7 @@
         <v>3.018931533510157</v>
       </c>
       <c r="D218" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="E218">
         <v>1.863502941828035</v>
@@ -12335,7 +12326,7 @@
         <v>3.06514593568235</v>
       </c>
       <c r="D219" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="E219">
         <v>1.813646396450594</v>
@@ -12485,7 +12476,7 @@
         <v>3.033933076549712</v>
       </c>
       <c r="D222" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="E222">
         <v>1.878401910214327</v>
@@ -12535,7 +12526,7 @@
         <v>3.080737282978161</v>
       </c>
       <c r="D223" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="E223">
         <v>1.831571317108114</v>
@@ -12585,7 +12576,7 @@
         <v>1.639859271051932</v>
       </c>
       <c r="D224" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="E224">
         <v>1.9209216037227</v>
@@ -12735,7 +12726,7 @@
         <v>3.05833801181463</v>
       </c>
       <c r="D227" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="E227">
         <v>1.902639974127007</v>
@@ -12785,7 +12776,7 @@
         <v>3.106101728518452</v>
       </c>
       <c r="D228" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="E228">
         <v>1.860732085911838</v>
@@ -12871,7 +12862,7 @@
         <v>1</v>
       </c>
       <c r="P229" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="230" spans="1:16">
@@ -12921,7 +12912,7 @@
         <v>1</v>
       </c>
       <c r="P230" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="231" spans="1:16">
@@ -12935,7 +12926,7 @@
         <v>3.085055612872655</v>
       </c>
       <c r="D231" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="E231">
         <v>1.929174890733353</v>
@@ -12971,7 +12962,7 @@
         <v>1</v>
       </c>
       <c r="P231" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="232" spans="1:16">
@@ -12985,7 +12976,7 @@
         <v>3.13386976517363</v>
       </c>
       <c r="D232" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="E232">
         <v>1.892656193842708</v>
@@ -13021,7 +13012,7 @@
         <v>1</v>
       </c>
       <c r="P232" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="233" spans="1:16">
@@ -13085,7 +13076,7 @@
         <v>3.103034611570727</v>
       </c>
       <c r="D234" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="E234">
         <v>1.947030956106994</v>
@@ -13135,7 +13126,7 @@
         <v>3.152555630487182</v>
       </c>
       <c r="D235" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="E235">
         <v>1.914138792287073</v>
@@ -13185,7 +13176,7 @@
         <v>1.641725609550694</v>
       </c>
       <c r="D236" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="E236">
         <v>1.89319910743864</v>
@@ -13271,7 +13262,7 @@
         <v>1</v>
       </c>
       <c r="P237" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="238" spans="1:16">
@@ -13285,7 +13276,7 @@
         <v>3.11979974827751</v>
       </c>
       <c r="D238" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="E238">
         <v>1.963681459400396</v>
@@ -13321,7 +13312,7 @@
         <v>1</v>
       </c>
       <c r="P238" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="239" spans="1:16">
@@ -13335,7 +13326,7 @@
         <v>3.169979909320897</v>
       </c>
       <c r="D239" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="E239">
         <v>1.934170981275177</v>
@@ -13371,7 +13362,7 @@
         <v>1</v>
       </c>
       <c r="P239" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="240" spans="1:16">
@@ -13385,7 +13376,7 @@
         <v>1.664480342106565</v>
       </c>
       <c r="D240" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E240">
         <v>2.221652319966786</v>
@@ -13421,7 +13412,7 @@
         <v>1</v>
       </c>
       <c r="P240" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="241" spans="1:16">
@@ -13485,7 +13476,7 @@
         <v>3.136490860930856</v>
       </c>
       <c r="D242" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="E242">
         <v>1.980258444787738</v>
@@ -13535,7 +13526,7 @@
         <v>3.187327253753777</v>
       </c>
       <c r="D243" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="E243">
         <v>1.954114721009688</v>
@@ -13735,7 +13726,7 @@
         <v>3.154470288152615</v>
       </c>
       <c r="D247" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="E247">
         <v>1.998114935754989</v>
@@ -13785,7 +13776,7 @@
         <v>3.206013564438956</v>
       </c>
       <c r="D248" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="E248">
         <v>1.975597831484915</v>
@@ -13971,7 +13962,7 @@
         <v>1</v>
       </c>
       <c r="P251" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="252" spans="1:16">
@@ -14021,7 +14012,7 @@
         <v>1</v>
       </c>
       <c r="P252" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="253" spans="1:16">
@@ -14035,7 +14026,7 @@
         <v>3.175183381627829</v>
       </c>
       <c r="D253" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="E253">
         <v>2.406837822852639</v>
@@ -14071,7 +14062,7 @@
         <v>1</v>
       </c>
       <c r="P253" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="254" spans="1:16">
@@ -14085,7 +14076,7 @@
         <v>3.227541018854222</v>
       </c>
       <c r="D254" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="E254">
         <v>2.000347322662993</v>
@@ -14121,7 +14112,7 @@
         <v>1</v>
       </c>
       <c r="P254" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="255" spans="1:16">
@@ -14171,7 +14162,7 @@
         <v>1</v>
       </c>
       <c r="P255" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="256" spans="1:16">
@@ -14221,7 +14212,7 @@
         <v>1</v>
       </c>
       <c r="P256" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="257" spans="1:16">
@@ -14335,7 +14326,7 @@
         <v>3.194491499183421</v>
       </c>
       <c r="D259" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="E259">
         <v>2.42485873257119</v>
@@ -14385,7 +14376,7 @@
         <v>3.247608258980375</v>
       </c>
       <c r="D260" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="E260">
         <v>2.023418047742236</v>
@@ -14635,7 +14626,7 @@
         <v>3.213727962726566</v>
       </c>
       <c r="D265" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="E265">
         <v>2.442812765211459</v>
@@ -14685,7 +14676,7 @@
         <v>3.26760102792778</v>
       </c>
       <c r="D266" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="E266">
         <v>2.046403155463022</v>
@@ -14885,7 +14876,7 @@
         <v>3.233647867837396</v>
       </c>
       <c r="D270" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="E270">
         <v>2.461404676648234</v>
@@ -14935,7 +14926,7 @@
         <v>3.288304108795105</v>
       </c>
       <c r="D271" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="E271">
         <v>2.070204888236475</v>
@@ -15135,7 +15126,7 @@
         <v>3.249417008017017</v>
       </c>
       <c r="D275" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="E275">
         <v>2.476122540815881</v>
@@ -15185,7 +15176,7 @@
         <v>3.304693232263839</v>
       </c>
       <c r="D276" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="E276">
         <v>2.089046989066485</v>
@@ -15335,7 +15326,7 @@
         <v>1.914875661806953</v>
       </c>
       <c r="D279" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="E279">
         <v>2.109898465499843</v>
@@ -15421,7 +15412,7 @@
         <v>1</v>
       </c>
       <c r="P280" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="281" spans="1:16">
@@ -15435,7 +15426,7 @@
         <v>3.261163134684622</v>
       </c>
       <c r="D281" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="E281">
         <v>2.487085592372312</v>
@@ -15471,7 +15462,7 @@
         <v>1</v>
       </c>
       <c r="P281" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="282" spans="1:16">
@@ -15485,7 +15476,7 @@
         <v>3.316901172458547</v>
       </c>
       <c r="D282" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="E282">
         <v>2.103082104520595</v>
@@ -15521,7 +15512,7 @@
         <v>1</v>
       </c>
       <c r="P282" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="283" spans="1:16">
@@ -15571,7 +15562,7 @@
         <v>1</v>
       </c>
       <c r="P283" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="284" spans="1:16">
@@ -15621,7 +15612,7 @@
         <v>1</v>
       </c>
       <c r="P284" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="285" spans="1:16">
@@ -15635,7 +15626,7 @@
         <v>1.930296217842372</v>
       </c>
       <c r="D285" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="E285">
         <v>2.383746445952788</v>
@@ -15671,7 +15662,7 @@
         <v>1</v>
       </c>
       <c r="P285" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="286" spans="1:16">
@@ -15721,7 +15712,7 @@
         <v>1</v>
       </c>
       <c r="P286" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
     <row r="287" spans="1:16">
@@ -15735,7 +15726,7 @@
         <v>3.267778188252251</v>
       </c>
       <c r="D287" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="E287">
         <v>2.493259642368766</v>
@@ -15771,7 +15762,7 @@
         <v>1</v>
       </c>
       <c r="P287" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
     <row r="288" spans="1:16">
@@ -15785,7 +15776,7 @@
         <v>3.323776305055329</v>
       </c>
       <c r="D288" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="E288">
         <v>2.110986245450121</v>
@@ -15821,7 +15812,7 @@
         <v>1</v>
       </c>
       <c r="P288" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
     <row r="289" spans="1:16">
@@ -15871,7 +15862,7 @@
         <v>1</v>
       </c>
       <c r="P289" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
     <row r="290" spans="1:16">
@@ -15921,7 +15912,7 @@
         <v>1</v>
       </c>
       <c r="P290" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
     <row r="291" spans="1:16">
@@ -15971,7 +15962,7 @@
         <v>1</v>
       </c>
       <c r="P291" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
     <row r="292" spans="1:16">
@@ -15985,7 +15976,7 @@
         <v>3.278598009747792</v>
       </c>
       <c r="D292" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="E292">
         <v>2.503358142431271</v>
@@ -16035,7 +16026,7 @@
         <v>3.335021521242147</v>
       </c>
       <c r="D293" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="E293">
         <v>2.123914544980693</v>
@@ -16185,7 +16176,7 @@
         <v>1.953185079463765</v>
       </c>
       <c r="D296" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="E296">
         <v>1.673185079463764</v>
@@ -16235,7 +16226,7 @@
         <v>1.838424946780282</v>
       </c>
       <c r="D297" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="E297">
         <v>1.673185079463764</v>
@@ -16285,7 +16276,7 @@
         <v>3.286491586851236</v>
       </c>
       <c r="D298" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="E298">
         <v>2.510725481061151</v>
@@ -16335,7 +16326,7 @@
         <v>3.343225444112052</v>
       </c>
       <c r="D299" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="E299">
         <v>2.133346357622241</v>
@@ -16485,7 +16476,7 @@
         <v>1.963547929404697</v>
       </c>
       <c r="D302" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E302">
         <v>2.040362444937774</v>
@@ -16535,7 +16526,7 @@
         <v>1.849314035194777</v>
       </c>
       <c r="D303" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E303">
         <v>2.040362444937774</v>
@@ -16585,7 +16576,7 @@
         <v>3.287218803551511</v>
       </c>
       <c r="D304" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="E304">
         <v>2.511404216648074</v>
@@ -16635,7 +16626,7 @@
         <v>3.34398125223815</v>
       </c>
       <c r="D305" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="E305">
         <v>2.134215288346162</v>
@@ -16785,7 +16776,7 @@
         <v>1.964502634406085</v>
       </c>
       <c r="D308" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="E308">
         <v>2.034789980466009</v>
@@ -16835,7 +16826,7 @@
         <v>1.850317221309513</v>
       </c>
       <c r="D309" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="E309">
         <v>2.034789980466009</v>
@@ -16885,7 +16876,7 @@
         <v>3.309574328279867</v>
       </c>
       <c r="D310" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="E310">
         <v>2.532269373061208</v>
@@ -16935,7 +16926,7 @@
         <v>3.367215712126766</v>
       </c>
       <c r="D311" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="E311">
         <v>2.160927274303631</v>
@@ -17185,7 +17176,7 @@
         <v>3.386581638751728</v>
       </c>
       <c r="D316" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="E316">
         <v>2.183191719551736</v>
@@ -17285,7 +17276,7 @@
         <v>2.018313648949551</v>
       </c>
       <c r="D318" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="E318">
         <v>2.020805677582523</v>
@@ -17335,7 +17326,7 @@
         <v>1.906860826435267</v>
       </c>
       <c r="D319" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="E319">
         <v>2.020805677582523</v>
@@ -17385,7 +17376,7 @@
         <v>1.784750528729781</v>
       </c>
       <c r="D320" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="E320">
         <v>2.020805677582523</v>
@@ -17435,7 +17426,7 @@
         <v>3.376305833526885</v>
       </c>
       <c r="D321" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="E321">
         <v>2.171377923742256</v>
@@ -17471,7 +17462,7 @@
         <v>1</v>
       </c>
       <c r="P321" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="322" spans="1:16">
@@ -17521,7 +17512,7 @@
         <v>1</v>
       </c>
       <c r="P322" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="323" spans="1:16">
@@ -17571,7 +17562,7 @@
         <v>1</v>
       </c>
       <c r="P323" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="324" spans="1:16">
@@ -17621,7 +17612,7 @@
         <v>1</v>
       </c>
       <c r="P324" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="325" spans="1:16">
@@ -17635,7 +17626,7 @@
         <v>3.346413966869674</v>
       </c>
       <c r="D325" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="E325">
         <v>2.137012109937338</v>
@@ -17671,7 +17662,7 @@
         <v>1</v>
       </c>
       <c r="P325" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="326" spans="1:16">
@@ -17721,7 +17712,7 @@
         <v>1</v>
       </c>
       <c r="P326" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="327" spans="1:16">
@@ -17735,7 +17726,7 @@
         <v>1.853546169841817</v>
       </c>
       <c r="D327" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="E327">
         <v>1.909412654865697</v>
@@ -17771,7 +17762,7 @@
         <v>1</v>
       </c>
       <c r="P327" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="328" spans="1:16">
@@ -17785,7 +17776,7 @@
         <v>1.729057523143315</v>
       </c>
       <c r="D328" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="E328">
         <v>1.909412654865697</v>
@@ -17821,7 +17812,7 @@
         <v>1</v>
       </c>
       <c r="P328" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="329" spans="1:16">
@@ -17835,7 +17826,7 @@
         <v>1.90213361560998</v>
       </c>
       <c r="D329" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="E329">
         <v>1.909412654865697</v>
@@ -17871,7 +17862,7 @@
         <v>1</v>
       </c>
       <c r="P329" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="330" spans="1:16">
@@ -17885,7 +17876,7 @@
         <v>3.335708401471214</v>
       </c>
       <c r="D330" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="E330">
         <v>2.124704231296676</v>
@@ -17921,7 +17912,7 @@
         <v>1</v>
       </c>
       <c r="P330" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
     </row>
     <row r="331" spans="1:16">
@@ -17971,7 +17962,7 @@
         <v>1</v>
       </c>
       <c r="P331" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
     </row>
     <row r="332" spans="1:16">
@@ -17985,7 +17976,7 @@
         <v>1.839336644715903</v>
       </c>
       <c r="D332" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E332">
         <v>2.572020438006287</v>
@@ -18021,7 +18012,7 @@
         <v>1</v>
       </c>
       <c r="P332" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
     </row>
     <row r="333" spans="1:16">
@@ -18035,7 +18026,7 @@
         <v>1.714214115855647</v>
       </c>
       <c r="D333" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E333">
         <v>2.572020438006287</v>
@@ -18071,7 +18062,7 @@
         <v>1</v>
       </c>
       <c r="P333" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
     </row>
     <row r="334" spans="1:16">
@@ -18085,7 +18076,7 @@
         <v>1.88846993345668</v>
       </c>
       <c r="D334" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E334">
         <v>2.572020438006287</v>
@@ -18121,7 +18112,7 @@
         <v>1</v>
       </c>
       <c r="P334" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
     </row>
     <row r="335" spans="1:16">
@@ -18135,7 +18126,7 @@
         <v>3.319807569063805</v>
       </c>
       <c r="D335" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="E335">
         <v>2.106423504565129</v>
@@ -18235,7 +18226,7 @@
         <v>1.818231428017253</v>
       </c>
       <c r="D337" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E337">
         <v>2.552327466291189</v>
@@ -18285,7 +18276,7 @@
         <v>1.692167402501294</v>
       </c>
       <c r="D338" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E338">
         <v>2.552327466291189</v>
@@ -18335,7 +18326,7 @@
         <v>1.86817544998933</v>
       </c>
       <c r="D339" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E339">
         <v>2.552327466291189</v>
@@ -18385,7 +18376,7 @@
         <v>3.297653300651016</v>
       </c>
       <c r="D340" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="E340">
         <v>2.080953383478715</v>
@@ -18421,7 +18412,7 @@
         <v>1</v>
       </c>
       <c r="P340" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="341" spans="1:16">
@@ -18471,7 +18462,7 @@
         <v>1</v>
       </c>
       <c r="P341" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="342" spans="1:16">
@@ -18485,7 +18476,7 @@
         <v>1.788826009252247</v>
       </c>
       <c r="D342" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E342">
         <v>2.524889696365481</v>
@@ -18521,7 +18512,7 @@
         <v>1</v>
       </c>
       <c r="P342" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="343" spans="1:16">
@@ -18535,7 +18526,7 @@
         <v>1.661450217843427</v>
       </c>
       <c r="D343" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E343">
         <v>2.524889696365481</v>
@@ -18571,7 +18562,7 @@
         <v>1</v>
       </c>
       <c r="P343" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="344" spans="1:16">
@@ -18585,7 +18576,7 @@
         <v>1.839899607409848</v>
       </c>
       <c r="D344" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E344">
         <v>2.524889696365481</v>
@@ -18621,7 +18612,7 @@
         <v>1</v>
       </c>
       <c r="P344" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="345" spans="1:16">
@@ -18635,7 +18626,7 @@
         <v>3.263703117123406</v>
       </c>
       <c r="D345" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="E345">
         <v>2.041921840245493</v>
@@ -18735,7 +18726,7 @@
         <v>1.743763841313463</v>
       </c>
       <c r="D347" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E347">
         <v>2.48284284077948</v>
@@ -18785,7 +18776,7 @@
         <v>1.614377841669459</v>
       </c>
       <c r="D348" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E348">
         <v>2.48284284077948</v>
@@ -18835,7 +18826,7 @@
         <v>1.796568452118031</v>
       </c>
       <c r="D349" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E349">
         <v>2.48284284077948</v>
@@ -18885,7 +18876,7 @@
         <v>3.242126022559422</v>
       </c>
       <c r="D350" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="E350">
         <v>2.017115279225386</v>
@@ -18921,7 +18912,7 @@
         <v>1</v>
       </c>
       <c r="P350" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="351" spans="1:16">
@@ -18971,7 +18962,7 @@
         <v>1</v>
       </c>
       <c r="P351" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="352" spans="1:16">
@@ -18985,7 +18976,7 @@
         <v>1.715124506916858</v>
       </c>
       <c r="D352" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E352">
         <v>2.456119893071122</v>
@@ -19021,7 +19012,7 @@
         <v>1</v>
       </c>
       <c r="P352" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="353" spans="1:16">
@@ -19035,7 +19026,7 @@
         <v>1.584460916147354</v>
       </c>
       <c r="D353" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E353">
         <v>2.456119893071122</v>
@@ -19071,7 +19062,7 @@
         <v>1</v>
       </c>
       <c r="P353" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="354" spans="1:16">
@@ -19085,7 +19076,7 @@
         <v>1.769029265635051</v>
       </c>
       <c r="D354" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E354">
         <v>2.456119893071122</v>
@@ -19121,7 +19112,7 @@
         <v>1</v>
       </c>
       <c r="P354" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="355" spans="1:16">
@@ -19135,7 +19126,7 @@
         <v>3.218796578894542</v>
       </c>
       <c r="D355" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="E355">
         <v>1.990294093169876</v>
@@ -19235,7 +19226,7 @@
         <v>1.684159274947191</v>
       </c>
       <c r="D357" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E357">
         <v>2.427226684058535</v>
@@ -19285,7 +19276,7 @@
         <v>1.552114335539635</v>
       </c>
       <c r="D358" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E358">
         <v>2.427226684058535</v>
@@ -19335,7 +19326,7 @@
         <v>1.739253528325928</v>
       </c>
       <c r="D359" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E359">
         <v>2.427226684058535</v>
@@ -19385,7 +19376,7 @@
         <v>3.223084813618858</v>
       </c>
       <c r="D360" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="E360">
         <v>1.995224152499308</v>
@@ -19421,7 +19412,7 @@
         <v>1</v>
       </c>
       <c r="P360" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="361" spans="1:16">
@@ -19435,7 +19426,7 @@
         <v>1.689851060181606</v>
       </c>
       <c r="D361" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E361">
         <v>2.432537606340457</v>
@@ -19471,7 +19462,7 @@
         <v>1</v>
       </c>
       <c r="P361" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="362" spans="1:16">
@@ -19485,7 +19476,7 @@
         <v>1.558060029409038</v>
       </c>
       <c r="D362" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E362">
         <v>2.432537606340457</v>
@@ -19521,7 +19512,7 @@
         <v>1</v>
       </c>
       <c r="P362" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="363" spans="1:16">
@@ -19535,7 +19526,7 @@
         <v>1.5546355793606</v>
       </c>
       <c r="D363" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E363">
         <v>2.429478755941318</v>
@@ -19585,7 +19576,7 @@
         <v>2.749895863416445</v>
       </c>
       <c r="D364" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="E364">
         <v>2.144120683335579</v>
@@ -19621,7 +19612,7 @@
         <v>1</v>
       </c>
       <c r="P364" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="365" spans="1:16">
@@ -19635,7 +19626,7 @@
         <v>1.575757316392718</v>
       </c>
       <c r="D365" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E365">
         <v>2.448345503254703</v>
@@ -19671,7 +19662,7 @@
         <v>1</v>
       </c>
       <c r="P365" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="366" spans="1:16">
@@ -19685,7 +19676,7 @@
         <v>1.708690594836302</v>
       </c>
       <c r="D366" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="E366">
         <v>1.95524223097577</v>
@@ -19721,7 +19712,7 @@
         <v>1</v>
       </c>
       <c r="P366" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="367" spans="1:16">
@@ -19735,7 +19726,7 @@
         <v>2.776972324350222</v>
       </c>
       <c r="D367" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="E367">
         <v>2.170167242074328</v>
@@ -19771,7 +19762,7 @@
         <v>1</v>
       </c>
       <c r="P367" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="368" spans="1:16">
@@ -19785,7 +19776,7 @@
         <v>1.603764011567165</v>
       </c>
       <c r="D368" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E368">
         <v>2.473362159798427</v>
@@ -19821,7 +19812,7 @@
         <v>1</v>
       </c>
       <c r="P368" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="369" spans="1:16">
@@ -19835,7 +19826,7 @@
         <v>1.733308579562596</v>
       </c>
       <c r="D369" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="E369">
         <v>2.069952921130998</v>
@@ -19871,7 +19862,7 @@
         <v>1</v>
       </c>
       <c r="P369" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="370" spans="1:16">
@@ -19885,7 +19876,7 @@
         <v>2.804318151096002</v>
       </c>
       <c r="D370" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="E370">
         <v>2.196472920808915</v>
@@ -19921,7 +19912,7 @@
         <v>1</v>
       </c>
       <c r="P370" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="371" spans="1:16">
@@ -19935,7 +19926,7 @@
         <v>1.632049326839176</v>
       </c>
       <c r="D371" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E371">
         <v>2.498627690521825</v>
@@ -19971,7 +19962,7 @@
         <v>1</v>
       </c>
       <c r="P371" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="372" spans="1:16">
@@ -19985,7 +19976,7 @@
         <v>1.758171472346181</v>
       </c>
       <c r="D372" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="E372">
         <v>2.648741745065742</v>
@@ -20021,7 +20012,7 @@
         <v>1</v>
       </c>
       <c r="P372" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="373" spans="1:16">
@@ -20035,7 +20026,7 @@
         <v>1.836308899819077</v>
       </c>
       <c r="D373" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E373">
         <v>2.387421432319158</v>
@@ -20071,7 +20062,7 @@
         <v>1</v>
       </c>
       <c r="P373" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="374" spans="1:16">
@@ -20121,7 +20112,7 @@
         <v>1</v>
       </c>
       <c r="P374" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="375" spans="1:16">
@@ -20135,7 +20126,7 @@
         <v>1.66686196794393</v>
       </c>
       <c r="D375" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E375">
         <v>2.529723679551338</v>
@@ -20171,7 +20162,7 @@
         <v>1</v>
       </c>
       <c r="P375" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="376" spans="1:16">
@@ -20185,7 +20176,7 @@
         <v>1.844881242140559</v>
       </c>
       <c r="D376" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E376">
         <v>2.529723679551338</v>
@@ -20221,7 +20212,7 @@
         <v>1</v>
       </c>
       <c r="P376" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="377" spans="1:16">
@@ -20235,7 +20226,7 @@
         <v>1.788771907765661</v>
       </c>
       <c r="D377" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="E377">
         <v>2.679961622497764</v>
@@ -20271,7 +20262,7 @@
         <v>1</v>
       </c>
       <c r="P377" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="378" spans="1:16">
@@ -20285,7 +20276,7 @@
         <v>1.861508767932467</v>
       </c>
       <c r="D378" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E378">
         <v>2.411732640096055</v>
@@ -20321,7 +20312,7 @@
         <v>1</v>
       </c>
       <c r="P378" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
     </row>
     <row r="379" spans="1:16">
@@ -20371,7 +20362,7 @@
         <v>1</v>
       </c>
       <c r="P379" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
     </row>
     <row r="380" spans="1:16">
@@ -20385,7 +20376,7 @@
         <v>1.693616991646184</v>
       </c>
       <c r="D380" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E380">
         <v>2.55362229502915</v>
@@ -20421,7 +20412,7 @@
         <v>1</v>
       </c>
       <c r="P380" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
     </row>
     <row r="381" spans="1:16">
@@ -20435,7 +20426,7 @@
         <v>1.869509828609061</v>
       </c>
       <c r="D381" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E381">
         <v>2.55362229502915</v>
@@ -20471,7 +20462,7 @@
         <v>1</v>
       </c>
       <c r="P381" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
     </row>
     <row r="382" spans="1:16">
@@ -20485,7 +20476,7 @@
         <v>2.574954921244757</v>
       </c>
       <c r="D382" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="E382">
         <v>2.17950982860906</v>
@@ -20521,7 +20512,7 @@
         <v>1</v>
       </c>
       <c r="P382" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
     </row>
     <row r="383" spans="1:16">
@@ -20535,7 +20526,7 @@
         <v>1.812289668813548</v>
       </c>
       <c r="D383" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="E383">
         <v>2.703955451583056</v>
@@ -20571,7 +20562,7 @@
         <v>1</v>
       </c>
       <c r="P383" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
     </row>
     <row r="384" spans="1:16">
@@ -20585,7 +20576,7 @@
         <v>1.878354735459471</v>
       </c>
       <c r="D384" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E384">
         <v>2.42798454327702</v>
@@ -20621,7 +20612,7 @@
         <v>1</v>
       </c>
       <c r="P384" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
     </row>
     <row r="385" spans="1:16">
@@ -20671,7 +20662,7 @@
         <v>1</v>
       </c>
       <c r="P385" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
     </row>
     <row r="386" spans="1:16">
@@ -20685,7 +20676,7 @@
         <v>1.711502571778759</v>
       </c>
       <c r="D386" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E386">
         <v>2.569598382620882</v>
@@ -20721,7 +20712,7 @@
         <v>1</v>
       </c>
       <c r="P386" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
     </row>
     <row r="387" spans="1:16">
@@ -20735,7 +20726,7 @@
         <v>1.885973897627895</v>
       </c>
       <c r="D387" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E387">
         <v>2.569598382620882</v>
@@ -20771,7 +20762,7 @@
         <v>1</v>
       </c>
       <c r="P387" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
     </row>
     <row r="388" spans="1:16">
@@ -20785,7 +20776,7 @@
         <v>2.591185607841933</v>
       </c>
       <c r="D388" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="E388">
         <v>2.195973897627894</v>
@@ -20821,7 +20812,7 @@
         <v>1</v>
       </c>
       <c r="P388" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
     </row>
     <row r="389" spans="1:16">
@@ -20835,7 +20826,7 @@
         <v>1.828011157399832</v>
       </c>
       <c r="D389" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="E389">
         <v>2.719995188926148</v>
@@ -20871,7 +20862,7 @@
         <v>1</v>
       </c>
       <c r="P389" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
     </row>
     <row r="390" spans="1:16">
@@ -20885,7 +20876,7 @@
         <v>1.884937981108568</v>
       </c>
       <c r="D390" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E390">
         <v>2.434335634167709</v>
@@ -20921,7 +20912,7 @@
         <v>1</v>
       </c>
       <c r="P390" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
     </row>
     <row r="391" spans="1:16">
@@ -20971,7 +20962,7 @@
         <v>1</v>
       </c>
       <c r="P391" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
     </row>
     <row r="392" spans="1:16">
@@ -20985,7 +20976,7 @@
         <v>1.718492088255065</v>
       </c>
       <c r="D392" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E392">
         <v>2.575841687373739</v>
@@ -21021,7 +21012,7 @@
         <v>1</v>
       </c>
       <c r="P392" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
     </row>
     <row r="393" spans="1:16">
@@ -21035,7 +21026,7 @@
         <v>1.892407900932305</v>
       </c>
       <c r="D393" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E393">
         <v>2.575841687373739</v>
@@ -21071,7 +21062,7 @@
         <v>1</v>
       </c>
       <c r="P393" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
     </row>
     <row r="394" spans="1:16">
@@ -21085,7 +21076,7 @@
         <v>1.834154967256232</v>
       </c>
       <c r="D394" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="E394">
         <v>2.726263367403121</v>
@@ -21121,7 +21112,7 @@
         <v>1</v>
       </c>
       <c r="P394" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
     </row>
     <row r="395" spans="1:16">
@@ -21135,7 +21126,7 @@
         <v>2.791624887079966</v>
       </c>
       <c r="D395" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="E395">
         <v>2.637829766815571</v>
@@ -21171,7 +21162,7 @@
         <v>1</v>
       </c>
       <c r="P395" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
     </row>
     <row r="396" spans="1:16">
@@ -21185,7 +21176,7 @@
         <v>1.897004594528006</v>
       </c>
       <c r="D396" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E396">
         <v>2.445976724695786</v>
@@ -21221,7 +21212,7 @@
         <v>1</v>
       </c>
       <c r="P396" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
     </row>
     <row r="397" spans="1:16">
@@ -21271,7 +21262,7 @@
         <v>1</v>
       </c>
       <c r="P397" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
     </row>
     <row r="398" spans="1:16">
@@ -21285,7 +21276,7 @@
         <v>1.731303366734398</v>
       </c>
       <c r="D398" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E398">
         <v>2.587285213702252</v>
@@ -21321,7 +21312,7 @@
         <v>1</v>
       </c>
       <c r="P398" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
     </row>
     <row r="399" spans="1:16">
@@ -21335,7 +21326,7 @@
         <v>1.904200963921582</v>
       </c>
       <c r="D399" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E399">
         <v>2.587285213702252</v>
@@ -21371,7 +21362,7 @@
         <v>1</v>
       </c>
       <c r="P399" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
     </row>
     <row r="400" spans="1:16">
@@ -21385,7 +21376,7 @@
         <v>1.845416126631299</v>
       </c>
       <c r="D400" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="E400">
         <v>2.737752485469994</v>
@@ -21421,7 +21412,7 @@
         <v>1</v>
       </c>
       <c r="P400" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
     </row>
     <row r="401" spans="1:16">
@@ -21435,7 +21426,7 @@
         <v>2.802612496024871</v>
       </c>
       <c r="D401" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="E401">
         <v>2.813453713263602</v>
@@ -21471,7 +21462,7 @@
         <v>1</v>
       </c>
       <c r="P401" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
     </row>
     <row r="402" spans="1:16">
@@ -21485,7 +21476,7 @@
         <v>1.915149243214803</v>
       </c>
       <c r="D402" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E402">
         <v>2.463481511716044</v>
@@ -21521,7 +21512,7 @@
         <v>1</v>
       </c>
       <c r="P402" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
     </row>
     <row r="403" spans="1:16">
@@ -21571,7 +21562,7 @@
         <v>1</v>
       </c>
       <c r="P403" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
     </row>
     <row r="404" spans="1:16">
@@ -21585,7 +21576,7 @@
         <v>1.750567773337632</v>
       </c>
       <c r="D404" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E404">
         <v>2.60449292209162</v>
@@ -21621,7 +21612,7 @@
         <v>1</v>
       </c>
       <c r="P404" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
     </row>
     <row r="405" spans="1:16">
@@ -21635,7 +21626,7 @@
         <v>1.921934272965604</v>
       </c>
       <c r="D405" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E405">
         <v>2.60449292209162</v>
@@ -21671,7 +21662,7 @@
         <v>1</v>
       </c>
       <c r="P405" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
     </row>
     <row r="406" spans="1:16">
@@ -21685,7 +21676,7 @@
         <v>1.862349608592151</v>
       </c>
       <c r="D406" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="E406">
         <v>2.75502875046649</v>
@@ -21721,7 +21712,7 @@
         <v>1</v>
       </c>
       <c r="P406" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
     </row>
     <row r="407" spans="1:16">
@@ -21735,7 +21726,7 @@
         <v>2.819134638342948</v>
       </c>
       <c r="D407" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="E407">
         <v>2.769730713091974</v>
@@ -21771,7 +21762,7 @@
         <v>1</v>
       </c>
       <c r="P407" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
     </row>
     <row r="408" spans="1:16">
@@ -21785,7 +21776,7 @@
         <v>1.92753511972947</v>
       </c>
       <c r="D408" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E408">
         <v>2.475430606691152</v>
@@ -21885,7 +21876,7 @@
         <v>1.76371801754653</v>
       </c>
       <c r="D410" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E410">
         <v>2.616239225637646</v>
@@ -21935,7 +21926,7 @@
         <v>1.934039361347697</v>
       </c>
       <c r="D411" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E411">
         <v>2.616239225637646</v>
@@ -21985,7 +21976,7 @@
         <v>1.873908720049794</v>
       </c>
       <c r="D412" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="E412">
         <v>2.766821852034614</v>
@@ -22035,7 +22026,7 @@
         <v>2.830412961668017</v>
       </c>
       <c r="D413" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="E413">
         <v>2.221708855759843</v>
@@ -22085,7 +22076,7 @@
         <v>1.937685341557977</v>
       </c>
       <c r="D414" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E414">
         <v>2.485222886188172</v>
@@ -22121,7 +22112,7 @@
         <v>1</v>
       </c>
       <c r="P414" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
     </row>
     <row r="415" spans="1:16">
@@ -22171,7 +22162,7 @@
         <v>1</v>
       </c>
       <c r="P415" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
     </row>
     <row r="416" spans="1:16">
@@ -22185,7 +22176,7 @@
         <v>1.774494638455131</v>
       </c>
       <c r="D416" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E416">
         <v>2.625865317623621</v>
@@ -22221,7 +22212,7 @@
         <v>1</v>
       </c>
       <c r="P416" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
     </row>
     <row r="417" spans="1:16">
@@ -22235,7 +22226,7 @@
         <v>1.943959477391676</v>
       </c>
       <c r="D417" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E417">
         <v>2.625865317623621</v>
@@ -22271,7 +22262,7 @@
         <v>1</v>
       </c>
       <c r="P417" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
     </row>
     <row r="418" spans="1:16">
@@ -22285,7 +22276,7 @@
         <v>1.883381408179421</v>
       </c>
       <c r="D418" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="E418">
         <v>2.776486294984675</v>
@@ -22321,7 +22312,7 @@
         <v>1</v>
       </c>
       <c r="P418" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
     </row>
     <row r="419" spans="1:16">
@@ -22335,7 +22326,7 @@
         <v>2.839655544013116</v>
       </c>
       <c r="D419" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="E419">
         <v>2.231475567947474</v>
@@ -22371,7 +22362,7 @@
         <v>1</v>
       </c>
       <c r="P419" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
     </row>
     <row r="420" spans="1:16">
@@ -22385,7 +22376,7 @@
         <v>1.950149148490695</v>
       </c>
       <c r="D420" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E420">
         <v>2.49724716340538</v>
@@ -22421,7 +22412,7 @@
         <v>1</v>
       </c>
       <c r="P420" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
     </row>
     <row r="421" spans="1:16">
@@ -22471,7 +22462,7 @@
         <v>1</v>
       </c>
       <c r="P421" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
     </row>
     <row r="422" spans="1:16">
@@ -22485,7 +22476,7 @@
         <v>1.787727622389998</v>
       </c>
       <c r="D422" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E422">
         <v>2.637685527472915</v>
@@ -22521,7 +22512,7 @@
         <v>1</v>
       </c>
       <c r="P422" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
     </row>
     <row r="423" spans="1:16">
@@ -22535,7 +22526,7 @@
         <v>1.956140729507283</v>
       </c>
       <c r="D423" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E423">
         <v>2.637685527472915</v>
@@ -22571,7 +22562,7 @@
         <v>1</v>
       </c>
       <c r="P423" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
     </row>
     <row r="424" spans="1:16">
@@ -22585,7 +22576,7 @@
         <v>1.895013248150637</v>
       </c>
       <c r="D424" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="E424">
         <v>2.788353597303487</v>
@@ -22621,7 +22612,7 @@
         <v>1</v>
       </c>
       <c r="P424" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
     </row>
     <row r="425" spans="1:16">
@@ -22635,7 +22626,7 @@
         <v>2.85100482916722</v>
       </c>
       <c r="D425" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="E425">
         <v>2.243468450185002</v>
@@ -22671,7 +22662,7 @@
         <v>1</v>
       </c>
       <c r="P425" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
     </row>
     <row r="426" spans="1:16">
@@ -22735,7 +22726,7 @@
         <v>1.796280604882195</v>
       </c>
       <c r="D427" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E427">
         <v>2.645325380161676</v>
@@ -22785,7 +22776,7 @@
         <v>1.964013937590256</v>
       </c>
       <c r="D428" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E428">
         <v>2.645325380161676</v>
@@ -22835,7 +22826,7 @@
         <v>1.902531350198938</v>
       </c>
       <c r="D429" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="E429">
         <v>2.796023887652364</v>
@@ -22885,7 +22876,7 @@
         <v>2.858340305254835</v>
       </c>
       <c r="D430" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="E430">
         <v>2.251219907627515</v>
@@ -22971,7 +22962,7 @@
         <v>1</v>
       </c>
       <c r="P431" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
     </row>
     <row r="432" spans="1:16">
@@ -22985,7 +22976,7 @@
         <v>1.81059278070445</v>
       </c>
       <c r="D432" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E432">
         <v>2.658109565682619</v>
@@ -23021,7 +23012,7 @@
         <v>1</v>
       </c>
       <c r="P432" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
     </row>
     <row r="433" spans="1:16">
@@ -23035,7 +23026,7 @@
         <v>1.977188609521534</v>
       </c>
       <c r="D433" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E433">
         <v>2.658109565682619</v>
@@ -23071,7 +23062,7 @@
         <v>1</v>
       </c>
       <c r="P433" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
     </row>
     <row r="434" spans="1:16">
@@ -23085,7 +23076,7 @@
         <v>1.915111803679711</v>
       </c>
       <c r="D434" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="E434">
         <v>2.808859006183351</v>
@@ -23121,7 +23112,7 @@
         <v>1</v>
       </c>
       <c r="P434" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
     </row>
     <row r="435" spans="1:16">
@@ -23135,7 +23126,7 @@
         <v>2.870615160675342</v>
       </c>
       <c r="D435" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="E435">
         <v>2.26419084751862</v>
@@ -23171,7 +23162,7 @@
         <v>1</v>
       </c>
       <c r="P435" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
     </row>
     <row r="436" spans="1:16">
@@ -23221,7 +23212,7 @@
         <v>1</v>
       </c>
       <c r="P436" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="437" spans="1:16">
@@ -23235,7 +23226,7 @@
         <v>1.82632056259726</v>
       </c>
       <c r="D437" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E437">
         <v>2.672158224953424</v>
@@ -23271,7 +23262,7 @@
         <v>1</v>
       </c>
       <c r="P437" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="438" spans="1:16">
@@ -23285,7 +23276,7 @@
         <v>1.991666377906849</v>
       </c>
       <c r="D438" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E438">
         <v>2.672158224953424</v>
@@ -23321,7 +23312,7 @@
         <v>1</v>
       </c>
       <c r="P438" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="439" spans="1:16">
@@ -23335,7 +23326,7 @@
         <v>1.928936579934245</v>
       </c>
       <c r="D439" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="E439">
         <v>2.822963636208222</v>
@@ -23371,7 +23362,7 @@
         <v>1</v>
       </c>
       <c r="P439" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="440" spans="1:16">
@@ -23385,7 +23376,7 @@
         <v>2.884104112405478</v>
       </c>
       <c r="D440" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="E440">
         <v>2.278444732887671</v>
@@ -23421,7 +23412,7 @@
         <v>1</v>
       </c>
       <c r="P440" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="441" spans="1:16">
@@ -23435,7 +23426,7 @@
         <v>1.850091985515281</v>
       </c>
       <c r="D441" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E441">
         <v>2.693391773538558</v>
@@ -23485,7 +23476,7 @@
         <v>2.013548494377055</v>
       </c>
       <c r="D442" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E442">
         <v>2.693391773538558</v>
@@ -23535,7 +23526,7 @@
         <v>1.949831745274995</v>
       </c>
       <c r="D443" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="E443">
         <v>2.844281780604454</v>
@@ -23585,7 +23576,7 @@
         <v>2.90449170287965</v>
       </c>
       <c r="D444" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="E444">
         <v>2.29998846611349</v>
@@ -23635,7 +23626,7 @@
         <v>1.883787347386825</v>
       </c>
       <c r="D445" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E445">
         <v>2.723489765815277</v>
@@ -23671,7 +23662,7 @@
         <v>1</v>
       </c>
       <c r="P445" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
     </row>
     <row r="446" spans="1:16">
@@ -23685,7 +23676,7 @@
         <v>2.044565814439117</v>
       </c>
       <c r="D446" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E446">
         <v>2.723489765815277</v>
@@ -23721,7 +23712,7 @@
         <v>1</v>
       </c>
       <c r="P446" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
     </row>
     <row r="447" spans="1:16">
@@ -23735,7 +23726,7 @@
         <v>2.74752944335815</v>
       </c>
       <c r="D447" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="E447">
         <v>2.354565814439116</v>
@@ -23771,7 +23762,7 @@
         <v>1</v>
       </c>
       <c r="P447" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
     </row>
     <row r="448" spans="1:16">
@@ -23785,7 +23776,7 @@
         <v>1.979450088272404</v>
       </c>
       <c r="D448" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="E448">
         <v>2.874499685200998</v>
@@ -23821,7 +23812,7 @@
         <v>1</v>
       </c>
       <c r="P448" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
     </row>
     <row r="449" spans="1:16">
@@ -23835,7 +23826,7 @@
         <v>2.933390571958093</v>
       </c>
       <c r="D449" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="E449">
         <v>2.330526136896243</v>
@@ -23871,7 +23862,7 @@
         <v>1</v>
       </c>
       <c r="P449" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
     </row>
     <row r="450" spans="1:16">
@@ -23921,7 +23912,7 @@
         <v>1</v>
       </c>
       <c r="P450" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
     </row>
     <row r="451" spans="1:16">
@@ -23935,7 +23926,7 @@
         <v>1.920897553279229</v>
       </c>
       <c r="D451" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E451">
         <v>2.756638028018099</v>
@@ -23971,7 +23962,7 @@
         <v>1</v>
       </c>
       <c r="P451" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
     </row>
     <row r="452" spans="1:16">
@@ -23985,7 +23976,7 @@
         <v>2.078726573362612</v>
       </c>
       <c r="D452" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E452">
         <v>2.756638028018099</v>
@@ -24021,7 +24012,7 @@
         <v>1</v>
       </c>
       <c r="P452" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
     </row>
     <row r="453" spans="1:16">
@@ -24035,7 +24026,7 @@
         <v>2.012070091316616</v>
       </c>
       <c r="D453" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="E453">
         <v>2.907780012193474</v>
@@ -24071,7 +24062,7 @@
         <v>1</v>
       </c>
       <c r="P453" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
     </row>
     <row r="454" spans="1:16">
@@ -24085,7 +24076,7 @@
         <v>2.965218186264387</v>
       </c>
       <c r="D454" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="E454">
         <v>2.364158636661127</v>
@@ -24121,7 +24112,7 @@
         <v>1</v>
       </c>
       <c r="P454" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
     </row>
     <row r="455" spans="1:16">
@@ -24135,7 +24126,7 @@
         <v>1.971362962924253</v>
       </c>
       <c r="D455" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E455">
         <v>2.801715671508852</v>
@@ -24185,7 +24176,7 @@
         <v>2.125181090426125</v>
       </c>
       <c r="D456" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E456">
         <v>2.801715671508852</v>
@@ -24235,7 +24226,7 @@
         <v>2.056429365986798</v>
       </c>
       <c r="D457" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="E457">
         <v>2.95303724788937</v>
@@ -24285,7 +24276,7 @@
         <v>3.008499907703719</v>
       </c>
       <c r="D458" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="E458">
         <v>2.409894784904068</v>
@@ -24335,7 +24326,7 @@
         <v>2.008171638992437</v>
       </c>
       <c r="D459" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E459">
         <v>2.834594595683633</v>
@@ -24371,7 +24362,7 @@
         <v>1</v>
       </c>
       <c r="P459" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="460" spans="1:16">
@@ -24385,7 +24376,7 @@
         <v>2.159064284529219</v>
       </c>
       <c r="D460" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E460">
         <v>2.834594595683633</v>
@@ -24421,7 +24412,7 @@
         <v>1</v>
       </c>
       <c r="P460" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="461" spans="1:16">
@@ -24435,7 +24426,7 @@
         <v>2.088784323242461</v>
       </c>
       <c r="D461" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="E461">
         <v>2.986047163793931</v>
@@ -24471,7 +24462,7 @@
         <v>1</v>
       </c>
       <c r="P461" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="462" spans="1:16">
@@ -24485,7 +24476,7 @@
         <v>3.040068914580697</v>
       </c>
       <c r="D462" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="E462">
         <v>2.443254012088044</v>
@@ -24521,7 +24512,7 @@
         <v>1</v>
       </c>
       <c r="P462" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="463" spans="1:16">
@@ -24535,7 +24526,7 @@
         <v>2.067700645146257</v>
       </c>
       <c r="D463" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E463">
         <v>2.887768191927794</v>
@@ -24585,7 +24576,7 @@
         <v>2.213862041083626</v>
       </c>
       <c r="D464" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E464">
         <v>2.887768191927794</v>
@@ -24635,7 +24626,7 @@
         <v>2.914425852356924</v>
       </c>
       <c r="D465" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="E465">
         <v>2.523862041083625</v>
@@ -24685,7 +24676,7 @@
         <v>2.141110531498665</v>
       </c>
       <c r="D466" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="E466">
         <v>3.039432607035081</v>
@@ -24735,7 +24726,7 @@
         <v>3.091124040854972</v>
       </c>
       <c r="D467" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="E467">
         <v>2.497204380654495</v>
@@ -24785,7 +24776,7 @@
         <v>2.102053433035913</v>
       </c>
       <c r="D468" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E468">
         <v>2.918453422391508</v>
@@ -24821,7 +24812,7 @@
         <v>1</v>
       </c>
       <c r="P468" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="469" spans="1:16">
@@ -24835,7 +24826,7 @@
         <v>2.245484536222857</v>
       </c>
       <c r="D469" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E469">
         <v>2.918453422391508</v>
@@ -24871,7 +24862,7 @@
         <v>1</v>
       </c>
       <c r="P469" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="470" spans="1:16">
@@ -24885,7 +24876,7 @@
         <v>2.945600090477427</v>
       </c>
       <c r="D470" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="E470">
         <v>2.555484536222856</v>
@@ -24921,7 +24912,7 @@
         <v>1</v>
       </c>
       <c r="P470" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="471" spans="1:16">
@@ -24935,7 +24926,7 @@
         <v>2.171306754305586</v>
       </c>
       <c r="D471" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="E471">
         <v>3.070240089412991</v>
@@ -24971,7 +24962,7 @@
         <v>1</v>
       </c>
       <c r="P471" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="472" spans="1:16">
@@ -24985,7 +24976,7 @@
         <v>3.120586752176706</v>
       </c>
       <c r="D472" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="E472">
         <v>2.528337868136934</v>
@@ -25021,7 +25012,7 @@
         <v>1</v>
       </c>
       <c r="P472" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="473" spans="1:16">
@@ -25035,7 +25026,7 @@
         <v>2.150109762840597</v>
       </c>
       <c r="D473" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E473">
         <v>2.961379183177897</v>
@@ -25071,7 +25062,7 @@
         <v>1</v>
       </c>
       <c r="P473" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
     </row>
     <row r="474" spans="1:16">
@@ -25085,7 +25076,7 @@
         <v>2.289721442425034</v>
       </c>
       <c r="D474" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E474">
         <v>2.961379183177897</v>
@@ -25121,7 +25112,7 @@
         <v>1</v>
       </c>
       <c r="P474" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
     </row>
     <row r="475" spans="1:16">
@@ -25135,7 +25126,7 @@
         <v>2.989209927132926</v>
       </c>
       <c r="D475" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="E475">
         <v>2.599721442425032</v>
@@ -25171,7 +25162,7 @@
         <v>1</v>
       </c>
       <c r="P475" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
     </row>
     <row r="476" spans="1:16">
@@ -25185,7 +25176,7 @@
         <v>2.213548439222873</v>
       </c>
       <c r="D476" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="E476">
         <v>3.113336869166659</v>
@@ -25221,7 +25212,7 @@
         <v>1</v>
       </c>
       <c r="P476" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
     </row>
     <row r="477" spans="1:16">
@@ -25235,7 +25226,7 @@
         <v>3.161802323290331</v>
       </c>
       <c r="D477" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="E477">
         <v>2.571890698470007</v>
@@ -25271,7 +25262,7 @@
         <v>1</v>
       </c>
       <c r="P477" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
     </row>
     <row r="478" spans="1:16">
@@ -25285,7 +25276,7 @@
         <v>2.189716387261424</v>
       </c>
       <c r="D478" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E478">
         <v>2.99675734235807</v>
@@ -25335,7 +25326,7 @@
         <v>2.326180209388927</v>
       </c>
       <c r="D479" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E479">
         <v>2.99675734235807</v>
@@ -25385,7 +25376,7 @@
         <v>2.248362803037622</v>
       </c>
       <c r="D480" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="E480">
         <v>3.148855977188184</v>
@@ -25435,7 +25426,7 @@
         <v>3.19577099405695</v>
       </c>
       <c r="D481" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="E481">
         <v>2.607785670068477</v>
@@ -25485,7 +25476,7 @@
         <v>2.215826782258592</v>
       </c>
       <c r="D482" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E482">
         <v>3.020080150700736</v>
@@ -25521,7 +25512,7 @@
         <v>1</v>
       </c>
       <c r="P482" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="483" spans="1:16">
@@ -25535,7 +25526,7 @@
         <v>2.350215400987747</v>
       </c>
       <c r="D483" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E483">
         <v>3.020080150700736</v>
@@ -25571,7 +25562,7 @@
         <v>1</v>
       </c>
       <c r="P483" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="484" spans="1:16">
@@ -25585,7 +25576,7 @@
         <v>2.271313933159689</v>
       </c>
       <c r="D484" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="E484">
         <v>3.172271705086001</v>
@@ -25621,7 +25612,7 @@
         <v>1</v>
       </c>
       <c r="P484" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="485" spans="1:16">
@@ -25635,7 +25626,7 @@
         <v>3.218164606848116</v>
       </c>
       <c r="D485" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="E485">
         <v>2.631449183446694</v>
@@ -25671,7 +25662,7 @@
         <v>1</v>
       </c>
       <c r="P485" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="486" spans="1:16">
@@ -25721,7 +25712,7 @@
         <v>1</v>
       </c>
       <c r="P486" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="487" spans="1:16">
@@ -25735,7 +25726,7 @@
         <v>2.227304742320833</v>
       </c>
       <c r="D487" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E487">
         <v>3.030332705774125</v>
@@ -25771,7 +25762,7 @@
         <v>1</v>
       </c>
       <c r="P487" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
     </row>
     <row r="488" spans="1:16">
@@ -25785,7 +25776,7 @@
         <v>2.360781115113841</v>
       </c>
       <c r="D488" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E488">
         <v>3.030332705774125</v>
@@ -25821,7 +25812,7 @@
         <v>1</v>
       </c>
       <c r="P488" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
     </row>
     <row r="489" spans="1:16">
@@ -25835,7 +25826,7 @@
         <v>2.28140310090123</v>
       </c>
       <c r="D489" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="E489">
         <v>3.182565106992353</v>
@@ -25871,7 +25862,7 @@
         <v>1</v>
       </c>
       <c r="P489" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
     </row>
     <row r="490" spans="1:16">
@@ -25885,7 +25876,7 @@
         <v>3.228008693591889</v>
       </c>
       <c r="D490" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="E490">
         <v>2.641851510240944</v>
@@ -25921,7 +25912,7 @@
         <v>1</v>
       </c>
       <c r="P490" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
     </row>
     <row r="491" spans="1:16">
@@ -25935,7 +25926,7 @@
         <v>2.326764722017106</v>
       </c>
       <c r="D491" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="E491">
         <v>2.338905512271317</v>
@@ -25971,7 +25962,7 @@
         <v>1</v>
       </c>
       <c r="P491" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
     </row>
     <row r="492" spans="1:16">
@@ -25985,7 +25976,7 @@
         <v>2.245345573811253</v>
       </c>
       <c r="D492" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E492">
         <v>3.046447469845635</v>
@@ -26021,7 +26012,7 @@
         <v>1</v>
       </c>
       <c r="P492" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
     </row>
     <row r="493" spans="1:16">
@@ -26035,7 +26026,7 @@
         <v>2.377388096414631</v>
       </c>
       <c r="D493" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E493">
         <v>3.046447469845635</v>
@@ -26071,7 +26062,7 @@
         <v>1</v>
       </c>
       <c r="P493" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
     </row>
     <row r="494" spans="1:16">
@@ -26085,7 +26076,7 @@
         <v>2.297261055983554</v>
       </c>
       <c r="D494" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="E494">
         <v>3.198744073311161</v>
@@ -26121,7 +26112,7 @@
         <v>1</v>
       </c>
       <c r="P494" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
     </row>
     <row r="495" spans="1:16">
@@ -26135,7 +26126,7 @@
         <v>3.243481435190432</v>
       </c>
       <c r="D495" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="E495">
         <v>2.658201682552544</v>
@@ -26171,7 +26162,7 @@
         <v>1</v>
       </c>
       <c r="P495" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
     </row>
     <row r="496" spans="1:16">
@@ -26221,7 +26212,7 @@
         <v>1</v>
       </c>
       <c r="P496" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
     </row>
     <row r="497" spans="1:16">
@@ -26235,7 +26226,7 @@
         <v>2.301170929293026</v>
       </c>
       <c r="D497" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="E497">
         <v>3.202733093853617</v>
@@ -26285,7 +26276,7 @@
         <v>3.247296331820319</v>
       </c>
       <c r="D498" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="E498">
         <v>2.662232914952593</v>
@@ -26385,7 +26376,7 @@
         <v>2.309276220482282</v>
       </c>
       <c r="D500" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="E500">
         <v>3.211002459763304</v>
@@ -26421,7 +26412,7 @@
         <v>1</v>
       </c>
       <c r="P500" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="501" spans="1:16">
@@ -26435,7 +26426,7 @@
         <v>3.25520473334506</v>
       </c>
       <c r="D501" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="E501">
         <v>2.670589787379843</v>
@@ -26471,7 +26462,7 @@
         <v>1</v>
       </c>
       <c r="P501" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="502" spans="1:16">
@@ -26485,7 +26476,7 @@
         <v>2.35659384998981</v>
       </c>
       <c r="D502" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="E502">
         <v>2.377701080695644</v>
@@ -26521,7 +26512,7 @@
         <v>1</v>
       </c>
       <c r="P502" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="503" spans="1:16">
@@ -26535,7 +26526,7 @@
         <v>2.318802840630408</v>
       </c>
       <c r="D503" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="E503">
         <v>3.220721926473129</v>
@@ -26585,7 +26576,7 @@
         <v>3.264499937619139</v>
       </c>
       <c r="D504" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="E504">
         <v>2.680412105589244</v>
@@ -26735,7 +26726,7 @@
         <v>2.968469110715926</v>
       </c>
       <c r="D507" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="E507">
         <v>3.65607053595874</v>
@@ -26771,7 +26762,7 @@
         <v>1</v>
       </c>
       <c r="P507" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="508" spans="1:16">
@@ -26785,7 +26776,7 @@
         <v>3.056098677724048</v>
       </c>
       <c r="D508" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="E508">
         <v>3.65607053595874</v>
@@ -26821,7 +26812,7 @@
         <v>1</v>
       </c>
       <c r="P508" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="509" spans="1:16">
@@ -26835,7 +26826,7 @@
         <v>3.085552267926261</v>
       </c>
       <c r="D509" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="E509">
         <v>3.65607053595874</v>
@@ -26871,7 +26862,7 @@
         <v>1</v>
       </c>
       <c r="P509" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="510" spans="1:16">
@@ -26885,7 +26876,7 @@
         <v>3.115403587495276</v>
       </c>
       <c r="D510" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="E510">
         <v>4.899694426383849</v>
@@ -26921,7 +26912,7 @@
         <v>1</v>
       </c>
       <c r="P510" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="511" spans="1:16">
@@ -26935,7 +26926,7 @@
         <v>2.857657467623699</v>
       </c>
       <c r="D511" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="E511">
         <v>4.899694426383849</v>
@@ -26971,7 +26962,7 @@
         <v>1</v>
       </c>
       <c r="P511" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="512" spans="1:16">
@@ -26985,7 +26976,7 @@
         <v>4.634833021734408</v>
       </c>
       <c r="D512" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="E512">
         <v>3.48240231940969</v>
@@ -27021,7 +27012,7 @@
         <v>1</v>
       </c>
       <c r="P512" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="513" spans="1:16">
@@ -27035,7 +27026,7 @@
         <v>3.013404560606677</v>
       </c>
       <c r="D513" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="E513">
         <v>3.707166946903694</v>
@@ -27071,7 +27062,7 @@
         <v>1</v>
       </c>
       <c r="P513" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="514" spans="1:16">
@@ -27085,7 +27076,7 @@
         <v>3.101938488870459</v>
       </c>
       <c r="D514" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="E514">
         <v>3.707166946903694</v>
@@ -27121,7 +27112,7 @@
         <v>1</v>
       </c>
       <c r="P514" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="515" spans="1:16">
@@ -27135,7 +27126,7 @@
         <v>3.133031233848563</v>
       </c>
       <c r="D515" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="E515">
         <v>3.707166946903694</v>
@@ -27171,7 +27162,7 @@
         <v>1</v>
       </c>
       <c r="P515" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="516" spans="1:16">
@@ -27185,7 +27176,7 @@
         <v>2.923647577997855</v>
       </c>
       <c r="D516" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="E516">
         <v>4.966814988327585</v>
@@ -27221,7 +27212,7 @@
         <v>1</v>
       </c>
       <c r="P516" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="517" spans="1:16">
@@ -27235,7 +27226,7 @@
         <v>4.706192777064061</v>
       </c>
       <c r="D517" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="E517">
         <v>3.555881671432303</v>
@@ -27271,7 +27262,7 @@
         <v>1</v>
       </c>
       <c r="P517" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="518" spans="1:16">
@@ -27285,7 +27276,7 @@
         <v>3.058294813446018</v>
       </c>
       <c r="D518" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="E518">
         <v>3.758211963968808</v>
@@ -27321,7 +27312,7 @@
         <v>1</v>
       </c>
       <c r="P518" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
     </row>
     <row r="519" spans="1:16">
@@ -27335,7 +27326,7 @@
         <v>3.147732193339273</v>
       </c>
       <c r="D519" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="E519">
         <v>3.758211963968808</v>
@@ -27371,7 +27362,7 @@
         <v>1</v>
       </c>
       <c r="P519" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
     </row>
     <row r="520" spans="1:16">
@@ -27385,7 +27376,7 @@
         <v>3.18046244439579</v>
       </c>
       <c r="D520" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="E520">
         <v>3.758211963968808</v>
@@ -27421,7 +27412,7 @@
         <v>1</v>
       </c>
       <c r="P520" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
     </row>
     <row r="521" spans="1:16">
@@ -27435,7 +27426,7 @@
         <v>3.225680173488445</v>
       </c>
       <c r="D521" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="E521">
         <v>5.033868038952384</v>
@@ -27471,7 +27462,7 @@
         <v>1</v>
       </c>
       <c r="P521" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
     </row>
     <row r="522" spans="1:16">
@@ -27485,7 +27476,7 @@
         <v>2.989571314085818</v>
       </c>
       <c r="D522" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="E522">
         <v>5.033868038952384</v>
@@ -27521,7 +27512,7 @@
         <v>1</v>
       </c>
       <c r="P522" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
     </row>
     <row r="523" spans="1:16">
@@ -27535,7 +27526,7 @@
         <v>4.77748075720201</v>
       </c>
       <c r="D523" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="E523">
         <v>3.629287116326825</v>
@@ -27571,7 +27562,7 @@
         <v>1</v>
       </c>
       <c r="P523" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
     </row>
     <row r="524" spans="1:16">
@@ -27585,7 +27576,7 @@
         <v>3.100990526217007</v>
       </c>
       <c r="D524" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="E524">
         <v>5.097643081613452</v>
@@ -27621,7 +27612,7 @@
         <v>1</v>
       </c>
       <c r="P524" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
     </row>
     <row r="525" spans="1:16">
@@ -27635,7 +27626,7 @@
         <v>3.19128719089559</v>
       </c>
       <c r="D525" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="E525">
         <v>5.097643081613452</v>
@@ -27671,7 +27662,7 @@
         <v>1</v>
       </c>
       <c r="P525" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
     </row>
     <row r="526" spans="1:16">
@@ -27685,7 +27676,7 @@
         <v>3.225574895625517</v>
       </c>
       <c r="D526" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="E526">
         <v>5.097643081613452</v>
@@ -27721,7 +27712,7 @@
         <v>1</v>
       </c>
       <c r="P526" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
     </row>
     <row r="527" spans="1:16">
@@ -27735,7 +27726,7 @@
         <v>3.205781960817575</v>
       </c>
       <c r="D527" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="E527">
         <v>5.097643081613452</v>
@@ -27771,7 +27762,7 @@
         <v>1</v>
       </c>
       <c r="P527" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
     </row>
     <row r="528" spans="1:16">
@@ -27785,7 +27776,7 @@
         <v>3.27809654539346</v>
       </c>
       <c r="D528" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="E528">
         <v>5.097643081613452</v>
@@ -27821,7 +27812,7 @@
         <v>1</v>
       </c>
       <c r="P528" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
     </row>
     <row r="529" spans="1:16">
@@ -27835,7 +27826,7 @@
         <v>3.052272250765228</v>
       </c>
       <c r="D529" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="E529">
         <v>5.097643081613452</v>
@@ -27871,7 +27862,7 @@
         <v>1</v>
       </c>
       <c r="P529" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
     </row>
     <row r="530" spans="1:16">
@@ -27885,7 +27876,7 @@
         <v>4.845283697294303</v>
       </c>
       <c r="D530" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="E530">
         <v>3.699104005134728</v>
@@ -27921,7 +27912,7 @@
         <v>1</v>
       </c>
       <c r="P530" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
     </row>
     <row r="531" spans="1:16">
@@ -27935,7 +27926,7 @@
         <v>3.135431759672713</v>
       </c>
       <c r="D531" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="E531">
         <v>5.149088320265843</v>
@@ -27971,7 +27962,7 @@
         <v>1</v>
       </c>
       <c r="P531" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
     </row>
     <row r="532" spans="1:16">
@@ -27985,7 +27976,7 @@
         <v>3.226421581251035</v>
       </c>
       <c r="D532" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="E532">
         <v>5.149088320265843</v>
@@ -28021,7 +28012,7 @@
         <v>1</v>
       </c>
       <c r="P532" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
     </row>
     <row r="533" spans="1:16">
@@ -28035,7 +28026,7 @@
         <v>3.261965632861735</v>
       </c>
       <c r="D533" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="E533">
         <v>5.149088320265843</v>
@@ -28071,7 +28062,7 @@
         <v>1</v>
       </c>
       <c r="P533" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
     </row>
     <row r="534" spans="1:16">
@@ -28085,7 +28076,7 @@
         <v>3.248497754763896</v>
       </c>
       <c r="D534" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="E534">
         <v>5.149088320265843</v>
@@ -28121,7 +28112,7 @@
         <v>1</v>
       </c>
       <c r="P534" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
     </row>
     <row r="535" spans="1:16">
@@ -28135,7 +28126,7 @@
         <v>3.320379116277444</v>
       </c>
       <c r="D535" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="E535">
         <v>5.149088320265843</v>
@@ -28171,7 +28162,7 @@
         <v>1</v>
       </c>
       <c r="P535" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
     </row>
     <row r="536" spans="1:16">
@@ -28185,7 +28176,7 @@
         <v>3.102851043292947</v>
       </c>
       <c r="D536" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="E536">
         <v>5.149088320265843</v>
@@ -28221,7 +28212,7 @@
         <v>1</v>
       </c>
       <c r="P536" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
     </row>
     <row r="537" spans="1:16">
@@ -28235,7 +28226,7 @@
         <v>4.899978108914215</v>
       </c>
       <c r="D537" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="E537">
         <v>3.755423003238402</v>
@@ -28271,7 +28262,7 @@
         <v>1</v>
       </c>
       <c r="P537" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
     </row>
     <row r="538" spans="1:16">
@@ -28285,7 +28276,7 @@
         <v>3.340758667101504</v>
       </c>
       <c r="D538" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="E538">
         <v>5.455787317211367</v>
@@ -28321,7 +28312,7 @@
         <v>1</v>
       </c>
       <c r="P538" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
     </row>
     <row r="539" spans="1:16">
@@ -28335,7 +28326,7 @@
         <v>3.596337846972439</v>
       </c>
       <c r="D539" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="E539">
         <v>5.455787317211367</v>
@@ -28371,7 +28362,7 @@
         <v>1</v>
       </c>
       <c r="P539" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
     </row>
     <row r="540" spans="1:16">
@@ -28385,7 +28376,7 @@
         <v>3.478914818069512</v>
       </c>
       <c r="D540" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="E540">
         <v>5.455787317211367</v>
@@ -28421,7 +28412,7 @@
         <v>1</v>
       </c>
       <c r="P540" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
     </row>
     <row r="541" spans="1:16">
@@ -28435,7 +28426,7 @@
         <v>3.503154774543503</v>
       </c>
       <c r="D541" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="E541">
         <v>5.455787317211367</v>
@@ -28471,7 +28462,7 @@
         <v>1</v>
       </c>
       <c r="P541" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
     </row>
     <row r="542" spans="1:16">
@@ -28485,7 +28476,7 @@
         <v>3.572453407661722</v>
       </c>
       <c r="D542" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="E542">
         <v>5.455787317211367</v>
@@ -28521,7 +28512,7 @@
         <v>1</v>
       </c>
       <c r="P542" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
     </row>
     <row r="543" spans="1:16">
@@ -28535,7 +28526,7 @@
         <v>3.404384583447808</v>
       </c>
       <c r="D543" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="E543">
         <v>5.455787317211367</v>
@@ -28571,7 +28562,7 @@
         <v>1</v>
       </c>
       <c r="P543" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
     </row>
     <row r="544" spans="1:16">
@@ -28585,7 +28576,7 @@
         <v>5.25250104043668</v>
       </c>
       <c r="D544" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="E544">
         <v>5.56320240731846</v>
@@ -28621,7 +28612,7 @@
         <v>1</v>
       </c>
       <c r="P544" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
     </row>
     <row r="545" spans="1:16">
@@ -28635,7 +28626,7 @@
         <v>3.408744253943432</v>
       </c>
       <c r="D545" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="E545">
         <v>5.557338115167074</v>
@@ -28671,7 +28662,7 @@
         <v>1</v>
       </c>
       <c r="P545" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
     </row>
     <row r="546" spans="1:16">
@@ -28685,7 +28676,7 @@
         <v>3.550748645676077</v>
       </c>
       <c r="D546" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="E546">
         <v>5.557338115167074</v>
@@ -28721,7 +28712,7 @@
         <v>1</v>
       </c>
       <c r="P546" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
     </row>
     <row r="547" spans="1:16">
@@ -28735,7 +28726,7 @@
         <v>3.587474005519777</v>
       </c>
       <c r="D547" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="E547">
         <v>5.557338115167074</v>
@@ -28771,7 +28762,7 @@
         <v>1</v>
       </c>
       <c r="P547" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
     </row>
     <row r="548" spans="1:16">
@@ -28785,7 +28776,7 @@
         <v>3.655917474023632</v>
       </c>
       <c r="D548" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="E548">
         <v>5.557338115167074</v>
@@ -28821,7 +28812,7 @@
         <v>1</v>
       </c>
       <c r="P548" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
     </row>
     <row r="549" spans="1:16">
@@ -28835,7 +28826,7 @@
         <v>3.504225052174785</v>
       </c>
       <c r="D549" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="E549">
         <v>5.557338115167074</v>
@@ -28871,7 +28862,7 @@
         <v>1</v>
       </c>
       <c r="P549" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
     </row>
     <row r="550" spans="1:16">
@@ -28885,7 +28876,7 @@
         <v>5.346996730323884</v>
       </c>
       <c r="D550" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="E550">
         <v>5.864438002961421</v>
@@ -28921,7 +28912,7 @@
         <v>1</v>
       </c>
       <c r="P550" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
     </row>
     <row r="551" spans="1:16">
@@ -28935,7 +28926,7 @@
         <v>5.267444590560391</v>
       </c>
       <c r="D551" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="E551">
         <v>5.864438002961421</v>
@@ -28971,7 +28962,7 @@
         <v>1</v>
       </c>
       <c r="P551" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
     </row>
     <row r="552" spans="1:16">
@@ -28985,7 +28976,7 @@
         <v>3.796322429340982</v>
       </c>
       <c r="D552" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="E552">
         <v>5.685955718590687</v>
@@ -29021,7 +29012,7 @@
         <v>1</v>
       </c>
       <c r="P552" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
     </row>
     <row r="553" spans="1:16">
@@ -29035,7 +29026,7 @@
         <v>3.641728676729411</v>
       </c>
       <c r="D553" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="E553">
         <v>5.685955718590687</v>
@@ -29071,7 +29062,7 @@
         <v>1</v>
       </c>
       <c r="P553" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
     </row>
     <row r="554" spans="1:16">
@@ -29085,7 +29076,7 @@
         <v>3.69426723244667</v>
       </c>
       <c r="D554" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="E554">
         <v>5.685955718590687</v>
@@ -29121,7 +29112,7 @@
         <v>1</v>
       </c>
       <c r="P554" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
     </row>
     <row r="555" spans="1:16">
@@ -29135,7 +29126,7 @@
         <v>3.761627605342749</v>
       </c>
       <c r="D555" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="E555">
         <v>5.685955718590687</v>
@@ -29171,7 +29162,7 @@
         <v>1</v>
       </c>
       <c r="P555" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
     </row>
     <row r="556" spans="1:16">
@@ -29185,7 +29176,7 @@
         <v>3.630676464382844</v>
       </c>
       <c r="D556" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="E556">
         <v>5.685955718590687</v>
@@ -29221,7 +29212,7 @@
         <v>1</v>
       </c>
       <c r="P556" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
     </row>
     <row r="557" spans="1:16">
@@ -29235,7 +29226,7 @@
         <v>5.466678794983334</v>
       </c>
       <c r="D557" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="E557">
         <v>5.209318422087254</v>
@@ -29271,7 +29262,7 @@
         <v>1</v>
       </c>
       <c r="P557" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
     </row>
     <row r="558" spans="1:16">
@@ -29285,7 +29276,7 @@
         <v>5.390917489847062</v>
       </c>
       <c r="D558" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="E558">
         <v>5.209318422087254</v>
@@ -29321,7 +29312,7 @@
         <v>1</v>
       </c>
       <c r="P558" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
     </row>
     <row r="559" spans="1:16">
@@ -29335,7 +29326,7 @@
         <v>4.159051079599863</v>
       </c>
       <c r="D559" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="E559">
         <v>5.343391662540899</v>
@@ -29371,7 +29362,7 @@
         <v>1</v>
       </c>
       <c r="P559" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
     </row>
     <row r="560" spans="1:16">
@@ -29385,7 +29376,7 @@
         <v>4.237780255555339</v>
       </c>
       <c r="D560" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E560">
         <v>5.313343652467495</v>
@@ -29421,7 +29412,7 @@
         <v>1</v>
       </c>
       <c r="P560" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
     </row>
     <row r="561" spans="1:16">
@@ -29435,7 +29426,7 @@
         <v>4.283295642394084</v>
       </c>
       <c r="D561" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E561">
         <v>5.313343652467495</v>
@@ -29471,7 +29462,7 @@
         <v>1</v>
       </c>
       <c r="P561" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
     </row>
     <row r="562" spans="1:16">
@@ -29521,7 +29512,7 @@
         <v>1</v>
       </c>
       <c r="P562" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
     </row>
     <row r="563" spans="1:16">
@@ -29535,7 +29526,7 @@
         <v>4.047954928502808</v>
       </c>
       <c r="D563" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="E563">
         <v>5.235960539108905</v>
@@ -29571,7 +29562,7 @@
         <v>1</v>
       </c>
       <c r="P563" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
     </row>
     <row r="564" spans="1:16">
@@ -29585,7 +29576,7 @@
         <v>4.137221058995326</v>
       </c>
       <c r="D564" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E564">
         <v>5.202705629828571</v>
@@ -29621,7 +29612,7 @@
         <v>1</v>
       </c>
       <c r="P564" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
     </row>
     <row r="565" spans="1:16">
@@ -29635,7 +29626,7 @@
         <v>4.169450720548237</v>
       </c>
       <c r="D565" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E565">
         <v>5.202705629828571</v>
@@ -29671,7 +29662,7 @@
         <v>1</v>
       </c>
       <c r="P565" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
     </row>
     <row r="566" spans="1:16">
@@ -29685,7 +29676,7 @@
         <v>6.314817655301979</v>
       </c>
       <c r="D566" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="E566">
         <v>6.624319057953503</v>
@@ -29721,7 +29712,7 @@
         <v>1</v>
       </c>
       <c r="P566" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
     </row>
     <row r="567" spans="1:16">
@@ -29735,7 +29726,7 @@
         <v>4.059730080999771</v>
       </c>
       <c r="D567" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E567">
         <v>5.117447902330046</v>
@@ -29785,7 +29776,7 @@
         <v>4.081721754571493</v>
       </c>
       <c r="D568" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E568">
         <v>5.117447902330046</v>
@@ -29885,7 +29876,7 @@
         <v>4.030557457706422</v>
       </c>
       <c r="D570" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E570">
         <v>5.085351371462874</v>
@@ -29921,7 +29912,7 @@
         <v>1</v>
       </c>
       <c r="P570" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="571" spans="1:16">
@@ -29935,7 +29926,7 @@
         <v>4.048694889476288</v>
       </c>
       <c r="D571" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E571">
         <v>5.085351371462874</v>
@@ -29971,7 +29962,7 @@
         <v>1</v>
       </c>
       <c r="P571" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="572" spans="1:16">
@@ -30021,7 +30012,7 @@
         <v>1</v>
       </c>
       <c r="P572" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="573" spans="1:16">
@@ -30035,7 +30026,7 @@
         <v>3.737521317704196</v>
       </c>
       <c r="D573" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E573">
         <v>4.762944866631269</v>
@@ -30071,7 +30062,7 @@
         <v>1</v>
       </c>
       <c r="P573" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
     </row>
     <row r="574" spans="1:16">
@@ -30085,7 +30076,7 @@
         <v>3.716943268562606</v>
       </c>
       <c r="D574" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E574">
         <v>4.762944866631269</v>
@@ -30121,7 +30112,7 @@
         <v>1</v>
       </c>
       <c r="P574" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
     </row>
     <row r="575" spans="1:16">
@@ -30171,7 +30162,7 @@
         <v>1</v>
       </c>
       <c r="P575" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
     </row>
     <row r="576" spans="1:16">
@@ -30221,7 +30212,7 @@
         <v>1</v>
       </c>
       <c r="P576" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
     </row>
     <row r="577" spans="1:16">
@@ -30235,7 +30226,7 @@
         <v>3.710853293730853</v>
       </c>
       <c r="D577" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E577">
         <v>4.733603965539871</v>
@@ -30271,7 +30262,7 @@
         <v>1</v>
       </c>
       <c r="P577" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
     </row>
     <row r="578" spans="1:16">
@@ -30285,7 +30276,7 @@
         <v>3.686751906570006</v>
       </c>
       <c r="D578" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E578">
         <v>4.733603965539871</v>
@@ -30321,7 +30312,7 @@
         <v>1</v>
       </c>
       <c r="P578" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
     </row>
     <row r="579" spans="1:16">
@@ -30371,7 +30362,7 @@
         <v>1</v>
       </c>
       <c r="P579" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
     </row>
     <row r="580" spans="1:16">
@@ -30421,7 +30412,7 @@
         <v>1</v>
       </c>
       <c r="P580" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
     </row>
     <row r="581" spans="1:16">
@@ -30471,7 +30462,7 @@
         <v>1</v>
       </c>
       <c r="P581" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
     </row>
     <row r="582" spans="1:16">
@@ -30521,7 +30512,7 @@
         <v>1</v>
       </c>
       <c r="P582" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
     </row>
     <row r="583" spans="1:16">
@@ -30571,7 +30562,7 @@
         <v>1</v>
       </c>
       <c r="P583" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
     </row>
     <row r="584" spans="1:16">
@@ -30621,7 +30612,7 @@
         <v>1</v>
       </c>
       <c r="P584" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
     </row>
     <row r="585" spans="1:16">
@@ -30671,7 +30662,7 @@
         <v>1</v>
       </c>
       <c r="P585" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
     </row>
     <row r="586" spans="1:16">
@@ -30721,7 +30712,7 @@
         <v>1</v>
       </c>
       <c r="P586" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
     </row>
     <row r="587" spans="1:16">
@@ -30771,7 +30762,7 @@
         <v>1</v>
       </c>
       <c r="P587" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
     </row>
     <row r="588" spans="1:16">
@@ -30821,7 +30812,7 @@
         <v>1</v>
       </c>
       <c r="P588" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
     </row>
     <row r="589" spans="1:16">
@@ -30871,7 +30862,7 @@
         <v>1</v>
       </c>
       <c r="P589" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
     </row>
     <row r="590" spans="1:16">
@@ -30921,7 +30912,7 @@
         <v>1</v>
       </c>
       <c r="P590" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
     </row>
     <row r="591" spans="1:16">
@@ -31171,7 +31162,7 @@
         <v>1</v>
       </c>
       <c r="P595" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
     </row>
     <row r="596" spans="1:16">
@@ -31221,7 +31212,7 @@
         <v>1</v>
       </c>
       <c r="P596" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
     </row>
     <row r="597" spans="1:16">
@@ -31271,7 +31262,7 @@
         <v>1</v>
       </c>
       <c r="P597" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
     </row>
     <row r="598" spans="1:16">
@@ -31321,7 +31312,7 @@
         <v>1</v>
       </c>
       <c r="P598" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
     </row>
     <row r="599" spans="1:16">
@@ -31371,7 +31362,7 @@
         <v>1</v>
       </c>
       <c r="P599" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
     </row>
     <row r="600" spans="1:16">
@@ -31421,7 +31412,7 @@
         <v>1</v>
       </c>
       <c r="P600" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
     </row>
     <row r="601" spans="1:16">
@@ -31635,7 +31626,7 @@
         <v>6.312844467716282</v>
       </c>
       <c r="D605" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E605">
         <v>7.044140001633426</v>
@@ -31721,7 +31712,7 @@
         <v>1</v>
       </c>
       <c r="P606" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
     </row>
     <row r="607" spans="1:16">
@@ -31771,7 +31762,7 @@
         <v>1</v>
       </c>
       <c r="P607" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
     </row>
     <row r="608" spans="1:16">
@@ -31821,7 +31812,7 @@
         <v>1</v>
       </c>
       <c r="P608" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
     </row>
     <row r="609" spans="1:16">
@@ -31871,7 +31862,7 @@
         <v>1</v>
       </c>
       <c r="P609" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
     </row>
     <row r="610" spans="1:16">
@@ -31921,7 +31912,7 @@
         <v>1</v>
       </c>
       <c r="P610" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
     </row>
     <row r="611" spans="1:16">
@@ -31971,7 +31962,7 @@
         <v>1</v>
       </c>
       <c r="P611" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
     </row>
     <row r="612" spans="1:16">
@@ -32021,7 +32012,7 @@
         <v>1</v>
       </c>
       <c r="P612" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
     </row>
     <row r="613" spans="1:16">
@@ -32071,7 +32062,7 @@
         <v>1</v>
       </c>
       <c r="P613" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
     </row>
     <row r="614" spans="1:16">
@@ -32121,7 +32112,7 @@
         <v>1</v>
       </c>
       <c r="P614" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
     </row>
     <row r="615" spans="1:16">
@@ -32171,7 +32162,7 @@
         <v>1</v>
       </c>
       <c r="P615" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="616" spans="1:16">
@@ -32221,7 +32212,7 @@
         <v>1</v>
       </c>
       <c r="P616" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="617" spans="1:16">
@@ -32271,7 +32262,7 @@
         <v>1</v>
       </c>
       <c r="P617" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="618" spans="1:16">
@@ -32321,7 +32312,7 @@
         <v>1</v>
       </c>
       <c r="P618" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="619" spans="1:16">
@@ -32371,7 +32362,7 @@
         <v>1</v>
       </c>
       <c r="P619" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
     </row>
     <row r="620" spans="1:16">
@@ -32421,7 +32412,7 @@
         <v>1</v>
       </c>
       <c r="P620" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
     </row>
     <row r="621" spans="1:16">
@@ -32471,7 +32462,7 @@
         <v>1</v>
       </c>
       <c r="P621" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
     </row>
     <row r="622" spans="1:16">
@@ -32485,7 +32476,7 @@
         <v>6.52789956231641</v>
       </c>
       <c r="D622" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="E622">
         <v>6.970266187949232</v>
@@ -32521,7 +32512,7 @@
         <v>1</v>
       </c>
       <c r="P622" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
     </row>
     <row r="623" spans="1:16">
@@ -32571,7 +32562,7 @@
         <v>1</v>
       </c>
       <c r="P623" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
     </row>
     <row r="624" spans="1:16">
@@ -32621,7 +32612,7 @@
         <v>1</v>
       </c>
       <c r="P624" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
     </row>
     <row r="625" spans="1:16">
@@ -32671,7 +32662,7 @@
         <v>1</v>
       </c>
       <c r="P625" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
     </row>
     <row r="626" spans="1:16">
@@ -32685,7 +32676,7 @@
         <v>2.603543847706</v>
       </c>
       <c r="D626" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="E626">
         <v>4.770094008155837</v>
@@ -32721,7 +32712,7 @@
         <v>1</v>
       </c>
       <c r="P626" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
     </row>
     <row r="627" spans="1:16">
@@ -32771,7 +32762,7 @@
         <v>1</v>
       </c>
       <c r="P627" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
     </row>
     <row r="628" spans="1:16">
@@ -32821,7 +32812,7 @@
         <v>1</v>
       </c>
       <c r="P628" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
     </row>
     <row r="629" spans="1:16">
@@ -32871,7 +32862,7 @@
         <v>1</v>
       </c>
       <c r="P629" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
     </row>
     <row r="630" spans="1:16">
@@ -32921,7 +32912,7 @@
         <v>1</v>
       </c>
       <c r="P630" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
     </row>
     <row r="631" spans="1:16">
@@ -32971,7 +32962,7 @@
         <v>1</v>
       </c>
       <c r="P631" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
     </row>
     <row r="632" spans="1:16">
@@ -32985,7 +32976,7 @@
         <v>2.478182256708074</v>
       </c>
       <c r="D632" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="E632">
         <v>4.645810796435313</v>
@@ -33021,7 +33012,7 @@
         <v>1</v>
       </c>
       <c r="P632" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
     </row>
     <row r="633" spans="1:16">
@@ -33071,7 +33062,7 @@
         <v>1</v>
       </c>
       <c r="P633" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
     </row>
     <row r="634" spans="1:16">
@@ -33121,7 +33112,7 @@
         <v>1</v>
       </c>
       <c r="P634" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
     </row>
     <row r="635" spans="1:16">
@@ -33171,7 +33162,7 @@
         <v>1</v>
       </c>
       <c r="P635" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
     </row>
     <row r="636" spans="1:16">
@@ -33221,7 +33212,7 @@
         <v>1</v>
       </c>
       <c r="P636" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
     </row>
     <row r="637" spans="1:16">
@@ -33235,7 +33226,7 @@
         <v>2.30694018299906</v>
       </c>
       <c r="D637" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="E637">
         <v>4.476041772822722</v>
@@ -33271,7 +33262,7 @@
         <v>1</v>
       </c>
       <c r="P637" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
     </row>
     <row r="638" spans="1:16">
@@ -33285,7 +33276,7 @@
         <v>5.979313720333828</v>
       </c>
       <c r="D638" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="E638">
         <v>6.921637837986275</v>
@@ -33321,7 +33312,7 @@
         <v>1</v>
       </c>
       <c r="P638" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
     </row>
     <row r="639" spans="1:16">
@@ -33335,7 +33326,7 @@
         <v>6.118014825265853</v>
       </c>
       <c r="D639" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="E639">
         <v>6.921637837986275</v>
@@ -33371,7 +33362,7 @@
         <v>1</v>
       </c>
       <c r="P639" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
     </row>
     <row r="640" spans="1:16">
@@ -33385,7 +33376,7 @@
         <v>2.180042495856011</v>
       </c>
       <c r="D640" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="E640">
         <v>4.350235678687355</v>
@@ -33421,7 +33412,7 @@
         <v>1</v>
       </c>
       <c r="P640" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
     </row>
     <row r="641" spans="1:16">
@@ -33471,7 +33462,7 @@
         <v>1</v>
       </c>
       <c r="P641" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
     </row>
     <row r="642" spans="1:16">
@@ -33521,7 +33512,7 @@
         <v>1</v>
       </c>
       <c r="P642" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
     </row>
     <row r="643" spans="1:16">
@@ -33571,7 +33562,7 @@
         <v>1</v>
       </c>
       <c r="P643" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
     </row>
     <row r="644" spans="1:16">
@@ -33585,7 +33576,7 @@
         <v>2.005501953213372</v>
       </c>
       <c r="D644" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="E644">
         <v>4.177196560067447</v>
@@ -33621,7 +33612,7 @@
         <v>1</v>
       </c>
       <c r="P644" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
     </row>
     <row r="645" spans="1:16">
@@ -33635,7 +33626,7 @@
         <v>6.03048720269387</v>
       </c>
       <c r="D645" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="E645">
         <v>7.646218976894719</v>
@@ -33671,7 +33662,7 @@
         <v>1</v>
       </c>
       <c r="P645" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
     </row>
     <row r="646" spans="1:16">
@@ -33685,7 +33676,7 @@
         <v>6.160487202693869</v>
       </c>
       <c r="D646" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="E646">
         <v>7.646218976894719</v>
@@ -33721,7 +33712,7 @@
         <v>1</v>
       </c>
       <c r="P646" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
     </row>
     <row r="647" spans="1:16">
@@ -33785,7 +33776,7 @@
         <v>5.929250610805834</v>
       </c>
       <c r="D648" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="E648">
         <v>6.44678700451809</v>
@@ -33835,7 +33826,7 @@
         <v>6.059250610805833</v>
       </c>
       <c r="D649" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="E649">
         <v>6.44678700451809</v>
@@ -33921,7 +33912,7 @@
         <v>1</v>
       </c>
       <c r="P650" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
     </row>
     <row r="651" spans="1:16">
@@ -33935,7 +33926,7 @@
         <v>6.444007644774246</v>
       </c>
       <c r="D651" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="E651">
         <v>5.9080963375586</v>
@@ -33971,7 +33962,7 @@
         <v>1</v>
       </c>
       <c r="P651" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
     </row>
     <row r="652" spans="1:16">
@@ -33985,7 +33976,7 @@
         <v>5.977845942063905</v>
       </c>
       <c r="D652" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="E652">
         <v>5.9080963375586</v>
@@ -34021,7 +34012,7 @@
         <v>1</v>
       </c>
       <c r="P652" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
     </row>
     <row r="653" spans="1:16">
@@ -34085,7 +34076,7 @@
         <v>6.325113724849238</v>
       </c>
       <c r="D654" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="E654">
         <v>5.966484401224733</v>
@@ -34135,7 +34126,7 @@
         <v>6.616965483162407</v>
       </c>
       <c r="D655" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="E655">
         <v>5.966484401224733</v>
@@ -34371,7 +34362,7 @@
         <v>1</v>
       </c>
       <c r="P659" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
     </row>
     <row r="660" spans="1:16">
@@ -34385,7 +34376,7 @@
         <v>6.182411935806901</v>
       </c>
       <c r="D660" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="E660">
         <v>5.820555041914538</v>
@@ -34421,7 +34412,7 @@
         <v>1</v>
       </c>
       <c r="P660" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
     </row>
     <row r="661" spans="1:16">
@@ -34435,7 +34426,7 @@
         <v>6.479370608860847</v>
       </c>
       <c r="D661" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="E661">
         <v>5.820555041914538</v>
@@ -34471,7 +34462,7 @@
         <v>1</v>
       </c>
       <c r="P661" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
     </row>
     <row r="662" spans="1:16">
@@ -34485,7 +34476,7 @@
         <v>6.247760471854665</v>
       </c>
       <c r="D662" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="E662">
         <v>5.820555041914538</v>
@@ -34521,7 +34512,7 @@
         <v>1</v>
       </c>
       <c r="P662" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
     </row>
     <row r="663" spans="1:16">
@@ -34635,7 +34626,7 @@
         <v>6.052746661470383</v>
       </c>
       <c r="D665" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="E665">
         <v>5.747828147206722</v>
@@ -34685,7 +34676,7 @@
         <v>6.354345707327784</v>
       </c>
       <c r="D666" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="E666">
         <v>5.747828147206722</v>
@@ -34735,7 +34726,7 @@
         <v>6.106229101349317</v>
       </c>
       <c r="D667" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="E667">
         <v>5.747828147206722</v>
@@ -34885,7 +34876,7 @@
         <v>5.992378168346487</v>
       </c>
       <c r="D670" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="E670">
         <v>5.919638041522585</v>
@@ -34935,7 +34926,7 @@
         <v>6.296137640849427</v>
       </c>
       <c r="D671" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="E671">
         <v>5.919638041522585</v>
@@ -34985,7 +34976,7 @@
         <v>6.0403360886604</v>
       </c>
       <c r="D672" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="E672">
         <v>5.919638041522585</v>
@@ -35071,7 +35062,7 @@
         <v>1</v>
       </c>
       <c r="P673" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
     <row r="674" spans="1:16">
@@ -35121,7 +35112,7 @@
         <v>1</v>
       </c>
       <c r="P674" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
     <row r="675" spans="1:16">
@@ -35135,7 +35126,7 @@
         <v>5.931074248482098</v>
       </c>
       <c r="D675" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="E675">
         <v>5.817063063996034</v>
@@ -35171,7 +35162,7 @@
         <v>1</v>
       </c>
       <c r="P675" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
     <row r="676" spans="1:16">
@@ -35185,7 +35176,7 @@
         <v>6.237027624047666</v>
       </c>
       <c r="D676" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="E676">
         <v>5.817063063996034</v>
@@ -35221,7 +35212,7 @@
         <v>1</v>
       </c>
       <c r="P676" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
     <row r="677" spans="1:16">
@@ -35235,7 +35226,7 @@
         <v>5.973422045250139</v>
       </c>
       <c r="D677" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="E677">
         <v>5.817063063996034</v>
@@ -35271,7 +35262,7 @@
         <v>1</v>
       </c>
       <c r="P677" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
     <row r="678" spans="1:16">
@@ -35385,7 +35376,7 @@
         <v>5.839386641650073</v>
       </c>
       <c r="D680" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="E680">
         <v>4.893781158276536</v>
@@ -35435,7 +35426,7 @@
         <v>6.148621271038877</v>
       </c>
       <c r="D681" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="E681">
         <v>4.893781158276536</v>
@@ -35485,7 +35476,7 @@
         <v>5.873343803641564</v>
       </c>
       <c r="D682" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="E682">
         <v>4.893781158276536</v>
@@ -35585,7 +35576,7 @@
         <v>6.049313264972337</v>
       </c>
       <c r="D684" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="E684">
         <v>4.936335249131968</v>
@@ -35635,7 +35626,7 @@
         <v>6.175722584965069</v>
       </c>
       <c r="D685" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="E685">
         <v>4.936335249131968</v>
@@ -35685,7 +35676,7 @@
         <v>5.760924613317037</v>
       </c>
       <c r="D686" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="E686">
         <v>4.936335249131968</v>
@@ -35835,7 +35826,7 @@
         <v>5.905539797299475</v>
       </c>
       <c r="D689" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="E689">
         <v>5.270502414665344</v>
@@ -35885,7 +35876,7 @@
         <v>6.021734035283636</v>
       </c>
       <c r="D690" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="E690">
         <v>5.270502414665344</v>
@@ -36035,7 +36026,7 @@
         <v>5.810134805942958</v>
       </c>
       <c r="D693" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="E693">
         <v>4.46837075668304</v>
@@ -36085,7 +36076,7 @@
         <v>5.919550534467003</v>
       </c>
       <c r="D694" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="E694">
         <v>4.46837075668304</v>
@@ -36135,7 +36126,7 @@
         <v>5.597681787127293</v>
       </c>
       <c r="D695" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="E695">
         <v>5.175448484795162</v>
@@ -36185,7 +36176,7 @@
         <v>5.69200276245871</v>
       </c>
       <c r="D696" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="E696">
         <v>5.175448484795162</v>
@@ -36271,7 +36262,7 @@
         <v>1</v>
       </c>
       <c r="P697" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
     </row>
     <row r="698" spans="1:16">
@@ -36321,7 +36312,7 @@
         <v>1</v>
       </c>
       <c r="P698" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
     </row>
     <row r="699" spans="1:16">
@@ -36371,7 +36362,7 @@
         <v>1</v>
       </c>
       <c r="P699" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
     </row>
     <row r="700" spans="1:16">
@@ -36421,7 +36412,7 @@
         <v>1</v>
       </c>
       <c r="P700" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
     </row>
     <row r="701" spans="1:16">
@@ -36435,7 +36426,7 @@
         <v>10.58920111380781</v>
       </c>
       <c r="D701" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="E701">
         <v>10.63805069137965</v>
@@ -36471,7 +36462,7 @@
         <v>1</v>
       </c>
       <c r="P701" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
     </row>
     <row r="702" spans="1:16">
@@ -36521,7 +36512,7 @@
         <v>1</v>
       </c>
       <c r="P702" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
     </row>
     <row r="703" spans="1:16">
@@ -36535,7 +36526,7 @@
         <v>13.29070024337744</v>
       </c>
       <c r="D703" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="E703">
         <v>12.1104855745369</v>
@@ -36571,7 +36562,7 @@
         <v>1</v>
       </c>
       <c r="P703" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
     </row>
     <row r="704" spans="1:16">
@@ -36621,7 +36612,7 @@
         <v>1</v>
       </c>
       <c r="P704" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
     </row>
     <row r="705" spans="1:16">
@@ -36635,7 +36626,7 @@
         <v>13.05967948318782</v>
       </c>
       <c r="D705" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="E705">
         <v>11.87581437344135</v>
@@ -36671,7 +36662,7 @@
         <v>1</v>
       </c>
       <c r="P705" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
     </row>
     <row r="706" spans="1:16">
@@ -36721,7 +36712,7 @@
         <v>1</v>
       </c>
       <c r="P706" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
     </row>
     <row r="707" spans="1:16">
@@ -36735,7 +36726,7 @@
         <v>12.8170626988293</v>
       </c>
       <c r="D707" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="E707">
         <v>10.97022453374666</v>
@@ -36771,7 +36762,7 @@
         <v>1</v>
       </c>
       <c r="P707" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
     </row>
     <row r="708" spans="1:16">
@@ -36821,7 +36812,7 @@
         <v>1</v>
       </c>
       <c r="P708" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
     </row>
     <row r="709" spans="1:16">
@@ -36835,7 +36826,7 @@
         <v>12.5987805539735</v>
       </c>
       <c r="D709" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="E709">
         <v>10.73863851098768</v>
@@ -36871,7 +36862,7 @@
         <v>1</v>
       </c>
       <c r="P709" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
     </row>
     <row r="710" spans="1:16">
@@ -36921,7 +36912,7 @@
         <v>1</v>
       </c>
       <c r="P710" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
     </row>
     <row r="711" spans="1:16">
@@ -36971,7 +36962,7 @@
         <v>1</v>
       </c>
       <c r="P711" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
     </row>
     <row r="712" spans="1:16">
@@ -37021,7 +37012,7 @@
         <v>1</v>
       </c>
       <c r="P712" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
     </row>
     <row r="713" spans="1:16">
@@ -37035,7 +37026,7 @@
         <v>12.45336310880131</v>
       </c>
       <c r="D713" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="E713">
         <v>10.58435815154991</v>
@@ -37071,7 +37062,7 @@
         <v>1</v>
       </c>
       <c r="P713" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
     </row>
     <row r="714" spans="1:16">
@@ -37121,7 +37112,7 @@
         <v>1</v>
       </c>
       <c r="P714" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
     </row>
     <row r="715" spans="1:16">
@@ -37171,7 +37162,7 @@
         <v>1</v>
       </c>
       <c r="P715" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
     </row>
     <row r="716" spans="1:16">
@@ -37221,7 +37212,7 @@
         <v>1</v>
       </c>
       <c r="P716" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
     </row>
     <row r="717" spans="1:16">
@@ -37271,7 +37262,7 @@
         <v>1</v>
       </c>
       <c r="P717" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
     </row>
     <row r="718" spans="1:16">
@@ -37321,7 +37312,7 @@
         <v>1</v>
       </c>
       <c r="P718" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
     </row>
     <row r="719" spans="1:16">
@@ -37371,7 +37362,7 @@
         <v>1</v>
       </c>
       <c r="P719" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
     </row>
     <row r="720" spans="1:16">
@@ -37385,7 +37376,7 @@
         <v>12.29210392935995</v>
       </c>
       <c r="D720" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="E720">
         <v>10.41327053453538</v>
@@ -37421,7 +37412,7 @@
         <v>1</v>
       </c>
       <c r="P720" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
     </row>
     <row r="721" spans="1:16">
@@ -37435,7 +37426,7 @@
         <v>9.171282848330055</v>
       </c>
       <c r="D721" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="E721">
         <v>6.850968108671186</v>
@@ -37471,7 +37462,7 @@
         <v>1</v>
       </c>
       <c r="P721" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
     </row>
     <row r="722" spans="1:16">
@@ -37485,7 +37476,7 @@
         <v>8.830116243154617</v>
       </c>
       <c r="D722" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="E722">
         <v>6.850968108671186</v>
@@ -37521,7 +37512,7 @@
         <v>1</v>
       </c>
       <c r="P722" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
     </row>
     <row r="723" spans="1:16">
@@ -37685,7 +37676,7 @@
         <v>12.09795277153261</v>
       </c>
       <c r="D726" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="E726">
         <v>10.20728623616326</v>
@@ -37735,7 +37726,7 @@
         <v>8.629829382822578</v>
       </c>
       <c r="D727" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="E727">
         <v>7.040051561279032</v>
@@ -37821,7 +37812,7 @@
         <v>1</v>
       </c>
       <c r="P728" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
     </row>
     <row r="729" spans="1:16">
@@ -37871,7 +37862,7 @@
         <v>1</v>
       </c>
       <c r="P729" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
     </row>
     <row r="730" spans="1:16">
@@ -37921,7 +37912,7 @@
         <v>1</v>
       </c>
       <c r="P730" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
     </row>
     <row r="731" spans="1:16">
@@ -37935,7 +37926,7 @@
         <v>11.86477339723001</v>
       </c>
       <c r="D731" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="E731">
         <v>9.95989502640656</v>
@@ -37971,7 +37962,7 @@
         <v>1</v>
       </c>
       <c r="P731" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
     </row>
     <row r="732" spans="1:16">
@@ -37985,7 +37976,7 @@
         <v>8.389280908654889</v>
       </c>
       <c r="D732" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="E732">
         <v>6.803093216210396</v>
@@ -38021,7 +38012,7 @@
         <v>1</v>
       </c>
       <c r="P732" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
     </row>
     <row r="733" spans="1:16">
@@ -38071,7 +38062,7 @@
         <v>1</v>
       </c>
       <c r="P733" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
     </row>
     <row r="734" spans="1:16">
@@ -38121,7 +38112,7 @@
         <v>1</v>
       </c>
       <c r="P734" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
     </row>
     <row r="735" spans="1:16">
@@ -38171,7 +38162,7 @@
         <v>1</v>
       </c>
       <c r="P735" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
     </row>
     <row r="736" spans="1:16">
@@ -38221,7 +38212,7 @@
         <v>1</v>
       </c>
       <c r="P736" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
     </row>
     <row r="737" spans="1:16">
@@ -38235,7 +38226,7 @@
         <v>7.721090409497048</v>
       </c>
       <c r="D737" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="E737">
         <v>6.845979077114176</v>
@@ -38271,7 +38262,7 @@
         <v>1</v>
       </c>
       <c r="P737" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
     </row>
     <row r="738" spans="1:16">
@@ -38321,7 +38312,7 @@
         <v>1</v>
       </c>
       <c r="P738" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
     </row>
     <row r="739" spans="1:16">
@@ -38371,7 +38362,7 @@
         <v>1</v>
       </c>
       <c r="P739" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
     </row>
     <row r="740" spans="1:16">
@@ -38421,7 +38412,7 @@
         <v>1</v>
       </c>
       <c r="P740" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
     </row>
     <row r="741" spans="1:16">
@@ -38435,7 +38426,7 @@
         <v>7.431928747420816</v>
       </c>
       <c r="D741" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="E741">
         <v>6.954602200047407</v>
@@ -38471,7 +38462,7 @@
         <v>1</v>
       </c>
       <c r="P741" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
     </row>
     <row r="742" spans="1:16">
@@ -38521,7 +38512,7 @@
         <v>1</v>
       </c>
       <c r="P742" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
     </row>
     <row r="743" spans="1:16">
@@ -38571,7 +38562,7 @@
         <v>1</v>
       </c>
       <c r="P743" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
     </row>
     <row r="744" spans="1:16">
@@ -38621,7 +38612,7 @@
         <v>1</v>
       </c>
       <c r="P744" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
     </row>
     <row r="745" spans="1:16">
@@ -38671,7 +38662,7 @@
         <v>1</v>
       </c>
       <c r="P745" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
     </row>
     <row r="746" spans="1:16">
@@ -38685,7 +38676,7 @@
         <v>7.15411432552343</v>
       </c>
       <c r="D746" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="E746">
         <v>7.077702572180645</v>
@@ -38721,7 +38712,7 @@
         <v>1</v>
       </c>
       <c r="P746" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
     </row>
     <row r="747" spans="1:16">
@@ -38985,7 +38976,7 @@
         <v>6.656074286112602</v>
       </c>
       <c r="D752" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="E752">
         <v>7.106777983579878</v>
@@ -39071,7 +39062,7 @@
         <v>1</v>
       </c>
       <c r="P753" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
     </row>
     <row r="754" spans="1:16">
@@ -39121,7 +39112,7 @@
         <v>1</v>
       </c>
       <c r="P754" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
     </row>
     <row r="755" spans="1:16">
@@ -39171,7 +39162,7 @@
         <v>1</v>
       </c>
       <c r="P755" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
     </row>
     <row r="756" spans="1:16">
@@ -39221,7 +39212,7 @@
         <v>1</v>
       </c>
       <c r="P756" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
     </row>
     <row r="757" spans="1:16">
@@ -39271,7 +39262,7 @@
         <v>1</v>
       </c>
       <c r="P757" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
     </row>
     <row r="758" spans="1:16">
@@ -39321,7 +39312,7 @@
         <v>1</v>
       </c>
       <c r="P758" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
     </row>
     <row r="759" spans="1:16">
@@ -39671,7 +39662,7 @@
         <v>1</v>
       </c>
       <c r="P765" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
     </row>
     <row r="766" spans="1:16">
@@ -39721,7 +39712,7 @@
         <v>1</v>
       </c>
       <c r="P766" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
     </row>
     <row r="767" spans="1:16">
@@ -39735,7 +39726,7 @@
         <v>5.189787984798581</v>
       </c>
       <c r="D767" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="E767">
         <v>6.127393152460147</v>
@@ -39771,7 +39762,7 @@
         <v>1</v>
       </c>
       <c r="P767" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
     </row>
     <row r="768" spans="1:16">
@@ -39785,7 +39776,7 @@
         <v>5.337615079752425</v>
       </c>
       <c r="D768" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="E768">
         <v>6.127393152460147</v>
@@ -39821,7 +39812,7 @@
         <v>1</v>
       </c>
       <c r="P768" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
     </row>
     <row r="769" spans="1:16">
@@ -39935,7 +39926,7 @@
         <v>4.573548410677798</v>
       </c>
       <c r="D771" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="E771">
         <v>5.983161604764781</v>
@@ -39985,7 +39976,7 @@
         <v>4.718587091269107</v>
       </c>
       <c r="D772" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="E772">
         <v>5.983161604764781</v>
@@ -40071,7 +40062,7 @@
         <v>1</v>
       </c>
       <c r="P773" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
     </row>
     <row r="774" spans="1:16">
@@ -40121,7 +40112,7 @@
         <v>1</v>
       </c>
       <c r="P774" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
     </row>
     <row r="775" spans="1:16">
@@ -40171,7 +40162,7 @@
         <v>1</v>
       </c>
       <c r="P775" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
     </row>
     <row r="776" spans="1:16">
@@ -40221,7 +40212,7 @@
         <v>1</v>
       </c>
       <c r="P776" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
     </row>
     <row r="777" spans="1:16">
@@ -40471,7 +40462,7 @@
         <v>1</v>
       </c>
       <c r="P781" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
     </row>
     <row r="782" spans="1:16">
@@ -40521,7 +40512,7 @@
         <v>1</v>
       </c>
       <c r="P782" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
     </row>
     <row r="783" spans="1:16">
@@ -40571,7 +40562,7 @@
         <v>1</v>
       </c>
       <c r="P783" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
     </row>
     <row r="784" spans="1:16">
@@ -40971,7 +40962,7 @@
         <v>1</v>
       </c>
       <c r="P791" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
     </row>
     <row r="792" spans="1:16">
@@ -41021,7 +41012,7 @@
         <v>1</v>
       </c>
       <c r="P792" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
     </row>
     <row r="793" spans="1:16">
@@ -41071,7 +41062,7 @@
         <v>1</v>
       </c>
       <c r="P793" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
     </row>
     <row r="794" spans="1:16">
@@ -41121,7 +41112,7 @@
         <v>1</v>
       </c>
       <c r="P794" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
     </row>
     <row r="795" spans="1:16">
@@ -41371,7 +41362,7 @@
         <v>1</v>
       </c>
       <c r="P799" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
     </row>
     <row r="800" spans="1:16">
@@ -41385,7 +41376,7 @@
         <v>1.03967143846625</v>
       </c>
       <c r="D800" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="E800">
         <v>2.609188567947417</v>
@@ -41421,7 +41412,7 @@
         <v>1</v>
       </c>
       <c r="P800" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
     </row>
     <row r="801" spans="1:16">
@@ -41435,7 +41426,7 @@
         <v>0.8130094478294367</v>
       </c>
       <c r="D801" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="E801">
         <v>2.609188567947417</v>
@@ -41471,7 +41462,7 @@
         <v>1</v>
       </c>
       <c r="P801" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
     </row>
     <row r="802" spans="1:16">
@@ -41521,7 +41512,7 @@
         <v>1</v>
       </c>
       <c r="P802" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
     </row>
     <row r="803" spans="1:16">
@@ -41535,7 +41526,7 @@
         <v>0.7465491084079581</v>
       </c>
       <c r="D803" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="E803">
         <v>2.329329691737918</v>
@@ -41571,7 +41562,7 @@
         <v>1</v>
       </c>
       <c r="P803" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
     </row>
     <row r="804" spans="1:16">
@@ -41585,7 +41576,7 @@
         <v>0.5106027000769942</v>
       </c>
       <c r="D804" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="E804">
         <v>2.329329691737918</v>
@@ -41621,7 +41612,7 @@
         <v>1</v>
       </c>
       <c r="P804" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
     </row>
     <row r="805" spans="1:16">
@@ -41635,7 +41626,7 @@
         <v>0.4893560218813207</v>
       </c>
       <c r="D805" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="E805">
         <v>2.083774301434204</v>
@@ -41685,7 +41676,7 @@
         <v>0.2452632261943108</v>
       </c>
       <c r="D806" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="E806">
         <v>2.083774301434204</v>
@@ -41735,7 +41726,7 @@
         <v>3.38720643044401</v>
       </c>
       <c r="D807" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="E807">
         <v>1.346565161657761</v>
@@ -41785,7 +41776,7 @@
         <v>0.03330516332946587</v>
       </c>
       <c r="D808" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="E808">
         <v>1.648359228337185</v>
@@ -41835,7 +41826,7 @@
         <v>-0.2252326821759354</v>
       </c>
       <c r="D809" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="E809">
         <v>1.648359228337185</v>
@@ -41885,7 +41876,7 @@
         <v>2.979030594147371</v>
       </c>
       <c r="D810" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="E810">
         <v>0.9008321958333205</v>
@@ -41935,7 +41926,7 @@
         <v>-0.3050434949915584</v>
       </c>
       <c r="D811" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="E811">
         <v>1.325320464057839</v>
@@ -41971,7 +41962,7 @@
         <v>1</v>
       </c>
       <c r="P811" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
     </row>
     <row r="812" spans="1:16">
@@ -41985,7 +41976,7 @@
         <v>-0.5742982663261245</v>
       </c>
       <c r="D812" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="E812">
         <v>1.325320464057839</v>
@@ -42021,7 +42012,7 @@
         <v>1</v>
       </c>
       <c r="P812" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
     </row>
     <row r="813" spans="1:16">
@@ -42035,7 +42026,7 @@
         <v>2.676200890003035</v>
       </c>
       <c r="D813" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="E813">
         <v>0.570138484533139</v>
@@ -42071,7 +42062,7 @@
         <v>1</v>
       </c>
       <c r="P813" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
     </row>
     <row r="814" spans="1:16">
@@ -42085,7 +42076,7 @@
         <v>-1.542729235915701</v>
       </c>
       <c r="D814" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="E814">
         <v>0.8740710626510406</v>
@@ -42135,7 +42126,7 @@
         <v>-1.06190425457612</v>
       </c>
       <c r="D815" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="E815">
         <v>0.8740710626510406</v>
@@ -42185,7 +42176,7 @@
         <v>2.253181308968607</v>
       </c>
       <c r="D816" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="E816">
         <v>0.1081959693489338</v>
@@ -42235,7 +42226,7 @@
         <v>-1.645106114375984</v>
       </c>
       <c r="D817" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="E817">
         <v>0.7789101756240804</v>
@@ -42285,7 +42276,7 @@
         <v>-1.164732132500994</v>
       </c>
       <c r="D818" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="E818">
         <v>0.7789101756240804</v>
@@ -42335,7 +42326,7 @@
         <v>1.705918320624114</v>
       </c>
       <c r="D819" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="E819">
         <v>0.01078008499905536</v>
@@ -42385,7 +42376,7 @@
         <v>2.163973614874138</v>
       </c>
       <c r="D820" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="E820">
         <v>0.01078008499905536</v>
@@ -42435,7 +42426,7 @@
         <v>2.083749225749141</v>
       </c>
       <c r="D821" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="E821">
         <v>-0.02146380625091737</v>
@@ -42485,7 +42476,7 @@
         <v>-1.354990011712744</v>
       </c>
       <c r="D822" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="E822">
         <v>1.048577566205335</v>
@@ -42535,7 +42526,7 @@
         <v>-0.8733379853326184</v>
       </c>
       <c r="D823" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="E823">
         <v>1.048577566205335</v>
@@ -42585,7 +42576,7 @@
         <v>1.965361355164372</v>
       </c>
       <c r="D824" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="E824">
         <v>0.2868376981059342</v>
@@ -42635,7 +42626,7 @@
         <v>2.41677081798775</v>
       </c>
       <c r="D825" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="E825">
         <v>0.2868376981059342</v>
@@ -42685,7 +42676,7 @@
         <v>2.335779602159679</v>
       </c>
       <c r="D826" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="E826">
         <v>0.246925539825213</v>
@@ -42735,7 +42726,7 @@
         <v>-1.093559587288276</v>
       </c>
       <c r="D827" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="E827">
         <v>-1.564638644835625</v>
@@ -42785,7 +42776,7 @@
         <v>-1.266714738768137</v>
       </c>
       <c r="D828" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="E828">
         <v>0.4727739583005963</v>
@@ -42821,7 +42812,7 @@
         <v>1</v>
       </c>
       <c r="P828" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="829" spans="1:16">
@@ -42835,7 +42826,7 @@
         <v>-0.7846738345336348</v>
       </c>
       <c r="D829" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="E829">
         <v>0.5188966710041001</v>
@@ -42871,7 +42862,7 @@
         <v>1</v>
       </c>
       <c r="P829" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="830" spans="1:16">
@@ -42885,7 +42876,7 @@
         <v>2.044303559603822</v>
       </c>
       <c r="D830" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="E830">
         <v>0.3708353146523429</v>
@@ -42921,7 +42912,7 @@
         <v>1</v>
       </c>
       <c r="P830" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="831" spans="1:16">
@@ -42935,7 +42926,7 @@
         <v>2.412466315043719</v>
       </c>
       <c r="D831" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="E831">
         <v>0.3285898892453361</v>
@@ -42971,7 +42962,7 @@
         <v>1</v>
       </c>
       <c r="P831" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="832" spans="1:16">
@@ -42985,7 +42976,7 @@
         <v>-1.016717323262487</v>
       </c>
       <c r="D832" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="E832">
         <v>-1.725082876878652</v>
@@ -43021,7 +43012,7 @@
         <v>1</v>
       </c>
       <c r="P832" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="833" spans="1:16">
@@ -43035,7 +43026,7 @@
         <v>-1.012419255686936</v>
       </c>
       <c r="D833" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="E833">
         <v>0.7130663861460427</v>
@@ -43085,7 +43076,7 @@
         <v>2.271713176632382</v>
       </c>
       <c r="D834" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="E834">
         <v>0.563841217205912</v>
@@ -43135,7 +43126,7 @@
         <v>2.633378514442889</v>
       </c>
       <c r="D835" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="E835">
         <v>0.563841217205912</v>
@@ -43185,7 +43176,7 @@
         <v>-0.7953570260957719</v>
       </c>
       <c r="D836" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="E836">
         <v>-0.6798364854873604</v>
@@ -43235,7 +43226,7 @@
         <v>-1.154980882524804</v>
       </c>
       <c r="D837" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="E837">
         <v>0.3632888214250194</v>
@@ -43271,7 +43262,7 @@
         <v>1</v>
       </c>
       <c r="P837" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="838" spans="1:16">
@@ -43285,7 +43276,7 @@
         <v>2.144224144702488</v>
       </c>
       <c r="D838" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="E838">
         <v>0.3406232020973725</v>
@@ -43321,7 +43312,7 @@
         <v>1</v>
       </c>
       <c r="P838" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="839" spans="1:16">
@@ -43335,7 +43326,7 @@
         <v>2.509532026282422</v>
       </c>
       <c r="D839" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="E839">
         <v>0.3406232020973725</v>
@@ -43371,7 +43362,7 @@
         <v>1</v>
       </c>
       <c r="P839" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="840" spans="1:16">
@@ -43421,7 +43412,7 @@
         <v>1</v>
       </c>
       <c r="P840" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="841" spans="1:16">
@@ -43435,7 +43426,7 @@
         <v>-0.7435135480053319</v>
       </c>
       <c r="D841" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="E841">
         <v>0.7484730002152737</v>
@@ -43585,7 +43576,7 @@
         <v>-0.3742444036399846</v>
       </c>
       <c r="D844" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="E844">
         <v>1.094154467958163</v>
@@ -43621,7 +43612,7 @@
         <v>1</v>
       </c>
       <c r="P844" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
     </row>
     <row r="845" spans="1:16">
@@ -43671,7 +43662,7 @@
         <v>1</v>
       </c>
       <c r="P845" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
     </row>
     <row r="846" spans="1:16">
@@ -43721,7 +43712,7 @@
         <v>1</v>
       </c>
       <c r="P846" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
     </row>
     <row r="847" spans="1:16">
@@ -43735,7 +43726,7 @@
         <v>-0.2301600625778306</v>
       </c>
       <c r="D847" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="E847">
         <v>1.229035183710177</v>
@@ -43771,7 +43762,7 @@
         <v>1</v>
       </c>
       <c r="P847" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
     </row>
     <row r="848" spans="1:16">
@@ -43821,7 +43812,7 @@
         <v>1</v>
       </c>
       <c r="P848" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
     </row>
     <row r="849" spans="1:16">
@@ -43871,7 +43862,7 @@
         <v>1</v>
       </c>
       <c r="P849" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
     </row>
     <row r="850" spans="1:16">
@@ -43885,7 +43876,7 @@
         <v>-0.008911774850371756</v>
       </c>
       <c r="D850" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="E850">
         <v>0.5721947646345491</v>
@@ -43921,7 +43912,7 @@
         <v>1</v>
       </c>
       <c r="P850" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
     </row>
     <row r="851" spans="1:16">
@@ -43935,7 +43926,7 @@
         <v>-0.1112036199752922</v>
       </c>
       <c r="D851" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="E851">
         <v>1.340393087027532</v>
@@ -44085,7 +44076,7 @@
         <v>0.09903988671845454</v>
       </c>
       <c r="D854" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="E854">
         <v>1.106317252320714</v>
@@ -44135,7 +44126,7 @@
         <v>-0.06944114310240224</v>
       </c>
       <c r="D855" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="E855">
         <v>1.379487916699293</v>
@@ -44171,7 +44162,7 @@
         <v>1</v>
       </c>
       <c r="P855" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="856" spans="1:16">
@@ -44221,7 +44212,7 @@
         <v>1</v>
       </c>
       <c r="P856" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="857" spans="1:16">
@@ -44271,7 +44262,7 @@
         <v>1</v>
       </c>
       <c r="P857" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="858" spans="1:16">
@@ -44285,7 +44276,7 @@
         <v>0.1369388745414319</v>
       </c>
       <c r="D858" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="E858">
         <v>1.371101739245933</v>
@@ -44321,7 +44312,7 @@
         <v>1</v>
       </c>
       <c r="P858" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="859" spans="1:16">
@@ -44332,46 +44323,46 @@
         <v>154</v>
       </c>
       <c r="C859">
-        <v>13.70922282990332</v>
+        <v>12.65888206048432</v>
       </c>
       <c r="D859" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="E859">
-        <v>12.65888206048432</v>
+        <v>13.43349103432044</v>
       </c>
       <c r="F859">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G859">
-        <v>0.05159077717009667</v>
+        <v>0.04978111793951567</v>
       </c>
       <c r="H859">
-        <v>0.04978111793951567</v>
+        <v>0.04844650896567956</v>
       </c>
       <c r="I859">
-        <v>1.050340769418998</v>
+        <v>0.7746089738361199</v>
       </c>
       <c r="J859">
         <v>0.8436871790688943</v>
       </c>
       <c r="K859">
-        <v>22.45</v>
+        <v>22</v>
       </c>
       <c r="L859">
-        <v>32.65</v>
+        <v>31.22</v>
       </c>
       <c r="M859">
-        <v>22</v>
+        <v>20.75</v>
       </c>
       <c r="N859">
-        <v>31.22</v>
+        <v>30.94</v>
       </c>
       <c r="O859">
         <v>1</v>
       </c>
       <c r="P859" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
     </row>
     <row r="860" spans="1:16">
@@ -44379,149 +44370,49 @@
         <v>0</v>
       </c>
       <c r="B860" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C860">
-        <v>12.51796460063045</v>
+        <v>12.57849638595733</v>
       </c>
       <c r="D860" t="s">
-        <v>156</v>
+        <v>265</v>
       </c>
       <c r="E860">
-        <v>12.97873629831807</v>
+        <v>13.3576727276643</v>
       </c>
       <c r="F860">
         <v>1</v>
       </c>
       <c r="G860">
-        <v>0.04946203539936955</v>
+        <v>0.04986150361404267</v>
       </c>
       <c r="H860">
-        <v>0.04882126370168193</v>
+        <v>0.0485223272723357</v>
       </c>
       <c r="I860">
-        <v>0.4607716976876262</v>
+        <v>0.7791763417069717</v>
       </c>
       <c r="J860">
         <v>0.8473410733655758</v>
       </c>
       <c r="K860">
-        <v>21.8</v>
+        <v>22</v>
       </c>
       <c r="L860">
-        <v>30.99</v>
+        <v>31.22</v>
       </c>
       <c r="M860">
-        <v>21.15</v>
+        <v>20.75</v>
       </c>
       <c r="N860">
-        <v>30.9</v>
+        <v>30.94</v>
       </c>
       <c r="O860">
         <v>1</v>
       </c>
       <c r="P860" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="861" spans="1:16">
-      <c r="A861" s="1">
-        <v>0</v>
-      </c>
-      <c r="B861" t="s">
-        <v>155</v>
-      </c>
-      <c r="C861">
-        <v>12.42436853267676</v>
-      </c>
-      <c r="D861" t="s">
-        <v>268</v>
-      </c>
-      <c r="E861">
-        <v>12.66793093881254</v>
-      </c>
-      <c r="F861">
-        <v>1</v>
-      </c>
-      <c r="G861">
-        <v>0.04955563146732324</v>
-      </c>
-      <c r="H861">
-        <v>0.04869206906118746</v>
-      </c>
-      <c r="I861">
-        <v>0.2435624061357871</v>
-      </c>
-      <c r="J861">
-        <v>0.8516344709781304</v>
-      </c>
-      <c r="K861">
-        <v>21.8</v>
-      </c>
-      <c r="L861">
-        <v>30.99</v>
-      </c>
-      <c r="M861">
-        <v>21.15</v>
-      </c>
-      <c r="N861">
-        <v>30.68</v>
-      </c>
-      <c r="O861">
-        <v>1</v>
-      </c>
-      <c r="P861" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="862" spans="1:16">
-      <c r="A862" s="1">
-        <v>1</v>
-      </c>
-      <c r="B862" t="s">
-        <v>156</v>
-      </c>
-      <c r="C862">
-        <v>12.88793093881254</v>
-      </c>
-      <c r="D862" t="s">
-        <v>269</v>
-      </c>
-      <c r="E862">
-        <v>12.82342128010598</v>
-      </c>
-      <c r="F862">
-        <v>-1</v>
-      </c>
-      <c r="G862">
-        <v>0.04891206906118745</v>
-      </c>
-      <c r="H862">
-        <v>0.04833657871989402</v>
-      </c>
-      <c r="I862">
-        <v>0.06450965870656233</v>
-      </c>
-      <c r="J862">
-        <v>0.8516344709781304</v>
-      </c>
-      <c r="K862">
-        <v>21.15</v>
-      </c>
-      <c r="L862">
-        <v>30.9</v>
-      </c>
-      <c r="M862">
-        <v>20.85</v>
-      </c>
-      <c r="N862">
-        <v>30.58</v>
-      </c>
-      <c r="O862">
-        <v>1</v>
-      </c>
-      <c r="P862" t="s">
-        <v>267</v>
+        <v>347</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-00763-000063.xlsx
+++ b/s60_signal/position-00763-000063.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2592" uniqueCount="348">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2610" uniqueCount="352">
   <si>
     <t>trade_time</t>
   </si>
@@ -481,6 +481,9 @@
     <t>2021-11-26</t>
   </si>
   <si>
+    <t>2021-12-06</t>
+  </si>
+  <si>
     <t>2017-03-17</t>
   </si>
   <si>
@@ -814,6 +817,9 @@
     <t>2021-12-03</t>
   </si>
   <si>
+    <t>2021-12-07</t>
+  </si>
+  <si>
     <t>2017-02-08</t>
   </si>
   <si>
@@ -1058,6 +1064,12 @@
   </si>
   <si>
     <t>2021-11-24</t>
+  </si>
+  <si>
+    <t>2021-11-25</t>
+  </si>
+  <si>
+    <t>2021-11-29</t>
   </si>
 </sst>
 </file>
@@ -1415,7 +1427,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P860"/>
+  <dimension ref="A1:P866"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -1476,7 +1488,7 @@
         <v>8.357775317423281</v>
       </c>
       <c r="D2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E2">
         <v>9.239078272099615</v>
@@ -1512,7 +1524,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -1526,7 +1538,7 @@
         <v>9.433191964550923</v>
       </c>
       <c r="D3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E3">
         <v>9.285575452539577</v>
@@ -1562,7 +1574,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -1576,7 +1588,7 @@
         <v>9.420218808988363</v>
       </c>
       <c r="D4" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E4">
         <v>9.285575452539577</v>
@@ -1612,7 +1624,7 @@
         <v>1</v>
       </c>
       <c r="P4" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -1626,7 +1638,7 @@
         <v>9.27302954676334</v>
       </c>
       <c r="D5" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E5">
         <v>9.285575452539577</v>
@@ -1662,7 +1674,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -1676,7 +1688,7 @@
         <v>8.163141562328137</v>
       </c>
       <c r="D6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E6">
         <v>8.870417830135191</v>
@@ -1712,7 +1724,7 @@
         <v>1</v>
       </c>
       <c r="P6" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -1726,7 +1738,7 @@
         <v>8.167981542028786</v>
       </c>
       <c r="D7" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E7">
         <v>8.870417830135191</v>
@@ -1762,7 +1774,7 @@
         <v>1</v>
       </c>
       <c r="P7" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -1776,7 +1788,7 @@
         <v>9.039124544167011</v>
       </c>
       <c r="D8" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E8">
         <v>9.113918803782131</v>
@@ -1812,7 +1824,7 @@
         <v>1</v>
       </c>
       <c r="P8" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -1826,7 +1838,7 @@
         <v>9.052076876787602</v>
       </c>
       <c r="D9" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E9">
         <v>9.113918803782131</v>
@@ -1862,7 +1874,7 @@
         <v>1</v>
       </c>
       <c r="P9" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -1876,7 +1888,7 @@
         <v>8.972076876787604</v>
       </c>
       <c r="D10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E10">
         <v>9.113918803782131</v>
@@ -1912,7 +1924,7 @@
         <v>1</v>
       </c>
       <c r="P10" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -1926,7 +1938,7 @@
         <v>1.247895028504875</v>
       </c>
       <c r="D11" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E11">
         <v>5.93332434483856</v>
@@ -1962,7 +1974,7 @@
         <v>1</v>
       </c>
       <c r="P11" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -1976,7 +1988,7 @@
         <v>2.464515501370315</v>
       </c>
       <c r="D12" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E12">
         <v>5.93332434483856</v>
@@ -2012,7 +2024,7 @@
         <v>1</v>
       </c>
       <c r="P12" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -2062,7 +2074,7 @@
         <v>1</v>
       </c>
       <c r="P13" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -2076,7 +2088,7 @@
         <v>1.224092499726471</v>
       </c>
       <c r="D14" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E14">
         <v>5.913320521841428</v>
@@ -2112,7 +2124,7 @@
         <v>1</v>
       </c>
       <c r="P14" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -2126,7 +2138,7 @@
         <v>2.442814384300704</v>
       </c>
       <c r="D15" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E15">
         <v>5.913320521841428</v>
@@ -2162,7 +2174,7 @@
         <v>1</v>
       </c>
       <c r="P15" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -2176,7 +2188,7 @@
         <v>8.399951396166678</v>
       </c>
       <c r="D16" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E16">
         <v>7.154665097353277</v>
@@ -2212,7 +2224,7 @@
         <v>1</v>
       </c>
       <c r="P16" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -2226,7 +2238,7 @@
         <v>1.231818368992485</v>
       </c>
       <c r="D17" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E17">
         <v>5.919813400087062</v>
@@ -2262,7 +2274,7 @@
         <v>1</v>
       </c>
       <c r="P17" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -2276,7 +2288,7 @@
         <v>2.449858173427781</v>
       </c>
       <c r="D18" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E18">
         <v>5.919813400087062</v>
@@ -2312,7 +2324,7 @@
         <v>1</v>
       </c>
       <c r="P18" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -2362,7 +2374,7 @@
         <v>1</v>
       </c>
       <c r="P19" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="20" spans="1:16">
@@ -2376,7 +2388,7 @@
         <v>1.145797529921555</v>
       </c>
       <c r="D20" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E20">
         <v>5.847520844331356</v>
@@ -2412,7 +2424,7 @@
         <v>1</v>
       </c>
       <c r="P20" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -2426,7 +2438,7 @@
         <v>2.37143170385038</v>
       </c>
       <c r="D21" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E21">
         <v>5.847520844331356</v>
@@ -2462,7 +2474,7 @@
         <v>1</v>
       </c>
       <c r="P21" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -2476,7 +2488,7 @@
         <v>8.323251570058975</v>
       </c>
       <c r="D22" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E22">
         <v>6.49770468378167</v>
@@ -2512,7 +2524,7 @@
         <v>1</v>
       </c>
       <c r="P22" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="23" spans="1:16">
@@ -2526,7 +2538,7 @@
         <v>8.298928068060523</v>
       </c>
       <c r="D23" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E23">
         <v>6.513844529583032</v>
@@ -2612,7 +2624,7 @@
         <v>1</v>
       </c>
       <c r="P24" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="25" spans="1:16">
@@ -2662,7 +2674,7 @@
         <v>1</v>
       </c>
       <c r="P25" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="26" spans="1:16">
@@ -2676,7 +2688,7 @@
         <v>4.521898732172186</v>
       </c>
       <c r="D26" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E26">
         <v>7.471272137184702</v>
@@ -2712,7 +2724,7 @@
         <v>1</v>
       </c>
       <c r="P26" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="27" spans="1:16">
@@ -2762,7 +2774,7 @@
         <v>1</v>
       </c>
       <c r="P27" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="28" spans="1:16">
@@ -2812,7 +2824,7 @@
         <v>1</v>
       </c>
       <c r="P28" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -2826,7 +2838,7 @@
         <v>10.06347633639325</v>
       </c>
       <c r="D29" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E29">
         <v>8.926863738767604</v>
@@ -2862,7 +2874,7 @@
         <v>1</v>
       </c>
       <c r="P29" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -3026,7 +3038,7 @@
         <v>10.57243502356749</v>
       </c>
       <c r="D33" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E33">
         <v>11.2289160904059</v>
@@ -3076,7 +3088,7 @@
         <v>10.58025171866791</v>
       </c>
       <c r="D34" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E34">
         <v>11.2289160904059</v>
@@ -3126,7 +3138,7 @@
         <v>6.89098969886382</v>
       </c>
       <c r="D35" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E35">
         <v>9.162922766970905</v>
@@ -3162,7 +3174,7 @@
         <v>1</v>
       </c>
       <c r="P35" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -3212,7 +3224,7 @@
         <v>1</v>
       </c>
       <c r="P36" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="37" spans="1:16">
@@ -3262,7 +3274,7 @@
         <v>1</v>
       </c>
       <c r="P37" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="38" spans="1:16">
@@ -3312,7 +3324,7 @@
         <v>1</v>
       </c>
       <c r="P38" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="39" spans="1:16">
@@ -3326,7 +3338,7 @@
         <v>10.57710841036202</v>
       </c>
       <c r="D39" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E39">
         <v>10.91875227586742</v>
@@ -3362,7 +3374,7 @@
         <v>1</v>
       </c>
       <c r="P39" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="40" spans="1:16">
@@ -3376,7 +3388,7 @@
         <v>10.58544939256899</v>
       </c>
       <c r="D40" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E40">
         <v>10.91875227586742</v>
@@ -3412,7 +3424,7 @@
         <v>1</v>
       </c>
       <c r="P40" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="41" spans="1:16">
@@ -3462,7 +3474,7 @@
         <v>1</v>
       </c>
       <c r="P41" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="42" spans="1:16">
@@ -3512,7 +3524,7 @@
         <v>1</v>
       </c>
       <c r="P42" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="43" spans="1:16">
@@ -3562,7 +3574,7 @@
         <v>1</v>
       </c>
       <c r="P43" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="44" spans="1:16">
@@ -3576,7 +3588,7 @@
         <v>10.50706987192051</v>
       </c>
       <c r="D44" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E44">
         <v>9.836117792760128</v>
@@ -3612,7 +3624,7 @@
         <v>1</v>
       </c>
       <c r="P44" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -3776,7 +3788,7 @@
         <v>11.00643298606593</v>
       </c>
       <c r="D48" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E48">
         <v>10.08970532444388</v>
@@ -3862,7 +3874,7 @@
         <v>1</v>
       </c>
       <c r="P49" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="50" spans="1:16">
@@ -3912,7 +3924,7 @@
         <v>1</v>
       </c>
       <c r="P50" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="51" spans="1:16">
@@ -3962,7 +3974,7 @@
         <v>1</v>
       </c>
       <c r="P51" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="52" spans="1:16">
@@ -4012,7 +4024,7 @@
         <v>1</v>
       </c>
       <c r="P52" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="53" spans="1:16">
@@ -4062,7 +4074,7 @@
         <v>1</v>
       </c>
       <c r="P53" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="54" spans="1:16">
@@ -4112,7 +4124,7 @@
         <v>1</v>
       </c>
       <c r="P54" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="55" spans="1:16">
@@ -4126,7 +4138,7 @@
         <v>10.96451987407661</v>
       </c>
       <c r="D55" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E55">
         <v>9.918825279734797</v>
@@ -4162,7 +4174,7 @@
         <v>1</v>
       </c>
       <c r="P55" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="56" spans="1:16">
@@ -4212,7 +4224,7 @@
         <v>1</v>
       </c>
       <c r="P56" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="57" spans="1:16">
@@ -4262,7 +4274,7 @@
         <v>1</v>
       </c>
       <c r="P57" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="58" spans="1:16">
@@ -4312,7 +4324,7 @@
         <v>1</v>
       </c>
       <c r="P58" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="59" spans="1:16">
@@ -4362,7 +4374,7 @@
         <v>1</v>
       </c>
       <c r="P59" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="60" spans="1:16">
@@ -4412,7 +4424,7 @@
         <v>1</v>
       </c>
       <c r="P60" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="61" spans="1:16">
@@ -4462,7 +4474,7 @@
         <v>1</v>
       </c>
       <c r="P61" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="62" spans="1:16">
@@ -4512,7 +4524,7 @@
         <v>1</v>
       </c>
       <c r="P62" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="63" spans="1:16">
@@ -4526,7 +4538,7 @@
         <v>10.70295290100141</v>
       </c>
       <c r="D63" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E63">
         <v>8.905400692050126</v>
@@ -4562,7 +4574,7 @@
         <v>1</v>
       </c>
       <c r="P63" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="64" spans="1:16">
@@ -4576,7 +4588,7 @@
         <v>11.20304517915771</v>
       </c>
       <c r="D64" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E64">
         <v>8.905400692050126</v>
@@ -4612,7 +4624,7 @@
         <v>1</v>
       </c>
       <c r="P64" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="65" spans="1:16">
@@ -4662,7 +4674,7 @@
         <v>1</v>
       </c>
       <c r="P65" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="66" spans="1:16">
@@ -4676,7 +4688,7 @@
         <v>10.69564352718713</v>
       </c>
       <c r="D66" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E66">
         <v>10.68408451836947</v>
@@ -4712,7 +4724,7 @@
         <v>1</v>
       </c>
       <c r="P66" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="67" spans="1:16">
@@ -4726,7 +4738,7 @@
         <v>11.03068966626528</v>
       </c>
       <c r="D67" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E67">
         <v>10.68408451836947</v>
@@ -4762,7 +4774,7 @@
         <v>1</v>
       </c>
       <c r="P67" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="68" spans="1:16">
@@ -4812,7 +4824,7 @@
         <v>1</v>
       </c>
       <c r="P68" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="69" spans="1:16">
@@ -4826,7 +4838,7 @@
         <v>10.52605158161457</v>
       </c>
       <c r="D69" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E69">
         <v>8.71498607743235</v>
@@ -4862,7 +4874,7 @@
         <v>1</v>
       </c>
       <c r="P69" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="70" spans="1:16">
@@ -4876,7 +4888,7 @@
         <v>11.02061569354003</v>
       </c>
       <c r="D70" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E70">
         <v>8.71498607743235</v>
@@ -4912,7 +4924,7 @@
         <v>1</v>
       </c>
       <c r="P70" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="71" spans="1:16">
@@ -4962,7 +4974,7 @@
         <v>1</v>
       </c>
       <c r="P71" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="72" spans="1:16">
@@ -4976,7 +4988,7 @@
         <v>10.52396325368498</v>
       </c>
       <c r="D72" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E72">
         <v>8.806051581614568</v>
@@ -5012,7 +5024,7 @@
         <v>1</v>
       </c>
       <c r="P72" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="73" spans="1:16">
@@ -5026,7 +5038,7 @@
         <v>10.8562453096477</v>
       </c>
       <c r="D73" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E73">
         <v>8.806051581614568</v>
@@ -5062,7 +5074,7 @@
         <v>1</v>
       </c>
       <c r="P73" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="74" spans="1:16">
@@ -5076,7 +5088,7 @@
         <v>10.34525014922946</v>
       </c>
       <c r="D74" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E74">
         <v>8.520373424517821</v>
@@ -5126,7 +5138,7 @@
         <v>10.83416421639288</v>
       </c>
       <c r="D75" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E75">
         <v>8.520373424517821</v>
@@ -5276,7 +5288,7 @@
         <v>10.34849797468624</v>
       </c>
       <c r="D78" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E78">
         <v>8.625250149229462</v>
@@ -5326,7 +5338,7 @@
         <v>10.67795500826794</v>
       </c>
       <c r="D79" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E79">
         <v>8.625250149229462</v>
@@ -5376,7 +5388,7 @@
         <v>10.18864383981015</v>
       </c>
       <c r="D80" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E80">
         <v>8.351804133128983</v>
@@ -5412,7 +5424,7 @@
         <v>1</v>
       </c>
       <c r="P80" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="81" spans="1:16">
@@ -5426,7 +5438,7 @@
         <v>10.67266395980422</v>
       </c>
       <c r="D81" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E81">
         <v>8.351804133128983</v>
@@ -5462,7 +5474,7 @@
         <v>1</v>
       </c>
       <c r="P81" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="82" spans="1:16">
@@ -5512,7 +5524,7 @@
         <v>1</v>
       </c>
       <c r="P82" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="83" spans="1:16">
@@ -5562,7 +5574,7 @@
         <v>1</v>
       </c>
       <c r="P83" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="84" spans="1:16">
@@ -5576,7 +5588,7 @@
         <v>10.19651372648243</v>
       </c>
       <c r="D84" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E84">
         <v>8.468643839810152</v>
@@ -5612,7 +5624,7 @@
         <v>1</v>
       </c>
       <c r="P84" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="85" spans="1:16">
@@ -5626,7 +5638,7 @@
         <v>10.52352378647946</v>
       </c>
       <c r="D85" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E85">
         <v>8.468643839810152</v>
@@ -5662,7 +5674,7 @@
         <v>1</v>
       </c>
       <c r="P85" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="86" spans="1:16">
@@ -5676,7 +5688,7 @@
         <v>-1.278554542763944</v>
       </c>
       <c r="D86" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E86">
         <v>0.01420169243589342</v>
@@ -5712,7 +5724,7 @@
         <v>1</v>
       </c>
       <c r="P86" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="87" spans="1:16">
@@ -5726,7 +5738,7 @@
         <v>-2.406586639852707</v>
       </c>
       <c r="D87" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E87">
         <v>0.01420169243589342</v>
@@ -5762,7 +5774,7 @@
         <v>1</v>
       </c>
       <c r="P87" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="88" spans="1:16">
@@ -5812,7 +5824,7 @@
         <v>1</v>
       </c>
       <c r="P88" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="89" spans="1:16">
@@ -5826,7 +5838,7 @@
         <v>-1.341212522415489</v>
       </c>
       <c r="D89" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E89">
         <v>0.1246199151405953</v>
@@ -5862,7 +5874,7 @@
         <v>1</v>
       </c>
       <c r="P89" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="90" spans="1:16">
@@ -5876,7 +5888,7 @@
         <v>-2.475362406493851</v>
       </c>
       <c r="D90" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E90">
         <v>0.1246199151405953</v>
@@ -5912,7 +5924,7 @@
         <v>1</v>
       </c>
       <c r="P90" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="91" spans="1:16">
@@ -5962,7 +5974,7 @@
         <v>1</v>
       </c>
       <c r="P91" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="92" spans="1:16">
@@ -5976,7 +5988,7 @@
         <v>-2.566016320350375</v>
       </c>
       <c r="D92" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E92">
         <v>0.02954385914472724</v>
@@ -6126,7 +6138,7 @@
         <v>-2.663355023194697</v>
       </c>
       <c r="D95" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E95">
         <v>0.03872013419191234</v>
@@ -6162,7 +6174,7 @@
         <v>1</v>
       </c>
       <c r="P95" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="96" spans="1:16">
@@ -6212,7 +6224,7 @@
         <v>1</v>
       </c>
       <c r="P96" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="97" spans="1:16">
@@ -6262,7 +6274,7 @@
         <v>1</v>
       </c>
       <c r="P97" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="98" spans="1:16">
@@ -6276,7 +6288,7 @@
         <v>-2.748103967913549</v>
       </c>
       <c r="D98" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E98">
         <v>-0.04760949385741853</v>
@@ -6312,7 +6324,7 @@
         <v>1</v>
       </c>
       <c r="P98" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="99" spans="1:16">
@@ -6326,7 +6338,7 @@
         <v>1.170412609918055</v>
       </c>
       <c r="D99" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E99">
         <v>1.469846093587645</v>
@@ -6362,7 +6374,7 @@
         <v>1</v>
       </c>
       <c r="P99" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="100" spans="1:16">
@@ -6376,7 +6388,7 @@
         <v>1.197090465141786</v>
       </c>
       <c r="D100" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E100">
         <v>1.469846093587645</v>
@@ -6412,7 +6424,7 @@
         <v>1</v>
       </c>
       <c r="P100" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="101" spans="1:16">
@@ -6426,7 +6438,7 @@
         <v>-2.807295369205091</v>
       </c>
       <c r="D101" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E101">
         <v>0.3363998775430197</v>
@@ -6462,7 +6474,7 @@
         <v>1</v>
       </c>
       <c r="P101" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="102" spans="1:16">
@@ -6512,7 +6524,7 @@
         <v>1</v>
       </c>
       <c r="P102" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="103" spans="1:16">
@@ -6612,7 +6624,7 @@
         <v>1</v>
       </c>
       <c r="P104" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="105" spans="1:16">
@@ -6626,7 +6638,7 @@
         <v>1.819034812951433</v>
       </c>
       <c r="D105" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E105">
         <v>1.780382458905816</v>
@@ -6662,7 +6674,7 @@
         <v>1</v>
       </c>
       <c r="P105" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="106" spans="1:16">
@@ -6676,7 +6688,7 @@
         <v>1.278232359359254</v>
       </c>
       <c r="D106" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E106">
         <v>1.780382458905816</v>
@@ -6712,7 +6724,7 @@
         <v>1</v>
       </c>
       <c r="P106" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="107" spans="1:16">
@@ -6726,7 +6738,7 @@
         <v>-1.27500579580901</v>
       </c>
       <c r="D107" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E107">
         <v>0.204597470791132</v>
@@ -6762,7 +6774,7 @@
         <v>1</v>
       </c>
       <c r="P107" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="108" spans="1:16">
@@ -6776,7 +6788,7 @@
         <v>-1.164182632644362</v>
       </c>
       <c r="D108" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E108">
         <v>0.204597470791132</v>
@@ -6812,7 +6824,7 @@
         <v>1</v>
       </c>
       <c r="P108" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="109" spans="1:16">
@@ -6862,7 +6874,7 @@
         <v>1</v>
       </c>
       <c r="P109" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="110" spans="1:16">
@@ -6912,7 +6924,7 @@
         <v>1</v>
       </c>
       <c r="P110" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="111" spans="1:16">
@@ -6926,7 +6938,7 @@
         <v>-1.330656541117063</v>
       </c>
       <c r="D111" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E111">
         <v>0.1498300706466971</v>
@@ -6962,7 +6974,7 @@
         <v>1</v>
       </c>
       <c r="P111" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="112" spans="1:16">
@@ -6976,7 +6988,7 @@
         <v>-1.089957636312631</v>
       </c>
       <c r="D112" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E112">
         <v>0.1498300706466971</v>
@@ -7012,7 +7024,7 @@
         <v>1</v>
       </c>
       <c r="P112" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="113" spans="1:16">
@@ -7026,7 +7038,7 @@
         <v>1.663161219313913</v>
       </c>
       <c r="D113" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E113">
         <v>1.394552474924428</v>
@@ -7062,7 +7074,7 @@
         <v>1</v>
       </c>
       <c r="P113" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="114" spans="1:16">
@@ -7076,7 +7088,7 @@
         <v>2.020453841772007</v>
       </c>
       <c r="D114" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E114">
         <v>1.394552474924428</v>
@@ -7112,7 +7124,7 @@
         <v>1</v>
       </c>
       <c r="P114" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="115" spans="1:16">
@@ -7162,7 +7174,7 @@
         <v>1</v>
       </c>
       <c r="P115" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="116" spans="1:16">
@@ -7212,7 +7224,7 @@
         <v>1</v>
       </c>
       <c r="P116" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="117" spans="1:16">
@@ -7262,7 +7274,7 @@
         <v>1</v>
       </c>
       <c r="P117" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="118" spans="1:16">
@@ -7312,7 +7324,7 @@
         <v>1</v>
       </c>
       <c r="P118" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="119" spans="1:16">
@@ -7362,7 +7374,7 @@
         <v>1</v>
       </c>
       <c r="P119" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="120" spans="1:16">
@@ -7412,7 +7424,7 @@
         <v>1</v>
       </c>
       <c r="P120" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="121" spans="1:16">
@@ -7462,7 +7474,7 @@
         <v>1</v>
       </c>
       <c r="P121" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="122" spans="1:16">
@@ -7512,7 +7524,7 @@
         <v>1</v>
       </c>
       <c r="P122" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="123" spans="1:16">
@@ -7562,7 +7574,7 @@
         <v>1</v>
       </c>
       <c r="P123" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="124" spans="1:16">
@@ -7612,7 +7624,7 @@
         <v>1</v>
       </c>
       <c r="P124" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="125" spans="1:16">
@@ -7726,7 +7738,7 @@
         <v>1.583716178161136</v>
       </c>
       <c r="D127" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E127">
         <v>1.731188504841963</v>
@@ -7776,7 +7788,7 @@
         <v>1.943294205912665</v>
       </c>
       <c r="D128" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E128">
         <v>1.731188504841963</v>
@@ -7826,7 +7838,7 @@
         <v>1.440029121201585</v>
       </c>
       <c r="D129" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E129">
         <v>1.731188504841963</v>
@@ -7912,7 +7924,7 @@
         <v>1</v>
       </c>
       <c r="P130" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="131" spans="1:16">
@@ -7962,7 +7974,7 @@
         <v>1</v>
       </c>
       <c r="P131" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="132" spans="1:16">
@@ -8012,7 +8024,7 @@
         <v>1</v>
       </c>
       <c r="P132" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="133" spans="1:16">
@@ -8062,7 +8074,7 @@
         <v>1</v>
       </c>
       <c r="P133" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="134" spans="1:16">
@@ -8112,7 +8124,7 @@
         <v>1</v>
       </c>
       <c r="P134" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="135" spans="1:16">
@@ -8126,7 +8138,7 @@
         <v>-0.8820242128746258</v>
       </c>
       <c r="D135" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E135">
         <v>0.3526024044326252</v>
@@ -8162,7 +8174,7 @@
         <v>1</v>
       </c>
       <c r="P135" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="136" spans="1:16">
@@ -8176,7 +8188,7 @@
         <v>-1.173427909927172</v>
       </c>
       <c r="D136" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E136">
         <v>0.3526024044326252</v>
@@ -8212,7 +8224,7 @@
         <v>1</v>
       </c>
       <c r="P136" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="137" spans="1:16">
@@ -8262,7 +8274,7 @@
         <v>1</v>
       </c>
       <c r="P137" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="138" spans="1:16">
@@ -8312,7 +8324,7 @@
         <v>1</v>
       </c>
       <c r="P138" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="139" spans="1:16">
@@ -8362,7 +8374,7 @@
         <v>1</v>
       </c>
       <c r="P139" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="140" spans="1:16">
@@ -8676,7 +8688,7 @@
         <v>1.916709703800588</v>
       </c>
       <c r="D146" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E146">
         <v>1.625228926806798</v>
@@ -8726,7 +8738,7 @@
         <v>1.775844332123576</v>
       </c>
       <c r="D147" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E147">
         <v>1.625228926806798</v>
@@ -8776,7 +8788,7 @@
         <v>1.706459737440355</v>
       </c>
       <c r="D148" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E148">
         <v>1.625228926806798</v>
@@ -8826,7 +8838,7 @@
         <v>1.898407474064776</v>
       </c>
       <c r="D149" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E149">
         <v>1.579058157468399</v>
@@ -8862,7 +8874,7 @@
         <v>1</v>
       </c>
       <c r="P149" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="150" spans="1:16">
@@ -8876,7 +8888,7 @@
         <v>1.757671173119327</v>
       </c>
       <c r="D150" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E150">
         <v>1.579058157468399</v>
@@ -8912,7 +8924,7 @@
         <v>1</v>
       </c>
       <c r="P150" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="151" spans="1:16">
@@ -8926,7 +8938,7 @@
         <v>1.688493091606606</v>
       </c>
       <c r="D151" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E151">
         <v>1.579058157468399</v>
@@ -8962,7 +8974,7 @@
         <v>1</v>
       </c>
       <c r="P151" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="152" spans="1:16">
@@ -9012,7 +9024,7 @@
         <v>1</v>
       </c>
       <c r="P152" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="153" spans="1:16">
@@ -9062,7 +9074,7 @@
         <v>1</v>
       </c>
       <c r="P153" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="154" spans="1:16">
@@ -9112,7 +9124,7 @@
         <v>1</v>
       </c>
       <c r="P154" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="155" spans="1:16">
@@ -9162,7 +9174,7 @@
         <v>1</v>
       </c>
       <c r="P155" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="156" spans="1:16">
@@ -9212,7 +9224,7 @@
         <v>1</v>
       </c>
       <c r="P156" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="157" spans="1:16">
@@ -9262,7 +9274,7 @@
         <v>1</v>
       </c>
       <c r="P157" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="158" spans="1:16">
@@ -9412,7 +9424,7 @@
         <v>1</v>
       </c>
       <c r="P160" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="161" spans="1:16">
@@ -9462,7 +9474,7 @@
         <v>1</v>
       </c>
       <c r="P161" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="162" spans="1:16">
@@ -9512,7 +9524,7 @@
         <v>1</v>
       </c>
       <c r="P162" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="163" spans="1:16">
@@ -9562,7 +9574,7 @@
         <v>1</v>
       </c>
       <c r="P163" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="164" spans="1:16">
@@ -9576,7 +9588,7 @@
         <v>2.0418888555804</v>
       </c>
       <c r="D164" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E164">
         <v>2.091052252009925</v>
@@ -9626,7 +9638,7 @@
         <v>2.437529947263654</v>
       </c>
       <c r="D165" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E165">
         <v>2.091052252009925</v>
@@ -9676,7 +9688,7 @@
         <v>2.035427646090795</v>
       </c>
       <c r="D166" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E166">
         <v>1.677256780401082</v>
@@ -9712,7 +9724,7 @@
         <v>1</v>
       </c>
       <c r="P166" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="167" spans="1:16">
@@ -9726,7 +9738,7 @@
         <v>2.4319519246827</v>
       </c>
       <c r="D167" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E167">
         <v>1.677256780401082</v>
@@ -9762,7 +9774,7 @@
         <v>1</v>
       </c>
       <c r="P167" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="168" spans="1:16">
@@ -9812,7 +9824,7 @@
         <v>1</v>
       </c>
       <c r="P168" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="169" spans="1:16">
@@ -9862,7 +9874,7 @@
         <v>1</v>
       </c>
       <c r="P169" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="170" spans="1:16">
@@ -9912,7 +9924,7 @@
         <v>1</v>
       </c>
       <c r="P170" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="171" spans="1:16">
@@ -9962,7 +9974,7 @@
         <v>1</v>
       </c>
       <c r="P171" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="172" spans="1:16">
@@ -10012,7 +10024,7 @@
         <v>1</v>
       </c>
       <c r="P172" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="173" spans="1:16">
@@ -10026,7 +10038,7 @@
         <v>2.053037839433713</v>
       </c>
       <c r="D173" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E173">
         <v>2.029053723158555</v>
@@ -10062,7 +10074,7 @@
         <v>1</v>
       </c>
       <c r="P173" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="174" spans="1:16">
@@ -10176,7 +10188,7 @@
         <v>2.072439051471395</v>
       </c>
       <c r="D176" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E176">
         <v>2.198537473651809</v>
@@ -10212,7 +10224,7 @@
         <v>1</v>
       </c>
       <c r="P176" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="177" spans="1:16">
@@ -10226,7 +10238,7 @@
         <v>2.176038435736924</v>
       </c>
       <c r="D177" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E177">
         <v>2.198537473651809</v>
@@ -10262,7 +10274,7 @@
         <v>1</v>
       </c>
       <c r="P177" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="178" spans="1:16">
@@ -10312,7 +10324,7 @@
         <v>1</v>
       </c>
       <c r="P178" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="179" spans="1:16">
@@ -10376,7 +10388,7 @@
         <v>2.199572666349018</v>
       </c>
       <c r="D180" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E180">
         <v>2.369622868222606</v>
@@ -10576,7 +10588,7 @@
         <v>2.441204477380014</v>
       </c>
       <c r="D184" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E184">
         <v>3.019740173907834</v>
@@ -10676,7 +10688,7 @@
         <v>2.450942264059425</v>
       </c>
       <c r="D186" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E186">
         <v>3.396065694761221</v>
@@ -10726,7 +10738,7 @@
         <v>2.93271297523739</v>
       </c>
       <c r="D187" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E187">
         <v>3.396065694761221</v>
@@ -10826,7 +10838,7 @@
         <v>2.613291041571109</v>
       </c>
       <c r="D189" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E189">
         <v>1.747095958240026</v>
@@ -10876,7 +10888,7 @@
         <v>2.94332933323569</v>
       </c>
       <c r="D190" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E190">
         <v>3.513960124909904</v>
@@ -11026,7 +11038,7 @@
         <v>2.630002520413537</v>
       </c>
       <c r="D193" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E193">
         <v>1.763414225815572</v>
@@ -11076,7 +11088,7 @@
         <v>2.960405936825934</v>
       </c>
       <c r="D194" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E194">
         <v>2.688557154970242</v>
@@ -11276,7 +11288,7 @@
         <v>2.642059072099817</v>
       </c>
       <c r="D198" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E198">
         <v>1.775187093932763</v>
@@ -11326,7 +11338,7 @@
         <v>2.972725908969226</v>
       </c>
       <c r="D199" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E199">
         <v>2.375803028433923</v>
@@ -11476,7 +11488,7 @@
         <v>2.666955617984192</v>
       </c>
       <c r="D202" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E202">
         <v>1.799497838737505</v>
@@ -11526,7 +11538,7 @@
         <v>2.998166412998973</v>
       </c>
       <c r="D203" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E203">
         <v>1.736641978102437</v>
@@ -11676,7 +11688,7 @@
         <v>2.973643871143521</v>
       </c>
       <c r="D206" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E206">
         <v>1.818524938691256</v>
@@ -11726,7 +11738,7 @@
         <v>3.018077732744034</v>
       </c>
       <c r="D207" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E207">
         <v>1.759533446033025</v>
@@ -11876,7 +11888,7 @@
         <v>2.990082102112254</v>
       </c>
       <c r="D210" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E210">
         <v>1.83485077149952</v>
@@ -11926,7 +11938,7 @@
         <v>3.03516225313547</v>
       </c>
       <c r="D211" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E211">
         <v>1.779175024575153</v>
@@ -12012,7 +12024,7 @@
         <v>1</v>
       </c>
       <c r="P212" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="213" spans="1:16">
@@ -12062,7 +12074,7 @@
         <v>1</v>
       </c>
       <c r="P213" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="214" spans="1:16">
@@ -12076,7 +12088,7 @@
         <v>3.005496469975766</v>
       </c>
       <c r="D214" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E214">
         <v>1.850159741975929</v>
@@ -12112,7 +12124,7 @@
         <v>1</v>
       </c>
       <c r="P214" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="215" spans="1:16">
@@ -12126,7 +12138,7 @@
         <v>3.051182655974811</v>
       </c>
       <c r="D215" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E215">
         <v>1.797593217971041</v>
@@ -12162,7 +12174,7 @@
         <v>1</v>
       </c>
       <c r="P215" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="216" spans="1:16">
@@ -12276,7 +12288,7 @@
         <v>3.018931533510157</v>
       </c>
       <c r="D218" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E218">
         <v>1.863502941828035</v>
@@ -12326,7 +12338,7 @@
         <v>3.06514593568235</v>
       </c>
       <c r="D219" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E219">
         <v>1.813646396450594</v>
@@ -12476,7 +12488,7 @@
         <v>3.033933076549712</v>
       </c>
       <c r="D222" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E222">
         <v>1.878401910214327</v>
@@ -12526,7 +12538,7 @@
         <v>3.080737282978161</v>
       </c>
       <c r="D223" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E223">
         <v>1.831571317108114</v>
@@ -12576,7 +12588,7 @@
         <v>1.639859271051932</v>
       </c>
       <c r="D224" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E224">
         <v>1.9209216037227</v>
@@ -12726,7 +12738,7 @@
         <v>3.05833801181463</v>
       </c>
       <c r="D227" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E227">
         <v>1.902639974127007</v>
@@ -12776,7 +12788,7 @@
         <v>3.106101728518452</v>
       </c>
       <c r="D228" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E228">
         <v>1.860732085911838</v>
@@ -12862,7 +12874,7 @@
         <v>1</v>
       </c>
       <c r="P229" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="230" spans="1:16">
@@ -12912,7 +12924,7 @@
         <v>1</v>
       </c>
       <c r="P230" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="231" spans="1:16">
@@ -12926,7 +12938,7 @@
         <v>3.085055612872655</v>
       </c>
       <c r="D231" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E231">
         <v>1.929174890733353</v>
@@ -12962,7 +12974,7 @@
         <v>1</v>
       </c>
       <c r="P231" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="232" spans="1:16">
@@ -12976,7 +12988,7 @@
         <v>3.13386976517363</v>
       </c>
       <c r="D232" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E232">
         <v>1.892656193842708</v>
@@ -13012,7 +13024,7 @@
         <v>1</v>
       </c>
       <c r="P232" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="233" spans="1:16">
@@ -13076,7 +13088,7 @@
         <v>3.103034611570727</v>
       </c>
       <c r="D234" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E234">
         <v>1.947030956106994</v>
@@ -13126,7 +13138,7 @@
         <v>3.152555630487182</v>
       </c>
       <c r="D235" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E235">
         <v>1.914138792287073</v>
@@ -13176,7 +13188,7 @@
         <v>1.641725609550694</v>
       </c>
       <c r="D236" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E236">
         <v>1.89319910743864</v>
@@ -13262,7 +13274,7 @@
         <v>1</v>
       </c>
       <c r="P237" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="238" spans="1:16">
@@ -13276,7 +13288,7 @@
         <v>3.11979974827751</v>
       </c>
       <c r="D238" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E238">
         <v>1.963681459400396</v>
@@ -13312,7 +13324,7 @@
         <v>1</v>
       </c>
       <c r="P238" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="239" spans="1:16">
@@ -13326,7 +13338,7 @@
         <v>3.169979909320897</v>
       </c>
       <c r="D239" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E239">
         <v>1.934170981275177</v>
@@ -13362,7 +13374,7 @@
         <v>1</v>
       </c>
       <c r="P239" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="240" spans="1:16">
@@ -13376,7 +13388,7 @@
         <v>1.664480342106565</v>
       </c>
       <c r="D240" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E240">
         <v>2.221652319966786</v>
@@ -13412,7 +13424,7 @@
         <v>1</v>
       </c>
       <c r="P240" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="241" spans="1:16">
@@ -13476,7 +13488,7 @@
         <v>3.136490860930856</v>
       </c>
       <c r="D242" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E242">
         <v>1.980258444787738</v>
@@ -13526,7 +13538,7 @@
         <v>3.187327253753777</v>
       </c>
       <c r="D243" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E243">
         <v>1.954114721009688</v>
@@ -13726,7 +13738,7 @@
         <v>3.154470288152615</v>
       </c>
       <c r="D247" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E247">
         <v>1.998114935754989</v>
@@ -13776,7 +13788,7 @@
         <v>3.206013564438956</v>
       </c>
       <c r="D248" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E248">
         <v>1.975597831484915</v>
@@ -13962,7 +13974,7 @@
         <v>1</v>
       </c>
       <c r="P251" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="252" spans="1:16">
@@ -14012,7 +14024,7 @@
         <v>1</v>
       </c>
       <c r="P252" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="253" spans="1:16">
@@ -14026,7 +14038,7 @@
         <v>3.175183381627829</v>
       </c>
       <c r="D253" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E253">
         <v>2.406837822852639</v>
@@ -14062,7 +14074,7 @@
         <v>1</v>
       </c>
       <c r="P253" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="254" spans="1:16">
@@ -14076,7 +14088,7 @@
         <v>3.227541018854222</v>
       </c>
       <c r="D254" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E254">
         <v>2.000347322662993</v>
@@ -14112,7 +14124,7 @@
         <v>1</v>
       </c>
       <c r="P254" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="255" spans="1:16">
@@ -14162,7 +14174,7 @@
         <v>1</v>
       </c>
       <c r="P255" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="256" spans="1:16">
@@ -14212,7 +14224,7 @@
         <v>1</v>
       </c>
       <c r="P256" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="257" spans="1:16">
@@ -14326,7 +14338,7 @@
         <v>3.194491499183421</v>
       </c>
       <c r="D259" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E259">
         <v>2.42485873257119</v>
@@ -14376,7 +14388,7 @@
         <v>3.247608258980375</v>
       </c>
       <c r="D260" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E260">
         <v>2.023418047742236</v>
@@ -14626,7 +14638,7 @@
         <v>3.213727962726566</v>
       </c>
       <c r="D265" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E265">
         <v>2.442812765211459</v>
@@ -14676,7 +14688,7 @@
         <v>3.26760102792778</v>
       </c>
       <c r="D266" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E266">
         <v>2.046403155463022</v>
@@ -14876,7 +14888,7 @@
         <v>3.233647867837396</v>
       </c>
       <c r="D270" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E270">
         <v>2.461404676648234</v>
@@ -14926,7 +14938,7 @@
         <v>3.288304108795105</v>
       </c>
       <c r="D271" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E271">
         <v>2.070204888236475</v>
@@ -15126,7 +15138,7 @@
         <v>3.249417008017017</v>
       </c>
       <c r="D275" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E275">
         <v>2.476122540815881</v>
@@ -15176,7 +15188,7 @@
         <v>3.304693232263839</v>
       </c>
       <c r="D276" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E276">
         <v>2.089046989066485</v>
@@ -15326,7 +15338,7 @@
         <v>1.914875661806953</v>
       </c>
       <c r="D279" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E279">
         <v>2.109898465499843</v>
@@ -15412,7 +15424,7 @@
         <v>1</v>
       </c>
       <c r="P280" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="281" spans="1:16">
@@ -15426,7 +15438,7 @@
         <v>3.261163134684622</v>
       </c>
       <c r="D281" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E281">
         <v>2.487085592372312</v>
@@ -15462,7 +15474,7 @@
         <v>1</v>
       </c>
       <c r="P281" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="282" spans="1:16">
@@ -15476,7 +15488,7 @@
         <v>3.316901172458547</v>
       </c>
       <c r="D282" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E282">
         <v>2.103082104520595</v>
@@ -15512,7 +15524,7 @@
         <v>1</v>
       </c>
       <c r="P282" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="283" spans="1:16">
@@ -15562,7 +15574,7 @@
         <v>1</v>
       </c>
       <c r="P283" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="284" spans="1:16">
@@ -15612,7 +15624,7 @@
         <v>1</v>
       </c>
       <c r="P284" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="285" spans="1:16">
@@ -15626,7 +15638,7 @@
         <v>1.930296217842372</v>
       </c>
       <c r="D285" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E285">
         <v>2.383746445952788</v>
@@ -15662,7 +15674,7 @@
         <v>1</v>
       </c>
       <c r="P285" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="286" spans="1:16">
@@ -15712,7 +15724,7 @@
         <v>1</v>
       </c>
       <c r="P286" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="287" spans="1:16">
@@ -15726,7 +15738,7 @@
         <v>3.267778188252251</v>
       </c>
       <c r="D287" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E287">
         <v>2.493259642368766</v>
@@ -15762,7 +15774,7 @@
         <v>1</v>
       </c>
       <c r="P287" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="288" spans="1:16">
@@ -15776,7 +15788,7 @@
         <v>3.323776305055329</v>
       </c>
       <c r="D288" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E288">
         <v>2.110986245450121</v>
@@ -15812,7 +15824,7 @@
         <v>1</v>
       </c>
       <c r="P288" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="289" spans="1:16">
@@ -15862,7 +15874,7 @@
         <v>1</v>
       </c>
       <c r="P289" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="290" spans="1:16">
@@ -15912,7 +15924,7 @@
         <v>1</v>
       </c>
       <c r="P290" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="291" spans="1:16">
@@ -15962,7 +15974,7 @@
         <v>1</v>
       </c>
       <c r="P291" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="292" spans="1:16">
@@ -15976,7 +15988,7 @@
         <v>3.278598009747792</v>
       </c>
       <c r="D292" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E292">
         <v>2.503358142431271</v>
@@ -16026,7 +16038,7 @@
         <v>3.335021521242147</v>
       </c>
       <c r="D293" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E293">
         <v>2.123914544980693</v>
@@ -16176,7 +16188,7 @@
         <v>1.953185079463765</v>
       </c>
       <c r="D296" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E296">
         <v>1.673185079463764</v>
@@ -16226,7 +16238,7 @@
         <v>1.838424946780282</v>
       </c>
       <c r="D297" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E297">
         <v>1.673185079463764</v>
@@ -16276,7 +16288,7 @@
         <v>3.286491586851236</v>
       </c>
       <c r="D298" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E298">
         <v>2.510725481061151</v>
@@ -16326,7 +16338,7 @@
         <v>3.343225444112052</v>
       </c>
       <c r="D299" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E299">
         <v>2.133346357622241</v>
@@ -16476,7 +16488,7 @@
         <v>1.963547929404697</v>
       </c>
       <c r="D302" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E302">
         <v>2.040362444937774</v>
@@ -16526,7 +16538,7 @@
         <v>1.849314035194777</v>
       </c>
       <c r="D303" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E303">
         <v>2.040362444937774</v>
@@ -16576,7 +16588,7 @@
         <v>3.287218803551511</v>
       </c>
       <c r="D304" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E304">
         <v>2.511404216648074</v>
@@ -16626,7 +16638,7 @@
         <v>3.34398125223815</v>
       </c>
       <c r="D305" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E305">
         <v>2.134215288346162</v>
@@ -16776,7 +16788,7 @@
         <v>1.964502634406085</v>
       </c>
       <c r="D308" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E308">
         <v>2.034789980466009</v>
@@ -16826,7 +16838,7 @@
         <v>1.850317221309513</v>
       </c>
       <c r="D309" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E309">
         <v>2.034789980466009</v>
@@ -16876,7 +16888,7 @@
         <v>3.309574328279867</v>
       </c>
       <c r="D310" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E310">
         <v>2.532269373061208</v>
@@ -16926,7 +16938,7 @@
         <v>3.367215712126766</v>
       </c>
       <c r="D311" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E311">
         <v>2.160927274303631</v>
@@ -17176,7 +17188,7 @@
         <v>3.386581638751728</v>
       </c>
       <c r="D316" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E316">
         <v>2.183191719551736</v>
@@ -17276,7 +17288,7 @@
         <v>2.018313648949551</v>
       </c>
       <c r="D318" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E318">
         <v>2.020805677582523</v>
@@ -17326,7 +17338,7 @@
         <v>1.906860826435267</v>
       </c>
       <c r="D319" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E319">
         <v>2.020805677582523</v>
@@ -17376,7 +17388,7 @@
         <v>1.784750528729781</v>
       </c>
       <c r="D320" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E320">
         <v>2.020805677582523</v>
@@ -17426,7 +17438,7 @@
         <v>3.376305833526885</v>
       </c>
       <c r="D321" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E321">
         <v>2.171377923742256</v>
@@ -17462,7 +17474,7 @@
         <v>1</v>
       </c>
       <c r="P321" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="322" spans="1:16">
@@ -17512,7 +17524,7 @@
         <v>1</v>
       </c>
       <c r="P322" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="323" spans="1:16">
@@ -17562,7 +17574,7 @@
         <v>1</v>
       </c>
       <c r="P323" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="324" spans="1:16">
@@ -17612,7 +17624,7 @@
         <v>1</v>
       </c>
       <c r="P324" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="325" spans="1:16">
@@ -17626,7 +17638,7 @@
         <v>3.346413966869674</v>
       </c>
       <c r="D325" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E325">
         <v>2.137012109937338</v>
@@ -17662,7 +17674,7 @@
         <v>1</v>
       </c>
       <c r="P325" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="326" spans="1:16">
@@ -17712,7 +17724,7 @@
         <v>1</v>
       </c>
       <c r="P326" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="327" spans="1:16">
@@ -17726,7 +17738,7 @@
         <v>1.853546169841817</v>
       </c>
       <c r="D327" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E327">
         <v>1.909412654865697</v>
@@ -17762,7 +17774,7 @@
         <v>1</v>
       </c>
       <c r="P327" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="328" spans="1:16">
@@ -17776,7 +17788,7 @@
         <v>1.729057523143315</v>
       </c>
       <c r="D328" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E328">
         <v>1.909412654865697</v>
@@ -17812,7 +17824,7 @@
         <v>1</v>
       </c>
       <c r="P328" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="329" spans="1:16">
@@ -17826,7 +17838,7 @@
         <v>1.90213361560998</v>
       </c>
       <c r="D329" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E329">
         <v>1.909412654865697</v>
@@ -17862,7 +17874,7 @@
         <v>1</v>
       </c>
       <c r="P329" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="330" spans="1:16">
@@ -17876,7 +17888,7 @@
         <v>3.335708401471214</v>
       </c>
       <c r="D330" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E330">
         <v>2.124704231296676</v>
@@ -17912,7 +17924,7 @@
         <v>1</v>
       </c>
       <c r="P330" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="331" spans="1:16">
@@ -17962,7 +17974,7 @@
         <v>1</v>
       </c>
       <c r="P331" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="332" spans="1:16">
@@ -17976,7 +17988,7 @@
         <v>1.839336644715903</v>
       </c>
       <c r="D332" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E332">
         <v>2.572020438006287</v>
@@ -18012,7 +18024,7 @@
         <v>1</v>
       </c>
       <c r="P332" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="333" spans="1:16">
@@ -18026,7 +18038,7 @@
         <v>1.714214115855647</v>
       </c>
       <c r="D333" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E333">
         <v>2.572020438006287</v>
@@ -18062,7 +18074,7 @@
         <v>1</v>
       </c>
       <c r="P333" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="334" spans="1:16">
@@ -18076,7 +18088,7 @@
         <v>1.88846993345668</v>
       </c>
       <c r="D334" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E334">
         <v>2.572020438006287</v>
@@ -18112,7 +18124,7 @@
         <v>1</v>
       </c>
       <c r="P334" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="335" spans="1:16">
@@ -18126,7 +18138,7 @@
         <v>3.319807569063805</v>
       </c>
       <c r="D335" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E335">
         <v>2.106423504565129</v>
@@ -18226,7 +18238,7 @@
         <v>1.818231428017253</v>
       </c>
       <c r="D337" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E337">
         <v>2.552327466291189</v>
@@ -18276,7 +18288,7 @@
         <v>1.692167402501294</v>
       </c>
       <c r="D338" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E338">
         <v>2.552327466291189</v>
@@ -18326,7 +18338,7 @@
         <v>1.86817544998933</v>
       </c>
       <c r="D339" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E339">
         <v>2.552327466291189</v>
@@ -18376,7 +18388,7 @@
         <v>3.297653300651016</v>
       </c>
       <c r="D340" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E340">
         <v>2.080953383478715</v>
@@ -18412,7 +18424,7 @@
         <v>1</v>
       </c>
       <c r="P340" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="341" spans="1:16">
@@ -18462,7 +18474,7 @@
         <v>1</v>
       </c>
       <c r="P341" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="342" spans="1:16">
@@ -18476,7 +18488,7 @@
         <v>1.788826009252247</v>
       </c>
       <c r="D342" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E342">
         <v>2.524889696365481</v>
@@ -18512,7 +18524,7 @@
         <v>1</v>
       </c>
       <c r="P342" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="343" spans="1:16">
@@ -18526,7 +18538,7 @@
         <v>1.661450217843427</v>
       </c>
       <c r="D343" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E343">
         <v>2.524889696365481</v>
@@ -18562,7 +18574,7 @@
         <v>1</v>
       </c>
       <c r="P343" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="344" spans="1:16">
@@ -18576,7 +18588,7 @@
         <v>1.839899607409848</v>
       </c>
       <c r="D344" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E344">
         <v>2.524889696365481</v>
@@ -18612,7 +18624,7 @@
         <v>1</v>
       </c>
       <c r="P344" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="345" spans="1:16">
@@ -18626,7 +18638,7 @@
         <v>3.263703117123406</v>
       </c>
       <c r="D345" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E345">
         <v>2.041921840245493</v>
@@ -18726,7 +18738,7 @@
         <v>1.743763841313463</v>
       </c>
       <c r="D347" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E347">
         <v>2.48284284077948</v>
@@ -18776,7 +18788,7 @@
         <v>1.614377841669459</v>
       </c>
       <c r="D348" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E348">
         <v>2.48284284077948</v>
@@ -18826,7 +18838,7 @@
         <v>1.796568452118031</v>
       </c>
       <c r="D349" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E349">
         <v>2.48284284077948</v>
@@ -18876,7 +18888,7 @@
         <v>3.242126022559422</v>
       </c>
       <c r="D350" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E350">
         <v>2.017115279225386</v>
@@ -18912,7 +18924,7 @@
         <v>1</v>
       </c>
       <c r="P350" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="351" spans="1:16">
@@ -18962,7 +18974,7 @@
         <v>1</v>
       </c>
       <c r="P351" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="352" spans="1:16">
@@ -18976,7 +18988,7 @@
         <v>1.715124506916858</v>
       </c>
       <c r="D352" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E352">
         <v>2.456119893071122</v>
@@ -19012,7 +19024,7 @@
         <v>1</v>
       </c>
       <c r="P352" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="353" spans="1:16">
@@ -19026,7 +19038,7 @@
         <v>1.584460916147354</v>
       </c>
       <c r="D353" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E353">
         <v>2.456119893071122</v>
@@ -19062,7 +19074,7 @@
         <v>1</v>
       </c>
       <c r="P353" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="354" spans="1:16">
@@ -19076,7 +19088,7 @@
         <v>1.769029265635051</v>
       </c>
       <c r="D354" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E354">
         <v>2.456119893071122</v>
@@ -19112,7 +19124,7 @@
         <v>1</v>
       </c>
       <c r="P354" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="355" spans="1:16">
@@ -19126,7 +19138,7 @@
         <v>3.218796578894542</v>
       </c>
       <c r="D355" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E355">
         <v>1.990294093169876</v>
@@ -19226,7 +19238,7 @@
         <v>1.684159274947191</v>
       </c>
       <c r="D357" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E357">
         <v>2.427226684058535</v>
@@ -19276,7 +19288,7 @@
         <v>1.552114335539635</v>
       </c>
       <c r="D358" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E358">
         <v>2.427226684058535</v>
@@ -19326,7 +19338,7 @@
         <v>1.739253528325928</v>
       </c>
       <c r="D359" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E359">
         <v>2.427226684058535</v>
@@ -19376,7 +19388,7 @@
         <v>3.223084813618858</v>
       </c>
       <c r="D360" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E360">
         <v>1.995224152499308</v>
@@ -19412,7 +19424,7 @@
         <v>1</v>
       </c>
       <c r="P360" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="361" spans="1:16">
@@ -19426,7 +19438,7 @@
         <v>1.689851060181606</v>
       </c>
       <c r="D361" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E361">
         <v>2.432537606340457</v>
@@ -19462,7 +19474,7 @@
         <v>1</v>
       </c>
       <c r="P361" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="362" spans="1:16">
@@ -19476,7 +19488,7 @@
         <v>1.558060029409038</v>
       </c>
       <c r="D362" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E362">
         <v>2.432537606340457</v>
@@ -19512,7 +19524,7 @@
         <v>1</v>
       </c>
       <c r="P362" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="363" spans="1:16">
@@ -19526,7 +19538,7 @@
         <v>1.5546355793606</v>
       </c>
       <c r="D363" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E363">
         <v>2.429478755941318</v>
@@ -19576,7 +19588,7 @@
         <v>2.749895863416445</v>
       </c>
       <c r="D364" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E364">
         <v>2.144120683335579</v>
@@ -19612,7 +19624,7 @@
         <v>1</v>
       </c>
       <c r="P364" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="365" spans="1:16">
@@ -19626,7 +19638,7 @@
         <v>1.575757316392718</v>
       </c>
       <c r="D365" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E365">
         <v>2.448345503254703</v>
@@ -19662,7 +19674,7 @@
         <v>1</v>
       </c>
       <c r="P365" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="366" spans="1:16">
@@ -19676,7 +19688,7 @@
         <v>1.708690594836302</v>
       </c>
       <c r="D366" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E366">
         <v>1.95524223097577</v>
@@ -19712,7 +19724,7 @@
         <v>1</v>
       </c>
       <c r="P366" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="367" spans="1:16">
@@ -19726,7 +19738,7 @@
         <v>2.776972324350222</v>
       </c>
       <c r="D367" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E367">
         <v>2.170167242074328</v>
@@ -19762,7 +19774,7 @@
         <v>1</v>
       </c>
       <c r="P367" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="368" spans="1:16">
@@ -19776,7 +19788,7 @@
         <v>1.603764011567165</v>
       </c>
       <c r="D368" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E368">
         <v>2.473362159798427</v>
@@ -19812,7 +19824,7 @@
         <v>1</v>
       </c>
       <c r="P368" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="369" spans="1:16">
@@ -19826,7 +19838,7 @@
         <v>1.733308579562596</v>
       </c>
       <c r="D369" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E369">
         <v>2.069952921130998</v>
@@ -19862,7 +19874,7 @@
         <v>1</v>
       </c>
       <c r="P369" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="370" spans="1:16">
@@ -19876,7 +19888,7 @@
         <v>2.804318151096002</v>
       </c>
       <c r="D370" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E370">
         <v>2.196472920808915</v>
@@ -19912,7 +19924,7 @@
         <v>1</v>
       </c>
       <c r="P370" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="371" spans="1:16">
@@ -19926,7 +19938,7 @@
         <v>1.632049326839176</v>
       </c>
       <c r="D371" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E371">
         <v>2.498627690521825</v>
@@ -19962,7 +19974,7 @@
         <v>1</v>
       </c>
       <c r="P371" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="372" spans="1:16">
@@ -19976,7 +19988,7 @@
         <v>1.758171472346181</v>
       </c>
       <c r="D372" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E372">
         <v>2.648741745065742</v>
@@ -20012,7 +20024,7 @@
         <v>1</v>
       </c>
       <c r="P372" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="373" spans="1:16">
@@ -20026,7 +20038,7 @@
         <v>1.836308899819077</v>
       </c>
       <c r="D373" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E373">
         <v>2.387421432319158</v>
@@ -20062,7 +20074,7 @@
         <v>1</v>
       </c>
       <c r="P373" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="374" spans="1:16">
@@ -20112,7 +20124,7 @@
         <v>1</v>
       </c>
       <c r="P374" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="375" spans="1:16">
@@ -20126,7 +20138,7 @@
         <v>1.66686196794393</v>
       </c>
       <c r="D375" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E375">
         <v>2.529723679551338</v>
@@ -20162,7 +20174,7 @@
         <v>1</v>
       </c>
       <c r="P375" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="376" spans="1:16">
@@ -20176,7 +20188,7 @@
         <v>1.844881242140559</v>
       </c>
       <c r="D376" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E376">
         <v>2.529723679551338</v>
@@ -20212,7 +20224,7 @@
         <v>1</v>
       </c>
       <c r="P376" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="377" spans="1:16">
@@ -20226,7 +20238,7 @@
         <v>1.788771907765661</v>
       </c>
       <c r="D377" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E377">
         <v>2.679961622497764</v>
@@ -20262,7 +20274,7 @@
         <v>1</v>
       </c>
       <c r="P377" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="378" spans="1:16">
@@ -20276,7 +20288,7 @@
         <v>1.861508767932467</v>
       </c>
       <c r="D378" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E378">
         <v>2.411732640096055</v>
@@ -20312,7 +20324,7 @@
         <v>1</v>
       </c>
       <c r="P378" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="379" spans="1:16">
@@ -20362,7 +20374,7 @@
         <v>1</v>
       </c>
       <c r="P379" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="380" spans="1:16">
@@ -20376,7 +20388,7 @@
         <v>1.693616991646184</v>
       </c>
       <c r="D380" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E380">
         <v>2.55362229502915</v>
@@ -20412,7 +20424,7 @@
         <v>1</v>
       </c>
       <c r="P380" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="381" spans="1:16">
@@ -20426,7 +20438,7 @@
         <v>1.869509828609061</v>
       </c>
       <c r="D381" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E381">
         <v>2.55362229502915</v>
@@ -20462,7 +20474,7 @@
         <v>1</v>
       </c>
       <c r="P381" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="382" spans="1:16">
@@ -20476,7 +20488,7 @@
         <v>2.574954921244757</v>
       </c>
       <c r="D382" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E382">
         <v>2.17950982860906</v>
@@ -20512,7 +20524,7 @@
         <v>1</v>
       </c>
       <c r="P382" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="383" spans="1:16">
@@ -20526,7 +20538,7 @@
         <v>1.812289668813548</v>
       </c>
       <c r="D383" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E383">
         <v>2.703955451583056</v>
@@ -20562,7 +20574,7 @@
         <v>1</v>
       </c>
       <c r="P383" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="384" spans="1:16">
@@ -20576,7 +20588,7 @@
         <v>1.878354735459471</v>
       </c>
       <c r="D384" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E384">
         <v>2.42798454327702</v>
@@ -20612,7 +20624,7 @@
         <v>1</v>
       </c>
       <c r="P384" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="385" spans="1:16">
@@ -20662,7 +20674,7 @@
         <v>1</v>
       </c>
       <c r="P385" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="386" spans="1:16">
@@ -20676,7 +20688,7 @@
         <v>1.711502571778759</v>
       </c>
       <c r="D386" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E386">
         <v>2.569598382620882</v>
@@ -20712,7 +20724,7 @@
         <v>1</v>
       </c>
       <c r="P386" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="387" spans="1:16">
@@ -20726,7 +20738,7 @@
         <v>1.885973897627895</v>
       </c>
       <c r="D387" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E387">
         <v>2.569598382620882</v>
@@ -20762,7 +20774,7 @@
         <v>1</v>
       </c>
       <c r="P387" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="388" spans="1:16">
@@ -20776,7 +20788,7 @@
         <v>2.591185607841933</v>
       </c>
       <c r="D388" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E388">
         <v>2.195973897627894</v>
@@ -20812,7 +20824,7 @@
         <v>1</v>
       </c>
       <c r="P388" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="389" spans="1:16">
@@ -20826,7 +20838,7 @@
         <v>1.828011157399832</v>
       </c>
       <c r="D389" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E389">
         <v>2.719995188926148</v>
@@ -20862,7 +20874,7 @@
         <v>1</v>
       </c>
       <c r="P389" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="390" spans="1:16">
@@ -20876,7 +20888,7 @@
         <v>1.884937981108568</v>
       </c>
       <c r="D390" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E390">
         <v>2.434335634167709</v>
@@ -20912,7 +20924,7 @@
         <v>1</v>
       </c>
       <c r="P390" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="391" spans="1:16">
@@ -20962,7 +20974,7 @@
         <v>1</v>
       </c>
       <c r="P391" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="392" spans="1:16">
@@ -20976,7 +20988,7 @@
         <v>1.718492088255065</v>
       </c>
       <c r="D392" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E392">
         <v>2.575841687373739</v>
@@ -21012,7 +21024,7 @@
         <v>1</v>
       </c>
       <c r="P392" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="393" spans="1:16">
@@ -21026,7 +21038,7 @@
         <v>1.892407900932305</v>
       </c>
       <c r="D393" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E393">
         <v>2.575841687373739</v>
@@ -21062,7 +21074,7 @@
         <v>1</v>
       </c>
       <c r="P393" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="394" spans="1:16">
@@ -21076,7 +21088,7 @@
         <v>1.834154967256232</v>
       </c>
       <c r="D394" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E394">
         <v>2.726263367403121</v>
@@ -21112,7 +21124,7 @@
         <v>1</v>
       </c>
       <c r="P394" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="395" spans="1:16">
@@ -21126,7 +21138,7 @@
         <v>2.791624887079966</v>
       </c>
       <c r="D395" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E395">
         <v>2.637829766815571</v>
@@ -21162,7 +21174,7 @@
         <v>1</v>
       </c>
       <c r="P395" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="396" spans="1:16">
@@ -21176,7 +21188,7 @@
         <v>1.897004594528006</v>
       </c>
       <c r="D396" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E396">
         <v>2.445976724695786</v>
@@ -21212,7 +21224,7 @@
         <v>1</v>
       </c>
       <c r="P396" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="397" spans="1:16">
@@ -21262,7 +21274,7 @@
         <v>1</v>
       </c>
       <c r="P397" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="398" spans="1:16">
@@ -21276,7 +21288,7 @@
         <v>1.731303366734398</v>
       </c>
       <c r="D398" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E398">
         <v>2.587285213702252</v>
@@ -21312,7 +21324,7 @@
         <v>1</v>
       </c>
       <c r="P398" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="399" spans="1:16">
@@ -21326,7 +21338,7 @@
         <v>1.904200963921582</v>
       </c>
       <c r="D399" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E399">
         <v>2.587285213702252</v>
@@ -21362,7 +21374,7 @@
         <v>1</v>
       </c>
       <c r="P399" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="400" spans="1:16">
@@ -21376,7 +21388,7 @@
         <v>1.845416126631299</v>
       </c>
       <c r="D400" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E400">
         <v>2.737752485469994</v>
@@ -21412,7 +21424,7 @@
         <v>1</v>
       </c>
       <c r="P400" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="401" spans="1:16">
@@ -21426,7 +21438,7 @@
         <v>2.802612496024871</v>
       </c>
       <c r="D401" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E401">
         <v>2.813453713263602</v>
@@ -21462,7 +21474,7 @@
         <v>1</v>
       </c>
       <c r="P401" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="402" spans="1:16">
@@ -21476,7 +21488,7 @@
         <v>1.915149243214803</v>
       </c>
       <c r="D402" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E402">
         <v>2.463481511716044</v>
@@ -21512,7 +21524,7 @@
         <v>1</v>
       </c>
       <c r="P402" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="403" spans="1:16">
@@ -21562,7 +21574,7 @@
         <v>1</v>
       </c>
       <c r="P403" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="404" spans="1:16">
@@ -21576,7 +21588,7 @@
         <v>1.750567773337632</v>
       </c>
       <c r="D404" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E404">
         <v>2.60449292209162</v>
@@ -21612,7 +21624,7 @@
         <v>1</v>
       </c>
       <c r="P404" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="405" spans="1:16">
@@ -21626,7 +21638,7 @@
         <v>1.921934272965604</v>
       </c>
       <c r="D405" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E405">
         <v>2.60449292209162</v>
@@ -21662,7 +21674,7 @@
         <v>1</v>
       </c>
       <c r="P405" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="406" spans="1:16">
@@ -21676,7 +21688,7 @@
         <v>1.862349608592151</v>
       </c>
       <c r="D406" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E406">
         <v>2.75502875046649</v>
@@ -21712,7 +21724,7 @@
         <v>1</v>
       </c>
       <c r="P406" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="407" spans="1:16">
@@ -21726,7 +21738,7 @@
         <v>2.819134638342948</v>
       </c>
       <c r="D407" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E407">
         <v>2.769730713091974</v>
@@ -21762,7 +21774,7 @@
         <v>1</v>
       </c>
       <c r="P407" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="408" spans="1:16">
@@ -21776,7 +21788,7 @@
         <v>1.92753511972947</v>
       </c>
       <c r="D408" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E408">
         <v>2.475430606691152</v>
@@ -21876,7 +21888,7 @@
         <v>1.76371801754653</v>
       </c>
       <c r="D410" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E410">
         <v>2.616239225637646</v>
@@ -21926,7 +21938,7 @@
         <v>1.934039361347697</v>
       </c>
       <c r="D411" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E411">
         <v>2.616239225637646</v>
@@ -21976,7 +21988,7 @@
         <v>1.873908720049794</v>
       </c>
       <c r="D412" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E412">
         <v>2.766821852034614</v>
@@ -22026,7 +22038,7 @@
         <v>2.830412961668017</v>
       </c>
       <c r="D413" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E413">
         <v>2.221708855759843</v>
@@ -22076,7 +22088,7 @@
         <v>1.937685341557977</v>
       </c>
       <c r="D414" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E414">
         <v>2.485222886188172</v>
@@ -22112,7 +22124,7 @@
         <v>1</v>
       </c>
       <c r="P414" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="415" spans="1:16">
@@ -22162,7 +22174,7 @@
         <v>1</v>
       </c>
       <c r="P415" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="416" spans="1:16">
@@ -22176,7 +22188,7 @@
         <v>1.774494638455131</v>
       </c>
       <c r="D416" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E416">
         <v>2.625865317623621</v>
@@ -22212,7 +22224,7 @@
         <v>1</v>
       </c>
       <c r="P416" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="417" spans="1:16">
@@ -22226,7 +22238,7 @@
         <v>1.943959477391676</v>
       </c>
       <c r="D417" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E417">
         <v>2.625865317623621</v>
@@ -22262,7 +22274,7 @@
         <v>1</v>
       </c>
       <c r="P417" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="418" spans="1:16">
@@ -22276,7 +22288,7 @@
         <v>1.883381408179421</v>
       </c>
       <c r="D418" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E418">
         <v>2.776486294984675</v>
@@ -22312,7 +22324,7 @@
         <v>1</v>
       </c>
       <c r="P418" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="419" spans="1:16">
@@ -22326,7 +22338,7 @@
         <v>2.839655544013116</v>
       </c>
       <c r="D419" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E419">
         <v>2.231475567947474</v>
@@ -22362,7 +22374,7 @@
         <v>1</v>
       </c>
       <c r="P419" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="420" spans="1:16">
@@ -22376,7 +22388,7 @@
         <v>1.950149148490695</v>
       </c>
       <c r="D420" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E420">
         <v>2.49724716340538</v>
@@ -22412,7 +22424,7 @@
         <v>1</v>
       </c>
       <c r="P420" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="421" spans="1:16">
@@ -22462,7 +22474,7 @@
         <v>1</v>
       </c>
       <c r="P421" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="422" spans="1:16">
@@ -22476,7 +22488,7 @@
         <v>1.787727622389998</v>
       </c>
       <c r="D422" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E422">
         <v>2.637685527472915</v>
@@ -22512,7 +22524,7 @@
         <v>1</v>
       </c>
       <c r="P422" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="423" spans="1:16">
@@ -22526,7 +22538,7 @@
         <v>1.956140729507283</v>
       </c>
       <c r="D423" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E423">
         <v>2.637685527472915</v>
@@ -22562,7 +22574,7 @@
         <v>1</v>
       </c>
       <c r="P423" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="424" spans="1:16">
@@ -22576,7 +22588,7 @@
         <v>1.895013248150637</v>
       </c>
       <c r="D424" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E424">
         <v>2.788353597303487</v>
@@ -22612,7 +22624,7 @@
         <v>1</v>
       </c>
       <c r="P424" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="425" spans="1:16">
@@ -22626,7 +22638,7 @@
         <v>2.85100482916722</v>
       </c>
       <c r="D425" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E425">
         <v>2.243468450185002</v>
@@ -22662,7 +22674,7 @@
         <v>1</v>
       </c>
       <c r="P425" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="426" spans="1:16">
@@ -22726,7 +22738,7 @@
         <v>1.796280604882195</v>
       </c>
       <c r="D427" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E427">
         <v>2.645325380161676</v>
@@ -22776,7 +22788,7 @@
         <v>1.964013937590256</v>
       </c>
       <c r="D428" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E428">
         <v>2.645325380161676</v>
@@ -22826,7 +22838,7 @@
         <v>1.902531350198938</v>
       </c>
       <c r="D429" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E429">
         <v>2.796023887652364</v>
@@ -22876,7 +22888,7 @@
         <v>2.858340305254835</v>
       </c>
       <c r="D430" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E430">
         <v>2.251219907627515</v>
@@ -22962,7 +22974,7 @@
         <v>1</v>
       </c>
       <c r="P431" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="432" spans="1:16">
@@ -22976,7 +22988,7 @@
         <v>1.81059278070445</v>
       </c>
       <c r="D432" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E432">
         <v>2.658109565682619</v>
@@ -23012,7 +23024,7 @@
         <v>1</v>
       </c>
       <c r="P432" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="433" spans="1:16">
@@ -23026,7 +23038,7 @@
         <v>1.977188609521534</v>
       </c>
       <c r="D433" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E433">
         <v>2.658109565682619</v>
@@ -23062,7 +23074,7 @@
         <v>1</v>
       </c>
       <c r="P433" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="434" spans="1:16">
@@ -23076,7 +23088,7 @@
         <v>1.915111803679711</v>
       </c>
       <c r="D434" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E434">
         <v>2.808859006183351</v>
@@ -23112,7 +23124,7 @@
         <v>1</v>
       </c>
       <c r="P434" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="435" spans="1:16">
@@ -23126,7 +23138,7 @@
         <v>2.870615160675342</v>
       </c>
       <c r="D435" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E435">
         <v>2.26419084751862</v>
@@ -23162,7 +23174,7 @@
         <v>1</v>
       </c>
       <c r="P435" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="436" spans="1:16">
@@ -23212,7 +23224,7 @@
         <v>1</v>
       </c>
       <c r="P436" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="437" spans="1:16">
@@ -23226,7 +23238,7 @@
         <v>1.82632056259726</v>
       </c>
       <c r="D437" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E437">
         <v>2.672158224953424</v>
@@ -23262,7 +23274,7 @@
         <v>1</v>
       </c>
       <c r="P437" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="438" spans="1:16">
@@ -23276,7 +23288,7 @@
         <v>1.991666377906849</v>
       </c>
       <c r="D438" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E438">
         <v>2.672158224953424</v>
@@ -23312,7 +23324,7 @@
         <v>1</v>
       </c>
       <c r="P438" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="439" spans="1:16">
@@ -23326,7 +23338,7 @@
         <v>1.928936579934245</v>
       </c>
       <c r="D439" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E439">
         <v>2.822963636208222</v>
@@ -23362,7 +23374,7 @@
         <v>1</v>
       </c>
       <c r="P439" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="440" spans="1:16">
@@ -23376,7 +23388,7 @@
         <v>2.884104112405478</v>
       </c>
       <c r="D440" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E440">
         <v>2.278444732887671</v>
@@ -23412,7 +23424,7 @@
         <v>1</v>
       </c>
       <c r="P440" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="441" spans="1:16">
@@ -23426,7 +23438,7 @@
         <v>1.850091985515281</v>
       </c>
       <c r="D441" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E441">
         <v>2.693391773538558</v>
@@ -23476,7 +23488,7 @@
         <v>2.013548494377055</v>
       </c>
       <c r="D442" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E442">
         <v>2.693391773538558</v>
@@ -23526,7 +23538,7 @@
         <v>1.949831745274995</v>
       </c>
       <c r="D443" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E443">
         <v>2.844281780604454</v>
@@ -23576,7 +23588,7 @@
         <v>2.90449170287965</v>
       </c>
       <c r="D444" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E444">
         <v>2.29998846611349</v>
@@ -23626,7 +23638,7 @@
         <v>1.883787347386825</v>
       </c>
       <c r="D445" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E445">
         <v>2.723489765815277</v>
@@ -23662,7 +23674,7 @@
         <v>1</v>
       </c>
       <c r="P445" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="446" spans="1:16">
@@ -23676,7 +23688,7 @@
         <v>2.044565814439117</v>
       </c>
       <c r="D446" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E446">
         <v>2.723489765815277</v>
@@ -23712,7 +23724,7 @@
         <v>1</v>
       </c>
       <c r="P446" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="447" spans="1:16">
@@ -23726,7 +23738,7 @@
         <v>2.74752944335815</v>
       </c>
       <c r="D447" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E447">
         <v>2.354565814439116</v>
@@ -23762,7 +23774,7 @@
         <v>1</v>
       </c>
       <c r="P447" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="448" spans="1:16">
@@ -23776,7 +23788,7 @@
         <v>1.979450088272404</v>
       </c>
       <c r="D448" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E448">
         <v>2.874499685200998</v>
@@ -23812,7 +23824,7 @@
         <v>1</v>
       </c>
       <c r="P448" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="449" spans="1:16">
@@ -23826,7 +23838,7 @@
         <v>2.933390571958093</v>
       </c>
       <c r="D449" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E449">
         <v>2.330526136896243</v>
@@ -23862,7 +23874,7 @@
         <v>1</v>
       </c>
       <c r="P449" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="450" spans="1:16">
@@ -23912,7 +23924,7 @@
         <v>1</v>
       </c>
       <c r="P450" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="451" spans="1:16">
@@ -23926,7 +23938,7 @@
         <v>1.920897553279229</v>
       </c>
       <c r="D451" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E451">
         <v>2.756638028018099</v>
@@ -23962,7 +23974,7 @@
         <v>1</v>
       </c>
       <c r="P451" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="452" spans="1:16">
@@ -23976,7 +23988,7 @@
         <v>2.078726573362612</v>
       </c>
       <c r="D452" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E452">
         <v>2.756638028018099</v>
@@ -24012,7 +24024,7 @@
         <v>1</v>
       </c>
       <c r="P452" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="453" spans="1:16">
@@ -24026,7 +24038,7 @@
         <v>2.012070091316616</v>
       </c>
       <c r="D453" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E453">
         <v>2.907780012193474</v>
@@ -24062,7 +24074,7 @@
         <v>1</v>
       </c>
       <c r="P453" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="454" spans="1:16">
@@ -24076,7 +24088,7 @@
         <v>2.965218186264387</v>
       </c>
       <c r="D454" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E454">
         <v>2.364158636661127</v>
@@ -24112,7 +24124,7 @@
         <v>1</v>
       </c>
       <c r="P454" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="455" spans="1:16">
@@ -24126,7 +24138,7 @@
         <v>1.971362962924253</v>
       </c>
       <c r="D455" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E455">
         <v>2.801715671508852</v>
@@ -24176,7 +24188,7 @@
         <v>2.125181090426125</v>
       </c>
       <c r="D456" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E456">
         <v>2.801715671508852</v>
@@ -24226,7 +24238,7 @@
         <v>2.056429365986798</v>
       </c>
       <c r="D457" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E457">
         <v>2.95303724788937</v>
@@ -24276,7 +24288,7 @@
         <v>3.008499907703719</v>
       </c>
       <c r="D458" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E458">
         <v>2.409894784904068</v>
@@ -24326,7 +24338,7 @@
         <v>2.008171638992437</v>
       </c>
       <c r="D459" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E459">
         <v>2.834594595683633</v>
@@ -24362,7 +24374,7 @@
         <v>1</v>
       </c>
       <c r="P459" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="460" spans="1:16">
@@ -24376,7 +24388,7 @@
         <v>2.159064284529219</v>
       </c>
       <c r="D460" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E460">
         <v>2.834594595683633</v>
@@ -24412,7 +24424,7 @@
         <v>1</v>
       </c>
       <c r="P460" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="461" spans="1:16">
@@ -24426,7 +24438,7 @@
         <v>2.088784323242461</v>
       </c>
       <c r="D461" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E461">
         <v>2.986047163793931</v>
@@ -24462,7 +24474,7 @@
         <v>1</v>
       </c>
       <c r="P461" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="462" spans="1:16">
@@ -24476,7 +24488,7 @@
         <v>3.040068914580697</v>
       </c>
       <c r="D462" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E462">
         <v>2.443254012088044</v>
@@ -24512,7 +24524,7 @@
         <v>1</v>
       </c>
       <c r="P462" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="463" spans="1:16">
@@ -24526,7 +24538,7 @@
         <v>2.067700645146257</v>
       </c>
       <c r="D463" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E463">
         <v>2.887768191927794</v>
@@ -24576,7 +24588,7 @@
         <v>2.213862041083626</v>
       </c>
       <c r="D464" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E464">
         <v>2.887768191927794</v>
@@ -24626,7 +24638,7 @@
         <v>2.914425852356924</v>
       </c>
       <c r="D465" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E465">
         <v>2.523862041083625</v>
@@ -24676,7 +24688,7 @@
         <v>2.141110531498665</v>
       </c>
       <c r="D466" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E466">
         <v>3.039432607035081</v>
@@ -24726,7 +24738,7 @@
         <v>3.091124040854972</v>
       </c>
       <c r="D467" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E467">
         <v>2.497204380654495</v>
@@ -24776,7 +24788,7 @@
         <v>2.102053433035913</v>
       </c>
       <c r="D468" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E468">
         <v>2.918453422391508</v>
@@ -24812,7 +24824,7 @@
         <v>1</v>
       </c>
       <c r="P468" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="469" spans="1:16">
@@ -24826,7 +24838,7 @@
         <v>2.245484536222857</v>
       </c>
       <c r="D469" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E469">
         <v>2.918453422391508</v>
@@ -24862,7 +24874,7 @@
         <v>1</v>
       </c>
       <c r="P469" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="470" spans="1:16">
@@ -24876,7 +24888,7 @@
         <v>2.945600090477427</v>
       </c>
       <c r="D470" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E470">
         <v>2.555484536222856</v>
@@ -24912,7 +24924,7 @@
         <v>1</v>
       </c>
       <c r="P470" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="471" spans="1:16">
@@ -24926,7 +24938,7 @@
         <v>2.171306754305586</v>
       </c>
       <c r="D471" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E471">
         <v>3.070240089412991</v>
@@ -24962,7 +24974,7 @@
         <v>1</v>
       </c>
       <c r="P471" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="472" spans="1:16">
@@ -24976,7 +24988,7 @@
         <v>3.120586752176706</v>
       </c>
       <c r="D472" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E472">
         <v>2.528337868136934</v>
@@ -25012,7 +25024,7 @@
         <v>1</v>
       </c>
       <c r="P472" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="473" spans="1:16">
@@ -25026,7 +25038,7 @@
         <v>2.150109762840597</v>
       </c>
       <c r="D473" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E473">
         <v>2.961379183177897</v>
@@ -25062,7 +25074,7 @@
         <v>1</v>
       </c>
       <c r="P473" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="474" spans="1:16">
@@ -25076,7 +25088,7 @@
         <v>2.289721442425034</v>
       </c>
       <c r="D474" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E474">
         <v>2.961379183177897</v>
@@ -25112,7 +25124,7 @@
         <v>1</v>
       </c>
       <c r="P474" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="475" spans="1:16">
@@ -25126,7 +25138,7 @@
         <v>2.989209927132926</v>
       </c>
       <c r="D475" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E475">
         <v>2.599721442425032</v>
@@ -25162,7 +25174,7 @@
         <v>1</v>
       </c>
       <c r="P475" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="476" spans="1:16">
@@ -25176,7 +25188,7 @@
         <v>2.213548439222873</v>
       </c>
       <c r="D476" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E476">
         <v>3.113336869166659</v>
@@ -25212,7 +25224,7 @@
         <v>1</v>
       </c>
       <c r="P476" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="477" spans="1:16">
@@ -25226,7 +25238,7 @@
         <v>3.161802323290331</v>
       </c>
       <c r="D477" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E477">
         <v>2.571890698470007</v>
@@ -25262,7 +25274,7 @@
         <v>1</v>
       </c>
       <c r="P477" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="478" spans="1:16">
@@ -25276,7 +25288,7 @@
         <v>2.189716387261424</v>
       </c>
       <c r="D478" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E478">
         <v>2.99675734235807</v>
@@ -25326,7 +25338,7 @@
         <v>2.326180209388927</v>
       </c>
       <c r="D479" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E479">
         <v>2.99675734235807</v>
@@ -25376,7 +25388,7 @@
         <v>2.248362803037622</v>
       </c>
       <c r="D480" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E480">
         <v>3.148855977188184</v>
@@ -25426,7 +25438,7 @@
         <v>3.19577099405695</v>
       </c>
       <c r="D481" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E481">
         <v>2.607785670068477</v>
@@ -25476,7 +25488,7 @@
         <v>2.215826782258592</v>
       </c>
       <c r="D482" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E482">
         <v>3.020080150700736</v>
@@ -25512,7 +25524,7 @@
         <v>1</v>
       </c>
       <c r="P482" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="483" spans="1:16">
@@ -25526,7 +25538,7 @@
         <v>2.350215400987747</v>
       </c>
       <c r="D483" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E483">
         <v>3.020080150700736</v>
@@ -25562,7 +25574,7 @@
         <v>1</v>
       </c>
       <c r="P483" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="484" spans="1:16">
@@ -25576,7 +25588,7 @@
         <v>2.271313933159689</v>
       </c>
       <c r="D484" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E484">
         <v>3.172271705086001</v>
@@ -25612,7 +25624,7 @@
         <v>1</v>
       </c>
       <c r="P484" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="485" spans="1:16">
@@ -25626,7 +25638,7 @@
         <v>3.218164606848116</v>
       </c>
       <c r="D485" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E485">
         <v>2.631449183446694</v>
@@ -25662,7 +25674,7 @@
         <v>1</v>
       </c>
       <c r="P485" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="486" spans="1:16">
@@ -25712,7 +25724,7 @@
         <v>1</v>
       </c>
       <c r="P486" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="487" spans="1:16">
@@ -25726,7 +25738,7 @@
         <v>2.227304742320833</v>
       </c>
       <c r="D487" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E487">
         <v>3.030332705774125</v>
@@ -25762,7 +25774,7 @@
         <v>1</v>
       </c>
       <c r="P487" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="488" spans="1:16">
@@ -25776,7 +25788,7 @@
         <v>2.360781115113841</v>
       </c>
       <c r="D488" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E488">
         <v>3.030332705774125</v>
@@ -25812,7 +25824,7 @@
         <v>1</v>
       </c>
       <c r="P488" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="489" spans="1:16">
@@ -25826,7 +25838,7 @@
         <v>2.28140310090123</v>
       </c>
       <c r="D489" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E489">
         <v>3.182565106992353</v>
@@ -25862,7 +25874,7 @@
         <v>1</v>
       </c>
       <c r="P489" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="490" spans="1:16">
@@ -25876,7 +25888,7 @@
         <v>3.228008693591889</v>
       </c>
       <c r="D490" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E490">
         <v>2.641851510240944</v>
@@ -25912,7 +25924,7 @@
         <v>1</v>
       </c>
       <c r="P490" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="491" spans="1:16">
@@ -25926,7 +25938,7 @@
         <v>2.326764722017106</v>
       </c>
       <c r="D491" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E491">
         <v>2.338905512271317</v>
@@ -25962,7 +25974,7 @@
         <v>1</v>
       </c>
       <c r="P491" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="492" spans="1:16">
@@ -25976,7 +25988,7 @@
         <v>2.245345573811253</v>
       </c>
       <c r="D492" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E492">
         <v>3.046447469845635</v>
@@ -26012,7 +26024,7 @@
         <v>1</v>
       </c>
       <c r="P492" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="493" spans="1:16">
@@ -26026,7 +26038,7 @@
         <v>2.377388096414631</v>
       </c>
       <c r="D493" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E493">
         <v>3.046447469845635</v>
@@ -26062,7 +26074,7 @@
         <v>1</v>
       </c>
       <c r="P493" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="494" spans="1:16">
@@ -26076,7 +26088,7 @@
         <v>2.297261055983554</v>
       </c>
       <c r="D494" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E494">
         <v>3.198744073311161</v>
@@ -26112,7 +26124,7 @@
         <v>1</v>
       </c>
       <c r="P494" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="495" spans="1:16">
@@ -26126,7 +26138,7 @@
         <v>3.243481435190432</v>
       </c>
       <c r="D495" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E495">
         <v>2.658201682552544</v>
@@ -26162,7 +26174,7 @@
         <v>1</v>
       </c>
       <c r="P495" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="496" spans="1:16">
@@ -26212,7 +26224,7 @@
         <v>1</v>
       </c>
       <c r="P496" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="497" spans="1:16">
@@ -26226,7 +26238,7 @@
         <v>2.301170929293026</v>
       </c>
       <c r="D497" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E497">
         <v>3.202733093853617</v>
@@ -26276,7 +26288,7 @@
         <v>3.247296331820319</v>
       </c>
       <c r="D498" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E498">
         <v>2.662232914952593</v>
@@ -26376,7 +26388,7 @@
         <v>2.309276220482282</v>
       </c>
       <c r="D500" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E500">
         <v>3.211002459763304</v>
@@ -26412,7 +26424,7 @@
         <v>1</v>
       </c>
       <c r="P500" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="501" spans="1:16">
@@ -26426,7 +26438,7 @@
         <v>3.25520473334506</v>
       </c>
       <c r="D501" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E501">
         <v>2.670589787379843</v>
@@ -26462,7 +26474,7 @@
         <v>1</v>
       </c>
       <c r="P501" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="502" spans="1:16">
@@ -26476,7 +26488,7 @@
         <v>2.35659384998981</v>
       </c>
       <c r="D502" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E502">
         <v>2.377701080695644</v>
@@ -26512,7 +26524,7 @@
         <v>1</v>
       </c>
       <c r="P502" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="503" spans="1:16">
@@ -26526,7 +26538,7 @@
         <v>2.318802840630408</v>
       </c>
       <c r="D503" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E503">
         <v>3.220721926473129</v>
@@ -26576,7 +26588,7 @@
         <v>3.264499937619139</v>
       </c>
       <c r="D504" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E504">
         <v>2.680412105589244</v>
@@ -26726,7 +26738,7 @@
         <v>2.968469110715926</v>
       </c>
       <c r="D507" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E507">
         <v>3.65607053595874</v>
@@ -26762,7 +26774,7 @@
         <v>1</v>
       </c>
       <c r="P507" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="508" spans="1:16">
@@ -26776,7 +26788,7 @@
         <v>3.056098677724048</v>
       </c>
       <c r="D508" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E508">
         <v>3.65607053595874</v>
@@ -26812,7 +26824,7 @@
         <v>1</v>
       </c>
       <c r="P508" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="509" spans="1:16">
@@ -26826,7 +26838,7 @@
         <v>3.085552267926261</v>
       </c>
       <c r="D509" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E509">
         <v>3.65607053595874</v>
@@ -26862,7 +26874,7 @@
         <v>1</v>
       </c>
       <c r="P509" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="510" spans="1:16">
@@ -26876,7 +26888,7 @@
         <v>3.115403587495276</v>
       </c>
       <c r="D510" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E510">
         <v>4.899694426383849</v>
@@ -26912,7 +26924,7 @@
         <v>1</v>
       </c>
       <c r="P510" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="511" spans="1:16">
@@ -26926,7 +26938,7 @@
         <v>2.857657467623699</v>
       </c>
       <c r="D511" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E511">
         <v>4.899694426383849</v>
@@ -26962,7 +26974,7 @@
         <v>1</v>
       </c>
       <c r="P511" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="512" spans="1:16">
@@ -26976,7 +26988,7 @@
         <v>4.634833021734408</v>
       </c>
       <c r="D512" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E512">
         <v>3.48240231940969</v>
@@ -27012,7 +27024,7 @@
         <v>1</v>
       </c>
       <c r="P512" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="513" spans="1:16">
@@ -27026,7 +27038,7 @@
         <v>3.013404560606677</v>
       </c>
       <c r="D513" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E513">
         <v>3.707166946903694</v>
@@ -27062,7 +27074,7 @@
         <v>1</v>
       </c>
       <c r="P513" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="514" spans="1:16">
@@ -27076,7 +27088,7 @@
         <v>3.101938488870459</v>
       </c>
       <c r="D514" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E514">
         <v>3.707166946903694</v>
@@ -27112,7 +27124,7 @@
         <v>1</v>
       </c>
       <c r="P514" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="515" spans="1:16">
@@ -27126,7 +27138,7 @@
         <v>3.133031233848563</v>
       </c>
       <c r="D515" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E515">
         <v>3.707166946903694</v>
@@ -27162,7 +27174,7 @@
         <v>1</v>
       </c>
       <c r="P515" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="516" spans="1:16">
@@ -27176,7 +27188,7 @@
         <v>2.923647577997855</v>
       </c>
       <c r="D516" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E516">
         <v>4.966814988327585</v>
@@ -27212,7 +27224,7 @@
         <v>1</v>
       </c>
       <c r="P516" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="517" spans="1:16">
@@ -27226,7 +27238,7 @@
         <v>4.706192777064061</v>
       </c>
       <c r="D517" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E517">
         <v>3.555881671432303</v>
@@ -27262,7 +27274,7 @@
         <v>1</v>
       </c>
       <c r="P517" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="518" spans="1:16">
@@ -27276,7 +27288,7 @@
         <v>3.058294813446018</v>
       </c>
       <c r="D518" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E518">
         <v>3.758211963968808</v>
@@ -27312,7 +27324,7 @@
         <v>1</v>
       </c>
       <c r="P518" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="519" spans="1:16">
@@ -27326,7 +27338,7 @@
         <v>3.147732193339273</v>
       </c>
       <c r="D519" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E519">
         <v>3.758211963968808</v>
@@ -27362,7 +27374,7 @@
         <v>1</v>
       </c>
       <c r="P519" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="520" spans="1:16">
@@ -27376,7 +27388,7 @@
         <v>3.18046244439579</v>
       </c>
       <c r="D520" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E520">
         <v>3.758211963968808</v>
@@ -27412,7 +27424,7 @@
         <v>1</v>
       </c>
       <c r="P520" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="521" spans="1:16">
@@ -27426,7 +27438,7 @@
         <v>3.225680173488445</v>
       </c>
       <c r="D521" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E521">
         <v>5.033868038952384</v>
@@ -27462,7 +27474,7 @@
         <v>1</v>
       </c>
       <c r="P521" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="522" spans="1:16">
@@ -27476,7 +27488,7 @@
         <v>2.989571314085818</v>
       </c>
       <c r="D522" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E522">
         <v>5.033868038952384</v>
@@ -27512,7 +27524,7 @@
         <v>1</v>
       </c>
       <c r="P522" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="523" spans="1:16">
@@ -27526,7 +27538,7 @@
         <v>4.77748075720201</v>
       </c>
       <c r="D523" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E523">
         <v>3.629287116326825</v>
@@ -27562,7 +27574,7 @@
         <v>1</v>
       </c>
       <c r="P523" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="524" spans="1:16">
@@ -27576,7 +27588,7 @@
         <v>3.100990526217007</v>
       </c>
       <c r="D524" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E524">
         <v>5.097643081613452</v>
@@ -27612,7 +27624,7 @@
         <v>1</v>
       </c>
       <c r="P524" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="525" spans="1:16">
@@ -27626,7 +27638,7 @@
         <v>3.19128719089559</v>
       </c>
       <c r="D525" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E525">
         <v>5.097643081613452</v>
@@ -27662,7 +27674,7 @@
         <v>1</v>
       </c>
       <c r="P525" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="526" spans="1:16">
@@ -27676,7 +27688,7 @@
         <v>3.225574895625517</v>
       </c>
       <c r="D526" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E526">
         <v>5.097643081613452</v>
@@ -27712,7 +27724,7 @@
         <v>1</v>
       </c>
       <c r="P526" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="527" spans="1:16">
@@ -27726,7 +27738,7 @@
         <v>3.205781960817575</v>
       </c>
       <c r="D527" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E527">
         <v>5.097643081613452</v>
@@ -27762,7 +27774,7 @@
         <v>1</v>
       </c>
       <c r="P527" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="528" spans="1:16">
@@ -27776,7 +27788,7 @@
         <v>3.27809654539346</v>
       </c>
       <c r="D528" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E528">
         <v>5.097643081613452</v>
@@ -27812,7 +27824,7 @@
         <v>1</v>
       </c>
       <c r="P528" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="529" spans="1:16">
@@ -27826,7 +27838,7 @@
         <v>3.052272250765228</v>
       </c>
       <c r="D529" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E529">
         <v>5.097643081613452</v>
@@ -27862,7 +27874,7 @@
         <v>1</v>
       </c>
       <c r="P529" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="530" spans="1:16">
@@ -27876,7 +27888,7 @@
         <v>4.845283697294303</v>
       </c>
       <c r="D530" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E530">
         <v>3.699104005134728</v>
@@ -27912,7 +27924,7 @@
         <v>1</v>
       </c>
       <c r="P530" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="531" spans="1:16">
@@ -27926,7 +27938,7 @@
         <v>3.135431759672713</v>
       </c>
       <c r="D531" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E531">
         <v>5.149088320265843</v>
@@ -27962,7 +27974,7 @@
         <v>1</v>
       </c>
       <c r="P531" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="532" spans="1:16">
@@ -27976,7 +27988,7 @@
         <v>3.226421581251035</v>
       </c>
       <c r="D532" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E532">
         <v>5.149088320265843</v>
@@ -28012,7 +28024,7 @@
         <v>1</v>
       </c>
       <c r="P532" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="533" spans="1:16">
@@ -28026,7 +28038,7 @@
         <v>3.261965632861735</v>
       </c>
       <c r="D533" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E533">
         <v>5.149088320265843</v>
@@ -28062,7 +28074,7 @@
         <v>1</v>
       </c>
       <c r="P533" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="534" spans="1:16">
@@ -28076,7 +28088,7 @@
         <v>3.248497754763896</v>
       </c>
       <c r="D534" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E534">
         <v>5.149088320265843</v>
@@ -28112,7 +28124,7 @@
         <v>1</v>
       </c>
       <c r="P534" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="535" spans="1:16">
@@ -28126,7 +28138,7 @@
         <v>3.320379116277444</v>
       </c>
       <c r="D535" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E535">
         <v>5.149088320265843</v>
@@ -28162,7 +28174,7 @@
         <v>1</v>
       </c>
       <c r="P535" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="536" spans="1:16">
@@ -28176,7 +28188,7 @@
         <v>3.102851043292947</v>
       </c>
       <c r="D536" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E536">
         <v>5.149088320265843</v>
@@ -28212,7 +28224,7 @@
         <v>1</v>
       </c>
       <c r="P536" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="537" spans="1:16">
@@ -28226,7 +28238,7 @@
         <v>4.899978108914215</v>
       </c>
       <c r="D537" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E537">
         <v>3.755423003238402</v>
@@ -28262,7 +28274,7 @@
         <v>1</v>
       </c>
       <c r="P537" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="538" spans="1:16">
@@ -28276,7 +28288,7 @@
         <v>3.340758667101504</v>
       </c>
       <c r="D538" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E538">
         <v>5.455787317211367</v>
@@ -28312,7 +28324,7 @@
         <v>1</v>
       </c>
       <c r="P538" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="539" spans="1:16">
@@ -28326,7 +28338,7 @@
         <v>3.596337846972439</v>
       </c>
       <c r="D539" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E539">
         <v>5.455787317211367</v>
@@ -28362,7 +28374,7 @@
         <v>1</v>
       </c>
       <c r="P539" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="540" spans="1:16">
@@ -28376,7 +28388,7 @@
         <v>3.478914818069512</v>
       </c>
       <c r="D540" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E540">
         <v>5.455787317211367</v>
@@ -28412,7 +28424,7 @@
         <v>1</v>
       </c>
       <c r="P540" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="541" spans="1:16">
@@ -28426,7 +28438,7 @@
         <v>3.503154774543503</v>
       </c>
       <c r="D541" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E541">
         <v>5.455787317211367</v>
@@ -28462,7 +28474,7 @@
         <v>1</v>
       </c>
       <c r="P541" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="542" spans="1:16">
@@ -28476,7 +28488,7 @@
         <v>3.572453407661722</v>
       </c>
       <c r="D542" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E542">
         <v>5.455787317211367</v>
@@ -28512,7 +28524,7 @@
         <v>1</v>
       </c>
       <c r="P542" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="543" spans="1:16">
@@ -28526,7 +28538,7 @@
         <v>3.404384583447808</v>
       </c>
       <c r="D543" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E543">
         <v>5.455787317211367</v>
@@ -28562,7 +28574,7 @@
         <v>1</v>
       </c>
       <c r="P543" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="544" spans="1:16">
@@ -28576,7 +28588,7 @@
         <v>5.25250104043668</v>
       </c>
       <c r="D544" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E544">
         <v>5.56320240731846</v>
@@ -28612,7 +28624,7 @@
         <v>1</v>
       </c>
       <c r="P544" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="545" spans="1:16">
@@ -28626,7 +28638,7 @@
         <v>3.408744253943432</v>
       </c>
       <c r="D545" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E545">
         <v>5.557338115167074</v>
@@ -28662,7 +28674,7 @@
         <v>1</v>
       </c>
       <c r="P545" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="546" spans="1:16">
@@ -28676,7 +28688,7 @@
         <v>3.550748645676077</v>
       </c>
       <c r="D546" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E546">
         <v>5.557338115167074</v>
@@ -28712,7 +28724,7 @@
         <v>1</v>
       </c>
       <c r="P546" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="547" spans="1:16">
@@ -28726,7 +28738,7 @@
         <v>3.587474005519777</v>
       </c>
       <c r="D547" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E547">
         <v>5.557338115167074</v>
@@ -28762,7 +28774,7 @@
         <v>1</v>
       </c>
       <c r="P547" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="548" spans="1:16">
@@ -28776,7 +28788,7 @@
         <v>3.655917474023632</v>
       </c>
       <c r="D548" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E548">
         <v>5.557338115167074</v>
@@ -28812,7 +28824,7 @@
         <v>1</v>
       </c>
       <c r="P548" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="549" spans="1:16">
@@ -28826,7 +28838,7 @@
         <v>3.504225052174785</v>
       </c>
       <c r="D549" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E549">
         <v>5.557338115167074</v>
@@ -28862,7 +28874,7 @@
         <v>1</v>
       </c>
       <c r="P549" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="550" spans="1:16">
@@ -28876,7 +28888,7 @@
         <v>5.346996730323884</v>
       </c>
       <c r="D550" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E550">
         <v>5.864438002961421</v>
@@ -28912,7 +28924,7 @@
         <v>1</v>
       </c>
       <c r="P550" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="551" spans="1:16">
@@ -28926,7 +28938,7 @@
         <v>5.267444590560391</v>
       </c>
       <c r="D551" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E551">
         <v>5.864438002961421</v>
@@ -28962,7 +28974,7 @@
         <v>1</v>
       </c>
       <c r="P551" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="552" spans="1:16">
@@ -28976,7 +28988,7 @@
         <v>3.796322429340982</v>
       </c>
       <c r="D552" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E552">
         <v>5.685955718590687</v>
@@ -29012,7 +29024,7 @@
         <v>1</v>
       </c>
       <c r="P552" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="553" spans="1:16">
@@ -29026,7 +29038,7 @@
         <v>3.641728676729411</v>
       </c>
       <c r="D553" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E553">
         <v>5.685955718590687</v>
@@ -29062,7 +29074,7 @@
         <v>1</v>
       </c>
       <c r="P553" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="554" spans="1:16">
@@ -29076,7 +29088,7 @@
         <v>3.69426723244667</v>
       </c>
       <c r="D554" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E554">
         <v>5.685955718590687</v>
@@ -29112,7 +29124,7 @@
         <v>1</v>
       </c>
       <c r="P554" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="555" spans="1:16">
@@ -29126,7 +29138,7 @@
         <v>3.761627605342749</v>
       </c>
       <c r="D555" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E555">
         <v>5.685955718590687</v>
@@ -29162,7 +29174,7 @@
         <v>1</v>
       </c>
       <c r="P555" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="556" spans="1:16">
@@ -29176,7 +29188,7 @@
         <v>3.630676464382844</v>
       </c>
       <c r="D556" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E556">
         <v>5.685955718590687</v>
@@ -29212,7 +29224,7 @@
         <v>1</v>
       </c>
       <c r="P556" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="557" spans="1:16">
@@ -29226,7 +29238,7 @@
         <v>5.466678794983334</v>
       </c>
       <c r="D557" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E557">
         <v>5.209318422087254</v>
@@ -29262,7 +29274,7 @@
         <v>1</v>
       </c>
       <c r="P557" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="558" spans="1:16">
@@ -29276,7 +29288,7 @@
         <v>5.390917489847062</v>
       </c>
       <c r="D558" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E558">
         <v>5.209318422087254</v>
@@ -29312,7 +29324,7 @@
         <v>1</v>
       </c>
       <c r="P558" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="559" spans="1:16">
@@ -29326,7 +29338,7 @@
         <v>4.159051079599863</v>
       </c>
       <c r="D559" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E559">
         <v>5.343391662540899</v>
@@ -29362,7 +29374,7 @@
         <v>1</v>
       </c>
       <c r="P559" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="560" spans="1:16">
@@ -29376,7 +29388,7 @@
         <v>4.237780255555339</v>
       </c>
       <c r="D560" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E560">
         <v>5.313343652467495</v>
@@ -29412,7 +29424,7 @@
         <v>1</v>
       </c>
       <c r="P560" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="561" spans="1:16">
@@ -29426,7 +29438,7 @@
         <v>4.283295642394084</v>
       </c>
       <c r="D561" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E561">
         <v>5.313343652467495</v>
@@ -29462,7 +29474,7 @@
         <v>1</v>
       </c>
       <c r="P561" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="562" spans="1:16">
@@ -29512,7 +29524,7 @@
         <v>1</v>
       </c>
       <c r="P562" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="563" spans="1:16">
@@ -29526,7 +29538,7 @@
         <v>4.047954928502808</v>
       </c>
       <c r="D563" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E563">
         <v>5.235960539108905</v>
@@ -29562,7 +29574,7 @@
         <v>1</v>
       </c>
       <c r="P563" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="564" spans="1:16">
@@ -29576,7 +29588,7 @@
         <v>4.137221058995326</v>
       </c>
       <c r="D564" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E564">
         <v>5.202705629828571</v>
@@ -29612,7 +29624,7 @@
         <v>1</v>
       </c>
       <c r="P564" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="565" spans="1:16">
@@ -29626,7 +29638,7 @@
         <v>4.169450720548237</v>
       </c>
       <c r="D565" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E565">
         <v>5.202705629828571</v>
@@ -29662,7 +29674,7 @@
         <v>1</v>
       </c>
       <c r="P565" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="566" spans="1:16">
@@ -29676,7 +29688,7 @@
         <v>6.314817655301979</v>
       </c>
       <c r="D566" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E566">
         <v>6.624319057953503</v>
@@ -29712,7 +29724,7 @@
         <v>1</v>
       </c>
       <c r="P566" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="567" spans="1:16">
@@ -29726,7 +29738,7 @@
         <v>4.059730080999771</v>
       </c>
       <c r="D567" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E567">
         <v>5.117447902330046</v>
@@ -29776,7 +29788,7 @@
         <v>4.081721754571493</v>
       </c>
       <c r="D568" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E568">
         <v>5.117447902330046</v>
@@ -29876,7 +29888,7 @@
         <v>4.030557457706422</v>
       </c>
       <c r="D570" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E570">
         <v>5.085351371462874</v>
@@ -29912,7 +29924,7 @@
         <v>1</v>
       </c>
       <c r="P570" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="571" spans="1:16">
@@ -29926,7 +29938,7 @@
         <v>4.048694889476288</v>
       </c>
       <c r="D571" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E571">
         <v>5.085351371462874</v>
@@ -29962,7 +29974,7 @@
         <v>1</v>
       </c>
       <c r="P571" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="572" spans="1:16">
@@ -30012,7 +30024,7 @@
         <v>1</v>
       </c>
       <c r="P572" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="573" spans="1:16">
@@ -30026,7 +30038,7 @@
         <v>3.737521317704196</v>
       </c>
       <c r="D573" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E573">
         <v>4.762944866631269</v>
@@ -30062,7 +30074,7 @@
         <v>1</v>
       </c>
       <c r="P573" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="574" spans="1:16">
@@ -30076,7 +30088,7 @@
         <v>3.716943268562606</v>
       </c>
       <c r="D574" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E574">
         <v>4.762944866631269</v>
@@ -30112,7 +30124,7 @@
         <v>1</v>
       </c>
       <c r="P574" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="575" spans="1:16">
@@ -30162,7 +30174,7 @@
         <v>1</v>
       </c>
       <c r="P575" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="576" spans="1:16">
@@ -30212,7 +30224,7 @@
         <v>1</v>
       </c>
       <c r="P576" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="577" spans="1:16">
@@ -30226,7 +30238,7 @@
         <v>3.710853293730853</v>
       </c>
       <c r="D577" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E577">
         <v>4.733603965539871</v>
@@ -30262,7 +30274,7 @@
         <v>1</v>
       </c>
       <c r="P577" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="578" spans="1:16">
@@ -30276,7 +30288,7 @@
         <v>3.686751906570006</v>
       </c>
       <c r="D578" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E578">
         <v>4.733603965539871</v>
@@ -30312,7 +30324,7 @@
         <v>1</v>
       </c>
       <c r="P578" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="579" spans="1:16">
@@ -30362,7 +30374,7 @@
         <v>1</v>
       </c>
       <c r="P579" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="580" spans="1:16">
@@ -30412,7 +30424,7 @@
         <v>1</v>
       </c>
       <c r="P580" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="581" spans="1:16">
@@ -30462,7 +30474,7 @@
         <v>1</v>
       </c>
       <c r="P581" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="582" spans="1:16">
@@ -30512,7 +30524,7 @@
         <v>1</v>
       </c>
       <c r="P582" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="583" spans="1:16">
@@ -30562,7 +30574,7 @@
         <v>1</v>
       </c>
       <c r="P583" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="584" spans="1:16">
@@ -30612,7 +30624,7 @@
         <v>1</v>
       </c>
       <c r="P584" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="585" spans="1:16">
@@ -30662,7 +30674,7 @@
         <v>1</v>
       </c>
       <c r="P585" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="586" spans="1:16">
@@ -30712,7 +30724,7 @@
         <v>1</v>
       </c>
       <c r="P586" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="587" spans="1:16">
@@ -30762,7 +30774,7 @@
         <v>1</v>
       </c>
       <c r="P587" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="588" spans="1:16">
@@ -30812,7 +30824,7 @@
         <v>1</v>
       </c>
       <c r="P588" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="589" spans="1:16">
@@ -30862,7 +30874,7 @@
         <v>1</v>
       </c>
       <c r="P589" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="590" spans="1:16">
@@ -30912,7 +30924,7 @@
         <v>1</v>
       </c>
       <c r="P590" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="591" spans="1:16">
@@ -31162,7 +31174,7 @@
         <v>1</v>
       </c>
       <c r="P595" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="596" spans="1:16">
@@ -31212,7 +31224,7 @@
         <v>1</v>
       </c>
       <c r="P596" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="597" spans="1:16">
@@ -31262,7 +31274,7 @@
         <v>1</v>
       </c>
       <c r="P597" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="598" spans="1:16">
@@ -31312,7 +31324,7 @@
         <v>1</v>
       </c>
       <c r="P598" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="599" spans="1:16">
@@ -31362,7 +31374,7 @@
         <v>1</v>
       </c>
       <c r="P599" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="600" spans="1:16">
@@ -31412,7 +31424,7 @@
         <v>1</v>
       </c>
       <c r="P600" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="601" spans="1:16">
@@ -31626,7 +31638,7 @@
         <v>6.312844467716282</v>
       </c>
       <c r="D605" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E605">
         <v>7.044140001633426</v>
@@ -31712,7 +31724,7 @@
         <v>1</v>
       </c>
       <c r="P606" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="607" spans="1:16">
@@ -31762,7 +31774,7 @@
         <v>1</v>
       </c>
       <c r="P607" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="608" spans="1:16">
@@ -31812,7 +31824,7 @@
         <v>1</v>
       </c>
       <c r="P608" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="609" spans="1:16">
@@ -31862,7 +31874,7 @@
         <v>1</v>
       </c>
       <c r="P609" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="610" spans="1:16">
@@ -31912,7 +31924,7 @@
         <v>1</v>
       </c>
       <c r="P610" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="611" spans="1:16">
@@ -31962,7 +31974,7 @@
         <v>1</v>
       </c>
       <c r="P611" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="612" spans="1:16">
@@ -32012,7 +32024,7 @@
         <v>1</v>
       </c>
       <c r="P612" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="613" spans="1:16">
@@ -32062,7 +32074,7 @@
         <v>1</v>
       </c>
       <c r="P613" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="614" spans="1:16">
@@ -32112,7 +32124,7 @@
         <v>1</v>
       </c>
       <c r="P614" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="615" spans="1:16">
@@ -32162,7 +32174,7 @@
         <v>1</v>
       </c>
       <c r="P615" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="616" spans="1:16">
@@ -32212,7 +32224,7 @@
         <v>1</v>
       </c>
       <c r="P616" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="617" spans="1:16">
@@ -32262,7 +32274,7 @@
         <v>1</v>
       </c>
       <c r="P617" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="618" spans="1:16">
@@ -32312,7 +32324,7 @@
         <v>1</v>
       </c>
       <c r="P618" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="619" spans="1:16">
@@ -32362,7 +32374,7 @@
         <v>1</v>
       </c>
       <c r="P619" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="620" spans="1:16">
@@ -32412,7 +32424,7 @@
         <v>1</v>
       </c>
       <c r="P620" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="621" spans="1:16">
@@ -32462,7 +32474,7 @@
         <v>1</v>
       </c>
       <c r="P621" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="622" spans="1:16">
@@ -32476,7 +32488,7 @@
         <v>6.52789956231641</v>
       </c>
       <c r="D622" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E622">
         <v>6.970266187949232</v>
@@ -32512,7 +32524,7 @@
         <v>1</v>
       </c>
       <c r="P622" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="623" spans="1:16">
@@ -32562,7 +32574,7 @@
         <v>1</v>
       </c>
       <c r="P623" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="624" spans="1:16">
@@ -32612,7 +32624,7 @@
         <v>1</v>
       </c>
       <c r="P624" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="625" spans="1:16">
@@ -32662,7 +32674,7 @@
         <v>1</v>
       </c>
       <c r="P625" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="626" spans="1:16">
@@ -32676,7 +32688,7 @@
         <v>2.603543847706</v>
       </c>
       <c r="D626" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E626">
         <v>4.770094008155837</v>
@@ -32712,7 +32724,7 @@
         <v>1</v>
       </c>
       <c r="P626" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="627" spans="1:16">
@@ -32762,7 +32774,7 @@
         <v>1</v>
       </c>
       <c r="P627" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="628" spans="1:16">
@@ -32812,7 +32824,7 @@
         <v>1</v>
       </c>
       <c r="P628" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="629" spans="1:16">
@@ -32862,7 +32874,7 @@
         <v>1</v>
       </c>
       <c r="P629" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="630" spans="1:16">
@@ -32912,7 +32924,7 @@
         <v>1</v>
       </c>
       <c r="P630" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="631" spans="1:16">
@@ -32962,7 +32974,7 @@
         <v>1</v>
       </c>
       <c r="P631" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="632" spans="1:16">
@@ -32976,7 +32988,7 @@
         <v>2.478182256708074</v>
       </c>
       <c r="D632" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E632">
         <v>4.645810796435313</v>
@@ -33012,7 +33024,7 @@
         <v>1</v>
       </c>
       <c r="P632" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="633" spans="1:16">
@@ -33062,7 +33074,7 @@
         <v>1</v>
       </c>
       <c r="P633" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="634" spans="1:16">
@@ -33112,7 +33124,7 @@
         <v>1</v>
       </c>
       <c r="P634" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="635" spans="1:16">
@@ -33162,7 +33174,7 @@
         <v>1</v>
       </c>
       <c r="P635" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="636" spans="1:16">
@@ -33212,7 +33224,7 @@
         <v>1</v>
       </c>
       <c r="P636" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="637" spans="1:16">
@@ -33226,7 +33238,7 @@
         <v>2.30694018299906</v>
       </c>
       <c r="D637" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E637">
         <v>4.476041772822722</v>
@@ -33262,7 +33274,7 @@
         <v>1</v>
       </c>
       <c r="P637" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="638" spans="1:16">
@@ -33276,7 +33288,7 @@
         <v>5.979313720333828</v>
       </c>
       <c r="D638" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E638">
         <v>6.921637837986275</v>
@@ -33312,7 +33324,7 @@
         <v>1</v>
       </c>
       <c r="P638" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="639" spans="1:16">
@@ -33326,7 +33338,7 @@
         <v>6.118014825265853</v>
       </c>
       <c r="D639" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E639">
         <v>6.921637837986275</v>
@@ -33362,7 +33374,7 @@
         <v>1</v>
       </c>
       <c r="P639" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="640" spans="1:16">
@@ -33376,7 +33388,7 @@
         <v>2.180042495856011</v>
       </c>
       <c r="D640" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E640">
         <v>4.350235678687355</v>
@@ -33412,7 +33424,7 @@
         <v>1</v>
       </c>
       <c r="P640" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="641" spans="1:16">
@@ -33462,7 +33474,7 @@
         <v>1</v>
       </c>
       <c r="P641" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="642" spans="1:16">
@@ -33512,7 +33524,7 @@
         <v>1</v>
       </c>
       <c r="P642" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="643" spans="1:16">
@@ -33562,7 +33574,7 @@
         <v>1</v>
       </c>
       <c r="P643" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="644" spans="1:16">
@@ -33576,7 +33588,7 @@
         <v>2.005501953213372</v>
       </c>
       <c r="D644" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E644">
         <v>4.177196560067447</v>
@@ -33612,7 +33624,7 @@
         <v>1</v>
       </c>
       <c r="P644" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="645" spans="1:16">
@@ -33626,7 +33638,7 @@
         <v>6.03048720269387</v>
       </c>
       <c r="D645" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E645">
         <v>7.646218976894719</v>
@@ -33662,7 +33674,7 @@
         <v>1</v>
       </c>
       <c r="P645" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="646" spans="1:16">
@@ -33676,7 +33688,7 @@
         <v>6.160487202693869</v>
       </c>
       <c r="D646" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E646">
         <v>7.646218976894719</v>
@@ -33712,7 +33724,7 @@
         <v>1</v>
       </c>
       <c r="P646" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="647" spans="1:16">
@@ -33776,7 +33788,7 @@
         <v>5.929250610805834</v>
       </c>
       <c r="D648" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E648">
         <v>6.44678700451809</v>
@@ -33826,7 +33838,7 @@
         <v>6.059250610805833</v>
       </c>
       <c r="D649" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E649">
         <v>6.44678700451809</v>
@@ -33912,7 +33924,7 @@
         <v>1</v>
       </c>
       <c r="P650" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="651" spans="1:16">
@@ -33926,7 +33938,7 @@
         <v>6.444007644774246</v>
       </c>
       <c r="D651" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E651">
         <v>5.9080963375586</v>
@@ -33962,7 +33974,7 @@
         <v>1</v>
       </c>
       <c r="P651" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="652" spans="1:16">
@@ -33976,7 +33988,7 @@
         <v>5.977845942063905</v>
       </c>
       <c r="D652" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E652">
         <v>5.9080963375586</v>
@@ -34012,7 +34024,7 @@
         <v>1</v>
       </c>
       <c r="P652" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="653" spans="1:16">
@@ -34076,7 +34088,7 @@
         <v>6.325113724849238</v>
       </c>
       <c r="D654" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="E654">
         <v>5.966484401224733</v>
@@ -34126,7 +34138,7 @@
         <v>6.616965483162407</v>
       </c>
       <c r="D655" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="E655">
         <v>5.966484401224733</v>
@@ -34362,7 +34374,7 @@
         <v>1</v>
       </c>
       <c r="P659" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="660" spans="1:16">
@@ -34376,7 +34388,7 @@
         <v>6.182411935806901</v>
       </c>
       <c r="D660" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E660">
         <v>5.820555041914538</v>
@@ -34412,7 +34424,7 @@
         <v>1</v>
       </c>
       <c r="P660" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="661" spans="1:16">
@@ -34426,7 +34438,7 @@
         <v>6.479370608860847</v>
       </c>
       <c r="D661" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E661">
         <v>5.820555041914538</v>
@@ -34462,7 +34474,7 @@
         <v>1</v>
       </c>
       <c r="P661" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="662" spans="1:16">
@@ -34476,7 +34488,7 @@
         <v>6.247760471854665</v>
       </c>
       <c r="D662" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E662">
         <v>5.820555041914538</v>
@@ -34512,7 +34524,7 @@
         <v>1</v>
       </c>
       <c r="P662" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="663" spans="1:16">
@@ -34626,7 +34638,7 @@
         <v>6.052746661470383</v>
       </c>
       <c r="D665" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E665">
         <v>5.747828147206722</v>
@@ -34676,7 +34688,7 @@
         <v>6.354345707327784</v>
       </c>
       <c r="D666" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E666">
         <v>5.747828147206722</v>
@@ -34726,7 +34738,7 @@
         <v>6.106229101349317</v>
       </c>
       <c r="D667" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E667">
         <v>5.747828147206722</v>
@@ -34876,7 +34888,7 @@
         <v>5.992378168346487</v>
       </c>
       <c r="D670" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E670">
         <v>5.919638041522585</v>
@@ -34926,7 +34938,7 @@
         <v>6.296137640849427</v>
       </c>
       <c r="D671" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E671">
         <v>5.919638041522585</v>
@@ -34976,7 +34988,7 @@
         <v>6.0403360886604</v>
       </c>
       <c r="D672" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E672">
         <v>5.919638041522585</v>
@@ -35062,7 +35074,7 @@
         <v>1</v>
       </c>
       <c r="P673" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="674" spans="1:16">
@@ -35112,7 +35124,7 @@
         <v>1</v>
       </c>
       <c r="P674" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="675" spans="1:16">
@@ -35126,7 +35138,7 @@
         <v>5.931074248482098</v>
       </c>
       <c r="D675" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E675">
         <v>5.817063063996034</v>
@@ -35162,7 +35174,7 @@
         <v>1</v>
       </c>
       <c r="P675" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="676" spans="1:16">
@@ -35176,7 +35188,7 @@
         <v>6.237027624047666</v>
       </c>
       <c r="D676" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E676">
         <v>5.817063063996034</v>
@@ -35212,7 +35224,7 @@
         <v>1</v>
       </c>
       <c r="P676" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="677" spans="1:16">
@@ -35226,7 +35238,7 @@
         <v>5.973422045250139</v>
       </c>
       <c r="D677" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E677">
         <v>5.817063063996034</v>
@@ -35262,7 +35274,7 @@
         <v>1</v>
       </c>
       <c r="P677" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="678" spans="1:16">
@@ -35376,7 +35388,7 @@
         <v>5.839386641650073</v>
       </c>
       <c r="D680" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E680">
         <v>4.893781158276536</v>
@@ -35426,7 +35438,7 @@
         <v>6.148621271038877</v>
       </c>
       <c r="D681" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E681">
         <v>4.893781158276536</v>
@@ -35476,7 +35488,7 @@
         <v>5.873343803641564</v>
       </c>
       <c r="D682" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E682">
         <v>4.893781158276536</v>
@@ -35576,7 +35588,7 @@
         <v>6.049313264972337</v>
       </c>
       <c r="D684" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E684">
         <v>4.936335249131968</v>
@@ -35626,7 +35638,7 @@
         <v>6.175722584965069</v>
       </c>
       <c r="D685" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E685">
         <v>4.936335249131968</v>
@@ -35676,7 +35688,7 @@
         <v>5.760924613317037</v>
       </c>
       <c r="D686" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E686">
         <v>4.936335249131968</v>
@@ -35826,7 +35838,7 @@
         <v>5.905539797299475</v>
       </c>
       <c r="D689" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E689">
         <v>5.270502414665344</v>
@@ -35876,7 +35888,7 @@
         <v>6.021734035283636</v>
       </c>
       <c r="D690" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E690">
         <v>5.270502414665344</v>
@@ -36026,7 +36038,7 @@
         <v>5.810134805942958</v>
       </c>
       <c r="D693" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E693">
         <v>4.46837075668304</v>
@@ -36076,7 +36088,7 @@
         <v>5.919550534467003</v>
       </c>
       <c r="D694" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E694">
         <v>4.46837075668304</v>
@@ -36126,7 +36138,7 @@
         <v>5.597681787127293</v>
       </c>
       <c r="D695" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="E695">
         <v>5.175448484795162</v>
@@ -36176,7 +36188,7 @@
         <v>5.69200276245871</v>
       </c>
       <c r="D696" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="E696">
         <v>5.175448484795162</v>
@@ -36262,7 +36274,7 @@
         <v>1</v>
       </c>
       <c r="P697" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="698" spans="1:16">
@@ -36312,7 +36324,7 @@
         <v>1</v>
       </c>
       <c r="P698" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="699" spans="1:16">
@@ -36362,7 +36374,7 @@
         <v>1</v>
       </c>
       <c r="P699" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="700" spans="1:16">
@@ -36412,7 +36424,7 @@
         <v>1</v>
       </c>
       <c r="P700" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="701" spans="1:16">
@@ -36426,7 +36438,7 @@
         <v>10.58920111380781</v>
       </c>
       <c r="D701" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="E701">
         <v>10.63805069137965</v>
@@ -36462,7 +36474,7 @@
         <v>1</v>
       </c>
       <c r="P701" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="702" spans="1:16">
@@ -36512,7 +36524,7 @@
         <v>1</v>
       </c>
       <c r="P702" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="703" spans="1:16">
@@ -36526,7 +36538,7 @@
         <v>13.29070024337744</v>
       </c>
       <c r="D703" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="E703">
         <v>12.1104855745369</v>
@@ -36562,7 +36574,7 @@
         <v>1</v>
       </c>
       <c r="P703" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="704" spans="1:16">
@@ -36612,7 +36624,7 @@
         <v>1</v>
       </c>
       <c r="P704" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="705" spans="1:16">
@@ -36626,7 +36638,7 @@
         <v>13.05967948318782</v>
       </c>
       <c r="D705" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="E705">
         <v>11.87581437344135</v>
@@ -36662,7 +36674,7 @@
         <v>1</v>
       </c>
       <c r="P705" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="706" spans="1:16">
@@ -36712,7 +36724,7 @@
         <v>1</v>
       </c>
       <c r="P706" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="707" spans="1:16">
@@ -36726,7 +36738,7 @@
         <v>12.8170626988293</v>
       </c>
       <c r="D707" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E707">
         <v>10.97022453374666</v>
@@ -36762,7 +36774,7 @@
         <v>1</v>
       </c>
       <c r="P707" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="708" spans="1:16">
@@ -36812,7 +36824,7 @@
         <v>1</v>
       </c>
       <c r="P708" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="709" spans="1:16">
@@ -36826,7 +36838,7 @@
         <v>12.5987805539735</v>
       </c>
       <c r="D709" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E709">
         <v>10.73863851098768</v>
@@ -36862,7 +36874,7 @@
         <v>1</v>
       </c>
       <c r="P709" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="710" spans="1:16">
@@ -36912,7 +36924,7 @@
         <v>1</v>
       </c>
       <c r="P710" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="711" spans="1:16">
@@ -36962,7 +36974,7 @@
         <v>1</v>
       </c>
       <c r="P711" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="712" spans="1:16">
@@ -37012,7 +37024,7 @@
         <v>1</v>
       </c>
       <c r="P712" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="713" spans="1:16">
@@ -37026,7 +37038,7 @@
         <v>12.45336310880131</v>
       </c>
       <c r="D713" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E713">
         <v>10.58435815154991</v>
@@ -37062,7 +37074,7 @@
         <v>1</v>
       </c>
       <c r="P713" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="714" spans="1:16">
@@ -37112,7 +37124,7 @@
         <v>1</v>
       </c>
       <c r="P714" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="715" spans="1:16">
@@ -37162,7 +37174,7 @@
         <v>1</v>
       </c>
       <c r="P715" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="716" spans="1:16">
@@ -37212,7 +37224,7 @@
         <v>1</v>
       </c>
       <c r="P716" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="717" spans="1:16">
@@ -37262,7 +37274,7 @@
         <v>1</v>
       </c>
       <c r="P717" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="718" spans="1:16">
@@ -37312,7 +37324,7 @@
         <v>1</v>
       </c>
       <c r="P718" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="719" spans="1:16">
@@ -37362,7 +37374,7 @@
         <v>1</v>
       </c>
       <c r="P719" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="720" spans="1:16">
@@ -37376,7 +37388,7 @@
         <v>12.29210392935995</v>
       </c>
       <c r="D720" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E720">
         <v>10.41327053453538</v>
@@ -37412,7 +37424,7 @@
         <v>1</v>
       </c>
       <c r="P720" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="721" spans="1:16">
@@ -37426,7 +37438,7 @@
         <v>9.171282848330055</v>
       </c>
       <c r="D721" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E721">
         <v>6.850968108671186</v>
@@ -37462,7 +37474,7 @@
         <v>1</v>
       </c>
       <c r="P721" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="722" spans="1:16">
@@ -37476,7 +37488,7 @@
         <v>8.830116243154617</v>
       </c>
       <c r="D722" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E722">
         <v>6.850968108671186</v>
@@ -37512,7 +37524,7 @@
         <v>1</v>
       </c>
       <c r="P722" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="723" spans="1:16">
@@ -37676,7 +37688,7 @@
         <v>12.09795277153261</v>
       </c>
       <c r="D726" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E726">
         <v>10.20728623616326</v>
@@ -37726,7 +37738,7 @@
         <v>8.629829382822578</v>
       </c>
       <c r="D727" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E727">
         <v>7.040051561279032</v>
@@ -37812,7 +37824,7 @@
         <v>1</v>
       </c>
       <c r="P728" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="729" spans="1:16">
@@ -37862,7 +37874,7 @@
         <v>1</v>
       </c>
       <c r="P729" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="730" spans="1:16">
@@ -37912,7 +37924,7 @@
         <v>1</v>
       </c>
       <c r="P730" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="731" spans="1:16">
@@ -37926,7 +37938,7 @@
         <v>11.86477339723001</v>
       </c>
       <c r="D731" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E731">
         <v>9.95989502640656</v>
@@ -37962,7 +37974,7 @@
         <v>1</v>
       </c>
       <c r="P731" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="732" spans="1:16">
@@ -37976,7 +37988,7 @@
         <v>8.389280908654889</v>
       </c>
       <c r="D732" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E732">
         <v>6.803093216210396</v>
@@ -38012,7 +38024,7 @@
         <v>1</v>
       </c>
       <c r="P732" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="733" spans="1:16">
@@ -38062,7 +38074,7 @@
         <v>1</v>
       </c>
       <c r="P733" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="734" spans="1:16">
@@ -38112,7 +38124,7 @@
         <v>1</v>
       </c>
       <c r="P734" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="735" spans="1:16">
@@ -38162,7 +38174,7 @@
         <v>1</v>
       </c>
       <c r="P735" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="736" spans="1:16">
@@ -38212,7 +38224,7 @@
         <v>1</v>
       </c>
       <c r="P736" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="737" spans="1:16">
@@ -38226,7 +38238,7 @@
         <v>7.721090409497048</v>
       </c>
       <c r="D737" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="E737">
         <v>6.845979077114176</v>
@@ -38262,7 +38274,7 @@
         <v>1</v>
       </c>
       <c r="P737" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="738" spans="1:16">
@@ -38312,7 +38324,7 @@
         <v>1</v>
       </c>
       <c r="P738" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="739" spans="1:16">
@@ -38362,7 +38374,7 @@
         <v>1</v>
       </c>
       <c r="P739" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="740" spans="1:16">
@@ -38412,7 +38424,7 @@
         <v>1</v>
       </c>
       <c r="P740" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="741" spans="1:16">
@@ -38426,7 +38438,7 @@
         <v>7.431928747420816</v>
       </c>
       <c r="D741" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E741">
         <v>6.954602200047407</v>
@@ -38462,7 +38474,7 @@
         <v>1</v>
       </c>
       <c r="P741" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="742" spans="1:16">
@@ -38512,7 +38524,7 @@
         <v>1</v>
       </c>
       <c r="P742" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="743" spans="1:16">
@@ -38562,7 +38574,7 @@
         <v>1</v>
       </c>
       <c r="P743" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="744" spans="1:16">
@@ -38612,7 +38624,7 @@
         <v>1</v>
       </c>
       <c r="P744" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="745" spans="1:16">
@@ -38662,7 +38674,7 @@
         <v>1</v>
       </c>
       <c r="P745" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="746" spans="1:16">
@@ -38676,7 +38688,7 @@
         <v>7.15411432552343</v>
       </c>
       <c r="D746" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E746">
         <v>7.077702572180645</v>
@@ -38712,7 +38724,7 @@
         <v>1</v>
       </c>
       <c r="P746" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="747" spans="1:16">
@@ -38976,7 +38988,7 @@
         <v>6.656074286112602</v>
       </c>
       <c r="D752" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E752">
         <v>7.106777983579878</v>
@@ -39062,7 +39074,7 @@
         <v>1</v>
       </c>
       <c r="P753" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="754" spans="1:16">
@@ -39112,7 +39124,7 @@
         <v>1</v>
       </c>
       <c r="P754" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="755" spans="1:16">
@@ -39162,7 +39174,7 @@
         <v>1</v>
       </c>
       <c r="P755" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="756" spans="1:16">
@@ -39212,7 +39224,7 @@
         <v>1</v>
       </c>
       <c r="P756" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="757" spans="1:16">
@@ -39262,7 +39274,7 @@
         <v>1</v>
       </c>
       <c r="P757" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="758" spans="1:16">
@@ -39312,7 +39324,7 @@
         <v>1</v>
       </c>
       <c r="P758" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="759" spans="1:16">
@@ -39662,7 +39674,7 @@
         <v>1</v>
       </c>
       <c r="P765" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="766" spans="1:16">
@@ -39712,7 +39724,7 @@
         <v>1</v>
       </c>
       <c r="P766" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="767" spans="1:16">
@@ -39726,7 +39738,7 @@
         <v>5.189787984798581</v>
       </c>
       <c r="D767" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E767">
         <v>6.127393152460147</v>
@@ -39762,7 +39774,7 @@
         <v>1</v>
       </c>
       <c r="P767" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="768" spans="1:16">
@@ -39776,7 +39788,7 @@
         <v>5.337615079752425</v>
       </c>
       <c r="D768" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E768">
         <v>6.127393152460147</v>
@@ -39812,7 +39824,7 @@
         <v>1</v>
       </c>
       <c r="P768" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="769" spans="1:16">
@@ -39926,7 +39938,7 @@
         <v>4.573548410677798</v>
       </c>
       <c r="D771" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E771">
         <v>5.983161604764781</v>
@@ -39976,7 +39988,7 @@
         <v>4.718587091269107</v>
       </c>
       <c r="D772" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E772">
         <v>5.983161604764781</v>
@@ -40062,7 +40074,7 @@
         <v>1</v>
       </c>
       <c r="P773" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="774" spans="1:16">
@@ -40112,7 +40124,7 @@
         <v>1</v>
       </c>
       <c r="P774" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="775" spans="1:16">
@@ -40162,7 +40174,7 @@
         <v>1</v>
       </c>
       <c r="P775" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="776" spans="1:16">
@@ -40212,7 +40224,7 @@
         <v>1</v>
       </c>
       <c r="P776" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="777" spans="1:16">
@@ -40462,7 +40474,7 @@
         <v>1</v>
       </c>
       <c r="P781" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="782" spans="1:16">
@@ -40512,7 +40524,7 @@
         <v>1</v>
       </c>
       <c r="P782" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="783" spans="1:16">
@@ -40562,7 +40574,7 @@
         <v>1</v>
       </c>
       <c r="P783" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="784" spans="1:16">
@@ -40962,7 +40974,7 @@
         <v>1</v>
       </c>
       <c r="P791" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="792" spans="1:16">
@@ -41012,7 +41024,7 @@
         <v>1</v>
       </c>
       <c r="P792" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="793" spans="1:16">
@@ -41062,7 +41074,7 @@
         <v>1</v>
       </c>
       <c r="P793" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="794" spans="1:16">
@@ -41112,7 +41124,7 @@
         <v>1</v>
       </c>
       <c r="P794" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="795" spans="1:16">
@@ -41362,7 +41374,7 @@
         <v>1</v>
       </c>
       <c r="P799" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="800" spans="1:16">
@@ -41376,7 +41388,7 @@
         <v>1.03967143846625</v>
       </c>
       <c r="D800" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E800">
         <v>2.609188567947417</v>
@@ -41412,7 +41424,7 @@
         <v>1</v>
       </c>
       <c r="P800" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="801" spans="1:16">
@@ -41426,7 +41438,7 @@
         <v>0.8130094478294367</v>
       </c>
       <c r="D801" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E801">
         <v>2.609188567947417</v>
@@ -41462,7 +41474,7 @@
         <v>1</v>
       </c>
       <c r="P801" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="802" spans="1:16">
@@ -41512,7 +41524,7 @@
         <v>1</v>
       </c>
       <c r="P802" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="803" spans="1:16">
@@ -41526,7 +41538,7 @@
         <v>0.7465491084079581</v>
       </c>
       <c r="D803" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E803">
         <v>2.329329691737918</v>
@@ -41562,7 +41574,7 @@
         <v>1</v>
       </c>
       <c r="P803" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="804" spans="1:16">
@@ -41576,7 +41588,7 @@
         <v>0.5106027000769942</v>
       </c>
       <c r="D804" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E804">
         <v>2.329329691737918</v>
@@ -41612,7 +41624,7 @@
         <v>1</v>
       </c>
       <c r="P804" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="805" spans="1:16">
@@ -41626,7 +41638,7 @@
         <v>0.4893560218813207</v>
       </c>
       <c r="D805" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E805">
         <v>2.083774301434204</v>
@@ -41676,7 +41688,7 @@
         <v>0.2452632261943108</v>
       </c>
       <c r="D806" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E806">
         <v>2.083774301434204</v>
@@ -41726,7 +41738,7 @@
         <v>3.38720643044401</v>
       </c>
       <c r="D807" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E807">
         <v>1.346565161657761</v>
@@ -41776,7 +41788,7 @@
         <v>0.03330516332946587</v>
       </c>
       <c r="D808" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E808">
         <v>1.648359228337185</v>
@@ -41826,7 +41838,7 @@
         <v>-0.2252326821759354</v>
       </c>
       <c r="D809" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E809">
         <v>1.648359228337185</v>
@@ -41876,7 +41888,7 @@
         <v>2.979030594147371</v>
       </c>
       <c r="D810" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E810">
         <v>0.9008321958333205</v>
@@ -41926,7 +41938,7 @@
         <v>-0.3050434949915584</v>
       </c>
       <c r="D811" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E811">
         <v>1.325320464057839</v>
@@ -41962,7 +41974,7 @@
         <v>1</v>
       </c>
       <c r="P811" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="812" spans="1:16">
@@ -41976,7 +41988,7 @@
         <v>-0.5742982663261245</v>
       </c>
       <c r="D812" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E812">
         <v>1.325320464057839</v>
@@ -42012,7 +42024,7 @@
         <v>1</v>
       </c>
       <c r="P812" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="813" spans="1:16">
@@ -42026,7 +42038,7 @@
         <v>2.676200890003035</v>
       </c>
       <c r="D813" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E813">
         <v>0.570138484533139</v>
@@ -42062,7 +42074,7 @@
         <v>1</v>
       </c>
       <c r="P813" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="814" spans="1:16">
@@ -42076,7 +42088,7 @@
         <v>-1.542729235915701</v>
       </c>
       <c r="D814" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E814">
         <v>0.8740710626510406</v>
@@ -42126,7 +42138,7 @@
         <v>-1.06190425457612</v>
       </c>
       <c r="D815" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E815">
         <v>0.8740710626510406</v>
@@ -42176,7 +42188,7 @@
         <v>2.253181308968607</v>
       </c>
       <c r="D816" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E816">
         <v>0.1081959693489338</v>
@@ -42226,7 +42238,7 @@
         <v>-1.645106114375984</v>
       </c>
       <c r="D817" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E817">
         <v>0.7789101756240804</v>
@@ -42276,7 +42288,7 @@
         <v>-1.164732132500994</v>
       </c>
       <c r="D818" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E818">
         <v>0.7789101756240804</v>
@@ -42326,7 +42338,7 @@
         <v>1.705918320624114</v>
       </c>
       <c r="D819" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E819">
         <v>0.01078008499905536</v>
@@ -42376,7 +42388,7 @@
         <v>2.163973614874138</v>
       </c>
       <c r="D820" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E820">
         <v>0.01078008499905536</v>
@@ -42426,7 +42438,7 @@
         <v>2.083749225749141</v>
       </c>
       <c r="D821" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E821">
         <v>-0.02146380625091737</v>
@@ -42476,7 +42488,7 @@
         <v>-1.354990011712744</v>
       </c>
       <c r="D822" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E822">
         <v>1.048577566205335</v>
@@ -42526,7 +42538,7 @@
         <v>-0.8733379853326184</v>
       </c>
       <c r="D823" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E823">
         <v>1.048577566205335</v>
@@ -42576,7 +42588,7 @@
         <v>1.965361355164372</v>
       </c>
       <c r="D824" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E824">
         <v>0.2868376981059342</v>
@@ -42626,7 +42638,7 @@
         <v>2.41677081798775</v>
       </c>
       <c r="D825" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E825">
         <v>0.2868376981059342</v>
@@ -42676,7 +42688,7 @@
         <v>2.335779602159679</v>
       </c>
       <c r="D826" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E826">
         <v>0.246925539825213</v>
@@ -42726,7 +42738,7 @@
         <v>-1.093559587288276</v>
       </c>
       <c r="D827" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E827">
         <v>-1.564638644835625</v>
@@ -42776,7 +42788,7 @@
         <v>-1.266714738768137</v>
       </c>
       <c r="D828" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E828">
         <v>0.4727739583005963</v>
@@ -42812,7 +42824,7 @@
         <v>1</v>
       </c>
       <c r="P828" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="829" spans="1:16">
@@ -42826,7 +42838,7 @@
         <v>-0.7846738345336348</v>
       </c>
       <c r="D829" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E829">
         <v>0.5188966710041001</v>
@@ -42862,7 +42874,7 @@
         <v>1</v>
       </c>
       <c r="P829" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="830" spans="1:16">
@@ -42876,7 +42888,7 @@
         <v>2.044303559603822</v>
       </c>
       <c r="D830" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E830">
         <v>0.3708353146523429</v>
@@ -42912,7 +42924,7 @@
         <v>1</v>
       </c>
       <c r="P830" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="831" spans="1:16">
@@ -42926,7 +42938,7 @@
         <v>2.412466315043719</v>
       </c>
       <c r="D831" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E831">
         <v>0.3285898892453361</v>
@@ -42962,7 +42974,7 @@
         <v>1</v>
       </c>
       <c r="P831" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="832" spans="1:16">
@@ -42976,7 +42988,7 @@
         <v>-1.016717323262487</v>
       </c>
       <c r="D832" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E832">
         <v>-1.725082876878652</v>
@@ -43012,7 +43024,7 @@
         <v>1</v>
       </c>
       <c r="P832" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="833" spans="1:16">
@@ -43026,7 +43038,7 @@
         <v>-1.012419255686936</v>
       </c>
       <c r="D833" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E833">
         <v>0.7130663861460427</v>
@@ -43076,7 +43088,7 @@
         <v>2.271713176632382</v>
       </c>
       <c r="D834" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E834">
         <v>0.563841217205912</v>
@@ -43126,7 +43138,7 @@
         <v>2.633378514442889</v>
       </c>
       <c r="D835" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E835">
         <v>0.563841217205912</v>
@@ -43176,7 +43188,7 @@
         <v>-0.7953570260957719</v>
       </c>
       <c r="D836" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E836">
         <v>-0.6798364854873604</v>
@@ -43226,7 +43238,7 @@
         <v>-1.154980882524804</v>
       </c>
       <c r="D837" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E837">
         <v>0.3632888214250194</v>
@@ -43262,7 +43274,7 @@
         <v>1</v>
       </c>
       <c r="P837" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="838" spans="1:16">
@@ -43276,7 +43288,7 @@
         <v>2.144224144702488</v>
       </c>
       <c r="D838" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E838">
         <v>0.3406232020973725</v>
@@ -43312,7 +43324,7 @@
         <v>1</v>
       </c>
       <c r="P838" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="839" spans="1:16">
@@ -43326,7 +43338,7 @@
         <v>2.509532026282422</v>
       </c>
       <c r="D839" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E839">
         <v>0.3406232020973725</v>
@@ -43362,7 +43374,7 @@
         <v>1</v>
       </c>
       <c r="P839" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="840" spans="1:16">
@@ -43412,7 +43424,7 @@
         <v>1</v>
       </c>
       <c r="P840" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="841" spans="1:16">
@@ -43426,7 +43438,7 @@
         <v>-0.7435135480053319</v>
       </c>
       <c r="D841" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E841">
         <v>0.7484730002152737</v>
@@ -43576,7 +43588,7 @@
         <v>-0.3742444036399846</v>
       </c>
       <c r="D844" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E844">
         <v>1.094154467958163</v>
@@ -43612,7 +43624,7 @@
         <v>1</v>
       </c>
       <c r="P844" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="845" spans="1:16">
@@ -43662,7 +43674,7 @@
         <v>1</v>
       </c>
       <c r="P845" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="846" spans="1:16">
@@ -43712,7 +43724,7 @@
         <v>1</v>
       </c>
       <c r="P846" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="847" spans="1:16">
@@ -43726,7 +43738,7 @@
         <v>-0.2301600625778306</v>
       </c>
       <c r="D847" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E847">
         <v>1.229035183710177</v>
@@ -43762,7 +43774,7 @@
         <v>1</v>
       </c>
       <c r="P847" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="848" spans="1:16">
@@ -43812,7 +43824,7 @@
         <v>1</v>
       </c>
       <c r="P848" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="849" spans="1:16">
@@ -43862,7 +43874,7 @@
         <v>1</v>
       </c>
       <c r="P849" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="850" spans="1:16">
@@ -43876,7 +43888,7 @@
         <v>-0.008911774850371756</v>
       </c>
       <c r="D850" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="E850">
         <v>0.5721947646345491</v>
@@ -43912,7 +43924,7 @@
         <v>1</v>
       </c>
       <c r="P850" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="851" spans="1:16">
@@ -43926,7 +43938,7 @@
         <v>-0.1112036199752922</v>
       </c>
       <c r="D851" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E851">
         <v>1.340393087027532</v>
@@ -44076,7 +44088,7 @@
         <v>0.09903988671845454</v>
       </c>
       <c r="D854" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="E854">
         <v>1.106317252320714</v>
@@ -44126,7 +44138,7 @@
         <v>-0.06944114310240224</v>
       </c>
       <c r="D855" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E855">
         <v>1.379487916699293</v>
@@ -44162,7 +44174,7 @@
         <v>1</v>
       </c>
       <c r="P855" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="856" spans="1:16">
@@ -44212,7 +44224,7 @@
         <v>1</v>
       </c>
       <c r="P856" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="857" spans="1:16">
@@ -44262,7 +44274,7 @@
         <v>1</v>
       </c>
       <c r="P857" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="858" spans="1:16">
@@ -44276,7 +44288,7 @@
         <v>0.1369388745414319</v>
       </c>
       <c r="D858" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E858">
         <v>1.371101739245933</v>
@@ -44312,7 +44324,7 @@
         <v>1</v>
       </c>
       <c r="P858" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="859" spans="1:16">
@@ -44326,7 +44338,7 @@
         <v>12.65888206048432</v>
       </c>
       <c r="D859" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E859">
         <v>13.43349103432044</v>
@@ -44362,57 +44374,357 @@
         <v>1</v>
       </c>
       <c r="P859" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="860" spans="1:16">
       <c r="A860" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B860" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C860">
-        <v>12.57849638595733</v>
+        <v>13.67315026490144</v>
       </c>
       <c r="D860" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="E860">
-        <v>13.3576727276643</v>
+        <v>13.48349103432044</v>
       </c>
       <c r="F860">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G860">
-        <v>0.04986150361404267</v>
+        <v>0.04792684973509856</v>
       </c>
       <c r="H860">
-        <v>0.0485223272723357</v>
+        <v>0.04849650896567955</v>
       </c>
       <c r="I860">
-        <v>0.7791763417069717</v>
+        <v>0.1896592305810039</v>
       </c>
       <c r="J860">
-        <v>0.8473410733655758</v>
+        <v>0.8436871790688943</v>
       </c>
       <c r="K860">
-        <v>22</v>
+        <v>20.3</v>
       </c>
       <c r="L860">
-        <v>31.22</v>
+        <v>30.8</v>
       </c>
       <c r="M860">
         <v>20.75</v>
       </c>
       <c r="N860">
+        <v>30.99</v>
+      </c>
+      <c r="O860">
+        <v>1</v>
+      </c>
+      <c r="P860" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="861" spans="1:16">
+      <c r="A861" s="1">
+        <v>0</v>
+      </c>
+      <c r="B861" t="s">
+        <v>154</v>
+      </c>
+      <c r="C861">
+        <v>12.57849638595733</v>
+      </c>
+      <c r="D861" t="s">
+        <v>266</v>
+      </c>
+      <c r="E861">
+        <v>13.3576727276643</v>
+      </c>
+      <c r="F861">
+        <v>1</v>
+      </c>
+      <c r="G861">
+        <v>0.04986150361404267</v>
+      </c>
+      <c r="H861">
+        <v>0.0485223272723357</v>
+      </c>
+      <c r="I861">
+        <v>0.7791763417069717</v>
+      </c>
+      <c r="J861">
+        <v>0.8473410733655758</v>
+      </c>
+      <c r="K861">
+        <v>22</v>
+      </c>
+      <c r="L861">
+        <v>31.22</v>
+      </c>
+      <c r="M861">
+        <v>20.75</v>
+      </c>
+      <c r="N861">
         <v>30.94</v>
       </c>
-      <c r="O860">
-        <v>1</v>
-      </c>
-      <c r="P860" t="s">
-        <v>347</v>
+      <c r="O861">
+        <v>1</v>
+      </c>
+      <c r="P861" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="862" spans="1:16">
+      <c r="A862" s="1">
+        <v>1</v>
+      </c>
+      <c r="B862" t="s">
+        <v>155</v>
+      </c>
+      <c r="C862">
+        <v>13.59897621067881</v>
+      </c>
+      <c r="D862" t="s">
+        <v>267</v>
+      </c>
+      <c r="E862">
+        <v>13.4076727276643</v>
+      </c>
+      <c r="F862">
+        <v>-1</v>
+      </c>
+      <c r="G862">
+        <v>0.0480010237893212</v>
+      </c>
+      <c r="H862">
+        <v>0.0485723272723357</v>
+      </c>
+      <c r="I862">
+        <v>0.1913034830145115</v>
+      </c>
+      <c r="J862">
+        <v>0.8473410733655758</v>
+      </c>
+      <c r="K862">
+        <v>20.3</v>
+      </c>
+      <c r="L862">
+        <v>30.8</v>
+      </c>
+      <c r="M862">
+        <v>20.75</v>
+      </c>
+      <c r="N862">
+        <v>30.99</v>
+      </c>
+      <c r="O862">
+        <v>1</v>
+      </c>
+      <c r="P862" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="863" spans="1:16">
+      <c r="A863" s="1">
+        <v>0</v>
+      </c>
+      <c r="B863" t="s">
+        <v>154</v>
+      </c>
+      <c r="C863">
+        <v>12.51871891898833</v>
+      </c>
+      <c r="D863" t="s">
+        <v>266</v>
+      </c>
+      <c r="E863">
+        <v>13.30129170768218</v>
+      </c>
+      <c r="F863">
+        <v>1</v>
+      </c>
+      <c r="G863">
+        <v>0.04992128108101167</v>
+      </c>
+      <c r="H863">
+        <v>0.04857870829231783</v>
+      </c>
+      <c r="I863">
+        <v>0.7825727886938481</v>
+      </c>
+      <c r="J863">
+        <v>0.8500582309550758</v>
+      </c>
+      <c r="K863">
+        <v>22</v>
+      </c>
+      <c r="L863">
+        <v>31.22</v>
+      </c>
+      <c r="M863">
+        <v>20.75</v>
+      </c>
+      <c r="N863">
+        <v>30.94</v>
+      </c>
+      <c r="O863">
+        <v>1</v>
+      </c>
+      <c r="P863" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="864" spans="1:16">
+      <c r="A864" s="1">
+        <v>1</v>
+      </c>
+      <c r="B864" t="s">
+        <v>155</v>
+      </c>
+      <c r="C864">
+        <v>13.54381791161196</v>
+      </c>
+      <c r="D864" t="s">
+        <v>267</v>
+      </c>
+      <c r="E864">
+        <v>13.35129170768218</v>
+      </c>
+      <c r="F864">
+        <v>-1</v>
+      </c>
+      <c r="G864">
+        <v>0.04805618208838804</v>
+      </c>
+      <c r="H864">
+        <v>0.04862870829231782</v>
+      </c>
+      <c r="I864">
+        <v>0.1925262039297841</v>
+      </c>
+      <c r="J864">
+        <v>0.8500582309550758</v>
+      </c>
+      <c r="K864">
+        <v>20.3</v>
+      </c>
+      <c r="L864">
+        <v>30.8</v>
+      </c>
+      <c r="M864">
+        <v>20.75</v>
+      </c>
+      <c r="N864">
+        <v>30.99</v>
+      </c>
+      <c r="O864">
+        <v>1</v>
+      </c>
+      <c r="P864" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="865" spans="1:16">
+      <c r="A865" s="1">
+        <v>0</v>
+      </c>
+      <c r="B865" t="s">
+        <v>155</v>
+      </c>
+      <c r="C865">
+        <v>13.51182023914395</v>
+      </c>
+      <c r="D865" t="s">
+        <v>267</v>
+      </c>
+      <c r="E865">
+        <v>13.31858472720379</v>
+      </c>
+      <c r="F865">
+        <v>-1</v>
+      </c>
+      <c r="G865">
+        <v>0.04808817976085605</v>
+      </c>
+      <c r="H865">
+        <v>0.04866141527279621</v>
+      </c>
+      <c r="I865">
+        <v>0.1932355119401628</v>
+      </c>
+      <c r="J865">
+        <v>0.8516344709781304</v>
+      </c>
+      <c r="K865">
+        <v>20.3</v>
+      </c>
+      <c r="L865">
+        <v>30.8</v>
+      </c>
+      <c r="M865">
+        <v>20.75</v>
+      </c>
+      <c r="N865">
+        <v>30.99</v>
+      </c>
+      <c r="O865">
+        <v>1</v>
+      </c>
+      <c r="P865" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="866" spans="1:16">
+      <c r="A866" s="1">
+        <v>0</v>
+      </c>
+      <c r="B866" t="s">
+        <v>155</v>
+      </c>
+      <c r="C866">
+        <v>13.43501557200262</v>
+      </c>
+      <c r="D866" t="s">
+        <v>267</v>
+      </c>
+      <c r="E866">
+        <v>13.24007749354947</v>
+      </c>
+      <c r="F866">
+        <v>-1</v>
+      </c>
+      <c r="G866">
+        <v>0.04816498442799738</v>
+      </c>
+      <c r="H866">
+        <v>0.04873992250645053</v>
+      </c>
+      <c r="I866">
+        <v>0.1949380784531449</v>
+      </c>
+      <c r="J866">
+        <v>0.8554179521180978</v>
+      </c>
+      <c r="K866">
+        <v>20.3</v>
+      </c>
+      <c r="L866">
+        <v>30.8</v>
+      </c>
+      <c r="M866">
+        <v>20.75</v>
+      </c>
+      <c r="N866">
+        <v>30.99</v>
+      </c>
+      <c r="O866">
+        <v>1</v>
+      </c>
+      <c r="P866" t="s">
+        <v>351</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-00763-000063.xlsx
+++ b/s60_signal/position-00763-000063.xlsx
@@ -817,7 +817,7 @@
     <t>2021-12-03</t>
   </si>
   <si>
-    <t>2021-12-07</t>
+    <t>2021-12-08</t>
   </si>
   <si>
     <t>2017-02-08</t>
@@ -44391,7 +44391,7 @@
         <v>267</v>
       </c>
       <c r="E860">
-        <v>13.48349103432044</v>
+        <v>13.92659718804111</v>
       </c>
       <c r="F860">
         <v>-1</v>
@@ -44400,10 +44400,10 @@
         <v>0.04792684973509856</v>
       </c>
       <c r="H860">
-        <v>0.04849650896567955</v>
+        <v>0.04843340281195889</v>
       </c>
       <c r="I860">
-        <v>0.1896592305810039</v>
+        <v>-0.2534469231396663</v>
       </c>
       <c r="J860">
         <v>0.8436871790688943</v>
@@ -44415,10 +44415,10 @@
         <v>30.8</v>
       </c>
       <c r="M860">
-        <v>20.75</v>
+        <v>20.45</v>
       </c>
       <c r="N860">
-        <v>30.99</v>
+        <v>31.18</v>
       </c>
       <c r="O860">
         <v>1</v>
@@ -44491,7 +44491,7 @@
         <v>267</v>
       </c>
       <c r="E862">
-        <v>13.4076727276643</v>
+        <v>13.85187504967397</v>
       </c>
       <c r="F862">
         <v>-1</v>
@@ -44500,10 +44500,10 @@
         <v>0.0480010237893212</v>
       </c>
       <c r="H862">
-        <v>0.0485723272723357</v>
+        <v>0.04850812495032602</v>
       </c>
       <c r="I862">
-        <v>0.1913034830145115</v>
+        <v>-0.252898838995165</v>
       </c>
       <c r="J862">
         <v>0.8473410733655758</v>
@@ -44515,10 +44515,10 @@
         <v>30.8</v>
       </c>
       <c r="M862">
-        <v>20.75</v>
+        <v>20.45</v>
       </c>
       <c r="N862">
-        <v>30.99</v>
+        <v>31.18</v>
       </c>
       <c r="O862">
         <v>1</v>
@@ -44591,7 +44591,7 @@
         <v>267</v>
       </c>
       <c r="E864">
-        <v>13.35129170768218</v>
+        <v>13.7963091769687</v>
       </c>
       <c r="F864">
         <v>-1</v>
@@ -44600,10 +44600,10 @@
         <v>0.04805618208838804</v>
       </c>
       <c r="H864">
-        <v>0.04862870829231782</v>
+        <v>0.0485636908230313</v>
       </c>
       <c r="I864">
-        <v>0.1925262039297841</v>
+        <v>-0.2524912653567384</v>
       </c>
       <c r="J864">
         <v>0.8500582309550758</v>
@@ -44615,10 +44615,10 @@
         <v>30.8</v>
       </c>
       <c r="M864">
-        <v>20.75</v>
+        <v>20.45</v>
       </c>
       <c r="N864">
-        <v>30.99</v>
+        <v>31.18</v>
       </c>
       <c r="O864">
         <v>1</v>
@@ -44641,7 +44641,7 @@
         <v>267</v>
       </c>
       <c r="E865">
-        <v>13.31858472720379</v>
+        <v>13.76407506849723</v>
       </c>
       <c r="F865">
         <v>-1</v>
@@ -44650,10 +44650,10 @@
         <v>0.04808817976085605</v>
       </c>
       <c r="H865">
-        <v>0.04866141527279621</v>
+        <v>0.04859592493150276</v>
       </c>
       <c r="I865">
-        <v>0.1932355119401628</v>
+        <v>-0.25225482935328</v>
       </c>
       <c r="J865">
         <v>0.8516344709781304</v>
@@ -44665,10 +44665,10 @@
         <v>30.8</v>
       </c>
       <c r="M865">
-        <v>20.75</v>
+        <v>20.45</v>
       </c>
       <c r="N865">
-        <v>30.99</v>
+        <v>31.18</v>
       </c>
       <c r="O865">
         <v>1</v>
@@ -44691,7 +44691,7 @@
         <v>267</v>
       </c>
       <c r="E866">
-        <v>13.24007749354947</v>
+        <v>13.6867028791849</v>
       </c>
       <c r="F866">
         <v>-1</v>
@@ -44700,10 +44700,10 @@
         <v>0.04816498442799738</v>
       </c>
       <c r="H866">
-        <v>0.04873992250645053</v>
+        <v>0.0486732971208151</v>
       </c>
       <c r="I866">
-        <v>0.1949380784531449</v>
+        <v>-0.2516873071822836</v>
       </c>
       <c r="J866">
         <v>0.8554179521180978</v>
@@ -44715,10 +44715,10 @@
         <v>30.8</v>
       </c>
       <c r="M866">
-        <v>20.75</v>
+        <v>20.45</v>
       </c>
       <c r="N866">
-        <v>30.99</v>
+        <v>31.18</v>
       </c>
       <c r="O866">
         <v>1</v>

--- a/s60_signal/position-00763-000063.xlsx
+++ b/s60_signal/position-00763-000063.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2610" uniqueCount="352">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2625" uniqueCount="353">
   <si>
     <t>trade_time</t>
   </si>
@@ -484,6 +484,9 @@
     <t>2021-12-06</t>
   </si>
   <si>
+    <t>2021-12-08</t>
+  </si>
+  <si>
     <t>2017-03-17</t>
   </si>
   <si>
@@ -817,7 +820,7 @@
     <t>2021-12-03</t>
   </si>
   <si>
-    <t>2021-12-08</t>
+    <t>2021-12-09</t>
   </si>
   <si>
     <t>2017-02-08</t>
@@ -1427,7 +1430,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P866"/>
+  <dimension ref="A1:P871"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -1488,7 +1491,7 @@
         <v>8.357775317423281</v>
       </c>
       <c r="D2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E2">
         <v>9.239078272099615</v>
@@ -1524,7 +1527,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -1538,7 +1541,7 @@
         <v>9.433191964550923</v>
       </c>
       <c r="D3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E3">
         <v>9.285575452539577</v>
@@ -1574,7 +1577,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -1588,7 +1591,7 @@
         <v>9.420218808988363</v>
       </c>
       <c r="D4" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E4">
         <v>9.285575452539577</v>
@@ -1624,7 +1627,7 @@
         <v>1</v>
       </c>
       <c r="P4" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -1638,7 +1641,7 @@
         <v>9.27302954676334</v>
       </c>
       <c r="D5" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E5">
         <v>9.285575452539577</v>
@@ -1674,7 +1677,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -1688,7 +1691,7 @@
         <v>8.163141562328137</v>
       </c>
       <c r="D6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E6">
         <v>8.870417830135191</v>
@@ -1724,7 +1727,7 @@
         <v>1</v>
       </c>
       <c r="P6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -1738,7 +1741,7 @@
         <v>8.167981542028786</v>
       </c>
       <c r="D7" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E7">
         <v>8.870417830135191</v>
@@ -1774,7 +1777,7 @@
         <v>1</v>
       </c>
       <c r="P7" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -1788,7 +1791,7 @@
         <v>9.039124544167011</v>
       </c>
       <c r="D8" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E8">
         <v>9.113918803782131</v>
@@ -1824,7 +1827,7 @@
         <v>1</v>
       </c>
       <c r="P8" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -1838,7 +1841,7 @@
         <v>9.052076876787602</v>
       </c>
       <c r="D9" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E9">
         <v>9.113918803782131</v>
@@ -1874,7 +1877,7 @@
         <v>1</v>
       </c>
       <c r="P9" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -1888,7 +1891,7 @@
         <v>8.972076876787604</v>
       </c>
       <c r="D10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E10">
         <v>9.113918803782131</v>
@@ -1924,7 +1927,7 @@
         <v>1</v>
       </c>
       <c r="P10" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -1938,7 +1941,7 @@
         <v>1.247895028504875</v>
       </c>
       <c r="D11" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E11">
         <v>5.93332434483856</v>
@@ -1974,7 +1977,7 @@
         <v>1</v>
       </c>
       <c r="P11" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -1988,7 +1991,7 @@
         <v>2.464515501370315</v>
       </c>
       <c r="D12" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E12">
         <v>5.93332434483856</v>
@@ -2024,7 +2027,7 @@
         <v>1</v>
       </c>
       <c r="P12" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -2074,7 +2077,7 @@
         <v>1</v>
       </c>
       <c r="P13" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -2088,7 +2091,7 @@
         <v>1.224092499726471</v>
       </c>
       <c r="D14" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E14">
         <v>5.913320521841428</v>
@@ -2124,7 +2127,7 @@
         <v>1</v>
       </c>
       <c r="P14" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -2138,7 +2141,7 @@
         <v>2.442814384300704</v>
       </c>
       <c r="D15" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E15">
         <v>5.913320521841428</v>
@@ -2174,7 +2177,7 @@
         <v>1</v>
       </c>
       <c r="P15" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -2188,7 +2191,7 @@
         <v>8.399951396166678</v>
       </c>
       <c r="D16" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E16">
         <v>7.154665097353277</v>
@@ -2224,7 +2227,7 @@
         <v>1</v>
       </c>
       <c r="P16" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -2238,7 +2241,7 @@
         <v>1.231818368992485</v>
       </c>
       <c r="D17" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E17">
         <v>5.919813400087062</v>
@@ -2274,7 +2277,7 @@
         <v>1</v>
       </c>
       <c r="P17" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -2288,7 +2291,7 @@
         <v>2.449858173427781</v>
       </c>
       <c r="D18" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E18">
         <v>5.919813400087062</v>
@@ -2324,7 +2327,7 @@
         <v>1</v>
       </c>
       <c r="P18" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -2374,7 +2377,7 @@
         <v>1</v>
       </c>
       <c r="P19" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="20" spans="1:16">
@@ -2388,7 +2391,7 @@
         <v>1.145797529921555</v>
       </c>
       <c r="D20" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E20">
         <v>5.847520844331356</v>
@@ -2424,7 +2427,7 @@
         <v>1</v>
       </c>
       <c r="P20" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -2438,7 +2441,7 @@
         <v>2.37143170385038</v>
       </c>
       <c r="D21" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E21">
         <v>5.847520844331356</v>
@@ -2474,7 +2477,7 @@
         <v>1</v>
       </c>
       <c r="P21" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -2488,7 +2491,7 @@
         <v>8.323251570058975</v>
       </c>
       <c r="D22" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E22">
         <v>6.49770468378167</v>
@@ -2524,7 +2527,7 @@
         <v>1</v>
       </c>
       <c r="P22" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="23" spans="1:16">
@@ -2538,7 +2541,7 @@
         <v>8.298928068060523</v>
       </c>
       <c r="D23" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E23">
         <v>6.513844529583032</v>
@@ -2624,7 +2627,7 @@
         <v>1</v>
       </c>
       <c r="P24" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="25" spans="1:16">
@@ -2674,7 +2677,7 @@
         <v>1</v>
       </c>
       <c r="P25" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="26" spans="1:16">
@@ -2688,7 +2691,7 @@
         <v>4.521898732172186</v>
       </c>
       <c r="D26" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E26">
         <v>7.471272137184702</v>
@@ -2724,7 +2727,7 @@
         <v>1</v>
       </c>
       <c r="P26" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="27" spans="1:16">
@@ -2774,7 +2777,7 @@
         <v>1</v>
       </c>
       <c r="P27" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="28" spans="1:16">
@@ -2824,7 +2827,7 @@
         <v>1</v>
       </c>
       <c r="P28" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -2838,7 +2841,7 @@
         <v>10.06347633639325</v>
       </c>
       <c r="D29" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E29">
         <v>8.926863738767604</v>
@@ -2874,7 +2877,7 @@
         <v>1</v>
       </c>
       <c r="P29" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -3038,7 +3041,7 @@
         <v>10.57243502356749</v>
       </c>
       <c r="D33" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E33">
         <v>11.2289160904059</v>
@@ -3088,7 +3091,7 @@
         <v>10.58025171866791</v>
       </c>
       <c r="D34" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E34">
         <v>11.2289160904059</v>
@@ -3138,7 +3141,7 @@
         <v>6.89098969886382</v>
       </c>
       <c r="D35" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E35">
         <v>9.162922766970905</v>
@@ -3174,7 +3177,7 @@
         <v>1</v>
       </c>
       <c r="P35" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -3224,7 +3227,7 @@
         <v>1</v>
       </c>
       <c r="P36" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="37" spans="1:16">
@@ -3274,7 +3277,7 @@
         <v>1</v>
       </c>
       <c r="P37" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="38" spans="1:16">
@@ -3324,7 +3327,7 @@
         <v>1</v>
       </c>
       <c r="P38" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="39" spans="1:16">
@@ -3338,7 +3341,7 @@
         <v>10.57710841036202</v>
       </c>
       <c r="D39" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E39">
         <v>10.91875227586742</v>
@@ -3374,7 +3377,7 @@
         <v>1</v>
       </c>
       <c r="P39" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="40" spans="1:16">
@@ -3388,7 +3391,7 @@
         <v>10.58544939256899</v>
       </c>
       <c r="D40" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E40">
         <v>10.91875227586742</v>
@@ -3424,7 +3427,7 @@
         <v>1</v>
       </c>
       <c r="P40" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="41" spans="1:16">
@@ -3474,7 +3477,7 @@
         <v>1</v>
       </c>
       <c r="P41" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="42" spans="1:16">
@@ -3524,7 +3527,7 @@
         <v>1</v>
       </c>
       <c r="P42" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="43" spans="1:16">
@@ -3574,7 +3577,7 @@
         <v>1</v>
       </c>
       <c r="P43" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="44" spans="1:16">
@@ -3588,7 +3591,7 @@
         <v>10.50706987192051</v>
       </c>
       <c r="D44" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E44">
         <v>9.836117792760128</v>
@@ -3624,7 +3627,7 @@
         <v>1</v>
       </c>
       <c r="P44" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -3788,7 +3791,7 @@
         <v>11.00643298606593</v>
       </c>
       <c r="D48" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E48">
         <v>10.08970532444388</v>
@@ -3874,7 +3877,7 @@
         <v>1</v>
       </c>
       <c r="P49" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="50" spans="1:16">
@@ -3924,7 +3927,7 @@
         <v>1</v>
       </c>
       <c r="P50" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="51" spans="1:16">
@@ -3974,7 +3977,7 @@
         <v>1</v>
       </c>
       <c r="P51" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="52" spans="1:16">
@@ -4024,7 +4027,7 @@
         <v>1</v>
       </c>
       <c r="P52" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="53" spans="1:16">
@@ -4074,7 +4077,7 @@
         <v>1</v>
       </c>
       <c r="P53" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="54" spans="1:16">
@@ -4124,7 +4127,7 @@
         <v>1</v>
       </c>
       <c r="P54" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="55" spans="1:16">
@@ -4138,7 +4141,7 @@
         <v>10.96451987407661</v>
       </c>
       <c r="D55" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E55">
         <v>9.918825279734797</v>
@@ -4174,7 +4177,7 @@
         <v>1</v>
       </c>
       <c r="P55" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="56" spans="1:16">
@@ -4224,7 +4227,7 @@
         <v>1</v>
       </c>
       <c r="P56" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="57" spans="1:16">
@@ -4274,7 +4277,7 @@
         <v>1</v>
       </c>
       <c r="P57" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="58" spans="1:16">
@@ -4324,7 +4327,7 @@
         <v>1</v>
       </c>
       <c r="P58" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="59" spans="1:16">
@@ -4374,7 +4377,7 @@
         <v>1</v>
       </c>
       <c r="P59" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="60" spans="1:16">
@@ -4424,7 +4427,7 @@
         <v>1</v>
       </c>
       <c r="P60" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="61" spans="1:16">
@@ -4474,7 +4477,7 @@
         <v>1</v>
       </c>
       <c r="P61" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="62" spans="1:16">
@@ -4524,7 +4527,7 @@
         <v>1</v>
       </c>
       <c r="P62" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="63" spans="1:16">
@@ -4538,7 +4541,7 @@
         <v>10.70295290100141</v>
       </c>
       <c r="D63" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E63">
         <v>8.905400692050126</v>
@@ -4574,7 +4577,7 @@
         <v>1</v>
       </c>
       <c r="P63" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="64" spans="1:16">
@@ -4588,7 +4591,7 @@
         <v>11.20304517915771</v>
       </c>
       <c r="D64" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E64">
         <v>8.905400692050126</v>
@@ -4624,7 +4627,7 @@
         <v>1</v>
       </c>
       <c r="P64" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="65" spans="1:16">
@@ -4674,7 +4677,7 @@
         <v>1</v>
       </c>
       <c r="P65" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="66" spans="1:16">
@@ -4688,7 +4691,7 @@
         <v>10.69564352718713</v>
       </c>
       <c r="D66" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E66">
         <v>10.68408451836947</v>
@@ -4724,7 +4727,7 @@
         <v>1</v>
       </c>
       <c r="P66" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="67" spans="1:16">
@@ -4738,7 +4741,7 @@
         <v>11.03068966626528</v>
       </c>
       <c r="D67" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E67">
         <v>10.68408451836947</v>
@@ -4774,7 +4777,7 @@
         <v>1</v>
       </c>
       <c r="P67" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="68" spans="1:16">
@@ -4824,7 +4827,7 @@
         <v>1</v>
       </c>
       <c r="P68" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="69" spans="1:16">
@@ -4838,7 +4841,7 @@
         <v>10.52605158161457</v>
       </c>
       <c r="D69" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E69">
         <v>8.71498607743235</v>
@@ -4874,7 +4877,7 @@
         <v>1</v>
       </c>
       <c r="P69" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="70" spans="1:16">
@@ -4888,7 +4891,7 @@
         <v>11.02061569354003</v>
       </c>
       <c r="D70" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E70">
         <v>8.71498607743235</v>
@@ -4924,7 +4927,7 @@
         <v>1</v>
       </c>
       <c r="P70" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="71" spans="1:16">
@@ -4974,7 +4977,7 @@
         <v>1</v>
       </c>
       <c r="P71" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="72" spans="1:16">
@@ -4988,7 +4991,7 @@
         <v>10.52396325368498</v>
       </c>
       <c r="D72" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E72">
         <v>8.806051581614568</v>
@@ -5024,7 +5027,7 @@
         <v>1</v>
       </c>
       <c r="P72" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="73" spans="1:16">
@@ -5038,7 +5041,7 @@
         <v>10.8562453096477</v>
       </c>
       <c r="D73" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E73">
         <v>8.806051581614568</v>
@@ -5074,7 +5077,7 @@
         <v>1</v>
       </c>
       <c r="P73" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="74" spans="1:16">
@@ -5088,7 +5091,7 @@
         <v>10.34525014922946</v>
       </c>
       <c r="D74" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E74">
         <v>8.520373424517821</v>
@@ -5138,7 +5141,7 @@
         <v>10.83416421639288</v>
       </c>
       <c r="D75" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E75">
         <v>8.520373424517821</v>
@@ -5288,7 +5291,7 @@
         <v>10.34849797468624</v>
       </c>
       <c r="D78" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E78">
         <v>8.625250149229462</v>
@@ -5338,7 +5341,7 @@
         <v>10.67795500826794</v>
       </c>
       <c r="D79" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E79">
         <v>8.625250149229462</v>
@@ -5388,7 +5391,7 @@
         <v>10.18864383981015</v>
       </c>
       <c r="D80" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E80">
         <v>8.351804133128983</v>
@@ -5424,7 +5427,7 @@
         <v>1</v>
       </c>
       <c r="P80" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="81" spans="1:16">
@@ -5438,7 +5441,7 @@
         <v>10.67266395980422</v>
       </c>
       <c r="D81" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E81">
         <v>8.351804133128983</v>
@@ -5474,7 +5477,7 @@
         <v>1</v>
       </c>
       <c r="P81" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="82" spans="1:16">
@@ -5524,7 +5527,7 @@
         <v>1</v>
       </c>
       <c r="P82" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="83" spans="1:16">
@@ -5574,7 +5577,7 @@
         <v>1</v>
       </c>
       <c r="P83" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="84" spans="1:16">
@@ -5588,7 +5591,7 @@
         <v>10.19651372648243</v>
       </c>
       <c r="D84" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E84">
         <v>8.468643839810152</v>
@@ -5624,7 +5627,7 @@
         <v>1</v>
       </c>
       <c r="P84" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="85" spans="1:16">
@@ -5638,7 +5641,7 @@
         <v>10.52352378647946</v>
       </c>
       <c r="D85" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E85">
         <v>8.468643839810152</v>
@@ -5674,7 +5677,7 @@
         <v>1</v>
       </c>
       <c r="P85" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="86" spans="1:16">
@@ -5688,7 +5691,7 @@
         <v>-1.278554542763944</v>
       </c>
       <c r="D86" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E86">
         <v>0.01420169243589342</v>
@@ -5724,7 +5727,7 @@
         <v>1</v>
       </c>
       <c r="P86" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="87" spans="1:16">
@@ -5738,7 +5741,7 @@
         <v>-2.406586639852707</v>
       </c>
       <c r="D87" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E87">
         <v>0.01420169243589342</v>
@@ -5774,7 +5777,7 @@
         <v>1</v>
       </c>
       <c r="P87" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="88" spans="1:16">
@@ -5824,7 +5827,7 @@
         <v>1</v>
       </c>
       <c r="P88" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="89" spans="1:16">
@@ -5838,7 +5841,7 @@
         <v>-1.341212522415489</v>
       </c>
       <c r="D89" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E89">
         <v>0.1246199151405953</v>
@@ -5874,7 +5877,7 @@
         <v>1</v>
       </c>
       <c r="P89" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="90" spans="1:16">
@@ -5888,7 +5891,7 @@
         <v>-2.475362406493851</v>
       </c>
       <c r="D90" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E90">
         <v>0.1246199151405953</v>
@@ -5924,7 +5927,7 @@
         <v>1</v>
       </c>
       <c r="P90" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="91" spans="1:16">
@@ -5974,7 +5977,7 @@
         <v>1</v>
       </c>
       <c r="P91" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="92" spans="1:16">
@@ -5988,7 +5991,7 @@
         <v>-2.566016320350375</v>
       </c>
       <c r="D92" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E92">
         <v>0.02954385914472724</v>
@@ -6138,7 +6141,7 @@
         <v>-2.663355023194697</v>
       </c>
       <c r="D95" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E95">
         <v>0.03872013419191234</v>
@@ -6174,7 +6177,7 @@
         <v>1</v>
       </c>
       <c r="P95" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="96" spans="1:16">
@@ -6224,7 +6227,7 @@
         <v>1</v>
       </c>
       <c r="P96" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="97" spans="1:16">
@@ -6274,7 +6277,7 @@
         <v>1</v>
       </c>
       <c r="P97" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="98" spans="1:16">
@@ -6288,7 +6291,7 @@
         <v>-2.748103967913549</v>
       </c>
       <c r="D98" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E98">
         <v>-0.04760949385741853</v>
@@ -6324,7 +6327,7 @@
         <v>1</v>
       </c>
       <c r="P98" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="99" spans="1:16">
@@ -6338,7 +6341,7 @@
         <v>1.170412609918055</v>
       </c>
       <c r="D99" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E99">
         <v>1.469846093587645</v>
@@ -6374,7 +6377,7 @@
         <v>1</v>
       </c>
       <c r="P99" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="100" spans="1:16">
@@ -6388,7 +6391,7 @@
         <v>1.197090465141786</v>
       </c>
       <c r="D100" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E100">
         <v>1.469846093587645</v>
@@ -6424,7 +6427,7 @@
         <v>1</v>
       </c>
       <c r="P100" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="101" spans="1:16">
@@ -6438,7 +6441,7 @@
         <v>-2.807295369205091</v>
       </c>
       <c r="D101" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E101">
         <v>0.3363998775430197</v>
@@ -6474,7 +6477,7 @@
         <v>1</v>
       </c>
       <c r="P101" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="102" spans="1:16">
@@ -6524,7 +6527,7 @@
         <v>1</v>
       </c>
       <c r="P102" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="103" spans="1:16">
@@ -6624,7 +6627,7 @@
         <v>1</v>
       </c>
       <c r="P104" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="105" spans="1:16">
@@ -6638,7 +6641,7 @@
         <v>1.819034812951433</v>
       </c>
       <c r="D105" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E105">
         <v>1.780382458905816</v>
@@ -6674,7 +6677,7 @@
         <v>1</v>
       </c>
       <c r="P105" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="106" spans="1:16">
@@ -6688,7 +6691,7 @@
         <v>1.278232359359254</v>
       </c>
       <c r="D106" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E106">
         <v>1.780382458905816</v>
@@ -6724,7 +6727,7 @@
         <v>1</v>
       </c>
       <c r="P106" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="107" spans="1:16">
@@ -6738,7 +6741,7 @@
         <v>-1.27500579580901</v>
       </c>
       <c r="D107" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E107">
         <v>0.204597470791132</v>
@@ -6774,7 +6777,7 @@
         <v>1</v>
       </c>
       <c r="P107" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="108" spans="1:16">
@@ -6788,7 +6791,7 @@
         <v>-1.164182632644362</v>
       </c>
       <c r="D108" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E108">
         <v>0.204597470791132</v>
@@ -6824,7 +6827,7 @@
         <v>1</v>
       </c>
       <c r="P108" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="109" spans="1:16">
@@ -6874,7 +6877,7 @@
         <v>1</v>
       </c>
       <c r="P109" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="110" spans="1:16">
@@ -6924,7 +6927,7 @@
         <v>1</v>
       </c>
       <c r="P110" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="111" spans="1:16">
@@ -6938,7 +6941,7 @@
         <v>-1.330656541117063</v>
       </c>
       <c r="D111" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E111">
         <v>0.1498300706466971</v>
@@ -6974,7 +6977,7 @@
         <v>1</v>
       </c>
       <c r="P111" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="112" spans="1:16">
@@ -6988,7 +6991,7 @@
         <v>-1.089957636312631</v>
       </c>
       <c r="D112" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E112">
         <v>0.1498300706466971</v>
@@ -7024,7 +7027,7 @@
         <v>1</v>
       </c>
       <c r="P112" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="113" spans="1:16">
@@ -7038,7 +7041,7 @@
         <v>1.663161219313913</v>
       </c>
       <c r="D113" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E113">
         <v>1.394552474924428</v>
@@ -7074,7 +7077,7 @@
         <v>1</v>
       </c>
       <c r="P113" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="114" spans="1:16">
@@ -7088,7 +7091,7 @@
         <v>2.020453841772007</v>
       </c>
       <c r="D114" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E114">
         <v>1.394552474924428</v>
@@ -7124,7 +7127,7 @@
         <v>1</v>
       </c>
       <c r="P114" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="115" spans="1:16">
@@ -7174,7 +7177,7 @@
         <v>1</v>
       </c>
       <c r="P115" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="116" spans="1:16">
@@ -7224,7 +7227,7 @@
         <v>1</v>
       </c>
       <c r="P116" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="117" spans="1:16">
@@ -7274,7 +7277,7 @@
         <v>1</v>
       </c>
       <c r="P117" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="118" spans="1:16">
@@ -7324,7 +7327,7 @@
         <v>1</v>
       </c>
       <c r="P118" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="119" spans="1:16">
@@ -7374,7 +7377,7 @@
         <v>1</v>
       </c>
       <c r="P119" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="120" spans="1:16">
@@ -7424,7 +7427,7 @@
         <v>1</v>
       </c>
       <c r="P120" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="121" spans="1:16">
@@ -7474,7 +7477,7 @@
         <v>1</v>
       </c>
       <c r="P121" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="122" spans="1:16">
@@ -7524,7 +7527,7 @@
         <v>1</v>
       </c>
       <c r="P122" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="123" spans="1:16">
@@ -7574,7 +7577,7 @@
         <v>1</v>
       </c>
       <c r="P123" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="124" spans="1:16">
@@ -7624,7 +7627,7 @@
         <v>1</v>
       </c>
       <c r="P124" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="125" spans="1:16">
@@ -7738,7 +7741,7 @@
         <v>1.583716178161136</v>
       </c>
       <c r="D127" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E127">
         <v>1.731188504841963</v>
@@ -7788,7 +7791,7 @@
         <v>1.943294205912665</v>
       </c>
       <c r="D128" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E128">
         <v>1.731188504841963</v>
@@ -7838,7 +7841,7 @@
         <v>1.440029121201585</v>
       </c>
       <c r="D129" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E129">
         <v>1.731188504841963</v>
@@ -7924,7 +7927,7 @@
         <v>1</v>
       </c>
       <c r="P130" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="131" spans="1:16">
@@ -7974,7 +7977,7 @@
         <v>1</v>
       </c>
       <c r="P131" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="132" spans="1:16">
@@ -8024,7 +8027,7 @@
         <v>1</v>
       </c>
       <c r="P132" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="133" spans="1:16">
@@ -8074,7 +8077,7 @@
         <v>1</v>
       </c>
       <c r="P133" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="134" spans="1:16">
@@ -8124,7 +8127,7 @@
         <v>1</v>
       </c>
       <c r="P134" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="135" spans="1:16">
@@ -8138,7 +8141,7 @@
         <v>-0.8820242128746258</v>
       </c>
       <c r="D135" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E135">
         <v>0.3526024044326252</v>
@@ -8174,7 +8177,7 @@
         <v>1</v>
       </c>
       <c r="P135" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="136" spans="1:16">
@@ -8188,7 +8191,7 @@
         <v>-1.173427909927172</v>
       </c>
       <c r="D136" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E136">
         <v>0.3526024044326252</v>
@@ -8224,7 +8227,7 @@
         <v>1</v>
       </c>
       <c r="P136" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="137" spans="1:16">
@@ -8274,7 +8277,7 @@
         <v>1</v>
       </c>
       <c r="P137" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="138" spans="1:16">
@@ -8324,7 +8327,7 @@
         <v>1</v>
       </c>
       <c r="P138" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="139" spans="1:16">
@@ -8374,7 +8377,7 @@
         <v>1</v>
       </c>
       <c r="P139" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="140" spans="1:16">
@@ -8688,7 +8691,7 @@
         <v>1.916709703800588</v>
       </c>
       <c r="D146" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E146">
         <v>1.625228926806798</v>
@@ -8738,7 +8741,7 @@
         <v>1.775844332123576</v>
       </c>
       <c r="D147" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E147">
         <v>1.625228926806798</v>
@@ -8788,7 +8791,7 @@
         <v>1.706459737440355</v>
       </c>
       <c r="D148" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E148">
         <v>1.625228926806798</v>
@@ -8838,7 +8841,7 @@
         <v>1.898407474064776</v>
       </c>
       <c r="D149" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E149">
         <v>1.579058157468399</v>
@@ -8874,7 +8877,7 @@
         <v>1</v>
       </c>
       <c r="P149" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="150" spans="1:16">
@@ -8888,7 +8891,7 @@
         <v>1.757671173119327</v>
       </c>
       <c r="D150" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E150">
         <v>1.579058157468399</v>
@@ -8924,7 +8927,7 @@
         <v>1</v>
       </c>
       <c r="P150" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="151" spans="1:16">
@@ -8938,7 +8941,7 @@
         <v>1.688493091606606</v>
       </c>
       <c r="D151" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E151">
         <v>1.579058157468399</v>
@@ -8974,7 +8977,7 @@
         <v>1</v>
       </c>
       <c r="P151" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="152" spans="1:16">
@@ -9024,7 +9027,7 @@
         <v>1</v>
       </c>
       <c r="P152" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="153" spans="1:16">
@@ -9074,7 +9077,7 @@
         <v>1</v>
       </c>
       <c r="P153" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="154" spans="1:16">
@@ -9124,7 +9127,7 @@
         <v>1</v>
       </c>
       <c r="P154" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="155" spans="1:16">
@@ -9174,7 +9177,7 @@
         <v>1</v>
       </c>
       <c r="P155" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="156" spans="1:16">
@@ -9224,7 +9227,7 @@
         <v>1</v>
       </c>
       <c r="P156" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="157" spans="1:16">
@@ -9274,7 +9277,7 @@
         <v>1</v>
       </c>
       <c r="P157" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="158" spans="1:16">
@@ -9424,7 +9427,7 @@
         <v>1</v>
       </c>
       <c r="P160" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="161" spans="1:16">
@@ -9474,7 +9477,7 @@
         <v>1</v>
       </c>
       <c r="P161" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="162" spans="1:16">
@@ -9524,7 +9527,7 @@
         <v>1</v>
       </c>
       <c r="P162" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="163" spans="1:16">
@@ -9574,7 +9577,7 @@
         <v>1</v>
       </c>
       <c r="P163" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="164" spans="1:16">
@@ -9588,7 +9591,7 @@
         <v>2.0418888555804</v>
       </c>
       <c r="D164" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E164">
         <v>2.091052252009925</v>
@@ -9638,7 +9641,7 @@
         <v>2.437529947263654</v>
       </c>
       <c r="D165" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E165">
         <v>2.091052252009925</v>
@@ -9688,7 +9691,7 @@
         <v>2.035427646090795</v>
       </c>
       <c r="D166" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E166">
         <v>1.677256780401082</v>
@@ -9724,7 +9727,7 @@
         <v>1</v>
       </c>
       <c r="P166" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="167" spans="1:16">
@@ -9738,7 +9741,7 @@
         <v>2.4319519246827</v>
       </c>
       <c r="D167" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E167">
         <v>1.677256780401082</v>
@@ -9774,7 +9777,7 @@
         <v>1</v>
       </c>
       <c r="P167" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="168" spans="1:16">
@@ -9824,7 +9827,7 @@
         <v>1</v>
       </c>
       <c r="P168" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="169" spans="1:16">
@@ -9874,7 +9877,7 @@
         <v>1</v>
       </c>
       <c r="P169" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="170" spans="1:16">
@@ -9924,7 +9927,7 @@
         <v>1</v>
       </c>
       <c r="P170" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="171" spans="1:16">
@@ -9974,7 +9977,7 @@
         <v>1</v>
       </c>
       <c r="P171" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="172" spans="1:16">
@@ -10024,7 +10027,7 @@
         <v>1</v>
       </c>
       <c r="P172" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="173" spans="1:16">
@@ -10038,7 +10041,7 @@
         <v>2.053037839433713</v>
       </c>
       <c r="D173" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E173">
         <v>2.029053723158555</v>
@@ -10074,7 +10077,7 @@
         <v>1</v>
       </c>
       <c r="P173" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="174" spans="1:16">
@@ -10188,7 +10191,7 @@
         <v>2.072439051471395</v>
       </c>
       <c r="D176" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E176">
         <v>2.198537473651809</v>
@@ -10224,7 +10227,7 @@
         <v>1</v>
       </c>
       <c r="P176" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="177" spans="1:16">
@@ -10238,7 +10241,7 @@
         <v>2.176038435736924</v>
       </c>
       <c r="D177" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E177">
         <v>2.198537473651809</v>
@@ -10274,7 +10277,7 @@
         <v>1</v>
       </c>
       <c r="P177" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="178" spans="1:16">
@@ -10324,7 +10327,7 @@
         <v>1</v>
       </c>
       <c r="P178" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="179" spans="1:16">
@@ -10388,7 +10391,7 @@
         <v>2.199572666349018</v>
       </c>
       <c r="D180" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E180">
         <v>2.369622868222606</v>
@@ -10588,7 +10591,7 @@
         <v>2.441204477380014</v>
       </c>
       <c r="D184" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E184">
         <v>3.019740173907834</v>
@@ -10688,7 +10691,7 @@
         <v>2.450942264059425</v>
       </c>
       <c r="D186" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E186">
         <v>3.396065694761221</v>
@@ -10738,7 +10741,7 @@
         <v>2.93271297523739</v>
       </c>
       <c r="D187" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E187">
         <v>3.396065694761221</v>
@@ -10838,7 +10841,7 @@
         <v>2.613291041571109</v>
       </c>
       <c r="D189" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E189">
         <v>1.747095958240026</v>
@@ -10888,7 +10891,7 @@
         <v>2.94332933323569</v>
       </c>
       <c r="D190" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E190">
         <v>3.513960124909904</v>
@@ -11038,7 +11041,7 @@
         <v>2.630002520413537</v>
       </c>
       <c r="D193" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E193">
         <v>1.763414225815572</v>
@@ -11088,7 +11091,7 @@
         <v>2.960405936825934</v>
       </c>
       <c r="D194" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E194">
         <v>2.688557154970242</v>
@@ -11288,7 +11291,7 @@
         <v>2.642059072099817</v>
       </c>
       <c r="D198" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E198">
         <v>1.775187093932763</v>
@@ -11338,7 +11341,7 @@
         <v>2.972725908969226</v>
       </c>
       <c r="D199" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E199">
         <v>2.375803028433923</v>
@@ -11488,7 +11491,7 @@
         <v>2.666955617984192</v>
       </c>
       <c r="D202" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E202">
         <v>1.799497838737505</v>
@@ -11538,7 +11541,7 @@
         <v>2.998166412998973</v>
       </c>
       <c r="D203" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E203">
         <v>1.736641978102437</v>
@@ -11688,7 +11691,7 @@
         <v>2.973643871143521</v>
       </c>
       <c r="D206" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E206">
         <v>1.818524938691256</v>
@@ -11738,7 +11741,7 @@
         <v>3.018077732744034</v>
       </c>
       <c r="D207" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E207">
         <v>1.759533446033025</v>
@@ -11888,7 +11891,7 @@
         <v>2.990082102112254</v>
       </c>
       <c r="D210" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E210">
         <v>1.83485077149952</v>
@@ -11938,7 +11941,7 @@
         <v>3.03516225313547</v>
       </c>
       <c r="D211" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E211">
         <v>1.779175024575153</v>
@@ -12024,7 +12027,7 @@
         <v>1</v>
       </c>
       <c r="P212" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="213" spans="1:16">
@@ -12074,7 +12077,7 @@
         <v>1</v>
       </c>
       <c r="P213" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="214" spans="1:16">
@@ -12088,7 +12091,7 @@
         <v>3.005496469975766</v>
       </c>
       <c r="D214" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E214">
         <v>1.850159741975929</v>
@@ -12124,7 +12127,7 @@
         <v>1</v>
       </c>
       <c r="P214" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="215" spans="1:16">
@@ -12138,7 +12141,7 @@
         <v>3.051182655974811</v>
       </c>
       <c r="D215" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E215">
         <v>1.797593217971041</v>
@@ -12174,7 +12177,7 @@
         <v>1</v>
       </c>
       <c r="P215" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="216" spans="1:16">
@@ -12288,7 +12291,7 @@
         <v>3.018931533510157</v>
       </c>
       <c r="D218" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E218">
         <v>1.863502941828035</v>
@@ -12338,7 +12341,7 @@
         <v>3.06514593568235</v>
       </c>
       <c r="D219" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E219">
         <v>1.813646396450594</v>
@@ -12488,7 +12491,7 @@
         <v>3.033933076549712</v>
       </c>
       <c r="D222" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E222">
         <v>1.878401910214327</v>
@@ -12538,7 +12541,7 @@
         <v>3.080737282978161</v>
       </c>
       <c r="D223" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E223">
         <v>1.831571317108114</v>
@@ -12588,7 +12591,7 @@
         <v>1.639859271051932</v>
       </c>
       <c r="D224" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E224">
         <v>1.9209216037227</v>
@@ -12738,7 +12741,7 @@
         <v>3.05833801181463</v>
       </c>
       <c r="D227" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E227">
         <v>1.902639974127007</v>
@@ -12788,7 +12791,7 @@
         <v>3.106101728518452</v>
       </c>
       <c r="D228" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E228">
         <v>1.860732085911838</v>
@@ -12874,7 +12877,7 @@
         <v>1</v>
       </c>
       <c r="P229" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="230" spans="1:16">
@@ -12924,7 +12927,7 @@
         <v>1</v>
       </c>
       <c r="P230" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="231" spans="1:16">
@@ -12938,7 +12941,7 @@
         <v>3.085055612872655</v>
       </c>
       <c r="D231" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E231">
         <v>1.929174890733353</v>
@@ -12974,7 +12977,7 @@
         <v>1</v>
       </c>
       <c r="P231" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="232" spans="1:16">
@@ -12988,7 +12991,7 @@
         <v>3.13386976517363</v>
       </c>
       <c r="D232" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E232">
         <v>1.892656193842708</v>
@@ -13024,7 +13027,7 @@
         <v>1</v>
       </c>
       <c r="P232" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="233" spans="1:16">
@@ -13088,7 +13091,7 @@
         <v>3.103034611570727</v>
       </c>
       <c r="D234" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E234">
         <v>1.947030956106994</v>
@@ -13138,7 +13141,7 @@
         <v>3.152555630487182</v>
       </c>
       <c r="D235" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E235">
         <v>1.914138792287073</v>
@@ -13188,7 +13191,7 @@
         <v>1.641725609550694</v>
       </c>
       <c r="D236" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E236">
         <v>1.89319910743864</v>
@@ -13274,7 +13277,7 @@
         <v>1</v>
       </c>
       <c r="P237" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="238" spans="1:16">
@@ -13288,7 +13291,7 @@
         <v>3.11979974827751</v>
       </c>
       <c r="D238" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E238">
         <v>1.963681459400396</v>
@@ -13324,7 +13327,7 @@
         <v>1</v>
       </c>
       <c r="P238" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="239" spans="1:16">
@@ -13338,7 +13341,7 @@
         <v>3.169979909320897</v>
       </c>
       <c r="D239" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E239">
         <v>1.934170981275177</v>
@@ -13374,7 +13377,7 @@
         <v>1</v>
       </c>
       <c r="P239" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="240" spans="1:16">
@@ -13388,7 +13391,7 @@
         <v>1.664480342106565</v>
       </c>
       <c r="D240" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E240">
         <v>2.221652319966786</v>
@@ -13424,7 +13427,7 @@
         <v>1</v>
       </c>
       <c r="P240" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="241" spans="1:16">
@@ -13488,7 +13491,7 @@
         <v>3.136490860930856</v>
       </c>
       <c r="D242" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E242">
         <v>1.980258444787738</v>
@@ -13538,7 +13541,7 @@
         <v>3.187327253753777</v>
       </c>
       <c r="D243" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E243">
         <v>1.954114721009688</v>
@@ -13738,7 +13741,7 @@
         <v>3.154470288152615</v>
       </c>
       <c r="D247" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E247">
         <v>1.998114935754989</v>
@@ -13788,7 +13791,7 @@
         <v>3.206013564438956</v>
       </c>
       <c r="D248" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E248">
         <v>1.975597831484915</v>
@@ -13974,7 +13977,7 @@
         <v>1</v>
       </c>
       <c r="P251" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="252" spans="1:16">
@@ -14024,7 +14027,7 @@
         <v>1</v>
       </c>
       <c r="P252" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="253" spans="1:16">
@@ -14038,7 +14041,7 @@
         <v>3.175183381627829</v>
       </c>
       <c r="D253" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E253">
         <v>2.406837822852639</v>
@@ -14074,7 +14077,7 @@
         <v>1</v>
       </c>
       <c r="P253" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="254" spans="1:16">
@@ -14088,7 +14091,7 @@
         <v>3.227541018854222</v>
       </c>
       <c r="D254" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E254">
         <v>2.000347322662993</v>
@@ -14124,7 +14127,7 @@
         <v>1</v>
       </c>
       <c r="P254" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="255" spans="1:16">
@@ -14174,7 +14177,7 @@
         <v>1</v>
       </c>
       <c r="P255" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="256" spans="1:16">
@@ -14224,7 +14227,7 @@
         <v>1</v>
       </c>
       <c r="P256" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="257" spans="1:16">
@@ -14338,7 +14341,7 @@
         <v>3.194491499183421</v>
       </c>
       <c r="D259" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E259">
         <v>2.42485873257119</v>
@@ -14388,7 +14391,7 @@
         <v>3.247608258980375</v>
       </c>
       <c r="D260" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E260">
         <v>2.023418047742236</v>
@@ -14638,7 +14641,7 @@
         <v>3.213727962726566</v>
       </c>
       <c r="D265" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E265">
         <v>2.442812765211459</v>
@@ -14688,7 +14691,7 @@
         <v>3.26760102792778</v>
       </c>
       <c r="D266" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E266">
         <v>2.046403155463022</v>
@@ -14888,7 +14891,7 @@
         <v>3.233647867837396</v>
       </c>
       <c r="D270" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E270">
         <v>2.461404676648234</v>
@@ -14938,7 +14941,7 @@
         <v>3.288304108795105</v>
       </c>
       <c r="D271" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E271">
         <v>2.070204888236475</v>
@@ -15138,7 +15141,7 @@
         <v>3.249417008017017</v>
       </c>
       <c r="D275" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E275">
         <v>2.476122540815881</v>
@@ -15188,7 +15191,7 @@
         <v>3.304693232263839</v>
       </c>
       <c r="D276" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E276">
         <v>2.089046989066485</v>
@@ -15338,7 +15341,7 @@
         <v>1.914875661806953</v>
       </c>
       <c r="D279" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E279">
         <v>2.109898465499843</v>
@@ -15424,7 +15427,7 @@
         <v>1</v>
       </c>
       <c r="P280" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="281" spans="1:16">
@@ -15438,7 +15441,7 @@
         <v>3.261163134684622</v>
       </c>
       <c r="D281" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E281">
         <v>2.487085592372312</v>
@@ -15474,7 +15477,7 @@
         <v>1</v>
       </c>
       <c r="P281" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="282" spans="1:16">
@@ -15488,7 +15491,7 @@
         <v>3.316901172458547</v>
       </c>
       <c r="D282" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E282">
         <v>2.103082104520595</v>
@@ -15524,7 +15527,7 @@
         <v>1</v>
       </c>
       <c r="P282" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="283" spans="1:16">
@@ -15574,7 +15577,7 @@
         <v>1</v>
       </c>
       <c r="P283" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="284" spans="1:16">
@@ -15624,7 +15627,7 @@
         <v>1</v>
       </c>
       <c r="P284" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="285" spans="1:16">
@@ -15638,7 +15641,7 @@
         <v>1.930296217842372</v>
       </c>
       <c r="D285" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E285">
         <v>2.383746445952788</v>
@@ -15674,7 +15677,7 @@
         <v>1</v>
       </c>
       <c r="P285" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="286" spans="1:16">
@@ -15724,7 +15727,7 @@
         <v>1</v>
       </c>
       <c r="P286" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="287" spans="1:16">
@@ -15738,7 +15741,7 @@
         <v>3.267778188252251</v>
       </c>
       <c r="D287" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E287">
         <v>2.493259642368766</v>
@@ -15774,7 +15777,7 @@
         <v>1</v>
       </c>
       <c r="P287" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="288" spans="1:16">
@@ -15788,7 +15791,7 @@
         <v>3.323776305055329</v>
       </c>
       <c r="D288" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E288">
         <v>2.110986245450121</v>
@@ -15824,7 +15827,7 @@
         <v>1</v>
       </c>
       <c r="P288" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="289" spans="1:16">
@@ -15874,7 +15877,7 @@
         <v>1</v>
       </c>
       <c r="P289" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="290" spans="1:16">
@@ -15924,7 +15927,7 @@
         <v>1</v>
       </c>
       <c r="P290" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="291" spans="1:16">
@@ -15974,7 +15977,7 @@
         <v>1</v>
       </c>
       <c r="P291" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="292" spans="1:16">
@@ -15988,7 +15991,7 @@
         <v>3.278598009747792</v>
       </c>
       <c r="D292" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E292">
         <v>2.503358142431271</v>
@@ -16038,7 +16041,7 @@
         <v>3.335021521242147</v>
       </c>
       <c r="D293" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E293">
         <v>2.123914544980693</v>
@@ -16188,7 +16191,7 @@
         <v>1.953185079463765</v>
       </c>
       <c r="D296" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E296">
         <v>1.673185079463764</v>
@@ -16238,7 +16241,7 @@
         <v>1.838424946780282</v>
       </c>
       <c r="D297" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E297">
         <v>1.673185079463764</v>
@@ -16288,7 +16291,7 @@
         <v>3.286491586851236</v>
       </c>
       <c r="D298" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E298">
         <v>2.510725481061151</v>
@@ -16338,7 +16341,7 @@
         <v>3.343225444112052</v>
       </c>
       <c r="D299" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E299">
         <v>2.133346357622241</v>
@@ -16488,7 +16491,7 @@
         <v>1.963547929404697</v>
       </c>
       <c r="D302" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E302">
         <v>2.040362444937774</v>
@@ -16538,7 +16541,7 @@
         <v>1.849314035194777</v>
       </c>
       <c r="D303" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E303">
         <v>2.040362444937774</v>
@@ -16588,7 +16591,7 @@
         <v>3.287218803551511</v>
       </c>
       <c r="D304" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E304">
         <v>2.511404216648074</v>
@@ -16638,7 +16641,7 @@
         <v>3.34398125223815</v>
       </c>
       <c r="D305" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E305">
         <v>2.134215288346162</v>
@@ -16788,7 +16791,7 @@
         <v>1.964502634406085</v>
       </c>
       <c r="D308" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E308">
         <v>2.034789980466009</v>
@@ -16838,7 +16841,7 @@
         <v>1.850317221309513</v>
       </c>
       <c r="D309" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E309">
         <v>2.034789980466009</v>
@@ -16888,7 +16891,7 @@
         <v>3.309574328279867</v>
       </c>
       <c r="D310" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E310">
         <v>2.532269373061208</v>
@@ -16938,7 +16941,7 @@
         <v>3.367215712126766</v>
       </c>
       <c r="D311" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E311">
         <v>2.160927274303631</v>
@@ -17188,7 +17191,7 @@
         <v>3.386581638751728</v>
       </c>
       <c r="D316" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E316">
         <v>2.183191719551736</v>
@@ -17288,7 +17291,7 @@
         <v>2.018313648949551</v>
       </c>
       <c r="D318" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E318">
         <v>2.020805677582523</v>
@@ -17338,7 +17341,7 @@
         <v>1.906860826435267</v>
       </c>
       <c r="D319" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E319">
         <v>2.020805677582523</v>
@@ -17388,7 +17391,7 @@
         <v>1.784750528729781</v>
       </c>
       <c r="D320" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E320">
         <v>2.020805677582523</v>
@@ -17438,7 +17441,7 @@
         <v>3.376305833526885</v>
       </c>
       <c r="D321" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E321">
         <v>2.171377923742256</v>
@@ -17474,7 +17477,7 @@
         <v>1</v>
       </c>
       <c r="P321" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="322" spans="1:16">
@@ -17524,7 +17527,7 @@
         <v>1</v>
       </c>
       <c r="P322" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="323" spans="1:16">
@@ -17574,7 +17577,7 @@
         <v>1</v>
       </c>
       <c r="P323" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="324" spans="1:16">
@@ -17624,7 +17627,7 @@
         <v>1</v>
       </c>
       <c r="P324" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="325" spans="1:16">
@@ -17638,7 +17641,7 @@
         <v>3.346413966869674</v>
       </c>
       <c r="D325" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E325">
         <v>2.137012109937338</v>
@@ -17674,7 +17677,7 @@
         <v>1</v>
       </c>
       <c r="P325" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="326" spans="1:16">
@@ -17724,7 +17727,7 @@
         <v>1</v>
       </c>
       <c r="P326" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="327" spans="1:16">
@@ -17738,7 +17741,7 @@
         <v>1.853546169841817</v>
       </c>
       <c r="D327" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E327">
         <v>1.909412654865697</v>
@@ -17774,7 +17777,7 @@
         <v>1</v>
       </c>
       <c r="P327" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="328" spans="1:16">
@@ -17788,7 +17791,7 @@
         <v>1.729057523143315</v>
       </c>
       <c r="D328" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E328">
         <v>1.909412654865697</v>
@@ -17824,7 +17827,7 @@
         <v>1</v>
       </c>
       <c r="P328" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="329" spans="1:16">
@@ -17838,7 +17841,7 @@
         <v>1.90213361560998</v>
       </c>
       <c r="D329" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E329">
         <v>1.909412654865697</v>
@@ -17874,7 +17877,7 @@
         <v>1</v>
       </c>
       <c r="P329" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="330" spans="1:16">
@@ -17888,7 +17891,7 @@
         <v>3.335708401471214</v>
       </c>
       <c r="D330" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E330">
         <v>2.124704231296676</v>
@@ -17924,7 +17927,7 @@
         <v>1</v>
       </c>
       <c r="P330" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="331" spans="1:16">
@@ -17974,7 +17977,7 @@
         <v>1</v>
       </c>
       <c r="P331" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="332" spans="1:16">
@@ -17988,7 +17991,7 @@
         <v>1.839336644715903</v>
       </c>
       <c r="D332" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E332">
         <v>2.572020438006287</v>
@@ -18024,7 +18027,7 @@
         <v>1</v>
       </c>
       <c r="P332" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="333" spans="1:16">
@@ -18038,7 +18041,7 @@
         <v>1.714214115855647</v>
       </c>
       <c r="D333" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E333">
         <v>2.572020438006287</v>
@@ -18074,7 +18077,7 @@
         <v>1</v>
       </c>
       <c r="P333" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="334" spans="1:16">
@@ -18088,7 +18091,7 @@
         <v>1.88846993345668</v>
       </c>
       <c r="D334" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E334">
         <v>2.572020438006287</v>
@@ -18124,7 +18127,7 @@
         <v>1</v>
       </c>
       <c r="P334" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="335" spans="1:16">
@@ -18138,7 +18141,7 @@
         <v>3.319807569063805</v>
       </c>
       <c r="D335" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E335">
         <v>2.106423504565129</v>
@@ -18238,7 +18241,7 @@
         <v>1.818231428017253</v>
       </c>
       <c r="D337" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E337">
         <v>2.552327466291189</v>
@@ -18288,7 +18291,7 @@
         <v>1.692167402501294</v>
       </c>
       <c r="D338" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E338">
         <v>2.552327466291189</v>
@@ -18338,7 +18341,7 @@
         <v>1.86817544998933</v>
       </c>
       <c r="D339" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E339">
         <v>2.552327466291189</v>
@@ -18388,7 +18391,7 @@
         <v>3.297653300651016</v>
       </c>
       <c r="D340" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E340">
         <v>2.080953383478715</v>
@@ -18424,7 +18427,7 @@
         <v>1</v>
       </c>
       <c r="P340" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="341" spans="1:16">
@@ -18474,7 +18477,7 @@
         <v>1</v>
       </c>
       <c r="P341" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="342" spans="1:16">
@@ -18488,7 +18491,7 @@
         <v>1.788826009252247</v>
       </c>
       <c r="D342" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E342">
         <v>2.524889696365481</v>
@@ -18524,7 +18527,7 @@
         <v>1</v>
       </c>
       <c r="P342" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="343" spans="1:16">
@@ -18538,7 +18541,7 @@
         <v>1.661450217843427</v>
       </c>
       <c r="D343" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E343">
         <v>2.524889696365481</v>
@@ -18574,7 +18577,7 @@
         <v>1</v>
       </c>
       <c r="P343" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="344" spans="1:16">
@@ -18588,7 +18591,7 @@
         <v>1.839899607409848</v>
       </c>
       <c r="D344" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E344">
         <v>2.524889696365481</v>
@@ -18624,7 +18627,7 @@
         <v>1</v>
       </c>
       <c r="P344" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="345" spans="1:16">
@@ -18638,7 +18641,7 @@
         <v>3.263703117123406</v>
       </c>
       <c r="D345" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E345">
         <v>2.041921840245493</v>
@@ -18738,7 +18741,7 @@
         <v>1.743763841313463</v>
       </c>
       <c r="D347" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E347">
         <v>2.48284284077948</v>
@@ -18788,7 +18791,7 @@
         <v>1.614377841669459</v>
       </c>
       <c r="D348" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E348">
         <v>2.48284284077948</v>
@@ -18838,7 +18841,7 @@
         <v>1.796568452118031</v>
       </c>
       <c r="D349" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E349">
         <v>2.48284284077948</v>
@@ -18888,7 +18891,7 @@
         <v>3.242126022559422</v>
       </c>
       <c r="D350" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E350">
         <v>2.017115279225386</v>
@@ -18924,7 +18927,7 @@
         <v>1</v>
       </c>
       <c r="P350" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="351" spans="1:16">
@@ -18974,7 +18977,7 @@
         <v>1</v>
       </c>
       <c r="P351" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="352" spans="1:16">
@@ -18988,7 +18991,7 @@
         <v>1.715124506916858</v>
       </c>
       <c r="D352" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E352">
         <v>2.456119893071122</v>
@@ -19024,7 +19027,7 @@
         <v>1</v>
       </c>
       <c r="P352" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="353" spans="1:16">
@@ -19038,7 +19041,7 @@
         <v>1.584460916147354</v>
       </c>
       <c r="D353" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E353">
         <v>2.456119893071122</v>
@@ -19074,7 +19077,7 @@
         <v>1</v>
       </c>
       <c r="P353" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="354" spans="1:16">
@@ -19088,7 +19091,7 @@
         <v>1.769029265635051</v>
       </c>
       <c r="D354" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E354">
         <v>2.456119893071122</v>
@@ -19124,7 +19127,7 @@
         <v>1</v>
       </c>
       <c r="P354" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="355" spans="1:16">
@@ -19138,7 +19141,7 @@
         <v>3.218796578894542</v>
       </c>
       <c r="D355" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E355">
         <v>1.990294093169876</v>
@@ -19238,7 +19241,7 @@
         <v>1.684159274947191</v>
       </c>
       <c r="D357" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E357">
         <v>2.427226684058535</v>
@@ -19288,7 +19291,7 @@
         <v>1.552114335539635</v>
       </c>
       <c r="D358" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E358">
         <v>2.427226684058535</v>
@@ -19338,7 +19341,7 @@
         <v>1.739253528325928</v>
       </c>
       <c r="D359" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E359">
         <v>2.427226684058535</v>
@@ -19388,7 +19391,7 @@
         <v>3.223084813618858</v>
       </c>
       <c r="D360" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E360">
         <v>1.995224152499308</v>
@@ -19424,7 +19427,7 @@
         <v>1</v>
       </c>
       <c r="P360" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="361" spans="1:16">
@@ -19438,7 +19441,7 @@
         <v>1.689851060181606</v>
       </c>
       <c r="D361" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E361">
         <v>2.432537606340457</v>
@@ -19474,7 +19477,7 @@
         <v>1</v>
       </c>
       <c r="P361" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="362" spans="1:16">
@@ -19488,7 +19491,7 @@
         <v>1.558060029409038</v>
       </c>
       <c r="D362" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E362">
         <v>2.432537606340457</v>
@@ -19524,7 +19527,7 @@
         <v>1</v>
       </c>
       <c r="P362" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="363" spans="1:16">
@@ -19538,7 +19541,7 @@
         <v>1.5546355793606</v>
       </c>
       <c r="D363" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E363">
         <v>2.429478755941318</v>
@@ -19588,7 +19591,7 @@
         <v>2.749895863416445</v>
       </c>
       <c r="D364" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E364">
         <v>2.144120683335579</v>
@@ -19624,7 +19627,7 @@
         <v>1</v>
       </c>
       <c r="P364" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="365" spans="1:16">
@@ -19638,7 +19641,7 @@
         <v>1.575757316392718</v>
       </c>
       <c r="D365" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E365">
         <v>2.448345503254703</v>
@@ -19674,7 +19677,7 @@
         <v>1</v>
       </c>
       <c r="P365" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="366" spans="1:16">
@@ -19688,7 +19691,7 @@
         <v>1.708690594836302</v>
       </c>
       <c r="D366" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E366">
         <v>1.95524223097577</v>
@@ -19724,7 +19727,7 @@
         <v>1</v>
       </c>
       <c r="P366" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="367" spans="1:16">
@@ -19738,7 +19741,7 @@
         <v>2.776972324350222</v>
       </c>
       <c r="D367" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E367">
         <v>2.170167242074328</v>
@@ -19774,7 +19777,7 @@
         <v>1</v>
       </c>
       <c r="P367" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="368" spans="1:16">
@@ -19788,7 +19791,7 @@
         <v>1.603764011567165</v>
       </c>
       <c r="D368" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E368">
         <v>2.473362159798427</v>
@@ -19824,7 +19827,7 @@
         <v>1</v>
       </c>
       <c r="P368" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="369" spans="1:16">
@@ -19838,7 +19841,7 @@
         <v>1.733308579562596</v>
       </c>
       <c r="D369" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E369">
         <v>2.069952921130998</v>
@@ -19874,7 +19877,7 @@
         <v>1</v>
       </c>
       <c r="P369" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="370" spans="1:16">
@@ -19888,7 +19891,7 @@
         <v>2.804318151096002</v>
       </c>
       <c r="D370" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E370">
         <v>2.196472920808915</v>
@@ -19924,7 +19927,7 @@
         <v>1</v>
       </c>
       <c r="P370" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="371" spans="1:16">
@@ -19938,7 +19941,7 @@
         <v>1.632049326839176</v>
       </c>
       <c r="D371" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E371">
         <v>2.498627690521825</v>
@@ -19974,7 +19977,7 @@
         <v>1</v>
       </c>
       <c r="P371" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="372" spans="1:16">
@@ -19988,7 +19991,7 @@
         <v>1.758171472346181</v>
       </c>
       <c r="D372" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E372">
         <v>2.648741745065742</v>
@@ -20024,7 +20027,7 @@
         <v>1</v>
       </c>
       <c r="P372" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="373" spans="1:16">
@@ -20038,7 +20041,7 @@
         <v>1.836308899819077</v>
       </c>
       <c r="D373" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E373">
         <v>2.387421432319158</v>
@@ -20074,7 +20077,7 @@
         <v>1</v>
       </c>
       <c r="P373" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="374" spans="1:16">
@@ -20124,7 +20127,7 @@
         <v>1</v>
       </c>
       <c r="P374" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="375" spans="1:16">
@@ -20138,7 +20141,7 @@
         <v>1.66686196794393</v>
       </c>
       <c r="D375" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E375">
         <v>2.529723679551338</v>
@@ -20174,7 +20177,7 @@
         <v>1</v>
       </c>
       <c r="P375" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="376" spans="1:16">
@@ -20188,7 +20191,7 @@
         <v>1.844881242140559</v>
       </c>
       <c r="D376" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E376">
         <v>2.529723679551338</v>
@@ -20224,7 +20227,7 @@
         <v>1</v>
       </c>
       <c r="P376" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="377" spans="1:16">
@@ -20238,7 +20241,7 @@
         <v>1.788771907765661</v>
       </c>
       <c r="D377" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E377">
         <v>2.679961622497764</v>
@@ -20274,7 +20277,7 @@
         <v>1</v>
       </c>
       <c r="P377" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="378" spans="1:16">
@@ -20288,7 +20291,7 @@
         <v>1.861508767932467</v>
       </c>
       <c r="D378" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E378">
         <v>2.411732640096055</v>
@@ -20324,7 +20327,7 @@
         <v>1</v>
       </c>
       <c r="P378" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="379" spans="1:16">
@@ -20374,7 +20377,7 @@
         <v>1</v>
       </c>
       <c r="P379" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="380" spans="1:16">
@@ -20388,7 +20391,7 @@
         <v>1.693616991646184</v>
       </c>
       <c r="D380" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E380">
         <v>2.55362229502915</v>
@@ -20424,7 +20427,7 @@
         <v>1</v>
       </c>
       <c r="P380" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="381" spans="1:16">
@@ -20438,7 +20441,7 @@
         <v>1.869509828609061</v>
       </c>
       <c r="D381" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E381">
         <v>2.55362229502915</v>
@@ -20474,7 +20477,7 @@
         <v>1</v>
       </c>
       <c r="P381" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="382" spans="1:16">
@@ -20488,7 +20491,7 @@
         <v>2.574954921244757</v>
       </c>
       <c r="D382" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E382">
         <v>2.17950982860906</v>
@@ -20524,7 +20527,7 @@
         <v>1</v>
       </c>
       <c r="P382" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="383" spans="1:16">
@@ -20538,7 +20541,7 @@
         <v>1.812289668813548</v>
       </c>
       <c r="D383" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E383">
         <v>2.703955451583056</v>
@@ -20574,7 +20577,7 @@
         <v>1</v>
       </c>
       <c r="P383" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="384" spans="1:16">
@@ -20588,7 +20591,7 @@
         <v>1.878354735459471</v>
       </c>
       <c r="D384" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E384">
         <v>2.42798454327702</v>
@@ -20624,7 +20627,7 @@
         <v>1</v>
       </c>
       <c r="P384" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="385" spans="1:16">
@@ -20674,7 +20677,7 @@
         <v>1</v>
       </c>
       <c r="P385" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="386" spans="1:16">
@@ -20688,7 +20691,7 @@
         <v>1.711502571778759</v>
       </c>
       <c r="D386" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E386">
         <v>2.569598382620882</v>
@@ -20724,7 +20727,7 @@
         <v>1</v>
       </c>
       <c r="P386" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="387" spans="1:16">
@@ -20738,7 +20741,7 @@
         <v>1.885973897627895</v>
       </c>
       <c r="D387" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E387">
         <v>2.569598382620882</v>
@@ -20774,7 +20777,7 @@
         <v>1</v>
       </c>
       <c r="P387" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="388" spans="1:16">
@@ -20788,7 +20791,7 @@
         <v>2.591185607841933</v>
       </c>
       <c r="D388" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E388">
         <v>2.195973897627894</v>
@@ -20824,7 +20827,7 @@
         <v>1</v>
       </c>
       <c r="P388" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="389" spans="1:16">
@@ -20838,7 +20841,7 @@
         <v>1.828011157399832</v>
       </c>
       <c r="D389" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E389">
         <v>2.719995188926148</v>
@@ -20874,7 +20877,7 @@
         <v>1</v>
       </c>
       <c r="P389" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="390" spans="1:16">
@@ -20888,7 +20891,7 @@
         <v>1.884937981108568</v>
       </c>
       <c r="D390" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E390">
         <v>2.434335634167709</v>
@@ -20924,7 +20927,7 @@
         <v>1</v>
       </c>
       <c r="P390" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="391" spans="1:16">
@@ -20974,7 +20977,7 @@
         <v>1</v>
       </c>
       <c r="P391" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="392" spans="1:16">
@@ -20988,7 +20991,7 @@
         <v>1.718492088255065</v>
       </c>
       <c r="D392" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E392">
         <v>2.575841687373739</v>
@@ -21024,7 +21027,7 @@
         <v>1</v>
       </c>
       <c r="P392" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="393" spans="1:16">
@@ -21038,7 +21041,7 @@
         <v>1.892407900932305</v>
       </c>
       <c r="D393" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E393">
         <v>2.575841687373739</v>
@@ -21074,7 +21077,7 @@
         <v>1</v>
       </c>
       <c r="P393" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="394" spans="1:16">
@@ -21088,7 +21091,7 @@
         <v>1.834154967256232</v>
       </c>
       <c r="D394" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E394">
         <v>2.726263367403121</v>
@@ -21124,7 +21127,7 @@
         <v>1</v>
       </c>
       <c r="P394" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="395" spans="1:16">
@@ -21138,7 +21141,7 @@
         <v>2.791624887079966</v>
       </c>
       <c r="D395" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E395">
         <v>2.637829766815571</v>
@@ -21174,7 +21177,7 @@
         <v>1</v>
       </c>
       <c r="P395" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="396" spans="1:16">
@@ -21188,7 +21191,7 @@
         <v>1.897004594528006</v>
       </c>
       <c r="D396" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E396">
         <v>2.445976724695786</v>
@@ -21224,7 +21227,7 @@
         <v>1</v>
       </c>
       <c r="P396" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="397" spans="1:16">
@@ -21274,7 +21277,7 @@
         <v>1</v>
       </c>
       <c r="P397" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="398" spans="1:16">
@@ -21288,7 +21291,7 @@
         <v>1.731303366734398</v>
       </c>
       <c r="D398" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E398">
         <v>2.587285213702252</v>
@@ -21324,7 +21327,7 @@
         <v>1</v>
       </c>
       <c r="P398" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="399" spans="1:16">
@@ -21338,7 +21341,7 @@
         <v>1.904200963921582</v>
       </c>
       <c r="D399" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E399">
         <v>2.587285213702252</v>
@@ -21374,7 +21377,7 @@
         <v>1</v>
       </c>
       <c r="P399" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="400" spans="1:16">
@@ -21388,7 +21391,7 @@
         <v>1.845416126631299</v>
       </c>
       <c r="D400" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E400">
         <v>2.737752485469994</v>
@@ -21424,7 +21427,7 @@
         <v>1</v>
       </c>
       <c r="P400" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="401" spans="1:16">
@@ -21438,7 +21441,7 @@
         <v>2.802612496024871</v>
       </c>
       <c r="D401" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E401">
         <v>2.813453713263602</v>
@@ -21474,7 +21477,7 @@
         <v>1</v>
       </c>
       <c r="P401" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="402" spans="1:16">
@@ -21488,7 +21491,7 @@
         <v>1.915149243214803</v>
       </c>
       <c r="D402" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E402">
         <v>2.463481511716044</v>
@@ -21524,7 +21527,7 @@
         <v>1</v>
       </c>
       <c r="P402" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="403" spans="1:16">
@@ -21574,7 +21577,7 @@
         <v>1</v>
       </c>
       <c r="P403" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="404" spans="1:16">
@@ -21588,7 +21591,7 @@
         <v>1.750567773337632</v>
       </c>
       <c r="D404" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E404">
         <v>2.60449292209162</v>
@@ -21624,7 +21627,7 @@
         <v>1</v>
       </c>
       <c r="P404" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="405" spans="1:16">
@@ -21638,7 +21641,7 @@
         <v>1.921934272965604</v>
       </c>
       <c r="D405" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E405">
         <v>2.60449292209162</v>
@@ -21674,7 +21677,7 @@
         <v>1</v>
       </c>
       <c r="P405" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="406" spans="1:16">
@@ -21688,7 +21691,7 @@
         <v>1.862349608592151</v>
       </c>
       <c r="D406" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E406">
         <v>2.75502875046649</v>
@@ -21724,7 +21727,7 @@
         <v>1</v>
       </c>
       <c r="P406" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="407" spans="1:16">
@@ -21738,7 +21741,7 @@
         <v>2.819134638342948</v>
       </c>
       <c r="D407" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E407">
         <v>2.769730713091974</v>
@@ -21774,7 +21777,7 @@
         <v>1</v>
       </c>
       <c r="P407" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="408" spans="1:16">
@@ -21788,7 +21791,7 @@
         <v>1.92753511972947</v>
       </c>
       <c r="D408" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E408">
         <v>2.475430606691152</v>
@@ -21888,7 +21891,7 @@
         <v>1.76371801754653</v>
       </c>
       <c r="D410" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E410">
         <v>2.616239225637646</v>
@@ -21938,7 +21941,7 @@
         <v>1.934039361347697</v>
       </c>
       <c r="D411" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E411">
         <v>2.616239225637646</v>
@@ -21988,7 +21991,7 @@
         <v>1.873908720049794</v>
       </c>
       <c r="D412" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E412">
         <v>2.766821852034614</v>
@@ -22038,7 +22041,7 @@
         <v>2.830412961668017</v>
       </c>
       <c r="D413" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E413">
         <v>2.221708855759843</v>
@@ -22088,7 +22091,7 @@
         <v>1.937685341557977</v>
       </c>
       <c r="D414" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E414">
         <v>2.485222886188172</v>
@@ -22124,7 +22127,7 @@
         <v>1</v>
       </c>
       <c r="P414" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="415" spans="1:16">
@@ -22174,7 +22177,7 @@
         <v>1</v>
       </c>
       <c r="P415" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="416" spans="1:16">
@@ -22188,7 +22191,7 @@
         <v>1.774494638455131</v>
       </c>
       <c r="D416" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E416">
         <v>2.625865317623621</v>
@@ -22224,7 +22227,7 @@
         <v>1</v>
       </c>
       <c r="P416" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="417" spans="1:16">
@@ -22238,7 +22241,7 @@
         <v>1.943959477391676</v>
       </c>
       <c r="D417" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E417">
         <v>2.625865317623621</v>
@@ -22274,7 +22277,7 @@
         <v>1</v>
       </c>
       <c r="P417" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="418" spans="1:16">
@@ -22288,7 +22291,7 @@
         <v>1.883381408179421</v>
       </c>
       <c r="D418" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E418">
         <v>2.776486294984675</v>
@@ -22324,7 +22327,7 @@
         <v>1</v>
       </c>
       <c r="P418" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="419" spans="1:16">
@@ -22338,7 +22341,7 @@
         <v>2.839655544013116</v>
       </c>
       <c r="D419" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E419">
         <v>2.231475567947474</v>
@@ -22374,7 +22377,7 @@
         <v>1</v>
       </c>
       <c r="P419" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="420" spans="1:16">
@@ -22388,7 +22391,7 @@
         <v>1.950149148490695</v>
       </c>
       <c r="D420" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E420">
         <v>2.49724716340538</v>
@@ -22424,7 +22427,7 @@
         <v>1</v>
       </c>
       <c r="P420" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="421" spans="1:16">
@@ -22474,7 +22477,7 @@
         <v>1</v>
       </c>
       <c r="P421" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="422" spans="1:16">
@@ -22488,7 +22491,7 @@
         <v>1.787727622389998</v>
       </c>
       <c r="D422" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E422">
         <v>2.637685527472915</v>
@@ -22524,7 +22527,7 @@
         <v>1</v>
       </c>
       <c r="P422" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="423" spans="1:16">
@@ -22538,7 +22541,7 @@
         <v>1.956140729507283</v>
       </c>
       <c r="D423" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E423">
         <v>2.637685527472915</v>
@@ -22574,7 +22577,7 @@
         <v>1</v>
       </c>
       <c r="P423" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="424" spans="1:16">
@@ -22588,7 +22591,7 @@
         <v>1.895013248150637</v>
       </c>
       <c r="D424" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E424">
         <v>2.788353597303487</v>
@@ -22624,7 +22627,7 @@
         <v>1</v>
       </c>
       <c r="P424" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="425" spans="1:16">
@@ -22638,7 +22641,7 @@
         <v>2.85100482916722</v>
       </c>
       <c r="D425" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E425">
         <v>2.243468450185002</v>
@@ -22674,7 +22677,7 @@
         <v>1</v>
       </c>
       <c r="P425" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="426" spans="1:16">
@@ -22738,7 +22741,7 @@
         <v>1.796280604882195</v>
       </c>
       <c r="D427" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E427">
         <v>2.645325380161676</v>
@@ -22788,7 +22791,7 @@
         <v>1.964013937590256</v>
       </c>
       <c r="D428" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E428">
         <v>2.645325380161676</v>
@@ -22838,7 +22841,7 @@
         <v>1.902531350198938</v>
       </c>
       <c r="D429" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E429">
         <v>2.796023887652364</v>
@@ -22888,7 +22891,7 @@
         <v>2.858340305254835</v>
       </c>
       <c r="D430" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E430">
         <v>2.251219907627515</v>
@@ -22974,7 +22977,7 @@
         <v>1</v>
       </c>
       <c r="P431" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="432" spans="1:16">
@@ -22988,7 +22991,7 @@
         <v>1.81059278070445</v>
       </c>
       <c r="D432" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E432">
         <v>2.658109565682619</v>
@@ -23024,7 +23027,7 @@
         <v>1</v>
       </c>
       <c r="P432" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="433" spans="1:16">
@@ -23038,7 +23041,7 @@
         <v>1.977188609521534</v>
       </c>
       <c r="D433" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E433">
         <v>2.658109565682619</v>
@@ -23074,7 +23077,7 @@
         <v>1</v>
       </c>
       <c r="P433" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="434" spans="1:16">
@@ -23088,7 +23091,7 @@
         <v>1.915111803679711</v>
       </c>
       <c r="D434" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E434">
         <v>2.808859006183351</v>
@@ -23124,7 +23127,7 @@
         <v>1</v>
       </c>
       <c r="P434" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="435" spans="1:16">
@@ -23138,7 +23141,7 @@
         <v>2.870615160675342</v>
       </c>
       <c r="D435" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E435">
         <v>2.26419084751862</v>
@@ -23174,7 +23177,7 @@
         <v>1</v>
       </c>
       <c r="P435" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="436" spans="1:16">
@@ -23224,7 +23227,7 @@
         <v>1</v>
       </c>
       <c r="P436" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="437" spans="1:16">
@@ -23238,7 +23241,7 @@
         <v>1.82632056259726</v>
       </c>
       <c r="D437" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E437">
         <v>2.672158224953424</v>
@@ -23274,7 +23277,7 @@
         <v>1</v>
       </c>
       <c r="P437" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="438" spans="1:16">
@@ -23288,7 +23291,7 @@
         <v>1.991666377906849</v>
       </c>
       <c r="D438" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E438">
         <v>2.672158224953424</v>
@@ -23324,7 +23327,7 @@
         <v>1</v>
       </c>
       <c r="P438" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="439" spans="1:16">
@@ -23338,7 +23341,7 @@
         <v>1.928936579934245</v>
       </c>
       <c r="D439" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E439">
         <v>2.822963636208222</v>
@@ -23374,7 +23377,7 @@
         <v>1</v>
       </c>
       <c r="P439" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="440" spans="1:16">
@@ -23388,7 +23391,7 @@
         <v>2.884104112405478</v>
       </c>
       <c r="D440" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E440">
         <v>2.278444732887671</v>
@@ -23424,7 +23427,7 @@
         <v>1</v>
       </c>
       <c r="P440" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="441" spans="1:16">
@@ -23438,7 +23441,7 @@
         <v>1.850091985515281</v>
       </c>
       <c r="D441" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E441">
         <v>2.693391773538558</v>
@@ -23488,7 +23491,7 @@
         <v>2.013548494377055</v>
       </c>
       <c r="D442" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E442">
         <v>2.693391773538558</v>
@@ -23538,7 +23541,7 @@
         <v>1.949831745274995</v>
       </c>
       <c r="D443" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E443">
         <v>2.844281780604454</v>
@@ -23588,7 +23591,7 @@
         <v>2.90449170287965</v>
       </c>
       <c r="D444" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E444">
         <v>2.29998846611349</v>
@@ -23638,7 +23641,7 @@
         <v>1.883787347386825</v>
       </c>
       <c r="D445" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E445">
         <v>2.723489765815277</v>
@@ -23674,7 +23677,7 @@
         <v>1</v>
       </c>
       <c r="P445" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="446" spans="1:16">
@@ -23688,7 +23691,7 @@
         <v>2.044565814439117</v>
       </c>
       <c r="D446" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E446">
         <v>2.723489765815277</v>
@@ -23724,7 +23727,7 @@
         <v>1</v>
       </c>
       <c r="P446" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="447" spans="1:16">
@@ -23738,7 +23741,7 @@
         <v>2.74752944335815</v>
       </c>
       <c r="D447" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E447">
         <v>2.354565814439116</v>
@@ -23774,7 +23777,7 @@
         <v>1</v>
       </c>
       <c r="P447" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="448" spans="1:16">
@@ -23788,7 +23791,7 @@
         <v>1.979450088272404</v>
       </c>
       <c r="D448" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E448">
         <v>2.874499685200998</v>
@@ -23824,7 +23827,7 @@
         <v>1</v>
       </c>
       <c r="P448" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="449" spans="1:16">
@@ -23838,7 +23841,7 @@
         <v>2.933390571958093</v>
       </c>
       <c r="D449" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E449">
         <v>2.330526136896243</v>
@@ -23874,7 +23877,7 @@
         <v>1</v>
       </c>
       <c r="P449" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="450" spans="1:16">
@@ -23924,7 +23927,7 @@
         <v>1</v>
       </c>
       <c r="P450" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="451" spans="1:16">
@@ -23938,7 +23941,7 @@
         <v>1.920897553279229</v>
       </c>
       <c r="D451" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E451">
         <v>2.756638028018099</v>
@@ -23974,7 +23977,7 @@
         <v>1</v>
       </c>
       <c r="P451" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="452" spans="1:16">
@@ -23988,7 +23991,7 @@
         <v>2.078726573362612</v>
       </c>
       <c r="D452" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E452">
         <v>2.756638028018099</v>
@@ -24024,7 +24027,7 @@
         <v>1</v>
       </c>
       <c r="P452" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="453" spans="1:16">
@@ -24038,7 +24041,7 @@
         <v>2.012070091316616</v>
       </c>
       <c r="D453" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E453">
         <v>2.907780012193474</v>
@@ -24074,7 +24077,7 @@
         <v>1</v>
       </c>
       <c r="P453" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="454" spans="1:16">
@@ -24088,7 +24091,7 @@
         <v>2.965218186264387</v>
       </c>
       <c r="D454" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E454">
         <v>2.364158636661127</v>
@@ -24124,7 +24127,7 @@
         <v>1</v>
       </c>
       <c r="P454" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="455" spans="1:16">
@@ -24138,7 +24141,7 @@
         <v>1.971362962924253</v>
       </c>
       <c r="D455" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E455">
         <v>2.801715671508852</v>
@@ -24188,7 +24191,7 @@
         <v>2.125181090426125</v>
       </c>
       <c r="D456" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E456">
         <v>2.801715671508852</v>
@@ -24238,7 +24241,7 @@
         <v>2.056429365986798</v>
       </c>
       <c r="D457" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E457">
         <v>2.95303724788937</v>
@@ -24288,7 +24291,7 @@
         <v>3.008499907703719</v>
       </c>
       <c r="D458" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E458">
         <v>2.409894784904068</v>
@@ -24338,7 +24341,7 @@
         <v>2.008171638992437</v>
       </c>
       <c r="D459" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E459">
         <v>2.834594595683633</v>
@@ -24374,7 +24377,7 @@
         <v>1</v>
       </c>
       <c r="P459" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="460" spans="1:16">
@@ -24388,7 +24391,7 @@
         <v>2.159064284529219</v>
       </c>
       <c r="D460" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E460">
         <v>2.834594595683633</v>
@@ -24424,7 +24427,7 @@
         <v>1</v>
       </c>
       <c r="P460" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="461" spans="1:16">
@@ -24438,7 +24441,7 @@
         <v>2.088784323242461</v>
       </c>
       <c r="D461" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E461">
         <v>2.986047163793931</v>
@@ -24474,7 +24477,7 @@
         <v>1</v>
       </c>
       <c r="P461" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="462" spans="1:16">
@@ -24488,7 +24491,7 @@
         <v>3.040068914580697</v>
       </c>
       <c r="D462" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E462">
         <v>2.443254012088044</v>
@@ -24524,7 +24527,7 @@
         <v>1</v>
       </c>
       <c r="P462" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="463" spans="1:16">
@@ -24538,7 +24541,7 @@
         <v>2.067700645146257</v>
       </c>
       <c r="D463" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E463">
         <v>2.887768191927794</v>
@@ -24588,7 +24591,7 @@
         <v>2.213862041083626</v>
       </c>
       <c r="D464" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E464">
         <v>2.887768191927794</v>
@@ -24638,7 +24641,7 @@
         <v>2.914425852356924</v>
       </c>
       <c r="D465" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E465">
         <v>2.523862041083625</v>
@@ -24688,7 +24691,7 @@
         <v>2.141110531498665</v>
       </c>
       <c r="D466" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E466">
         <v>3.039432607035081</v>
@@ -24738,7 +24741,7 @@
         <v>3.091124040854972</v>
       </c>
       <c r="D467" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E467">
         <v>2.497204380654495</v>
@@ -24788,7 +24791,7 @@
         <v>2.102053433035913</v>
       </c>
       <c r="D468" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E468">
         <v>2.918453422391508</v>
@@ -24824,7 +24827,7 @@
         <v>1</v>
       </c>
       <c r="P468" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="469" spans="1:16">
@@ -24838,7 +24841,7 @@
         <v>2.245484536222857</v>
       </c>
       <c r="D469" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E469">
         <v>2.918453422391508</v>
@@ -24874,7 +24877,7 @@
         <v>1</v>
       </c>
       <c r="P469" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="470" spans="1:16">
@@ -24888,7 +24891,7 @@
         <v>2.945600090477427</v>
       </c>
       <c r="D470" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E470">
         <v>2.555484536222856</v>
@@ -24924,7 +24927,7 @@
         <v>1</v>
       </c>
       <c r="P470" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="471" spans="1:16">
@@ -24938,7 +24941,7 @@
         <v>2.171306754305586</v>
       </c>
       <c r="D471" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E471">
         <v>3.070240089412991</v>
@@ -24974,7 +24977,7 @@
         <v>1</v>
       </c>
       <c r="P471" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="472" spans="1:16">
@@ -24988,7 +24991,7 @@
         <v>3.120586752176706</v>
       </c>
       <c r="D472" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E472">
         <v>2.528337868136934</v>
@@ -25024,7 +25027,7 @@
         <v>1</v>
       </c>
       <c r="P472" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="473" spans="1:16">
@@ -25038,7 +25041,7 @@
         <v>2.150109762840597</v>
       </c>
       <c r="D473" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E473">
         <v>2.961379183177897</v>
@@ -25074,7 +25077,7 @@
         <v>1</v>
       </c>
       <c r="P473" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="474" spans="1:16">
@@ -25088,7 +25091,7 @@
         <v>2.289721442425034</v>
       </c>
       <c r="D474" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E474">
         <v>2.961379183177897</v>
@@ -25124,7 +25127,7 @@
         <v>1</v>
       </c>
       <c r="P474" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="475" spans="1:16">
@@ -25138,7 +25141,7 @@
         <v>2.989209927132926</v>
       </c>
       <c r="D475" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E475">
         <v>2.599721442425032</v>
@@ -25174,7 +25177,7 @@
         <v>1</v>
       </c>
       <c r="P475" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="476" spans="1:16">
@@ -25188,7 +25191,7 @@
         <v>2.213548439222873</v>
       </c>
       <c r="D476" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E476">
         <v>3.113336869166659</v>
@@ -25224,7 +25227,7 @@
         <v>1</v>
       </c>
       <c r="P476" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="477" spans="1:16">
@@ -25238,7 +25241,7 @@
         <v>3.161802323290331</v>
       </c>
       <c r="D477" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E477">
         <v>2.571890698470007</v>
@@ -25274,7 +25277,7 @@
         <v>1</v>
       </c>
       <c r="P477" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="478" spans="1:16">
@@ -25288,7 +25291,7 @@
         <v>2.189716387261424</v>
       </c>
       <c r="D478" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E478">
         <v>2.99675734235807</v>
@@ -25338,7 +25341,7 @@
         <v>2.326180209388927</v>
       </c>
       <c r="D479" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E479">
         <v>2.99675734235807</v>
@@ -25388,7 +25391,7 @@
         <v>2.248362803037622</v>
       </c>
       <c r="D480" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E480">
         <v>3.148855977188184</v>
@@ -25438,7 +25441,7 @@
         <v>3.19577099405695</v>
       </c>
       <c r="D481" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E481">
         <v>2.607785670068477</v>
@@ -25488,7 +25491,7 @@
         <v>2.215826782258592</v>
       </c>
       <c r="D482" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E482">
         <v>3.020080150700736</v>
@@ -25524,7 +25527,7 @@
         <v>1</v>
       </c>
       <c r="P482" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="483" spans="1:16">
@@ -25538,7 +25541,7 @@
         <v>2.350215400987747</v>
       </c>
       <c r="D483" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E483">
         <v>3.020080150700736</v>
@@ -25574,7 +25577,7 @@
         <v>1</v>
       </c>
       <c r="P483" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="484" spans="1:16">
@@ -25588,7 +25591,7 @@
         <v>2.271313933159689</v>
       </c>
       <c r="D484" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E484">
         <v>3.172271705086001</v>
@@ -25624,7 +25627,7 @@
         <v>1</v>
       </c>
       <c r="P484" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="485" spans="1:16">
@@ -25638,7 +25641,7 @@
         <v>3.218164606848116</v>
       </c>
       <c r="D485" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E485">
         <v>2.631449183446694</v>
@@ -25674,7 +25677,7 @@
         <v>1</v>
       </c>
       <c r="P485" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="486" spans="1:16">
@@ -25724,7 +25727,7 @@
         <v>1</v>
       </c>
       <c r="P486" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="487" spans="1:16">
@@ -25738,7 +25741,7 @@
         <v>2.227304742320833</v>
       </c>
       <c r="D487" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E487">
         <v>3.030332705774125</v>
@@ -25774,7 +25777,7 @@
         <v>1</v>
       </c>
       <c r="P487" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="488" spans="1:16">
@@ -25788,7 +25791,7 @@
         <v>2.360781115113841</v>
       </c>
       <c r="D488" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E488">
         <v>3.030332705774125</v>
@@ -25824,7 +25827,7 @@
         <v>1</v>
       </c>
       <c r="P488" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="489" spans="1:16">
@@ -25838,7 +25841,7 @@
         <v>2.28140310090123</v>
       </c>
       <c r="D489" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E489">
         <v>3.182565106992353</v>
@@ -25874,7 +25877,7 @@
         <v>1</v>
       </c>
       <c r="P489" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="490" spans="1:16">
@@ -25888,7 +25891,7 @@
         <v>3.228008693591889</v>
       </c>
       <c r="D490" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E490">
         <v>2.641851510240944</v>
@@ -25924,7 +25927,7 @@
         <v>1</v>
       </c>
       <c r="P490" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="491" spans="1:16">
@@ -25938,7 +25941,7 @@
         <v>2.326764722017106</v>
       </c>
       <c r="D491" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E491">
         <v>2.338905512271317</v>
@@ -25974,7 +25977,7 @@
         <v>1</v>
       </c>
       <c r="P491" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="492" spans="1:16">
@@ -25988,7 +25991,7 @@
         <v>2.245345573811253</v>
       </c>
       <c r="D492" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E492">
         <v>3.046447469845635</v>
@@ -26024,7 +26027,7 @@
         <v>1</v>
       </c>
       <c r="P492" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="493" spans="1:16">
@@ -26038,7 +26041,7 @@
         <v>2.377388096414631</v>
       </c>
       <c r="D493" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E493">
         <v>3.046447469845635</v>
@@ -26074,7 +26077,7 @@
         <v>1</v>
       </c>
       <c r="P493" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="494" spans="1:16">
@@ -26088,7 +26091,7 @@
         <v>2.297261055983554</v>
       </c>
       <c r="D494" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E494">
         <v>3.198744073311161</v>
@@ -26124,7 +26127,7 @@
         <v>1</v>
       </c>
       <c r="P494" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="495" spans="1:16">
@@ -26138,7 +26141,7 @@
         <v>3.243481435190432</v>
       </c>
       <c r="D495" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E495">
         <v>2.658201682552544</v>
@@ -26174,7 +26177,7 @@
         <v>1</v>
       </c>
       <c r="P495" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="496" spans="1:16">
@@ -26224,7 +26227,7 @@
         <v>1</v>
       </c>
       <c r="P496" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="497" spans="1:16">
@@ -26238,7 +26241,7 @@
         <v>2.301170929293026</v>
       </c>
       <c r="D497" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E497">
         <v>3.202733093853617</v>
@@ -26288,7 +26291,7 @@
         <v>3.247296331820319</v>
       </c>
       <c r="D498" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E498">
         <v>2.662232914952593</v>
@@ -26388,7 +26391,7 @@
         <v>2.309276220482282</v>
       </c>
       <c r="D500" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E500">
         <v>3.211002459763304</v>
@@ -26424,7 +26427,7 @@
         <v>1</v>
       </c>
       <c r="P500" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="501" spans="1:16">
@@ -26438,7 +26441,7 @@
         <v>3.25520473334506</v>
       </c>
       <c r="D501" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E501">
         <v>2.670589787379843</v>
@@ -26474,7 +26477,7 @@
         <v>1</v>
       </c>
       <c r="P501" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="502" spans="1:16">
@@ -26488,7 +26491,7 @@
         <v>2.35659384998981</v>
       </c>
       <c r="D502" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E502">
         <v>2.377701080695644</v>
@@ -26524,7 +26527,7 @@
         <v>1</v>
       </c>
       <c r="P502" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="503" spans="1:16">
@@ -26538,7 +26541,7 @@
         <v>2.318802840630408</v>
       </c>
       <c r="D503" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E503">
         <v>3.220721926473129</v>
@@ -26588,7 +26591,7 @@
         <v>3.264499937619139</v>
       </c>
       <c r="D504" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E504">
         <v>2.680412105589244</v>
@@ -26738,7 +26741,7 @@
         <v>2.968469110715926</v>
       </c>
       <c r="D507" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E507">
         <v>3.65607053595874</v>
@@ -26774,7 +26777,7 @@
         <v>1</v>
       </c>
       <c r="P507" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="508" spans="1:16">
@@ -26788,7 +26791,7 @@
         <v>3.056098677724048</v>
       </c>
       <c r="D508" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E508">
         <v>3.65607053595874</v>
@@ -26824,7 +26827,7 @@
         <v>1</v>
       </c>
       <c r="P508" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="509" spans="1:16">
@@ -26838,7 +26841,7 @@
         <v>3.085552267926261</v>
       </c>
       <c r="D509" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E509">
         <v>3.65607053595874</v>
@@ -26874,7 +26877,7 @@
         <v>1</v>
       </c>
       <c r="P509" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="510" spans="1:16">
@@ -26888,7 +26891,7 @@
         <v>3.115403587495276</v>
       </c>
       <c r="D510" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E510">
         <v>4.899694426383849</v>
@@ -26924,7 +26927,7 @@
         <v>1</v>
       </c>
       <c r="P510" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="511" spans="1:16">
@@ -26938,7 +26941,7 @@
         <v>2.857657467623699</v>
       </c>
       <c r="D511" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E511">
         <v>4.899694426383849</v>
@@ -26974,7 +26977,7 @@
         <v>1</v>
       </c>
       <c r="P511" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="512" spans="1:16">
@@ -26988,7 +26991,7 @@
         <v>4.634833021734408</v>
       </c>
       <c r="D512" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E512">
         <v>3.48240231940969</v>
@@ -27024,7 +27027,7 @@
         <v>1</v>
       </c>
       <c r="P512" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="513" spans="1:16">
@@ -27038,7 +27041,7 @@
         <v>3.013404560606677</v>
       </c>
       <c r="D513" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E513">
         <v>3.707166946903694</v>
@@ -27074,7 +27077,7 @@
         <v>1</v>
       </c>
       <c r="P513" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="514" spans="1:16">
@@ -27088,7 +27091,7 @@
         <v>3.101938488870459</v>
       </c>
       <c r="D514" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E514">
         <v>3.707166946903694</v>
@@ -27124,7 +27127,7 @@
         <v>1</v>
       </c>
       <c r="P514" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="515" spans="1:16">
@@ -27138,7 +27141,7 @@
         <v>3.133031233848563</v>
       </c>
       <c r="D515" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E515">
         <v>3.707166946903694</v>
@@ -27174,7 +27177,7 @@
         <v>1</v>
       </c>
       <c r="P515" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="516" spans="1:16">
@@ -27188,7 +27191,7 @@
         <v>2.923647577997855</v>
       </c>
       <c r="D516" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E516">
         <v>4.966814988327585</v>
@@ -27224,7 +27227,7 @@
         <v>1</v>
       </c>
       <c r="P516" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="517" spans="1:16">
@@ -27238,7 +27241,7 @@
         <v>4.706192777064061</v>
       </c>
       <c r="D517" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E517">
         <v>3.555881671432303</v>
@@ -27274,7 +27277,7 @@
         <v>1</v>
       </c>
       <c r="P517" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="518" spans="1:16">
@@ -27288,7 +27291,7 @@
         <v>3.058294813446018</v>
       </c>
       <c r="D518" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E518">
         <v>3.758211963968808</v>
@@ -27324,7 +27327,7 @@
         <v>1</v>
       </c>
       <c r="P518" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="519" spans="1:16">
@@ -27338,7 +27341,7 @@
         <v>3.147732193339273</v>
       </c>
       <c r="D519" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E519">
         <v>3.758211963968808</v>
@@ -27374,7 +27377,7 @@
         <v>1</v>
       </c>
       <c r="P519" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="520" spans="1:16">
@@ -27388,7 +27391,7 @@
         <v>3.18046244439579</v>
       </c>
       <c r="D520" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E520">
         <v>3.758211963968808</v>
@@ -27424,7 +27427,7 @@
         <v>1</v>
       </c>
       <c r="P520" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="521" spans="1:16">
@@ -27438,7 +27441,7 @@
         <v>3.225680173488445</v>
       </c>
       <c r="D521" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E521">
         <v>5.033868038952384</v>
@@ -27474,7 +27477,7 @@
         <v>1</v>
       </c>
       <c r="P521" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="522" spans="1:16">
@@ -27488,7 +27491,7 @@
         <v>2.989571314085818</v>
       </c>
       <c r="D522" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E522">
         <v>5.033868038952384</v>
@@ -27524,7 +27527,7 @@
         <v>1</v>
       </c>
       <c r="P522" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="523" spans="1:16">
@@ -27538,7 +27541,7 @@
         <v>4.77748075720201</v>
       </c>
       <c r="D523" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E523">
         <v>3.629287116326825</v>
@@ -27574,7 +27577,7 @@
         <v>1</v>
       </c>
       <c r="P523" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="524" spans="1:16">
@@ -27588,7 +27591,7 @@
         <v>3.100990526217007</v>
       </c>
       <c r="D524" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E524">
         <v>5.097643081613452</v>
@@ -27624,7 +27627,7 @@
         <v>1</v>
       </c>
       <c r="P524" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="525" spans="1:16">
@@ -27638,7 +27641,7 @@
         <v>3.19128719089559</v>
       </c>
       <c r="D525" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E525">
         <v>5.097643081613452</v>
@@ -27674,7 +27677,7 @@
         <v>1</v>
       </c>
       <c r="P525" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="526" spans="1:16">
@@ -27688,7 +27691,7 @@
         <v>3.225574895625517</v>
       </c>
       <c r="D526" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E526">
         <v>5.097643081613452</v>
@@ -27724,7 +27727,7 @@
         <v>1</v>
       </c>
       <c r="P526" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="527" spans="1:16">
@@ -27738,7 +27741,7 @@
         <v>3.205781960817575</v>
       </c>
       <c r="D527" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E527">
         <v>5.097643081613452</v>
@@ -27774,7 +27777,7 @@
         <v>1</v>
       </c>
       <c r="P527" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="528" spans="1:16">
@@ -27788,7 +27791,7 @@
         <v>3.27809654539346</v>
       </c>
       <c r="D528" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E528">
         <v>5.097643081613452</v>
@@ -27824,7 +27827,7 @@
         <v>1</v>
       </c>
       <c r="P528" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="529" spans="1:16">
@@ -27838,7 +27841,7 @@
         <v>3.052272250765228</v>
       </c>
       <c r="D529" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E529">
         <v>5.097643081613452</v>
@@ -27874,7 +27877,7 @@
         <v>1</v>
       </c>
       <c r="P529" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="530" spans="1:16">
@@ -27888,7 +27891,7 @@
         <v>4.845283697294303</v>
       </c>
       <c r="D530" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E530">
         <v>3.699104005134728</v>
@@ -27924,7 +27927,7 @@
         <v>1</v>
       </c>
       <c r="P530" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="531" spans="1:16">
@@ -27938,7 +27941,7 @@
         <v>3.135431759672713</v>
       </c>
       <c r="D531" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E531">
         <v>5.149088320265843</v>
@@ -27974,7 +27977,7 @@
         <v>1</v>
       </c>
       <c r="P531" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="532" spans="1:16">
@@ -27988,7 +27991,7 @@
         <v>3.226421581251035</v>
       </c>
       <c r="D532" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E532">
         <v>5.149088320265843</v>
@@ -28024,7 +28027,7 @@
         <v>1</v>
       </c>
       <c r="P532" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="533" spans="1:16">
@@ -28038,7 +28041,7 @@
         <v>3.261965632861735</v>
       </c>
       <c r="D533" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E533">
         <v>5.149088320265843</v>
@@ -28074,7 +28077,7 @@
         <v>1</v>
       </c>
       <c r="P533" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="534" spans="1:16">
@@ -28088,7 +28091,7 @@
         <v>3.248497754763896</v>
       </c>
       <c r="D534" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E534">
         <v>5.149088320265843</v>
@@ -28124,7 +28127,7 @@
         <v>1</v>
       </c>
       <c r="P534" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="535" spans="1:16">
@@ -28138,7 +28141,7 @@
         <v>3.320379116277444</v>
       </c>
       <c r="D535" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E535">
         <v>5.149088320265843</v>
@@ -28174,7 +28177,7 @@
         <v>1</v>
       </c>
       <c r="P535" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="536" spans="1:16">
@@ -28188,7 +28191,7 @@
         <v>3.102851043292947</v>
       </c>
       <c r="D536" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E536">
         <v>5.149088320265843</v>
@@ -28224,7 +28227,7 @@
         <v>1</v>
       </c>
       <c r="P536" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="537" spans="1:16">
@@ -28238,7 +28241,7 @@
         <v>4.899978108914215</v>
       </c>
       <c r="D537" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E537">
         <v>3.755423003238402</v>
@@ -28274,7 +28277,7 @@
         <v>1</v>
       </c>
       <c r="P537" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="538" spans="1:16">
@@ -28288,7 +28291,7 @@
         <v>3.340758667101504</v>
       </c>
       <c r="D538" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E538">
         <v>5.455787317211367</v>
@@ -28324,7 +28327,7 @@
         <v>1</v>
       </c>
       <c r="P538" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="539" spans="1:16">
@@ -28338,7 +28341,7 @@
         <v>3.596337846972439</v>
       </c>
       <c r="D539" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E539">
         <v>5.455787317211367</v>
@@ -28374,7 +28377,7 @@
         <v>1</v>
       </c>
       <c r="P539" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="540" spans="1:16">
@@ -28388,7 +28391,7 @@
         <v>3.478914818069512</v>
       </c>
       <c r="D540" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E540">
         <v>5.455787317211367</v>
@@ -28424,7 +28427,7 @@
         <v>1</v>
       </c>
       <c r="P540" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="541" spans="1:16">
@@ -28438,7 +28441,7 @@
         <v>3.503154774543503</v>
       </c>
       <c r="D541" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E541">
         <v>5.455787317211367</v>
@@ -28474,7 +28477,7 @@
         <v>1</v>
       </c>
       <c r="P541" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="542" spans="1:16">
@@ -28488,7 +28491,7 @@
         <v>3.572453407661722</v>
       </c>
       <c r="D542" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E542">
         <v>5.455787317211367</v>
@@ -28524,7 +28527,7 @@
         <v>1</v>
       </c>
       <c r="P542" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="543" spans="1:16">
@@ -28538,7 +28541,7 @@
         <v>3.404384583447808</v>
       </c>
       <c r="D543" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E543">
         <v>5.455787317211367</v>
@@ -28574,7 +28577,7 @@
         <v>1</v>
       </c>
       <c r="P543" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="544" spans="1:16">
@@ -28588,7 +28591,7 @@
         <v>5.25250104043668</v>
       </c>
       <c r="D544" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E544">
         <v>5.56320240731846</v>
@@ -28624,7 +28627,7 @@
         <v>1</v>
       </c>
       <c r="P544" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="545" spans="1:16">
@@ -28638,7 +28641,7 @@
         <v>3.408744253943432</v>
       </c>
       <c r="D545" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E545">
         <v>5.557338115167074</v>
@@ -28674,7 +28677,7 @@
         <v>1</v>
       </c>
       <c r="P545" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="546" spans="1:16">
@@ -28688,7 +28691,7 @@
         <v>3.550748645676077</v>
       </c>
       <c r="D546" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E546">
         <v>5.557338115167074</v>
@@ -28724,7 +28727,7 @@
         <v>1</v>
       </c>
       <c r="P546" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="547" spans="1:16">
@@ -28738,7 +28741,7 @@
         <v>3.587474005519777</v>
       </c>
       <c r="D547" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E547">
         <v>5.557338115167074</v>
@@ -28774,7 +28777,7 @@
         <v>1</v>
       </c>
       <c r="P547" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="548" spans="1:16">
@@ -28788,7 +28791,7 @@
         <v>3.655917474023632</v>
       </c>
       <c r="D548" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E548">
         <v>5.557338115167074</v>
@@ -28824,7 +28827,7 @@
         <v>1</v>
       </c>
       <c r="P548" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="549" spans="1:16">
@@ -28838,7 +28841,7 @@
         <v>3.504225052174785</v>
       </c>
       <c r="D549" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E549">
         <v>5.557338115167074</v>
@@ -28874,7 +28877,7 @@
         <v>1</v>
       </c>
       <c r="P549" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="550" spans="1:16">
@@ -28888,7 +28891,7 @@
         <v>5.346996730323884</v>
       </c>
       <c r="D550" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E550">
         <v>5.864438002961421</v>
@@ -28924,7 +28927,7 @@
         <v>1</v>
       </c>
       <c r="P550" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="551" spans="1:16">
@@ -28938,7 +28941,7 @@
         <v>5.267444590560391</v>
       </c>
       <c r="D551" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E551">
         <v>5.864438002961421</v>
@@ -28974,7 +28977,7 @@
         <v>1</v>
       </c>
       <c r="P551" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="552" spans="1:16">
@@ -28988,7 +28991,7 @@
         <v>3.796322429340982</v>
       </c>
       <c r="D552" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E552">
         <v>5.685955718590687</v>
@@ -29024,7 +29027,7 @@
         <v>1</v>
       </c>
       <c r="P552" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="553" spans="1:16">
@@ -29038,7 +29041,7 @@
         <v>3.641728676729411</v>
       </c>
       <c r="D553" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E553">
         <v>5.685955718590687</v>
@@ -29074,7 +29077,7 @@
         <v>1</v>
       </c>
       <c r="P553" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="554" spans="1:16">
@@ -29088,7 +29091,7 @@
         <v>3.69426723244667</v>
       </c>
       <c r="D554" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E554">
         <v>5.685955718590687</v>
@@ -29124,7 +29127,7 @@
         <v>1</v>
       </c>
       <c r="P554" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="555" spans="1:16">
@@ -29138,7 +29141,7 @@
         <v>3.761627605342749</v>
       </c>
       <c r="D555" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E555">
         <v>5.685955718590687</v>
@@ -29174,7 +29177,7 @@
         <v>1</v>
       </c>
       <c r="P555" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="556" spans="1:16">
@@ -29188,7 +29191,7 @@
         <v>3.630676464382844</v>
       </c>
       <c r="D556" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E556">
         <v>5.685955718590687</v>
@@ -29224,7 +29227,7 @@
         <v>1</v>
       </c>
       <c r="P556" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="557" spans="1:16">
@@ -29238,7 +29241,7 @@
         <v>5.466678794983334</v>
       </c>
       <c r="D557" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E557">
         <v>5.209318422087254</v>
@@ -29274,7 +29277,7 @@
         <v>1</v>
       </c>
       <c r="P557" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="558" spans="1:16">
@@ -29288,7 +29291,7 @@
         <v>5.390917489847062</v>
       </c>
       <c r="D558" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E558">
         <v>5.209318422087254</v>
@@ -29324,7 +29327,7 @@
         <v>1</v>
       </c>
       <c r="P558" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="559" spans="1:16">
@@ -29338,7 +29341,7 @@
         <v>4.159051079599863</v>
       </c>
       <c r="D559" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E559">
         <v>5.343391662540899</v>
@@ -29374,7 +29377,7 @@
         <v>1</v>
       </c>
       <c r="P559" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="560" spans="1:16">
@@ -29388,7 +29391,7 @@
         <v>4.237780255555339</v>
       </c>
       <c r="D560" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E560">
         <v>5.313343652467495</v>
@@ -29424,7 +29427,7 @@
         <v>1</v>
       </c>
       <c r="P560" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="561" spans="1:16">
@@ -29438,7 +29441,7 @@
         <v>4.283295642394084</v>
       </c>
       <c r="D561" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E561">
         <v>5.313343652467495</v>
@@ -29474,7 +29477,7 @@
         <v>1</v>
       </c>
       <c r="P561" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="562" spans="1:16">
@@ -29524,7 +29527,7 @@
         <v>1</v>
       </c>
       <c r="P562" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="563" spans="1:16">
@@ -29538,7 +29541,7 @@
         <v>4.047954928502808</v>
       </c>
       <c r="D563" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E563">
         <v>5.235960539108905</v>
@@ -29574,7 +29577,7 @@
         <v>1</v>
       </c>
       <c r="P563" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="564" spans="1:16">
@@ -29588,7 +29591,7 @@
         <v>4.137221058995326</v>
       </c>
       <c r="D564" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E564">
         <v>5.202705629828571</v>
@@ -29624,7 +29627,7 @@
         <v>1</v>
       </c>
       <c r="P564" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="565" spans="1:16">
@@ -29638,7 +29641,7 @@
         <v>4.169450720548237</v>
       </c>
       <c r="D565" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E565">
         <v>5.202705629828571</v>
@@ -29674,7 +29677,7 @@
         <v>1</v>
       </c>
       <c r="P565" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="566" spans="1:16">
@@ -29688,7 +29691,7 @@
         <v>6.314817655301979</v>
       </c>
       <c r="D566" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E566">
         <v>6.624319057953503</v>
@@ -29724,7 +29727,7 @@
         <v>1</v>
       </c>
       <c r="P566" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="567" spans="1:16">
@@ -29738,7 +29741,7 @@
         <v>4.059730080999771</v>
       </c>
       <c r="D567" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E567">
         <v>5.117447902330046</v>
@@ -29788,7 +29791,7 @@
         <v>4.081721754571493</v>
       </c>
       <c r="D568" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E568">
         <v>5.117447902330046</v>
@@ -29888,7 +29891,7 @@
         <v>4.030557457706422</v>
       </c>
       <c r="D570" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E570">
         <v>5.085351371462874</v>
@@ -29924,7 +29927,7 @@
         <v>1</v>
       </c>
       <c r="P570" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="571" spans="1:16">
@@ -29938,7 +29941,7 @@
         <v>4.048694889476288</v>
       </c>
       <c r="D571" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E571">
         <v>5.085351371462874</v>
@@ -29974,7 +29977,7 @@
         <v>1</v>
       </c>
       <c r="P571" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="572" spans="1:16">
@@ -30024,7 +30027,7 @@
         <v>1</v>
       </c>
       <c r="P572" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="573" spans="1:16">
@@ -30038,7 +30041,7 @@
         <v>3.737521317704196</v>
       </c>
       <c r="D573" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E573">
         <v>4.762944866631269</v>
@@ -30074,7 +30077,7 @@
         <v>1</v>
       </c>
       <c r="P573" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="574" spans="1:16">
@@ -30088,7 +30091,7 @@
         <v>3.716943268562606</v>
       </c>
       <c r="D574" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E574">
         <v>4.762944866631269</v>
@@ -30124,7 +30127,7 @@
         <v>1</v>
       </c>
       <c r="P574" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="575" spans="1:16">
@@ -30174,7 +30177,7 @@
         <v>1</v>
       </c>
       <c r="P575" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="576" spans="1:16">
@@ -30224,7 +30227,7 @@
         <v>1</v>
       </c>
       <c r="P576" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="577" spans="1:16">
@@ -30238,7 +30241,7 @@
         <v>3.710853293730853</v>
       </c>
       <c r="D577" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E577">
         <v>4.733603965539871</v>
@@ -30274,7 +30277,7 @@
         <v>1</v>
       </c>
       <c r="P577" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="578" spans="1:16">
@@ -30288,7 +30291,7 @@
         <v>3.686751906570006</v>
       </c>
       <c r="D578" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E578">
         <v>4.733603965539871</v>
@@ -30324,7 +30327,7 @@
         <v>1</v>
       </c>
       <c r="P578" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="579" spans="1:16">
@@ -30374,7 +30377,7 @@
         <v>1</v>
       </c>
       <c r="P579" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="580" spans="1:16">
@@ -30424,7 +30427,7 @@
         <v>1</v>
       </c>
       <c r="P580" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="581" spans="1:16">
@@ -30474,7 +30477,7 @@
         <v>1</v>
       </c>
       <c r="P581" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="582" spans="1:16">
@@ -30524,7 +30527,7 @@
         <v>1</v>
       </c>
       <c r="P582" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="583" spans="1:16">
@@ -30574,7 +30577,7 @@
         <v>1</v>
       </c>
       <c r="P583" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="584" spans="1:16">
@@ -30624,7 +30627,7 @@
         <v>1</v>
       </c>
       <c r="P584" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="585" spans="1:16">
@@ -30674,7 +30677,7 @@
         <v>1</v>
       </c>
       <c r="P585" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="586" spans="1:16">
@@ -30724,7 +30727,7 @@
         <v>1</v>
       </c>
       <c r="P586" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="587" spans="1:16">
@@ -30774,7 +30777,7 @@
         <v>1</v>
       </c>
       <c r="P587" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="588" spans="1:16">
@@ -30824,7 +30827,7 @@
         <v>1</v>
       </c>
       <c r="P588" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="589" spans="1:16">
@@ -30874,7 +30877,7 @@
         <v>1</v>
       </c>
       <c r="P589" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="590" spans="1:16">
@@ -30924,7 +30927,7 @@
         <v>1</v>
       </c>
       <c r="P590" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="591" spans="1:16">
@@ -31174,7 +31177,7 @@
         <v>1</v>
       </c>
       <c r="P595" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="596" spans="1:16">
@@ -31224,7 +31227,7 @@
         <v>1</v>
       </c>
       <c r="P596" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="597" spans="1:16">
@@ -31274,7 +31277,7 @@
         <v>1</v>
       </c>
       <c r="P597" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="598" spans="1:16">
@@ -31324,7 +31327,7 @@
         <v>1</v>
       </c>
       <c r="P598" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="599" spans="1:16">
@@ -31374,7 +31377,7 @@
         <v>1</v>
       </c>
       <c r="P599" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="600" spans="1:16">
@@ -31424,7 +31427,7 @@
         <v>1</v>
       </c>
       <c r="P600" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="601" spans="1:16">
@@ -31638,7 +31641,7 @@
         <v>6.312844467716282</v>
       </c>
       <c r="D605" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E605">
         <v>7.044140001633426</v>
@@ -31724,7 +31727,7 @@
         <v>1</v>
       </c>
       <c r="P606" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="607" spans="1:16">
@@ -31774,7 +31777,7 @@
         <v>1</v>
       </c>
       <c r="P607" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="608" spans="1:16">
@@ -31824,7 +31827,7 @@
         <v>1</v>
       </c>
       <c r="P608" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="609" spans="1:16">
@@ -31874,7 +31877,7 @@
         <v>1</v>
       </c>
       <c r="P609" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="610" spans="1:16">
@@ -31924,7 +31927,7 @@
         <v>1</v>
       </c>
       <c r="P610" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="611" spans="1:16">
@@ -31974,7 +31977,7 @@
         <v>1</v>
       </c>
       <c r="P611" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="612" spans="1:16">
@@ -32024,7 +32027,7 @@
         <v>1</v>
       </c>
       <c r="P612" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="613" spans="1:16">
@@ -32074,7 +32077,7 @@
         <v>1</v>
       </c>
       <c r="P613" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="614" spans="1:16">
@@ -32124,7 +32127,7 @@
         <v>1</v>
       </c>
       <c r="P614" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="615" spans="1:16">
@@ -32174,7 +32177,7 @@
         <v>1</v>
       </c>
       <c r="P615" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="616" spans="1:16">
@@ -32224,7 +32227,7 @@
         <v>1</v>
       </c>
       <c r="P616" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="617" spans="1:16">
@@ -32274,7 +32277,7 @@
         <v>1</v>
       </c>
       <c r="P617" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="618" spans="1:16">
@@ -32324,7 +32327,7 @@
         <v>1</v>
       </c>
       <c r="P618" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="619" spans="1:16">
@@ -32374,7 +32377,7 @@
         <v>1</v>
       </c>
       <c r="P619" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="620" spans="1:16">
@@ -32424,7 +32427,7 @@
         <v>1</v>
       </c>
       <c r="P620" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="621" spans="1:16">
@@ -32474,7 +32477,7 @@
         <v>1</v>
       </c>
       <c r="P621" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="622" spans="1:16">
@@ -32488,7 +32491,7 @@
         <v>6.52789956231641</v>
       </c>
       <c r="D622" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E622">
         <v>6.970266187949232</v>
@@ -32524,7 +32527,7 @@
         <v>1</v>
       </c>
       <c r="P622" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="623" spans="1:16">
@@ -32574,7 +32577,7 @@
         <v>1</v>
       </c>
       <c r="P623" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="624" spans="1:16">
@@ -32624,7 +32627,7 @@
         <v>1</v>
       </c>
       <c r="P624" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="625" spans="1:16">
@@ -32674,7 +32677,7 @@
         <v>1</v>
       </c>
       <c r="P625" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="626" spans="1:16">
@@ -32688,7 +32691,7 @@
         <v>2.603543847706</v>
       </c>
       <c r="D626" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E626">
         <v>4.770094008155837</v>
@@ -32724,7 +32727,7 @@
         <v>1</v>
       </c>
       <c r="P626" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="627" spans="1:16">
@@ -32774,7 +32777,7 @@
         <v>1</v>
       </c>
       <c r="P627" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="628" spans="1:16">
@@ -32824,7 +32827,7 @@
         <v>1</v>
       </c>
       <c r="P628" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="629" spans="1:16">
@@ -32874,7 +32877,7 @@
         <v>1</v>
       </c>
       <c r="P629" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="630" spans="1:16">
@@ -32924,7 +32927,7 @@
         <v>1</v>
       </c>
       <c r="P630" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="631" spans="1:16">
@@ -32974,7 +32977,7 @@
         <v>1</v>
       </c>
       <c r="P631" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="632" spans="1:16">
@@ -32988,7 +32991,7 @@
         <v>2.478182256708074</v>
       </c>
       <c r="D632" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E632">
         <v>4.645810796435313</v>
@@ -33024,7 +33027,7 @@
         <v>1</v>
       </c>
       <c r="P632" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="633" spans="1:16">
@@ -33074,7 +33077,7 @@
         <v>1</v>
       </c>
       <c r="P633" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="634" spans="1:16">
@@ -33124,7 +33127,7 @@
         <v>1</v>
       </c>
       <c r="P634" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="635" spans="1:16">
@@ -33174,7 +33177,7 @@
         <v>1</v>
       </c>
       <c r="P635" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="636" spans="1:16">
@@ -33224,7 +33227,7 @@
         <v>1</v>
       </c>
       <c r="P636" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="637" spans="1:16">
@@ -33238,7 +33241,7 @@
         <v>2.30694018299906</v>
       </c>
       <c r="D637" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E637">
         <v>4.476041772822722</v>
@@ -33274,7 +33277,7 @@
         <v>1</v>
       </c>
       <c r="P637" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="638" spans="1:16">
@@ -33288,7 +33291,7 @@
         <v>5.979313720333828</v>
       </c>
       <c r="D638" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E638">
         <v>6.921637837986275</v>
@@ -33324,7 +33327,7 @@
         <v>1</v>
       </c>
       <c r="P638" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="639" spans="1:16">
@@ -33338,7 +33341,7 @@
         <v>6.118014825265853</v>
       </c>
       <c r="D639" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E639">
         <v>6.921637837986275</v>
@@ -33374,7 +33377,7 @@
         <v>1</v>
       </c>
       <c r="P639" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="640" spans="1:16">
@@ -33388,7 +33391,7 @@
         <v>2.180042495856011</v>
       </c>
       <c r="D640" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E640">
         <v>4.350235678687355</v>
@@ -33424,7 +33427,7 @@
         <v>1</v>
       </c>
       <c r="P640" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="641" spans="1:16">
@@ -33474,7 +33477,7 @@
         <v>1</v>
       </c>
       <c r="P641" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="642" spans="1:16">
@@ -33524,7 +33527,7 @@
         <v>1</v>
       </c>
       <c r="P642" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="643" spans="1:16">
@@ -33574,7 +33577,7 @@
         <v>1</v>
       </c>
       <c r="P643" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="644" spans="1:16">
@@ -33588,7 +33591,7 @@
         <v>2.005501953213372</v>
       </c>
       <c r="D644" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E644">
         <v>4.177196560067447</v>
@@ -33624,7 +33627,7 @@
         <v>1</v>
       </c>
       <c r="P644" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="645" spans="1:16">
@@ -33638,7 +33641,7 @@
         <v>6.03048720269387</v>
       </c>
       <c r="D645" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E645">
         <v>7.646218976894719</v>
@@ -33674,7 +33677,7 @@
         <v>1</v>
       </c>
       <c r="P645" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="646" spans="1:16">
@@ -33688,7 +33691,7 @@
         <v>6.160487202693869</v>
       </c>
       <c r="D646" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E646">
         <v>7.646218976894719</v>
@@ -33724,7 +33727,7 @@
         <v>1</v>
       </c>
       <c r="P646" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="647" spans="1:16">
@@ -33788,7 +33791,7 @@
         <v>5.929250610805834</v>
       </c>
       <c r="D648" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E648">
         <v>6.44678700451809</v>
@@ -33838,7 +33841,7 @@
         <v>6.059250610805833</v>
       </c>
       <c r="D649" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E649">
         <v>6.44678700451809</v>
@@ -33924,7 +33927,7 @@
         <v>1</v>
       </c>
       <c r="P650" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="651" spans="1:16">
@@ -33938,7 +33941,7 @@
         <v>6.444007644774246</v>
       </c>
       <c r="D651" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="E651">
         <v>5.9080963375586</v>
@@ -33974,7 +33977,7 @@
         <v>1</v>
       </c>
       <c r="P651" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="652" spans="1:16">
@@ -33988,7 +33991,7 @@
         <v>5.977845942063905</v>
       </c>
       <c r="D652" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="E652">
         <v>5.9080963375586</v>
@@ -34024,7 +34027,7 @@
         <v>1</v>
       </c>
       <c r="P652" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="653" spans="1:16">
@@ -34088,7 +34091,7 @@
         <v>6.325113724849238</v>
       </c>
       <c r="D654" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E654">
         <v>5.966484401224733</v>
@@ -34138,7 +34141,7 @@
         <v>6.616965483162407</v>
       </c>
       <c r="D655" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E655">
         <v>5.966484401224733</v>
@@ -34374,7 +34377,7 @@
         <v>1</v>
       </c>
       <c r="P659" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="660" spans="1:16">
@@ -34388,7 +34391,7 @@
         <v>6.182411935806901</v>
       </c>
       <c r="D660" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E660">
         <v>5.820555041914538</v>
@@ -34424,7 +34427,7 @@
         <v>1</v>
       </c>
       <c r="P660" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="661" spans="1:16">
@@ -34438,7 +34441,7 @@
         <v>6.479370608860847</v>
       </c>
       <c r="D661" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E661">
         <v>5.820555041914538</v>
@@ -34474,7 +34477,7 @@
         <v>1</v>
       </c>
       <c r="P661" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="662" spans="1:16">
@@ -34488,7 +34491,7 @@
         <v>6.247760471854665</v>
       </c>
       <c r="D662" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E662">
         <v>5.820555041914538</v>
@@ -34524,7 +34527,7 @@
         <v>1</v>
       </c>
       <c r="P662" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="663" spans="1:16">
@@ -34638,7 +34641,7 @@
         <v>6.052746661470383</v>
       </c>
       <c r="D665" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E665">
         <v>5.747828147206722</v>
@@ -34688,7 +34691,7 @@
         <v>6.354345707327784</v>
       </c>
       <c r="D666" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E666">
         <v>5.747828147206722</v>
@@ -34738,7 +34741,7 @@
         <v>6.106229101349317</v>
       </c>
       <c r="D667" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E667">
         <v>5.747828147206722</v>
@@ -34888,7 +34891,7 @@
         <v>5.992378168346487</v>
       </c>
       <c r="D670" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E670">
         <v>5.919638041522585</v>
@@ -34938,7 +34941,7 @@
         <v>6.296137640849427</v>
       </c>
       <c r="D671" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E671">
         <v>5.919638041522585</v>
@@ -34988,7 +34991,7 @@
         <v>6.0403360886604</v>
       </c>
       <c r="D672" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E672">
         <v>5.919638041522585</v>
@@ -35074,7 +35077,7 @@
         <v>1</v>
       </c>
       <c r="P673" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="674" spans="1:16">
@@ -35124,7 +35127,7 @@
         <v>1</v>
       </c>
       <c r="P674" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="675" spans="1:16">
@@ -35138,7 +35141,7 @@
         <v>5.931074248482098</v>
       </c>
       <c r="D675" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E675">
         <v>5.817063063996034</v>
@@ -35174,7 +35177,7 @@
         <v>1</v>
       </c>
       <c r="P675" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="676" spans="1:16">
@@ -35188,7 +35191,7 @@
         <v>6.237027624047666</v>
       </c>
       <c r="D676" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E676">
         <v>5.817063063996034</v>
@@ -35224,7 +35227,7 @@
         <v>1</v>
       </c>
       <c r="P676" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="677" spans="1:16">
@@ -35238,7 +35241,7 @@
         <v>5.973422045250139</v>
       </c>
       <c r="D677" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E677">
         <v>5.817063063996034</v>
@@ -35274,7 +35277,7 @@
         <v>1</v>
       </c>
       <c r="P677" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="678" spans="1:16">
@@ -35388,7 +35391,7 @@
         <v>5.839386641650073</v>
       </c>
       <c r="D680" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E680">
         <v>4.893781158276536</v>
@@ -35438,7 +35441,7 @@
         <v>6.148621271038877</v>
       </c>
       <c r="D681" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E681">
         <v>4.893781158276536</v>
@@ -35488,7 +35491,7 @@
         <v>5.873343803641564</v>
       </c>
       <c r="D682" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E682">
         <v>4.893781158276536</v>
@@ -35588,7 +35591,7 @@
         <v>6.049313264972337</v>
       </c>
       <c r="D684" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E684">
         <v>4.936335249131968</v>
@@ -35638,7 +35641,7 @@
         <v>6.175722584965069</v>
       </c>
       <c r="D685" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E685">
         <v>4.936335249131968</v>
@@ -35688,7 +35691,7 @@
         <v>5.760924613317037</v>
       </c>
       <c r="D686" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E686">
         <v>4.936335249131968</v>
@@ -35838,7 +35841,7 @@
         <v>5.905539797299475</v>
       </c>
       <c r="D689" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E689">
         <v>5.270502414665344</v>
@@ -35888,7 +35891,7 @@
         <v>6.021734035283636</v>
       </c>
       <c r="D690" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E690">
         <v>5.270502414665344</v>
@@ -36038,7 +36041,7 @@
         <v>5.810134805942958</v>
       </c>
       <c r="D693" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="E693">
         <v>4.46837075668304</v>
@@ -36088,7 +36091,7 @@
         <v>5.919550534467003</v>
       </c>
       <c r="D694" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="E694">
         <v>4.46837075668304</v>
@@ -36138,7 +36141,7 @@
         <v>5.597681787127293</v>
       </c>
       <c r="D695" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="E695">
         <v>5.175448484795162</v>
@@ -36188,7 +36191,7 @@
         <v>5.69200276245871</v>
       </c>
       <c r="D696" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="E696">
         <v>5.175448484795162</v>
@@ -36274,7 +36277,7 @@
         <v>1</v>
       </c>
       <c r="P697" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="698" spans="1:16">
@@ -36324,7 +36327,7 @@
         <v>1</v>
       </c>
       <c r="P698" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="699" spans="1:16">
@@ -36374,7 +36377,7 @@
         <v>1</v>
       </c>
       <c r="P699" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="700" spans="1:16">
@@ -36424,7 +36427,7 @@
         <v>1</v>
       </c>
       <c r="P700" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="701" spans="1:16">
@@ -36438,7 +36441,7 @@
         <v>10.58920111380781</v>
       </c>
       <c r="D701" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="E701">
         <v>10.63805069137965</v>
@@ -36474,7 +36477,7 @@
         <v>1</v>
       </c>
       <c r="P701" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="702" spans="1:16">
@@ -36524,7 +36527,7 @@
         <v>1</v>
       </c>
       <c r="P702" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="703" spans="1:16">
@@ -36538,7 +36541,7 @@
         <v>13.29070024337744</v>
       </c>
       <c r="D703" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E703">
         <v>12.1104855745369</v>
@@ -36574,7 +36577,7 @@
         <v>1</v>
       </c>
       <c r="P703" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="704" spans="1:16">
@@ -36624,7 +36627,7 @@
         <v>1</v>
       </c>
       <c r="P704" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="705" spans="1:16">
@@ -36638,7 +36641,7 @@
         <v>13.05967948318782</v>
       </c>
       <c r="D705" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E705">
         <v>11.87581437344135</v>
@@ -36674,7 +36677,7 @@
         <v>1</v>
       </c>
       <c r="P705" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="706" spans="1:16">
@@ -36724,7 +36727,7 @@
         <v>1</v>
       </c>
       <c r="P706" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="707" spans="1:16">
@@ -36738,7 +36741,7 @@
         <v>12.8170626988293</v>
       </c>
       <c r="D707" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E707">
         <v>10.97022453374666</v>
@@ -36774,7 +36777,7 @@
         <v>1</v>
       </c>
       <c r="P707" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="708" spans="1:16">
@@ -36824,7 +36827,7 @@
         <v>1</v>
       </c>
       <c r="P708" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="709" spans="1:16">
@@ -36838,7 +36841,7 @@
         <v>12.5987805539735</v>
       </c>
       <c r="D709" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E709">
         <v>10.73863851098768</v>
@@ -36874,7 +36877,7 @@
         <v>1</v>
       </c>
       <c r="P709" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="710" spans="1:16">
@@ -36924,7 +36927,7 @@
         <v>1</v>
       </c>
       <c r="P710" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="711" spans="1:16">
@@ -36974,7 +36977,7 @@
         <v>1</v>
       </c>
       <c r="P711" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="712" spans="1:16">
@@ -37024,7 +37027,7 @@
         <v>1</v>
       </c>
       <c r="P712" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="713" spans="1:16">
@@ -37038,7 +37041,7 @@
         <v>12.45336310880131</v>
       </c>
       <c r="D713" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E713">
         <v>10.58435815154991</v>
@@ -37074,7 +37077,7 @@
         <v>1</v>
       </c>
       <c r="P713" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="714" spans="1:16">
@@ -37124,7 +37127,7 @@
         <v>1</v>
       </c>
       <c r="P714" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="715" spans="1:16">
@@ -37174,7 +37177,7 @@
         <v>1</v>
       </c>
       <c r="P715" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="716" spans="1:16">
@@ -37224,7 +37227,7 @@
         <v>1</v>
       </c>
       <c r="P716" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="717" spans="1:16">
@@ -37274,7 +37277,7 @@
         <v>1</v>
       </c>
       <c r="P717" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="718" spans="1:16">
@@ -37324,7 +37327,7 @@
         <v>1</v>
       </c>
       <c r="P718" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="719" spans="1:16">
@@ -37374,7 +37377,7 @@
         <v>1</v>
       </c>
       <c r="P719" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="720" spans="1:16">
@@ -37388,7 +37391,7 @@
         <v>12.29210392935995</v>
       </c>
       <c r="D720" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E720">
         <v>10.41327053453538</v>
@@ -37424,7 +37427,7 @@
         <v>1</v>
       </c>
       <c r="P720" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="721" spans="1:16">
@@ -37438,7 +37441,7 @@
         <v>9.171282848330055</v>
       </c>
       <c r="D721" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E721">
         <v>6.850968108671186</v>
@@ -37474,7 +37477,7 @@
         <v>1</v>
       </c>
       <c r="P721" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="722" spans="1:16">
@@ -37488,7 +37491,7 @@
         <v>8.830116243154617</v>
       </c>
       <c r="D722" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E722">
         <v>6.850968108671186</v>
@@ -37524,7 +37527,7 @@
         <v>1</v>
       </c>
       <c r="P722" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="723" spans="1:16">
@@ -37688,7 +37691,7 @@
         <v>12.09795277153261</v>
       </c>
       <c r="D726" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E726">
         <v>10.20728623616326</v>
@@ -37738,7 +37741,7 @@
         <v>8.629829382822578</v>
       </c>
       <c r="D727" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E727">
         <v>7.040051561279032</v>
@@ -37824,7 +37827,7 @@
         <v>1</v>
       </c>
       <c r="P728" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="729" spans="1:16">
@@ -37874,7 +37877,7 @@
         <v>1</v>
       </c>
       <c r="P729" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="730" spans="1:16">
@@ -37924,7 +37927,7 @@
         <v>1</v>
       </c>
       <c r="P730" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="731" spans="1:16">
@@ -37938,7 +37941,7 @@
         <v>11.86477339723001</v>
       </c>
       <c r="D731" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E731">
         <v>9.95989502640656</v>
@@ -37974,7 +37977,7 @@
         <v>1</v>
       </c>
       <c r="P731" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="732" spans="1:16">
@@ -37988,7 +37991,7 @@
         <v>8.389280908654889</v>
       </c>
       <c r="D732" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="E732">
         <v>6.803093216210396</v>
@@ -38024,7 +38027,7 @@
         <v>1</v>
       </c>
       <c r="P732" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="733" spans="1:16">
@@ -38074,7 +38077,7 @@
         <v>1</v>
       </c>
       <c r="P733" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="734" spans="1:16">
@@ -38124,7 +38127,7 @@
         <v>1</v>
       </c>
       <c r="P734" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="735" spans="1:16">
@@ -38174,7 +38177,7 @@
         <v>1</v>
       </c>
       <c r="P735" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="736" spans="1:16">
@@ -38224,7 +38227,7 @@
         <v>1</v>
       </c>
       <c r="P736" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="737" spans="1:16">
@@ -38238,7 +38241,7 @@
         <v>7.721090409497048</v>
       </c>
       <c r="D737" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E737">
         <v>6.845979077114176</v>
@@ -38274,7 +38277,7 @@
         <v>1</v>
       </c>
       <c r="P737" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="738" spans="1:16">
@@ -38324,7 +38327,7 @@
         <v>1</v>
       </c>
       <c r="P738" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="739" spans="1:16">
@@ -38374,7 +38377,7 @@
         <v>1</v>
       </c>
       <c r="P739" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="740" spans="1:16">
@@ -38424,7 +38427,7 @@
         <v>1</v>
       </c>
       <c r="P740" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="741" spans="1:16">
@@ -38438,7 +38441,7 @@
         <v>7.431928747420816</v>
       </c>
       <c r="D741" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E741">
         <v>6.954602200047407</v>
@@ -38474,7 +38477,7 @@
         <v>1</v>
       </c>
       <c r="P741" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="742" spans="1:16">
@@ -38524,7 +38527,7 @@
         <v>1</v>
       </c>
       <c r="P742" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="743" spans="1:16">
@@ -38574,7 +38577,7 @@
         <v>1</v>
       </c>
       <c r="P743" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="744" spans="1:16">
@@ -38624,7 +38627,7 @@
         <v>1</v>
       </c>
       <c r="P744" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="745" spans="1:16">
@@ -38674,7 +38677,7 @@
         <v>1</v>
       </c>
       <c r="P745" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="746" spans="1:16">
@@ -38688,7 +38691,7 @@
         <v>7.15411432552343</v>
       </c>
       <c r="D746" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E746">
         <v>7.077702572180645</v>
@@ -38724,7 +38727,7 @@
         <v>1</v>
       </c>
       <c r="P746" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="747" spans="1:16">
@@ -38988,7 +38991,7 @@
         <v>6.656074286112602</v>
       </c>
       <c r="D752" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E752">
         <v>7.106777983579878</v>
@@ -39074,7 +39077,7 @@
         <v>1</v>
       </c>
       <c r="P753" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="754" spans="1:16">
@@ -39124,7 +39127,7 @@
         <v>1</v>
       </c>
       <c r="P754" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="755" spans="1:16">
@@ -39174,7 +39177,7 @@
         <v>1</v>
       </c>
       <c r="P755" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="756" spans="1:16">
@@ -39224,7 +39227,7 @@
         <v>1</v>
       </c>
       <c r="P756" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="757" spans="1:16">
@@ -39274,7 +39277,7 @@
         <v>1</v>
       </c>
       <c r="P757" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="758" spans="1:16">
@@ -39324,7 +39327,7 @@
         <v>1</v>
       </c>
       <c r="P758" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="759" spans="1:16">
@@ -39674,7 +39677,7 @@
         <v>1</v>
       </c>
       <c r="P765" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="766" spans="1:16">
@@ -39724,7 +39727,7 @@
         <v>1</v>
       </c>
       <c r="P766" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="767" spans="1:16">
@@ -39738,7 +39741,7 @@
         <v>5.189787984798581</v>
       </c>
       <c r="D767" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E767">
         <v>6.127393152460147</v>
@@ -39774,7 +39777,7 @@
         <v>1</v>
       </c>
       <c r="P767" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="768" spans="1:16">
@@ -39788,7 +39791,7 @@
         <v>5.337615079752425</v>
       </c>
       <c r="D768" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E768">
         <v>6.127393152460147</v>
@@ -39824,7 +39827,7 @@
         <v>1</v>
       </c>
       <c r="P768" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="769" spans="1:16">
@@ -39938,7 +39941,7 @@
         <v>4.573548410677798</v>
       </c>
       <c r="D771" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E771">
         <v>5.983161604764781</v>
@@ -39988,7 +39991,7 @@
         <v>4.718587091269107</v>
       </c>
       <c r="D772" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E772">
         <v>5.983161604764781</v>
@@ -40074,7 +40077,7 @@
         <v>1</v>
       </c>
       <c r="P773" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="774" spans="1:16">
@@ -40124,7 +40127,7 @@
         <v>1</v>
       </c>
       <c r="P774" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="775" spans="1:16">
@@ -40174,7 +40177,7 @@
         <v>1</v>
       </c>
       <c r="P775" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="776" spans="1:16">
@@ -40224,7 +40227,7 @@
         <v>1</v>
       </c>
       <c r="P776" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="777" spans="1:16">
@@ -40474,7 +40477,7 @@
         <v>1</v>
       </c>
       <c r="P781" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="782" spans="1:16">
@@ -40524,7 +40527,7 @@
         <v>1</v>
       </c>
       <c r="P782" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="783" spans="1:16">
@@ -40574,7 +40577,7 @@
         <v>1</v>
       </c>
       <c r="P783" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="784" spans="1:16">
@@ -40974,7 +40977,7 @@
         <v>1</v>
       </c>
       <c r="P791" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="792" spans="1:16">
@@ -41024,7 +41027,7 @@
         <v>1</v>
       </c>
       <c r="P792" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="793" spans="1:16">
@@ -41074,7 +41077,7 @@
         <v>1</v>
       </c>
       <c r="P793" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="794" spans="1:16">
@@ -41124,7 +41127,7 @@
         <v>1</v>
       </c>
       <c r="P794" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="795" spans="1:16">
@@ -41374,7 +41377,7 @@
         <v>1</v>
       </c>
       <c r="P799" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="800" spans="1:16">
@@ -41388,7 +41391,7 @@
         <v>1.03967143846625</v>
       </c>
       <c r="D800" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E800">
         <v>2.609188567947417</v>
@@ -41424,7 +41427,7 @@
         <v>1</v>
       </c>
       <c r="P800" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="801" spans="1:16">
@@ -41438,7 +41441,7 @@
         <v>0.8130094478294367</v>
       </c>
       <c r="D801" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E801">
         <v>2.609188567947417</v>
@@ -41474,7 +41477,7 @@
         <v>1</v>
       </c>
       <c r="P801" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="802" spans="1:16">
@@ -41524,7 +41527,7 @@
         <v>1</v>
       </c>
       <c r="P802" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="803" spans="1:16">
@@ -41538,7 +41541,7 @@
         <v>0.7465491084079581</v>
       </c>
       <c r="D803" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E803">
         <v>2.329329691737918</v>
@@ -41574,7 +41577,7 @@
         <v>1</v>
       </c>
       <c r="P803" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="804" spans="1:16">
@@ -41588,7 +41591,7 @@
         <v>0.5106027000769942</v>
       </c>
       <c r="D804" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E804">
         <v>2.329329691737918</v>
@@ -41624,7 +41627,7 @@
         <v>1</v>
       </c>
       <c r="P804" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="805" spans="1:16">
@@ -41638,7 +41641,7 @@
         <v>0.4893560218813207</v>
       </c>
       <c r="D805" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E805">
         <v>2.083774301434204</v>
@@ -41688,7 +41691,7 @@
         <v>0.2452632261943108</v>
       </c>
       <c r="D806" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E806">
         <v>2.083774301434204</v>
@@ -41738,7 +41741,7 @@
         <v>3.38720643044401</v>
       </c>
       <c r="D807" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E807">
         <v>1.346565161657761</v>
@@ -41788,7 +41791,7 @@
         <v>0.03330516332946587</v>
       </c>
       <c r="D808" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E808">
         <v>1.648359228337185</v>
@@ -41838,7 +41841,7 @@
         <v>-0.2252326821759354</v>
       </c>
       <c r="D809" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E809">
         <v>1.648359228337185</v>
@@ -41888,7 +41891,7 @@
         <v>2.979030594147371</v>
       </c>
       <c r="D810" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E810">
         <v>0.9008321958333205</v>
@@ -41938,7 +41941,7 @@
         <v>-0.3050434949915584</v>
       </c>
       <c r="D811" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E811">
         <v>1.325320464057839</v>
@@ -41974,7 +41977,7 @@
         <v>1</v>
       </c>
       <c r="P811" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="812" spans="1:16">
@@ -41988,7 +41991,7 @@
         <v>-0.5742982663261245</v>
       </c>
       <c r="D812" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E812">
         <v>1.325320464057839</v>
@@ -42024,7 +42027,7 @@
         <v>1</v>
       </c>
       <c r="P812" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="813" spans="1:16">
@@ -42038,7 +42041,7 @@
         <v>2.676200890003035</v>
       </c>
       <c r="D813" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E813">
         <v>0.570138484533139</v>
@@ -42074,7 +42077,7 @@
         <v>1</v>
       </c>
       <c r="P813" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="814" spans="1:16">
@@ -42088,7 +42091,7 @@
         <v>-1.542729235915701</v>
       </c>
       <c r="D814" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E814">
         <v>0.8740710626510406</v>
@@ -42138,7 +42141,7 @@
         <v>-1.06190425457612</v>
       </c>
       <c r="D815" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E815">
         <v>0.8740710626510406</v>
@@ -42188,7 +42191,7 @@
         <v>2.253181308968607</v>
       </c>
       <c r="D816" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E816">
         <v>0.1081959693489338</v>
@@ -42238,7 +42241,7 @@
         <v>-1.645106114375984</v>
       </c>
       <c r="D817" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E817">
         <v>0.7789101756240804</v>
@@ -42288,7 +42291,7 @@
         <v>-1.164732132500994</v>
       </c>
       <c r="D818" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E818">
         <v>0.7789101756240804</v>
@@ -42338,7 +42341,7 @@
         <v>1.705918320624114</v>
       </c>
       <c r="D819" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E819">
         <v>0.01078008499905536</v>
@@ -42388,7 +42391,7 @@
         <v>2.163973614874138</v>
       </c>
       <c r="D820" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E820">
         <v>0.01078008499905536</v>
@@ -42438,7 +42441,7 @@
         <v>2.083749225749141</v>
       </c>
       <c r="D821" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E821">
         <v>-0.02146380625091737</v>
@@ -42488,7 +42491,7 @@
         <v>-1.354990011712744</v>
       </c>
       <c r="D822" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E822">
         <v>1.048577566205335</v>
@@ -42538,7 +42541,7 @@
         <v>-0.8733379853326184</v>
       </c>
       <c r="D823" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E823">
         <v>1.048577566205335</v>
@@ -42588,7 +42591,7 @@
         <v>1.965361355164372</v>
       </c>
       <c r="D824" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E824">
         <v>0.2868376981059342</v>
@@ -42638,7 +42641,7 @@
         <v>2.41677081798775</v>
       </c>
       <c r="D825" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E825">
         <v>0.2868376981059342</v>
@@ -42688,7 +42691,7 @@
         <v>2.335779602159679</v>
       </c>
       <c r="D826" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E826">
         <v>0.246925539825213</v>
@@ -42738,7 +42741,7 @@
         <v>-1.093559587288276</v>
       </c>
       <c r="D827" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E827">
         <v>-1.564638644835625</v>
@@ -42788,7 +42791,7 @@
         <v>-1.266714738768137</v>
       </c>
       <c r="D828" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E828">
         <v>0.4727739583005963</v>
@@ -42824,7 +42827,7 @@
         <v>1</v>
       </c>
       <c r="P828" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="829" spans="1:16">
@@ -42838,7 +42841,7 @@
         <v>-0.7846738345336348</v>
       </c>
       <c r="D829" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E829">
         <v>0.5188966710041001</v>
@@ -42874,7 +42877,7 @@
         <v>1</v>
       </c>
       <c r="P829" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="830" spans="1:16">
@@ -42888,7 +42891,7 @@
         <v>2.044303559603822</v>
       </c>
       <c r="D830" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E830">
         <v>0.3708353146523429</v>
@@ -42924,7 +42927,7 @@
         <v>1</v>
       </c>
       <c r="P830" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="831" spans="1:16">
@@ -42938,7 +42941,7 @@
         <v>2.412466315043719</v>
       </c>
       <c r="D831" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E831">
         <v>0.3285898892453361</v>
@@ -42974,7 +42977,7 @@
         <v>1</v>
       </c>
       <c r="P831" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="832" spans="1:16">
@@ -42988,7 +42991,7 @@
         <v>-1.016717323262487</v>
       </c>
       <c r="D832" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E832">
         <v>-1.725082876878652</v>
@@ -43024,7 +43027,7 @@
         <v>1</v>
       </c>
       <c r="P832" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="833" spans="1:16">
@@ -43038,7 +43041,7 @@
         <v>-1.012419255686936</v>
       </c>
       <c r="D833" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E833">
         <v>0.7130663861460427</v>
@@ -43088,7 +43091,7 @@
         <v>2.271713176632382</v>
       </c>
       <c r="D834" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E834">
         <v>0.563841217205912</v>
@@ -43138,7 +43141,7 @@
         <v>2.633378514442889</v>
       </c>
       <c r="D835" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E835">
         <v>0.563841217205912</v>
@@ -43188,7 +43191,7 @@
         <v>-0.7953570260957719</v>
       </c>
       <c r="D836" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E836">
         <v>-0.6798364854873604</v>
@@ -43238,7 +43241,7 @@
         <v>-1.154980882524804</v>
       </c>
       <c r="D837" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E837">
         <v>0.3632888214250194</v>
@@ -43274,7 +43277,7 @@
         <v>1</v>
       </c>
       <c r="P837" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="838" spans="1:16">
@@ -43288,7 +43291,7 @@
         <v>2.144224144702488</v>
       </c>
       <c r="D838" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="E838">
         <v>0.3406232020973725</v>
@@ -43324,7 +43327,7 @@
         <v>1</v>
       </c>
       <c r="P838" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="839" spans="1:16">
@@ -43338,7 +43341,7 @@
         <v>2.509532026282422</v>
       </c>
       <c r="D839" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="E839">
         <v>0.3406232020973725</v>
@@ -43374,7 +43377,7 @@
         <v>1</v>
       </c>
       <c r="P839" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="840" spans="1:16">
@@ -43424,7 +43427,7 @@
         <v>1</v>
       </c>
       <c r="P840" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="841" spans="1:16">
@@ -43438,7 +43441,7 @@
         <v>-0.7435135480053319</v>
       </c>
       <c r="D841" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E841">
         <v>0.7484730002152737</v>
@@ -43588,7 +43591,7 @@
         <v>-0.3742444036399846</v>
       </c>
       <c r="D844" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E844">
         <v>1.094154467958163</v>
@@ -43624,7 +43627,7 @@
         <v>1</v>
       </c>
       <c r="P844" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="845" spans="1:16">
@@ -43674,7 +43677,7 @@
         <v>1</v>
       </c>
       <c r="P845" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="846" spans="1:16">
@@ -43724,7 +43727,7 @@
         <v>1</v>
       </c>
       <c r="P846" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="847" spans="1:16">
@@ -43738,7 +43741,7 @@
         <v>-0.2301600625778306</v>
       </c>
       <c r="D847" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E847">
         <v>1.229035183710177</v>
@@ -43774,7 +43777,7 @@
         <v>1</v>
       </c>
       <c r="P847" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="848" spans="1:16">
@@ -43824,7 +43827,7 @@
         <v>1</v>
       </c>
       <c r="P848" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="849" spans="1:16">
@@ -43874,7 +43877,7 @@
         <v>1</v>
       </c>
       <c r="P849" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="850" spans="1:16">
@@ -43888,7 +43891,7 @@
         <v>-0.008911774850371756</v>
       </c>
       <c r="D850" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="E850">
         <v>0.5721947646345491</v>
@@ -43924,7 +43927,7 @@
         <v>1</v>
       </c>
       <c r="P850" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="851" spans="1:16">
@@ -43938,7 +43941,7 @@
         <v>-0.1112036199752922</v>
       </c>
       <c r="D851" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E851">
         <v>1.340393087027532</v>
@@ -44088,7 +44091,7 @@
         <v>0.09903988671845454</v>
       </c>
       <c r="D854" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E854">
         <v>1.106317252320714</v>
@@ -44138,7 +44141,7 @@
         <v>-0.06944114310240224</v>
       </c>
       <c r="D855" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E855">
         <v>1.379487916699293</v>
@@ -44174,7 +44177,7 @@
         <v>1</v>
       </c>
       <c r="P855" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="856" spans="1:16">
@@ -44224,7 +44227,7 @@
         <v>1</v>
       </c>
       <c r="P856" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="857" spans="1:16">
@@ -44274,7 +44277,7 @@
         <v>1</v>
       </c>
       <c r="P857" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="858" spans="1:16">
@@ -44288,7 +44291,7 @@
         <v>0.1369388745414319</v>
       </c>
       <c r="D858" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E858">
         <v>1.371101739245933</v>
@@ -44324,7 +44327,7 @@
         <v>1</v>
       </c>
       <c r="P858" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="859" spans="1:16">
@@ -44338,7 +44341,7 @@
         <v>12.65888206048432</v>
       </c>
       <c r="D859" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="E859">
         <v>13.43349103432044</v>
@@ -44374,7 +44377,7 @@
         <v>1</v>
       </c>
       <c r="P859" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="860" spans="1:16">
@@ -44388,10 +44391,10 @@
         <v>13.67315026490144</v>
       </c>
       <c r="D860" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E860">
-        <v>13.92659718804111</v>
+        <v>13.36888206048432</v>
       </c>
       <c r="F860">
         <v>-1</v>
@@ -44400,10 +44403,10 @@
         <v>0.04792684973509856</v>
       </c>
       <c r="H860">
-        <v>0.04843340281195889</v>
+        <v>0.05049111793951568</v>
       </c>
       <c r="I860">
-        <v>-0.2534469231396663</v>
+        <v>0.3042682044171201</v>
       </c>
       <c r="J860">
         <v>0.8436871790688943</v>
@@ -44415,60 +44418,60 @@
         <v>30.8</v>
       </c>
       <c r="M860">
-        <v>20.45</v>
+        <v>22</v>
       </c>
       <c r="N860">
-        <v>31.18</v>
+        <v>31.93</v>
       </c>
       <c r="O860">
         <v>1</v>
       </c>
       <c r="P860" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="861" spans="1:16">
       <c r="A861" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B861" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C861">
-        <v>12.57849638595733</v>
+        <v>13.92659718804111</v>
       </c>
       <c r="D861" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="E861">
-        <v>13.3576727276643</v>
+        <v>13.36888206048432</v>
       </c>
       <c r="F861">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G861">
-        <v>0.04986150361404267</v>
+        <v>0.04843340281195889</v>
       </c>
       <c r="H861">
-        <v>0.0485223272723357</v>
+        <v>0.05049111793951568</v>
       </c>
       <c r="I861">
-        <v>0.7791763417069717</v>
+        <v>0.5577151275567864</v>
       </c>
       <c r="J861">
-        <v>0.8473410733655758</v>
+        <v>0.8436871790688943</v>
       </c>
       <c r="K861">
+        <v>20.45</v>
+      </c>
+      <c r="L861">
+        <v>31.18</v>
+      </c>
+      <c r="M861">
         <v>22</v>
       </c>
-      <c r="L861">
-        <v>31.22</v>
-      </c>
-      <c r="M861">
-        <v>20.75</v>
-      </c>
       <c r="N861">
-        <v>30.94</v>
+        <v>31.93</v>
       </c>
       <c r="O861">
         <v>1</v>
@@ -44479,96 +44482,96 @@
     </row>
     <row r="862" spans="1:16">
       <c r="A862" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B862" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C862">
-        <v>13.59897621067881</v>
+        <v>12.57849638595733</v>
       </c>
       <c r="D862" t="s">
         <v>267</v>
       </c>
       <c r="E862">
-        <v>13.85187504967397</v>
+        <v>13.3576727276643</v>
       </c>
       <c r="F862">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G862">
-        <v>0.0480010237893212</v>
+        <v>0.04986150361404267</v>
       </c>
       <c r="H862">
-        <v>0.04850812495032602</v>
+        <v>0.0485223272723357</v>
       </c>
       <c r="I862">
-        <v>-0.252898838995165</v>
+        <v>0.7791763417069717</v>
       </c>
       <c r="J862">
         <v>0.8473410733655758</v>
       </c>
       <c r="K862">
-        <v>20.3</v>
+        <v>22</v>
       </c>
       <c r="L862">
-        <v>30.8</v>
+        <v>31.22</v>
       </c>
       <c r="M862">
-        <v>20.45</v>
+        <v>20.75</v>
       </c>
       <c r="N862">
-        <v>31.18</v>
+        <v>30.94</v>
       </c>
       <c r="O862">
         <v>1</v>
       </c>
       <c r="P862" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="863" spans="1:16">
       <c r="A863" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B863" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C863">
-        <v>12.51871891898833</v>
+        <v>13.59897621067881</v>
       </c>
       <c r="D863" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="E863">
-        <v>13.30129170768218</v>
+        <v>13.28849638595733</v>
       </c>
       <c r="F863">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G863">
-        <v>0.04992128108101167</v>
+        <v>0.0480010237893212</v>
       </c>
       <c r="H863">
-        <v>0.04857870829231783</v>
+        <v>0.05057150361404267</v>
       </c>
       <c r="I863">
-        <v>0.7825727886938481</v>
+        <v>0.3104798247214795</v>
       </c>
       <c r="J863">
-        <v>0.8500582309550758</v>
+        <v>0.8473410733655758</v>
       </c>
       <c r="K863">
+        <v>20.3</v>
+      </c>
+      <c r="L863">
+        <v>30.8</v>
+      </c>
+      <c r="M863">
         <v>22</v>
       </c>
-      <c r="L863">
-        <v>31.22</v>
-      </c>
-      <c r="M863">
-        <v>20.75</v>
-      </c>
       <c r="N863">
-        <v>30.94</v>
+        <v>31.93</v>
       </c>
       <c r="O863">
         <v>1</v>
@@ -44579,46 +44582,46 @@
     </row>
     <row r="864" spans="1:16">
       <c r="A864" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B864" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C864">
-        <v>13.54381791161196</v>
+        <v>13.85187504967397</v>
       </c>
       <c r="D864" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E864">
-        <v>13.7963091769687</v>
+        <v>13.28849638595733</v>
       </c>
       <c r="F864">
         <v>-1</v>
       </c>
       <c r="G864">
-        <v>0.04805618208838804</v>
+        <v>0.04850812495032602</v>
       </c>
       <c r="H864">
-        <v>0.0485636908230313</v>
+        <v>0.05057150361404267</v>
       </c>
       <c r="I864">
-        <v>-0.2524912653567384</v>
+        <v>0.5633786637166445</v>
       </c>
       <c r="J864">
-        <v>0.8500582309550758</v>
+        <v>0.8473410733655758</v>
       </c>
       <c r="K864">
-        <v>20.3</v>
+        <v>20.45</v>
       </c>
       <c r="L864">
-        <v>30.8</v>
+        <v>31.18</v>
       </c>
       <c r="M864">
-        <v>20.45</v>
+        <v>22</v>
       </c>
       <c r="N864">
-        <v>31.18</v>
+        <v>31.93</v>
       </c>
       <c r="O864">
         <v>1</v>
@@ -44632,81 +44635,81 @@
         <v>0</v>
       </c>
       <c r="B865" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C865">
-        <v>13.51182023914395</v>
+        <v>12.51871891898833</v>
       </c>
       <c r="D865" t="s">
         <v>267</v>
       </c>
       <c r="E865">
-        <v>13.76407506849723</v>
+        <v>13.30129170768218</v>
       </c>
       <c r="F865">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G865">
-        <v>0.04808817976085605</v>
+        <v>0.04992128108101167</v>
       </c>
       <c r="H865">
-        <v>0.04859592493150276</v>
+        <v>0.04857870829231783</v>
       </c>
       <c r="I865">
-        <v>-0.25225482935328</v>
+        <v>0.7825727886938481</v>
       </c>
       <c r="J865">
-        <v>0.8516344709781304</v>
+        <v>0.8500582309550758</v>
       </c>
       <c r="K865">
-        <v>20.3</v>
+        <v>22</v>
       </c>
       <c r="L865">
-        <v>30.8</v>
+        <v>31.22</v>
       </c>
       <c r="M865">
-        <v>20.45</v>
+        <v>20.75</v>
       </c>
       <c r="N865">
-        <v>31.18</v>
+        <v>30.94</v>
       </c>
       <c r="O865">
         <v>1</v>
       </c>
       <c r="P865" t="s">
-        <v>154</v>
+        <v>351</v>
       </c>
     </row>
     <row r="866" spans="1:16">
       <c r="A866" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B866" t="s">
         <v>155</v>
       </c>
       <c r="C866">
-        <v>13.43501557200262</v>
+        <v>13.54381791161196</v>
       </c>
       <c r="D866" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E866">
-        <v>13.6867028791849</v>
+        <v>13.22871891898833</v>
       </c>
       <c r="F866">
         <v>-1</v>
       </c>
       <c r="G866">
-        <v>0.04816498442799738</v>
+        <v>0.04805618208838804</v>
       </c>
       <c r="H866">
-        <v>0.0486732971208151</v>
+        <v>0.05063128108101166</v>
       </c>
       <c r="I866">
-        <v>-0.2516873071822836</v>
+        <v>0.3150989926236285</v>
       </c>
       <c r="J866">
-        <v>0.8554179521180978</v>
+        <v>0.8500582309550758</v>
       </c>
       <c r="K866">
         <v>20.3</v>
@@ -44715,16 +44718,266 @@
         <v>30.8</v>
       </c>
       <c r="M866">
-        <v>20.45</v>
+        <v>22</v>
       </c>
       <c r="N866">
-        <v>31.18</v>
+        <v>31.93</v>
       </c>
       <c r="O866">
         <v>1</v>
       </c>
       <c r="P866" t="s">
         <v>351</v>
+      </c>
+    </row>
+    <row r="867" spans="1:16">
+      <c r="A867" s="1">
+        <v>2</v>
+      </c>
+      <c r="B867" t="s">
+        <v>156</v>
+      </c>
+      <c r="C867">
+        <v>13.7963091769687</v>
+      </c>
+      <c r="D867" t="s">
+        <v>268</v>
+      </c>
+      <c r="E867">
+        <v>13.22871891898833</v>
+      </c>
+      <c r="F867">
+        <v>-1</v>
+      </c>
+      <c r="G867">
+        <v>0.0485636908230313</v>
+      </c>
+      <c r="H867">
+        <v>0.05063128108101166</v>
+      </c>
+      <c r="I867">
+        <v>0.5675902579803669</v>
+      </c>
+      <c r="J867">
+        <v>0.8500582309550758</v>
+      </c>
+      <c r="K867">
+        <v>20.45</v>
+      </c>
+      <c r="L867">
+        <v>31.18</v>
+      </c>
+      <c r="M867">
+        <v>22</v>
+      </c>
+      <c r="N867">
+        <v>31.93</v>
+      </c>
+      <c r="O867">
+        <v>1</v>
+      </c>
+      <c r="P867" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="868" spans="1:16">
+      <c r="A868" s="1">
+        <v>0</v>
+      </c>
+      <c r="B868" t="s">
+        <v>155</v>
+      </c>
+      <c r="C868">
+        <v>13.51182023914395</v>
+      </c>
+      <c r="D868" t="s">
+        <v>268</v>
+      </c>
+      <c r="E868">
+        <v>13.19404163848113</v>
+      </c>
+      <c r="F868">
+        <v>-1</v>
+      </c>
+      <c r="G868">
+        <v>0.04808817976085605</v>
+      </c>
+      <c r="H868">
+        <v>0.05066595836151887</v>
+      </c>
+      <c r="I868">
+        <v>0.3177786006628232</v>
+      </c>
+      <c r="J868">
+        <v>0.8516344709781304</v>
+      </c>
+      <c r="K868">
+        <v>20.3</v>
+      </c>
+      <c r="L868">
+        <v>30.8</v>
+      </c>
+      <c r="M868">
+        <v>22</v>
+      </c>
+      <c r="N868">
+        <v>31.93</v>
+      </c>
+      <c r="O868">
+        <v>1</v>
+      </c>
+      <c r="P868" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="869" spans="1:16">
+      <c r="A869" s="1">
+        <v>1</v>
+      </c>
+      <c r="B869" t="s">
+        <v>156</v>
+      </c>
+      <c r="C869">
+        <v>13.76407506849723</v>
+      </c>
+      <c r="D869" t="s">
+        <v>268</v>
+      </c>
+      <c r="E869">
+        <v>13.19404163848113</v>
+      </c>
+      <c r="F869">
+        <v>-1</v>
+      </c>
+      <c r="G869">
+        <v>0.04859592493150276</v>
+      </c>
+      <c r="H869">
+        <v>0.05066595836151887</v>
+      </c>
+      <c r="I869">
+        <v>0.5700334300161032</v>
+      </c>
+      <c r="J869">
+        <v>0.8516344709781304</v>
+      </c>
+      <c r="K869">
+        <v>20.45</v>
+      </c>
+      <c r="L869">
+        <v>31.18</v>
+      </c>
+      <c r="M869">
+        <v>22</v>
+      </c>
+      <c r="N869">
+        <v>31.93</v>
+      </c>
+      <c r="O869">
+        <v>1</v>
+      </c>
+      <c r="P869" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="870" spans="1:16">
+      <c r="A870" s="1">
+        <v>0</v>
+      </c>
+      <c r="B870" t="s">
+        <v>155</v>
+      </c>
+      <c r="C870">
+        <v>13.43501557200262</v>
+      </c>
+      <c r="D870" t="s">
+        <v>268</v>
+      </c>
+      <c r="E870">
+        <v>13.11080505340185</v>
+      </c>
+      <c r="F870">
+        <v>-1</v>
+      </c>
+      <c r="G870">
+        <v>0.04816498442799738</v>
+      </c>
+      <c r="H870">
+        <v>0.05074919494659815</v>
+      </c>
+      <c r="I870">
+        <v>0.3242105186007684</v>
+      </c>
+      <c r="J870">
+        <v>0.8554179521180978</v>
+      </c>
+      <c r="K870">
+        <v>20.3</v>
+      </c>
+      <c r="L870">
+        <v>30.8</v>
+      </c>
+      <c r="M870">
+        <v>22</v>
+      </c>
+      <c r="N870">
+        <v>31.93</v>
+      </c>
+      <c r="O870">
+        <v>1</v>
+      </c>
+      <c r="P870" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="871" spans="1:16">
+      <c r="A871" s="1">
+        <v>1</v>
+      </c>
+      <c r="B871" t="s">
+        <v>156</v>
+      </c>
+      <c r="C871">
+        <v>13.6867028791849</v>
+      </c>
+      <c r="D871" t="s">
+        <v>268</v>
+      </c>
+      <c r="E871">
+        <v>13.11080505340185</v>
+      </c>
+      <c r="F871">
+        <v>-1</v>
+      </c>
+      <c r="G871">
+        <v>0.0486732971208151</v>
+      </c>
+      <c r="H871">
+        <v>0.05074919494659815</v>
+      </c>
+      <c r="I871">
+        <v>0.575897825783052</v>
+      </c>
+      <c r="J871">
+        <v>0.8554179521180978</v>
+      </c>
+      <c r="K871">
+        <v>20.45</v>
+      </c>
+      <c r="L871">
+        <v>31.18</v>
+      </c>
+      <c r="M871">
+        <v>22</v>
+      </c>
+      <c r="N871">
+        <v>31.93</v>
+      </c>
+      <c r="O871">
+        <v>1</v>
+      </c>
+      <c r="P871" t="s">
+        <v>352</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-00763-000063.xlsx
+++ b/s60_signal/position-00763-000063.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2625" uniqueCount="353">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2622" uniqueCount="354">
   <si>
     <t>trade_time</t>
   </si>
@@ -481,10 +481,10 @@
     <t>2021-11-26</t>
   </si>
   <si>
-    <t>2021-12-06</t>
+    <t>2021-12-08</t>
   </si>
   <si>
-    <t>2021-12-08</t>
+    <t>2021-12-10</t>
   </si>
   <si>
     <t>2017-03-17</t>
@@ -818,6 +818,9 @@
   </si>
   <si>
     <t>2021-12-03</t>
+  </si>
+  <si>
+    <t>2021-12-13</t>
   </si>
   <si>
     <t>2021-12-09</t>
@@ -1430,7 +1433,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P871"/>
+  <dimension ref="A1:P870"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -1527,7 +1530,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -1577,7 +1580,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -1627,7 +1630,7 @@
         <v>1</v>
       </c>
       <c r="P4" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -1677,7 +1680,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -1727,7 +1730,7 @@
         <v>1</v>
       </c>
       <c r="P6" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -1777,7 +1780,7 @@
         <v>1</v>
       </c>
       <c r="P7" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -1827,7 +1830,7 @@
         <v>1</v>
       </c>
       <c r="P8" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -1877,7 +1880,7 @@
         <v>1</v>
       </c>
       <c r="P9" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -1927,7 +1930,7 @@
         <v>1</v>
       </c>
       <c r="P10" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -1977,7 +1980,7 @@
         <v>1</v>
       </c>
       <c r="P11" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -2027,7 +2030,7 @@
         <v>1</v>
       </c>
       <c r="P12" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -2077,7 +2080,7 @@
         <v>1</v>
       </c>
       <c r="P13" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -2127,7 +2130,7 @@
         <v>1</v>
       </c>
       <c r="P14" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -2177,7 +2180,7 @@
         <v>1</v>
       </c>
       <c r="P15" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -2227,7 +2230,7 @@
         <v>1</v>
       </c>
       <c r="P16" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -2277,7 +2280,7 @@
         <v>1</v>
       </c>
       <c r="P17" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -2327,7 +2330,7 @@
         <v>1</v>
       </c>
       <c r="P18" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -2377,7 +2380,7 @@
         <v>1</v>
       </c>
       <c r="P19" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="20" spans="1:16">
@@ -2427,7 +2430,7 @@
         <v>1</v>
       </c>
       <c r="P20" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -2477,7 +2480,7 @@
         <v>1</v>
       </c>
       <c r="P21" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -2527,7 +2530,7 @@
         <v>1</v>
       </c>
       <c r="P22" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="23" spans="1:16">
@@ -2627,7 +2630,7 @@
         <v>1</v>
       </c>
       <c r="P24" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="25" spans="1:16">
@@ -2677,7 +2680,7 @@
         <v>1</v>
       </c>
       <c r="P25" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="26" spans="1:16">
@@ -2727,7 +2730,7 @@
         <v>1</v>
       </c>
       <c r="P26" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="27" spans="1:16">
@@ -2777,7 +2780,7 @@
         <v>1</v>
       </c>
       <c r="P27" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="28" spans="1:16">
@@ -2827,7 +2830,7 @@
         <v>1</v>
       </c>
       <c r="P28" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -2877,7 +2880,7 @@
         <v>1</v>
       </c>
       <c r="P29" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -3177,7 +3180,7 @@
         <v>1</v>
       </c>
       <c r="P35" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -3227,7 +3230,7 @@
         <v>1</v>
       </c>
       <c r="P36" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="37" spans="1:16">
@@ -3277,7 +3280,7 @@
         <v>1</v>
       </c>
       <c r="P37" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="38" spans="1:16">
@@ -3327,7 +3330,7 @@
         <v>1</v>
       </c>
       <c r="P38" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="39" spans="1:16">
@@ -3377,7 +3380,7 @@
         <v>1</v>
       </c>
       <c r="P39" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="40" spans="1:16">
@@ -3427,7 +3430,7 @@
         <v>1</v>
       </c>
       <c r="P40" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="41" spans="1:16">
@@ -3477,7 +3480,7 @@
         <v>1</v>
       </c>
       <c r="P41" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="42" spans="1:16">
@@ -3527,7 +3530,7 @@
         <v>1</v>
       </c>
       <c r="P42" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="43" spans="1:16">
@@ -3577,7 +3580,7 @@
         <v>1</v>
       </c>
       <c r="P43" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="44" spans="1:16">
@@ -3627,7 +3630,7 @@
         <v>1</v>
       </c>
       <c r="P44" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -3877,7 +3880,7 @@
         <v>1</v>
       </c>
       <c r="P49" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="50" spans="1:16">
@@ -3927,7 +3930,7 @@
         <v>1</v>
       </c>
       <c r="P50" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="51" spans="1:16">
@@ -3977,7 +3980,7 @@
         <v>1</v>
       </c>
       <c r="P51" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="52" spans="1:16">
@@ -4027,7 +4030,7 @@
         <v>1</v>
       </c>
       <c r="P52" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="53" spans="1:16">
@@ -4077,7 +4080,7 @@
         <v>1</v>
       </c>
       <c r="P53" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="54" spans="1:16">
@@ -4127,7 +4130,7 @@
         <v>1</v>
       </c>
       <c r="P54" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="55" spans="1:16">
@@ -4177,7 +4180,7 @@
         <v>1</v>
       </c>
       <c r="P55" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="56" spans="1:16">
@@ -4527,7 +4530,7 @@
         <v>1</v>
       </c>
       <c r="P62" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="63" spans="1:16">
@@ -4577,7 +4580,7 @@
         <v>1</v>
       </c>
       <c r="P63" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="64" spans="1:16">
@@ -4627,7 +4630,7 @@
         <v>1</v>
       </c>
       <c r="P64" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="65" spans="1:16">
@@ -4677,7 +4680,7 @@
         <v>1</v>
       </c>
       <c r="P65" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="66" spans="1:16">
@@ -4727,7 +4730,7 @@
         <v>1</v>
       </c>
       <c r="P66" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="67" spans="1:16">
@@ -4777,7 +4780,7 @@
         <v>1</v>
       </c>
       <c r="P67" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="68" spans="1:16">
@@ -4827,7 +4830,7 @@
         <v>1</v>
       </c>
       <c r="P68" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="69" spans="1:16">
@@ -4877,7 +4880,7 @@
         <v>1</v>
       </c>
       <c r="P69" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="70" spans="1:16">
@@ -4927,7 +4930,7 @@
         <v>1</v>
       </c>
       <c r="P70" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="71" spans="1:16">
@@ -4977,7 +4980,7 @@
         <v>1</v>
       </c>
       <c r="P71" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="72" spans="1:16">
@@ -5027,7 +5030,7 @@
         <v>1</v>
       </c>
       <c r="P72" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="73" spans="1:16">
@@ -5077,7 +5080,7 @@
         <v>1</v>
       </c>
       <c r="P73" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="74" spans="1:16">
@@ -5727,7 +5730,7 @@
         <v>1</v>
       </c>
       <c r="P86" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="87" spans="1:16">
@@ -5777,7 +5780,7 @@
         <v>1</v>
       </c>
       <c r="P87" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="88" spans="1:16">
@@ -5827,7 +5830,7 @@
         <v>1</v>
       </c>
       <c r="P88" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="89" spans="1:16">
@@ -5877,7 +5880,7 @@
         <v>1</v>
       </c>
       <c r="P89" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="90" spans="1:16">
@@ -5927,7 +5930,7 @@
         <v>1</v>
       </c>
       <c r="P90" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="91" spans="1:16">
@@ -5977,7 +5980,7 @@
         <v>1</v>
       </c>
       <c r="P91" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="92" spans="1:16">
@@ -6177,7 +6180,7 @@
         <v>1</v>
       </c>
       <c r="P95" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="96" spans="1:16">
@@ -6227,7 +6230,7 @@
         <v>1</v>
       </c>
       <c r="P96" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="97" spans="1:16">
@@ -6277,7 +6280,7 @@
         <v>1</v>
       </c>
       <c r="P97" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="98" spans="1:16">
@@ -6327,7 +6330,7 @@
         <v>1</v>
       </c>
       <c r="P98" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="99" spans="1:16">
@@ -6377,7 +6380,7 @@
         <v>1</v>
       </c>
       <c r="P99" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="100" spans="1:16">
@@ -6427,7 +6430,7 @@
         <v>1</v>
       </c>
       <c r="P100" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="101" spans="1:16">
@@ -6477,7 +6480,7 @@
         <v>1</v>
       </c>
       <c r="P101" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="102" spans="1:16">
@@ -6527,7 +6530,7 @@
         <v>1</v>
       </c>
       <c r="P102" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="103" spans="1:16">
@@ -6627,7 +6630,7 @@
         <v>1</v>
       </c>
       <c r="P104" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="105" spans="1:16">
@@ -6677,7 +6680,7 @@
         <v>1</v>
       </c>
       <c r="P105" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="106" spans="1:16">
@@ -6727,7 +6730,7 @@
         <v>1</v>
       </c>
       <c r="P106" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="107" spans="1:16">
@@ -6777,7 +6780,7 @@
         <v>1</v>
       </c>
       <c r="P107" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="108" spans="1:16">
@@ -6827,7 +6830,7 @@
         <v>1</v>
       </c>
       <c r="P108" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="109" spans="1:16">
@@ -6877,7 +6880,7 @@
         <v>1</v>
       </c>
       <c r="P109" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="110" spans="1:16">
@@ -6927,7 +6930,7 @@
         <v>1</v>
       </c>
       <c r="P110" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="111" spans="1:16">
@@ -6977,7 +6980,7 @@
         <v>1</v>
       </c>
       <c r="P111" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="112" spans="1:16">
@@ -7027,7 +7030,7 @@
         <v>1</v>
       </c>
       <c r="P112" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="113" spans="1:16">
@@ -7077,7 +7080,7 @@
         <v>1</v>
       </c>
       <c r="P113" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="114" spans="1:16">
@@ -7127,7 +7130,7 @@
         <v>1</v>
       </c>
       <c r="P114" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="115" spans="1:16">
@@ -7177,7 +7180,7 @@
         <v>1</v>
       </c>
       <c r="P115" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="116" spans="1:16">
@@ -7227,7 +7230,7 @@
         <v>1</v>
       </c>
       <c r="P116" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="117" spans="1:16">
@@ -7277,7 +7280,7 @@
         <v>1</v>
       </c>
       <c r="P117" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="118" spans="1:16">
@@ -7327,7 +7330,7 @@
         <v>1</v>
       </c>
       <c r="P118" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="119" spans="1:16">
@@ -7377,7 +7380,7 @@
         <v>1</v>
       </c>
       <c r="P119" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="120" spans="1:16">
@@ -8877,7 +8880,7 @@
         <v>1</v>
       </c>
       <c r="P149" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="150" spans="1:16">
@@ -8927,7 +8930,7 @@
         <v>1</v>
       </c>
       <c r="P150" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="151" spans="1:16">
@@ -8977,7 +8980,7 @@
         <v>1</v>
       </c>
       <c r="P151" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="152" spans="1:16">
@@ -9027,7 +9030,7 @@
         <v>1</v>
       </c>
       <c r="P152" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="153" spans="1:16">
@@ -9077,7 +9080,7 @@
         <v>1</v>
       </c>
       <c r="P153" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="154" spans="1:16">
@@ -9127,7 +9130,7 @@
         <v>1</v>
       </c>
       <c r="P154" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="155" spans="1:16">
@@ -9177,7 +9180,7 @@
         <v>1</v>
       </c>
       <c r="P155" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="156" spans="1:16">
@@ -9227,7 +9230,7 @@
         <v>1</v>
       </c>
       <c r="P156" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="157" spans="1:16">
@@ -9277,7 +9280,7 @@
         <v>1</v>
       </c>
       <c r="P157" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="158" spans="1:16">
@@ -9427,7 +9430,7 @@
         <v>1</v>
       </c>
       <c r="P160" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="161" spans="1:16">
@@ -9477,7 +9480,7 @@
         <v>1</v>
       </c>
       <c r="P161" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="162" spans="1:16">
@@ -9527,7 +9530,7 @@
         <v>1</v>
       </c>
       <c r="P162" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="163" spans="1:16">
@@ -9577,7 +9580,7 @@
         <v>1</v>
       </c>
       <c r="P163" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="164" spans="1:16">
@@ -9727,7 +9730,7 @@
         <v>1</v>
       </c>
       <c r="P166" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="167" spans="1:16">
@@ -9777,7 +9780,7 @@
         <v>1</v>
       </c>
       <c r="P167" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="168" spans="1:16">
@@ -9827,7 +9830,7 @@
         <v>1</v>
       </c>
       <c r="P168" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="169" spans="1:16">
@@ -9877,7 +9880,7 @@
         <v>1</v>
       </c>
       <c r="P169" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="170" spans="1:16">
@@ -10327,7 +10330,7 @@
         <v>1</v>
       </c>
       <c r="P178" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="179" spans="1:16">
@@ -17927,7 +17930,7 @@
         <v>1</v>
       </c>
       <c r="P330" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="331" spans="1:16">
@@ -17977,7 +17980,7 @@
         <v>1</v>
       </c>
       <c r="P331" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="332" spans="1:16">
@@ -18027,7 +18030,7 @@
         <v>1</v>
       </c>
       <c r="P332" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="333" spans="1:16">
@@ -18077,7 +18080,7 @@
         <v>1</v>
       </c>
       <c r="P333" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="334" spans="1:16">
@@ -18127,7 +18130,7 @@
         <v>1</v>
       </c>
       <c r="P334" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="335" spans="1:16">
@@ -20927,7 +20930,7 @@
         <v>1</v>
       </c>
       <c r="P390" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="391" spans="1:16">
@@ -20977,7 +20980,7 @@
         <v>1</v>
       </c>
       <c r="P391" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="392" spans="1:16">
@@ -21027,7 +21030,7 @@
         <v>1</v>
       </c>
       <c r="P392" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="393" spans="1:16">
@@ -21077,7 +21080,7 @@
         <v>1</v>
       </c>
       <c r="P393" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="394" spans="1:16">
@@ -21127,7 +21130,7 @@
         <v>1</v>
       </c>
       <c r="P394" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="395" spans="1:16">
@@ -21177,7 +21180,7 @@
         <v>1</v>
       </c>
       <c r="P395" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="396" spans="1:16">
@@ -21227,7 +21230,7 @@
         <v>1</v>
       </c>
       <c r="P396" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="397" spans="1:16">
@@ -21277,7 +21280,7 @@
         <v>1</v>
       </c>
       <c r="P397" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="398" spans="1:16">
@@ -21327,7 +21330,7 @@
         <v>1</v>
       </c>
       <c r="P398" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="399" spans="1:16">
@@ -21377,7 +21380,7 @@
         <v>1</v>
       </c>
       <c r="P399" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="400" spans="1:16">
@@ -21427,7 +21430,7 @@
         <v>1</v>
       </c>
       <c r="P400" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="401" spans="1:16">
@@ -21477,7 +21480,7 @@
         <v>1</v>
       </c>
       <c r="P401" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="402" spans="1:16">
@@ -21527,7 +21530,7 @@
         <v>1</v>
       </c>
       <c r="P402" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="403" spans="1:16">
@@ -21577,7 +21580,7 @@
         <v>1</v>
       </c>
       <c r="P403" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="404" spans="1:16">
@@ -21627,7 +21630,7 @@
         <v>1</v>
       </c>
       <c r="P404" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="405" spans="1:16">
@@ -21677,7 +21680,7 @@
         <v>1</v>
       </c>
       <c r="P405" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="406" spans="1:16">
@@ -21727,7 +21730,7 @@
         <v>1</v>
       </c>
       <c r="P406" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="407" spans="1:16">
@@ -21777,7 +21780,7 @@
         <v>1</v>
       </c>
       <c r="P407" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="408" spans="1:16">
@@ -22427,7 +22430,7 @@
         <v>1</v>
       </c>
       <c r="P420" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="421" spans="1:16">
@@ -22477,7 +22480,7 @@
         <v>1</v>
       </c>
       <c r="P421" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="422" spans="1:16">
@@ -22527,7 +22530,7 @@
         <v>1</v>
       </c>
       <c r="P422" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="423" spans="1:16">
@@ -22577,7 +22580,7 @@
         <v>1</v>
       </c>
       <c r="P423" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="424" spans="1:16">
@@ -22627,7 +22630,7 @@
         <v>1</v>
       </c>
       <c r="P424" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="425" spans="1:16">
@@ -22677,7 +22680,7 @@
         <v>1</v>
       </c>
       <c r="P425" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="426" spans="1:16">
@@ -23677,7 +23680,7 @@
         <v>1</v>
       </c>
       <c r="P445" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="446" spans="1:16">
@@ -23727,7 +23730,7 @@
         <v>1</v>
       </c>
       <c r="P446" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="447" spans="1:16">
@@ -23777,7 +23780,7 @@
         <v>1</v>
       </c>
       <c r="P447" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="448" spans="1:16">
@@ -23827,7 +23830,7 @@
         <v>1</v>
       </c>
       <c r="P448" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="449" spans="1:16">
@@ -23877,7 +23880,7 @@
         <v>1</v>
       </c>
       <c r="P449" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="450" spans="1:16">
@@ -23927,7 +23930,7 @@
         <v>1</v>
       </c>
       <c r="P450" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="451" spans="1:16">
@@ -23977,7 +23980,7 @@
         <v>1</v>
       </c>
       <c r="P451" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="452" spans="1:16">
@@ -24027,7 +24030,7 @@
         <v>1</v>
       </c>
       <c r="P452" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="453" spans="1:16">
@@ -24077,7 +24080,7 @@
         <v>1</v>
       </c>
       <c r="P453" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="454" spans="1:16">
@@ -24127,7 +24130,7 @@
         <v>1</v>
       </c>
       <c r="P454" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="455" spans="1:16">
@@ -27327,7 +27330,7 @@
         <v>1</v>
       </c>
       <c r="P518" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="519" spans="1:16">
@@ -27377,7 +27380,7 @@
         <v>1</v>
       </c>
       <c r="P519" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="520" spans="1:16">
@@ -27427,7 +27430,7 @@
         <v>1</v>
       </c>
       <c r="P520" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="521" spans="1:16">
@@ -27477,7 +27480,7 @@
         <v>1</v>
       </c>
       <c r="P521" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="522" spans="1:16">
@@ -27527,7 +27530,7 @@
         <v>1</v>
       </c>
       <c r="P522" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="523" spans="1:16">
@@ -27577,7 +27580,7 @@
         <v>1</v>
       </c>
       <c r="P523" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="524" spans="1:16">
@@ -27627,7 +27630,7 @@
         <v>1</v>
       </c>
       <c r="P524" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="525" spans="1:16">
@@ -27677,7 +27680,7 @@
         <v>1</v>
       </c>
       <c r="P525" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="526" spans="1:16">
@@ -27727,7 +27730,7 @@
         <v>1</v>
       </c>
       <c r="P526" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="527" spans="1:16">
@@ -27777,7 +27780,7 @@
         <v>1</v>
       </c>
       <c r="P527" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="528" spans="1:16">
@@ -27827,7 +27830,7 @@
         <v>1</v>
       </c>
       <c r="P528" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="529" spans="1:16">
@@ -27877,7 +27880,7 @@
         <v>1</v>
       </c>
       <c r="P529" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="530" spans="1:16">
@@ -27927,7 +27930,7 @@
         <v>1</v>
       </c>
       <c r="P530" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="531" spans="1:16">
@@ -27977,7 +27980,7 @@
         <v>1</v>
       </c>
       <c r="P531" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="532" spans="1:16">
@@ -28027,7 +28030,7 @@
         <v>1</v>
       </c>
       <c r="P532" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="533" spans="1:16">
@@ -28077,7 +28080,7 @@
         <v>1</v>
       </c>
       <c r="P533" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="534" spans="1:16">
@@ -28127,7 +28130,7 @@
         <v>1</v>
       </c>
       <c r="P534" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="535" spans="1:16">
@@ -28177,7 +28180,7 @@
         <v>1</v>
       </c>
       <c r="P535" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="536" spans="1:16">
@@ -28227,7 +28230,7 @@
         <v>1</v>
       </c>
       <c r="P536" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="537" spans="1:16">
@@ -28277,7 +28280,7 @@
         <v>1</v>
       </c>
       <c r="P537" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="538" spans="1:16">
@@ -28327,7 +28330,7 @@
         <v>1</v>
       </c>
       <c r="P538" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="539" spans="1:16">
@@ -28377,7 +28380,7 @@
         <v>1</v>
       </c>
       <c r="P539" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="540" spans="1:16">
@@ -28427,7 +28430,7 @@
         <v>1</v>
       </c>
       <c r="P540" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="541" spans="1:16">
@@ -28477,7 +28480,7 @@
         <v>1</v>
       </c>
       <c r="P541" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="542" spans="1:16">
@@ -28527,7 +28530,7 @@
         <v>1</v>
       </c>
       <c r="P542" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="543" spans="1:16">
@@ -28577,7 +28580,7 @@
         <v>1</v>
       </c>
       <c r="P543" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="544" spans="1:16">
@@ -28627,7 +28630,7 @@
         <v>1</v>
       </c>
       <c r="P544" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="545" spans="1:16">
@@ -28677,7 +28680,7 @@
         <v>1</v>
       </c>
       <c r="P545" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="546" spans="1:16">
@@ -28727,7 +28730,7 @@
         <v>1</v>
       </c>
       <c r="P546" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="547" spans="1:16">
@@ -28777,7 +28780,7 @@
         <v>1</v>
       </c>
       <c r="P547" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="548" spans="1:16">
@@ -28827,7 +28830,7 @@
         <v>1</v>
       </c>
       <c r="P548" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="549" spans="1:16">
@@ -28877,7 +28880,7 @@
         <v>1</v>
       </c>
       <c r="P549" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="550" spans="1:16">
@@ -28927,7 +28930,7 @@
         <v>1</v>
       </c>
       <c r="P550" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="551" spans="1:16">
@@ -28977,7 +28980,7 @@
         <v>1</v>
       </c>
       <c r="P551" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="552" spans="1:16">
@@ -29027,7 +29030,7 @@
         <v>1</v>
       </c>
       <c r="P552" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="553" spans="1:16">
@@ -29077,7 +29080,7 @@
         <v>1</v>
       </c>
       <c r="P553" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="554" spans="1:16">
@@ -29127,7 +29130,7 @@
         <v>1</v>
       </c>
       <c r="P554" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="555" spans="1:16">
@@ -29177,7 +29180,7 @@
         <v>1</v>
       </c>
       <c r="P555" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="556" spans="1:16">
@@ -29227,7 +29230,7 @@
         <v>1</v>
       </c>
       <c r="P556" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="557" spans="1:16">
@@ -29277,7 +29280,7 @@
         <v>1</v>
       </c>
       <c r="P557" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="558" spans="1:16">
@@ -29327,7 +29330,7 @@
         <v>1</v>
       </c>
       <c r="P558" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="559" spans="1:16">
@@ -29577,7 +29580,7 @@
         <v>1</v>
       </c>
       <c r="P563" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="564" spans="1:16">
@@ -29627,7 +29630,7 @@
         <v>1</v>
       </c>
       <c r="P564" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="565" spans="1:16">
@@ -29677,7 +29680,7 @@
         <v>1</v>
       </c>
       <c r="P565" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="566" spans="1:16">
@@ -29727,7 +29730,7 @@
         <v>1</v>
       </c>
       <c r="P566" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="567" spans="1:16">
@@ -30277,7 +30280,7 @@
         <v>1</v>
       </c>
       <c r="P577" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="578" spans="1:16">
@@ -30327,7 +30330,7 @@
         <v>1</v>
       </c>
       <c r="P578" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="579" spans="1:16">
@@ -30377,7 +30380,7 @@
         <v>1</v>
       </c>
       <c r="P579" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="580" spans="1:16">
@@ -30427,7 +30430,7 @@
         <v>1</v>
       </c>
       <c r="P580" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="581" spans="1:16">
@@ -30477,7 +30480,7 @@
         <v>1</v>
       </c>
       <c r="P581" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="582" spans="1:16">
@@ -30527,7 +30530,7 @@
         <v>1</v>
       </c>
       <c r="P582" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="583" spans="1:16">
@@ -30577,7 +30580,7 @@
         <v>1</v>
       </c>
       <c r="P583" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="584" spans="1:16">
@@ -30627,7 +30630,7 @@
         <v>1</v>
       </c>
       <c r="P584" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="585" spans="1:16">
@@ -30677,7 +30680,7 @@
         <v>1</v>
       </c>
       <c r="P585" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="586" spans="1:16">
@@ -30727,7 +30730,7 @@
         <v>1</v>
       </c>
       <c r="P586" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="587" spans="1:16">
@@ -30777,7 +30780,7 @@
         <v>1</v>
       </c>
       <c r="P587" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="588" spans="1:16">
@@ -30827,7 +30830,7 @@
         <v>1</v>
       </c>
       <c r="P588" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="589" spans="1:16">
@@ -30877,7 +30880,7 @@
         <v>1</v>
       </c>
       <c r="P589" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="590" spans="1:16">
@@ -30927,7 +30930,7 @@
         <v>1</v>
       </c>
       <c r="P590" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="591" spans="1:16">
@@ -31177,7 +31180,7 @@
         <v>1</v>
       </c>
       <c r="P595" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="596" spans="1:16">
@@ -31227,7 +31230,7 @@
         <v>1</v>
       </c>
       <c r="P596" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="597" spans="1:16">
@@ -31277,7 +31280,7 @@
         <v>1</v>
       </c>
       <c r="P597" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="598" spans="1:16">
@@ -31327,7 +31330,7 @@
         <v>1</v>
       </c>
       <c r="P598" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="599" spans="1:16">
@@ -31377,7 +31380,7 @@
         <v>1</v>
       </c>
       <c r="P599" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="600" spans="1:16">
@@ -31427,7 +31430,7 @@
         <v>1</v>
       </c>
       <c r="P600" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="601" spans="1:16">
@@ -31727,7 +31730,7 @@
         <v>1</v>
       </c>
       <c r="P606" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="607" spans="1:16">
@@ -31777,7 +31780,7 @@
         <v>1</v>
       </c>
       <c r="P607" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="608" spans="1:16">
@@ -31827,7 +31830,7 @@
         <v>1</v>
       </c>
       <c r="P608" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="609" spans="1:16">
@@ -31877,7 +31880,7 @@
         <v>1</v>
       </c>
       <c r="P609" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="610" spans="1:16">
@@ -31927,7 +31930,7 @@
         <v>1</v>
       </c>
       <c r="P610" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="611" spans="1:16">
@@ -32577,7 +32580,7 @@
         <v>1</v>
       </c>
       <c r="P623" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="624" spans="1:16">
@@ -32627,7 +32630,7 @@
         <v>1</v>
       </c>
       <c r="P624" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="625" spans="1:16">
@@ -32677,7 +32680,7 @@
         <v>1</v>
       </c>
       <c r="P625" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="626" spans="1:16">
@@ -32727,7 +32730,7 @@
         <v>1</v>
       </c>
       <c r="P626" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="627" spans="1:16">
@@ -32777,7 +32780,7 @@
         <v>1</v>
       </c>
       <c r="P627" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="628" spans="1:16">
@@ -32827,7 +32830,7 @@
         <v>1</v>
       </c>
       <c r="P628" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="629" spans="1:16">
@@ -32877,7 +32880,7 @@
         <v>1</v>
       </c>
       <c r="P629" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="630" spans="1:16">
@@ -32927,7 +32930,7 @@
         <v>1</v>
       </c>
       <c r="P630" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="631" spans="1:16">
@@ -32977,7 +32980,7 @@
         <v>1</v>
       </c>
       <c r="P631" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="632" spans="1:16">
@@ -33027,7 +33030,7 @@
         <v>1</v>
       </c>
       <c r="P632" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="633" spans="1:16">
@@ -33077,7 +33080,7 @@
         <v>1</v>
       </c>
       <c r="P633" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="634" spans="1:16">
@@ -33127,7 +33130,7 @@
         <v>1</v>
       </c>
       <c r="P634" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="635" spans="1:16">
@@ -33177,7 +33180,7 @@
         <v>1</v>
       </c>
       <c r="P635" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="636" spans="1:16">
@@ -33227,7 +33230,7 @@
         <v>1</v>
       </c>
       <c r="P636" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="637" spans="1:16">
@@ -33277,7 +33280,7 @@
         <v>1</v>
       </c>
       <c r="P637" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="638" spans="1:16">
@@ -33327,7 +33330,7 @@
         <v>1</v>
       </c>
       <c r="P638" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="639" spans="1:16">
@@ -33377,7 +33380,7 @@
         <v>1</v>
       </c>
       <c r="P639" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="640" spans="1:16">
@@ -33427,7 +33430,7 @@
         <v>1</v>
       </c>
       <c r="P640" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="641" spans="1:16">
@@ -33477,7 +33480,7 @@
         <v>1</v>
       </c>
       <c r="P641" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="642" spans="1:16">
@@ -33527,7 +33530,7 @@
         <v>1</v>
       </c>
       <c r="P642" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="643" spans="1:16">
@@ -33577,7 +33580,7 @@
         <v>1</v>
       </c>
       <c r="P643" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="644" spans="1:16">
@@ -33627,7 +33630,7 @@
         <v>1</v>
       </c>
       <c r="P644" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="645" spans="1:16">
@@ -33677,7 +33680,7 @@
         <v>1</v>
       </c>
       <c r="P645" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="646" spans="1:16">
@@ -33727,7 +33730,7 @@
         <v>1</v>
       </c>
       <c r="P646" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="647" spans="1:16">
@@ -33927,7 +33930,7 @@
         <v>1</v>
       </c>
       <c r="P650" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="651" spans="1:16">
@@ -33977,7 +33980,7 @@
         <v>1</v>
       </c>
       <c r="P651" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="652" spans="1:16">
@@ -34027,7 +34030,7 @@
         <v>1</v>
       </c>
       <c r="P652" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="653" spans="1:16">
@@ -34377,7 +34380,7 @@
         <v>1</v>
       </c>
       <c r="P659" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="660" spans="1:16">
@@ -34427,7 +34430,7 @@
         <v>1</v>
       </c>
       <c r="P660" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="661" spans="1:16">
@@ -34477,7 +34480,7 @@
         <v>1</v>
       </c>
       <c r="P661" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="662" spans="1:16">
@@ -34527,7 +34530,7 @@
         <v>1</v>
       </c>
       <c r="P662" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="663" spans="1:16">
@@ -36277,7 +36280,7 @@
         <v>1</v>
       </c>
       <c r="P697" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="698" spans="1:16">
@@ -36327,7 +36330,7 @@
         <v>1</v>
       </c>
       <c r="P698" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="699" spans="1:16">
@@ -36377,7 +36380,7 @@
         <v>1</v>
       </c>
       <c r="P699" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="700" spans="1:16">
@@ -36427,7 +36430,7 @@
         <v>1</v>
       </c>
       <c r="P700" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="701" spans="1:16">
@@ -36477,7 +36480,7 @@
         <v>1</v>
       </c>
       <c r="P701" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="702" spans="1:16">
@@ -36527,7 +36530,7 @@
         <v>1</v>
       </c>
       <c r="P702" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="703" spans="1:16">
@@ -36577,7 +36580,7 @@
         <v>1</v>
       </c>
       <c r="P703" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="704" spans="1:16">
@@ -36627,7 +36630,7 @@
         <v>1</v>
       </c>
       <c r="P704" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="705" spans="1:16">
@@ -36677,7 +36680,7 @@
         <v>1</v>
       </c>
       <c r="P705" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="706" spans="1:16">
@@ -36727,7 +36730,7 @@
         <v>1</v>
       </c>
       <c r="P706" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="707" spans="1:16">
@@ -36777,7 +36780,7 @@
         <v>1</v>
       </c>
       <c r="P707" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="708" spans="1:16">
@@ -36827,7 +36830,7 @@
         <v>1</v>
       </c>
       <c r="P708" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="709" spans="1:16">
@@ -36877,7 +36880,7 @@
         <v>1</v>
       </c>
       <c r="P709" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="710" spans="1:16">
@@ -36927,7 +36930,7 @@
         <v>1</v>
       </c>
       <c r="P710" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="711" spans="1:16">
@@ -36977,7 +36980,7 @@
         <v>1</v>
       </c>
       <c r="P711" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="712" spans="1:16">
@@ -37027,7 +37030,7 @@
         <v>1</v>
       </c>
       <c r="P712" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="713" spans="1:16">
@@ -37077,7 +37080,7 @@
         <v>1</v>
       </c>
       <c r="P713" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="714" spans="1:16">
@@ -37127,7 +37130,7 @@
         <v>1</v>
       </c>
       <c r="P714" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="715" spans="1:16">
@@ -37177,7 +37180,7 @@
         <v>1</v>
       </c>
       <c r="P715" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="716" spans="1:16">
@@ -37227,7 +37230,7 @@
         <v>1</v>
       </c>
       <c r="P716" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="717" spans="1:16">
@@ -37277,7 +37280,7 @@
         <v>1</v>
       </c>
       <c r="P717" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="718" spans="1:16">
@@ -37327,7 +37330,7 @@
         <v>1</v>
       </c>
       <c r="P718" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="719" spans="1:16">
@@ -37377,7 +37380,7 @@
         <v>1</v>
       </c>
       <c r="P719" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="720" spans="1:16">
@@ -37427,7 +37430,7 @@
         <v>1</v>
       </c>
       <c r="P720" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="721" spans="1:16">
@@ -37477,7 +37480,7 @@
         <v>1</v>
       </c>
       <c r="P721" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="722" spans="1:16">
@@ -37527,7 +37530,7 @@
         <v>1</v>
       </c>
       <c r="P722" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="723" spans="1:16">
@@ -37827,7 +37830,7 @@
         <v>1</v>
       </c>
       <c r="P728" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="729" spans="1:16">
@@ -37877,7 +37880,7 @@
         <v>1</v>
       </c>
       <c r="P729" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="730" spans="1:16">
@@ -37927,7 +37930,7 @@
         <v>1</v>
       </c>
       <c r="P730" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="731" spans="1:16">
@@ -37977,7 +37980,7 @@
         <v>1</v>
       </c>
       <c r="P731" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="732" spans="1:16">
@@ -38027,7 +38030,7 @@
         <v>1</v>
       </c>
       <c r="P732" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="733" spans="1:16">
@@ -38077,7 +38080,7 @@
         <v>1</v>
       </c>
       <c r="P733" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="734" spans="1:16">
@@ -38127,7 +38130,7 @@
         <v>1</v>
       </c>
       <c r="P734" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="735" spans="1:16">
@@ -38177,7 +38180,7 @@
         <v>1</v>
       </c>
       <c r="P735" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="736" spans="1:16">
@@ -38227,7 +38230,7 @@
         <v>1</v>
       </c>
       <c r="P736" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="737" spans="1:16">
@@ -38277,7 +38280,7 @@
         <v>1</v>
       </c>
       <c r="P737" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="738" spans="1:16">
@@ -38327,7 +38330,7 @@
         <v>1</v>
       </c>
       <c r="P738" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="739" spans="1:16">
@@ -38377,7 +38380,7 @@
         <v>1</v>
       </c>
       <c r="P739" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="740" spans="1:16">
@@ -38427,7 +38430,7 @@
         <v>1</v>
       </c>
       <c r="P740" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="741" spans="1:16">
@@ -38477,7 +38480,7 @@
         <v>1</v>
       </c>
       <c r="P741" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="742" spans="1:16">
@@ -38527,7 +38530,7 @@
         <v>1</v>
       </c>
       <c r="P742" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="743" spans="1:16">
@@ -38577,7 +38580,7 @@
         <v>1</v>
       </c>
       <c r="P743" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="744" spans="1:16">
@@ -38627,7 +38630,7 @@
         <v>1</v>
       </c>
       <c r="P744" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="745" spans="1:16">
@@ -38677,7 +38680,7 @@
         <v>1</v>
       </c>
       <c r="P745" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="746" spans="1:16">
@@ -38727,7 +38730,7 @@
         <v>1</v>
       </c>
       <c r="P746" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="747" spans="1:16">
@@ -39077,7 +39080,7 @@
         <v>1</v>
       </c>
       <c r="P753" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="754" spans="1:16">
@@ -39127,7 +39130,7 @@
         <v>1</v>
       </c>
       <c r="P754" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="755" spans="1:16">
@@ -39177,7 +39180,7 @@
         <v>1</v>
       </c>
       <c r="P755" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="756" spans="1:16">
@@ -39227,7 +39230,7 @@
         <v>1</v>
       </c>
       <c r="P756" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="757" spans="1:16">
@@ -39277,7 +39280,7 @@
         <v>1</v>
       </c>
       <c r="P757" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="758" spans="1:16">
@@ -39327,7 +39330,7 @@
         <v>1</v>
       </c>
       <c r="P758" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="759" spans="1:16">
@@ -39677,7 +39680,7 @@
         <v>1</v>
       </c>
       <c r="P765" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="766" spans="1:16">
@@ -39727,7 +39730,7 @@
         <v>1</v>
       </c>
       <c r="P766" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="767" spans="1:16">
@@ -39777,7 +39780,7 @@
         <v>1</v>
       </c>
       <c r="P767" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="768" spans="1:16">
@@ -39827,7 +39830,7 @@
         <v>1</v>
       </c>
       <c r="P768" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="769" spans="1:16">
@@ -40077,7 +40080,7 @@
         <v>1</v>
       </c>
       <c r="P773" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="774" spans="1:16">
@@ -40127,7 +40130,7 @@
         <v>1</v>
       </c>
       <c r="P774" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="775" spans="1:16">
@@ -40177,7 +40180,7 @@
         <v>1</v>
       </c>
       <c r="P775" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="776" spans="1:16">
@@ -40227,7 +40230,7 @@
         <v>1</v>
       </c>
       <c r="P776" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="777" spans="1:16">
@@ -40477,7 +40480,7 @@
         <v>1</v>
       </c>
       <c r="P781" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="782" spans="1:16">
@@ -40527,7 +40530,7 @@
         <v>1</v>
       </c>
       <c r="P782" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="783" spans="1:16">
@@ -40577,7 +40580,7 @@
         <v>1</v>
       </c>
       <c r="P783" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="784" spans="1:16">
@@ -40977,7 +40980,7 @@
         <v>1</v>
       </c>
       <c r="P791" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="792" spans="1:16">
@@ -41027,7 +41030,7 @@
         <v>1</v>
       </c>
       <c r="P792" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="793" spans="1:16">
@@ -41077,7 +41080,7 @@
         <v>1</v>
       </c>
       <c r="P793" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="794" spans="1:16">
@@ -41127,7 +41130,7 @@
         <v>1</v>
       </c>
       <c r="P794" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="795" spans="1:16">
@@ -41377,7 +41380,7 @@
         <v>1</v>
       </c>
       <c r="P799" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="800" spans="1:16">
@@ -41427,7 +41430,7 @@
         <v>1</v>
       </c>
       <c r="P800" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="801" spans="1:16">
@@ -41477,7 +41480,7 @@
         <v>1</v>
       </c>
       <c r="P801" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="802" spans="1:16">
@@ -41527,7 +41530,7 @@
         <v>1</v>
       </c>
       <c r="P802" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="803" spans="1:16">
@@ -41577,7 +41580,7 @@
         <v>1</v>
       </c>
       <c r="P803" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="804" spans="1:16">
@@ -41627,7 +41630,7 @@
         <v>1</v>
       </c>
       <c r="P804" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="805" spans="1:16">
@@ -41977,7 +41980,7 @@
         <v>1</v>
       </c>
       <c r="P811" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="812" spans="1:16">
@@ -42027,7 +42030,7 @@
         <v>1</v>
       </c>
       <c r="P812" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="813" spans="1:16">
@@ -42077,7 +42080,7 @@
         <v>1</v>
       </c>
       <c r="P813" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="814" spans="1:16">
@@ -43627,7 +43630,7 @@
         <v>1</v>
       </c>
       <c r="P844" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="845" spans="1:16">
@@ -43677,7 +43680,7 @@
         <v>1</v>
       </c>
       <c r="P845" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="846" spans="1:16">
@@ -43727,7 +43730,7 @@
         <v>1</v>
       </c>
       <c r="P846" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="847" spans="1:16">
@@ -43777,7 +43780,7 @@
         <v>1</v>
       </c>
       <c r="P847" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="848" spans="1:16">
@@ -43827,7 +43830,7 @@
         <v>1</v>
       </c>
       <c r="P848" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="849" spans="1:16">
@@ -43877,7 +43880,7 @@
         <v>1</v>
       </c>
       <c r="P849" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="850" spans="1:16">
@@ -43927,7 +43930,7 @@
         <v>1</v>
       </c>
       <c r="P850" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="851" spans="1:16">
@@ -44377,7 +44380,7 @@
         <v>1</v>
       </c>
       <c r="P859" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="860" spans="1:16">
@@ -44388,46 +44391,46 @@
         <v>155</v>
       </c>
       <c r="C860">
-        <v>13.67315026490144</v>
+        <v>13.92659718804111</v>
       </c>
       <c r="D860" t="s">
         <v>268</v>
       </c>
       <c r="E860">
-        <v>13.36888206048432</v>
+        <v>13.79266975304299</v>
       </c>
       <c r="F860">
         <v>-1</v>
       </c>
       <c r="G860">
-        <v>0.04792684973509856</v>
+        <v>0.04843340281195889</v>
       </c>
       <c r="H860">
-        <v>0.05049111793951568</v>
+        <v>0.05192733024695701</v>
       </c>
       <c r="I860">
-        <v>0.3042682044171201</v>
+        <v>0.1339274349981245</v>
       </c>
       <c r="J860">
         <v>0.8436871790688943</v>
       </c>
       <c r="K860">
-        <v>20.3</v>
+        <v>20.45</v>
       </c>
       <c r="L860">
-        <v>30.8</v>
+        <v>31.18</v>
       </c>
       <c r="M860">
-        <v>22</v>
+        <v>22.6</v>
       </c>
       <c r="N860">
-        <v>31.93</v>
+        <v>32.86</v>
       </c>
       <c r="O860">
         <v>1</v>
       </c>
       <c r="P860" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="861" spans="1:16">
@@ -44438,46 +44441,46 @@
         <v>156</v>
       </c>
       <c r="C861">
-        <v>13.92659718804111</v>
+        <v>13.88635693211188</v>
       </c>
       <c r="D861" t="s">
         <v>268</v>
       </c>
       <c r="E861">
-        <v>13.36888206048432</v>
+        <v>13.79266975304299</v>
       </c>
       <c r="F861">
         <v>-1</v>
       </c>
       <c r="G861">
-        <v>0.04843340281195889</v>
+        <v>0.05033364306788812</v>
       </c>
       <c r="H861">
-        <v>0.05049111793951568</v>
+        <v>0.05192733024695701</v>
       </c>
       <c r="I861">
-        <v>0.5577151275567864</v>
+        <v>0.09368717906889401</v>
       </c>
       <c r="J861">
         <v>0.8436871790688943</v>
       </c>
       <c r="K861">
-        <v>20.45</v>
+        <v>21.6</v>
       </c>
       <c r="L861">
-        <v>31.18</v>
+        <v>32.11</v>
       </c>
       <c r="M861">
-        <v>22</v>
+        <v>22.6</v>
       </c>
       <c r="N861">
-        <v>31.93</v>
+        <v>32.86</v>
       </c>
       <c r="O861">
         <v>1</v>
       </c>
       <c r="P861" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="862" spans="1:16">
@@ -44527,7 +44530,7 @@
         <v>1</v>
       </c>
       <c r="P862" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="863" spans="1:16">
@@ -44538,46 +44541,46 @@
         <v>155</v>
       </c>
       <c r="C863">
-        <v>13.59897621067881</v>
+        <v>13.85187504967397</v>
       </c>
       <c r="D863" t="s">
         <v>268</v>
       </c>
       <c r="E863">
-        <v>13.28849638595733</v>
+        <v>13.71009174193798</v>
       </c>
       <c r="F863">
         <v>-1</v>
       </c>
       <c r="G863">
-        <v>0.0480010237893212</v>
+        <v>0.04850812495032602</v>
       </c>
       <c r="H863">
-        <v>0.05057150361404267</v>
+        <v>0.05200990825806201</v>
       </c>
       <c r="I863">
-        <v>0.3104798247214795</v>
+        <v>0.1417833077359916</v>
       </c>
       <c r="J863">
         <v>0.8473410733655758</v>
       </c>
       <c r="K863">
-        <v>20.3</v>
+        <v>20.45</v>
       </c>
       <c r="L863">
-        <v>30.8</v>
+        <v>31.18</v>
       </c>
       <c r="M863">
-        <v>22</v>
+        <v>22.6</v>
       </c>
       <c r="N863">
-        <v>31.93</v>
+        <v>32.86</v>
       </c>
       <c r="O863">
         <v>1</v>
       </c>
       <c r="P863" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="864" spans="1:16">
@@ -44588,46 +44591,46 @@
         <v>156</v>
       </c>
       <c r="C864">
-        <v>13.85187504967397</v>
+        <v>13.80743281530356</v>
       </c>
       <c r="D864" t="s">
         <v>268</v>
       </c>
       <c r="E864">
-        <v>13.28849638595733</v>
+        <v>13.71009174193798</v>
       </c>
       <c r="F864">
         <v>-1</v>
       </c>
       <c r="G864">
-        <v>0.04850812495032602</v>
+        <v>0.05041256718469644</v>
       </c>
       <c r="H864">
-        <v>0.05057150361404267</v>
+        <v>0.05200990825806201</v>
       </c>
       <c r="I864">
-        <v>0.5633786637166445</v>
+        <v>0.09734107336557685</v>
       </c>
       <c r="J864">
         <v>0.8473410733655758</v>
       </c>
       <c r="K864">
-        <v>20.45</v>
+        <v>21.6</v>
       </c>
       <c r="L864">
-        <v>31.18</v>
+        <v>32.11</v>
       </c>
       <c r="M864">
-        <v>22</v>
+        <v>22.6</v>
       </c>
       <c r="N864">
-        <v>31.93</v>
+        <v>32.86</v>
       </c>
       <c r="O864">
         <v>1</v>
       </c>
       <c r="P864" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="865" spans="1:16">
@@ -44677,7 +44680,7 @@
         <v>1</v>
       </c>
       <c r="P865" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="866" spans="1:16">
@@ -44688,46 +44691,46 @@
         <v>155</v>
       </c>
       <c r="C866">
-        <v>13.54381791161196</v>
+        <v>13.7963091769687</v>
       </c>
       <c r="D866" t="s">
         <v>268</v>
       </c>
       <c r="E866">
-        <v>13.22871891898833</v>
+        <v>13.64868398041529</v>
       </c>
       <c r="F866">
         <v>-1</v>
       </c>
       <c r="G866">
-        <v>0.04805618208838804</v>
+        <v>0.0485636908230313</v>
       </c>
       <c r="H866">
-        <v>0.05063128108101166</v>
+        <v>0.05207131601958472</v>
       </c>
       <c r="I866">
-        <v>0.3150989926236285</v>
+        <v>0.1476251965534132</v>
       </c>
       <c r="J866">
         <v>0.8500582309550758</v>
       </c>
       <c r="K866">
-        <v>20.3</v>
+        <v>20.45</v>
       </c>
       <c r="L866">
-        <v>30.8</v>
+        <v>31.18</v>
       </c>
       <c r="M866">
-        <v>22</v>
+        <v>22.6</v>
       </c>
       <c r="N866">
-        <v>31.93</v>
+        <v>32.86</v>
       </c>
       <c r="O866">
         <v>1</v>
       </c>
       <c r="P866" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="867" spans="1:16">
@@ -44738,46 +44741,46 @@
         <v>156</v>
       </c>
       <c r="C867">
-        <v>13.7963091769687</v>
+        <v>13.74874221137036</v>
       </c>
       <c r="D867" t="s">
         <v>268</v>
       </c>
       <c r="E867">
-        <v>13.22871891898833</v>
+        <v>13.64868398041529</v>
       </c>
       <c r="F867">
         <v>-1</v>
       </c>
       <c r="G867">
-        <v>0.0485636908230313</v>
+        <v>0.05047125778862965</v>
       </c>
       <c r="H867">
-        <v>0.05063128108101166</v>
+        <v>0.05207131601958472</v>
       </c>
       <c r="I867">
-        <v>0.5675902579803669</v>
+        <v>0.1000582309550744</v>
       </c>
       <c r="J867">
         <v>0.8500582309550758</v>
       </c>
       <c r="K867">
-        <v>20.45</v>
+        <v>21.6</v>
       </c>
       <c r="L867">
-        <v>31.18</v>
+        <v>32.11</v>
       </c>
       <c r="M867">
-        <v>22</v>
+        <v>22.6</v>
       </c>
       <c r="N867">
-        <v>31.93</v>
+        <v>32.86</v>
       </c>
       <c r="O867">
         <v>1</v>
       </c>
       <c r="P867" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="868" spans="1:16">
@@ -44788,40 +44791,40 @@
         <v>155</v>
       </c>
       <c r="C868">
-        <v>13.51182023914395</v>
+        <v>13.76407506849723</v>
       </c>
       <c r="D868" t="s">
         <v>268</v>
       </c>
       <c r="E868">
-        <v>13.19404163848113</v>
+        <v>13.61306095589425</v>
       </c>
       <c r="F868">
         <v>-1</v>
       </c>
       <c r="G868">
-        <v>0.04808817976085605</v>
+        <v>0.04859592493150276</v>
       </c>
       <c r="H868">
-        <v>0.05066595836151887</v>
+        <v>0.05210693904410574</v>
       </c>
       <c r="I868">
-        <v>0.3177786006628232</v>
+        <v>0.1510141126029829</v>
       </c>
       <c r="J868">
         <v>0.8516344709781304</v>
       </c>
       <c r="K868">
-        <v>20.3</v>
+        <v>20.45</v>
       </c>
       <c r="L868">
-        <v>30.8</v>
+        <v>31.18</v>
       </c>
       <c r="M868">
-        <v>22</v>
+        <v>22.6</v>
       </c>
       <c r="N868">
-        <v>31.93</v>
+        <v>32.86</v>
       </c>
       <c r="O868">
         <v>1</v>
@@ -44838,40 +44841,40 @@
         <v>156</v>
       </c>
       <c r="C869">
-        <v>13.76407506849723</v>
+        <v>13.71469542687238</v>
       </c>
       <c r="D869" t="s">
         <v>268</v>
       </c>
       <c r="E869">
-        <v>13.19404163848113</v>
+        <v>13.61306095589425</v>
       </c>
       <c r="F869">
         <v>-1</v>
       </c>
       <c r="G869">
-        <v>0.04859592493150276</v>
+        <v>0.05050530457312762</v>
       </c>
       <c r="H869">
-        <v>0.05066595836151887</v>
+        <v>0.05210693904410574</v>
       </c>
       <c r="I869">
-        <v>0.5700334300161032</v>
+        <v>0.1016344709781301</v>
       </c>
       <c r="J869">
         <v>0.8516344709781304</v>
       </c>
       <c r="K869">
-        <v>20.45</v>
+        <v>21.6</v>
       </c>
       <c r="L869">
-        <v>31.18</v>
+        <v>32.11</v>
       </c>
       <c r="M869">
-        <v>22</v>
+        <v>22.6</v>
       </c>
       <c r="N869">
-        <v>31.93</v>
+        <v>32.86</v>
       </c>
       <c r="O869">
         <v>1</v>
@@ -44888,10 +44891,10 @@
         <v>155</v>
       </c>
       <c r="C870">
-        <v>13.43501557200262</v>
+        <v>13.6867028791849</v>
       </c>
       <c r="D870" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E870">
         <v>13.11080505340185</v>
@@ -44900,22 +44903,22 @@
         <v>-1</v>
       </c>
       <c r="G870">
-        <v>0.04816498442799738</v>
+        <v>0.0486732971208151</v>
       </c>
       <c r="H870">
         <v>0.05074919494659815</v>
       </c>
       <c r="I870">
-        <v>0.3242105186007684</v>
+        <v>0.575897825783052</v>
       </c>
       <c r="J870">
         <v>0.8554179521180978</v>
       </c>
       <c r="K870">
-        <v>20.3</v>
+        <v>20.45</v>
       </c>
       <c r="L870">
-        <v>30.8</v>
+        <v>31.18</v>
       </c>
       <c r="M870">
         <v>22</v>
@@ -44927,57 +44930,7 @@
         <v>1</v>
       </c>
       <c r="P870" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="871" spans="1:16">
-      <c r="A871" s="1">
-        <v>1</v>
-      </c>
-      <c r="B871" t="s">
-        <v>156</v>
-      </c>
-      <c r="C871">
-        <v>13.6867028791849</v>
-      </c>
-      <c r="D871" t="s">
-        <v>268</v>
-      </c>
-      <c r="E871">
-        <v>13.11080505340185</v>
-      </c>
-      <c r="F871">
-        <v>-1</v>
-      </c>
-      <c r="G871">
-        <v>0.0486732971208151</v>
-      </c>
-      <c r="H871">
-        <v>0.05074919494659815</v>
-      </c>
-      <c r="I871">
-        <v>0.575897825783052</v>
-      </c>
-      <c r="J871">
-        <v>0.8554179521180978</v>
-      </c>
-      <c r="K871">
-        <v>20.45</v>
-      </c>
-      <c r="L871">
-        <v>31.18</v>
-      </c>
-      <c r="M871">
-        <v>22</v>
-      </c>
-      <c r="N871">
-        <v>31.93</v>
-      </c>
-      <c r="O871">
-        <v>1</v>
-      </c>
-      <c r="P871" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-00763-000063.xlsx
+++ b/s60_signal/position-00763-000063.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2622" uniqueCount="354">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2616" uniqueCount="354">
   <si>
     <t>trade_time</t>
   </si>
@@ -820,7 +820,7 @@
     <t>2021-12-03</t>
   </si>
   <si>
-    <t>2021-12-13</t>
+    <t>2021-12-14</t>
   </si>
   <si>
     <t>2021-12-09</t>
@@ -1433,7 +1433,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P870"/>
+  <dimension ref="A1:P868"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -44397,7 +44397,7 @@
         <v>268</v>
       </c>
       <c r="E860">
-        <v>13.79266975304299</v>
+        <v>14.18888206048432</v>
       </c>
       <c r="F860">
         <v>-1</v>
@@ -44406,10 +44406,10 @@
         <v>0.04843340281195889</v>
       </c>
       <c r="H860">
-        <v>0.05192733024695701</v>
+        <v>0.05131111793951568</v>
       </c>
       <c r="I860">
-        <v>0.1339274349981245</v>
+        <v>-0.2622848724432139</v>
       </c>
       <c r="J860">
         <v>0.8436871790688943</v>
@@ -44421,10 +44421,10 @@
         <v>31.18</v>
       </c>
       <c r="M860">
-        <v>22.6</v>
+        <v>22</v>
       </c>
       <c r="N860">
-        <v>32.86</v>
+        <v>32.75</v>
       </c>
       <c r="O860">
         <v>1</v>
@@ -44447,7 +44447,7 @@
         <v>268</v>
       </c>
       <c r="E861">
-        <v>13.79266975304299</v>
+        <v>14.18888206048432</v>
       </c>
       <c r="F861">
         <v>-1</v>
@@ -44456,10 +44456,10 @@
         <v>0.05033364306788812</v>
       </c>
       <c r="H861">
-        <v>0.05192733024695701</v>
+        <v>0.05131111793951568</v>
       </c>
       <c r="I861">
-        <v>0.09368717906889401</v>
+        <v>-0.3025251283724444</v>
       </c>
       <c r="J861">
         <v>0.8436871790688943</v>
@@ -44471,10 +44471,10 @@
         <v>32.11</v>
       </c>
       <c r="M861">
-        <v>22.6</v>
+        <v>22</v>
       </c>
       <c r="N861">
-        <v>32.86</v>
+        <v>32.75</v>
       </c>
       <c r="O861">
         <v>1</v>
@@ -44544,10 +44544,10 @@
         <v>13.85187504967397</v>
       </c>
       <c r="D863" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E863">
-        <v>13.71009174193798</v>
+        <v>13.28849638595733</v>
       </c>
       <c r="F863">
         <v>-1</v>
@@ -44556,10 +44556,10 @@
         <v>0.04850812495032602</v>
       </c>
       <c r="H863">
-        <v>0.05200990825806201</v>
+        <v>0.05057150361404267</v>
       </c>
       <c r="I863">
-        <v>0.1417833077359916</v>
+        <v>0.5633786637166445</v>
       </c>
       <c r="J863">
         <v>0.8473410733655758</v>
@@ -44571,10 +44571,10 @@
         <v>31.18</v>
       </c>
       <c r="M863">
-        <v>22.6</v>
+        <v>22</v>
       </c>
       <c r="N863">
-        <v>32.86</v>
+        <v>31.93</v>
       </c>
       <c r="O863">
         <v>1</v>
@@ -44585,96 +44585,96 @@
     </row>
     <row r="864" spans="1:16">
       <c r="A864" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B864" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C864">
-        <v>13.80743281530356</v>
+        <v>12.51871891898833</v>
       </c>
       <c r="D864" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="E864">
-        <v>13.71009174193798</v>
+        <v>13.30129170768218</v>
       </c>
       <c r="F864">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G864">
-        <v>0.05041256718469644</v>
+        <v>0.04992128108101167</v>
       </c>
       <c r="H864">
-        <v>0.05200990825806201</v>
+        <v>0.04857870829231783</v>
       </c>
       <c r="I864">
-        <v>0.09734107336557685</v>
+        <v>0.7825727886938481</v>
       </c>
       <c r="J864">
-        <v>0.8473410733655758</v>
+        <v>0.8500582309550758</v>
       </c>
       <c r="K864">
-        <v>21.6</v>
+        <v>22</v>
       </c>
       <c r="L864">
-        <v>32.11</v>
+        <v>31.22</v>
       </c>
       <c r="M864">
-        <v>22.6</v>
+        <v>20.75</v>
       </c>
       <c r="N864">
-        <v>32.86</v>
+        <v>30.94</v>
       </c>
       <c r="O864">
         <v>1</v>
       </c>
       <c r="P864" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="865" spans="1:16">
       <c r="A865" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B865" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C865">
-        <v>12.51871891898833</v>
+        <v>13.7963091769687</v>
       </c>
       <c r="D865" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E865">
-        <v>13.30129170768218</v>
+        <v>14.04871891898833</v>
       </c>
       <c r="F865">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G865">
-        <v>0.04992128108101167</v>
+        <v>0.0485636908230313</v>
       </c>
       <c r="H865">
-        <v>0.04857870829231783</v>
+        <v>0.05145128108101167</v>
       </c>
       <c r="I865">
-        <v>0.7825727886938481</v>
+        <v>-0.2524097420196334</v>
       </c>
       <c r="J865">
         <v>0.8500582309550758</v>
       </c>
       <c r="K865">
+        <v>20.45</v>
+      </c>
+      <c r="L865">
+        <v>31.18</v>
+      </c>
+      <c r="M865">
         <v>22</v>
       </c>
-      <c r="L865">
-        <v>31.22</v>
-      </c>
-      <c r="M865">
-        <v>20.75</v>
-      </c>
       <c r="N865">
-        <v>30.94</v>
+        <v>32.75</v>
       </c>
       <c r="O865">
         <v>1</v>
@@ -44685,46 +44685,46 @@
     </row>
     <row r="866" spans="1:16">
       <c r="A866" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B866" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C866">
-        <v>13.7963091769687</v>
+        <v>13.74874221137036</v>
       </c>
       <c r="D866" t="s">
         <v>268</v>
       </c>
       <c r="E866">
-        <v>13.64868398041529</v>
+        <v>14.04871891898833</v>
       </c>
       <c r="F866">
         <v>-1</v>
       </c>
       <c r="G866">
-        <v>0.0485636908230313</v>
+        <v>0.05047125778862965</v>
       </c>
       <c r="H866">
-        <v>0.05207131601958472</v>
+        <v>0.05145128108101167</v>
       </c>
       <c r="I866">
-        <v>0.1476251965534132</v>
+        <v>-0.2999767076179722</v>
       </c>
       <c r="J866">
         <v>0.8500582309550758</v>
       </c>
       <c r="K866">
-        <v>20.45</v>
+        <v>21.6</v>
       </c>
       <c r="L866">
-        <v>31.18</v>
+        <v>32.11</v>
       </c>
       <c r="M866">
-        <v>22.6</v>
+        <v>22</v>
       </c>
       <c r="N866">
-        <v>32.86</v>
+        <v>32.75</v>
       </c>
       <c r="O866">
         <v>1</v>
@@ -44735,52 +44735,52 @@
     </row>
     <row r="867" spans="1:16">
       <c r="A867" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B867" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C867">
-        <v>13.74874221137036</v>
+        <v>13.76407506849723</v>
       </c>
       <c r="D867" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E867">
-        <v>13.64868398041529</v>
+        <v>13.19404163848113</v>
       </c>
       <c r="F867">
         <v>-1</v>
       </c>
       <c r="G867">
-        <v>0.05047125778862965</v>
+        <v>0.04859592493150276</v>
       </c>
       <c r="H867">
-        <v>0.05207131601958472</v>
+        <v>0.05066595836151887</v>
       </c>
       <c r="I867">
-        <v>0.1000582309550744</v>
+        <v>0.5700334300161032</v>
       </c>
       <c r="J867">
-        <v>0.8500582309550758</v>
+        <v>0.8516344709781304</v>
       </c>
       <c r="K867">
-        <v>21.6</v>
+        <v>20.45</v>
       </c>
       <c r="L867">
-        <v>32.11</v>
+        <v>31.18</v>
       </c>
       <c r="M867">
-        <v>22.6</v>
+        <v>22</v>
       </c>
       <c r="N867">
-        <v>32.86</v>
+        <v>31.93</v>
       </c>
       <c r="O867">
         <v>1</v>
       </c>
       <c r="P867" t="s">
-        <v>352</v>
+        <v>154</v>
       </c>
     </row>
     <row r="868" spans="1:16">
@@ -44791,28 +44791,28 @@
         <v>155</v>
       </c>
       <c r="C868">
-        <v>13.76407506849723</v>
+        <v>13.6867028791849</v>
       </c>
       <c r="D868" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E868">
-        <v>13.61306095589425</v>
+        <v>13.11080505340185</v>
       </c>
       <c r="F868">
         <v>-1</v>
       </c>
       <c r="G868">
-        <v>0.04859592493150276</v>
+        <v>0.0486732971208151</v>
       </c>
       <c r="H868">
-        <v>0.05210693904410574</v>
+        <v>0.05074919494659815</v>
       </c>
       <c r="I868">
-        <v>0.1510141126029829</v>
+        <v>0.575897825783052</v>
       </c>
       <c r="J868">
-        <v>0.8516344709781304</v>
+        <v>0.8554179521180978</v>
       </c>
       <c r="K868">
         <v>20.45</v>
@@ -44821,115 +44821,15 @@
         <v>31.18</v>
       </c>
       <c r="M868">
-        <v>22.6</v>
+        <v>22</v>
       </c>
       <c r="N868">
-        <v>32.86</v>
+        <v>31.93</v>
       </c>
       <c r="O868">
         <v>1</v>
       </c>
       <c r="P868" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="869" spans="1:16">
-      <c r="A869" s="1">
-        <v>1</v>
-      </c>
-      <c r="B869" t="s">
-        <v>156</v>
-      </c>
-      <c r="C869">
-        <v>13.71469542687238</v>
-      </c>
-      <c r="D869" t="s">
-        <v>268</v>
-      </c>
-      <c r="E869">
-        <v>13.61306095589425</v>
-      </c>
-      <c r="F869">
-        <v>-1</v>
-      </c>
-      <c r="G869">
-        <v>0.05050530457312762</v>
-      </c>
-      <c r="H869">
-        <v>0.05210693904410574</v>
-      </c>
-      <c r="I869">
-        <v>0.1016344709781301</v>
-      </c>
-      <c r="J869">
-        <v>0.8516344709781304</v>
-      </c>
-      <c r="K869">
-        <v>21.6</v>
-      </c>
-      <c r="L869">
-        <v>32.11</v>
-      </c>
-      <c r="M869">
-        <v>22.6</v>
-      </c>
-      <c r="N869">
-        <v>32.86</v>
-      </c>
-      <c r="O869">
-        <v>1</v>
-      </c>
-      <c r="P869" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="870" spans="1:16">
-      <c r="A870" s="1">
-        <v>0</v>
-      </c>
-      <c r="B870" t="s">
-        <v>155</v>
-      </c>
-      <c r="C870">
-        <v>13.6867028791849</v>
-      </c>
-      <c r="D870" t="s">
-        <v>269</v>
-      </c>
-      <c r="E870">
-        <v>13.11080505340185</v>
-      </c>
-      <c r="F870">
-        <v>-1</v>
-      </c>
-      <c r="G870">
-        <v>0.0486732971208151</v>
-      </c>
-      <c r="H870">
-        <v>0.05074919494659815</v>
-      </c>
-      <c r="I870">
-        <v>0.575897825783052</v>
-      </c>
-      <c r="J870">
-        <v>0.8554179521180978</v>
-      </c>
-      <c r="K870">
-        <v>20.45</v>
-      </c>
-      <c r="L870">
-        <v>31.18</v>
-      </c>
-      <c r="M870">
-        <v>22</v>
-      </c>
-      <c r="N870">
-        <v>31.93</v>
-      </c>
-      <c r="O870">
-        <v>1</v>
-      </c>
-      <c r="P870" t="s">
         <v>353</v>
       </c>
     </row>

--- a/s60_signal/position-00763-000063.xlsx
+++ b/s60_signal/position-00763-000063.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2616" uniqueCount="354">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2607" uniqueCount="351">
   <si>
     <t>trade_time</t>
   </si>
@@ -481,10 +481,7 @@
     <t>2021-11-26</t>
   </si>
   <si>
-    <t>2021-12-08</t>
-  </si>
-  <si>
-    <t>2021-12-10</t>
+    <t>2021-12-14</t>
   </si>
   <si>
     <t>2017-03-17</t>
@@ -817,13 +814,10 @@
     <t>2021-03-26</t>
   </si>
   <si>
-    <t>2021-12-03</t>
+    <t>2021-12-06</t>
   </si>
   <si>
-    <t>2021-12-14</t>
-  </si>
-  <si>
-    <t>2021-12-09</t>
+    <t>2021-12-15</t>
   </si>
   <si>
     <t>2017-02-08</t>
@@ -1073,9 +1067,6 @@
   </si>
   <si>
     <t>2021-11-25</t>
-  </si>
-  <si>
-    <t>2021-11-29</t>
   </si>
 </sst>
 </file>
@@ -1433,7 +1424,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P868"/>
+  <dimension ref="A1:P865"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -1494,7 +1485,7 @@
         <v>8.357775317423281</v>
       </c>
       <c r="D2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E2">
         <v>9.239078272099615</v>
@@ -1530,7 +1521,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -1544,7 +1535,7 @@
         <v>9.433191964550923</v>
       </c>
       <c r="D3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E3">
         <v>9.285575452539577</v>
@@ -1580,7 +1571,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -1594,7 +1585,7 @@
         <v>9.420218808988363</v>
       </c>
       <c r="D4" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E4">
         <v>9.285575452539577</v>
@@ -1630,7 +1621,7 @@
         <v>1</v>
       </c>
       <c r="P4" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -1644,7 +1635,7 @@
         <v>9.27302954676334</v>
       </c>
       <c r="D5" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E5">
         <v>9.285575452539577</v>
@@ -1680,7 +1671,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -1694,7 +1685,7 @@
         <v>8.163141562328137</v>
       </c>
       <c r="D6" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E6">
         <v>8.870417830135191</v>
@@ -1730,7 +1721,7 @@
         <v>1</v>
       </c>
       <c r="P6" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -1744,7 +1735,7 @@
         <v>8.167981542028786</v>
       </c>
       <c r="D7" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E7">
         <v>8.870417830135191</v>
@@ -1780,7 +1771,7 @@
         <v>1</v>
       </c>
       <c r="P7" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -1794,7 +1785,7 @@
         <v>9.039124544167011</v>
       </c>
       <c r="D8" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E8">
         <v>9.113918803782131</v>
@@ -1830,7 +1821,7 @@
         <v>1</v>
       </c>
       <c r="P8" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -1844,7 +1835,7 @@
         <v>9.052076876787602</v>
       </c>
       <c r="D9" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E9">
         <v>9.113918803782131</v>
@@ -1880,7 +1871,7 @@
         <v>1</v>
       </c>
       <c r="P9" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -1894,7 +1885,7 @@
         <v>8.972076876787604</v>
       </c>
       <c r="D10" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E10">
         <v>9.113918803782131</v>
@@ -1930,7 +1921,7 @@
         <v>1</v>
       </c>
       <c r="P10" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -1944,7 +1935,7 @@
         <v>1.247895028504875</v>
       </c>
       <c r="D11" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E11">
         <v>5.93332434483856</v>
@@ -1980,7 +1971,7 @@
         <v>1</v>
       </c>
       <c r="P11" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -1994,7 +1985,7 @@
         <v>2.464515501370315</v>
       </c>
       <c r="D12" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E12">
         <v>5.93332434483856</v>
@@ -2030,7 +2021,7 @@
         <v>1</v>
       </c>
       <c r="P12" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -2080,7 +2071,7 @@
         <v>1</v>
       </c>
       <c r="P13" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -2094,7 +2085,7 @@
         <v>1.224092499726471</v>
       </c>
       <c r="D14" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E14">
         <v>5.913320521841428</v>
@@ -2130,7 +2121,7 @@
         <v>1</v>
       </c>
       <c r="P14" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -2144,7 +2135,7 @@
         <v>2.442814384300704</v>
       </c>
       <c r="D15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E15">
         <v>5.913320521841428</v>
@@ -2180,7 +2171,7 @@
         <v>1</v>
       </c>
       <c r="P15" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -2194,7 +2185,7 @@
         <v>8.399951396166678</v>
       </c>
       <c r="D16" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E16">
         <v>7.154665097353277</v>
@@ -2230,7 +2221,7 @@
         <v>1</v>
       </c>
       <c r="P16" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -2244,7 +2235,7 @@
         <v>1.231818368992485</v>
       </c>
       <c r="D17" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E17">
         <v>5.919813400087062</v>
@@ -2280,7 +2271,7 @@
         <v>1</v>
       </c>
       <c r="P17" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -2294,7 +2285,7 @@
         <v>2.449858173427781</v>
       </c>
       <c r="D18" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E18">
         <v>5.919813400087062</v>
@@ -2330,7 +2321,7 @@
         <v>1</v>
       </c>
       <c r="P18" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -2380,7 +2371,7 @@
         <v>1</v>
       </c>
       <c r="P19" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
     </row>
     <row r="20" spans="1:16">
@@ -2394,7 +2385,7 @@
         <v>1.145797529921555</v>
       </c>
       <c r="D20" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E20">
         <v>5.847520844331356</v>
@@ -2430,7 +2421,7 @@
         <v>1</v>
       </c>
       <c r="P20" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -2444,7 +2435,7 @@
         <v>2.37143170385038</v>
       </c>
       <c r="D21" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E21">
         <v>5.847520844331356</v>
@@ -2480,7 +2471,7 @@
         <v>1</v>
       </c>
       <c r="P21" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -2494,7 +2485,7 @@
         <v>8.323251570058975</v>
       </c>
       <c r="D22" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E22">
         <v>6.49770468378167</v>
@@ -2530,7 +2521,7 @@
         <v>1</v>
       </c>
       <c r="P22" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
     </row>
     <row r="23" spans="1:16">
@@ -2544,7 +2535,7 @@
         <v>8.298928068060523</v>
       </c>
       <c r="D23" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E23">
         <v>6.513844529583032</v>
@@ -2630,7 +2621,7 @@
         <v>1</v>
       </c>
       <c r="P24" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="25" spans="1:16">
@@ -2680,7 +2671,7 @@
         <v>1</v>
       </c>
       <c r="P25" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="26" spans="1:16">
@@ -2694,7 +2685,7 @@
         <v>4.521898732172186</v>
       </c>
       <c r="D26" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E26">
         <v>7.471272137184702</v>
@@ -2730,7 +2721,7 @@
         <v>1</v>
       </c>
       <c r="P26" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
     </row>
     <row r="27" spans="1:16">
@@ -2780,7 +2771,7 @@
         <v>1</v>
       </c>
       <c r="P27" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
     </row>
     <row r="28" spans="1:16">
@@ -2830,7 +2821,7 @@
         <v>1</v>
       </c>
       <c r="P28" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -2844,7 +2835,7 @@
         <v>10.06347633639325</v>
       </c>
       <c r="D29" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E29">
         <v>8.926863738767604</v>
@@ -2880,7 +2871,7 @@
         <v>1</v>
       </c>
       <c r="P29" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -3044,7 +3035,7 @@
         <v>10.57243502356749</v>
       </c>
       <c r="D33" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E33">
         <v>11.2289160904059</v>
@@ -3094,7 +3085,7 @@
         <v>10.58025171866791</v>
       </c>
       <c r="D34" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E34">
         <v>11.2289160904059</v>
@@ -3144,7 +3135,7 @@
         <v>6.89098969886382</v>
       </c>
       <c r="D35" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E35">
         <v>9.162922766970905</v>
@@ -3180,7 +3171,7 @@
         <v>1</v>
       </c>
       <c r="P35" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -3230,7 +3221,7 @@
         <v>1</v>
       </c>
       <c r="P36" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="37" spans="1:16">
@@ -3280,7 +3271,7 @@
         <v>1</v>
       </c>
       <c r="P37" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="38" spans="1:16">
@@ -3330,7 +3321,7 @@
         <v>1</v>
       </c>
       <c r="P38" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="39" spans="1:16">
@@ -3344,7 +3335,7 @@
         <v>10.57710841036202</v>
       </c>
       <c r="D39" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E39">
         <v>10.91875227586742</v>
@@ -3380,7 +3371,7 @@
         <v>1</v>
       </c>
       <c r="P39" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="40" spans="1:16">
@@ -3394,7 +3385,7 @@
         <v>10.58544939256899</v>
       </c>
       <c r="D40" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E40">
         <v>10.91875227586742</v>
@@ -3430,7 +3421,7 @@
         <v>1</v>
       </c>
       <c r="P40" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="41" spans="1:16">
@@ -3480,7 +3471,7 @@
         <v>1</v>
       </c>
       <c r="P41" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
     </row>
     <row r="42" spans="1:16">
@@ -3530,7 +3521,7 @@
         <v>1</v>
       </c>
       <c r="P42" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
     </row>
     <row r="43" spans="1:16">
@@ -3580,7 +3571,7 @@
         <v>1</v>
       </c>
       <c r="P43" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
     </row>
     <row r="44" spans="1:16">
@@ -3594,7 +3585,7 @@
         <v>10.50706987192051</v>
       </c>
       <c r="D44" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E44">
         <v>9.836117792760128</v>
@@ -3630,7 +3621,7 @@
         <v>1</v>
       </c>
       <c r="P44" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -3794,7 +3785,7 @@
         <v>11.00643298606593</v>
       </c>
       <c r="D48" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E48">
         <v>10.08970532444388</v>
@@ -3880,7 +3871,7 @@
         <v>1</v>
       </c>
       <c r="P49" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
     </row>
     <row r="50" spans="1:16">
@@ -3930,7 +3921,7 @@
         <v>1</v>
       </c>
       <c r="P50" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
     </row>
     <row r="51" spans="1:16">
@@ -3980,7 +3971,7 @@
         <v>1</v>
       </c>
       <c r="P51" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
     </row>
     <row r="52" spans="1:16">
@@ -4030,7 +4021,7 @@
         <v>1</v>
       </c>
       <c r="P52" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
     </row>
     <row r="53" spans="1:16">
@@ -4080,7 +4071,7 @@
         <v>1</v>
       </c>
       <c r="P53" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
     </row>
     <row r="54" spans="1:16">
@@ -4130,7 +4121,7 @@
         <v>1</v>
       </c>
       <c r="P54" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
     </row>
     <row r="55" spans="1:16">
@@ -4144,7 +4135,7 @@
         <v>10.96451987407661</v>
       </c>
       <c r="D55" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E55">
         <v>9.918825279734797</v>
@@ -4180,7 +4171,7 @@
         <v>1</v>
       </c>
       <c r="P55" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
     </row>
     <row r="56" spans="1:16">
@@ -4230,7 +4221,7 @@
         <v>1</v>
       </c>
       <c r="P56" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="57" spans="1:16">
@@ -4280,7 +4271,7 @@
         <v>1</v>
       </c>
       <c r="P57" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="58" spans="1:16">
@@ -4330,7 +4321,7 @@
         <v>1</v>
       </c>
       <c r="P58" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="59" spans="1:16">
@@ -4380,7 +4371,7 @@
         <v>1</v>
       </c>
       <c r="P59" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="60" spans="1:16">
@@ -4430,7 +4421,7 @@
         <v>1</v>
       </c>
       <c r="P60" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="61" spans="1:16">
@@ -4480,7 +4471,7 @@
         <v>1</v>
       </c>
       <c r="P61" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="62" spans="1:16">
@@ -4530,7 +4521,7 @@
         <v>1</v>
       </c>
       <c r="P62" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
     </row>
     <row r="63" spans="1:16">
@@ -4544,7 +4535,7 @@
         <v>10.70295290100141</v>
       </c>
       <c r="D63" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E63">
         <v>8.905400692050126</v>
@@ -4580,7 +4571,7 @@
         <v>1</v>
       </c>
       <c r="P63" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
     </row>
     <row r="64" spans="1:16">
@@ -4594,7 +4585,7 @@
         <v>11.20304517915771</v>
       </c>
       <c r="D64" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E64">
         <v>8.905400692050126</v>
@@ -4630,7 +4621,7 @@
         <v>1</v>
       </c>
       <c r="P64" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
     </row>
     <row r="65" spans="1:16">
@@ -4680,7 +4671,7 @@
         <v>1</v>
       </c>
       <c r="P65" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
     </row>
     <row r="66" spans="1:16">
@@ -4694,7 +4685,7 @@
         <v>10.69564352718713</v>
       </c>
       <c r="D66" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E66">
         <v>10.68408451836947</v>
@@ -4730,7 +4721,7 @@
         <v>1</v>
       </c>
       <c r="P66" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
     </row>
     <row r="67" spans="1:16">
@@ -4744,7 +4735,7 @@
         <v>11.03068966626528</v>
       </c>
       <c r="D67" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E67">
         <v>10.68408451836947</v>
@@ -4780,7 +4771,7 @@
         <v>1</v>
       </c>
       <c r="P67" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
     </row>
     <row r="68" spans="1:16">
@@ -4830,7 +4821,7 @@
         <v>1</v>
       </c>
       <c r="P68" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
     </row>
     <row r="69" spans="1:16">
@@ -4844,7 +4835,7 @@
         <v>10.52605158161457</v>
       </c>
       <c r="D69" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E69">
         <v>8.71498607743235</v>
@@ -4880,7 +4871,7 @@
         <v>1</v>
       </c>
       <c r="P69" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
     </row>
     <row r="70" spans="1:16">
@@ -4894,7 +4885,7 @@
         <v>11.02061569354003</v>
       </c>
       <c r="D70" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E70">
         <v>8.71498607743235</v>
@@ -4930,7 +4921,7 @@
         <v>1</v>
       </c>
       <c r="P70" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
     </row>
     <row r="71" spans="1:16">
@@ -4980,7 +4971,7 @@
         <v>1</v>
       </c>
       <c r="P71" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
     </row>
     <row r="72" spans="1:16">
@@ -4994,7 +4985,7 @@
         <v>10.52396325368498</v>
       </c>
       <c r="D72" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E72">
         <v>8.806051581614568</v>
@@ -5030,7 +5021,7 @@
         <v>1</v>
       </c>
       <c r="P72" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
     </row>
     <row r="73" spans="1:16">
@@ -5044,7 +5035,7 @@
         <v>10.8562453096477</v>
       </c>
       <c r="D73" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E73">
         <v>8.806051581614568</v>
@@ -5080,7 +5071,7 @@
         <v>1</v>
       </c>
       <c r="P73" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
     </row>
     <row r="74" spans="1:16">
@@ -5094,7 +5085,7 @@
         <v>10.34525014922946</v>
       </c>
       <c r="D74" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E74">
         <v>8.520373424517821</v>
@@ -5144,7 +5135,7 @@
         <v>10.83416421639288</v>
       </c>
       <c r="D75" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E75">
         <v>8.520373424517821</v>
@@ -5294,7 +5285,7 @@
         <v>10.34849797468624</v>
       </c>
       <c r="D78" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E78">
         <v>8.625250149229462</v>
@@ -5344,7 +5335,7 @@
         <v>10.67795500826794</v>
       </c>
       <c r="D79" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E79">
         <v>8.625250149229462</v>
@@ -5394,7 +5385,7 @@
         <v>10.18864383981015</v>
       </c>
       <c r="D80" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E80">
         <v>8.351804133128983</v>
@@ -5430,7 +5421,7 @@
         <v>1</v>
       </c>
       <c r="P80" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="81" spans="1:16">
@@ -5444,7 +5435,7 @@
         <v>10.67266395980422</v>
       </c>
       <c r="D81" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E81">
         <v>8.351804133128983</v>
@@ -5480,7 +5471,7 @@
         <v>1</v>
       </c>
       <c r="P81" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="82" spans="1:16">
@@ -5530,7 +5521,7 @@
         <v>1</v>
       </c>
       <c r="P82" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="83" spans="1:16">
@@ -5580,7 +5571,7 @@
         <v>1</v>
       </c>
       <c r="P83" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="84" spans="1:16">
@@ -5594,7 +5585,7 @@
         <v>10.19651372648243</v>
       </c>
       <c r="D84" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E84">
         <v>8.468643839810152</v>
@@ -5630,7 +5621,7 @@
         <v>1</v>
       </c>
       <c r="P84" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="85" spans="1:16">
@@ -5644,7 +5635,7 @@
         <v>10.52352378647946</v>
       </c>
       <c r="D85" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E85">
         <v>8.468643839810152</v>
@@ -5680,7 +5671,7 @@
         <v>1</v>
       </c>
       <c r="P85" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="86" spans="1:16">
@@ -5694,7 +5685,7 @@
         <v>-1.278554542763944</v>
       </c>
       <c r="D86" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E86">
         <v>0.01420169243589342</v>
@@ -5730,7 +5721,7 @@
         <v>1</v>
       </c>
       <c r="P86" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
     </row>
     <row r="87" spans="1:16">
@@ -5744,7 +5735,7 @@
         <v>-2.406586639852707</v>
       </c>
       <c r="D87" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E87">
         <v>0.01420169243589342</v>
@@ -5780,7 +5771,7 @@
         <v>1</v>
       </c>
       <c r="P87" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
     </row>
     <row r="88" spans="1:16">
@@ -5830,7 +5821,7 @@
         <v>1</v>
       </c>
       <c r="P88" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
     </row>
     <row r="89" spans="1:16">
@@ -5844,7 +5835,7 @@
         <v>-1.341212522415489</v>
       </c>
       <c r="D89" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E89">
         <v>0.1246199151405953</v>
@@ -5880,7 +5871,7 @@
         <v>1</v>
       </c>
       <c r="P89" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
     </row>
     <row r="90" spans="1:16">
@@ -5894,7 +5885,7 @@
         <v>-2.475362406493851</v>
       </c>
       <c r="D90" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E90">
         <v>0.1246199151405953</v>
@@ -5930,7 +5921,7 @@
         <v>1</v>
       </c>
       <c r="P90" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
     </row>
     <row r="91" spans="1:16">
@@ -5980,7 +5971,7 @@
         <v>1</v>
       </c>
       <c r="P91" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
     </row>
     <row r="92" spans="1:16">
@@ -5994,7 +5985,7 @@
         <v>-2.566016320350375</v>
       </c>
       <c r="D92" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E92">
         <v>0.02954385914472724</v>
@@ -6144,7 +6135,7 @@
         <v>-2.663355023194697</v>
       </c>
       <c r="D95" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E95">
         <v>0.03872013419191234</v>
@@ -6180,7 +6171,7 @@
         <v>1</v>
       </c>
       <c r="P95" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="96" spans="1:16">
@@ -6230,7 +6221,7 @@
         <v>1</v>
       </c>
       <c r="P96" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="97" spans="1:16">
@@ -6280,7 +6271,7 @@
         <v>1</v>
       </c>
       <c r="P97" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="98" spans="1:16">
@@ -6294,7 +6285,7 @@
         <v>-2.748103967913549</v>
       </c>
       <c r="D98" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E98">
         <v>-0.04760949385741853</v>
@@ -6330,7 +6321,7 @@
         <v>1</v>
       </c>
       <c r="P98" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="99" spans="1:16">
@@ -6344,7 +6335,7 @@
         <v>1.170412609918055</v>
       </c>
       <c r="D99" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E99">
         <v>1.469846093587645</v>
@@ -6380,7 +6371,7 @@
         <v>1</v>
       </c>
       <c r="P99" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="100" spans="1:16">
@@ -6394,7 +6385,7 @@
         <v>1.197090465141786</v>
       </c>
       <c r="D100" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E100">
         <v>1.469846093587645</v>
@@ -6430,7 +6421,7 @@
         <v>1</v>
       </c>
       <c r="P100" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="101" spans="1:16">
@@ -6444,7 +6435,7 @@
         <v>-2.807295369205091</v>
       </c>
       <c r="D101" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E101">
         <v>0.3363998775430197</v>
@@ -6480,7 +6471,7 @@
         <v>1</v>
       </c>
       <c r="P101" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
     </row>
     <row r="102" spans="1:16">
@@ -6530,7 +6521,7 @@
         <v>1</v>
       </c>
       <c r="P102" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
     </row>
     <row r="103" spans="1:16">
@@ -6630,7 +6621,7 @@
         <v>1</v>
       </c>
       <c r="P104" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
     </row>
     <row r="105" spans="1:16">
@@ -6644,7 +6635,7 @@
         <v>1.819034812951433</v>
       </c>
       <c r="D105" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E105">
         <v>1.780382458905816</v>
@@ -6680,7 +6671,7 @@
         <v>1</v>
       </c>
       <c r="P105" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
     </row>
     <row r="106" spans="1:16">
@@ -6694,7 +6685,7 @@
         <v>1.278232359359254</v>
       </c>
       <c r="D106" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E106">
         <v>1.780382458905816</v>
@@ -6730,7 +6721,7 @@
         <v>1</v>
       </c>
       <c r="P106" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
     </row>
     <row r="107" spans="1:16">
@@ -6744,7 +6735,7 @@
         <v>-1.27500579580901</v>
       </c>
       <c r="D107" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E107">
         <v>0.204597470791132</v>
@@ -6780,7 +6771,7 @@
         <v>1</v>
       </c>
       <c r="P107" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
     </row>
     <row r="108" spans="1:16">
@@ -6794,7 +6785,7 @@
         <v>-1.164182632644362</v>
       </c>
       <c r="D108" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E108">
         <v>0.204597470791132</v>
@@ -6830,7 +6821,7 @@
         <v>1</v>
       </c>
       <c r="P108" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
     </row>
     <row r="109" spans="1:16">
@@ -6880,7 +6871,7 @@
         <v>1</v>
       </c>
       <c r="P109" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
     </row>
     <row r="110" spans="1:16">
@@ -6930,7 +6921,7 @@
         <v>1</v>
       </c>
       <c r="P110" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
     </row>
     <row r="111" spans="1:16">
@@ -6944,7 +6935,7 @@
         <v>-1.330656541117063</v>
       </c>
       <c r="D111" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E111">
         <v>0.1498300706466971</v>
@@ -6980,7 +6971,7 @@
         <v>1</v>
       </c>
       <c r="P111" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
     </row>
     <row r="112" spans="1:16">
@@ -6994,7 +6985,7 @@
         <v>-1.089957636312631</v>
       </c>
       <c r="D112" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E112">
         <v>0.1498300706466971</v>
@@ -7030,7 +7021,7 @@
         <v>1</v>
       </c>
       <c r="P112" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
     </row>
     <row r="113" spans="1:16">
@@ -7044,7 +7035,7 @@
         <v>1.663161219313913</v>
       </c>
       <c r="D113" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E113">
         <v>1.394552474924428</v>
@@ -7080,7 +7071,7 @@
         <v>1</v>
       </c>
       <c r="P113" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
     </row>
     <row r="114" spans="1:16">
@@ -7094,7 +7085,7 @@
         <v>2.020453841772007</v>
       </c>
       <c r="D114" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E114">
         <v>1.394552474924428</v>
@@ -7130,7 +7121,7 @@
         <v>1</v>
       </c>
       <c r="P114" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
     </row>
     <row r="115" spans="1:16">
@@ -7180,7 +7171,7 @@
         <v>1</v>
       </c>
       <c r="P115" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
     </row>
     <row r="116" spans="1:16">
@@ -7230,7 +7221,7 @@
         <v>1</v>
       </c>
       <c r="P116" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
     </row>
     <row r="117" spans="1:16">
@@ -7280,7 +7271,7 @@
         <v>1</v>
       </c>
       <c r="P117" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
     </row>
     <row r="118" spans="1:16">
@@ -7330,7 +7321,7 @@
         <v>1</v>
       </c>
       <c r="P118" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
     </row>
     <row r="119" spans="1:16">
@@ -7380,7 +7371,7 @@
         <v>1</v>
       </c>
       <c r="P119" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
     </row>
     <row r="120" spans="1:16">
@@ -7430,7 +7421,7 @@
         <v>1</v>
       </c>
       <c r="P120" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="121" spans="1:16">
@@ -7480,7 +7471,7 @@
         <v>1</v>
       </c>
       <c r="P121" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="122" spans="1:16">
@@ -7530,7 +7521,7 @@
         <v>1</v>
       </c>
       <c r="P122" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="123" spans="1:16">
@@ -7580,7 +7571,7 @@
         <v>1</v>
       </c>
       <c r="P123" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="124" spans="1:16">
@@ -7630,7 +7621,7 @@
         <v>1</v>
       </c>
       <c r="P124" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="125" spans="1:16">
@@ -7744,7 +7735,7 @@
         <v>1.583716178161136</v>
       </c>
       <c r="D127" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E127">
         <v>1.731188504841963</v>
@@ -7794,7 +7785,7 @@
         <v>1.943294205912665</v>
       </c>
       <c r="D128" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E128">
         <v>1.731188504841963</v>
@@ -7844,7 +7835,7 @@
         <v>1.440029121201585</v>
       </c>
       <c r="D129" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E129">
         <v>1.731188504841963</v>
@@ -7930,7 +7921,7 @@
         <v>1</v>
       </c>
       <c r="P130" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="131" spans="1:16">
@@ -7980,7 +7971,7 @@
         <v>1</v>
       </c>
       <c r="P131" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="132" spans="1:16">
@@ -8030,7 +8021,7 @@
         <v>1</v>
       </c>
       <c r="P132" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="133" spans="1:16">
@@ -8080,7 +8071,7 @@
         <v>1</v>
       </c>
       <c r="P133" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="134" spans="1:16">
@@ -8130,7 +8121,7 @@
         <v>1</v>
       </c>
       <c r="P134" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="135" spans="1:16">
@@ -8144,7 +8135,7 @@
         <v>-0.8820242128746258</v>
       </c>
       <c r="D135" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E135">
         <v>0.3526024044326252</v>
@@ -8180,7 +8171,7 @@
         <v>1</v>
       </c>
       <c r="P135" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="136" spans="1:16">
@@ -8194,7 +8185,7 @@
         <v>-1.173427909927172</v>
       </c>
       <c r="D136" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E136">
         <v>0.3526024044326252</v>
@@ -8230,7 +8221,7 @@
         <v>1</v>
       </c>
       <c r="P136" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="137" spans="1:16">
@@ -8280,7 +8271,7 @@
         <v>1</v>
       </c>
       <c r="P137" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="138" spans="1:16">
@@ -8330,7 +8321,7 @@
         <v>1</v>
       </c>
       <c r="P138" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="139" spans="1:16">
@@ -8380,7 +8371,7 @@
         <v>1</v>
       </c>
       <c r="P139" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="140" spans="1:16">
@@ -8694,7 +8685,7 @@
         <v>1.916709703800588</v>
       </c>
       <c r="D146" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E146">
         <v>1.625228926806798</v>
@@ -8744,7 +8735,7 @@
         <v>1.775844332123576</v>
       </c>
       <c r="D147" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E147">
         <v>1.625228926806798</v>
@@ -8794,7 +8785,7 @@
         <v>1.706459737440355</v>
       </c>
       <c r="D148" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E148">
         <v>1.625228926806798</v>
@@ -8844,7 +8835,7 @@
         <v>1.898407474064776</v>
       </c>
       <c r="D149" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E149">
         <v>1.579058157468399</v>
@@ -8880,7 +8871,7 @@
         <v>1</v>
       </c>
       <c r="P149" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="150" spans="1:16">
@@ -8894,7 +8885,7 @@
         <v>1.757671173119327</v>
       </c>
       <c r="D150" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E150">
         <v>1.579058157468399</v>
@@ -8930,7 +8921,7 @@
         <v>1</v>
       </c>
       <c r="P150" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="151" spans="1:16">
@@ -8944,7 +8935,7 @@
         <v>1.688493091606606</v>
       </c>
       <c r="D151" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E151">
         <v>1.579058157468399</v>
@@ -8980,7 +8971,7 @@
         <v>1</v>
       </c>
       <c r="P151" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="152" spans="1:16">
@@ -9030,7 +9021,7 @@
         <v>1</v>
       </c>
       <c r="P152" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
     </row>
     <row r="153" spans="1:16">
@@ -9080,7 +9071,7 @@
         <v>1</v>
       </c>
       <c r="P153" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
     </row>
     <row r="154" spans="1:16">
@@ -9130,7 +9121,7 @@
         <v>1</v>
       </c>
       <c r="P154" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
     </row>
     <row r="155" spans="1:16">
@@ -9180,7 +9171,7 @@
         <v>1</v>
       </c>
       <c r="P155" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
     </row>
     <row r="156" spans="1:16">
@@ -9230,7 +9221,7 @@
         <v>1</v>
       </c>
       <c r="P156" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
     </row>
     <row r="157" spans="1:16">
@@ -9280,7 +9271,7 @@
         <v>1</v>
       </c>
       <c r="P157" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
     </row>
     <row r="158" spans="1:16">
@@ -9430,7 +9421,7 @@
         <v>1</v>
       </c>
       <c r="P160" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
     </row>
     <row r="161" spans="1:16">
@@ -9480,7 +9471,7 @@
         <v>1</v>
       </c>
       <c r="P161" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
     </row>
     <row r="162" spans="1:16">
@@ -9530,7 +9521,7 @@
         <v>1</v>
       </c>
       <c r="P162" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
     </row>
     <row r="163" spans="1:16">
@@ -9580,7 +9571,7 @@
         <v>1</v>
       </c>
       <c r="P163" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
     </row>
     <row r="164" spans="1:16">
@@ -9594,7 +9585,7 @@
         <v>2.0418888555804</v>
       </c>
       <c r="D164" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E164">
         <v>2.091052252009925</v>
@@ -9644,7 +9635,7 @@
         <v>2.437529947263654</v>
       </c>
       <c r="D165" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E165">
         <v>2.091052252009925</v>
@@ -9694,7 +9685,7 @@
         <v>2.035427646090795</v>
       </c>
       <c r="D166" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E166">
         <v>1.677256780401082</v>
@@ -9730,7 +9721,7 @@
         <v>1</v>
       </c>
       <c r="P166" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
     </row>
     <row r="167" spans="1:16">
@@ -9744,7 +9735,7 @@
         <v>2.4319519246827</v>
       </c>
       <c r="D167" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E167">
         <v>1.677256780401082</v>
@@ -9780,7 +9771,7 @@
         <v>1</v>
       </c>
       <c r="P167" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
     </row>
     <row r="168" spans="1:16">
@@ -9830,7 +9821,7 @@
         <v>1</v>
       </c>
       <c r="P168" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
     </row>
     <row r="169" spans="1:16">
@@ -9880,7 +9871,7 @@
         <v>1</v>
       </c>
       <c r="P169" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
     </row>
     <row r="170" spans="1:16">
@@ -9930,7 +9921,7 @@
         <v>1</v>
       </c>
       <c r="P170" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="171" spans="1:16">
@@ -9980,7 +9971,7 @@
         <v>1</v>
       </c>
       <c r="P171" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="172" spans="1:16">
@@ -10030,7 +10021,7 @@
         <v>1</v>
       </c>
       <c r="P172" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="173" spans="1:16">
@@ -10044,7 +10035,7 @@
         <v>2.053037839433713</v>
       </c>
       <c r="D173" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E173">
         <v>2.029053723158555</v>
@@ -10080,7 +10071,7 @@
         <v>1</v>
       </c>
       <c r="P173" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="174" spans="1:16">
@@ -10194,7 +10185,7 @@
         <v>2.072439051471395</v>
       </c>
       <c r="D176" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E176">
         <v>2.198537473651809</v>
@@ -10230,7 +10221,7 @@
         <v>1</v>
       </c>
       <c r="P176" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="177" spans="1:16">
@@ -10244,7 +10235,7 @@
         <v>2.176038435736924</v>
       </c>
       <c r="D177" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E177">
         <v>2.198537473651809</v>
@@ -10280,7 +10271,7 @@
         <v>1</v>
       </c>
       <c r="P177" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="178" spans="1:16">
@@ -10330,7 +10321,7 @@
         <v>1</v>
       </c>
       <c r="P178" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
     </row>
     <row r="179" spans="1:16">
@@ -10394,7 +10385,7 @@
         <v>2.199572666349018</v>
       </c>
       <c r="D180" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E180">
         <v>2.369622868222606</v>
@@ -10594,7 +10585,7 @@
         <v>2.441204477380014</v>
       </c>
       <c r="D184" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E184">
         <v>3.019740173907834</v>
@@ -10694,7 +10685,7 @@
         <v>2.450942264059425</v>
       </c>
       <c r="D186" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E186">
         <v>3.396065694761221</v>
@@ -10744,7 +10735,7 @@
         <v>2.93271297523739</v>
       </c>
       <c r="D187" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E187">
         <v>3.396065694761221</v>
@@ -10844,7 +10835,7 @@
         <v>2.613291041571109</v>
       </c>
       <c r="D189" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E189">
         <v>1.747095958240026</v>
@@ -10894,7 +10885,7 @@
         <v>2.94332933323569</v>
       </c>
       <c r="D190" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E190">
         <v>3.513960124909904</v>
@@ -11044,7 +11035,7 @@
         <v>2.630002520413537</v>
       </c>
       <c r="D193" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E193">
         <v>1.763414225815572</v>
@@ -11094,7 +11085,7 @@
         <v>2.960405936825934</v>
       </c>
       <c r="D194" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E194">
         <v>2.688557154970242</v>
@@ -11294,7 +11285,7 @@
         <v>2.642059072099817</v>
       </c>
       <c r="D198" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E198">
         <v>1.775187093932763</v>
@@ -11344,7 +11335,7 @@
         <v>2.972725908969226</v>
       </c>
       <c r="D199" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E199">
         <v>2.375803028433923</v>
@@ -11494,7 +11485,7 @@
         <v>2.666955617984192</v>
       </c>
       <c r="D202" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E202">
         <v>1.799497838737505</v>
@@ -11544,7 +11535,7 @@
         <v>2.998166412998973</v>
       </c>
       <c r="D203" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E203">
         <v>1.736641978102437</v>
@@ -11694,7 +11685,7 @@
         <v>2.973643871143521</v>
       </c>
       <c r="D206" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E206">
         <v>1.818524938691256</v>
@@ -11744,7 +11735,7 @@
         <v>3.018077732744034</v>
       </c>
       <c r="D207" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E207">
         <v>1.759533446033025</v>
@@ -11894,7 +11885,7 @@
         <v>2.990082102112254</v>
       </c>
       <c r="D210" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E210">
         <v>1.83485077149952</v>
@@ -11944,7 +11935,7 @@
         <v>3.03516225313547</v>
       </c>
       <c r="D211" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E211">
         <v>1.779175024575153</v>
@@ -12030,7 +12021,7 @@
         <v>1</v>
       </c>
       <c r="P212" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="213" spans="1:16">
@@ -12080,7 +12071,7 @@
         <v>1</v>
       </c>
       <c r="P213" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="214" spans="1:16">
@@ -12094,7 +12085,7 @@
         <v>3.005496469975766</v>
       </c>
       <c r="D214" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E214">
         <v>1.850159741975929</v>
@@ -12130,7 +12121,7 @@
         <v>1</v>
       </c>
       <c r="P214" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="215" spans="1:16">
@@ -12144,7 +12135,7 @@
         <v>3.051182655974811</v>
       </c>
       <c r="D215" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E215">
         <v>1.797593217971041</v>
@@ -12180,7 +12171,7 @@
         <v>1</v>
       </c>
       <c r="P215" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="216" spans="1:16">
@@ -12294,7 +12285,7 @@
         <v>3.018931533510157</v>
       </c>
       <c r="D218" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E218">
         <v>1.863502941828035</v>
@@ -12344,7 +12335,7 @@
         <v>3.06514593568235</v>
       </c>
       <c r="D219" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E219">
         <v>1.813646396450594</v>
@@ -12494,7 +12485,7 @@
         <v>3.033933076549712</v>
       </c>
       <c r="D222" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E222">
         <v>1.878401910214327</v>
@@ -12544,7 +12535,7 @@
         <v>3.080737282978161</v>
       </c>
       <c r="D223" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E223">
         <v>1.831571317108114</v>
@@ -12594,7 +12585,7 @@
         <v>1.639859271051932</v>
       </c>
       <c r="D224" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E224">
         <v>1.9209216037227</v>
@@ -12744,7 +12735,7 @@
         <v>3.05833801181463</v>
       </c>
       <c r="D227" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E227">
         <v>1.902639974127007</v>
@@ -12794,7 +12785,7 @@
         <v>3.106101728518452</v>
       </c>
       <c r="D228" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E228">
         <v>1.860732085911838</v>
@@ -12880,7 +12871,7 @@
         <v>1</v>
       </c>
       <c r="P229" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="230" spans="1:16">
@@ -12930,7 +12921,7 @@
         <v>1</v>
       </c>
       <c r="P230" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="231" spans="1:16">
@@ -12944,7 +12935,7 @@
         <v>3.085055612872655</v>
       </c>
       <c r="D231" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E231">
         <v>1.929174890733353</v>
@@ -12980,7 +12971,7 @@
         <v>1</v>
       </c>
       <c r="P231" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="232" spans="1:16">
@@ -12994,7 +12985,7 @@
         <v>3.13386976517363</v>
       </c>
       <c r="D232" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E232">
         <v>1.892656193842708</v>
@@ -13030,7 +13021,7 @@
         <v>1</v>
       </c>
       <c r="P232" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="233" spans="1:16">
@@ -13094,7 +13085,7 @@
         <v>3.103034611570727</v>
       </c>
       <c r="D234" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E234">
         <v>1.947030956106994</v>
@@ -13144,7 +13135,7 @@
         <v>3.152555630487182</v>
       </c>
       <c r="D235" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E235">
         <v>1.914138792287073</v>
@@ -13194,7 +13185,7 @@
         <v>1.641725609550694</v>
       </c>
       <c r="D236" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E236">
         <v>1.89319910743864</v>
@@ -13280,7 +13271,7 @@
         <v>1</v>
       </c>
       <c r="P237" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="238" spans="1:16">
@@ -13294,7 +13285,7 @@
         <v>3.11979974827751</v>
       </c>
       <c r="D238" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E238">
         <v>1.963681459400396</v>
@@ -13330,7 +13321,7 @@
         <v>1</v>
       </c>
       <c r="P238" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="239" spans="1:16">
@@ -13344,7 +13335,7 @@
         <v>3.169979909320897</v>
       </c>
       <c r="D239" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E239">
         <v>1.934170981275177</v>
@@ -13380,7 +13371,7 @@
         <v>1</v>
       </c>
       <c r="P239" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="240" spans="1:16">
@@ -13394,7 +13385,7 @@
         <v>1.664480342106565</v>
       </c>
       <c r="D240" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E240">
         <v>2.221652319966786</v>
@@ -13430,7 +13421,7 @@
         <v>1</v>
       </c>
       <c r="P240" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="241" spans="1:16">
@@ -13494,7 +13485,7 @@
         <v>3.136490860930856</v>
       </c>
       <c r="D242" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E242">
         <v>1.980258444787738</v>
@@ -13544,7 +13535,7 @@
         <v>3.187327253753777</v>
       </c>
       <c r="D243" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E243">
         <v>1.954114721009688</v>
@@ -13744,7 +13735,7 @@
         <v>3.154470288152615</v>
       </c>
       <c r="D247" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E247">
         <v>1.998114935754989</v>
@@ -13794,7 +13785,7 @@
         <v>3.206013564438956</v>
       </c>
       <c r="D248" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E248">
         <v>1.975597831484915</v>
@@ -13980,7 +13971,7 @@
         <v>1</v>
       </c>
       <c r="P251" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="252" spans="1:16">
@@ -14030,7 +14021,7 @@
         <v>1</v>
       </c>
       <c r="P252" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="253" spans="1:16">
@@ -14044,7 +14035,7 @@
         <v>3.175183381627829</v>
       </c>
       <c r="D253" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E253">
         <v>2.406837822852639</v>
@@ -14080,7 +14071,7 @@
         <v>1</v>
       </c>
       <c r="P253" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="254" spans="1:16">
@@ -14094,7 +14085,7 @@
         <v>3.227541018854222</v>
       </c>
       <c r="D254" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E254">
         <v>2.000347322662993</v>
@@ -14130,7 +14121,7 @@
         <v>1</v>
       </c>
       <c r="P254" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="255" spans="1:16">
@@ -14180,7 +14171,7 @@
         <v>1</v>
       </c>
       <c r="P255" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="256" spans="1:16">
@@ -14230,7 +14221,7 @@
         <v>1</v>
       </c>
       <c r="P256" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="257" spans="1:16">
@@ -14344,7 +14335,7 @@
         <v>3.194491499183421</v>
       </c>
       <c r="D259" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E259">
         <v>2.42485873257119</v>
@@ -14394,7 +14385,7 @@
         <v>3.247608258980375</v>
       </c>
       <c r="D260" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E260">
         <v>2.023418047742236</v>
@@ -14644,7 +14635,7 @@
         <v>3.213727962726566</v>
       </c>
       <c r="D265" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E265">
         <v>2.442812765211459</v>
@@ -14694,7 +14685,7 @@
         <v>3.26760102792778</v>
       </c>
       <c r="D266" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E266">
         <v>2.046403155463022</v>
@@ -14894,7 +14885,7 @@
         <v>3.233647867837396</v>
       </c>
       <c r="D270" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E270">
         <v>2.461404676648234</v>
@@ -14944,7 +14935,7 @@
         <v>3.288304108795105</v>
       </c>
       <c r="D271" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E271">
         <v>2.070204888236475</v>
@@ -15144,7 +15135,7 @@
         <v>3.249417008017017</v>
       </c>
       <c r="D275" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E275">
         <v>2.476122540815881</v>
@@ -15194,7 +15185,7 @@
         <v>3.304693232263839</v>
       </c>
       <c r="D276" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E276">
         <v>2.089046989066485</v>
@@ -15344,7 +15335,7 @@
         <v>1.914875661806953</v>
       </c>
       <c r="D279" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E279">
         <v>2.109898465499843</v>
@@ -15430,7 +15421,7 @@
         <v>1</v>
       </c>
       <c r="P280" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="281" spans="1:16">
@@ -15444,7 +15435,7 @@
         <v>3.261163134684622</v>
       </c>
       <c r="D281" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E281">
         <v>2.487085592372312</v>
@@ -15480,7 +15471,7 @@
         <v>1</v>
       </c>
       <c r="P281" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="282" spans="1:16">
@@ -15494,7 +15485,7 @@
         <v>3.316901172458547</v>
       </c>
       <c r="D282" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E282">
         <v>2.103082104520595</v>
@@ -15530,7 +15521,7 @@
         <v>1</v>
       </c>
       <c r="P282" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="283" spans="1:16">
@@ -15580,7 +15571,7 @@
         <v>1</v>
       </c>
       <c r="P283" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="284" spans="1:16">
@@ -15630,7 +15621,7 @@
         <v>1</v>
       </c>
       <c r="P284" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="285" spans="1:16">
@@ -15644,7 +15635,7 @@
         <v>1.930296217842372</v>
       </c>
       <c r="D285" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E285">
         <v>2.383746445952788</v>
@@ -15680,7 +15671,7 @@
         <v>1</v>
       </c>
       <c r="P285" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="286" spans="1:16">
@@ -15730,7 +15721,7 @@
         <v>1</v>
       </c>
       <c r="P286" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="287" spans="1:16">
@@ -15744,7 +15735,7 @@
         <v>3.267778188252251</v>
       </c>
       <c r="D287" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E287">
         <v>2.493259642368766</v>
@@ -15780,7 +15771,7 @@
         <v>1</v>
       </c>
       <c r="P287" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="288" spans="1:16">
@@ -15794,7 +15785,7 @@
         <v>3.323776305055329</v>
       </c>
       <c r="D288" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E288">
         <v>2.110986245450121</v>
@@ -15830,7 +15821,7 @@
         <v>1</v>
       </c>
       <c r="P288" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="289" spans="1:16">
@@ -15880,7 +15871,7 @@
         <v>1</v>
       </c>
       <c r="P289" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="290" spans="1:16">
@@ -15930,7 +15921,7 @@
         <v>1</v>
       </c>
       <c r="P290" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="291" spans="1:16">
@@ -15980,7 +15971,7 @@
         <v>1</v>
       </c>
       <c r="P291" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="292" spans="1:16">
@@ -15994,7 +15985,7 @@
         <v>3.278598009747792</v>
       </c>
       <c r="D292" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E292">
         <v>2.503358142431271</v>
@@ -16044,7 +16035,7 @@
         <v>3.335021521242147</v>
       </c>
       <c r="D293" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E293">
         <v>2.123914544980693</v>
@@ -16194,7 +16185,7 @@
         <v>1.953185079463765</v>
       </c>
       <c r="D296" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E296">
         <v>1.673185079463764</v>
@@ -16244,7 +16235,7 @@
         <v>1.838424946780282</v>
       </c>
       <c r="D297" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E297">
         <v>1.673185079463764</v>
@@ -16294,7 +16285,7 @@
         <v>3.286491586851236</v>
       </c>
       <c r="D298" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E298">
         <v>2.510725481061151</v>
@@ -16344,7 +16335,7 @@
         <v>3.343225444112052</v>
       </c>
       <c r="D299" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E299">
         <v>2.133346357622241</v>
@@ -16494,7 +16485,7 @@
         <v>1.963547929404697</v>
       </c>
       <c r="D302" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E302">
         <v>2.040362444937774</v>
@@ -16544,7 +16535,7 @@
         <v>1.849314035194777</v>
       </c>
       <c r="D303" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E303">
         <v>2.040362444937774</v>
@@ -16594,7 +16585,7 @@
         <v>3.287218803551511</v>
       </c>
       <c r="D304" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E304">
         <v>2.511404216648074</v>
@@ -16644,7 +16635,7 @@
         <v>3.34398125223815</v>
       </c>
       <c r="D305" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E305">
         <v>2.134215288346162</v>
@@ -16794,7 +16785,7 @@
         <v>1.964502634406085</v>
       </c>
       <c r="D308" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E308">
         <v>2.034789980466009</v>
@@ -16844,7 +16835,7 @@
         <v>1.850317221309513</v>
       </c>
       <c r="D309" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E309">
         <v>2.034789980466009</v>
@@ -16894,7 +16885,7 @@
         <v>3.309574328279867</v>
       </c>
       <c r="D310" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E310">
         <v>2.532269373061208</v>
@@ -16944,7 +16935,7 @@
         <v>3.367215712126766</v>
       </c>
       <c r="D311" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E311">
         <v>2.160927274303631</v>
@@ -17194,7 +17185,7 @@
         <v>3.386581638751728</v>
       </c>
       <c r="D316" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E316">
         <v>2.183191719551736</v>
@@ -17294,7 +17285,7 @@
         <v>2.018313648949551</v>
       </c>
       <c r="D318" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E318">
         <v>2.020805677582523</v>
@@ -17344,7 +17335,7 @@
         <v>1.906860826435267</v>
       </c>
       <c r="D319" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E319">
         <v>2.020805677582523</v>
@@ -17394,7 +17385,7 @@
         <v>1.784750528729781</v>
       </c>
       <c r="D320" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E320">
         <v>2.020805677582523</v>
@@ -17444,7 +17435,7 @@
         <v>3.376305833526885</v>
       </c>
       <c r="D321" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E321">
         <v>2.171377923742256</v>
@@ -17480,7 +17471,7 @@
         <v>1</v>
       </c>
       <c r="P321" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="322" spans="1:16">
@@ -17530,7 +17521,7 @@
         <v>1</v>
       </c>
       <c r="P322" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="323" spans="1:16">
@@ -17580,7 +17571,7 @@
         <v>1</v>
       </c>
       <c r="P323" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="324" spans="1:16">
@@ -17630,7 +17621,7 @@
         <v>1</v>
       </c>
       <c r="P324" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="325" spans="1:16">
@@ -17644,7 +17635,7 @@
         <v>3.346413966869674</v>
       </c>
       <c r="D325" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E325">
         <v>2.137012109937338</v>
@@ -17680,7 +17671,7 @@
         <v>1</v>
       </c>
       <c r="P325" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="326" spans="1:16">
@@ -17730,7 +17721,7 @@
         <v>1</v>
       </c>
       <c r="P326" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="327" spans="1:16">
@@ -17744,7 +17735,7 @@
         <v>1.853546169841817</v>
       </c>
       <c r="D327" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E327">
         <v>1.909412654865697</v>
@@ -17780,7 +17771,7 @@
         <v>1</v>
       </c>
       <c r="P327" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="328" spans="1:16">
@@ -17794,7 +17785,7 @@
         <v>1.729057523143315</v>
       </c>
       <c r="D328" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E328">
         <v>1.909412654865697</v>
@@ -17830,7 +17821,7 @@
         <v>1</v>
       </c>
       <c r="P328" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="329" spans="1:16">
@@ -17844,7 +17835,7 @@
         <v>1.90213361560998</v>
       </c>
       <c r="D329" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E329">
         <v>1.909412654865697</v>
@@ -17880,7 +17871,7 @@
         <v>1</v>
       </c>
       <c r="P329" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="330" spans="1:16">
@@ -17894,7 +17885,7 @@
         <v>3.335708401471214</v>
       </c>
       <c r="D330" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E330">
         <v>2.124704231296676</v>
@@ -17930,7 +17921,7 @@
         <v>1</v>
       </c>
       <c r="P330" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
     </row>
     <row r="331" spans="1:16">
@@ -17980,7 +17971,7 @@
         <v>1</v>
       </c>
       <c r="P331" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
     </row>
     <row r="332" spans="1:16">
@@ -17994,7 +17985,7 @@
         <v>1.839336644715903</v>
       </c>
       <c r="D332" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E332">
         <v>2.572020438006287</v>
@@ -18030,7 +18021,7 @@
         <v>1</v>
       </c>
       <c r="P332" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
     </row>
     <row r="333" spans="1:16">
@@ -18044,7 +18035,7 @@
         <v>1.714214115855647</v>
       </c>
       <c r="D333" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E333">
         <v>2.572020438006287</v>
@@ -18080,7 +18071,7 @@
         <v>1</v>
       </c>
       <c r="P333" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
     </row>
     <row r="334" spans="1:16">
@@ -18094,7 +18085,7 @@
         <v>1.88846993345668</v>
       </c>
       <c r="D334" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E334">
         <v>2.572020438006287</v>
@@ -18130,7 +18121,7 @@
         <v>1</v>
       </c>
       <c r="P334" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
     </row>
     <row r="335" spans="1:16">
@@ -18144,7 +18135,7 @@
         <v>3.319807569063805</v>
       </c>
       <c r="D335" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E335">
         <v>2.106423504565129</v>
@@ -18244,7 +18235,7 @@
         <v>1.818231428017253</v>
       </c>
       <c r="D337" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E337">
         <v>2.552327466291189</v>
@@ -18294,7 +18285,7 @@
         <v>1.692167402501294</v>
       </c>
       <c r="D338" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E338">
         <v>2.552327466291189</v>
@@ -18344,7 +18335,7 @@
         <v>1.86817544998933</v>
       </c>
       <c r="D339" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E339">
         <v>2.552327466291189</v>
@@ -18394,7 +18385,7 @@
         <v>3.297653300651016</v>
       </c>
       <c r="D340" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E340">
         <v>2.080953383478715</v>
@@ -18430,7 +18421,7 @@
         <v>1</v>
       </c>
       <c r="P340" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="341" spans="1:16">
@@ -18480,7 +18471,7 @@
         <v>1</v>
       </c>
       <c r="P341" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="342" spans="1:16">
@@ -18494,7 +18485,7 @@
         <v>1.788826009252247</v>
       </c>
       <c r="D342" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E342">
         <v>2.524889696365481</v>
@@ -18530,7 +18521,7 @@
         <v>1</v>
       </c>
       <c r="P342" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="343" spans="1:16">
@@ -18544,7 +18535,7 @@
         <v>1.661450217843427</v>
       </c>
       <c r="D343" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E343">
         <v>2.524889696365481</v>
@@ -18580,7 +18571,7 @@
         <v>1</v>
       </c>
       <c r="P343" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="344" spans="1:16">
@@ -18594,7 +18585,7 @@
         <v>1.839899607409848</v>
       </c>
       <c r="D344" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E344">
         <v>2.524889696365481</v>
@@ -18630,7 +18621,7 @@
         <v>1</v>
       </c>
       <c r="P344" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="345" spans="1:16">
@@ -18644,7 +18635,7 @@
         <v>3.263703117123406</v>
       </c>
       <c r="D345" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E345">
         <v>2.041921840245493</v>
@@ -18744,7 +18735,7 @@
         <v>1.743763841313463</v>
       </c>
       <c r="D347" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E347">
         <v>2.48284284077948</v>
@@ -18794,7 +18785,7 @@
         <v>1.614377841669459</v>
       </c>
       <c r="D348" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E348">
         <v>2.48284284077948</v>
@@ -18844,7 +18835,7 @@
         <v>1.796568452118031</v>
       </c>
       <c r="D349" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E349">
         <v>2.48284284077948</v>
@@ -18894,7 +18885,7 @@
         <v>3.242126022559422</v>
       </c>
       <c r="D350" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E350">
         <v>2.017115279225386</v>
@@ -18930,7 +18921,7 @@
         <v>1</v>
       </c>
       <c r="P350" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="351" spans="1:16">
@@ -18980,7 +18971,7 @@
         <v>1</v>
       </c>
       <c r="P351" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="352" spans="1:16">
@@ -18994,7 +18985,7 @@
         <v>1.715124506916858</v>
       </c>
       <c r="D352" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E352">
         <v>2.456119893071122</v>
@@ -19030,7 +19021,7 @@
         <v>1</v>
       </c>
       <c r="P352" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="353" spans="1:16">
@@ -19044,7 +19035,7 @@
         <v>1.584460916147354</v>
       </c>
       <c r="D353" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E353">
         <v>2.456119893071122</v>
@@ -19080,7 +19071,7 @@
         <v>1</v>
       </c>
       <c r="P353" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="354" spans="1:16">
@@ -19094,7 +19085,7 @@
         <v>1.769029265635051</v>
       </c>
       <c r="D354" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E354">
         <v>2.456119893071122</v>
@@ -19130,7 +19121,7 @@
         <v>1</v>
       </c>
       <c r="P354" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="355" spans="1:16">
@@ -19144,7 +19135,7 @@
         <v>3.218796578894542</v>
       </c>
       <c r="D355" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E355">
         <v>1.990294093169876</v>
@@ -19244,7 +19235,7 @@
         <v>1.684159274947191</v>
       </c>
       <c r="D357" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E357">
         <v>2.427226684058535</v>
@@ -19294,7 +19285,7 @@
         <v>1.552114335539635</v>
       </c>
       <c r="D358" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E358">
         <v>2.427226684058535</v>
@@ -19344,7 +19335,7 @@
         <v>1.739253528325928</v>
       </c>
       <c r="D359" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E359">
         <v>2.427226684058535</v>
@@ -19394,7 +19385,7 @@
         <v>3.223084813618858</v>
       </c>
       <c r="D360" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E360">
         <v>1.995224152499308</v>
@@ -19430,7 +19421,7 @@
         <v>1</v>
       </c>
       <c r="P360" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="361" spans="1:16">
@@ -19444,7 +19435,7 @@
         <v>1.689851060181606</v>
       </c>
       <c r="D361" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E361">
         <v>2.432537606340457</v>
@@ -19480,7 +19471,7 @@
         <v>1</v>
       </c>
       <c r="P361" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="362" spans="1:16">
@@ -19494,7 +19485,7 @@
         <v>1.558060029409038</v>
       </c>
       <c r="D362" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E362">
         <v>2.432537606340457</v>
@@ -19530,7 +19521,7 @@
         <v>1</v>
       </c>
       <c r="P362" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="363" spans="1:16">
@@ -19544,7 +19535,7 @@
         <v>1.5546355793606</v>
       </c>
       <c r="D363" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E363">
         <v>2.429478755941318</v>
@@ -19594,7 +19585,7 @@
         <v>2.749895863416445</v>
       </c>
       <c r="D364" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E364">
         <v>2.144120683335579</v>
@@ -19630,7 +19621,7 @@
         <v>1</v>
       </c>
       <c r="P364" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="365" spans="1:16">
@@ -19644,7 +19635,7 @@
         <v>1.575757316392718</v>
       </c>
       <c r="D365" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E365">
         <v>2.448345503254703</v>
@@ -19680,7 +19671,7 @@
         <v>1</v>
       </c>
       <c r="P365" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="366" spans="1:16">
@@ -19694,7 +19685,7 @@
         <v>1.708690594836302</v>
       </c>
       <c r="D366" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E366">
         <v>1.95524223097577</v>
@@ -19730,7 +19721,7 @@
         <v>1</v>
       </c>
       <c r="P366" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="367" spans="1:16">
@@ -19744,7 +19735,7 @@
         <v>2.776972324350222</v>
       </c>
       <c r="D367" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E367">
         <v>2.170167242074328</v>
@@ -19780,7 +19771,7 @@
         <v>1</v>
       </c>
       <c r="P367" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="368" spans="1:16">
@@ -19794,7 +19785,7 @@
         <v>1.603764011567165</v>
       </c>
       <c r="D368" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E368">
         <v>2.473362159798427</v>
@@ -19830,7 +19821,7 @@
         <v>1</v>
       </c>
       <c r="P368" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="369" spans="1:16">
@@ -19844,7 +19835,7 @@
         <v>1.733308579562596</v>
       </c>
       <c r="D369" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E369">
         <v>2.069952921130998</v>
@@ -19880,7 +19871,7 @@
         <v>1</v>
       </c>
       <c r="P369" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="370" spans="1:16">
@@ -19894,7 +19885,7 @@
         <v>2.804318151096002</v>
       </c>
       <c r="D370" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E370">
         <v>2.196472920808915</v>
@@ -19930,7 +19921,7 @@
         <v>1</v>
       </c>
       <c r="P370" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="371" spans="1:16">
@@ -19944,7 +19935,7 @@
         <v>1.632049326839176</v>
       </c>
       <c r="D371" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E371">
         <v>2.498627690521825</v>
@@ -19980,7 +19971,7 @@
         <v>1</v>
       </c>
       <c r="P371" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="372" spans="1:16">
@@ -19994,7 +19985,7 @@
         <v>1.758171472346181</v>
       </c>
       <c r="D372" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E372">
         <v>2.648741745065742</v>
@@ -20030,7 +20021,7 @@
         <v>1</v>
       </c>
       <c r="P372" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="373" spans="1:16">
@@ -20044,7 +20035,7 @@
         <v>1.836308899819077</v>
       </c>
       <c r="D373" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E373">
         <v>2.387421432319158</v>
@@ -20080,7 +20071,7 @@
         <v>1</v>
       </c>
       <c r="P373" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="374" spans="1:16">
@@ -20130,7 +20121,7 @@
         <v>1</v>
       </c>
       <c r="P374" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="375" spans="1:16">
@@ -20144,7 +20135,7 @@
         <v>1.66686196794393</v>
       </c>
       <c r="D375" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E375">
         <v>2.529723679551338</v>
@@ -20180,7 +20171,7 @@
         <v>1</v>
       </c>
       <c r="P375" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="376" spans="1:16">
@@ -20194,7 +20185,7 @@
         <v>1.844881242140559</v>
       </c>
       <c r="D376" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E376">
         <v>2.529723679551338</v>
@@ -20230,7 +20221,7 @@
         <v>1</v>
       </c>
       <c r="P376" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="377" spans="1:16">
@@ -20244,7 +20235,7 @@
         <v>1.788771907765661</v>
       </c>
       <c r="D377" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E377">
         <v>2.679961622497764</v>
@@ -20280,7 +20271,7 @@
         <v>1</v>
       </c>
       <c r="P377" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="378" spans="1:16">
@@ -20294,7 +20285,7 @@
         <v>1.861508767932467</v>
       </c>
       <c r="D378" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E378">
         <v>2.411732640096055</v>
@@ -20330,7 +20321,7 @@
         <v>1</v>
       </c>
       <c r="P378" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="379" spans="1:16">
@@ -20380,7 +20371,7 @@
         <v>1</v>
       </c>
       <c r="P379" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="380" spans="1:16">
@@ -20394,7 +20385,7 @@
         <v>1.693616991646184</v>
       </c>
       <c r="D380" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E380">
         <v>2.55362229502915</v>
@@ -20430,7 +20421,7 @@
         <v>1</v>
       </c>
       <c r="P380" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="381" spans="1:16">
@@ -20444,7 +20435,7 @@
         <v>1.869509828609061</v>
       </c>
       <c r="D381" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E381">
         <v>2.55362229502915</v>
@@ -20480,7 +20471,7 @@
         <v>1</v>
       </c>
       <c r="P381" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="382" spans="1:16">
@@ -20494,7 +20485,7 @@
         <v>2.574954921244757</v>
       </c>
       <c r="D382" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E382">
         <v>2.17950982860906</v>
@@ -20530,7 +20521,7 @@
         <v>1</v>
       </c>
       <c r="P382" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="383" spans="1:16">
@@ -20544,7 +20535,7 @@
         <v>1.812289668813548</v>
       </c>
       <c r="D383" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E383">
         <v>2.703955451583056</v>
@@ -20580,7 +20571,7 @@
         <v>1</v>
       </c>
       <c r="P383" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="384" spans="1:16">
@@ -20594,7 +20585,7 @@
         <v>1.878354735459471</v>
       </c>
       <c r="D384" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E384">
         <v>2.42798454327702</v>
@@ -20630,7 +20621,7 @@
         <v>1</v>
       </c>
       <c r="P384" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="385" spans="1:16">
@@ -20680,7 +20671,7 @@
         <v>1</v>
       </c>
       <c r="P385" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="386" spans="1:16">
@@ -20694,7 +20685,7 @@
         <v>1.711502571778759</v>
       </c>
       <c r="D386" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E386">
         <v>2.569598382620882</v>
@@ -20730,7 +20721,7 @@
         <v>1</v>
       </c>
       <c r="P386" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="387" spans="1:16">
@@ -20744,7 +20735,7 @@
         <v>1.885973897627895</v>
       </c>
       <c r="D387" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E387">
         <v>2.569598382620882</v>
@@ -20780,7 +20771,7 @@
         <v>1</v>
       </c>
       <c r="P387" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="388" spans="1:16">
@@ -20794,7 +20785,7 @@
         <v>2.591185607841933</v>
       </c>
       <c r="D388" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E388">
         <v>2.195973897627894</v>
@@ -20830,7 +20821,7 @@
         <v>1</v>
       </c>
       <c r="P388" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="389" spans="1:16">
@@ -20844,7 +20835,7 @@
         <v>1.828011157399832</v>
       </c>
       <c r="D389" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E389">
         <v>2.719995188926148</v>
@@ -20880,7 +20871,7 @@
         <v>1</v>
       </c>
       <c r="P389" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="390" spans="1:16">
@@ -20894,7 +20885,7 @@
         <v>1.884937981108568</v>
       </c>
       <c r="D390" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E390">
         <v>2.434335634167709</v>
@@ -20930,7 +20921,7 @@
         <v>1</v>
       </c>
       <c r="P390" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="391" spans="1:16">
@@ -20980,7 +20971,7 @@
         <v>1</v>
       </c>
       <c r="P391" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="392" spans="1:16">
@@ -20994,7 +20985,7 @@
         <v>1.718492088255065</v>
       </c>
       <c r="D392" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E392">
         <v>2.575841687373739</v>
@@ -21030,7 +21021,7 @@
         <v>1</v>
       </c>
       <c r="P392" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="393" spans="1:16">
@@ -21044,7 +21035,7 @@
         <v>1.892407900932305</v>
       </c>
       <c r="D393" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E393">
         <v>2.575841687373739</v>
@@ -21080,7 +21071,7 @@
         <v>1</v>
       </c>
       <c r="P393" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="394" spans="1:16">
@@ -21094,7 +21085,7 @@
         <v>1.834154967256232</v>
       </c>
       <c r="D394" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E394">
         <v>2.726263367403121</v>
@@ -21130,7 +21121,7 @@
         <v>1</v>
       </c>
       <c r="P394" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="395" spans="1:16">
@@ -21144,7 +21135,7 @@
         <v>2.791624887079966</v>
       </c>
       <c r="D395" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="E395">
         <v>2.637829766815571</v>
@@ -21180,7 +21171,7 @@
         <v>1</v>
       </c>
       <c r="P395" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="396" spans="1:16">
@@ -21194,7 +21185,7 @@
         <v>1.897004594528006</v>
       </c>
       <c r="D396" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E396">
         <v>2.445976724695786</v>
@@ -21230,7 +21221,7 @@
         <v>1</v>
       </c>
       <c r="P396" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
     </row>
     <row r="397" spans="1:16">
@@ -21280,7 +21271,7 @@
         <v>1</v>
       </c>
       <c r="P397" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
     </row>
     <row r="398" spans="1:16">
@@ -21294,7 +21285,7 @@
         <v>1.731303366734398</v>
       </c>
       <c r="D398" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E398">
         <v>2.587285213702252</v>
@@ -21330,7 +21321,7 @@
         <v>1</v>
       </c>
       <c r="P398" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
     </row>
     <row r="399" spans="1:16">
@@ -21344,7 +21335,7 @@
         <v>1.904200963921582</v>
       </c>
       <c r="D399" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E399">
         <v>2.587285213702252</v>
@@ -21380,7 +21371,7 @@
         <v>1</v>
       </c>
       <c r="P399" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
     </row>
     <row r="400" spans="1:16">
@@ -21394,7 +21385,7 @@
         <v>1.845416126631299</v>
       </c>
       <c r="D400" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E400">
         <v>2.737752485469994</v>
@@ -21430,7 +21421,7 @@
         <v>1</v>
       </c>
       <c r="P400" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
     </row>
     <row r="401" spans="1:16">
@@ -21444,7 +21435,7 @@
         <v>2.802612496024871</v>
       </c>
       <c r="D401" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E401">
         <v>2.813453713263602</v>
@@ -21480,7 +21471,7 @@
         <v>1</v>
       </c>
       <c r="P401" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
     </row>
     <row r="402" spans="1:16">
@@ -21494,7 +21485,7 @@
         <v>1.915149243214803</v>
       </c>
       <c r="D402" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E402">
         <v>2.463481511716044</v>
@@ -21530,7 +21521,7 @@
         <v>1</v>
       </c>
       <c r="P402" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
     </row>
     <row r="403" spans="1:16">
@@ -21580,7 +21571,7 @@
         <v>1</v>
       </c>
       <c r="P403" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
     </row>
     <row r="404" spans="1:16">
@@ -21594,7 +21585,7 @@
         <v>1.750567773337632</v>
       </c>
       <c r="D404" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E404">
         <v>2.60449292209162</v>
@@ -21630,7 +21621,7 @@
         <v>1</v>
       </c>
       <c r="P404" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
     </row>
     <row r="405" spans="1:16">
@@ -21644,7 +21635,7 @@
         <v>1.921934272965604</v>
       </c>
       <c r="D405" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E405">
         <v>2.60449292209162</v>
@@ -21680,7 +21671,7 @@
         <v>1</v>
       </c>
       <c r="P405" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
     </row>
     <row r="406" spans="1:16">
@@ -21694,7 +21685,7 @@
         <v>1.862349608592151</v>
       </c>
       <c r="D406" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E406">
         <v>2.75502875046649</v>
@@ -21730,7 +21721,7 @@
         <v>1</v>
       </c>
       <c r="P406" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
     </row>
     <row r="407" spans="1:16">
@@ -21744,7 +21735,7 @@
         <v>2.819134638342948</v>
       </c>
       <c r="D407" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E407">
         <v>2.769730713091974</v>
@@ -21780,7 +21771,7 @@
         <v>1</v>
       </c>
       <c r="P407" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
     </row>
     <row r="408" spans="1:16">
@@ -21794,7 +21785,7 @@
         <v>1.92753511972947</v>
       </c>
       <c r="D408" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E408">
         <v>2.475430606691152</v>
@@ -21894,7 +21885,7 @@
         <v>1.76371801754653</v>
       </c>
       <c r="D410" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E410">
         <v>2.616239225637646</v>
@@ -21944,7 +21935,7 @@
         <v>1.934039361347697</v>
       </c>
       <c r="D411" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E411">
         <v>2.616239225637646</v>
@@ -21994,7 +21985,7 @@
         <v>1.873908720049794</v>
       </c>
       <c r="D412" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E412">
         <v>2.766821852034614</v>
@@ -22044,7 +22035,7 @@
         <v>2.830412961668017</v>
       </c>
       <c r="D413" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E413">
         <v>2.221708855759843</v>
@@ -22094,7 +22085,7 @@
         <v>1.937685341557977</v>
       </c>
       <c r="D414" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E414">
         <v>2.485222886188172</v>
@@ -22130,7 +22121,7 @@
         <v>1</v>
       </c>
       <c r="P414" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="415" spans="1:16">
@@ -22180,7 +22171,7 @@
         <v>1</v>
       </c>
       <c r="P415" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="416" spans="1:16">
@@ -22194,7 +22185,7 @@
         <v>1.774494638455131</v>
       </c>
       <c r="D416" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E416">
         <v>2.625865317623621</v>
@@ -22230,7 +22221,7 @@
         <v>1</v>
       </c>
       <c r="P416" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="417" spans="1:16">
@@ -22244,7 +22235,7 @@
         <v>1.943959477391676</v>
       </c>
       <c r="D417" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E417">
         <v>2.625865317623621</v>
@@ -22280,7 +22271,7 @@
         <v>1</v>
       </c>
       <c r="P417" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="418" spans="1:16">
@@ -22294,7 +22285,7 @@
         <v>1.883381408179421</v>
       </c>
       <c r="D418" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E418">
         <v>2.776486294984675</v>
@@ -22330,7 +22321,7 @@
         <v>1</v>
       </c>
       <c r="P418" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="419" spans="1:16">
@@ -22344,7 +22335,7 @@
         <v>2.839655544013116</v>
       </c>
       <c r="D419" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E419">
         <v>2.231475567947474</v>
@@ -22380,7 +22371,7 @@
         <v>1</v>
       </c>
       <c r="P419" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="420" spans="1:16">
@@ -22394,7 +22385,7 @@
         <v>1.950149148490695</v>
       </c>
       <c r="D420" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E420">
         <v>2.49724716340538</v>
@@ -22430,7 +22421,7 @@
         <v>1</v>
       </c>
       <c r="P420" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="421" spans="1:16">
@@ -22480,7 +22471,7 @@
         <v>1</v>
       </c>
       <c r="P421" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="422" spans="1:16">
@@ -22494,7 +22485,7 @@
         <v>1.787727622389998</v>
       </c>
       <c r="D422" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E422">
         <v>2.637685527472915</v>
@@ -22530,7 +22521,7 @@
         <v>1</v>
       </c>
       <c r="P422" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="423" spans="1:16">
@@ -22544,7 +22535,7 @@
         <v>1.956140729507283</v>
       </c>
       <c r="D423" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E423">
         <v>2.637685527472915</v>
@@ -22580,7 +22571,7 @@
         <v>1</v>
       </c>
       <c r="P423" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="424" spans="1:16">
@@ -22594,7 +22585,7 @@
         <v>1.895013248150637</v>
       </c>
       <c r="D424" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E424">
         <v>2.788353597303487</v>
@@ -22630,7 +22621,7 @@
         <v>1</v>
       </c>
       <c r="P424" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="425" spans="1:16">
@@ -22644,7 +22635,7 @@
         <v>2.85100482916722</v>
       </c>
       <c r="D425" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E425">
         <v>2.243468450185002</v>
@@ -22680,7 +22671,7 @@
         <v>1</v>
       </c>
       <c r="P425" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="426" spans="1:16">
@@ -22744,7 +22735,7 @@
         <v>1.796280604882195</v>
       </c>
       <c r="D427" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E427">
         <v>2.645325380161676</v>
@@ -22794,7 +22785,7 @@
         <v>1.964013937590256</v>
       </c>
       <c r="D428" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E428">
         <v>2.645325380161676</v>
@@ -22844,7 +22835,7 @@
         <v>1.902531350198938</v>
       </c>
       <c r="D429" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E429">
         <v>2.796023887652364</v>
@@ -22894,7 +22885,7 @@
         <v>2.858340305254835</v>
       </c>
       <c r="D430" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E430">
         <v>2.251219907627515</v>
@@ -22980,7 +22971,7 @@
         <v>1</v>
       </c>
       <c r="P431" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="432" spans="1:16">
@@ -22994,7 +22985,7 @@
         <v>1.81059278070445</v>
       </c>
       <c r="D432" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E432">
         <v>2.658109565682619</v>
@@ -23030,7 +23021,7 @@
         <v>1</v>
       </c>
       <c r="P432" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="433" spans="1:16">
@@ -23044,7 +23035,7 @@
         <v>1.977188609521534</v>
       </c>
       <c r="D433" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E433">
         <v>2.658109565682619</v>
@@ -23080,7 +23071,7 @@
         <v>1</v>
       </c>
       <c r="P433" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="434" spans="1:16">
@@ -23094,7 +23085,7 @@
         <v>1.915111803679711</v>
       </c>
       <c r="D434" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E434">
         <v>2.808859006183351</v>
@@ -23130,7 +23121,7 @@
         <v>1</v>
       </c>
       <c r="P434" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="435" spans="1:16">
@@ -23144,7 +23135,7 @@
         <v>2.870615160675342</v>
       </c>
       <c r="D435" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E435">
         <v>2.26419084751862</v>
@@ -23180,7 +23171,7 @@
         <v>1</v>
       </c>
       <c r="P435" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="436" spans="1:16">
@@ -23230,7 +23221,7 @@
         <v>1</v>
       </c>
       <c r="P436" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="437" spans="1:16">
@@ -23244,7 +23235,7 @@
         <v>1.82632056259726</v>
       </c>
       <c r="D437" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E437">
         <v>2.672158224953424</v>
@@ -23280,7 +23271,7 @@
         <v>1</v>
       </c>
       <c r="P437" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="438" spans="1:16">
@@ -23294,7 +23285,7 @@
         <v>1.991666377906849</v>
       </c>
       <c r="D438" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E438">
         <v>2.672158224953424</v>
@@ -23330,7 +23321,7 @@
         <v>1</v>
       </c>
       <c r="P438" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="439" spans="1:16">
@@ -23344,7 +23335,7 @@
         <v>1.928936579934245</v>
       </c>
       <c r="D439" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E439">
         <v>2.822963636208222</v>
@@ -23380,7 +23371,7 @@
         <v>1</v>
       </c>
       <c r="P439" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="440" spans="1:16">
@@ -23394,7 +23385,7 @@
         <v>2.884104112405478</v>
       </c>
       <c r="D440" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E440">
         <v>2.278444732887671</v>
@@ -23430,7 +23421,7 @@
         <v>1</v>
       </c>
       <c r="P440" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="441" spans="1:16">
@@ -23444,7 +23435,7 @@
         <v>1.850091985515281</v>
       </c>
       <c r="D441" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E441">
         <v>2.693391773538558</v>
@@ -23494,7 +23485,7 @@
         <v>2.013548494377055</v>
       </c>
       <c r="D442" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E442">
         <v>2.693391773538558</v>
@@ -23544,7 +23535,7 @@
         <v>1.949831745274995</v>
       </c>
       <c r="D443" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E443">
         <v>2.844281780604454</v>
@@ -23594,7 +23585,7 @@
         <v>2.90449170287965</v>
       </c>
       <c r="D444" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E444">
         <v>2.29998846611349</v>
@@ -23644,7 +23635,7 @@
         <v>1.883787347386825</v>
       </c>
       <c r="D445" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E445">
         <v>2.723489765815277</v>
@@ -23680,7 +23671,7 @@
         <v>1</v>
       </c>
       <c r="P445" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
     </row>
     <row r="446" spans="1:16">
@@ -23694,7 +23685,7 @@
         <v>2.044565814439117</v>
       </c>
       <c r="D446" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E446">
         <v>2.723489765815277</v>
@@ -23730,7 +23721,7 @@
         <v>1</v>
       </c>
       <c r="P446" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
     </row>
     <row r="447" spans="1:16">
@@ -23744,7 +23735,7 @@
         <v>2.74752944335815</v>
       </c>
       <c r="D447" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E447">
         <v>2.354565814439116</v>
@@ -23780,7 +23771,7 @@
         <v>1</v>
       </c>
       <c r="P447" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
     </row>
     <row r="448" spans="1:16">
@@ -23794,7 +23785,7 @@
         <v>1.979450088272404</v>
       </c>
       <c r="D448" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E448">
         <v>2.874499685200998</v>
@@ -23830,7 +23821,7 @@
         <v>1</v>
       </c>
       <c r="P448" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
     </row>
     <row r="449" spans="1:16">
@@ -23844,7 +23835,7 @@
         <v>2.933390571958093</v>
       </c>
       <c r="D449" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E449">
         <v>2.330526136896243</v>
@@ -23880,7 +23871,7 @@
         <v>1</v>
       </c>
       <c r="P449" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
     </row>
     <row r="450" spans="1:16">
@@ -23930,7 +23921,7 @@
         <v>1</v>
       </c>
       <c r="P450" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
     </row>
     <row r="451" spans="1:16">
@@ -23944,7 +23935,7 @@
         <v>1.920897553279229</v>
       </c>
       <c r="D451" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E451">
         <v>2.756638028018099</v>
@@ -23980,7 +23971,7 @@
         <v>1</v>
       </c>
       <c r="P451" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
     </row>
     <row r="452" spans="1:16">
@@ -23994,7 +23985,7 @@
         <v>2.078726573362612</v>
       </c>
       <c r="D452" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E452">
         <v>2.756638028018099</v>
@@ -24030,7 +24021,7 @@
         <v>1</v>
       </c>
       <c r="P452" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
     </row>
     <row r="453" spans="1:16">
@@ -24044,7 +24035,7 @@
         <v>2.012070091316616</v>
       </c>
       <c r="D453" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E453">
         <v>2.907780012193474</v>
@@ -24080,7 +24071,7 @@
         <v>1</v>
       </c>
       <c r="P453" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
     </row>
     <row r="454" spans="1:16">
@@ -24094,7 +24085,7 @@
         <v>2.965218186264387</v>
       </c>
       <c r="D454" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E454">
         <v>2.364158636661127</v>
@@ -24130,7 +24121,7 @@
         <v>1</v>
       </c>
       <c r="P454" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
     </row>
     <row r="455" spans="1:16">
@@ -24144,7 +24135,7 @@
         <v>1.971362962924253</v>
       </c>
       <c r="D455" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E455">
         <v>2.801715671508852</v>
@@ -24194,7 +24185,7 @@
         <v>2.125181090426125</v>
       </c>
       <c r="D456" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E456">
         <v>2.801715671508852</v>
@@ -24244,7 +24235,7 @@
         <v>2.056429365986798</v>
       </c>
       <c r="D457" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E457">
         <v>2.95303724788937</v>
@@ -24294,7 +24285,7 @@
         <v>3.008499907703719</v>
       </c>
       <c r="D458" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E458">
         <v>2.409894784904068</v>
@@ -24344,7 +24335,7 @@
         <v>2.008171638992437</v>
       </c>
       <c r="D459" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E459">
         <v>2.834594595683633</v>
@@ -24380,7 +24371,7 @@
         <v>1</v>
       </c>
       <c r="P459" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="460" spans="1:16">
@@ -24394,7 +24385,7 @@
         <v>2.159064284529219</v>
       </c>
       <c r="D460" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E460">
         <v>2.834594595683633</v>
@@ -24430,7 +24421,7 @@
         <v>1</v>
       </c>
       <c r="P460" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="461" spans="1:16">
@@ -24444,7 +24435,7 @@
         <v>2.088784323242461</v>
       </c>
       <c r="D461" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E461">
         <v>2.986047163793931</v>
@@ -24480,7 +24471,7 @@
         <v>1</v>
       </c>
       <c r="P461" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="462" spans="1:16">
@@ -24494,7 +24485,7 @@
         <v>3.040068914580697</v>
       </c>
       <c r="D462" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E462">
         <v>2.443254012088044</v>
@@ -24530,7 +24521,7 @@
         <v>1</v>
       </c>
       <c r="P462" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="463" spans="1:16">
@@ -24544,7 +24535,7 @@
         <v>2.067700645146257</v>
       </c>
       <c r="D463" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E463">
         <v>2.887768191927794</v>
@@ -24594,7 +24585,7 @@
         <v>2.213862041083626</v>
       </c>
       <c r="D464" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E464">
         <v>2.887768191927794</v>
@@ -24644,7 +24635,7 @@
         <v>2.914425852356924</v>
       </c>
       <c r="D465" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E465">
         <v>2.523862041083625</v>
@@ -24694,7 +24685,7 @@
         <v>2.141110531498665</v>
       </c>
       <c r="D466" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E466">
         <v>3.039432607035081</v>
@@ -24744,7 +24735,7 @@
         <v>3.091124040854972</v>
       </c>
       <c r="D467" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E467">
         <v>2.497204380654495</v>
@@ -24794,7 +24785,7 @@
         <v>2.102053433035913</v>
       </c>
       <c r="D468" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E468">
         <v>2.918453422391508</v>
@@ -24830,7 +24821,7 @@
         <v>1</v>
       </c>
       <c r="P468" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="469" spans="1:16">
@@ -24844,7 +24835,7 @@
         <v>2.245484536222857</v>
       </c>
       <c r="D469" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E469">
         <v>2.918453422391508</v>
@@ -24880,7 +24871,7 @@
         <v>1</v>
       </c>
       <c r="P469" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="470" spans="1:16">
@@ -24894,7 +24885,7 @@
         <v>2.945600090477427</v>
       </c>
       <c r="D470" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E470">
         <v>2.555484536222856</v>
@@ -24930,7 +24921,7 @@
         <v>1</v>
       </c>
       <c r="P470" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="471" spans="1:16">
@@ -24944,7 +24935,7 @@
         <v>2.171306754305586</v>
       </c>
       <c r="D471" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E471">
         <v>3.070240089412991</v>
@@ -24980,7 +24971,7 @@
         <v>1</v>
       </c>
       <c r="P471" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="472" spans="1:16">
@@ -24994,7 +24985,7 @@
         <v>3.120586752176706</v>
       </c>
       <c r="D472" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E472">
         <v>2.528337868136934</v>
@@ -25030,7 +25021,7 @@
         <v>1</v>
       </c>
       <c r="P472" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="473" spans="1:16">
@@ -25044,7 +25035,7 @@
         <v>2.150109762840597</v>
       </c>
       <c r="D473" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E473">
         <v>2.961379183177897</v>
@@ -25080,7 +25071,7 @@
         <v>1</v>
       </c>
       <c r="P473" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="474" spans="1:16">
@@ -25094,7 +25085,7 @@
         <v>2.289721442425034</v>
       </c>
       <c r="D474" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E474">
         <v>2.961379183177897</v>
@@ -25130,7 +25121,7 @@
         <v>1</v>
       </c>
       <c r="P474" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="475" spans="1:16">
@@ -25144,7 +25135,7 @@
         <v>2.989209927132926</v>
       </c>
       <c r="D475" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E475">
         <v>2.599721442425032</v>
@@ -25180,7 +25171,7 @@
         <v>1</v>
       </c>
       <c r="P475" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="476" spans="1:16">
@@ -25194,7 +25185,7 @@
         <v>2.213548439222873</v>
       </c>
       <c r="D476" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E476">
         <v>3.113336869166659</v>
@@ -25230,7 +25221,7 @@
         <v>1</v>
       </c>
       <c r="P476" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="477" spans="1:16">
@@ -25244,7 +25235,7 @@
         <v>3.161802323290331</v>
       </c>
       <c r="D477" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E477">
         <v>2.571890698470007</v>
@@ -25280,7 +25271,7 @@
         <v>1</v>
       </c>
       <c r="P477" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="478" spans="1:16">
@@ -25294,7 +25285,7 @@
         <v>2.189716387261424</v>
       </c>
       <c r="D478" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E478">
         <v>2.99675734235807</v>
@@ -25344,7 +25335,7 @@
         <v>2.326180209388927</v>
       </c>
       <c r="D479" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E479">
         <v>2.99675734235807</v>
@@ -25394,7 +25385,7 @@
         <v>2.248362803037622</v>
       </c>
       <c r="D480" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E480">
         <v>3.148855977188184</v>
@@ -25444,7 +25435,7 @@
         <v>3.19577099405695</v>
       </c>
       <c r="D481" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E481">
         <v>2.607785670068477</v>
@@ -25494,7 +25485,7 @@
         <v>2.215826782258592</v>
       </c>
       <c r="D482" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E482">
         <v>3.020080150700736</v>
@@ -25530,7 +25521,7 @@
         <v>1</v>
       </c>
       <c r="P482" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="483" spans="1:16">
@@ -25544,7 +25535,7 @@
         <v>2.350215400987747</v>
       </c>
       <c r="D483" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E483">
         <v>3.020080150700736</v>
@@ -25580,7 +25571,7 @@
         <v>1</v>
       </c>
       <c r="P483" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="484" spans="1:16">
@@ -25594,7 +25585,7 @@
         <v>2.271313933159689</v>
       </c>
       <c r="D484" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E484">
         <v>3.172271705086001</v>
@@ -25630,7 +25621,7 @@
         <v>1</v>
       </c>
       <c r="P484" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="485" spans="1:16">
@@ -25644,7 +25635,7 @@
         <v>3.218164606848116</v>
       </c>
       <c r="D485" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E485">
         <v>2.631449183446694</v>
@@ -25680,7 +25671,7 @@
         <v>1</v>
       </c>
       <c r="P485" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="486" spans="1:16">
@@ -25730,7 +25721,7 @@
         <v>1</v>
       </c>
       <c r="P486" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="487" spans="1:16">
@@ -25744,7 +25735,7 @@
         <v>2.227304742320833</v>
       </c>
       <c r="D487" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E487">
         <v>3.030332705774125</v>
@@ -25780,7 +25771,7 @@
         <v>1</v>
       </c>
       <c r="P487" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="488" spans="1:16">
@@ -25794,7 +25785,7 @@
         <v>2.360781115113841</v>
       </c>
       <c r="D488" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E488">
         <v>3.030332705774125</v>
@@ -25830,7 +25821,7 @@
         <v>1</v>
       </c>
       <c r="P488" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="489" spans="1:16">
@@ -25844,7 +25835,7 @@
         <v>2.28140310090123</v>
       </c>
       <c r="D489" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E489">
         <v>3.182565106992353</v>
@@ -25880,7 +25871,7 @@
         <v>1</v>
       </c>
       <c r="P489" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="490" spans="1:16">
@@ -25894,7 +25885,7 @@
         <v>3.228008693591889</v>
       </c>
       <c r="D490" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E490">
         <v>2.641851510240944</v>
@@ -25930,7 +25921,7 @@
         <v>1</v>
       </c>
       <c r="P490" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="491" spans="1:16">
@@ -25944,7 +25935,7 @@
         <v>2.326764722017106</v>
       </c>
       <c r="D491" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E491">
         <v>2.338905512271317</v>
@@ -25980,7 +25971,7 @@
         <v>1</v>
       </c>
       <c r="P491" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="492" spans="1:16">
@@ -25994,7 +25985,7 @@
         <v>2.245345573811253</v>
       </c>
       <c r="D492" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E492">
         <v>3.046447469845635</v>
@@ -26030,7 +26021,7 @@
         <v>1</v>
       </c>
       <c r="P492" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="493" spans="1:16">
@@ -26044,7 +26035,7 @@
         <v>2.377388096414631</v>
       </c>
       <c r="D493" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E493">
         <v>3.046447469845635</v>
@@ -26080,7 +26071,7 @@
         <v>1</v>
       </c>
       <c r="P493" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="494" spans="1:16">
@@ -26094,7 +26085,7 @@
         <v>2.297261055983554</v>
       </c>
       <c r="D494" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E494">
         <v>3.198744073311161</v>
@@ -26130,7 +26121,7 @@
         <v>1</v>
       </c>
       <c r="P494" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="495" spans="1:16">
@@ -26144,7 +26135,7 @@
         <v>3.243481435190432</v>
       </c>
       <c r="D495" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E495">
         <v>2.658201682552544</v>
@@ -26180,7 +26171,7 @@
         <v>1</v>
       </c>
       <c r="P495" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="496" spans="1:16">
@@ -26230,7 +26221,7 @@
         <v>1</v>
       </c>
       <c r="P496" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="497" spans="1:16">
@@ -26244,7 +26235,7 @@
         <v>2.301170929293026</v>
       </c>
       <c r="D497" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E497">
         <v>3.202733093853617</v>
@@ -26294,7 +26285,7 @@
         <v>3.247296331820319</v>
       </c>
       <c r="D498" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E498">
         <v>2.662232914952593</v>
@@ -26394,7 +26385,7 @@
         <v>2.309276220482282</v>
       </c>
       <c r="D500" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E500">
         <v>3.211002459763304</v>
@@ -26430,7 +26421,7 @@
         <v>1</v>
       </c>
       <c r="P500" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="501" spans="1:16">
@@ -26444,7 +26435,7 @@
         <v>3.25520473334506</v>
       </c>
       <c r="D501" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E501">
         <v>2.670589787379843</v>
@@ -26480,7 +26471,7 @@
         <v>1</v>
       </c>
       <c r="P501" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="502" spans="1:16">
@@ -26494,7 +26485,7 @@
         <v>2.35659384998981</v>
       </c>
       <c r="D502" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E502">
         <v>2.377701080695644</v>
@@ -26530,7 +26521,7 @@
         <v>1</v>
       </c>
       <c r="P502" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="503" spans="1:16">
@@ -26544,7 +26535,7 @@
         <v>2.318802840630408</v>
       </c>
       <c r="D503" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E503">
         <v>3.220721926473129</v>
@@ -26594,7 +26585,7 @@
         <v>3.264499937619139</v>
       </c>
       <c r="D504" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E504">
         <v>2.680412105589244</v>
@@ -26744,7 +26735,7 @@
         <v>2.968469110715926</v>
       </c>
       <c r="D507" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E507">
         <v>3.65607053595874</v>
@@ -26780,7 +26771,7 @@
         <v>1</v>
       </c>
       <c r="P507" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="508" spans="1:16">
@@ -26794,7 +26785,7 @@
         <v>3.056098677724048</v>
       </c>
       <c r="D508" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E508">
         <v>3.65607053595874</v>
@@ -26830,7 +26821,7 @@
         <v>1</v>
       </c>
       <c r="P508" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="509" spans="1:16">
@@ -26844,7 +26835,7 @@
         <v>3.085552267926261</v>
       </c>
       <c r="D509" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E509">
         <v>3.65607053595874</v>
@@ -26880,7 +26871,7 @@
         <v>1</v>
       </c>
       <c r="P509" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="510" spans="1:16">
@@ -26894,7 +26885,7 @@
         <v>3.115403587495276</v>
       </c>
       <c r="D510" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E510">
         <v>4.899694426383849</v>
@@ -26930,7 +26921,7 @@
         <v>1</v>
       </c>
       <c r="P510" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="511" spans="1:16">
@@ -26944,7 +26935,7 @@
         <v>2.857657467623699</v>
       </c>
       <c r="D511" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E511">
         <v>4.899694426383849</v>
@@ -26980,7 +26971,7 @@
         <v>1</v>
       </c>
       <c r="P511" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="512" spans="1:16">
@@ -26994,7 +26985,7 @@
         <v>4.634833021734408</v>
       </c>
       <c r="D512" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E512">
         <v>3.48240231940969</v>
@@ -27030,7 +27021,7 @@
         <v>1</v>
       </c>
       <c r="P512" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="513" spans="1:16">
@@ -27044,7 +27035,7 @@
         <v>3.013404560606677</v>
       </c>
       <c r="D513" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E513">
         <v>3.707166946903694</v>
@@ -27080,7 +27071,7 @@
         <v>1</v>
       </c>
       <c r="P513" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="514" spans="1:16">
@@ -27094,7 +27085,7 @@
         <v>3.101938488870459</v>
       </c>
       <c r="D514" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E514">
         <v>3.707166946903694</v>
@@ -27130,7 +27121,7 @@
         <v>1</v>
       </c>
       <c r="P514" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="515" spans="1:16">
@@ -27144,7 +27135,7 @@
         <v>3.133031233848563</v>
       </c>
       <c r="D515" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E515">
         <v>3.707166946903694</v>
@@ -27180,7 +27171,7 @@
         <v>1</v>
       </c>
       <c r="P515" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="516" spans="1:16">
@@ -27194,7 +27185,7 @@
         <v>2.923647577997855</v>
       </c>
       <c r="D516" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E516">
         <v>4.966814988327585</v>
@@ -27230,7 +27221,7 @@
         <v>1</v>
       </c>
       <c r="P516" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="517" spans="1:16">
@@ -27244,7 +27235,7 @@
         <v>4.706192777064061</v>
       </c>
       <c r="D517" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E517">
         <v>3.555881671432303</v>
@@ -27280,7 +27271,7 @@
         <v>1</v>
       </c>
       <c r="P517" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="518" spans="1:16">
@@ -27294,7 +27285,7 @@
         <v>3.058294813446018</v>
       </c>
       <c r="D518" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E518">
         <v>3.758211963968808</v>
@@ -27330,7 +27321,7 @@
         <v>1</v>
       </c>
       <c r="P518" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
     </row>
     <row r="519" spans="1:16">
@@ -27344,7 +27335,7 @@
         <v>3.147732193339273</v>
       </c>
       <c r="D519" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E519">
         <v>3.758211963968808</v>
@@ -27380,7 +27371,7 @@
         <v>1</v>
       </c>
       <c r="P519" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
     </row>
     <row r="520" spans="1:16">
@@ -27394,7 +27385,7 @@
         <v>3.18046244439579</v>
       </c>
       <c r="D520" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E520">
         <v>3.758211963968808</v>
@@ -27430,7 +27421,7 @@
         <v>1</v>
       </c>
       <c r="P520" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
     </row>
     <row r="521" spans="1:16">
@@ -27444,7 +27435,7 @@
         <v>3.225680173488445</v>
       </c>
       <c r="D521" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E521">
         <v>5.033868038952384</v>
@@ -27480,7 +27471,7 @@
         <v>1</v>
       </c>
       <c r="P521" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
     </row>
     <row r="522" spans="1:16">
@@ -27494,7 +27485,7 @@
         <v>2.989571314085818</v>
       </c>
       <c r="D522" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E522">
         <v>5.033868038952384</v>
@@ -27530,7 +27521,7 @@
         <v>1</v>
       </c>
       <c r="P522" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
     </row>
     <row r="523" spans="1:16">
@@ -27544,7 +27535,7 @@
         <v>4.77748075720201</v>
       </c>
       <c r="D523" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E523">
         <v>3.629287116326825</v>
@@ -27580,7 +27571,7 @@
         <v>1</v>
       </c>
       <c r="P523" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
     </row>
     <row r="524" spans="1:16">
@@ -27594,7 +27585,7 @@
         <v>3.100990526217007</v>
       </c>
       <c r="D524" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E524">
         <v>5.097643081613452</v>
@@ -27630,7 +27621,7 @@
         <v>1</v>
       </c>
       <c r="P524" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
     </row>
     <row r="525" spans="1:16">
@@ -27644,7 +27635,7 @@
         <v>3.19128719089559</v>
       </c>
       <c r="D525" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E525">
         <v>5.097643081613452</v>
@@ -27680,7 +27671,7 @@
         <v>1</v>
       </c>
       <c r="P525" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
     </row>
     <row r="526" spans="1:16">
@@ -27694,7 +27685,7 @@
         <v>3.225574895625517</v>
       </c>
       <c r="D526" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E526">
         <v>5.097643081613452</v>
@@ -27730,7 +27721,7 @@
         <v>1</v>
       </c>
       <c r="P526" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
     </row>
     <row r="527" spans="1:16">
@@ -27744,7 +27735,7 @@
         <v>3.205781960817575</v>
       </c>
       <c r="D527" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E527">
         <v>5.097643081613452</v>
@@ -27780,7 +27771,7 @@
         <v>1</v>
       </c>
       <c r="P527" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
     </row>
     <row r="528" spans="1:16">
@@ -27794,7 +27785,7 @@
         <v>3.27809654539346</v>
       </c>
       <c r="D528" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E528">
         <v>5.097643081613452</v>
@@ -27830,7 +27821,7 @@
         <v>1</v>
       </c>
       <c r="P528" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
     </row>
     <row r="529" spans="1:16">
@@ -27844,7 +27835,7 @@
         <v>3.052272250765228</v>
       </c>
       <c r="D529" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E529">
         <v>5.097643081613452</v>
@@ -27880,7 +27871,7 @@
         <v>1</v>
       </c>
       <c r="P529" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
     </row>
     <row r="530" spans="1:16">
@@ -27894,7 +27885,7 @@
         <v>4.845283697294303</v>
       </c>
       <c r="D530" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E530">
         <v>3.699104005134728</v>
@@ -27930,7 +27921,7 @@
         <v>1</v>
       </c>
       <c r="P530" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
     </row>
     <row r="531" spans="1:16">
@@ -27944,7 +27935,7 @@
         <v>3.135431759672713</v>
       </c>
       <c r="D531" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E531">
         <v>5.149088320265843</v>
@@ -27980,7 +27971,7 @@
         <v>1</v>
       </c>
       <c r="P531" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
     </row>
     <row r="532" spans="1:16">
@@ -27994,7 +27985,7 @@
         <v>3.226421581251035</v>
       </c>
       <c r="D532" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E532">
         <v>5.149088320265843</v>
@@ -28030,7 +28021,7 @@
         <v>1</v>
       </c>
       <c r="P532" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
     </row>
     <row r="533" spans="1:16">
@@ -28044,7 +28035,7 @@
         <v>3.261965632861735</v>
       </c>
       <c r="D533" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E533">
         <v>5.149088320265843</v>
@@ -28080,7 +28071,7 @@
         <v>1</v>
       </c>
       <c r="P533" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
     </row>
     <row r="534" spans="1:16">
@@ -28094,7 +28085,7 @@
         <v>3.248497754763896</v>
       </c>
       <c r="D534" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E534">
         <v>5.149088320265843</v>
@@ -28130,7 +28121,7 @@
         <v>1</v>
       </c>
       <c r="P534" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
     </row>
     <row r="535" spans="1:16">
@@ -28144,7 +28135,7 @@
         <v>3.320379116277444</v>
       </c>
       <c r="D535" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E535">
         <v>5.149088320265843</v>
@@ -28180,7 +28171,7 @@
         <v>1</v>
       </c>
       <c r="P535" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
     </row>
     <row r="536" spans="1:16">
@@ -28194,7 +28185,7 @@
         <v>3.102851043292947</v>
       </c>
       <c r="D536" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E536">
         <v>5.149088320265843</v>
@@ -28230,7 +28221,7 @@
         <v>1</v>
       </c>
       <c r="P536" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
     </row>
     <row r="537" spans="1:16">
@@ -28244,7 +28235,7 @@
         <v>4.899978108914215</v>
       </c>
       <c r="D537" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E537">
         <v>3.755423003238402</v>
@@ -28280,7 +28271,7 @@
         <v>1</v>
       </c>
       <c r="P537" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
     </row>
     <row r="538" spans="1:16">
@@ -28294,7 +28285,7 @@
         <v>3.340758667101504</v>
       </c>
       <c r="D538" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E538">
         <v>5.455787317211367</v>
@@ -28330,7 +28321,7 @@
         <v>1</v>
       </c>
       <c r="P538" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
     </row>
     <row r="539" spans="1:16">
@@ -28344,7 +28335,7 @@
         <v>3.596337846972439</v>
       </c>
       <c r="D539" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E539">
         <v>5.455787317211367</v>
@@ -28380,7 +28371,7 @@
         <v>1</v>
       </c>
       <c r="P539" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
     </row>
     <row r="540" spans="1:16">
@@ -28394,7 +28385,7 @@
         <v>3.478914818069512</v>
       </c>
       <c r="D540" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E540">
         <v>5.455787317211367</v>
@@ -28430,7 +28421,7 @@
         <v>1</v>
       </c>
       <c r="P540" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
     </row>
     <row r="541" spans="1:16">
@@ -28444,7 +28435,7 @@
         <v>3.503154774543503</v>
       </c>
       <c r="D541" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E541">
         <v>5.455787317211367</v>
@@ -28480,7 +28471,7 @@
         <v>1</v>
       </c>
       <c r="P541" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
     </row>
     <row r="542" spans="1:16">
@@ -28494,7 +28485,7 @@
         <v>3.572453407661722</v>
       </c>
       <c r="D542" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E542">
         <v>5.455787317211367</v>
@@ -28530,7 +28521,7 @@
         <v>1</v>
       </c>
       <c r="P542" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
     </row>
     <row r="543" spans="1:16">
@@ -28544,7 +28535,7 @@
         <v>3.404384583447808</v>
       </c>
       <c r="D543" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E543">
         <v>5.455787317211367</v>
@@ -28580,7 +28571,7 @@
         <v>1</v>
       </c>
       <c r="P543" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
     </row>
     <row r="544" spans="1:16">
@@ -28594,7 +28585,7 @@
         <v>5.25250104043668</v>
       </c>
       <c r="D544" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E544">
         <v>5.56320240731846</v>
@@ -28630,7 +28621,7 @@
         <v>1</v>
       </c>
       <c r="P544" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
     </row>
     <row r="545" spans="1:16">
@@ -28644,7 +28635,7 @@
         <v>3.408744253943432</v>
       </c>
       <c r="D545" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E545">
         <v>5.557338115167074</v>
@@ -28680,7 +28671,7 @@
         <v>1</v>
       </c>
       <c r="P545" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="546" spans="1:16">
@@ -28694,7 +28685,7 @@
         <v>3.550748645676077</v>
       </c>
       <c r="D546" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E546">
         <v>5.557338115167074</v>
@@ -28730,7 +28721,7 @@
         <v>1</v>
       </c>
       <c r="P546" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="547" spans="1:16">
@@ -28744,7 +28735,7 @@
         <v>3.587474005519777</v>
       </c>
       <c r="D547" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E547">
         <v>5.557338115167074</v>
@@ -28780,7 +28771,7 @@
         <v>1</v>
       </c>
       <c r="P547" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="548" spans="1:16">
@@ -28794,7 +28785,7 @@
         <v>3.655917474023632</v>
       </c>
       <c r="D548" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E548">
         <v>5.557338115167074</v>
@@ -28830,7 +28821,7 @@
         <v>1</v>
       </c>
       <c r="P548" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="549" spans="1:16">
@@ -28844,7 +28835,7 @@
         <v>3.504225052174785</v>
       </c>
       <c r="D549" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E549">
         <v>5.557338115167074</v>
@@ -28880,7 +28871,7 @@
         <v>1</v>
       </c>
       <c r="P549" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="550" spans="1:16">
@@ -28894,7 +28885,7 @@
         <v>5.346996730323884</v>
       </c>
       <c r="D550" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E550">
         <v>5.864438002961421</v>
@@ -28930,7 +28921,7 @@
         <v>1</v>
       </c>
       <c r="P550" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="551" spans="1:16">
@@ -28944,7 +28935,7 @@
         <v>5.267444590560391</v>
       </c>
       <c r="D551" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E551">
         <v>5.864438002961421</v>
@@ -28980,7 +28971,7 @@
         <v>1</v>
       </c>
       <c r="P551" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="552" spans="1:16">
@@ -28994,7 +28985,7 @@
         <v>3.796322429340982</v>
       </c>
       <c r="D552" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E552">
         <v>5.685955718590687</v>
@@ -29030,7 +29021,7 @@
         <v>1</v>
       </c>
       <c r="P552" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
     </row>
     <row r="553" spans="1:16">
@@ -29044,7 +29035,7 @@
         <v>3.641728676729411</v>
       </c>
       <c r="D553" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E553">
         <v>5.685955718590687</v>
@@ -29080,7 +29071,7 @@
         <v>1</v>
       </c>
       <c r="P553" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
     </row>
     <row r="554" spans="1:16">
@@ -29094,7 +29085,7 @@
         <v>3.69426723244667</v>
       </c>
       <c r="D554" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E554">
         <v>5.685955718590687</v>
@@ -29130,7 +29121,7 @@
         <v>1</v>
       </c>
       <c r="P554" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
     </row>
     <row r="555" spans="1:16">
@@ -29144,7 +29135,7 @@
         <v>3.761627605342749</v>
       </c>
       <c r="D555" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E555">
         <v>5.685955718590687</v>
@@ -29180,7 +29171,7 @@
         <v>1</v>
       </c>
       <c r="P555" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
     </row>
     <row r="556" spans="1:16">
@@ -29194,7 +29185,7 @@
         <v>3.630676464382844</v>
       </c>
       <c r="D556" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E556">
         <v>5.685955718590687</v>
@@ -29230,7 +29221,7 @@
         <v>1</v>
       </c>
       <c r="P556" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
     </row>
     <row r="557" spans="1:16">
@@ -29244,7 +29235,7 @@
         <v>5.466678794983334</v>
       </c>
       <c r="D557" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E557">
         <v>5.209318422087254</v>
@@ -29280,7 +29271,7 @@
         <v>1</v>
       </c>
       <c r="P557" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
     </row>
     <row r="558" spans="1:16">
@@ -29294,7 +29285,7 @@
         <v>5.390917489847062</v>
       </c>
       <c r="D558" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E558">
         <v>5.209318422087254</v>
@@ -29330,7 +29321,7 @@
         <v>1</v>
       </c>
       <c r="P558" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
     </row>
     <row r="559" spans="1:16">
@@ -29344,7 +29335,7 @@
         <v>4.159051079599863</v>
       </c>
       <c r="D559" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E559">
         <v>5.343391662540899</v>
@@ -29380,7 +29371,7 @@
         <v>1</v>
       </c>
       <c r="P559" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="560" spans="1:16">
@@ -29394,7 +29385,7 @@
         <v>4.237780255555339</v>
       </c>
       <c r="D560" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E560">
         <v>5.313343652467495</v>
@@ -29430,7 +29421,7 @@
         <v>1</v>
       </c>
       <c r="P560" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="561" spans="1:16">
@@ -29444,7 +29435,7 @@
         <v>4.283295642394084</v>
       </c>
       <c r="D561" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E561">
         <v>5.313343652467495</v>
@@ -29480,7 +29471,7 @@
         <v>1</v>
       </c>
       <c r="P561" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="562" spans="1:16">
@@ -29530,7 +29521,7 @@
         <v>1</v>
       </c>
       <c r="P562" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="563" spans="1:16">
@@ -29544,7 +29535,7 @@
         <v>4.047954928502808</v>
       </c>
       <c r="D563" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E563">
         <v>5.235960539108905</v>
@@ -29580,7 +29571,7 @@
         <v>1</v>
       </c>
       <c r="P563" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="564" spans="1:16">
@@ -29594,7 +29585,7 @@
         <v>4.137221058995326</v>
       </c>
       <c r="D564" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E564">
         <v>5.202705629828571</v>
@@ -29630,7 +29621,7 @@
         <v>1</v>
       </c>
       <c r="P564" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="565" spans="1:16">
@@ -29644,7 +29635,7 @@
         <v>4.169450720548237</v>
       </c>
       <c r="D565" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E565">
         <v>5.202705629828571</v>
@@ -29680,7 +29671,7 @@
         <v>1</v>
       </c>
       <c r="P565" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="566" spans="1:16">
@@ -29694,7 +29685,7 @@
         <v>6.314817655301979</v>
       </c>
       <c r="D566" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E566">
         <v>6.624319057953503</v>
@@ -29730,7 +29721,7 @@
         <v>1</v>
       </c>
       <c r="P566" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="567" spans="1:16">
@@ -29744,7 +29735,7 @@
         <v>4.059730080999771</v>
       </c>
       <c r="D567" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E567">
         <v>5.117447902330046</v>
@@ -29794,7 +29785,7 @@
         <v>4.081721754571493</v>
       </c>
       <c r="D568" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E568">
         <v>5.117447902330046</v>
@@ -29894,7 +29885,7 @@
         <v>4.030557457706422</v>
       </c>
       <c r="D570" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E570">
         <v>5.085351371462874</v>
@@ -29930,7 +29921,7 @@
         <v>1</v>
       </c>
       <c r="P570" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="571" spans="1:16">
@@ -29944,7 +29935,7 @@
         <v>4.048694889476288</v>
       </c>
       <c r="D571" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E571">
         <v>5.085351371462874</v>
@@ -29980,7 +29971,7 @@
         <v>1</v>
       </c>
       <c r="P571" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="572" spans="1:16">
@@ -30030,7 +30021,7 @@
         <v>1</v>
       </c>
       <c r="P572" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="573" spans="1:16">
@@ -30044,7 +30035,7 @@
         <v>3.737521317704196</v>
       </c>
       <c r="D573" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E573">
         <v>4.762944866631269</v>
@@ -30080,7 +30071,7 @@
         <v>1</v>
       </c>
       <c r="P573" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="574" spans="1:16">
@@ -30094,7 +30085,7 @@
         <v>3.716943268562606</v>
       </c>
       <c r="D574" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E574">
         <v>4.762944866631269</v>
@@ -30130,7 +30121,7 @@
         <v>1</v>
       </c>
       <c r="P574" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="575" spans="1:16">
@@ -30180,7 +30171,7 @@
         <v>1</v>
       </c>
       <c r="P575" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="576" spans="1:16">
@@ -30230,7 +30221,7 @@
         <v>1</v>
       </c>
       <c r="P576" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="577" spans="1:16">
@@ -30244,7 +30235,7 @@
         <v>3.710853293730853</v>
       </c>
       <c r="D577" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E577">
         <v>4.733603965539871</v>
@@ -30280,7 +30271,7 @@
         <v>1</v>
       </c>
       <c r="P577" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
     </row>
     <row r="578" spans="1:16">
@@ -30294,7 +30285,7 @@
         <v>3.686751906570006</v>
       </c>
       <c r="D578" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E578">
         <v>4.733603965539871</v>
@@ -30330,7 +30321,7 @@
         <v>1</v>
       </c>
       <c r="P578" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
     </row>
     <row r="579" spans="1:16">
@@ -30380,7 +30371,7 @@
         <v>1</v>
       </c>
       <c r="P579" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
     </row>
     <row r="580" spans="1:16">
@@ -30430,7 +30421,7 @@
         <v>1</v>
       </c>
       <c r="P580" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
     </row>
     <row r="581" spans="1:16">
@@ -30480,7 +30471,7 @@
         <v>1</v>
       </c>
       <c r="P581" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
     </row>
     <row r="582" spans="1:16">
@@ -30530,7 +30521,7 @@
         <v>1</v>
       </c>
       <c r="P582" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
     </row>
     <row r="583" spans="1:16">
@@ -30580,7 +30571,7 @@
         <v>1</v>
       </c>
       <c r="P583" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
     </row>
     <row r="584" spans="1:16">
@@ -30630,7 +30621,7 @@
         <v>1</v>
       </c>
       <c r="P584" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
     </row>
     <row r="585" spans="1:16">
@@ -30680,7 +30671,7 @@
         <v>1</v>
       </c>
       <c r="P585" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
     </row>
     <row r="586" spans="1:16">
@@ -30730,7 +30721,7 @@
         <v>1</v>
       </c>
       <c r="P586" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
     </row>
     <row r="587" spans="1:16">
@@ -30780,7 +30771,7 @@
         <v>1</v>
       </c>
       <c r="P587" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
     </row>
     <row r="588" spans="1:16">
@@ -30830,7 +30821,7 @@
         <v>1</v>
       </c>
       <c r="P588" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
     </row>
     <row r="589" spans="1:16">
@@ -30880,7 +30871,7 @@
         <v>1</v>
       </c>
       <c r="P589" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
     </row>
     <row r="590" spans="1:16">
@@ -30930,7 +30921,7 @@
         <v>1</v>
       </c>
       <c r="P590" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
     </row>
     <row r="591" spans="1:16">
@@ -31180,7 +31171,7 @@
         <v>1</v>
       </c>
       <c r="P595" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="596" spans="1:16">
@@ -31230,7 +31221,7 @@
         <v>1</v>
       </c>
       <c r="P596" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="597" spans="1:16">
@@ -31280,7 +31271,7 @@
         <v>1</v>
       </c>
       <c r="P597" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="598" spans="1:16">
@@ -31330,7 +31321,7 @@
         <v>1</v>
       </c>
       <c r="P598" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="599" spans="1:16">
@@ -31380,7 +31371,7 @@
         <v>1</v>
       </c>
       <c r="P599" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="600" spans="1:16">
@@ -31430,7 +31421,7 @@
         <v>1</v>
       </c>
       <c r="P600" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="601" spans="1:16">
@@ -31644,7 +31635,7 @@
         <v>6.312844467716282</v>
       </c>
       <c r="D605" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E605">
         <v>7.044140001633426</v>
@@ -31730,7 +31721,7 @@
         <v>1</v>
       </c>
       <c r="P606" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
     </row>
     <row r="607" spans="1:16">
@@ -31780,7 +31771,7 @@
         <v>1</v>
       </c>
       <c r="P607" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
     </row>
     <row r="608" spans="1:16">
@@ -31830,7 +31821,7 @@
         <v>1</v>
       </c>
       <c r="P608" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
     </row>
     <row r="609" spans="1:16">
@@ -31880,7 +31871,7 @@
         <v>1</v>
       </c>
       <c r="P609" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
     </row>
     <row r="610" spans="1:16">
@@ -31930,7 +31921,7 @@
         <v>1</v>
       </c>
       <c r="P610" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
     </row>
     <row r="611" spans="1:16">
@@ -31980,7 +31971,7 @@
         <v>1</v>
       </c>
       <c r="P611" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="612" spans="1:16">
@@ -32030,7 +32021,7 @@
         <v>1</v>
       </c>
       <c r="P612" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="613" spans="1:16">
@@ -32080,7 +32071,7 @@
         <v>1</v>
       </c>
       <c r="P613" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="614" spans="1:16">
@@ -32130,7 +32121,7 @@
         <v>1</v>
       </c>
       <c r="P614" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="615" spans="1:16">
@@ -32180,7 +32171,7 @@
         <v>1</v>
       </c>
       <c r="P615" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="616" spans="1:16">
@@ -32230,7 +32221,7 @@
         <v>1</v>
       </c>
       <c r="P616" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="617" spans="1:16">
@@ -32280,7 +32271,7 @@
         <v>1</v>
       </c>
       <c r="P617" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="618" spans="1:16">
@@ -32330,7 +32321,7 @@
         <v>1</v>
       </c>
       <c r="P618" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="619" spans="1:16">
@@ -32380,7 +32371,7 @@
         <v>1</v>
       </c>
       <c r="P619" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="620" spans="1:16">
@@ -32430,7 +32421,7 @@
         <v>1</v>
       </c>
       <c r="P620" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="621" spans="1:16">
@@ -32480,7 +32471,7 @@
         <v>1</v>
       </c>
       <c r="P621" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="622" spans="1:16">
@@ -32494,7 +32485,7 @@
         <v>6.52789956231641</v>
       </c>
       <c r="D622" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E622">
         <v>6.970266187949232</v>
@@ -32530,7 +32521,7 @@
         <v>1</v>
       </c>
       <c r="P622" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="623" spans="1:16">
@@ -32580,7 +32571,7 @@
         <v>1</v>
       </c>
       <c r="P623" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
     </row>
     <row r="624" spans="1:16">
@@ -32630,7 +32621,7 @@
         <v>1</v>
       </c>
       <c r="P624" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
     </row>
     <row r="625" spans="1:16">
@@ -32680,7 +32671,7 @@
         <v>1</v>
       </c>
       <c r="P625" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
     </row>
     <row r="626" spans="1:16">
@@ -32694,7 +32685,7 @@
         <v>2.603543847706</v>
       </c>
       <c r="D626" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="E626">
         <v>4.770094008155837</v>
@@ -32730,7 +32721,7 @@
         <v>1</v>
       </c>
       <c r="P626" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
     </row>
     <row r="627" spans="1:16">
@@ -32780,7 +32771,7 @@
         <v>1</v>
       </c>
       <c r="P627" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
     </row>
     <row r="628" spans="1:16">
@@ -32830,7 +32821,7 @@
         <v>1</v>
       </c>
       <c r="P628" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
     </row>
     <row r="629" spans="1:16">
@@ -32880,7 +32871,7 @@
         <v>1</v>
       </c>
       <c r="P629" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
     </row>
     <row r="630" spans="1:16">
@@ -32930,7 +32921,7 @@
         <v>1</v>
       </c>
       <c r="P630" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
     </row>
     <row r="631" spans="1:16">
@@ -32980,7 +32971,7 @@
         <v>1</v>
       </c>
       <c r="P631" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
     </row>
     <row r="632" spans="1:16">
@@ -32994,7 +32985,7 @@
         <v>2.478182256708074</v>
       </c>
       <c r="D632" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="E632">
         <v>4.645810796435313</v>
@@ -33030,7 +33021,7 @@
         <v>1</v>
       </c>
       <c r="P632" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
     </row>
     <row r="633" spans="1:16">
@@ -33080,7 +33071,7 @@
         <v>1</v>
       </c>
       <c r="P633" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
     </row>
     <row r="634" spans="1:16">
@@ -33130,7 +33121,7 @@
         <v>1</v>
       </c>
       <c r="P634" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
     </row>
     <row r="635" spans="1:16">
@@ -33180,7 +33171,7 @@
         <v>1</v>
       </c>
       <c r="P635" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
     </row>
     <row r="636" spans="1:16">
@@ -33230,7 +33221,7 @@
         <v>1</v>
       </c>
       <c r="P636" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
     </row>
     <row r="637" spans="1:16">
@@ -33244,7 +33235,7 @@
         <v>2.30694018299906</v>
       </c>
       <c r="D637" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="E637">
         <v>4.476041772822722</v>
@@ -33280,7 +33271,7 @@
         <v>1</v>
       </c>
       <c r="P637" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
     </row>
     <row r="638" spans="1:16">
@@ -33294,7 +33285,7 @@
         <v>5.979313720333828</v>
       </c>
       <c r="D638" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E638">
         <v>6.921637837986275</v>
@@ -33330,7 +33321,7 @@
         <v>1</v>
       </c>
       <c r="P638" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
     </row>
     <row r="639" spans="1:16">
@@ -33344,7 +33335,7 @@
         <v>6.118014825265853</v>
       </c>
       <c r="D639" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E639">
         <v>6.921637837986275</v>
@@ -33380,7 +33371,7 @@
         <v>1</v>
       </c>
       <c r="P639" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
     </row>
     <row r="640" spans="1:16">
@@ -33394,7 +33385,7 @@
         <v>2.180042495856011</v>
       </c>
       <c r="D640" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="E640">
         <v>4.350235678687355</v>
@@ -33430,7 +33421,7 @@
         <v>1</v>
       </c>
       <c r="P640" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
     </row>
     <row r="641" spans="1:16">
@@ -33480,7 +33471,7 @@
         <v>1</v>
       </c>
       <c r="P641" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
     </row>
     <row r="642" spans="1:16">
@@ -33530,7 +33521,7 @@
         <v>1</v>
       </c>
       <c r="P642" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
     </row>
     <row r="643" spans="1:16">
@@ -33580,7 +33571,7 @@
         <v>1</v>
       </c>
       <c r="P643" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
     </row>
     <row r="644" spans="1:16">
@@ -33594,7 +33585,7 @@
         <v>2.005501953213372</v>
       </c>
       <c r="D644" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="E644">
         <v>4.177196560067447</v>
@@ -33630,7 +33621,7 @@
         <v>1</v>
       </c>
       <c r="P644" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
     </row>
     <row r="645" spans="1:16">
@@ -33644,7 +33635,7 @@
         <v>6.03048720269387</v>
       </c>
       <c r="D645" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E645">
         <v>7.646218976894719</v>
@@ -33680,7 +33671,7 @@
         <v>1</v>
       </c>
       <c r="P645" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
     </row>
     <row r="646" spans="1:16">
@@ -33694,7 +33685,7 @@
         <v>6.160487202693869</v>
       </c>
       <c r="D646" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E646">
         <v>7.646218976894719</v>
@@ -33730,7 +33721,7 @@
         <v>1</v>
       </c>
       <c r="P646" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
     </row>
     <row r="647" spans="1:16">
@@ -33794,7 +33785,7 @@
         <v>5.929250610805834</v>
       </c>
       <c r="D648" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="E648">
         <v>6.44678700451809</v>
@@ -33844,7 +33835,7 @@
         <v>6.059250610805833</v>
       </c>
       <c r="D649" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="E649">
         <v>6.44678700451809</v>
@@ -33930,7 +33921,7 @@
         <v>1</v>
       </c>
       <c r="P650" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
     </row>
     <row r="651" spans="1:16">
@@ -33944,7 +33935,7 @@
         <v>6.444007644774246</v>
       </c>
       <c r="D651" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E651">
         <v>5.9080963375586</v>
@@ -33980,7 +33971,7 @@
         <v>1</v>
       </c>
       <c r="P651" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
     </row>
     <row r="652" spans="1:16">
@@ -33994,7 +33985,7 @@
         <v>5.977845942063905</v>
       </c>
       <c r="D652" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E652">
         <v>5.9080963375586</v>
@@ -34030,7 +34021,7 @@
         <v>1</v>
       </c>
       <c r="P652" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
     </row>
     <row r="653" spans="1:16">
@@ -34094,7 +34085,7 @@
         <v>6.325113724849238</v>
       </c>
       <c r="D654" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E654">
         <v>5.966484401224733</v>
@@ -34144,7 +34135,7 @@
         <v>6.616965483162407</v>
       </c>
       <c r="D655" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E655">
         <v>5.966484401224733</v>
@@ -34380,7 +34371,7 @@
         <v>1</v>
       </c>
       <c r="P659" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
     </row>
     <row r="660" spans="1:16">
@@ -34394,7 +34385,7 @@
         <v>6.182411935806901</v>
       </c>
       <c r="D660" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E660">
         <v>5.820555041914538</v>
@@ -34430,7 +34421,7 @@
         <v>1</v>
       </c>
       <c r="P660" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
     </row>
     <row r="661" spans="1:16">
@@ -34444,7 +34435,7 @@
         <v>6.479370608860847</v>
       </c>
       <c r="D661" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E661">
         <v>5.820555041914538</v>
@@ -34480,7 +34471,7 @@
         <v>1</v>
       </c>
       <c r="P661" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
     </row>
     <row r="662" spans="1:16">
@@ -34494,7 +34485,7 @@
         <v>6.247760471854665</v>
       </c>
       <c r="D662" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E662">
         <v>5.820555041914538</v>
@@ -34530,7 +34521,7 @@
         <v>1</v>
       </c>
       <c r="P662" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
     </row>
     <row r="663" spans="1:16">
@@ -34644,7 +34635,7 @@
         <v>6.052746661470383</v>
       </c>
       <c r="D665" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E665">
         <v>5.747828147206722</v>
@@ -34694,7 +34685,7 @@
         <v>6.354345707327784</v>
       </c>
       <c r="D666" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E666">
         <v>5.747828147206722</v>
@@ -34744,7 +34735,7 @@
         <v>6.106229101349317</v>
       </c>
       <c r="D667" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E667">
         <v>5.747828147206722</v>
@@ -34894,7 +34885,7 @@
         <v>5.992378168346487</v>
       </c>
       <c r="D670" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E670">
         <v>5.919638041522585</v>
@@ -34944,7 +34935,7 @@
         <v>6.296137640849427</v>
       </c>
       <c r="D671" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E671">
         <v>5.919638041522585</v>
@@ -34994,7 +34985,7 @@
         <v>6.0403360886604</v>
       </c>
       <c r="D672" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E672">
         <v>5.919638041522585</v>
@@ -35080,7 +35071,7 @@
         <v>1</v>
       </c>
       <c r="P673" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="674" spans="1:16">
@@ -35130,7 +35121,7 @@
         <v>1</v>
       </c>
       <c r="P674" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="675" spans="1:16">
@@ -35144,7 +35135,7 @@
         <v>5.931074248482098</v>
       </c>
       <c r="D675" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E675">
         <v>5.817063063996034</v>
@@ -35180,7 +35171,7 @@
         <v>1</v>
       </c>
       <c r="P675" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="676" spans="1:16">
@@ -35194,7 +35185,7 @@
         <v>6.237027624047666</v>
       </c>
       <c r="D676" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E676">
         <v>5.817063063996034</v>
@@ -35230,7 +35221,7 @@
         <v>1</v>
       </c>
       <c r="P676" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="677" spans="1:16">
@@ -35244,7 +35235,7 @@
         <v>5.973422045250139</v>
       </c>
       <c r="D677" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E677">
         <v>5.817063063996034</v>
@@ -35280,7 +35271,7 @@
         <v>1</v>
       </c>
       <c r="P677" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="678" spans="1:16">
@@ -35394,7 +35385,7 @@
         <v>5.839386641650073</v>
       </c>
       <c r="D680" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E680">
         <v>4.893781158276536</v>
@@ -35444,7 +35435,7 @@
         <v>6.148621271038877</v>
       </c>
       <c r="D681" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E681">
         <v>4.893781158276536</v>
@@ -35494,7 +35485,7 @@
         <v>5.873343803641564</v>
       </c>
       <c r="D682" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E682">
         <v>4.893781158276536</v>
@@ -35594,7 +35585,7 @@
         <v>6.049313264972337</v>
       </c>
       <c r="D684" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E684">
         <v>4.936335249131968</v>
@@ -35644,7 +35635,7 @@
         <v>6.175722584965069</v>
       </c>
       <c r="D685" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E685">
         <v>4.936335249131968</v>
@@ -35694,7 +35685,7 @@
         <v>5.760924613317037</v>
       </c>
       <c r="D686" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E686">
         <v>4.936335249131968</v>
@@ -35844,7 +35835,7 @@
         <v>5.905539797299475</v>
       </c>
       <c r="D689" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E689">
         <v>5.270502414665344</v>
@@ -35894,7 +35885,7 @@
         <v>6.021734035283636</v>
       </c>
       <c r="D690" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E690">
         <v>5.270502414665344</v>
@@ -36044,7 +36035,7 @@
         <v>5.810134805942958</v>
       </c>
       <c r="D693" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="E693">
         <v>4.46837075668304</v>
@@ -36094,7 +36085,7 @@
         <v>5.919550534467003</v>
       </c>
       <c r="D694" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="E694">
         <v>4.46837075668304</v>
@@ -36144,7 +36135,7 @@
         <v>5.597681787127293</v>
       </c>
       <c r="D695" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="E695">
         <v>5.175448484795162</v>
@@ -36194,7 +36185,7 @@
         <v>5.69200276245871</v>
       </c>
       <c r="D696" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="E696">
         <v>5.175448484795162</v>
@@ -36280,7 +36271,7 @@
         <v>1</v>
       </c>
       <c r="P697" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
     </row>
     <row r="698" spans="1:16">
@@ -36330,7 +36321,7 @@
         <v>1</v>
       </c>
       <c r="P698" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
     </row>
     <row r="699" spans="1:16">
@@ -36380,7 +36371,7 @@
         <v>1</v>
       </c>
       <c r="P699" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
     </row>
     <row r="700" spans="1:16">
@@ -36430,7 +36421,7 @@
         <v>1</v>
       </c>
       <c r="P700" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
     </row>
     <row r="701" spans="1:16">
@@ -36444,7 +36435,7 @@
         <v>10.58920111380781</v>
       </c>
       <c r="D701" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="E701">
         <v>10.63805069137965</v>
@@ -36480,7 +36471,7 @@
         <v>1</v>
       </c>
       <c r="P701" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
     </row>
     <row r="702" spans="1:16">
@@ -36530,7 +36521,7 @@
         <v>1</v>
       </c>
       <c r="P702" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
     </row>
     <row r="703" spans="1:16">
@@ -36544,7 +36535,7 @@
         <v>13.29070024337744</v>
       </c>
       <c r="D703" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="E703">
         <v>12.1104855745369</v>
@@ -36580,7 +36571,7 @@
         <v>1</v>
       </c>
       <c r="P703" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
     </row>
     <row r="704" spans="1:16">
@@ -36630,7 +36621,7 @@
         <v>1</v>
       </c>
       <c r="P704" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
     </row>
     <row r="705" spans="1:16">
@@ -36644,7 +36635,7 @@
         <v>13.05967948318782</v>
       </c>
       <c r="D705" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="E705">
         <v>11.87581437344135</v>
@@ -36680,7 +36671,7 @@
         <v>1</v>
       </c>
       <c r="P705" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
     </row>
     <row r="706" spans="1:16">
@@ -36730,7 +36721,7 @@
         <v>1</v>
       </c>
       <c r="P706" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
     </row>
     <row r="707" spans="1:16">
@@ -36744,7 +36735,7 @@
         <v>12.8170626988293</v>
       </c>
       <c r="D707" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E707">
         <v>10.97022453374666</v>
@@ -36780,7 +36771,7 @@
         <v>1</v>
       </c>
       <c r="P707" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
     </row>
     <row r="708" spans="1:16">
@@ -36830,7 +36821,7 @@
         <v>1</v>
       </c>
       <c r="P708" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
     </row>
     <row r="709" spans="1:16">
@@ -36844,7 +36835,7 @@
         <v>12.5987805539735</v>
       </c>
       <c r="D709" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E709">
         <v>10.73863851098768</v>
@@ -36880,7 +36871,7 @@
         <v>1</v>
       </c>
       <c r="P709" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
     </row>
     <row r="710" spans="1:16">
@@ -36930,7 +36921,7 @@
         <v>1</v>
       </c>
       <c r="P710" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
     </row>
     <row r="711" spans="1:16">
@@ -36980,7 +36971,7 @@
         <v>1</v>
       </c>
       <c r="P711" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="712" spans="1:16">
@@ -37030,7 +37021,7 @@
         <v>1</v>
       </c>
       <c r="P712" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="713" spans="1:16">
@@ -37044,7 +37035,7 @@
         <v>12.45336310880131</v>
       </c>
       <c r="D713" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E713">
         <v>10.58435815154991</v>
@@ -37080,7 +37071,7 @@
         <v>1</v>
       </c>
       <c r="P713" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="714" spans="1:16">
@@ -37130,7 +37121,7 @@
         <v>1</v>
       </c>
       <c r="P714" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="715" spans="1:16">
@@ -37180,7 +37171,7 @@
         <v>1</v>
       </c>
       <c r="P715" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="716" spans="1:16">
@@ -37230,7 +37221,7 @@
         <v>1</v>
       </c>
       <c r="P716" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
     </row>
     <row r="717" spans="1:16">
@@ -37280,7 +37271,7 @@
         <v>1</v>
       </c>
       <c r="P717" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
     </row>
     <row r="718" spans="1:16">
@@ -37330,7 +37321,7 @@
         <v>1</v>
       </c>
       <c r="P718" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
     </row>
     <row r="719" spans="1:16">
@@ -37380,7 +37371,7 @@
         <v>1</v>
       </c>
       <c r="P719" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
     </row>
     <row r="720" spans="1:16">
@@ -37394,7 +37385,7 @@
         <v>12.29210392935995</v>
       </c>
       <c r="D720" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E720">
         <v>10.41327053453538</v>
@@ -37430,7 +37421,7 @@
         <v>1</v>
       </c>
       <c r="P720" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
     </row>
     <row r="721" spans="1:16">
@@ -37444,7 +37435,7 @@
         <v>9.171282848330055</v>
       </c>
       <c r="D721" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E721">
         <v>6.850968108671186</v>
@@ -37480,7 +37471,7 @@
         <v>1</v>
       </c>
       <c r="P721" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
     </row>
     <row r="722" spans="1:16">
@@ -37494,7 +37485,7 @@
         <v>8.830116243154617</v>
       </c>
       <c r="D722" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E722">
         <v>6.850968108671186</v>
@@ -37530,7 +37521,7 @@
         <v>1</v>
       </c>
       <c r="P722" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
     </row>
     <row r="723" spans="1:16">
@@ -37694,7 +37685,7 @@
         <v>12.09795277153261</v>
       </c>
       <c r="D726" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E726">
         <v>10.20728623616326</v>
@@ -37744,7 +37735,7 @@
         <v>8.629829382822578</v>
       </c>
       <c r="D727" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E727">
         <v>7.040051561279032</v>
@@ -37830,7 +37821,7 @@
         <v>1</v>
       </c>
       <c r="P728" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
     </row>
     <row r="729" spans="1:16">
@@ -37880,7 +37871,7 @@
         <v>1</v>
       </c>
       <c r="P729" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
     </row>
     <row r="730" spans="1:16">
@@ -37930,7 +37921,7 @@
         <v>1</v>
       </c>
       <c r="P730" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
     </row>
     <row r="731" spans="1:16">
@@ -37944,7 +37935,7 @@
         <v>11.86477339723001</v>
       </c>
       <c r="D731" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E731">
         <v>9.95989502640656</v>
@@ -37980,7 +37971,7 @@
         <v>1</v>
       </c>
       <c r="P731" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
     </row>
     <row r="732" spans="1:16">
@@ -37994,7 +37985,7 @@
         <v>8.389280908654889</v>
       </c>
       <c r="D732" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="E732">
         <v>6.803093216210396</v>
@@ -38030,7 +38021,7 @@
         <v>1</v>
       </c>
       <c r="P732" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
     </row>
     <row r="733" spans="1:16">
@@ -38080,7 +38071,7 @@
         <v>1</v>
       </c>
       <c r="P733" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
     </row>
     <row r="734" spans="1:16">
@@ -38130,7 +38121,7 @@
         <v>1</v>
       </c>
       <c r="P734" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
     </row>
     <row r="735" spans="1:16">
@@ -38180,7 +38171,7 @@
         <v>1</v>
       </c>
       <c r="P735" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
     </row>
     <row r="736" spans="1:16">
@@ -38230,7 +38221,7 @@
         <v>1</v>
       </c>
       <c r="P736" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
     </row>
     <row r="737" spans="1:16">
@@ -38244,7 +38235,7 @@
         <v>7.721090409497048</v>
       </c>
       <c r="D737" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E737">
         <v>6.845979077114176</v>
@@ -38280,7 +38271,7 @@
         <v>1</v>
       </c>
       <c r="P737" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
     </row>
     <row r="738" spans="1:16">
@@ -38330,7 +38321,7 @@
         <v>1</v>
       </c>
       <c r="P738" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
     </row>
     <row r="739" spans="1:16">
@@ -38380,7 +38371,7 @@
         <v>1</v>
       </c>
       <c r="P739" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
     </row>
     <row r="740" spans="1:16">
@@ -38430,7 +38421,7 @@
         <v>1</v>
       </c>
       <c r="P740" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
     </row>
     <row r="741" spans="1:16">
@@ -38444,7 +38435,7 @@
         <v>7.431928747420816</v>
       </c>
       <c r="D741" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="E741">
         <v>6.954602200047407</v>
@@ -38480,7 +38471,7 @@
         <v>1</v>
       </c>
       <c r="P741" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
     </row>
     <row r="742" spans="1:16">
@@ -38530,7 +38521,7 @@
         <v>1</v>
       </c>
       <c r="P742" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
     </row>
     <row r="743" spans="1:16">
@@ -38580,7 +38571,7 @@
         <v>1</v>
       </c>
       <c r="P743" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
     </row>
     <row r="744" spans="1:16">
@@ -38630,7 +38621,7 @@
         <v>1</v>
       </c>
       <c r="P744" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
     </row>
     <row r="745" spans="1:16">
@@ -38680,7 +38671,7 @@
         <v>1</v>
       </c>
       <c r="P745" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
     </row>
     <row r="746" spans="1:16">
@@ -38694,7 +38685,7 @@
         <v>7.15411432552343</v>
       </c>
       <c r="D746" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="E746">
         <v>7.077702572180645</v>
@@ -38730,7 +38721,7 @@
         <v>1</v>
       </c>
       <c r="P746" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
     </row>
     <row r="747" spans="1:16">
@@ -38994,7 +38985,7 @@
         <v>6.656074286112602</v>
       </c>
       <c r="D752" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="E752">
         <v>7.106777983579878</v>
@@ -39080,7 +39071,7 @@
         <v>1</v>
       </c>
       <c r="P753" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
     </row>
     <row r="754" spans="1:16">
@@ -39130,7 +39121,7 @@
         <v>1</v>
       </c>
       <c r="P754" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
     </row>
     <row r="755" spans="1:16">
@@ -39180,7 +39171,7 @@
         <v>1</v>
       </c>
       <c r="P755" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
     </row>
     <row r="756" spans="1:16">
@@ -39230,7 +39221,7 @@
         <v>1</v>
       </c>
       <c r="P756" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
     </row>
     <row r="757" spans="1:16">
@@ -39280,7 +39271,7 @@
         <v>1</v>
       </c>
       <c r="P757" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
     </row>
     <row r="758" spans="1:16">
@@ -39330,7 +39321,7 @@
         <v>1</v>
       </c>
       <c r="P758" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
     </row>
     <row r="759" spans="1:16">
@@ -39680,7 +39671,7 @@
         <v>1</v>
       </c>
       <c r="P765" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
     </row>
     <row r="766" spans="1:16">
@@ -39730,7 +39721,7 @@
         <v>1</v>
       </c>
       <c r="P766" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
     </row>
     <row r="767" spans="1:16">
@@ -39744,7 +39735,7 @@
         <v>5.189787984798581</v>
       </c>
       <c r="D767" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E767">
         <v>6.127393152460147</v>
@@ -39780,7 +39771,7 @@
         <v>1</v>
       </c>
       <c r="P767" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
     </row>
     <row r="768" spans="1:16">
@@ -39794,7 +39785,7 @@
         <v>5.337615079752425</v>
       </c>
       <c r="D768" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E768">
         <v>6.127393152460147</v>
@@ -39830,7 +39821,7 @@
         <v>1</v>
       </c>
       <c r="P768" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
     </row>
     <row r="769" spans="1:16">
@@ -39944,7 +39935,7 @@
         <v>4.573548410677798</v>
       </c>
       <c r="D771" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="E771">
         <v>5.983161604764781</v>
@@ -39994,7 +39985,7 @@
         <v>4.718587091269107</v>
       </c>
       <c r="D772" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="E772">
         <v>5.983161604764781</v>
@@ -40080,7 +40071,7 @@
         <v>1</v>
       </c>
       <c r="P773" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
     </row>
     <row r="774" spans="1:16">
@@ -40130,7 +40121,7 @@
         <v>1</v>
       </c>
       <c r="P774" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
     </row>
     <row r="775" spans="1:16">
@@ -40180,7 +40171,7 @@
         <v>1</v>
       </c>
       <c r="P775" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
     </row>
     <row r="776" spans="1:16">
@@ -40230,7 +40221,7 @@
         <v>1</v>
       </c>
       <c r="P776" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
     </row>
     <row r="777" spans="1:16">
@@ -40480,7 +40471,7 @@
         <v>1</v>
       </c>
       <c r="P781" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="782" spans="1:16">
@@ -40530,7 +40521,7 @@
         <v>1</v>
       </c>
       <c r="P782" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="783" spans="1:16">
@@ -40580,7 +40571,7 @@
         <v>1</v>
       </c>
       <c r="P783" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="784" spans="1:16">
@@ -40980,7 +40971,7 @@
         <v>1</v>
       </c>
       <c r="P791" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
     </row>
     <row r="792" spans="1:16">
@@ -41030,7 +41021,7 @@
         <v>1</v>
       </c>
       <c r="P792" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
     </row>
     <row r="793" spans="1:16">
@@ -41080,7 +41071,7 @@
         <v>1</v>
       </c>
       <c r="P793" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
     </row>
     <row r="794" spans="1:16">
@@ -41130,7 +41121,7 @@
         <v>1</v>
       </c>
       <c r="P794" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
     </row>
     <row r="795" spans="1:16">
@@ -41380,7 +41371,7 @@
         <v>1</v>
       </c>
       <c r="P799" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
     </row>
     <row r="800" spans="1:16">
@@ -41394,7 +41385,7 @@
         <v>1.03967143846625</v>
       </c>
       <c r="D800" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="E800">
         <v>2.609188567947417</v>
@@ -41430,7 +41421,7 @@
         <v>1</v>
       </c>
       <c r="P800" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
     </row>
     <row r="801" spans="1:16">
@@ -41444,7 +41435,7 @@
         <v>0.8130094478294367</v>
       </c>
       <c r="D801" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="E801">
         <v>2.609188567947417</v>
@@ -41480,7 +41471,7 @@
         <v>1</v>
       </c>
       <c r="P801" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
     </row>
     <row r="802" spans="1:16">
@@ -41530,7 +41521,7 @@
         <v>1</v>
       </c>
       <c r="P802" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
     </row>
     <row r="803" spans="1:16">
@@ -41544,7 +41535,7 @@
         <v>0.7465491084079581</v>
       </c>
       <c r="D803" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="E803">
         <v>2.329329691737918</v>
@@ -41580,7 +41571,7 @@
         <v>1</v>
       </c>
       <c r="P803" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
     </row>
     <row r="804" spans="1:16">
@@ -41594,7 +41585,7 @@
         <v>0.5106027000769942</v>
       </c>
       <c r="D804" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="E804">
         <v>2.329329691737918</v>
@@ -41630,7 +41621,7 @@
         <v>1</v>
       </c>
       <c r="P804" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
     </row>
     <row r="805" spans="1:16">
@@ -41644,7 +41635,7 @@
         <v>0.4893560218813207</v>
       </c>
       <c r="D805" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="E805">
         <v>2.083774301434204</v>
@@ -41694,7 +41685,7 @@
         <v>0.2452632261943108</v>
       </c>
       <c r="D806" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="E806">
         <v>2.083774301434204</v>
@@ -41744,7 +41735,7 @@
         <v>3.38720643044401</v>
       </c>
       <c r="D807" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E807">
         <v>1.346565161657761</v>
@@ -41794,7 +41785,7 @@
         <v>0.03330516332946587</v>
       </c>
       <c r="D808" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="E808">
         <v>1.648359228337185</v>
@@ -41844,7 +41835,7 @@
         <v>-0.2252326821759354</v>
       </c>
       <c r="D809" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="E809">
         <v>1.648359228337185</v>
@@ -41894,7 +41885,7 @@
         <v>2.979030594147371</v>
       </c>
       <c r="D810" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E810">
         <v>0.9008321958333205</v>
@@ -41944,7 +41935,7 @@
         <v>-0.3050434949915584</v>
       </c>
       <c r="D811" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="E811">
         <v>1.325320464057839</v>
@@ -41980,7 +41971,7 @@
         <v>1</v>
       </c>
       <c r="P811" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
     </row>
     <row r="812" spans="1:16">
@@ -41994,7 +41985,7 @@
         <v>-0.5742982663261245</v>
       </c>
       <c r="D812" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="E812">
         <v>1.325320464057839</v>
@@ -42030,7 +42021,7 @@
         <v>1</v>
       </c>
       <c r="P812" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
     </row>
     <row r="813" spans="1:16">
@@ -42044,7 +42035,7 @@
         <v>2.676200890003035</v>
       </c>
       <c r="D813" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E813">
         <v>0.570138484533139</v>
@@ -42080,7 +42071,7 @@
         <v>1</v>
       </c>
       <c r="P813" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
     </row>
     <row r="814" spans="1:16">
@@ -42094,7 +42085,7 @@
         <v>-1.542729235915701</v>
       </c>
       <c r="D814" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="E814">
         <v>0.8740710626510406</v>
@@ -42144,7 +42135,7 @@
         <v>-1.06190425457612</v>
       </c>
       <c r="D815" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="E815">
         <v>0.8740710626510406</v>
@@ -42194,7 +42185,7 @@
         <v>2.253181308968607</v>
       </c>
       <c r="D816" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E816">
         <v>0.1081959693489338</v>
@@ -42244,7 +42235,7 @@
         <v>-1.645106114375984</v>
       </c>
       <c r="D817" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="E817">
         <v>0.7789101756240804</v>
@@ -42294,7 +42285,7 @@
         <v>-1.164732132500994</v>
       </c>
       <c r="D818" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="E818">
         <v>0.7789101756240804</v>
@@ -42344,7 +42335,7 @@
         <v>1.705918320624114</v>
       </c>
       <c r="D819" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E819">
         <v>0.01078008499905536</v>
@@ -42394,7 +42385,7 @@
         <v>2.163973614874138</v>
       </c>
       <c r="D820" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E820">
         <v>0.01078008499905536</v>
@@ -42444,7 +42435,7 @@
         <v>2.083749225749141</v>
       </c>
       <c r="D821" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E821">
         <v>-0.02146380625091737</v>
@@ -42494,7 +42485,7 @@
         <v>-1.354990011712744</v>
       </c>
       <c r="D822" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="E822">
         <v>1.048577566205335</v>
@@ -42544,7 +42535,7 @@
         <v>-0.8733379853326184</v>
       </c>
       <c r="D823" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="E823">
         <v>1.048577566205335</v>
@@ -42594,7 +42585,7 @@
         <v>1.965361355164372</v>
       </c>
       <c r="D824" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E824">
         <v>0.2868376981059342</v>
@@ -42644,7 +42635,7 @@
         <v>2.41677081798775</v>
       </c>
       <c r="D825" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E825">
         <v>0.2868376981059342</v>
@@ -42694,7 +42685,7 @@
         <v>2.335779602159679</v>
       </c>
       <c r="D826" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E826">
         <v>0.246925539825213</v>
@@ -42744,7 +42735,7 @@
         <v>-1.093559587288276</v>
       </c>
       <c r="D827" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E827">
         <v>-1.564638644835625</v>
@@ -42794,7 +42785,7 @@
         <v>-1.266714738768137</v>
       </c>
       <c r="D828" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="E828">
         <v>0.4727739583005963</v>
@@ -42830,7 +42821,7 @@
         <v>1</v>
       </c>
       <c r="P828" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="829" spans="1:16">
@@ -42844,7 +42835,7 @@
         <v>-0.7846738345336348</v>
       </c>
       <c r="D829" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E829">
         <v>0.5188966710041001</v>
@@ -42880,7 +42871,7 @@
         <v>1</v>
       </c>
       <c r="P829" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="830" spans="1:16">
@@ -42894,7 +42885,7 @@
         <v>2.044303559603822</v>
       </c>
       <c r="D830" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E830">
         <v>0.3708353146523429</v>
@@ -42930,7 +42921,7 @@
         <v>1</v>
       </c>
       <c r="P830" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="831" spans="1:16">
@@ -42944,7 +42935,7 @@
         <v>2.412466315043719</v>
       </c>
       <c r="D831" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E831">
         <v>0.3285898892453361</v>
@@ -42980,7 +42971,7 @@
         <v>1</v>
       </c>
       <c r="P831" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="832" spans="1:16">
@@ -42994,7 +42985,7 @@
         <v>-1.016717323262487</v>
       </c>
       <c r="D832" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E832">
         <v>-1.725082876878652</v>
@@ -43030,7 +43021,7 @@
         <v>1</v>
       </c>
       <c r="P832" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="833" spans="1:16">
@@ -43044,7 +43035,7 @@
         <v>-1.012419255686936</v>
       </c>
       <c r="D833" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="E833">
         <v>0.7130663861460427</v>
@@ -43094,7 +43085,7 @@
         <v>2.271713176632382</v>
       </c>
       <c r="D834" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E834">
         <v>0.563841217205912</v>
@@ -43144,7 +43135,7 @@
         <v>2.633378514442889</v>
       </c>
       <c r="D835" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E835">
         <v>0.563841217205912</v>
@@ -43194,7 +43185,7 @@
         <v>-0.7953570260957719</v>
       </c>
       <c r="D836" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E836">
         <v>-0.6798364854873604</v>
@@ -43244,7 +43235,7 @@
         <v>-1.154980882524804</v>
       </c>
       <c r="D837" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="E837">
         <v>0.3632888214250194</v>
@@ -43280,7 +43271,7 @@
         <v>1</v>
       </c>
       <c r="P837" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="838" spans="1:16">
@@ -43294,7 +43285,7 @@
         <v>2.144224144702488</v>
       </c>
       <c r="D838" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E838">
         <v>0.3406232020973725</v>
@@ -43330,7 +43321,7 @@
         <v>1</v>
       </c>
       <c r="P838" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="839" spans="1:16">
@@ -43344,7 +43335,7 @@
         <v>2.509532026282422</v>
       </c>
       <c r="D839" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E839">
         <v>0.3406232020973725</v>
@@ -43380,7 +43371,7 @@
         <v>1</v>
       </c>
       <c r="P839" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="840" spans="1:16">
@@ -43430,7 +43421,7 @@
         <v>1</v>
       </c>
       <c r="P840" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="841" spans="1:16">
@@ -43444,7 +43435,7 @@
         <v>-0.7435135480053319</v>
       </c>
       <c r="D841" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="E841">
         <v>0.7484730002152737</v>
@@ -43594,7 +43585,7 @@
         <v>-0.3742444036399846</v>
       </c>
       <c r="D844" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="E844">
         <v>1.094154467958163</v>
@@ -43630,7 +43621,7 @@
         <v>1</v>
       </c>
       <c r="P844" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="845" spans="1:16">
@@ -43680,7 +43671,7 @@
         <v>1</v>
       </c>
       <c r="P845" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="846" spans="1:16">
@@ -43730,7 +43721,7 @@
         <v>1</v>
       </c>
       <c r="P846" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="847" spans="1:16">
@@ -43744,7 +43735,7 @@
         <v>-0.2301600625778306</v>
       </c>
       <c r="D847" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="E847">
         <v>1.229035183710177</v>
@@ -43780,7 +43771,7 @@
         <v>1</v>
       </c>
       <c r="P847" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
     </row>
     <row r="848" spans="1:16">
@@ -43830,7 +43821,7 @@
         <v>1</v>
       </c>
       <c r="P848" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
     </row>
     <row r="849" spans="1:16">
@@ -43880,7 +43871,7 @@
         <v>1</v>
       </c>
       <c r="P849" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
     </row>
     <row r="850" spans="1:16">
@@ -43894,7 +43885,7 @@
         <v>-0.008911774850371756</v>
       </c>
       <c r="D850" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E850">
         <v>0.5721947646345491</v>
@@ -43930,7 +43921,7 @@
         <v>1</v>
       </c>
       <c r="P850" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
     </row>
     <row r="851" spans="1:16">
@@ -43944,7 +43935,7 @@
         <v>-0.1112036199752922</v>
       </c>
       <c r="D851" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="E851">
         <v>1.340393087027532</v>
@@ -44094,7 +44085,7 @@
         <v>0.09903988671845454</v>
       </c>
       <c r="D854" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="E854">
         <v>1.106317252320714</v>
@@ -44144,7 +44135,7 @@
         <v>-0.06944114310240224</v>
       </c>
       <c r="D855" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="E855">
         <v>1.379487916699293</v>
@@ -44180,7 +44171,7 @@
         <v>1</v>
       </c>
       <c r="P855" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="856" spans="1:16">
@@ -44230,7 +44221,7 @@
         <v>1</v>
       </c>
       <c r="P856" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="857" spans="1:16">
@@ -44280,7 +44271,7 @@
         <v>1</v>
       </c>
       <c r="P857" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="858" spans="1:16">
@@ -44294,7 +44285,7 @@
         <v>0.1369388745414319</v>
       </c>
       <c r="D858" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="E858">
         <v>1.371101739245933</v>
@@ -44330,7 +44321,7 @@
         <v>1</v>
       </c>
       <c r="P858" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="859" spans="1:16">
@@ -44344,10 +44335,10 @@
         <v>12.65888206048432</v>
       </c>
       <c r="D859" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E859">
-        <v>13.43349103432044</v>
+        <v>13.67315026490144</v>
       </c>
       <c r="F859">
         <v>1</v>
@@ -44356,10 +44347,10 @@
         <v>0.04978111793951567</v>
       </c>
       <c r="H859">
-        <v>0.04844650896567956</v>
+        <v>0.04792684973509856</v>
       </c>
       <c r="I859">
-        <v>0.7746089738361199</v>
+        <v>1.014268204417121</v>
       </c>
       <c r="J859">
         <v>0.8436871790688943</v>
@@ -44371,16 +44362,16 @@
         <v>31.22</v>
       </c>
       <c r="M859">
-        <v>20.75</v>
+        <v>20.3</v>
       </c>
       <c r="N859">
-        <v>30.94</v>
+        <v>30.8</v>
       </c>
       <c r="O859">
         <v>1</v>
       </c>
       <c r="P859" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
     </row>
     <row r="860" spans="1:16">
@@ -44391,125 +44382,125 @@
         <v>155</v>
       </c>
       <c r="C860">
-        <v>13.92659718804111</v>
+        <v>14.18888206048432</v>
       </c>
       <c r="D860" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="E860">
-        <v>14.18888206048432</v>
+        <v>15.13291000897221</v>
       </c>
       <c r="F860">
         <v>-1</v>
       </c>
       <c r="G860">
-        <v>0.04843340281195889</v>
+        <v>0.05131111793951568</v>
       </c>
       <c r="H860">
-        <v>0.05131111793951568</v>
+        <v>0.05132708999102778</v>
       </c>
       <c r="I860">
-        <v>-0.2622848724432139</v>
+        <v>-0.9440279484878893</v>
       </c>
       <c r="J860">
         <v>0.8436871790688943</v>
       </c>
       <c r="K860">
-        <v>20.45</v>
+        <v>22</v>
       </c>
       <c r="L860">
-        <v>31.18</v>
+        <v>32.75</v>
       </c>
       <c r="M860">
-        <v>22</v>
+        <v>21.45</v>
       </c>
       <c r="N860">
-        <v>32.75</v>
+        <v>33.23</v>
       </c>
       <c r="O860">
         <v>1</v>
       </c>
       <c r="P860" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
     </row>
     <row r="861" spans="1:16">
       <c r="A861" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B861" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C861">
-        <v>13.88635693211188</v>
+        <v>12.57849638595733</v>
       </c>
       <c r="D861" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="E861">
-        <v>14.18888206048432</v>
+        <v>13.59897621067881</v>
       </c>
       <c r="F861">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G861">
-        <v>0.05033364306788812</v>
+        <v>0.04986150361404267</v>
       </c>
       <c r="H861">
-        <v>0.05131111793951568</v>
+        <v>0.0480010237893212</v>
       </c>
       <c r="I861">
-        <v>-0.3025251283724444</v>
+        <v>1.02047982472148</v>
       </c>
       <c r="J861">
-        <v>0.8436871790688943</v>
+        <v>0.8473410733655758</v>
       </c>
       <c r="K861">
-        <v>21.6</v>
+        <v>22</v>
       </c>
       <c r="L861">
-        <v>32.11</v>
+        <v>31.22</v>
       </c>
       <c r="M861">
-        <v>22</v>
+        <v>20.3</v>
       </c>
       <c r="N861">
-        <v>32.75</v>
+        <v>30.8</v>
       </c>
       <c r="O861">
         <v>1</v>
       </c>
       <c r="P861" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="862" spans="1:16">
       <c r="A862" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B862" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C862">
-        <v>12.57849638595733</v>
+        <v>14.10849638595733</v>
       </c>
       <c r="D862" t="s">
         <v>267</v>
       </c>
       <c r="E862">
-        <v>13.3576727276643</v>
+        <v>15.0545339763084</v>
       </c>
       <c r="F862">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G862">
-        <v>0.04986150361404267</v>
+        <v>0.05139150361404267</v>
       </c>
       <c r="H862">
-        <v>0.0485223272723357</v>
+        <v>0.0514054660236916</v>
       </c>
       <c r="I862">
-        <v>0.7791763417069717</v>
+        <v>-0.9460375903510645</v>
       </c>
       <c r="J862">
         <v>0.8473410733655758</v>
@@ -44518,98 +44509,98 @@
         <v>22</v>
       </c>
       <c r="L862">
-        <v>31.22</v>
+        <v>32.75</v>
       </c>
       <c r="M862">
-        <v>20.75</v>
+        <v>21.45</v>
       </c>
       <c r="N862">
-        <v>30.94</v>
+        <v>33.23</v>
       </c>
       <c r="O862">
         <v>1</v>
       </c>
       <c r="P862" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
     </row>
     <row r="863" spans="1:16">
       <c r="A863" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B863" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C863">
-        <v>13.85187504967397</v>
+        <v>12.51871891898833</v>
       </c>
       <c r="D863" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="E863">
-        <v>13.28849638595733</v>
+        <v>13.54381791161196</v>
       </c>
       <c r="F863">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G863">
-        <v>0.04850812495032602</v>
+        <v>0.04992128108101167</v>
       </c>
       <c r="H863">
-        <v>0.05057150361404267</v>
+        <v>0.04805618208838804</v>
       </c>
       <c r="I863">
-        <v>0.5633786637166445</v>
+        <v>1.025098992623629</v>
       </c>
       <c r="J863">
-        <v>0.8473410733655758</v>
+        <v>0.8500582309550758</v>
       </c>
       <c r="K863">
-        <v>20.45</v>
+        <v>22</v>
       </c>
       <c r="L863">
-        <v>31.18</v>
+        <v>31.22</v>
       </c>
       <c r="M863">
-        <v>22</v>
+        <v>20.3</v>
       </c>
       <c r="N863">
-        <v>31.93</v>
+        <v>30.8</v>
       </c>
       <c r="O863">
         <v>1</v>
       </c>
       <c r="P863" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="864" spans="1:16">
       <c r="A864" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B864" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C864">
-        <v>12.51871891898833</v>
+        <v>14.04871891898833</v>
       </c>
       <c r="D864" t="s">
         <v>267</v>
       </c>
       <c r="E864">
-        <v>13.30129170768218</v>
+        <v>14.99625094601362</v>
       </c>
       <c r="F864">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G864">
-        <v>0.04992128108101167</v>
+        <v>0.05145128108101167</v>
       </c>
       <c r="H864">
-        <v>0.04857870829231783</v>
+        <v>0.05146374905398637</v>
       </c>
       <c r="I864">
-        <v>0.7825727886938481</v>
+        <v>-0.9475320270252894</v>
       </c>
       <c r="J864">
         <v>0.8500582309550758</v>
@@ -44618,219 +44609,69 @@
         <v>22</v>
       </c>
       <c r="L864">
-        <v>31.22</v>
+        <v>32.75</v>
       </c>
       <c r="M864">
-        <v>20.75</v>
+        <v>21.45</v>
       </c>
       <c r="N864">
-        <v>30.94</v>
+        <v>33.23</v>
       </c>
       <c r="O864">
         <v>1</v>
       </c>
       <c r="P864" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
     </row>
     <row r="865" spans="1:16">
       <c r="A865" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B865" t="s">
         <v>155</v>
       </c>
       <c r="C865">
-        <v>13.7963091769687</v>
+        <v>14.01404163848113</v>
       </c>
       <c r="D865" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="E865">
-        <v>14.04871891898833</v>
+        <v>14.9624405975191</v>
       </c>
       <c r="F865">
         <v>-1</v>
       </c>
       <c r="G865">
-        <v>0.0485636908230313</v>
+        <v>0.05148595836151887</v>
       </c>
       <c r="H865">
-        <v>0.05145128108101167</v>
+        <v>0.05149755940248089</v>
       </c>
       <c r="I865">
-        <v>-0.2524097420196334</v>
+        <v>-0.94839895903797</v>
       </c>
       <c r="J865">
-        <v>0.8500582309550758</v>
+        <v>0.8516344709781304</v>
       </c>
       <c r="K865">
-        <v>20.45</v>
+        <v>22</v>
       </c>
       <c r="L865">
-        <v>31.18</v>
+        <v>32.75</v>
       </c>
       <c r="M865">
-        <v>22</v>
+        <v>21.45</v>
       </c>
       <c r="N865">
-        <v>32.75</v>
+        <v>33.23</v>
       </c>
       <c r="O865">
         <v>1</v>
       </c>
       <c r="P865" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="866" spans="1:16">
-      <c r="A866" s="1">
-        <v>2</v>
-      </c>
-      <c r="B866" t="s">
-        <v>156</v>
-      </c>
-      <c r="C866">
-        <v>13.74874221137036</v>
-      </c>
-      <c r="D866" t="s">
-        <v>268</v>
-      </c>
-      <c r="E866">
-        <v>14.04871891898833</v>
-      </c>
-      <c r="F866">
-        <v>-1</v>
-      </c>
-      <c r="G866">
-        <v>0.05047125778862965</v>
-      </c>
-      <c r="H866">
-        <v>0.05145128108101167</v>
-      </c>
-      <c r="I866">
-        <v>-0.2999767076179722</v>
-      </c>
-      <c r="J866">
-        <v>0.8500582309550758</v>
-      </c>
-      <c r="K866">
-        <v>21.6</v>
-      </c>
-      <c r="L866">
-        <v>32.11</v>
-      </c>
-      <c r="M866">
-        <v>22</v>
-      </c>
-      <c r="N866">
-        <v>32.75</v>
-      </c>
-      <c r="O866">
-        <v>1</v>
-      </c>
-      <c r="P866" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="867" spans="1:16">
-      <c r="A867" s="1">
-        <v>0</v>
-      </c>
-      <c r="B867" t="s">
-        <v>155</v>
-      </c>
-      <c r="C867">
-        <v>13.76407506849723</v>
-      </c>
-      <c r="D867" t="s">
-        <v>269</v>
-      </c>
-      <c r="E867">
-        <v>13.19404163848113</v>
-      </c>
-      <c r="F867">
-        <v>-1</v>
-      </c>
-      <c r="G867">
-        <v>0.04859592493150276</v>
-      </c>
-      <c r="H867">
-        <v>0.05066595836151887</v>
-      </c>
-      <c r="I867">
-        <v>0.5700334300161032</v>
-      </c>
-      <c r="J867">
-        <v>0.8516344709781304</v>
-      </c>
-      <c r="K867">
-        <v>20.45</v>
-      </c>
-      <c r="L867">
-        <v>31.18</v>
-      </c>
-      <c r="M867">
-        <v>22</v>
-      </c>
-      <c r="N867">
-        <v>31.93</v>
-      </c>
-      <c r="O867">
-        <v>1</v>
-      </c>
-      <c r="P867" t="s">
         <v>154</v>
-      </c>
-    </row>
-    <row r="868" spans="1:16">
-      <c r="A868" s="1">
-        <v>0</v>
-      </c>
-      <c r="B868" t="s">
-        <v>155</v>
-      </c>
-      <c r="C868">
-        <v>13.6867028791849</v>
-      </c>
-      <c r="D868" t="s">
-        <v>269</v>
-      </c>
-      <c r="E868">
-        <v>13.11080505340185</v>
-      </c>
-      <c r="F868">
-        <v>-1</v>
-      </c>
-      <c r="G868">
-        <v>0.0486732971208151</v>
-      </c>
-      <c r="H868">
-        <v>0.05074919494659815</v>
-      </c>
-      <c r="I868">
-        <v>0.575897825783052</v>
-      </c>
-      <c r="J868">
-        <v>0.8554179521180978</v>
-      </c>
-      <c r="K868">
-        <v>20.45</v>
-      </c>
-      <c r="L868">
-        <v>31.18</v>
-      </c>
-      <c r="M868">
-        <v>22</v>
-      </c>
-      <c r="N868">
-        <v>31.93</v>
-      </c>
-      <c r="O868">
-        <v>1</v>
-      </c>
-      <c r="P868" t="s">
-        <v>353</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-00763-000063.xlsx
+++ b/s60_signal/position-00763-000063.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2607" uniqueCount="351">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2610" uniqueCount="352">
   <si>
     <t>trade_time</t>
   </si>
@@ -481,7 +481,7 @@
     <t>2021-11-26</t>
   </si>
   <si>
-    <t>2021-12-14</t>
+    <t>2021-12-15</t>
   </si>
   <si>
     <t>2017-03-17</t>
@@ -817,7 +817,7 @@
     <t>2021-12-06</t>
   </si>
   <si>
-    <t>2021-12-15</t>
+    <t>2021-12-16</t>
   </si>
   <si>
     <t>2017-02-08</t>
@@ -1067,6 +1067,9 @@
   </si>
   <si>
     <t>2021-11-25</t>
+  </si>
+  <si>
+    <t>2021-11-29</t>
   </si>
 </sst>
 </file>
@@ -1424,7 +1427,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P865"/>
+  <dimension ref="A1:P866"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -44382,40 +44385,40 @@
         <v>155</v>
       </c>
       <c r="C860">
-        <v>14.18888206048432</v>
+        <v>15.13291000897221</v>
       </c>
       <c r="D860" t="s">
         <v>267</v>
       </c>
       <c r="E860">
-        <v>15.13291000897221</v>
+        <v>14.93509436792566</v>
       </c>
       <c r="F860">
         <v>-1</v>
       </c>
       <c r="G860">
-        <v>0.05131111793951568</v>
+        <v>0.05132708999102778</v>
       </c>
       <c r="H860">
-        <v>0.05132708999102778</v>
+        <v>0.05104490563207434</v>
       </c>
       <c r="I860">
-        <v>-0.9440279484878893</v>
+        <v>0.1978156410465495</v>
       </c>
       <c r="J860">
         <v>0.8436871790688943</v>
       </c>
       <c r="K860">
-        <v>22</v>
+        <v>21.45</v>
       </c>
       <c r="L860">
-        <v>32.75</v>
+        <v>33.23</v>
       </c>
       <c r="M860">
-        <v>21.45</v>
+        <v>21.4</v>
       </c>
       <c r="N860">
-        <v>33.23</v>
+        <v>32.99</v>
       </c>
       <c r="O860">
         <v>1</v>
@@ -44482,40 +44485,40 @@
         <v>155</v>
       </c>
       <c r="C862">
-        <v>14.10849638595733</v>
+        <v>15.0545339763084</v>
       </c>
       <c r="D862" t="s">
         <v>267</v>
       </c>
       <c r="E862">
-        <v>15.0545339763084</v>
+        <v>14.85690102997668</v>
       </c>
       <c r="F862">
         <v>-1</v>
       </c>
       <c r="G862">
-        <v>0.05139150361404267</v>
+        <v>0.0514054660236916</v>
       </c>
       <c r="H862">
-        <v>0.0514054660236916</v>
+        <v>0.05112309897002332</v>
       </c>
       <c r="I862">
-        <v>-0.9460375903510645</v>
+        <v>0.1976329463317157</v>
       </c>
       <c r="J862">
         <v>0.8473410733655758</v>
       </c>
       <c r="K862">
-        <v>22</v>
+        <v>21.45</v>
       </c>
       <c r="L862">
-        <v>32.75</v>
+        <v>33.23</v>
       </c>
       <c r="M862">
-        <v>21.45</v>
+        <v>21.4</v>
       </c>
       <c r="N862">
-        <v>33.23</v>
+        <v>32.99</v>
       </c>
       <c r="O862">
         <v>1</v>
@@ -44582,40 +44585,40 @@
         <v>155</v>
       </c>
       <c r="C864">
-        <v>14.04871891898833</v>
+        <v>14.99625094601362</v>
       </c>
       <c r="D864" t="s">
         <v>267</v>
       </c>
       <c r="E864">
-        <v>14.99625094601362</v>
+        <v>14.79875385756138</v>
       </c>
       <c r="F864">
         <v>-1</v>
       </c>
       <c r="G864">
-        <v>0.05145128108101167</v>
+        <v>0.05146374905398637</v>
       </c>
       <c r="H864">
-        <v>0.05146374905398637</v>
+        <v>0.05118124614243862</v>
       </c>
       <c r="I864">
-        <v>-0.9475320270252894</v>
+        <v>0.1974970884522413</v>
       </c>
       <c r="J864">
         <v>0.8500582309550758</v>
       </c>
       <c r="K864">
-        <v>22</v>
+        <v>21.45</v>
       </c>
       <c r="L864">
-        <v>32.75</v>
+        <v>33.23</v>
       </c>
       <c r="M864">
-        <v>21.45</v>
+        <v>21.4</v>
       </c>
       <c r="N864">
-        <v>33.23</v>
+        <v>32.99</v>
       </c>
       <c r="O864">
         <v>1</v>
@@ -44632,46 +44635,96 @@
         <v>155</v>
       </c>
       <c r="C865">
-        <v>14.01404163848113</v>
+        <v>14.9624405975191</v>
       </c>
       <c r="D865" t="s">
         <v>267</v>
       </c>
       <c r="E865">
-        <v>14.9624405975191</v>
+        <v>14.76502232106801</v>
       </c>
       <c r="F865">
         <v>-1</v>
       </c>
       <c r="G865">
-        <v>0.05148595836151887</v>
+        <v>0.05149755940248089</v>
       </c>
       <c r="H865">
-        <v>0.05149755940248089</v>
+        <v>0.05121497767893199</v>
       </c>
       <c r="I865">
-        <v>-0.94839895903797</v>
+        <v>0.1974182764510886</v>
       </c>
       <c r="J865">
         <v>0.8516344709781304</v>
       </c>
       <c r="K865">
-        <v>22</v>
+        <v>21.45</v>
       </c>
       <c r="L865">
-        <v>32.75</v>
+        <v>33.23</v>
       </c>
       <c r="M865">
-        <v>21.45</v>
+        <v>21.4</v>
       </c>
       <c r="N865">
-        <v>33.23</v>
+        <v>32.99</v>
       </c>
       <c r="O865">
         <v>1</v>
       </c>
       <c r="P865" t="s">
         <v>154</v>
+      </c>
+    </row>
+    <row r="866" spans="1:16">
+      <c r="A866" s="1">
+        <v>0</v>
+      </c>
+      <c r="B866" t="s">
+        <v>155</v>
+      </c>
+      <c r="C866">
+        <v>14.8812849270668</v>
+      </c>
+      <c r="D866" t="s">
+        <v>267</v>
+      </c>
+      <c r="E866">
+        <v>14.68405582467271</v>
+      </c>
+      <c r="F866">
+        <v>-1</v>
+      </c>
+      <c r="G866">
+        <v>0.05157871507293319</v>
+      </c>
+      <c r="H866">
+        <v>0.05129594417532729</v>
+      </c>
+      <c r="I866">
+        <v>0.1972291023940898</v>
+      </c>
+      <c r="J866">
+        <v>0.8554179521180978</v>
+      </c>
+      <c r="K866">
+        <v>21.45</v>
+      </c>
+      <c r="L866">
+        <v>33.23</v>
+      </c>
+      <c r="M866">
+        <v>21.4</v>
+      </c>
+      <c r="N866">
+        <v>32.99</v>
+      </c>
+      <c r="O866">
+        <v>1</v>
+      </c>
+      <c r="P866" t="s">
+        <v>351</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-00763-000063.xlsx
+++ b/s60_signal/position-00763-000063.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2610" uniqueCount="352">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2613" uniqueCount="354">
   <si>
     <t>trade_time</t>
   </si>
@@ -484,6 +484,9 @@
     <t>2021-12-15</t>
   </si>
   <si>
+    <t>2021-12-02</t>
+  </si>
+  <si>
     <t>2017-03-17</t>
   </si>
   <si>
@@ -817,7 +820,10 @@
     <t>2021-12-06</t>
   </si>
   <si>
-    <t>2021-12-16</t>
+    <t>2021-12-20</t>
+  </si>
+  <si>
+    <t>2021-12-08</t>
   </si>
   <si>
     <t>2017-02-08</t>
@@ -1427,7 +1433,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P866"/>
+  <dimension ref="A1:P867"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -1488,7 +1494,7 @@
         <v>8.357775317423281</v>
       </c>
       <c r="D2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E2">
         <v>9.239078272099615</v>
@@ -1524,7 +1530,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -1538,7 +1544,7 @@
         <v>9.433191964550923</v>
       </c>
       <c r="D3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E3">
         <v>9.285575452539577</v>
@@ -1574,7 +1580,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -1588,7 +1594,7 @@
         <v>9.420218808988363</v>
       </c>
       <c r="D4" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E4">
         <v>9.285575452539577</v>
@@ -1624,7 +1630,7 @@
         <v>1</v>
       </c>
       <c r="P4" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -1638,7 +1644,7 @@
         <v>9.27302954676334</v>
       </c>
       <c r="D5" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E5">
         <v>9.285575452539577</v>
@@ -1674,7 +1680,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -1688,7 +1694,7 @@
         <v>8.163141562328137</v>
       </c>
       <c r="D6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E6">
         <v>8.870417830135191</v>
@@ -1724,7 +1730,7 @@
         <v>1</v>
       </c>
       <c r="P6" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -1738,7 +1744,7 @@
         <v>8.167981542028786</v>
       </c>
       <c r="D7" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E7">
         <v>8.870417830135191</v>
@@ -1774,7 +1780,7 @@
         <v>1</v>
       </c>
       <c r="P7" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -1788,7 +1794,7 @@
         <v>9.039124544167011</v>
       </c>
       <c r="D8" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E8">
         <v>9.113918803782131</v>
@@ -1824,7 +1830,7 @@
         <v>1</v>
       </c>
       <c r="P8" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -1838,7 +1844,7 @@
         <v>9.052076876787602</v>
       </c>
       <c r="D9" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E9">
         <v>9.113918803782131</v>
@@ -1874,7 +1880,7 @@
         <v>1</v>
       </c>
       <c r="P9" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -1888,7 +1894,7 @@
         <v>8.972076876787604</v>
       </c>
       <c r="D10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E10">
         <v>9.113918803782131</v>
@@ -1924,7 +1930,7 @@
         <v>1</v>
       </c>
       <c r="P10" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -1938,7 +1944,7 @@
         <v>1.247895028504875</v>
       </c>
       <c r="D11" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E11">
         <v>5.93332434483856</v>
@@ -1974,7 +1980,7 @@
         <v>1</v>
       </c>
       <c r="P11" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -1988,7 +1994,7 @@
         <v>2.464515501370315</v>
       </c>
       <c r="D12" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E12">
         <v>5.93332434483856</v>
@@ -2024,7 +2030,7 @@
         <v>1</v>
       </c>
       <c r="P12" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -2074,7 +2080,7 @@
         <v>1</v>
       </c>
       <c r="P13" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -2088,7 +2094,7 @@
         <v>1.224092499726471</v>
       </c>
       <c r="D14" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E14">
         <v>5.913320521841428</v>
@@ -2124,7 +2130,7 @@
         <v>1</v>
       </c>
       <c r="P14" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -2138,7 +2144,7 @@
         <v>2.442814384300704</v>
       </c>
       <c r="D15" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E15">
         <v>5.913320521841428</v>
@@ -2174,7 +2180,7 @@
         <v>1</v>
       </c>
       <c r="P15" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -2188,7 +2194,7 @@
         <v>8.399951396166678</v>
       </c>
       <c r="D16" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E16">
         <v>7.154665097353277</v>
@@ -2224,7 +2230,7 @@
         <v>1</v>
       </c>
       <c r="P16" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -2238,7 +2244,7 @@
         <v>1.231818368992485</v>
       </c>
       <c r="D17" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E17">
         <v>5.919813400087062</v>
@@ -2274,7 +2280,7 @@
         <v>1</v>
       </c>
       <c r="P17" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -2288,7 +2294,7 @@
         <v>2.449858173427781</v>
       </c>
       <c r="D18" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E18">
         <v>5.919813400087062</v>
@@ -2324,7 +2330,7 @@
         <v>1</v>
       </c>
       <c r="P18" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -2374,7 +2380,7 @@
         <v>1</v>
       </c>
       <c r="P19" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="20" spans="1:16">
@@ -2388,7 +2394,7 @@
         <v>1.145797529921555</v>
       </c>
       <c r="D20" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E20">
         <v>5.847520844331356</v>
@@ -2424,7 +2430,7 @@
         <v>1</v>
       </c>
       <c r="P20" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -2438,7 +2444,7 @@
         <v>2.37143170385038</v>
       </c>
       <c r="D21" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E21">
         <v>5.847520844331356</v>
@@ -2474,7 +2480,7 @@
         <v>1</v>
       </c>
       <c r="P21" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -2488,7 +2494,7 @@
         <v>8.323251570058975</v>
       </c>
       <c r="D22" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E22">
         <v>6.49770468378167</v>
@@ -2524,7 +2530,7 @@
         <v>1</v>
       </c>
       <c r="P22" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="23" spans="1:16">
@@ -2538,7 +2544,7 @@
         <v>8.298928068060523</v>
       </c>
       <c r="D23" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E23">
         <v>6.513844529583032</v>
@@ -2624,7 +2630,7 @@
         <v>1</v>
       </c>
       <c r="P24" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="25" spans="1:16">
@@ -2674,7 +2680,7 @@
         <v>1</v>
       </c>
       <c r="P25" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="26" spans="1:16">
@@ -2688,7 +2694,7 @@
         <v>4.521898732172186</v>
       </c>
       <c r="D26" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E26">
         <v>7.471272137184702</v>
@@ -2724,7 +2730,7 @@
         <v>1</v>
       </c>
       <c r="P26" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="27" spans="1:16">
@@ -2774,7 +2780,7 @@
         <v>1</v>
       </c>
       <c r="P27" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="28" spans="1:16">
@@ -2824,7 +2830,7 @@
         <v>1</v>
       </c>
       <c r="P28" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -2838,7 +2844,7 @@
         <v>10.06347633639325</v>
       </c>
       <c r="D29" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E29">
         <v>8.926863738767604</v>
@@ -2874,7 +2880,7 @@
         <v>1</v>
       </c>
       <c r="P29" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -3038,7 +3044,7 @@
         <v>10.57243502356749</v>
       </c>
       <c r="D33" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E33">
         <v>11.2289160904059</v>
@@ -3088,7 +3094,7 @@
         <v>10.58025171866791</v>
       </c>
       <c r="D34" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E34">
         <v>11.2289160904059</v>
@@ -3138,7 +3144,7 @@
         <v>6.89098969886382</v>
       </c>
       <c r="D35" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E35">
         <v>9.162922766970905</v>
@@ -3174,7 +3180,7 @@
         <v>1</v>
       </c>
       <c r="P35" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -3224,7 +3230,7 @@
         <v>1</v>
       </c>
       <c r="P36" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="37" spans="1:16">
@@ -3274,7 +3280,7 @@
         <v>1</v>
       </c>
       <c r="P37" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="38" spans="1:16">
@@ -3324,7 +3330,7 @@
         <v>1</v>
       </c>
       <c r="P38" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="39" spans="1:16">
@@ -3338,7 +3344,7 @@
         <v>10.57710841036202</v>
       </c>
       <c r="D39" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E39">
         <v>10.91875227586742</v>
@@ -3374,7 +3380,7 @@
         <v>1</v>
       </c>
       <c r="P39" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="40" spans="1:16">
@@ -3388,7 +3394,7 @@
         <v>10.58544939256899</v>
       </c>
       <c r="D40" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E40">
         <v>10.91875227586742</v>
@@ -3424,7 +3430,7 @@
         <v>1</v>
       </c>
       <c r="P40" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="41" spans="1:16">
@@ -3474,7 +3480,7 @@
         <v>1</v>
       </c>
       <c r="P41" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="42" spans="1:16">
@@ -3524,7 +3530,7 @@
         <v>1</v>
       </c>
       <c r="P42" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="43" spans="1:16">
@@ -3574,7 +3580,7 @@
         <v>1</v>
       </c>
       <c r="P43" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="44" spans="1:16">
@@ -3588,7 +3594,7 @@
         <v>10.50706987192051</v>
       </c>
       <c r="D44" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E44">
         <v>9.836117792760128</v>
@@ -3624,7 +3630,7 @@
         <v>1</v>
       </c>
       <c r="P44" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -3788,7 +3794,7 @@
         <v>11.00643298606593</v>
       </c>
       <c r="D48" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E48">
         <v>10.08970532444388</v>
@@ -3874,7 +3880,7 @@
         <v>1</v>
       </c>
       <c r="P49" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="50" spans="1:16">
@@ -3924,7 +3930,7 @@
         <v>1</v>
       </c>
       <c r="P50" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="51" spans="1:16">
@@ -3974,7 +3980,7 @@
         <v>1</v>
       </c>
       <c r="P51" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="52" spans="1:16">
@@ -4024,7 +4030,7 @@
         <v>1</v>
       </c>
       <c r="P52" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="53" spans="1:16">
@@ -4074,7 +4080,7 @@
         <v>1</v>
       </c>
       <c r="P53" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="54" spans="1:16">
@@ -4124,7 +4130,7 @@
         <v>1</v>
       </c>
       <c r="P54" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="55" spans="1:16">
@@ -4138,7 +4144,7 @@
         <v>10.96451987407661</v>
       </c>
       <c r="D55" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E55">
         <v>9.918825279734797</v>
@@ -4174,7 +4180,7 @@
         <v>1</v>
       </c>
       <c r="P55" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="56" spans="1:16">
@@ -4224,7 +4230,7 @@
         <v>1</v>
       </c>
       <c r="P56" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="57" spans="1:16">
@@ -4274,7 +4280,7 @@
         <v>1</v>
       </c>
       <c r="P57" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="58" spans="1:16">
@@ -4324,7 +4330,7 @@
         <v>1</v>
       </c>
       <c r="P58" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="59" spans="1:16">
@@ -4374,7 +4380,7 @@
         <v>1</v>
       </c>
       <c r="P59" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="60" spans="1:16">
@@ -4424,7 +4430,7 @@
         <v>1</v>
       </c>
       <c r="P60" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="61" spans="1:16">
@@ -4474,7 +4480,7 @@
         <v>1</v>
       </c>
       <c r="P61" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="62" spans="1:16">
@@ -4524,7 +4530,7 @@
         <v>1</v>
       </c>
       <c r="P62" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="63" spans="1:16">
@@ -4538,7 +4544,7 @@
         <v>10.70295290100141</v>
       </c>
       <c r="D63" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E63">
         <v>8.905400692050126</v>
@@ -4574,7 +4580,7 @@
         <v>1</v>
       </c>
       <c r="P63" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="64" spans="1:16">
@@ -4588,7 +4594,7 @@
         <v>11.20304517915771</v>
       </c>
       <c r="D64" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E64">
         <v>8.905400692050126</v>
@@ -4624,7 +4630,7 @@
         <v>1</v>
       </c>
       <c r="P64" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="65" spans="1:16">
@@ -4674,7 +4680,7 @@
         <v>1</v>
       </c>
       <c r="P65" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="66" spans="1:16">
@@ -4688,7 +4694,7 @@
         <v>10.69564352718713</v>
       </c>
       <c r="D66" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E66">
         <v>10.68408451836947</v>
@@ -4724,7 +4730,7 @@
         <v>1</v>
       </c>
       <c r="P66" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="67" spans="1:16">
@@ -4738,7 +4744,7 @@
         <v>11.03068966626528</v>
       </c>
       <c r="D67" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E67">
         <v>10.68408451836947</v>
@@ -4774,7 +4780,7 @@
         <v>1</v>
       </c>
       <c r="P67" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="68" spans="1:16">
@@ -4824,7 +4830,7 @@
         <v>1</v>
       </c>
       <c r="P68" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="69" spans="1:16">
@@ -4838,7 +4844,7 @@
         <v>10.52605158161457</v>
       </c>
       <c r="D69" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E69">
         <v>8.71498607743235</v>
@@ -4874,7 +4880,7 @@
         <v>1</v>
       </c>
       <c r="P69" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="70" spans="1:16">
@@ -4888,7 +4894,7 @@
         <v>11.02061569354003</v>
       </c>
       <c r="D70" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E70">
         <v>8.71498607743235</v>
@@ -4924,7 +4930,7 @@
         <v>1</v>
       </c>
       <c r="P70" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="71" spans="1:16">
@@ -4974,7 +4980,7 @@
         <v>1</v>
       </c>
       <c r="P71" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="72" spans="1:16">
@@ -4988,7 +4994,7 @@
         <v>10.52396325368498</v>
       </c>
       <c r="D72" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E72">
         <v>8.806051581614568</v>
@@ -5024,7 +5030,7 @@
         <v>1</v>
       </c>
       <c r="P72" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="73" spans="1:16">
@@ -5038,7 +5044,7 @@
         <v>10.8562453096477</v>
       </c>
       <c r="D73" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E73">
         <v>8.806051581614568</v>
@@ -5074,7 +5080,7 @@
         <v>1</v>
       </c>
       <c r="P73" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="74" spans="1:16">
@@ -5088,7 +5094,7 @@
         <v>10.34525014922946</v>
       </c>
       <c r="D74" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E74">
         <v>8.520373424517821</v>
@@ -5138,7 +5144,7 @@
         <v>10.83416421639288</v>
       </c>
       <c r="D75" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E75">
         <v>8.520373424517821</v>
@@ -5288,7 +5294,7 @@
         <v>10.34849797468624</v>
       </c>
       <c r="D78" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E78">
         <v>8.625250149229462</v>
@@ -5338,7 +5344,7 @@
         <v>10.67795500826794</v>
       </c>
       <c r="D79" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E79">
         <v>8.625250149229462</v>
@@ -5388,7 +5394,7 @@
         <v>10.18864383981015</v>
       </c>
       <c r="D80" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E80">
         <v>8.351804133128983</v>
@@ -5424,7 +5430,7 @@
         <v>1</v>
       </c>
       <c r="P80" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="81" spans="1:16">
@@ -5438,7 +5444,7 @@
         <v>10.67266395980422</v>
       </c>
       <c r="D81" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E81">
         <v>8.351804133128983</v>
@@ -5474,7 +5480,7 @@
         <v>1</v>
       </c>
       <c r="P81" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="82" spans="1:16">
@@ -5524,7 +5530,7 @@
         <v>1</v>
       </c>
       <c r="P82" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="83" spans="1:16">
@@ -5574,7 +5580,7 @@
         <v>1</v>
       </c>
       <c r="P83" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="84" spans="1:16">
@@ -5588,7 +5594,7 @@
         <v>10.19651372648243</v>
       </c>
       <c r="D84" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E84">
         <v>8.468643839810152</v>
@@ -5624,7 +5630,7 @@
         <v>1</v>
       </c>
       <c r="P84" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="85" spans="1:16">
@@ -5638,7 +5644,7 @@
         <v>10.52352378647946</v>
       </c>
       <c r="D85" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E85">
         <v>8.468643839810152</v>
@@ -5674,7 +5680,7 @@
         <v>1</v>
       </c>
       <c r="P85" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="86" spans="1:16">
@@ -5688,7 +5694,7 @@
         <v>-1.278554542763944</v>
       </c>
       <c r="D86" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E86">
         <v>0.01420169243589342</v>
@@ -5724,7 +5730,7 @@
         <v>1</v>
       </c>
       <c r="P86" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="87" spans="1:16">
@@ -5738,7 +5744,7 @@
         <v>-2.406586639852707</v>
       </c>
       <c r="D87" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E87">
         <v>0.01420169243589342</v>
@@ -5774,7 +5780,7 @@
         <v>1</v>
       </c>
       <c r="P87" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="88" spans="1:16">
@@ -5824,7 +5830,7 @@
         <v>1</v>
       </c>
       <c r="P88" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="89" spans="1:16">
@@ -5838,7 +5844,7 @@
         <v>-1.341212522415489</v>
       </c>
       <c r="D89" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E89">
         <v>0.1246199151405953</v>
@@ -5874,7 +5880,7 @@
         <v>1</v>
       </c>
       <c r="P89" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="90" spans="1:16">
@@ -5888,7 +5894,7 @@
         <v>-2.475362406493851</v>
       </c>
       <c r="D90" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E90">
         <v>0.1246199151405953</v>
@@ -5924,7 +5930,7 @@
         <v>1</v>
       </c>
       <c r="P90" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="91" spans="1:16">
@@ -5974,7 +5980,7 @@
         <v>1</v>
       </c>
       <c r="P91" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="92" spans="1:16">
@@ -5988,7 +5994,7 @@
         <v>-2.566016320350375</v>
       </c>
       <c r="D92" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E92">
         <v>0.02954385914472724</v>
@@ -6138,7 +6144,7 @@
         <v>-2.663355023194697</v>
       </c>
       <c r="D95" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E95">
         <v>0.03872013419191234</v>
@@ -6174,7 +6180,7 @@
         <v>1</v>
       </c>
       <c r="P95" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="96" spans="1:16">
@@ -6224,7 +6230,7 @@
         <v>1</v>
       </c>
       <c r="P96" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="97" spans="1:16">
@@ -6274,7 +6280,7 @@
         <v>1</v>
       </c>
       <c r="P97" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="98" spans="1:16">
@@ -6288,7 +6294,7 @@
         <v>-2.748103967913549</v>
       </c>
       <c r="D98" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E98">
         <v>-0.04760949385741853</v>
@@ -6324,7 +6330,7 @@
         <v>1</v>
       </c>
       <c r="P98" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="99" spans="1:16">
@@ -6338,7 +6344,7 @@
         <v>1.170412609918055</v>
       </c>
       <c r="D99" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E99">
         <v>1.469846093587645</v>
@@ -6374,7 +6380,7 @@
         <v>1</v>
       </c>
       <c r="P99" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="100" spans="1:16">
@@ -6388,7 +6394,7 @@
         <v>1.197090465141786</v>
       </c>
       <c r="D100" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E100">
         <v>1.469846093587645</v>
@@ -6424,7 +6430,7 @@
         <v>1</v>
       </c>
       <c r="P100" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="101" spans="1:16">
@@ -6438,7 +6444,7 @@
         <v>-2.807295369205091</v>
       </c>
       <c r="D101" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E101">
         <v>0.3363998775430197</v>
@@ -6474,7 +6480,7 @@
         <v>1</v>
       </c>
       <c r="P101" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="102" spans="1:16">
@@ -6524,7 +6530,7 @@
         <v>1</v>
       </c>
       <c r="P102" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="103" spans="1:16">
@@ -6624,7 +6630,7 @@
         <v>1</v>
       </c>
       <c r="P104" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="105" spans="1:16">
@@ -6638,7 +6644,7 @@
         <v>1.819034812951433</v>
       </c>
       <c r="D105" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E105">
         <v>1.780382458905816</v>
@@ -6674,7 +6680,7 @@
         <v>1</v>
       </c>
       <c r="P105" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="106" spans="1:16">
@@ -6688,7 +6694,7 @@
         <v>1.278232359359254</v>
       </c>
       <c r="D106" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E106">
         <v>1.780382458905816</v>
@@ -6724,7 +6730,7 @@
         <v>1</v>
       </c>
       <c r="P106" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="107" spans="1:16">
@@ -6738,7 +6744,7 @@
         <v>-1.27500579580901</v>
       </c>
       <c r="D107" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E107">
         <v>0.204597470791132</v>
@@ -6774,7 +6780,7 @@
         <v>1</v>
       </c>
       <c r="P107" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="108" spans="1:16">
@@ -6788,7 +6794,7 @@
         <v>-1.164182632644362</v>
       </c>
       <c r="D108" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E108">
         <v>0.204597470791132</v>
@@ -6824,7 +6830,7 @@
         <v>1</v>
       </c>
       <c r="P108" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="109" spans="1:16">
@@ -6874,7 +6880,7 @@
         <v>1</v>
       </c>
       <c r="P109" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="110" spans="1:16">
@@ -6924,7 +6930,7 @@
         <v>1</v>
       </c>
       <c r="P110" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="111" spans="1:16">
@@ -6938,7 +6944,7 @@
         <v>-1.330656541117063</v>
       </c>
       <c r="D111" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E111">
         <v>0.1498300706466971</v>
@@ -6974,7 +6980,7 @@
         <v>1</v>
       </c>
       <c r="P111" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="112" spans="1:16">
@@ -6988,7 +6994,7 @@
         <v>-1.089957636312631</v>
       </c>
       <c r="D112" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E112">
         <v>0.1498300706466971</v>
@@ -7024,7 +7030,7 @@
         <v>1</v>
       </c>
       <c r="P112" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="113" spans="1:16">
@@ -7038,7 +7044,7 @@
         <v>1.663161219313913</v>
       </c>
       <c r="D113" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E113">
         <v>1.394552474924428</v>
@@ -7074,7 +7080,7 @@
         <v>1</v>
       </c>
       <c r="P113" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="114" spans="1:16">
@@ -7088,7 +7094,7 @@
         <v>2.020453841772007</v>
       </c>
       <c r="D114" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E114">
         <v>1.394552474924428</v>
@@ -7124,7 +7130,7 @@
         <v>1</v>
       </c>
       <c r="P114" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="115" spans="1:16">
@@ -7174,7 +7180,7 @@
         <v>1</v>
       </c>
       <c r="P115" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="116" spans="1:16">
@@ -7224,7 +7230,7 @@
         <v>1</v>
       </c>
       <c r="P116" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="117" spans="1:16">
@@ -7274,7 +7280,7 @@
         <v>1</v>
       </c>
       <c r="P117" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="118" spans="1:16">
@@ -7324,7 +7330,7 @@
         <v>1</v>
       </c>
       <c r="P118" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="119" spans="1:16">
@@ -7374,7 +7380,7 @@
         <v>1</v>
       </c>
       <c r="P119" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="120" spans="1:16">
@@ -7424,7 +7430,7 @@
         <v>1</v>
       </c>
       <c r="P120" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="121" spans="1:16">
@@ -7474,7 +7480,7 @@
         <v>1</v>
       </c>
       <c r="P121" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="122" spans="1:16">
@@ -7524,7 +7530,7 @@
         <v>1</v>
       </c>
       <c r="P122" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="123" spans="1:16">
@@ -7574,7 +7580,7 @@
         <v>1</v>
       </c>
       <c r="P123" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="124" spans="1:16">
@@ -7624,7 +7630,7 @@
         <v>1</v>
       </c>
       <c r="P124" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="125" spans="1:16">
@@ -7738,7 +7744,7 @@
         <v>1.583716178161136</v>
       </c>
       <c r="D127" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E127">
         <v>1.731188504841963</v>
@@ -7788,7 +7794,7 @@
         <v>1.943294205912665</v>
       </c>
       <c r="D128" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E128">
         <v>1.731188504841963</v>
@@ -7838,7 +7844,7 @@
         <v>1.440029121201585</v>
       </c>
       <c r="D129" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E129">
         <v>1.731188504841963</v>
@@ -7924,7 +7930,7 @@
         <v>1</v>
       </c>
       <c r="P130" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="131" spans="1:16">
@@ -7974,7 +7980,7 @@
         <v>1</v>
       </c>
       <c r="P131" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="132" spans="1:16">
@@ -8024,7 +8030,7 @@
         <v>1</v>
       </c>
       <c r="P132" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="133" spans="1:16">
@@ -8074,7 +8080,7 @@
         <v>1</v>
       </c>
       <c r="P133" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="134" spans="1:16">
@@ -8124,7 +8130,7 @@
         <v>1</v>
       </c>
       <c r="P134" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="135" spans="1:16">
@@ -8138,7 +8144,7 @@
         <v>-0.8820242128746258</v>
       </c>
       <c r="D135" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E135">
         <v>0.3526024044326252</v>
@@ -8174,7 +8180,7 @@
         <v>1</v>
       </c>
       <c r="P135" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="136" spans="1:16">
@@ -8188,7 +8194,7 @@
         <v>-1.173427909927172</v>
       </c>
       <c r="D136" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E136">
         <v>0.3526024044326252</v>
@@ -8224,7 +8230,7 @@
         <v>1</v>
       </c>
       <c r="P136" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="137" spans="1:16">
@@ -8274,7 +8280,7 @@
         <v>1</v>
       </c>
       <c r="P137" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="138" spans="1:16">
@@ -8324,7 +8330,7 @@
         <v>1</v>
       </c>
       <c r="P138" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="139" spans="1:16">
@@ -8374,7 +8380,7 @@
         <v>1</v>
       </c>
       <c r="P139" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="140" spans="1:16">
@@ -8688,7 +8694,7 @@
         <v>1.916709703800588</v>
       </c>
       <c r="D146" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E146">
         <v>1.625228926806798</v>
@@ -8738,7 +8744,7 @@
         <v>1.775844332123576</v>
       </c>
       <c r="D147" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E147">
         <v>1.625228926806798</v>
@@ -8788,7 +8794,7 @@
         <v>1.706459737440355</v>
       </c>
       <c r="D148" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E148">
         <v>1.625228926806798</v>
@@ -8838,7 +8844,7 @@
         <v>1.898407474064776</v>
       </c>
       <c r="D149" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E149">
         <v>1.579058157468399</v>
@@ -8874,7 +8880,7 @@
         <v>1</v>
       </c>
       <c r="P149" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="150" spans="1:16">
@@ -8888,7 +8894,7 @@
         <v>1.757671173119327</v>
       </c>
       <c r="D150" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E150">
         <v>1.579058157468399</v>
@@ -8924,7 +8930,7 @@
         <v>1</v>
       </c>
       <c r="P150" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="151" spans="1:16">
@@ -8938,7 +8944,7 @@
         <v>1.688493091606606</v>
       </c>
       <c r="D151" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E151">
         <v>1.579058157468399</v>
@@ -8974,7 +8980,7 @@
         <v>1</v>
       </c>
       <c r="P151" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="152" spans="1:16">
@@ -9024,7 +9030,7 @@
         <v>1</v>
       </c>
       <c r="P152" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="153" spans="1:16">
@@ -9074,7 +9080,7 @@
         <v>1</v>
       </c>
       <c r="P153" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="154" spans="1:16">
@@ -9124,7 +9130,7 @@
         <v>1</v>
       </c>
       <c r="P154" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="155" spans="1:16">
@@ -9174,7 +9180,7 @@
         <v>1</v>
       </c>
       <c r="P155" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="156" spans="1:16">
@@ -9224,7 +9230,7 @@
         <v>1</v>
       </c>
       <c r="P156" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="157" spans="1:16">
@@ -9274,7 +9280,7 @@
         <v>1</v>
       </c>
       <c r="P157" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="158" spans="1:16">
@@ -9424,7 +9430,7 @@
         <v>1</v>
       </c>
       <c r="P160" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="161" spans="1:16">
@@ -9474,7 +9480,7 @@
         <v>1</v>
       </c>
       <c r="P161" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="162" spans="1:16">
@@ -9524,7 +9530,7 @@
         <v>1</v>
       </c>
       <c r="P162" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="163" spans="1:16">
@@ -9574,7 +9580,7 @@
         <v>1</v>
       </c>
       <c r="P163" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="164" spans="1:16">
@@ -9588,7 +9594,7 @@
         <v>2.0418888555804</v>
       </c>
       <c r="D164" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E164">
         <v>2.091052252009925</v>
@@ -9638,7 +9644,7 @@
         <v>2.437529947263654</v>
       </c>
       <c r="D165" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E165">
         <v>2.091052252009925</v>
@@ -9688,7 +9694,7 @@
         <v>2.035427646090795</v>
       </c>
       <c r="D166" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E166">
         <v>1.677256780401082</v>
@@ -9724,7 +9730,7 @@
         <v>1</v>
       </c>
       <c r="P166" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="167" spans="1:16">
@@ -9738,7 +9744,7 @@
         <v>2.4319519246827</v>
       </c>
       <c r="D167" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E167">
         <v>1.677256780401082</v>
@@ -9774,7 +9780,7 @@
         <v>1</v>
       </c>
       <c r="P167" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="168" spans="1:16">
@@ -9824,7 +9830,7 @@
         <v>1</v>
       </c>
       <c r="P168" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="169" spans="1:16">
@@ -9874,7 +9880,7 @@
         <v>1</v>
       </c>
       <c r="P169" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="170" spans="1:16">
@@ -9924,7 +9930,7 @@
         <v>1</v>
       </c>
       <c r="P170" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="171" spans="1:16">
@@ -9974,7 +9980,7 @@
         <v>1</v>
       </c>
       <c r="P171" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="172" spans="1:16">
@@ -10024,7 +10030,7 @@
         <v>1</v>
       </c>
       <c r="P172" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="173" spans="1:16">
@@ -10038,7 +10044,7 @@
         <v>2.053037839433713</v>
       </c>
       <c r="D173" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E173">
         <v>2.029053723158555</v>
@@ -10074,7 +10080,7 @@
         <v>1</v>
       </c>
       <c r="P173" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="174" spans="1:16">
@@ -10188,7 +10194,7 @@
         <v>2.072439051471395</v>
       </c>
       <c r="D176" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E176">
         <v>2.198537473651809</v>
@@ -10224,7 +10230,7 @@
         <v>1</v>
       </c>
       <c r="P176" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="177" spans="1:16">
@@ -10238,7 +10244,7 @@
         <v>2.176038435736924</v>
       </c>
       <c r="D177" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E177">
         <v>2.198537473651809</v>
@@ -10274,7 +10280,7 @@
         <v>1</v>
       </c>
       <c r="P177" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="178" spans="1:16">
@@ -10324,7 +10330,7 @@
         <v>1</v>
       </c>
       <c r="P178" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="179" spans="1:16">
@@ -10388,7 +10394,7 @@
         <v>2.199572666349018</v>
       </c>
       <c r="D180" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E180">
         <v>2.369622868222606</v>
@@ -10588,7 +10594,7 @@
         <v>2.441204477380014</v>
       </c>
       <c r="D184" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E184">
         <v>3.019740173907834</v>
@@ -10688,7 +10694,7 @@
         <v>2.450942264059425</v>
       </c>
       <c r="D186" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E186">
         <v>3.396065694761221</v>
@@ -10738,7 +10744,7 @@
         <v>2.93271297523739</v>
       </c>
       <c r="D187" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E187">
         <v>3.396065694761221</v>
@@ -10838,7 +10844,7 @@
         <v>2.613291041571109</v>
       </c>
       <c r="D189" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E189">
         <v>1.747095958240026</v>
@@ -10888,7 +10894,7 @@
         <v>2.94332933323569</v>
       </c>
       <c r="D190" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E190">
         <v>3.513960124909904</v>
@@ -11038,7 +11044,7 @@
         <v>2.630002520413537</v>
       </c>
       <c r="D193" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E193">
         <v>1.763414225815572</v>
@@ -11088,7 +11094,7 @@
         <v>2.960405936825934</v>
       </c>
       <c r="D194" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E194">
         <v>2.688557154970242</v>
@@ -11288,7 +11294,7 @@
         <v>2.642059072099817</v>
       </c>
       <c r="D198" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E198">
         <v>1.775187093932763</v>
@@ -11338,7 +11344,7 @@
         <v>2.972725908969226</v>
       </c>
       <c r="D199" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E199">
         <v>2.375803028433923</v>
@@ -11488,7 +11494,7 @@
         <v>2.666955617984192</v>
       </c>
       <c r="D202" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E202">
         <v>1.799497838737505</v>
@@ -11538,7 +11544,7 @@
         <v>2.998166412998973</v>
       </c>
       <c r="D203" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E203">
         <v>1.736641978102437</v>
@@ -11688,7 +11694,7 @@
         <v>2.973643871143521</v>
       </c>
       <c r="D206" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E206">
         <v>1.818524938691256</v>
@@ -11738,7 +11744,7 @@
         <v>3.018077732744034</v>
       </c>
       <c r="D207" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E207">
         <v>1.759533446033025</v>
@@ -11888,7 +11894,7 @@
         <v>2.990082102112254</v>
       </c>
       <c r="D210" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E210">
         <v>1.83485077149952</v>
@@ -11938,7 +11944,7 @@
         <v>3.03516225313547</v>
       </c>
       <c r="D211" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E211">
         <v>1.779175024575153</v>
@@ -12024,7 +12030,7 @@
         <v>1</v>
       </c>
       <c r="P212" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="213" spans="1:16">
@@ -12074,7 +12080,7 @@
         <v>1</v>
       </c>
       <c r="P213" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="214" spans="1:16">
@@ -12088,7 +12094,7 @@
         <v>3.005496469975766</v>
       </c>
       <c r="D214" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E214">
         <v>1.850159741975929</v>
@@ -12124,7 +12130,7 @@
         <v>1</v>
       </c>
       <c r="P214" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="215" spans="1:16">
@@ -12138,7 +12144,7 @@
         <v>3.051182655974811</v>
       </c>
       <c r="D215" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E215">
         <v>1.797593217971041</v>
@@ -12174,7 +12180,7 @@
         <v>1</v>
       </c>
       <c r="P215" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="216" spans="1:16">
@@ -12288,7 +12294,7 @@
         <v>3.018931533510157</v>
       </c>
       <c r="D218" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E218">
         <v>1.863502941828035</v>
@@ -12338,7 +12344,7 @@
         <v>3.06514593568235</v>
       </c>
       <c r="D219" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E219">
         <v>1.813646396450594</v>
@@ -12488,7 +12494,7 @@
         <v>3.033933076549712</v>
       </c>
       <c r="D222" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E222">
         <v>1.878401910214327</v>
@@ -12538,7 +12544,7 @@
         <v>3.080737282978161</v>
       </c>
       <c r="D223" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E223">
         <v>1.831571317108114</v>
@@ -12588,7 +12594,7 @@
         <v>1.639859271051932</v>
       </c>
       <c r="D224" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E224">
         <v>1.9209216037227</v>
@@ -12738,7 +12744,7 @@
         <v>3.05833801181463</v>
       </c>
       <c r="D227" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E227">
         <v>1.902639974127007</v>
@@ -12788,7 +12794,7 @@
         <v>3.106101728518452</v>
       </c>
       <c r="D228" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E228">
         <v>1.860732085911838</v>
@@ -12874,7 +12880,7 @@
         <v>1</v>
       </c>
       <c r="P229" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="230" spans="1:16">
@@ -12924,7 +12930,7 @@
         <v>1</v>
       </c>
       <c r="P230" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="231" spans="1:16">
@@ -12938,7 +12944,7 @@
         <v>3.085055612872655</v>
       </c>
       <c r="D231" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E231">
         <v>1.929174890733353</v>
@@ -12974,7 +12980,7 @@
         <v>1</v>
       </c>
       <c r="P231" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="232" spans="1:16">
@@ -12988,7 +12994,7 @@
         <v>3.13386976517363</v>
       </c>
       <c r="D232" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E232">
         <v>1.892656193842708</v>
@@ -13024,7 +13030,7 @@
         <v>1</v>
       </c>
       <c r="P232" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="233" spans="1:16">
@@ -13088,7 +13094,7 @@
         <v>3.103034611570727</v>
       </c>
       <c r="D234" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E234">
         <v>1.947030956106994</v>
@@ -13138,7 +13144,7 @@
         <v>3.152555630487182</v>
       </c>
       <c r="D235" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E235">
         <v>1.914138792287073</v>
@@ -13188,7 +13194,7 @@
         <v>1.641725609550694</v>
       </c>
       <c r="D236" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E236">
         <v>1.89319910743864</v>
@@ -13274,7 +13280,7 @@
         <v>1</v>
       </c>
       <c r="P237" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="238" spans="1:16">
@@ -13288,7 +13294,7 @@
         <v>3.11979974827751</v>
       </c>
       <c r="D238" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E238">
         <v>1.963681459400396</v>
@@ -13324,7 +13330,7 @@
         <v>1</v>
       </c>
       <c r="P238" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="239" spans="1:16">
@@ -13338,7 +13344,7 @@
         <v>3.169979909320897</v>
       </c>
       <c r="D239" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E239">
         <v>1.934170981275177</v>
@@ -13374,7 +13380,7 @@
         <v>1</v>
       </c>
       <c r="P239" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="240" spans="1:16">
@@ -13388,7 +13394,7 @@
         <v>1.664480342106565</v>
       </c>
       <c r="D240" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E240">
         <v>2.221652319966786</v>
@@ -13424,7 +13430,7 @@
         <v>1</v>
       </c>
       <c r="P240" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="241" spans="1:16">
@@ -13488,7 +13494,7 @@
         <v>3.136490860930856</v>
       </c>
       <c r="D242" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E242">
         <v>1.980258444787738</v>
@@ -13538,7 +13544,7 @@
         <v>3.187327253753777</v>
       </c>
       <c r="D243" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E243">
         <v>1.954114721009688</v>
@@ -13738,7 +13744,7 @@
         <v>3.154470288152615</v>
       </c>
       <c r="D247" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E247">
         <v>1.998114935754989</v>
@@ -13788,7 +13794,7 @@
         <v>3.206013564438956</v>
       </c>
       <c r="D248" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E248">
         <v>1.975597831484915</v>
@@ -13974,7 +13980,7 @@
         <v>1</v>
       </c>
       <c r="P251" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="252" spans="1:16">
@@ -14024,7 +14030,7 @@
         <v>1</v>
       </c>
       <c r="P252" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="253" spans="1:16">
@@ -14038,7 +14044,7 @@
         <v>3.175183381627829</v>
       </c>
       <c r="D253" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E253">
         <v>2.406837822852639</v>
@@ -14074,7 +14080,7 @@
         <v>1</v>
       </c>
       <c r="P253" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="254" spans="1:16">
@@ -14088,7 +14094,7 @@
         <v>3.227541018854222</v>
       </c>
       <c r="D254" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E254">
         <v>2.000347322662993</v>
@@ -14124,7 +14130,7 @@
         <v>1</v>
       </c>
       <c r="P254" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="255" spans="1:16">
@@ -14174,7 +14180,7 @@
         <v>1</v>
       </c>
       <c r="P255" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="256" spans="1:16">
@@ -14224,7 +14230,7 @@
         <v>1</v>
       </c>
       <c r="P256" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="257" spans="1:16">
@@ -14338,7 +14344,7 @@
         <v>3.194491499183421</v>
       </c>
       <c r="D259" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E259">
         <v>2.42485873257119</v>
@@ -14388,7 +14394,7 @@
         <v>3.247608258980375</v>
       </c>
       <c r="D260" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E260">
         <v>2.023418047742236</v>
@@ -14638,7 +14644,7 @@
         <v>3.213727962726566</v>
       </c>
       <c r="D265" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E265">
         <v>2.442812765211459</v>
@@ -14688,7 +14694,7 @@
         <v>3.26760102792778</v>
       </c>
       <c r="D266" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E266">
         <v>2.046403155463022</v>
@@ -14888,7 +14894,7 @@
         <v>3.233647867837396</v>
       </c>
       <c r="D270" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E270">
         <v>2.461404676648234</v>
@@ -14938,7 +14944,7 @@
         <v>3.288304108795105</v>
       </c>
       <c r="D271" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E271">
         <v>2.070204888236475</v>
@@ -15138,7 +15144,7 @@
         <v>3.249417008017017</v>
       </c>
       <c r="D275" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E275">
         <v>2.476122540815881</v>
@@ -15188,7 +15194,7 @@
         <v>3.304693232263839</v>
       </c>
       <c r="D276" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E276">
         <v>2.089046989066485</v>
@@ -15338,7 +15344,7 @@
         <v>1.914875661806953</v>
       </c>
       <c r="D279" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E279">
         <v>2.109898465499843</v>
@@ -15424,7 +15430,7 @@
         <v>1</v>
       </c>
       <c r="P280" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="281" spans="1:16">
@@ -15438,7 +15444,7 @@
         <v>3.261163134684622</v>
       </c>
       <c r="D281" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E281">
         <v>2.487085592372312</v>
@@ -15474,7 +15480,7 @@
         <v>1</v>
       </c>
       <c r="P281" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="282" spans="1:16">
@@ -15488,7 +15494,7 @@
         <v>3.316901172458547</v>
       </c>
       <c r="D282" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E282">
         <v>2.103082104520595</v>
@@ -15524,7 +15530,7 @@
         <v>1</v>
       </c>
       <c r="P282" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="283" spans="1:16">
@@ -15574,7 +15580,7 @@
         <v>1</v>
       </c>
       <c r="P283" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="284" spans="1:16">
@@ -15624,7 +15630,7 @@
         <v>1</v>
       </c>
       <c r="P284" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="285" spans="1:16">
@@ -15638,7 +15644,7 @@
         <v>1.930296217842372</v>
       </c>
       <c r="D285" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E285">
         <v>2.383746445952788</v>
@@ -15674,7 +15680,7 @@
         <v>1</v>
       </c>
       <c r="P285" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="286" spans="1:16">
@@ -15724,7 +15730,7 @@
         <v>1</v>
       </c>
       <c r="P286" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="287" spans="1:16">
@@ -15738,7 +15744,7 @@
         <v>3.267778188252251</v>
       </c>
       <c r="D287" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E287">
         <v>2.493259642368766</v>
@@ -15774,7 +15780,7 @@
         <v>1</v>
       </c>
       <c r="P287" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="288" spans="1:16">
@@ -15788,7 +15794,7 @@
         <v>3.323776305055329</v>
       </c>
       <c r="D288" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E288">
         <v>2.110986245450121</v>
@@ -15824,7 +15830,7 @@
         <v>1</v>
       </c>
       <c r="P288" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="289" spans="1:16">
@@ -15874,7 +15880,7 @@
         <v>1</v>
       </c>
       <c r="P289" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="290" spans="1:16">
@@ -15924,7 +15930,7 @@
         <v>1</v>
       </c>
       <c r="P290" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="291" spans="1:16">
@@ -15974,7 +15980,7 @@
         <v>1</v>
       </c>
       <c r="P291" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="292" spans="1:16">
@@ -15988,7 +15994,7 @@
         <v>3.278598009747792</v>
       </c>
       <c r="D292" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E292">
         <v>2.503358142431271</v>
@@ -16038,7 +16044,7 @@
         <v>3.335021521242147</v>
       </c>
       <c r="D293" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E293">
         <v>2.123914544980693</v>
@@ -16188,7 +16194,7 @@
         <v>1.953185079463765</v>
       </c>
       <c r="D296" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E296">
         <v>1.673185079463764</v>
@@ -16238,7 +16244,7 @@
         <v>1.838424946780282</v>
       </c>
       <c r="D297" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E297">
         <v>1.673185079463764</v>
@@ -16288,7 +16294,7 @@
         <v>3.286491586851236</v>
       </c>
       <c r="D298" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E298">
         <v>2.510725481061151</v>
@@ -16338,7 +16344,7 @@
         <v>3.343225444112052</v>
       </c>
       <c r="D299" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E299">
         <v>2.133346357622241</v>
@@ -16488,7 +16494,7 @@
         <v>1.963547929404697</v>
       </c>
       <c r="D302" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E302">
         <v>2.040362444937774</v>
@@ -16538,7 +16544,7 @@
         <v>1.849314035194777</v>
       </c>
       <c r="D303" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E303">
         <v>2.040362444937774</v>
@@ -16588,7 +16594,7 @@
         <v>3.287218803551511</v>
       </c>
       <c r="D304" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E304">
         <v>2.511404216648074</v>
@@ -16638,7 +16644,7 @@
         <v>3.34398125223815</v>
       </c>
       <c r="D305" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E305">
         <v>2.134215288346162</v>
@@ -16788,7 +16794,7 @@
         <v>1.964502634406085</v>
       </c>
       <c r="D308" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E308">
         <v>2.034789980466009</v>
@@ -16838,7 +16844,7 @@
         <v>1.850317221309513</v>
       </c>
       <c r="D309" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E309">
         <v>2.034789980466009</v>
@@ -16888,7 +16894,7 @@
         <v>3.309574328279867</v>
       </c>
       <c r="D310" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E310">
         <v>2.532269373061208</v>
@@ -16938,7 +16944,7 @@
         <v>3.367215712126766</v>
       </c>
       <c r="D311" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E311">
         <v>2.160927274303631</v>
@@ -17188,7 +17194,7 @@
         <v>3.386581638751728</v>
       </c>
       <c r="D316" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E316">
         <v>2.183191719551736</v>
@@ -17288,7 +17294,7 @@
         <v>2.018313648949551</v>
       </c>
       <c r="D318" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E318">
         <v>2.020805677582523</v>
@@ -17338,7 +17344,7 @@
         <v>1.906860826435267</v>
       </c>
       <c r="D319" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E319">
         <v>2.020805677582523</v>
@@ -17388,7 +17394,7 @@
         <v>1.784750528729781</v>
       </c>
       <c r="D320" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E320">
         <v>2.020805677582523</v>
@@ -17438,7 +17444,7 @@
         <v>3.376305833526885</v>
       </c>
       <c r="D321" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E321">
         <v>2.171377923742256</v>
@@ -17474,7 +17480,7 @@
         <v>1</v>
       </c>
       <c r="P321" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="322" spans="1:16">
@@ -17524,7 +17530,7 @@
         <v>1</v>
       </c>
       <c r="P322" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="323" spans="1:16">
@@ -17574,7 +17580,7 @@
         <v>1</v>
       </c>
       <c r="P323" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="324" spans="1:16">
@@ -17624,7 +17630,7 @@
         <v>1</v>
       </c>
       <c r="P324" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="325" spans="1:16">
@@ -17638,7 +17644,7 @@
         <v>3.346413966869674</v>
       </c>
       <c r="D325" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E325">
         <v>2.137012109937338</v>
@@ -17674,7 +17680,7 @@
         <v>1</v>
       </c>
       <c r="P325" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="326" spans="1:16">
@@ -17724,7 +17730,7 @@
         <v>1</v>
       </c>
       <c r="P326" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="327" spans="1:16">
@@ -17738,7 +17744,7 @@
         <v>1.853546169841817</v>
       </c>
       <c r="D327" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E327">
         <v>1.909412654865697</v>
@@ -17774,7 +17780,7 @@
         <v>1</v>
       </c>
       <c r="P327" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="328" spans="1:16">
@@ -17788,7 +17794,7 @@
         <v>1.729057523143315</v>
       </c>
       <c r="D328" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E328">
         <v>1.909412654865697</v>
@@ -17824,7 +17830,7 @@
         <v>1</v>
       </c>
       <c r="P328" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="329" spans="1:16">
@@ -17838,7 +17844,7 @@
         <v>1.90213361560998</v>
       </c>
       <c r="D329" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E329">
         <v>1.909412654865697</v>
@@ -17874,7 +17880,7 @@
         <v>1</v>
       </c>
       <c r="P329" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="330" spans="1:16">
@@ -17888,7 +17894,7 @@
         <v>3.335708401471214</v>
       </c>
       <c r="D330" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E330">
         <v>2.124704231296676</v>
@@ -17924,7 +17930,7 @@
         <v>1</v>
       </c>
       <c r="P330" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="331" spans="1:16">
@@ -17974,7 +17980,7 @@
         <v>1</v>
       </c>
       <c r="P331" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="332" spans="1:16">
@@ -17988,7 +17994,7 @@
         <v>1.839336644715903</v>
       </c>
       <c r="D332" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E332">
         <v>2.572020438006287</v>
@@ -18024,7 +18030,7 @@
         <v>1</v>
       </c>
       <c r="P332" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="333" spans="1:16">
@@ -18038,7 +18044,7 @@
         <v>1.714214115855647</v>
       </c>
       <c r="D333" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E333">
         <v>2.572020438006287</v>
@@ -18074,7 +18080,7 @@
         <v>1</v>
       </c>
       <c r="P333" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="334" spans="1:16">
@@ -18088,7 +18094,7 @@
         <v>1.88846993345668</v>
       </c>
       <c r="D334" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E334">
         <v>2.572020438006287</v>
@@ -18124,7 +18130,7 @@
         <v>1</v>
       </c>
       <c r="P334" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="335" spans="1:16">
@@ -18138,7 +18144,7 @@
         <v>3.319807569063805</v>
       </c>
       <c r="D335" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E335">
         <v>2.106423504565129</v>
@@ -18238,7 +18244,7 @@
         <v>1.818231428017253</v>
       </c>
       <c r="D337" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E337">
         <v>2.552327466291189</v>
@@ -18288,7 +18294,7 @@
         <v>1.692167402501294</v>
       </c>
       <c r="D338" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E338">
         <v>2.552327466291189</v>
@@ -18338,7 +18344,7 @@
         <v>1.86817544998933</v>
       </c>
       <c r="D339" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E339">
         <v>2.552327466291189</v>
@@ -18388,7 +18394,7 @@
         <v>3.297653300651016</v>
       </c>
       <c r="D340" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E340">
         <v>2.080953383478715</v>
@@ -18424,7 +18430,7 @@
         <v>1</v>
       </c>
       <c r="P340" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="341" spans="1:16">
@@ -18474,7 +18480,7 @@
         <v>1</v>
       </c>
       <c r="P341" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="342" spans="1:16">
@@ -18488,7 +18494,7 @@
         <v>1.788826009252247</v>
       </c>
       <c r="D342" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E342">
         <v>2.524889696365481</v>
@@ -18524,7 +18530,7 @@
         <v>1</v>
       </c>
       <c r="P342" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="343" spans="1:16">
@@ -18538,7 +18544,7 @@
         <v>1.661450217843427</v>
       </c>
       <c r="D343" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E343">
         <v>2.524889696365481</v>
@@ -18574,7 +18580,7 @@
         <v>1</v>
       </c>
       <c r="P343" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="344" spans="1:16">
@@ -18588,7 +18594,7 @@
         <v>1.839899607409848</v>
       </c>
       <c r="D344" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E344">
         <v>2.524889696365481</v>
@@ -18624,7 +18630,7 @@
         <v>1</v>
       </c>
       <c r="P344" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="345" spans="1:16">
@@ -18638,7 +18644,7 @@
         <v>3.263703117123406</v>
       </c>
       <c r="D345" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E345">
         <v>2.041921840245493</v>
@@ -18738,7 +18744,7 @@
         <v>1.743763841313463</v>
       </c>
       <c r="D347" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E347">
         <v>2.48284284077948</v>
@@ -18788,7 +18794,7 @@
         <v>1.614377841669459</v>
       </c>
       <c r="D348" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E348">
         <v>2.48284284077948</v>
@@ -18838,7 +18844,7 @@
         <v>1.796568452118031</v>
       </c>
       <c r="D349" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E349">
         <v>2.48284284077948</v>
@@ -18888,7 +18894,7 @@
         <v>3.242126022559422</v>
       </c>
       <c r="D350" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E350">
         <v>2.017115279225386</v>
@@ -18924,7 +18930,7 @@
         <v>1</v>
       </c>
       <c r="P350" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="351" spans="1:16">
@@ -18974,7 +18980,7 @@
         <v>1</v>
       </c>
       <c r="P351" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="352" spans="1:16">
@@ -18988,7 +18994,7 @@
         <v>1.715124506916858</v>
       </c>
       <c r="D352" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E352">
         <v>2.456119893071122</v>
@@ -19024,7 +19030,7 @@
         <v>1</v>
       </c>
       <c r="P352" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="353" spans="1:16">
@@ -19038,7 +19044,7 @@
         <v>1.584460916147354</v>
       </c>
       <c r="D353" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E353">
         <v>2.456119893071122</v>
@@ -19074,7 +19080,7 @@
         <v>1</v>
       </c>
       <c r="P353" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="354" spans="1:16">
@@ -19088,7 +19094,7 @@
         <v>1.769029265635051</v>
       </c>
       <c r="D354" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E354">
         <v>2.456119893071122</v>
@@ -19124,7 +19130,7 @@
         <v>1</v>
       </c>
       <c r="P354" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="355" spans="1:16">
@@ -19138,7 +19144,7 @@
         <v>3.218796578894542</v>
       </c>
       <c r="D355" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E355">
         <v>1.990294093169876</v>
@@ -19238,7 +19244,7 @@
         <v>1.684159274947191</v>
       </c>
       <c r="D357" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E357">
         <v>2.427226684058535</v>
@@ -19288,7 +19294,7 @@
         <v>1.552114335539635</v>
       </c>
       <c r="D358" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E358">
         <v>2.427226684058535</v>
@@ -19338,7 +19344,7 @@
         <v>1.739253528325928</v>
       </c>
       <c r="D359" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E359">
         <v>2.427226684058535</v>
@@ -19388,7 +19394,7 @@
         <v>3.223084813618858</v>
       </c>
       <c r="D360" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E360">
         <v>1.995224152499308</v>
@@ -19424,7 +19430,7 @@
         <v>1</v>
       </c>
       <c r="P360" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="361" spans="1:16">
@@ -19438,7 +19444,7 @@
         <v>1.689851060181606</v>
       </c>
       <c r="D361" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E361">
         <v>2.432537606340457</v>
@@ -19474,7 +19480,7 @@
         <v>1</v>
       </c>
       <c r="P361" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="362" spans="1:16">
@@ -19488,7 +19494,7 @@
         <v>1.558060029409038</v>
       </c>
       <c r="D362" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E362">
         <v>2.432537606340457</v>
@@ -19524,7 +19530,7 @@
         <v>1</v>
       </c>
       <c r="P362" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="363" spans="1:16">
@@ -19538,7 +19544,7 @@
         <v>1.5546355793606</v>
       </c>
       <c r="D363" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E363">
         <v>2.429478755941318</v>
@@ -19588,7 +19594,7 @@
         <v>2.749895863416445</v>
       </c>
       <c r="D364" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E364">
         <v>2.144120683335579</v>
@@ -19624,7 +19630,7 @@
         <v>1</v>
       </c>
       <c r="P364" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="365" spans="1:16">
@@ -19638,7 +19644,7 @@
         <v>1.575757316392718</v>
       </c>
       <c r="D365" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E365">
         <v>2.448345503254703</v>
@@ -19674,7 +19680,7 @@
         <v>1</v>
       </c>
       <c r="P365" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="366" spans="1:16">
@@ -19688,7 +19694,7 @@
         <v>1.708690594836302</v>
       </c>
       <c r="D366" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E366">
         <v>1.95524223097577</v>
@@ -19724,7 +19730,7 @@
         <v>1</v>
       </c>
       <c r="P366" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="367" spans="1:16">
@@ -19738,7 +19744,7 @@
         <v>2.776972324350222</v>
       </c>
       <c r="D367" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E367">
         <v>2.170167242074328</v>
@@ -19774,7 +19780,7 @@
         <v>1</v>
       </c>
       <c r="P367" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="368" spans="1:16">
@@ -19788,7 +19794,7 @@
         <v>1.603764011567165</v>
       </c>
       <c r="D368" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E368">
         <v>2.473362159798427</v>
@@ -19824,7 +19830,7 @@
         <v>1</v>
       </c>
       <c r="P368" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="369" spans="1:16">
@@ -19838,7 +19844,7 @@
         <v>1.733308579562596</v>
       </c>
       <c r="D369" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E369">
         <v>2.069952921130998</v>
@@ -19874,7 +19880,7 @@
         <v>1</v>
       </c>
       <c r="P369" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="370" spans="1:16">
@@ -19888,7 +19894,7 @@
         <v>2.804318151096002</v>
       </c>
       <c r="D370" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E370">
         <v>2.196472920808915</v>
@@ -19924,7 +19930,7 @@
         <v>1</v>
       </c>
       <c r="P370" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="371" spans="1:16">
@@ -19938,7 +19944,7 @@
         <v>1.632049326839176</v>
       </c>
       <c r="D371" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E371">
         <v>2.498627690521825</v>
@@ -19974,7 +19980,7 @@
         <v>1</v>
       </c>
       <c r="P371" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="372" spans="1:16">
@@ -19988,7 +19994,7 @@
         <v>1.758171472346181</v>
       </c>
       <c r="D372" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E372">
         <v>2.648741745065742</v>
@@ -20024,7 +20030,7 @@
         <v>1</v>
       </c>
       <c r="P372" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="373" spans="1:16">
@@ -20038,7 +20044,7 @@
         <v>1.836308899819077</v>
       </c>
       <c r="D373" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E373">
         <v>2.387421432319158</v>
@@ -20074,7 +20080,7 @@
         <v>1</v>
       </c>
       <c r="P373" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="374" spans="1:16">
@@ -20124,7 +20130,7 @@
         <v>1</v>
       </c>
       <c r="P374" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="375" spans="1:16">
@@ -20138,7 +20144,7 @@
         <v>1.66686196794393</v>
       </c>
       <c r="D375" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E375">
         <v>2.529723679551338</v>
@@ -20174,7 +20180,7 @@
         <v>1</v>
       </c>
       <c r="P375" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="376" spans="1:16">
@@ -20188,7 +20194,7 @@
         <v>1.844881242140559</v>
       </c>
       <c r="D376" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E376">
         <v>2.529723679551338</v>
@@ -20224,7 +20230,7 @@
         <v>1</v>
       </c>
       <c r="P376" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="377" spans="1:16">
@@ -20238,7 +20244,7 @@
         <v>1.788771907765661</v>
       </c>
       <c r="D377" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E377">
         <v>2.679961622497764</v>
@@ -20274,7 +20280,7 @@
         <v>1</v>
       </c>
       <c r="P377" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="378" spans="1:16">
@@ -20288,7 +20294,7 @@
         <v>1.861508767932467</v>
       </c>
       <c r="D378" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E378">
         <v>2.411732640096055</v>
@@ -20324,7 +20330,7 @@
         <v>1</v>
       </c>
       <c r="P378" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="379" spans="1:16">
@@ -20374,7 +20380,7 @@
         <v>1</v>
       </c>
       <c r="P379" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="380" spans="1:16">
@@ -20388,7 +20394,7 @@
         <v>1.693616991646184</v>
       </c>
       <c r="D380" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E380">
         <v>2.55362229502915</v>
@@ -20424,7 +20430,7 @@
         <v>1</v>
       </c>
       <c r="P380" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="381" spans="1:16">
@@ -20438,7 +20444,7 @@
         <v>1.869509828609061</v>
       </c>
       <c r="D381" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E381">
         <v>2.55362229502915</v>
@@ -20474,7 +20480,7 @@
         <v>1</v>
       </c>
       <c r="P381" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="382" spans="1:16">
@@ -20488,7 +20494,7 @@
         <v>2.574954921244757</v>
       </c>
       <c r="D382" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E382">
         <v>2.17950982860906</v>
@@ -20524,7 +20530,7 @@
         <v>1</v>
       </c>
       <c r="P382" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="383" spans="1:16">
@@ -20538,7 +20544,7 @@
         <v>1.812289668813548</v>
       </c>
       <c r="D383" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E383">
         <v>2.703955451583056</v>
@@ -20574,7 +20580,7 @@
         <v>1</v>
       </c>
       <c r="P383" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="384" spans="1:16">
@@ -20588,7 +20594,7 @@
         <v>1.878354735459471</v>
       </c>
       <c r="D384" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E384">
         <v>2.42798454327702</v>
@@ -20624,7 +20630,7 @@
         <v>1</v>
       </c>
       <c r="P384" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="385" spans="1:16">
@@ -20674,7 +20680,7 @@
         <v>1</v>
       </c>
       <c r="P385" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="386" spans="1:16">
@@ -20688,7 +20694,7 @@
         <v>1.711502571778759</v>
       </c>
       <c r="D386" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E386">
         <v>2.569598382620882</v>
@@ -20724,7 +20730,7 @@
         <v>1</v>
       </c>
       <c r="P386" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="387" spans="1:16">
@@ -20738,7 +20744,7 @@
         <v>1.885973897627895</v>
       </c>
       <c r="D387" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E387">
         <v>2.569598382620882</v>
@@ -20774,7 +20780,7 @@
         <v>1</v>
       </c>
       <c r="P387" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="388" spans="1:16">
@@ -20788,7 +20794,7 @@
         <v>2.591185607841933</v>
       </c>
       <c r="D388" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E388">
         <v>2.195973897627894</v>
@@ -20824,7 +20830,7 @@
         <v>1</v>
       </c>
       <c r="P388" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="389" spans="1:16">
@@ -20838,7 +20844,7 @@
         <v>1.828011157399832</v>
       </c>
       <c r="D389" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E389">
         <v>2.719995188926148</v>
@@ -20874,7 +20880,7 @@
         <v>1</v>
       </c>
       <c r="P389" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="390" spans="1:16">
@@ -20888,7 +20894,7 @@
         <v>1.884937981108568</v>
       </c>
       <c r="D390" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E390">
         <v>2.434335634167709</v>
@@ -20924,7 +20930,7 @@
         <v>1</v>
       </c>
       <c r="P390" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="391" spans="1:16">
@@ -20974,7 +20980,7 @@
         <v>1</v>
       </c>
       <c r="P391" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="392" spans="1:16">
@@ -20988,7 +20994,7 @@
         <v>1.718492088255065</v>
       </c>
       <c r="D392" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E392">
         <v>2.575841687373739</v>
@@ -21024,7 +21030,7 @@
         <v>1</v>
       </c>
       <c r="P392" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="393" spans="1:16">
@@ -21038,7 +21044,7 @@
         <v>1.892407900932305</v>
       </c>
       <c r="D393" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E393">
         <v>2.575841687373739</v>
@@ -21074,7 +21080,7 @@
         <v>1</v>
       </c>
       <c r="P393" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="394" spans="1:16">
@@ -21088,7 +21094,7 @@
         <v>1.834154967256232</v>
       </c>
       <c r="D394" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E394">
         <v>2.726263367403121</v>
@@ -21124,7 +21130,7 @@
         <v>1</v>
       </c>
       <c r="P394" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="395" spans="1:16">
@@ -21138,7 +21144,7 @@
         <v>2.791624887079966</v>
       </c>
       <c r="D395" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E395">
         <v>2.637829766815571</v>
@@ -21174,7 +21180,7 @@
         <v>1</v>
       </c>
       <c r="P395" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="396" spans="1:16">
@@ -21188,7 +21194,7 @@
         <v>1.897004594528006</v>
       </c>
       <c r="D396" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E396">
         <v>2.445976724695786</v>
@@ -21224,7 +21230,7 @@
         <v>1</v>
       </c>
       <c r="P396" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="397" spans="1:16">
@@ -21274,7 +21280,7 @@
         <v>1</v>
       </c>
       <c r="P397" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="398" spans="1:16">
@@ -21288,7 +21294,7 @@
         <v>1.731303366734398</v>
       </c>
       <c r="D398" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E398">
         <v>2.587285213702252</v>
@@ -21324,7 +21330,7 @@
         <v>1</v>
       </c>
       <c r="P398" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="399" spans="1:16">
@@ -21338,7 +21344,7 @@
         <v>1.904200963921582</v>
       </c>
       <c r="D399" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E399">
         <v>2.587285213702252</v>
@@ -21374,7 +21380,7 @@
         <v>1</v>
       </c>
       <c r="P399" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="400" spans="1:16">
@@ -21388,7 +21394,7 @@
         <v>1.845416126631299</v>
       </c>
       <c r="D400" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E400">
         <v>2.737752485469994</v>
@@ -21424,7 +21430,7 @@
         <v>1</v>
       </c>
       <c r="P400" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="401" spans="1:16">
@@ -21438,7 +21444,7 @@
         <v>2.802612496024871</v>
       </c>
       <c r="D401" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E401">
         <v>2.813453713263602</v>
@@ -21474,7 +21480,7 @@
         <v>1</v>
       </c>
       <c r="P401" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="402" spans="1:16">
@@ -21488,7 +21494,7 @@
         <v>1.915149243214803</v>
       </c>
       <c r="D402" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E402">
         <v>2.463481511716044</v>
@@ -21524,7 +21530,7 @@
         <v>1</v>
       </c>
       <c r="P402" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="403" spans="1:16">
@@ -21574,7 +21580,7 @@
         <v>1</v>
       </c>
       <c r="P403" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="404" spans="1:16">
@@ -21588,7 +21594,7 @@
         <v>1.750567773337632</v>
       </c>
       <c r="D404" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E404">
         <v>2.60449292209162</v>
@@ -21624,7 +21630,7 @@
         <v>1</v>
       </c>
       <c r="P404" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="405" spans="1:16">
@@ -21638,7 +21644,7 @@
         <v>1.921934272965604</v>
       </c>
       <c r="D405" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E405">
         <v>2.60449292209162</v>
@@ -21674,7 +21680,7 @@
         <v>1</v>
       </c>
       <c r="P405" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="406" spans="1:16">
@@ -21688,7 +21694,7 @@
         <v>1.862349608592151</v>
       </c>
       <c r="D406" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E406">
         <v>2.75502875046649</v>
@@ -21724,7 +21730,7 @@
         <v>1</v>
       </c>
       <c r="P406" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="407" spans="1:16">
@@ -21738,7 +21744,7 @@
         <v>2.819134638342948</v>
       </c>
       <c r="D407" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E407">
         <v>2.769730713091974</v>
@@ -21774,7 +21780,7 @@
         <v>1</v>
       </c>
       <c r="P407" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="408" spans="1:16">
@@ -21788,7 +21794,7 @@
         <v>1.92753511972947</v>
       </c>
       <c r="D408" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E408">
         <v>2.475430606691152</v>
@@ -21888,7 +21894,7 @@
         <v>1.76371801754653</v>
       </c>
       <c r="D410" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E410">
         <v>2.616239225637646</v>
@@ -21938,7 +21944,7 @@
         <v>1.934039361347697</v>
       </c>
       <c r="D411" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E411">
         <v>2.616239225637646</v>
@@ -21988,7 +21994,7 @@
         <v>1.873908720049794</v>
       </c>
       <c r="D412" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E412">
         <v>2.766821852034614</v>
@@ -22038,7 +22044,7 @@
         <v>2.830412961668017</v>
       </c>
       <c r="D413" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E413">
         <v>2.221708855759843</v>
@@ -22088,7 +22094,7 @@
         <v>1.937685341557977</v>
       </c>
       <c r="D414" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E414">
         <v>2.485222886188172</v>
@@ -22124,7 +22130,7 @@
         <v>1</v>
       </c>
       <c r="P414" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="415" spans="1:16">
@@ -22174,7 +22180,7 @@
         <v>1</v>
       </c>
       <c r="P415" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="416" spans="1:16">
@@ -22188,7 +22194,7 @@
         <v>1.774494638455131</v>
       </c>
       <c r="D416" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E416">
         <v>2.625865317623621</v>
@@ -22224,7 +22230,7 @@
         <v>1</v>
       </c>
       <c r="P416" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="417" spans="1:16">
@@ -22238,7 +22244,7 @@
         <v>1.943959477391676</v>
       </c>
       <c r="D417" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E417">
         <v>2.625865317623621</v>
@@ -22274,7 +22280,7 @@
         <v>1</v>
       </c>
       <c r="P417" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="418" spans="1:16">
@@ -22288,7 +22294,7 @@
         <v>1.883381408179421</v>
       </c>
       <c r="D418" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E418">
         <v>2.776486294984675</v>
@@ -22324,7 +22330,7 @@
         <v>1</v>
       </c>
       <c r="P418" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="419" spans="1:16">
@@ -22338,7 +22344,7 @@
         <v>2.839655544013116</v>
       </c>
       <c r="D419" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E419">
         <v>2.231475567947474</v>
@@ -22374,7 +22380,7 @@
         <v>1</v>
       </c>
       <c r="P419" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="420" spans="1:16">
@@ -22388,7 +22394,7 @@
         <v>1.950149148490695</v>
       </c>
       <c r="D420" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E420">
         <v>2.49724716340538</v>
@@ -22424,7 +22430,7 @@
         <v>1</v>
       </c>
       <c r="P420" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="421" spans="1:16">
@@ -22474,7 +22480,7 @@
         <v>1</v>
       </c>
       <c r="P421" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="422" spans="1:16">
@@ -22488,7 +22494,7 @@
         <v>1.787727622389998</v>
       </c>
       <c r="D422" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E422">
         <v>2.637685527472915</v>
@@ -22524,7 +22530,7 @@
         <v>1</v>
       </c>
       <c r="P422" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="423" spans="1:16">
@@ -22538,7 +22544,7 @@
         <v>1.956140729507283</v>
       </c>
       <c r="D423" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E423">
         <v>2.637685527472915</v>
@@ -22574,7 +22580,7 @@
         <v>1</v>
       </c>
       <c r="P423" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="424" spans="1:16">
@@ -22588,7 +22594,7 @@
         <v>1.895013248150637</v>
       </c>
       <c r="D424" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E424">
         <v>2.788353597303487</v>
@@ -22624,7 +22630,7 @@
         <v>1</v>
       </c>
       <c r="P424" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="425" spans="1:16">
@@ -22638,7 +22644,7 @@
         <v>2.85100482916722</v>
       </c>
       <c r="D425" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E425">
         <v>2.243468450185002</v>
@@ -22674,7 +22680,7 @@
         <v>1</v>
       </c>
       <c r="P425" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="426" spans="1:16">
@@ -22738,7 +22744,7 @@
         <v>1.796280604882195</v>
       </c>
       <c r="D427" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E427">
         <v>2.645325380161676</v>
@@ -22788,7 +22794,7 @@
         <v>1.964013937590256</v>
       </c>
       <c r="D428" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E428">
         <v>2.645325380161676</v>
@@ -22838,7 +22844,7 @@
         <v>1.902531350198938</v>
       </c>
       <c r="D429" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E429">
         <v>2.796023887652364</v>
@@ -22888,7 +22894,7 @@
         <v>2.858340305254835</v>
       </c>
       <c r="D430" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E430">
         <v>2.251219907627515</v>
@@ -22974,7 +22980,7 @@
         <v>1</v>
       </c>
       <c r="P431" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="432" spans="1:16">
@@ -22988,7 +22994,7 @@
         <v>1.81059278070445</v>
       </c>
       <c r="D432" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E432">
         <v>2.658109565682619</v>
@@ -23024,7 +23030,7 @@
         <v>1</v>
       </c>
       <c r="P432" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="433" spans="1:16">
@@ -23038,7 +23044,7 @@
         <v>1.977188609521534</v>
       </c>
       <c r="D433" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E433">
         <v>2.658109565682619</v>
@@ -23074,7 +23080,7 @@
         <v>1</v>
       </c>
       <c r="P433" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="434" spans="1:16">
@@ -23088,7 +23094,7 @@
         <v>1.915111803679711</v>
       </c>
       <c r="D434" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E434">
         <v>2.808859006183351</v>
@@ -23124,7 +23130,7 @@
         <v>1</v>
       </c>
       <c r="P434" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="435" spans="1:16">
@@ -23138,7 +23144,7 @@
         <v>2.870615160675342</v>
       </c>
       <c r="D435" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E435">
         <v>2.26419084751862</v>
@@ -23174,7 +23180,7 @@
         <v>1</v>
       </c>
       <c r="P435" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="436" spans="1:16">
@@ -23224,7 +23230,7 @@
         <v>1</v>
       </c>
       <c r="P436" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="437" spans="1:16">
@@ -23238,7 +23244,7 @@
         <v>1.82632056259726</v>
       </c>
       <c r="D437" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E437">
         <v>2.672158224953424</v>
@@ -23274,7 +23280,7 @@
         <v>1</v>
       </c>
       <c r="P437" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="438" spans="1:16">
@@ -23288,7 +23294,7 @@
         <v>1.991666377906849</v>
       </c>
       <c r="D438" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E438">
         <v>2.672158224953424</v>
@@ -23324,7 +23330,7 @@
         <v>1</v>
       </c>
       <c r="P438" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="439" spans="1:16">
@@ -23338,7 +23344,7 @@
         <v>1.928936579934245</v>
       </c>
       <c r="D439" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E439">
         <v>2.822963636208222</v>
@@ -23374,7 +23380,7 @@
         <v>1</v>
       </c>
       <c r="P439" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="440" spans="1:16">
@@ -23388,7 +23394,7 @@
         <v>2.884104112405478</v>
       </c>
       <c r="D440" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E440">
         <v>2.278444732887671</v>
@@ -23424,7 +23430,7 @@
         <v>1</v>
       </c>
       <c r="P440" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="441" spans="1:16">
@@ -23438,7 +23444,7 @@
         <v>1.850091985515281</v>
       </c>
       <c r="D441" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E441">
         <v>2.693391773538558</v>
@@ -23488,7 +23494,7 @@
         <v>2.013548494377055</v>
       </c>
       <c r="D442" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E442">
         <v>2.693391773538558</v>
@@ -23538,7 +23544,7 @@
         <v>1.949831745274995</v>
       </c>
       <c r="D443" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E443">
         <v>2.844281780604454</v>
@@ -23588,7 +23594,7 @@
         <v>2.90449170287965</v>
       </c>
       <c r="D444" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E444">
         <v>2.29998846611349</v>
@@ -23638,7 +23644,7 @@
         <v>1.883787347386825</v>
       </c>
       <c r="D445" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E445">
         <v>2.723489765815277</v>
@@ -23674,7 +23680,7 @@
         <v>1</v>
       </c>
       <c r="P445" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="446" spans="1:16">
@@ -23688,7 +23694,7 @@
         <v>2.044565814439117</v>
       </c>
       <c r="D446" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E446">
         <v>2.723489765815277</v>
@@ -23724,7 +23730,7 @@
         <v>1</v>
       </c>
       <c r="P446" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="447" spans="1:16">
@@ -23738,7 +23744,7 @@
         <v>2.74752944335815</v>
       </c>
       <c r="D447" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E447">
         <v>2.354565814439116</v>
@@ -23774,7 +23780,7 @@
         <v>1</v>
       </c>
       <c r="P447" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="448" spans="1:16">
@@ -23788,7 +23794,7 @@
         <v>1.979450088272404</v>
       </c>
       <c r="D448" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E448">
         <v>2.874499685200998</v>
@@ -23824,7 +23830,7 @@
         <v>1</v>
       </c>
       <c r="P448" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="449" spans="1:16">
@@ -23838,7 +23844,7 @@
         <v>2.933390571958093</v>
       </c>
       <c r="D449" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E449">
         <v>2.330526136896243</v>
@@ -23874,7 +23880,7 @@
         <v>1</v>
       </c>
       <c r="P449" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="450" spans="1:16">
@@ -23924,7 +23930,7 @@
         <v>1</v>
       </c>
       <c r="P450" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="451" spans="1:16">
@@ -23938,7 +23944,7 @@
         <v>1.920897553279229</v>
       </c>
       <c r="D451" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E451">
         <v>2.756638028018099</v>
@@ -23974,7 +23980,7 @@
         <v>1</v>
       </c>
       <c r="P451" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="452" spans="1:16">
@@ -23988,7 +23994,7 @@
         <v>2.078726573362612</v>
       </c>
       <c r="D452" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E452">
         <v>2.756638028018099</v>
@@ -24024,7 +24030,7 @@
         <v>1</v>
       </c>
       <c r="P452" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="453" spans="1:16">
@@ -24038,7 +24044,7 @@
         <v>2.012070091316616</v>
       </c>
       <c r="D453" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E453">
         <v>2.907780012193474</v>
@@ -24074,7 +24080,7 @@
         <v>1</v>
       </c>
       <c r="P453" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="454" spans="1:16">
@@ -24088,7 +24094,7 @@
         <v>2.965218186264387</v>
       </c>
       <c r="D454" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E454">
         <v>2.364158636661127</v>
@@ -24124,7 +24130,7 @@
         <v>1</v>
       </c>
       <c r="P454" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="455" spans="1:16">
@@ -24138,7 +24144,7 @@
         <v>1.971362962924253</v>
       </c>
       <c r="D455" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E455">
         <v>2.801715671508852</v>
@@ -24188,7 +24194,7 @@
         <v>2.125181090426125</v>
       </c>
       <c r="D456" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E456">
         <v>2.801715671508852</v>
@@ -24238,7 +24244,7 @@
         <v>2.056429365986798</v>
       </c>
       <c r="D457" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E457">
         <v>2.95303724788937</v>
@@ -24288,7 +24294,7 @@
         <v>3.008499907703719</v>
       </c>
       <c r="D458" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E458">
         <v>2.409894784904068</v>
@@ -24338,7 +24344,7 @@
         <v>2.008171638992437</v>
       </c>
       <c r="D459" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E459">
         <v>2.834594595683633</v>
@@ -24374,7 +24380,7 @@
         <v>1</v>
       </c>
       <c r="P459" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="460" spans="1:16">
@@ -24388,7 +24394,7 @@
         <v>2.159064284529219</v>
       </c>
       <c r="D460" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E460">
         <v>2.834594595683633</v>
@@ -24424,7 +24430,7 @@
         <v>1</v>
       </c>
       <c r="P460" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="461" spans="1:16">
@@ -24438,7 +24444,7 @@
         <v>2.088784323242461</v>
       </c>
       <c r="D461" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E461">
         <v>2.986047163793931</v>
@@ -24474,7 +24480,7 @@
         <v>1</v>
       </c>
       <c r="P461" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="462" spans="1:16">
@@ -24488,7 +24494,7 @@
         <v>3.040068914580697</v>
       </c>
       <c r="D462" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E462">
         <v>2.443254012088044</v>
@@ -24524,7 +24530,7 @@
         <v>1</v>
       </c>
       <c r="P462" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="463" spans="1:16">
@@ -24538,7 +24544,7 @@
         <v>2.067700645146257</v>
       </c>
       <c r="D463" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E463">
         <v>2.887768191927794</v>
@@ -24588,7 +24594,7 @@
         <v>2.213862041083626</v>
       </c>
       <c r="D464" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E464">
         <v>2.887768191927794</v>
@@ -24638,7 +24644,7 @@
         <v>2.914425852356924</v>
       </c>
       <c r="D465" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E465">
         <v>2.523862041083625</v>
@@ -24688,7 +24694,7 @@
         <v>2.141110531498665</v>
       </c>
       <c r="D466" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E466">
         <v>3.039432607035081</v>
@@ -24738,7 +24744,7 @@
         <v>3.091124040854972</v>
       </c>
       <c r="D467" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E467">
         <v>2.497204380654495</v>
@@ -24788,7 +24794,7 @@
         <v>2.102053433035913</v>
       </c>
       <c r="D468" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E468">
         <v>2.918453422391508</v>
@@ -24824,7 +24830,7 @@
         <v>1</v>
       </c>
       <c r="P468" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="469" spans="1:16">
@@ -24838,7 +24844,7 @@
         <v>2.245484536222857</v>
       </c>
       <c r="D469" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E469">
         <v>2.918453422391508</v>
@@ -24874,7 +24880,7 @@
         <v>1</v>
       </c>
       <c r="P469" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="470" spans="1:16">
@@ -24888,7 +24894,7 @@
         <v>2.945600090477427</v>
       </c>
       <c r="D470" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E470">
         <v>2.555484536222856</v>
@@ -24924,7 +24930,7 @@
         <v>1</v>
       </c>
       <c r="P470" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="471" spans="1:16">
@@ -24938,7 +24944,7 @@
         <v>2.171306754305586</v>
       </c>
       <c r="D471" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E471">
         <v>3.070240089412991</v>
@@ -24974,7 +24980,7 @@
         <v>1</v>
       </c>
       <c r="P471" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="472" spans="1:16">
@@ -24988,7 +24994,7 @@
         <v>3.120586752176706</v>
       </c>
       <c r="D472" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E472">
         <v>2.528337868136934</v>
@@ -25024,7 +25030,7 @@
         <v>1</v>
       </c>
       <c r="P472" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="473" spans="1:16">
@@ -25038,7 +25044,7 @@
         <v>2.150109762840597</v>
       </c>
       <c r="D473" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E473">
         <v>2.961379183177897</v>
@@ -25074,7 +25080,7 @@
         <v>1</v>
       </c>
       <c r="P473" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="474" spans="1:16">
@@ -25088,7 +25094,7 @@
         <v>2.289721442425034</v>
       </c>
       <c r="D474" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E474">
         <v>2.961379183177897</v>
@@ -25124,7 +25130,7 @@
         <v>1</v>
       </c>
       <c r="P474" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="475" spans="1:16">
@@ -25138,7 +25144,7 @@
         <v>2.989209927132926</v>
       </c>
       <c r="D475" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E475">
         <v>2.599721442425032</v>
@@ -25174,7 +25180,7 @@
         <v>1</v>
       </c>
       <c r="P475" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="476" spans="1:16">
@@ -25188,7 +25194,7 @@
         <v>2.213548439222873</v>
       </c>
       <c r="D476" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E476">
         <v>3.113336869166659</v>
@@ -25224,7 +25230,7 @@
         <v>1</v>
       </c>
       <c r="P476" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="477" spans="1:16">
@@ -25238,7 +25244,7 @@
         <v>3.161802323290331</v>
       </c>
       <c r="D477" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E477">
         <v>2.571890698470007</v>
@@ -25274,7 +25280,7 @@
         <v>1</v>
       </c>
       <c r="P477" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="478" spans="1:16">
@@ -25288,7 +25294,7 @@
         <v>2.189716387261424</v>
       </c>
       <c r="D478" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E478">
         <v>2.99675734235807</v>
@@ -25338,7 +25344,7 @@
         <v>2.326180209388927</v>
       </c>
       <c r="D479" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E479">
         <v>2.99675734235807</v>
@@ -25388,7 +25394,7 @@
         <v>2.248362803037622</v>
       </c>
       <c r="D480" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E480">
         <v>3.148855977188184</v>
@@ -25438,7 +25444,7 @@
         <v>3.19577099405695</v>
       </c>
       <c r="D481" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E481">
         <v>2.607785670068477</v>
@@ -25488,7 +25494,7 @@
         <v>2.215826782258592</v>
       </c>
       <c r="D482" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E482">
         <v>3.020080150700736</v>
@@ -25524,7 +25530,7 @@
         <v>1</v>
       </c>
       <c r="P482" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="483" spans="1:16">
@@ -25538,7 +25544,7 @@
         <v>2.350215400987747</v>
       </c>
       <c r="D483" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E483">
         <v>3.020080150700736</v>
@@ -25574,7 +25580,7 @@
         <v>1</v>
       </c>
       <c r="P483" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="484" spans="1:16">
@@ -25588,7 +25594,7 @@
         <v>2.271313933159689</v>
       </c>
       <c r="D484" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E484">
         <v>3.172271705086001</v>
@@ -25624,7 +25630,7 @@
         <v>1</v>
       </c>
       <c r="P484" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="485" spans="1:16">
@@ -25638,7 +25644,7 @@
         <v>3.218164606848116</v>
       </c>
       <c r="D485" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E485">
         <v>2.631449183446694</v>
@@ -25674,7 +25680,7 @@
         <v>1</v>
       </c>
       <c r="P485" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="486" spans="1:16">
@@ -25724,7 +25730,7 @@
         <v>1</v>
       </c>
       <c r="P486" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="487" spans="1:16">
@@ -25738,7 +25744,7 @@
         <v>2.227304742320833</v>
       </c>
       <c r="D487" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E487">
         <v>3.030332705774125</v>
@@ -25774,7 +25780,7 @@
         <v>1</v>
       </c>
       <c r="P487" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="488" spans="1:16">
@@ -25788,7 +25794,7 @@
         <v>2.360781115113841</v>
       </c>
       <c r="D488" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E488">
         <v>3.030332705774125</v>
@@ -25824,7 +25830,7 @@
         <v>1</v>
       </c>
       <c r="P488" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="489" spans="1:16">
@@ -25838,7 +25844,7 @@
         <v>2.28140310090123</v>
       </c>
       <c r="D489" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E489">
         <v>3.182565106992353</v>
@@ -25874,7 +25880,7 @@
         <v>1</v>
       </c>
       <c r="P489" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="490" spans="1:16">
@@ -25888,7 +25894,7 @@
         <v>3.228008693591889</v>
       </c>
       <c r="D490" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E490">
         <v>2.641851510240944</v>
@@ -25924,7 +25930,7 @@
         <v>1</v>
       </c>
       <c r="P490" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="491" spans="1:16">
@@ -25938,7 +25944,7 @@
         <v>2.326764722017106</v>
       </c>
       <c r="D491" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E491">
         <v>2.338905512271317</v>
@@ -25974,7 +25980,7 @@
         <v>1</v>
       </c>
       <c r="P491" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="492" spans="1:16">
@@ -25988,7 +25994,7 @@
         <v>2.245345573811253</v>
       </c>
       <c r="D492" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E492">
         <v>3.046447469845635</v>
@@ -26024,7 +26030,7 @@
         <v>1</v>
       </c>
       <c r="P492" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="493" spans="1:16">
@@ -26038,7 +26044,7 @@
         <v>2.377388096414631</v>
       </c>
       <c r="D493" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E493">
         <v>3.046447469845635</v>
@@ -26074,7 +26080,7 @@
         <v>1</v>
       </c>
       <c r="P493" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="494" spans="1:16">
@@ -26088,7 +26094,7 @@
         <v>2.297261055983554</v>
       </c>
       <c r="D494" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E494">
         <v>3.198744073311161</v>
@@ -26124,7 +26130,7 @@
         <v>1</v>
       </c>
       <c r="P494" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="495" spans="1:16">
@@ -26138,7 +26144,7 @@
         <v>3.243481435190432</v>
       </c>
       <c r="D495" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E495">
         <v>2.658201682552544</v>
@@ -26174,7 +26180,7 @@
         <v>1</v>
       </c>
       <c r="P495" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="496" spans="1:16">
@@ -26224,7 +26230,7 @@
         <v>1</v>
       </c>
       <c r="P496" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="497" spans="1:16">
@@ -26238,7 +26244,7 @@
         <v>2.301170929293026</v>
       </c>
       <c r="D497" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E497">
         <v>3.202733093853617</v>
@@ -26288,7 +26294,7 @@
         <v>3.247296331820319</v>
       </c>
       <c r="D498" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E498">
         <v>2.662232914952593</v>
@@ -26388,7 +26394,7 @@
         <v>2.309276220482282</v>
       </c>
       <c r="D500" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E500">
         <v>3.211002459763304</v>
@@ -26424,7 +26430,7 @@
         <v>1</v>
       </c>
       <c r="P500" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="501" spans="1:16">
@@ -26438,7 +26444,7 @@
         <v>3.25520473334506</v>
       </c>
       <c r="D501" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E501">
         <v>2.670589787379843</v>
@@ -26474,7 +26480,7 @@
         <v>1</v>
       </c>
       <c r="P501" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="502" spans="1:16">
@@ -26488,7 +26494,7 @@
         <v>2.35659384998981</v>
       </c>
       <c r="D502" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E502">
         <v>2.377701080695644</v>
@@ -26524,7 +26530,7 @@
         <v>1</v>
       </c>
       <c r="P502" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="503" spans="1:16">
@@ -26538,7 +26544,7 @@
         <v>2.318802840630408</v>
       </c>
       <c r="D503" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E503">
         <v>3.220721926473129</v>
@@ -26588,7 +26594,7 @@
         <v>3.264499937619139</v>
       </c>
       <c r="D504" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E504">
         <v>2.680412105589244</v>
@@ -26738,7 +26744,7 @@
         <v>2.968469110715926</v>
       </c>
       <c r="D507" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E507">
         <v>3.65607053595874</v>
@@ -26774,7 +26780,7 @@
         <v>1</v>
       </c>
       <c r="P507" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="508" spans="1:16">
@@ -26788,7 +26794,7 @@
         <v>3.056098677724048</v>
       </c>
       <c r="D508" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E508">
         <v>3.65607053595874</v>
@@ -26824,7 +26830,7 @@
         <v>1</v>
       </c>
       <c r="P508" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="509" spans="1:16">
@@ -26838,7 +26844,7 @@
         <v>3.085552267926261</v>
       </c>
       <c r="D509" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E509">
         <v>3.65607053595874</v>
@@ -26874,7 +26880,7 @@
         <v>1</v>
       </c>
       <c r="P509" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="510" spans="1:16">
@@ -26888,7 +26894,7 @@
         <v>3.115403587495276</v>
       </c>
       <c r="D510" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E510">
         <v>4.899694426383849</v>
@@ -26924,7 +26930,7 @@
         <v>1</v>
       </c>
       <c r="P510" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="511" spans="1:16">
@@ -26938,7 +26944,7 @@
         <v>2.857657467623699</v>
       </c>
       <c r="D511" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E511">
         <v>4.899694426383849</v>
@@ -26974,7 +26980,7 @@
         <v>1</v>
       </c>
       <c r="P511" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="512" spans="1:16">
@@ -26988,7 +26994,7 @@
         <v>4.634833021734408</v>
       </c>
       <c r="D512" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E512">
         <v>3.48240231940969</v>
@@ -27024,7 +27030,7 @@
         <v>1</v>
       </c>
       <c r="P512" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="513" spans="1:16">
@@ -27038,7 +27044,7 @@
         <v>3.013404560606677</v>
       </c>
       <c r="D513" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E513">
         <v>3.707166946903694</v>
@@ -27074,7 +27080,7 @@
         <v>1</v>
       </c>
       <c r="P513" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="514" spans="1:16">
@@ -27088,7 +27094,7 @@
         <v>3.101938488870459</v>
       </c>
       <c r="D514" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E514">
         <v>3.707166946903694</v>
@@ -27124,7 +27130,7 @@
         <v>1</v>
       </c>
       <c r="P514" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="515" spans="1:16">
@@ -27138,7 +27144,7 @@
         <v>3.133031233848563</v>
       </c>
       <c r="D515" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E515">
         <v>3.707166946903694</v>
@@ -27174,7 +27180,7 @@
         <v>1</v>
       </c>
       <c r="P515" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="516" spans="1:16">
@@ -27188,7 +27194,7 @@
         <v>2.923647577997855</v>
       </c>
       <c r="D516" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E516">
         <v>4.966814988327585</v>
@@ -27224,7 +27230,7 @@
         <v>1</v>
       </c>
       <c r="P516" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="517" spans="1:16">
@@ -27238,7 +27244,7 @@
         <v>4.706192777064061</v>
       </c>
       <c r="D517" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E517">
         <v>3.555881671432303</v>
@@ -27274,7 +27280,7 @@
         <v>1</v>
       </c>
       <c r="P517" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="518" spans="1:16">
@@ -27288,7 +27294,7 @@
         <v>3.058294813446018</v>
       </c>
       <c r="D518" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E518">
         <v>3.758211963968808</v>
@@ -27324,7 +27330,7 @@
         <v>1</v>
       </c>
       <c r="P518" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="519" spans="1:16">
@@ -27338,7 +27344,7 @@
         <v>3.147732193339273</v>
       </c>
       <c r="D519" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E519">
         <v>3.758211963968808</v>
@@ -27374,7 +27380,7 @@
         <v>1</v>
       </c>
       <c r="P519" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="520" spans="1:16">
@@ -27388,7 +27394,7 @@
         <v>3.18046244439579</v>
       </c>
       <c r="D520" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E520">
         <v>3.758211963968808</v>
@@ -27424,7 +27430,7 @@
         <v>1</v>
       </c>
       <c r="P520" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="521" spans="1:16">
@@ -27438,7 +27444,7 @@
         <v>3.225680173488445</v>
       </c>
       <c r="D521" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E521">
         <v>5.033868038952384</v>
@@ -27474,7 +27480,7 @@
         <v>1</v>
       </c>
       <c r="P521" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="522" spans="1:16">
@@ -27488,7 +27494,7 @@
         <v>2.989571314085818</v>
       </c>
       <c r="D522" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E522">
         <v>5.033868038952384</v>
@@ -27524,7 +27530,7 @@
         <v>1</v>
       </c>
       <c r="P522" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="523" spans="1:16">
@@ -27538,7 +27544,7 @@
         <v>4.77748075720201</v>
       </c>
       <c r="D523" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E523">
         <v>3.629287116326825</v>
@@ -27574,7 +27580,7 @@
         <v>1</v>
       </c>
       <c r="P523" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="524" spans="1:16">
@@ -27588,7 +27594,7 @@
         <v>3.100990526217007</v>
       </c>
       <c r="D524" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E524">
         <v>5.097643081613452</v>
@@ -27624,7 +27630,7 @@
         <v>1</v>
       </c>
       <c r="P524" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="525" spans="1:16">
@@ -27638,7 +27644,7 @@
         <v>3.19128719089559</v>
       </c>
       <c r="D525" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E525">
         <v>5.097643081613452</v>
@@ -27674,7 +27680,7 @@
         <v>1</v>
       </c>
       <c r="P525" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="526" spans="1:16">
@@ -27688,7 +27694,7 @@
         <v>3.225574895625517</v>
       </c>
       <c r="D526" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E526">
         <v>5.097643081613452</v>
@@ -27724,7 +27730,7 @@
         <v>1</v>
       </c>
       <c r="P526" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="527" spans="1:16">
@@ -27738,7 +27744,7 @@
         <v>3.205781960817575</v>
       </c>
       <c r="D527" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E527">
         <v>5.097643081613452</v>
@@ -27774,7 +27780,7 @@
         <v>1</v>
       </c>
       <c r="P527" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="528" spans="1:16">
@@ -27788,7 +27794,7 @@
         <v>3.27809654539346</v>
       </c>
       <c r="D528" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E528">
         <v>5.097643081613452</v>
@@ -27824,7 +27830,7 @@
         <v>1</v>
       </c>
       <c r="P528" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="529" spans="1:16">
@@ -27838,7 +27844,7 @@
         <v>3.052272250765228</v>
       </c>
       <c r="D529" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E529">
         <v>5.097643081613452</v>
@@ -27874,7 +27880,7 @@
         <v>1</v>
       </c>
       <c r="P529" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="530" spans="1:16">
@@ -27888,7 +27894,7 @@
         <v>4.845283697294303</v>
       </c>
       <c r="D530" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E530">
         <v>3.699104005134728</v>
@@ -27924,7 +27930,7 @@
         <v>1</v>
       </c>
       <c r="P530" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="531" spans="1:16">
@@ -27938,7 +27944,7 @@
         <v>3.135431759672713</v>
       </c>
       <c r="D531" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E531">
         <v>5.149088320265843</v>
@@ -27974,7 +27980,7 @@
         <v>1</v>
       </c>
       <c r="P531" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="532" spans="1:16">
@@ -27988,7 +27994,7 @@
         <v>3.226421581251035</v>
       </c>
       <c r="D532" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E532">
         <v>5.149088320265843</v>
@@ -28024,7 +28030,7 @@
         <v>1</v>
       </c>
       <c r="P532" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="533" spans="1:16">
@@ -28038,7 +28044,7 @@
         <v>3.261965632861735</v>
       </c>
       <c r="D533" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E533">
         <v>5.149088320265843</v>
@@ -28074,7 +28080,7 @@
         <v>1</v>
       </c>
       <c r="P533" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="534" spans="1:16">
@@ -28088,7 +28094,7 @@
         <v>3.248497754763896</v>
       </c>
       <c r="D534" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E534">
         <v>5.149088320265843</v>
@@ -28124,7 +28130,7 @@
         <v>1</v>
       </c>
       <c r="P534" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="535" spans="1:16">
@@ -28138,7 +28144,7 @@
         <v>3.320379116277444</v>
       </c>
       <c r="D535" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E535">
         <v>5.149088320265843</v>
@@ -28174,7 +28180,7 @@
         <v>1</v>
       </c>
       <c r="P535" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="536" spans="1:16">
@@ -28188,7 +28194,7 @@
         <v>3.102851043292947</v>
       </c>
       <c r="D536" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E536">
         <v>5.149088320265843</v>
@@ -28224,7 +28230,7 @@
         <v>1</v>
       </c>
       <c r="P536" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="537" spans="1:16">
@@ -28238,7 +28244,7 @@
         <v>4.899978108914215</v>
       </c>
       <c r="D537" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E537">
         <v>3.755423003238402</v>
@@ -28274,7 +28280,7 @@
         <v>1</v>
       </c>
       <c r="P537" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="538" spans="1:16">
@@ -28288,7 +28294,7 @@
         <v>3.340758667101504</v>
       </c>
       <c r="D538" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E538">
         <v>5.455787317211367</v>
@@ -28324,7 +28330,7 @@
         <v>1</v>
       </c>
       <c r="P538" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="539" spans="1:16">
@@ -28338,7 +28344,7 @@
         <v>3.596337846972439</v>
       </c>
       <c r="D539" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E539">
         <v>5.455787317211367</v>
@@ -28374,7 +28380,7 @@
         <v>1</v>
       </c>
       <c r="P539" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="540" spans="1:16">
@@ -28388,7 +28394,7 @@
         <v>3.478914818069512</v>
       </c>
       <c r="D540" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E540">
         <v>5.455787317211367</v>
@@ -28424,7 +28430,7 @@
         <v>1</v>
       </c>
       <c r="P540" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="541" spans="1:16">
@@ -28438,7 +28444,7 @@
         <v>3.503154774543503</v>
       </c>
       <c r="D541" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E541">
         <v>5.455787317211367</v>
@@ -28474,7 +28480,7 @@
         <v>1</v>
       </c>
       <c r="P541" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="542" spans="1:16">
@@ -28488,7 +28494,7 @@
         <v>3.572453407661722</v>
       </c>
       <c r="D542" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E542">
         <v>5.455787317211367</v>
@@ -28524,7 +28530,7 @@
         <v>1</v>
       </c>
       <c r="P542" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="543" spans="1:16">
@@ -28538,7 +28544,7 @@
         <v>3.404384583447808</v>
       </c>
       <c r="D543" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E543">
         <v>5.455787317211367</v>
@@ -28574,7 +28580,7 @@
         <v>1</v>
       </c>
       <c r="P543" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="544" spans="1:16">
@@ -28588,7 +28594,7 @@
         <v>5.25250104043668</v>
       </c>
       <c r="D544" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E544">
         <v>5.56320240731846</v>
@@ -28624,7 +28630,7 @@
         <v>1</v>
       </c>
       <c r="P544" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="545" spans="1:16">
@@ -28638,7 +28644,7 @@
         <v>3.408744253943432</v>
       </c>
       <c r="D545" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E545">
         <v>5.557338115167074</v>
@@ -28674,7 +28680,7 @@
         <v>1</v>
       </c>
       <c r="P545" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="546" spans="1:16">
@@ -28688,7 +28694,7 @@
         <v>3.550748645676077</v>
       </c>
       <c r="D546" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E546">
         <v>5.557338115167074</v>
@@ -28724,7 +28730,7 @@
         <v>1</v>
       </c>
       <c r="P546" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="547" spans="1:16">
@@ -28738,7 +28744,7 @@
         <v>3.587474005519777</v>
       </c>
       <c r="D547" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E547">
         <v>5.557338115167074</v>
@@ -28774,7 +28780,7 @@
         <v>1</v>
       </c>
       <c r="P547" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="548" spans="1:16">
@@ -28788,7 +28794,7 @@
         <v>3.655917474023632</v>
       </c>
       <c r="D548" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E548">
         <v>5.557338115167074</v>
@@ -28824,7 +28830,7 @@
         <v>1</v>
       </c>
       <c r="P548" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="549" spans="1:16">
@@ -28838,7 +28844,7 @@
         <v>3.504225052174785</v>
       </c>
       <c r="D549" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E549">
         <v>5.557338115167074</v>
@@ -28874,7 +28880,7 @@
         <v>1</v>
       </c>
       <c r="P549" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="550" spans="1:16">
@@ -28888,7 +28894,7 @@
         <v>5.346996730323884</v>
       </c>
       <c r="D550" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E550">
         <v>5.864438002961421</v>
@@ -28924,7 +28930,7 @@
         <v>1</v>
       </c>
       <c r="P550" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="551" spans="1:16">
@@ -28938,7 +28944,7 @@
         <v>5.267444590560391</v>
       </c>
       <c r="D551" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E551">
         <v>5.864438002961421</v>
@@ -28974,7 +28980,7 @@
         <v>1</v>
       </c>
       <c r="P551" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="552" spans="1:16">
@@ -28988,7 +28994,7 @@
         <v>3.796322429340982</v>
       </c>
       <c r="D552" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E552">
         <v>5.685955718590687</v>
@@ -29024,7 +29030,7 @@
         <v>1</v>
       </c>
       <c r="P552" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="553" spans="1:16">
@@ -29038,7 +29044,7 @@
         <v>3.641728676729411</v>
       </c>
       <c r="D553" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E553">
         <v>5.685955718590687</v>
@@ -29074,7 +29080,7 @@
         <v>1</v>
       </c>
       <c r="P553" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="554" spans="1:16">
@@ -29088,7 +29094,7 @@
         <v>3.69426723244667</v>
       </c>
       <c r="D554" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E554">
         <v>5.685955718590687</v>
@@ -29124,7 +29130,7 @@
         <v>1</v>
       </c>
       <c r="P554" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="555" spans="1:16">
@@ -29138,7 +29144,7 @@
         <v>3.761627605342749</v>
       </c>
       <c r="D555" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E555">
         <v>5.685955718590687</v>
@@ -29174,7 +29180,7 @@
         <v>1</v>
       </c>
       <c r="P555" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="556" spans="1:16">
@@ -29188,7 +29194,7 @@
         <v>3.630676464382844</v>
       </c>
       <c r="D556" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E556">
         <v>5.685955718590687</v>
@@ -29224,7 +29230,7 @@
         <v>1</v>
       </c>
       <c r="P556" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="557" spans="1:16">
@@ -29238,7 +29244,7 @@
         <v>5.466678794983334</v>
       </c>
       <c r="D557" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E557">
         <v>5.209318422087254</v>
@@ -29274,7 +29280,7 @@
         <v>1</v>
       </c>
       <c r="P557" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="558" spans="1:16">
@@ -29288,7 +29294,7 @@
         <v>5.390917489847062</v>
       </c>
       <c r="D558" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E558">
         <v>5.209318422087254</v>
@@ -29324,7 +29330,7 @@
         <v>1</v>
       </c>
       <c r="P558" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="559" spans="1:16">
@@ -29338,7 +29344,7 @@
         <v>4.159051079599863</v>
       </c>
       <c r="D559" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E559">
         <v>5.343391662540899</v>
@@ -29374,7 +29380,7 @@
         <v>1</v>
       </c>
       <c r="P559" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="560" spans="1:16">
@@ -29388,7 +29394,7 @@
         <v>4.237780255555339</v>
       </c>
       <c r="D560" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E560">
         <v>5.313343652467495</v>
@@ -29424,7 +29430,7 @@
         <v>1</v>
       </c>
       <c r="P560" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="561" spans="1:16">
@@ -29438,7 +29444,7 @@
         <v>4.283295642394084</v>
       </c>
       <c r="D561" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E561">
         <v>5.313343652467495</v>
@@ -29474,7 +29480,7 @@
         <v>1</v>
       </c>
       <c r="P561" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="562" spans="1:16">
@@ -29524,7 +29530,7 @@
         <v>1</v>
       </c>
       <c r="P562" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="563" spans="1:16">
@@ -29538,7 +29544,7 @@
         <v>4.047954928502808</v>
       </c>
       <c r="D563" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E563">
         <v>5.235960539108905</v>
@@ -29574,7 +29580,7 @@
         <v>1</v>
       </c>
       <c r="P563" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="564" spans="1:16">
@@ -29588,7 +29594,7 @@
         <v>4.137221058995326</v>
       </c>
       <c r="D564" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E564">
         <v>5.202705629828571</v>
@@ -29624,7 +29630,7 @@
         <v>1</v>
       </c>
       <c r="P564" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="565" spans="1:16">
@@ -29638,7 +29644,7 @@
         <v>4.169450720548237</v>
       </c>
       <c r="D565" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E565">
         <v>5.202705629828571</v>
@@ -29674,7 +29680,7 @@
         <v>1</v>
       </c>
       <c r="P565" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="566" spans="1:16">
@@ -29688,7 +29694,7 @@
         <v>6.314817655301979</v>
       </c>
       <c r="D566" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E566">
         <v>6.624319057953503</v>
@@ -29724,7 +29730,7 @@
         <v>1</v>
       </c>
       <c r="P566" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="567" spans="1:16">
@@ -29738,7 +29744,7 @@
         <v>4.059730080999771</v>
       </c>
       <c r="D567" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E567">
         <v>5.117447902330046</v>
@@ -29788,7 +29794,7 @@
         <v>4.081721754571493</v>
       </c>
       <c r="D568" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E568">
         <v>5.117447902330046</v>
@@ -29888,7 +29894,7 @@
         <v>4.030557457706422</v>
       </c>
       <c r="D570" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E570">
         <v>5.085351371462874</v>
@@ -29924,7 +29930,7 @@
         <v>1</v>
       </c>
       <c r="P570" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="571" spans="1:16">
@@ -29938,7 +29944,7 @@
         <v>4.048694889476288</v>
       </c>
       <c r="D571" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E571">
         <v>5.085351371462874</v>
@@ -29974,7 +29980,7 @@
         <v>1</v>
       </c>
       <c r="P571" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="572" spans="1:16">
@@ -30024,7 +30030,7 @@
         <v>1</v>
       </c>
       <c r="P572" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="573" spans="1:16">
@@ -30038,7 +30044,7 @@
         <v>3.737521317704196</v>
       </c>
       <c r="D573" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E573">
         <v>4.762944866631269</v>
@@ -30074,7 +30080,7 @@
         <v>1</v>
       </c>
       <c r="P573" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="574" spans="1:16">
@@ -30088,7 +30094,7 @@
         <v>3.716943268562606</v>
       </c>
       <c r="D574" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E574">
         <v>4.762944866631269</v>
@@ -30124,7 +30130,7 @@
         <v>1</v>
       </c>
       <c r="P574" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="575" spans="1:16">
@@ -30174,7 +30180,7 @@
         <v>1</v>
       </c>
       <c r="P575" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="576" spans="1:16">
@@ -30224,7 +30230,7 @@
         <v>1</v>
       </c>
       <c r="P576" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="577" spans="1:16">
@@ -30238,7 +30244,7 @@
         <v>3.710853293730853</v>
       </c>
       <c r="D577" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E577">
         <v>4.733603965539871</v>
@@ -30274,7 +30280,7 @@
         <v>1</v>
       </c>
       <c r="P577" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="578" spans="1:16">
@@ -30288,7 +30294,7 @@
         <v>3.686751906570006</v>
       </c>
       <c r="D578" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E578">
         <v>4.733603965539871</v>
@@ -30324,7 +30330,7 @@
         <v>1</v>
       </c>
       <c r="P578" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="579" spans="1:16">
@@ -30374,7 +30380,7 @@
         <v>1</v>
       </c>
       <c r="P579" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="580" spans="1:16">
@@ -30424,7 +30430,7 @@
         <v>1</v>
       </c>
       <c r="P580" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="581" spans="1:16">
@@ -30474,7 +30480,7 @@
         <v>1</v>
       </c>
       <c r="P581" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="582" spans="1:16">
@@ -30524,7 +30530,7 @@
         <v>1</v>
       </c>
       <c r="P582" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="583" spans="1:16">
@@ -30574,7 +30580,7 @@
         <v>1</v>
       </c>
       <c r="P583" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="584" spans="1:16">
@@ -30624,7 +30630,7 @@
         <v>1</v>
       </c>
       <c r="P584" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="585" spans="1:16">
@@ -30674,7 +30680,7 @@
         <v>1</v>
       </c>
       <c r="P585" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="586" spans="1:16">
@@ -30724,7 +30730,7 @@
         <v>1</v>
       </c>
       <c r="P586" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="587" spans="1:16">
@@ -30774,7 +30780,7 @@
         <v>1</v>
       </c>
       <c r="P587" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="588" spans="1:16">
@@ -30824,7 +30830,7 @@
         <v>1</v>
       </c>
       <c r="P588" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="589" spans="1:16">
@@ -30874,7 +30880,7 @@
         <v>1</v>
       </c>
       <c r="P589" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="590" spans="1:16">
@@ -30924,7 +30930,7 @@
         <v>1</v>
       </c>
       <c r="P590" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="591" spans="1:16">
@@ -31174,7 +31180,7 @@
         <v>1</v>
       </c>
       <c r="P595" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="596" spans="1:16">
@@ -31224,7 +31230,7 @@
         <v>1</v>
       </c>
       <c r="P596" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="597" spans="1:16">
@@ -31274,7 +31280,7 @@
         <v>1</v>
       </c>
       <c r="P597" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="598" spans="1:16">
@@ -31324,7 +31330,7 @@
         <v>1</v>
       </c>
       <c r="P598" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="599" spans="1:16">
@@ -31374,7 +31380,7 @@
         <v>1</v>
       </c>
       <c r="P599" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="600" spans="1:16">
@@ -31424,7 +31430,7 @@
         <v>1</v>
       </c>
       <c r="P600" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="601" spans="1:16">
@@ -31638,7 +31644,7 @@
         <v>6.312844467716282</v>
       </c>
       <c r="D605" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E605">
         <v>7.044140001633426</v>
@@ -31724,7 +31730,7 @@
         <v>1</v>
       </c>
       <c r="P606" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="607" spans="1:16">
@@ -31774,7 +31780,7 @@
         <v>1</v>
       </c>
       <c r="P607" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="608" spans="1:16">
@@ -31824,7 +31830,7 @@
         <v>1</v>
       </c>
       <c r="P608" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="609" spans="1:16">
@@ -31874,7 +31880,7 @@
         <v>1</v>
       </c>
       <c r="P609" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="610" spans="1:16">
@@ -31924,7 +31930,7 @@
         <v>1</v>
       </c>
       <c r="P610" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="611" spans="1:16">
@@ -31974,7 +31980,7 @@
         <v>1</v>
       </c>
       <c r="P611" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="612" spans="1:16">
@@ -32024,7 +32030,7 @@
         <v>1</v>
       </c>
       <c r="P612" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="613" spans="1:16">
@@ -32074,7 +32080,7 @@
         <v>1</v>
       </c>
       <c r="P613" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="614" spans="1:16">
@@ -32124,7 +32130,7 @@
         <v>1</v>
       </c>
       <c r="P614" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="615" spans="1:16">
@@ -32174,7 +32180,7 @@
         <v>1</v>
       </c>
       <c r="P615" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="616" spans="1:16">
@@ -32224,7 +32230,7 @@
         <v>1</v>
       </c>
       <c r="P616" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="617" spans="1:16">
@@ -32274,7 +32280,7 @@
         <v>1</v>
       </c>
       <c r="P617" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="618" spans="1:16">
@@ -32324,7 +32330,7 @@
         <v>1</v>
       </c>
       <c r="P618" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="619" spans="1:16">
@@ -32374,7 +32380,7 @@
         <v>1</v>
       </c>
       <c r="P619" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="620" spans="1:16">
@@ -32424,7 +32430,7 @@
         <v>1</v>
       </c>
       <c r="P620" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="621" spans="1:16">
@@ -32474,7 +32480,7 @@
         <v>1</v>
       </c>
       <c r="P621" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="622" spans="1:16">
@@ -32488,7 +32494,7 @@
         <v>6.52789956231641</v>
       </c>
       <c r="D622" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E622">
         <v>6.970266187949232</v>
@@ -32524,7 +32530,7 @@
         <v>1</v>
       </c>
       <c r="P622" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="623" spans="1:16">
@@ -32574,7 +32580,7 @@
         <v>1</v>
       </c>
       <c r="P623" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="624" spans="1:16">
@@ -32624,7 +32630,7 @@
         <v>1</v>
       </c>
       <c r="P624" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="625" spans="1:16">
@@ -32674,7 +32680,7 @@
         <v>1</v>
       </c>
       <c r="P625" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="626" spans="1:16">
@@ -32688,7 +32694,7 @@
         <v>2.603543847706</v>
       </c>
       <c r="D626" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E626">
         <v>4.770094008155837</v>
@@ -32724,7 +32730,7 @@
         <v>1</v>
       </c>
       <c r="P626" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="627" spans="1:16">
@@ -32774,7 +32780,7 @@
         <v>1</v>
       </c>
       <c r="P627" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="628" spans="1:16">
@@ -32824,7 +32830,7 @@
         <v>1</v>
       </c>
       <c r="P628" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="629" spans="1:16">
@@ -32874,7 +32880,7 @@
         <v>1</v>
       </c>
       <c r="P629" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="630" spans="1:16">
@@ -32924,7 +32930,7 @@
         <v>1</v>
       </c>
       <c r="P630" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="631" spans="1:16">
@@ -32974,7 +32980,7 @@
         <v>1</v>
       </c>
       <c r="P631" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="632" spans="1:16">
@@ -32988,7 +32994,7 @@
         <v>2.478182256708074</v>
       </c>
       <c r="D632" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E632">
         <v>4.645810796435313</v>
@@ -33024,7 +33030,7 @@
         <v>1</v>
       </c>
       <c r="P632" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="633" spans="1:16">
@@ -33074,7 +33080,7 @@
         <v>1</v>
       </c>
       <c r="P633" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="634" spans="1:16">
@@ -33124,7 +33130,7 @@
         <v>1</v>
       </c>
       <c r="P634" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="635" spans="1:16">
@@ -33174,7 +33180,7 @@
         <v>1</v>
       </c>
       <c r="P635" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="636" spans="1:16">
@@ -33224,7 +33230,7 @@
         <v>1</v>
       </c>
       <c r="P636" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="637" spans="1:16">
@@ -33238,7 +33244,7 @@
         <v>2.30694018299906</v>
       </c>
       <c r="D637" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E637">
         <v>4.476041772822722</v>
@@ -33274,7 +33280,7 @@
         <v>1</v>
       </c>
       <c r="P637" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="638" spans="1:16">
@@ -33288,7 +33294,7 @@
         <v>5.979313720333828</v>
       </c>
       <c r="D638" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E638">
         <v>6.921637837986275</v>
@@ -33324,7 +33330,7 @@
         <v>1</v>
       </c>
       <c r="P638" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="639" spans="1:16">
@@ -33338,7 +33344,7 @@
         <v>6.118014825265853</v>
       </c>
       <c r="D639" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E639">
         <v>6.921637837986275</v>
@@ -33374,7 +33380,7 @@
         <v>1</v>
       </c>
       <c r="P639" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="640" spans="1:16">
@@ -33388,7 +33394,7 @@
         <v>2.180042495856011</v>
       </c>
       <c r="D640" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E640">
         <v>4.350235678687355</v>
@@ -33424,7 +33430,7 @@
         <v>1</v>
       </c>
       <c r="P640" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="641" spans="1:16">
@@ -33474,7 +33480,7 @@
         <v>1</v>
       </c>
       <c r="P641" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="642" spans="1:16">
@@ -33524,7 +33530,7 @@
         <v>1</v>
       </c>
       <c r="P642" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="643" spans="1:16">
@@ -33574,7 +33580,7 @@
         <v>1</v>
       </c>
       <c r="P643" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="644" spans="1:16">
@@ -33588,7 +33594,7 @@
         <v>2.005501953213372</v>
       </c>
       <c r="D644" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E644">
         <v>4.177196560067447</v>
@@ -33624,7 +33630,7 @@
         <v>1</v>
       </c>
       <c r="P644" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="645" spans="1:16">
@@ -33638,7 +33644,7 @@
         <v>6.03048720269387</v>
       </c>
       <c r="D645" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E645">
         <v>7.646218976894719</v>
@@ -33674,7 +33680,7 @@
         <v>1</v>
       </c>
       <c r="P645" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="646" spans="1:16">
@@ -33688,7 +33694,7 @@
         <v>6.160487202693869</v>
       </c>
       <c r="D646" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E646">
         <v>7.646218976894719</v>
@@ -33724,7 +33730,7 @@
         <v>1</v>
       </c>
       <c r="P646" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="647" spans="1:16">
@@ -33788,7 +33794,7 @@
         <v>5.929250610805834</v>
       </c>
       <c r="D648" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E648">
         <v>6.44678700451809</v>
@@ -33838,7 +33844,7 @@
         <v>6.059250610805833</v>
       </c>
       <c r="D649" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E649">
         <v>6.44678700451809</v>
@@ -33924,7 +33930,7 @@
         <v>1</v>
       </c>
       <c r="P650" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="651" spans="1:16">
@@ -33938,7 +33944,7 @@
         <v>6.444007644774246</v>
       </c>
       <c r="D651" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="E651">
         <v>5.9080963375586</v>
@@ -33974,7 +33980,7 @@
         <v>1</v>
       </c>
       <c r="P651" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="652" spans="1:16">
@@ -33988,7 +33994,7 @@
         <v>5.977845942063905</v>
       </c>
       <c r="D652" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="E652">
         <v>5.9080963375586</v>
@@ -34024,7 +34030,7 @@
         <v>1</v>
       </c>
       <c r="P652" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="653" spans="1:16">
@@ -34088,7 +34094,7 @@
         <v>6.325113724849238</v>
       </c>
       <c r="D654" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E654">
         <v>5.966484401224733</v>
@@ -34138,7 +34144,7 @@
         <v>6.616965483162407</v>
       </c>
       <c r="D655" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E655">
         <v>5.966484401224733</v>
@@ -34374,7 +34380,7 @@
         <v>1</v>
       </c>
       <c r="P659" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="660" spans="1:16">
@@ -34388,7 +34394,7 @@
         <v>6.182411935806901</v>
       </c>
       <c r="D660" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E660">
         <v>5.820555041914538</v>
@@ -34424,7 +34430,7 @@
         <v>1</v>
       </c>
       <c r="P660" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="661" spans="1:16">
@@ -34438,7 +34444,7 @@
         <v>6.479370608860847</v>
       </c>
       <c r="D661" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E661">
         <v>5.820555041914538</v>
@@ -34474,7 +34480,7 @@
         <v>1</v>
       </c>
       <c r="P661" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="662" spans="1:16">
@@ -34488,7 +34494,7 @@
         <v>6.247760471854665</v>
       </c>
       <c r="D662" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E662">
         <v>5.820555041914538</v>
@@ -34524,7 +34530,7 @@
         <v>1</v>
       </c>
       <c r="P662" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="663" spans="1:16">
@@ -34638,7 +34644,7 @@
         <v>6.052746661470383</v>
       </c>
       <c r="D665" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E665">
         <v>5.747828147206722</v>
@@ -34688,7 +34694,7 @@
         <v>6.354345707327784</v>
       </c>
       <c r="D666" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E666">
         <v>5.747828147206722</v>
@@ -34738,7 +34744,7 @@
         <v>6.106229101349317</v>
       </c>
       <c r="D667" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E667">
         <v>5.747828147206722</v>
@@ -34888,7 +34894,7 @@
         <v>5.992378168346487</v>
       </c>
       <c r="D670" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E670">
         <v>5.919638041522585</v>
@@ -34938,7 +34944,7 @@
         <v>6.296137640849427</v>
       </c>
       <c r="D671" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E671">
         <v>5.919638041522585</v>
@@ -34988,7 +34994,7 @@
         <v>6.0403360886604</v>
       </c>
       <c r="D672" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E672">
         <v>5.919638041522585</v>
@@ -35074,7 +35080,7 @@
         <v>1</v>
       </c>
       <c r="P673" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="674" spans="1:16">
@@ -35124,7 +35130,7 @@
         <v>1</v>
       </c>
       <c r="P674" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="675" spans="1:16">
@@ -35138,7 +35144,7 @@
         <v>5.931074248482098</v>
       </c>
       <c r="D675" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E675">
         <v>5.817063063996034</v>
@@ -35174,7 +35180,7 @@
         <v>1</v>
       </c>
       <c r="P675" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="676" spans="1:16">
@@ -35188,7 +35194,7 @@
         <v>6.237027624047666</v>
       </c>
       <c r="D676" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E676">
         <v>5.817063063996034</v>
@@ -35224,7 +35230,7 @@
         <v>1</v>
       </c>
       <c r="P676" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="677" spans="1:16">
@@ -35238,7 +35244,7 @@
         <v>5.973422045250139</v>
       </c>
       <c r="D677" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E677">
         <v>5.817063063996034</v>
@@ -35274,7 +35280,7 @@
         <v>1</v>
       </c>
       <c r="P677" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="678" spans="1:16">
@@ -35388,7 +35394,7 @@
         <v>5.839386641650073</v>
       </c>
       <c r="D680" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E680">
         <v>4.893781158276536</v>
@@ -35438,7 +35444,7 @@
         <v>6.148621271038877</v>
       </c>
       <c r="D681" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E681">
         <v>4.893781158276536</v>
@@ -35488,7 +35494,7 @@
         <v>5.873343803641564</v>
       </c>
       <c r="D682" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E682">
         <v>4.893781158276536</v>
@@ -35588,7 +35594,7 @@
         <v>6.049313264972337</v>
       </c>
       <c r="D684" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E684">
         <v>4.936335249131968</v>
@@ -35638,7 +35644,7 @@
         <v>6.175722584965069</v>
       </c>
       <c r="D685" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E685">
         <v>4.936335249131968</v>
@@ -35688,7 +35694,7 @@
         <v>5.760924613317037</v>
       </c>
       <c r="D686" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E686">
         <v>4.936335249131968</v>
@@ -35838,7 +35844,7 @@
         <v>5.905539797299475</v>
       </c>
       <c r="D689" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E689">
         <v>5.270502414665344</v>
@@ -35888,7 +35894,7 @@
         <v>6.021734035283636</v>
       </c>
       <c r="D690" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E690">
         <v>5.270502414665344</v>
@@ -36038,7 +36044,7 @@
         <v>5.810134805942958</v>
       </c>
       <c r="D693" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="E693">
         <v>4.46837075668304</v>
@@ -36088,7 +36094,7 @@
         <v>5.919550534467003</v>
       </c>
       <c r="D694" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="E694">
         <v>4.46837075668304</v>
@@ -36138,7 +36144,7 @@
         <v>5.597681787127293</v>
       </c>
       <c r="D695" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="E695">
         <v>5.175448484795162</v>
@@ -36188,7 +36194,7 @@
         <v>5.69200276245871</v>
       </c>
       <c r="D696" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="E696">
         <v>5.175448484795162</v>
@@ -36274,7 +36280,7 @@
         <v>1</v>
       </c>
       <c r="P697" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="698" spans="1:16">
@@ -36324,7 +36330,7 @@
         <v>1</v>
       </c>
       <c r="P698" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="699" spans="1:16">
@@ -36374,7 +36380,7 @@
         <v>1</v>
       </c>
       <c r="P699" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="700" spans="1:16">
@@ -36424,7 +36430,7 @@
         <v>1</v>
       </c>
       <c r="P700" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="701" spans="1:16">
@@ -36438,7 +36444,7 @@
         <v>10.58920111380781</v>
       </c>
       <c r="D701" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="E701">
         <v>10.63805069137965</v>
@@ -36474,7 +36480,7 @@
         <v>1</v>
       </c>
       <c r="P701" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="702" spans="1:16">
@@ -36524,7 +36530,7 @@
         <v>1</v>
       </c>
       <c r="P702" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="703" spans="1:16">
@@ -36538,7 +36544,7 @@
         <v>13.29070024337744</v>
       </c>
       <c r="D703" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E703">
         <v>12.1104855745369</v>
@@ -36574,7 +36580,7 @@
         <v>1</v>
       </c>
       <c r="P703" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="704" spans="1:16">
@@ -36624,7 +36630,7 @@
         <v>1</v>
       </c>
       <c r="P704" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="705" spans="1:16">
@@ -36638,7 +36644,7 @@
         <v>13.05967948318782</v>
       </c>
       <c r="D705" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E705">
         <v>11.87581437344135</v>
@@ -36674,7 +36680,7 @@
         <v>1</v>
       </c>
       <c r="P705" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="706" spans="1:16">
@@ -36724,7 +36730,7 @@
         <v>1</v>
       </c>
       <c r="P706" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="707" spans="1:16">
@@ -36738,7 +36744,7 @@
         <v>12.8170626988293</v>
       </c>
       <c r="D707" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E707">
         <v>10.97022453374666</v>
@@ -36774,7 +36780,7 @@
         <v>1</v>
       </c>
       <c r="P707" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="708" spans="1:16">
@@ -36824,7 +36830,7 @@
         <v>1</v>
       </c>
       <c r="P708" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="709" spans="1:16">
@@ -36838,7 +36844,7 @@
         <v>12.5987805539735</v>
       </c>
       <c r="D709" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E709">
         <v>10.73863851098768</v>
@@ -36874,7 +36880,7 @@
         <v>1</v>
       </c>
       <c r="P709" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="710" spans="1:16">
@@ -36924,7 +36930,7 @@
         <v>1</v>
       </c>
       <c r="P710" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="711" spans="1:16">
@@ -36974,7 +36980,7 @@
         <v>1</v>
       </c>
       <c r="P711" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="712" spans="1:16">
@@ -37024,7 +37030,7 @@
         <v>1</v>
       </c>
       <c r="P712" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="713" spans="1:16">
@@ -37038,7 +37044,7 @@
         <v>12.45336310880131</v>
       </c>
       <c r="D713" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E713">
         <v>10.58435815154991</v>
@@ -37074,7 +37080,7 @@
         <v>1</v>
       </c>
       <c r="P713" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="714" spans="1:16">
@@ -37124,7 +37130,7 @@
         <v>1</v>
       </c>
       <c r="P714" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="715" spans="1:16">
@@ -37174,7 +37180,7 @@
         <v>1</v>
       </c>
       <c r="P715" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="716" spans="1:16">
@@ -37224,7 +37230,7 @@
         <v>1</v>
       </c>
       <c r="P716" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="717" spans="1:16">
@@ -37274,7 +37280,7 @@
         <v>1</v>
       </c>
       <c r="P717" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="718" spans="1:16">
@@ -37324,7 +37330,7 @@
         <v>1</v>
       </c>
       <c r="P718" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="719" spans="1:16">
@@ -37374,7 +37380,7 @@
         <v>1</v>
       </c>
       <c r="P719" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="720" spans="1:16">
@@ -37388,7 +37394,7 @@
         <v>12.29210392935995</v>
       </c>
       <c r="D720" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E720">
         <v>10.41327053453538</v>
@@ -37424,7 +37430,7 @@
         <v>1</v>
       </c>
       <c r="P720" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="721" spans="1:16">
@@ -37438,7 +37444,7 @@
         <v>9.171282848330055</v>
       </c>
       <c r="D721" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E721">
         <v>6.850968108671186</v>
@@ -37474,7 +37480,7 @@
         <v>1</v>
       </c>
       <c r="P721" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="722" spans="1:16">
@@ -37488,7 +37494,7 @@
         <v>8.830116243154617</v>
       </c>
       <c r="D722" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E722">
         <v>6.850968108671186</v>
@@ -37524,7 +37530,7 @@
         <v>1</v>
       </c>
       <c r="P722" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="723" spans="1:16">
@@ -37688,7 +37694,7 @@
         <v>12.09795277153261</v>
       </c>
       <c r="D726" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E726">
         <v>10.20728623616326</v>
@@ -37738,7 +37744,7 @@
         <v>8.629829382822578</v>
       </c>
       <c r="D727" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E727">
         <v>7.040051561279032</v>
@@ -37824,7 +37830,7 @@
         <v>1</v>
       </c>
       <c r="P728" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="729" spans="1:16">
@@ -37874,7 +37880,7 @@
         <v>1</v>
       </c>
       <c r="P729" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="730" spans="1:16">
@@ -37924,7 +37930,7 @@
         <v>1</v>
       </c>
       <c r="P730" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="731" spans="1:16">
@@ -37938,7 +37944,7 @@
         <v>11.86477339723001</v>
       </c>
       <c r="D731" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E731">
         <v>9.95989502640656</v>
@@ -37974,7 +37980,7 @@
         <v>1</v>
       </c>
       <c r="P731" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="732" spans="1:16">
@@ -37988,7 +37994,7 @@
         <v>8.389280908654889</v>
       </c>
       <c r="D732" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="E732">
         <v>6.803093216210396</v>
@@ -38024,7 +38030,7 @@
         <v>1</v>
       </c>
       <c r="P732" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="733" spans="1:16">
@@ -38074,7 +38080,7 @@
         <v>1</v>
       </c>
       <c r="P733" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="734" spans="1:16">
@@ -38124,7 +38130,7 @@
         <v>1</v>
       </c>
       <c r="P734" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="735" spans="1:16">
@@ -38174,7 +38180,7 @@
         <v>1</v>
       </c>
       <c r="P735" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="736" spans="1:16">
@@ -38224,7 +38230,7 @@
         <v>1</v>
       </c>
       <c r="P736" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="737" spans="1:16">
@@ -38238,7 +38244,7 @@
         <v>7.721090409497048</v>
       </c>
       <c r="D737" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E737">
         <v>6.845979077114176</v>
@@ -38274,7 +38280,7 @@
         <v>1</v>
       </c>
       <c r="P737" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="738" spans="1:16">
@@ -38324,7 +38330,7 @@
         <v>1</v>
       </c>
       <c r="P738" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="739" spans="1:16">
@@ -38374,7 +38380,7 @@
         <v>1</v>
       </c>
       <c r="P739" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="740" spans="1:16">
@@ -38424,7 +38430,7 @@
         <v>1</v>
       </c>
       <c r="P740" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="741" spans="1:16">
@@ -38438,7 +38444,7 @@
         <v>7.431928747420816</v>
       </c>
       <c r="D741" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E741">
         <v>6.954602200047407</v>
@@ -38474,7 +38480,7 @@
         <v>1</v>
       </c>
       <c r="P741" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="742" spans="1:16">
@@ -38524,7 +38530,7 @@
         <v>1</v>
       </c>
       <c r="P742" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="743" spans="1:16">
@@ -38574,7 +38580,7 @@
         <v>1</v>
       </c>
       <c r="P743" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="744" spans="1:16">
@@ -38624,7 +38630,7 @@
         <v>1</v>
       </c>
       <c r="P744" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="745" spans="1:16">
@@ -38674,7 +38680,7 @@
         <v>1</v>
       </c>
       <c r="P745" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="746" spans="1:16">
@@ -38688,7 +38694,7 @@
         <v>7.15411432552343</v>
       </c>
       <c r="D746" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E746">
         <v>7.077702572180645</v>
@@ -38724,7 +38730,7 @@
         <v>1</v>
       </c>
       <c r="P746" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="747" spans="1:16">
@@ -38988,7 +38994,7 @@
         <v>6.656074286112602</v>
       </c>
       <c r="D752" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E752">
         <v>7.106777983579878</v>
@@ -39074,7 +39080,7 @@
         <v>1</v>
       </c>
       <c r="P753" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="754" spans="1:16">
@@ -39124,7 +39130,7 @@
         <v>1</v>
       </c>
       <c r="P754" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="755" spans="1:16">
@@ -39174,7 +39180,7 @@
         <v>1</v>
       </c>
       <c r="P755" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="756" spans="1:16">
@@ -39224,7 +39230,7 @@
         <v>1</v>
       </c>
       <c r="P756" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="757" spans="1:16">
@@ -39274,7 +39280,7 @@
         <v>1</v>
       </c>
       <c r="P757" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="758" spans="1:16">
@@ -39324,7 +39330,7 @@
         <v>1</v>
       </c>
       <c r="P758" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="759" spans="1:16">
@@ -39674,7 +39680,7 @@
         <v>1</v>
       </c>
       <c r="P765" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="766" spans="1:16">
@@ -39724,7 +39730,7 @@
         <v>1</v>
       </c>
       <c r="P766" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="767" spans="1:16">
@@ -39738,7 +39744,7 @@
         <v>5.189787984798581</v>
       </c>
       <c r="D767" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E767">
         <v>6.127393152460147</v>
@@ -39774,7 +39780,7 @@
         <v>1</v>
       </c>
       <c r="P767" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="768" spans="1:16">
@@ -39788,7 +39794,7 @@
         <v>5.337615079752425</v>
       </c>
       <c r="D768" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E768">
         <v>6.127393152460147</v>
@@ -39824,7 +39830,7 @@
         <v>1</v>
       </c>
       <c r="P768" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="769" spans="1:16">
@@ -39938,7 +39944,7 @@
         <v>4.573548410677798</v>
       </c>
       <c r="D771" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E771">
         <v>5.983161604764781</v>
@@ -39988,7 +39994,7 @@
         <v>4.718587091269107</v>
       </c>
       <c r="D772" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E772">
         <v>5.983161604764781</v>
@@ -40074,7 +40080,7 @@
         <v>1</v>
       </c>
       <c r="P773" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="774" spans="1:16">
@@ -40124,7 +40130,7 @@
         <v>1</v>
       </c>
       <c r="P774" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="775" spans="1:16">
@@ -40174,7 +40180,7 @@
         <v>1</v>
       </c>
       <c r="P775" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="776" spans="1:16">
@@ -40224,7 +40230,7 @@
         <v>1</v>
       </c>
       <c r="P776" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="777" spans="1:16">
@@ -40474,7 +40480,7 @@
         <v>1</v>
       </c>
       <c r="P781" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="782" spans="1:16">
@@ -40524,7 +40530,7 @@
         <v>1</v>
       </c>
       <c r="P782" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="783" spans="1:16">
@@ -40574,7 +40580,7 @@
         <v>1</v>
       </c>
       <c r="P783" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="784" spans="1:16">
@@ -40974,7 +40980,7 @@
         <v>1</v>
       </c>
       <c r="P791" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="792" spans="1:16">
@@ -41024,7 +41030,7 @@
         <v>1</v>
       </c>
       <c r="P792" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="793" spans="1:16">
@@ -41074,7 +41080,7 @@
         <v>1</v>
       </c>
       <c r="P793" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="794" spans="1:16">
@@ -41124,7 +41130,7 @@
         <v>1</v>
       </c>
       <c r="P794" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="795" spans="1:16">
@@ -41374,7 +41380,7 @@
         <v>1</v>
       </c>
       <c r="P799" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="800" spans="1:16">
@@ -41388,7 +41394,7 @@
         <v>1.03967143846625</v>
       </c>
       <c r="D800" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E800">
         <v>2.609188567947417</v>
@@ -41424,7 +41430,7 @@
         <v>1</v>
       </c>
       <c r="P800" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="801" spans="1:16">
@@ -41438,7 +41444,7 @@
         <v>0.8130094478294367</v>
       </c>
       <c r="D801" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E801">
         <v>2.609188567947417</v>
@@ -41474,7 +41480,7 @@
         <v>1</v>
       </c>
       <c r="P801" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="802" spans="1:16">
@@ -41524,7 +41530,7 @@
         <v>1</v>
       </c>
       <c r="P802" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="803" spans="1:16">
@@ -41538,7 +41544,7 @@
         <v>0.7465491084079581</v>
       </c>
       <c r="D803" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E803">
         <v>2.329329691737918</v>
@@ -41574,7 +41580,7 @@
         <v>1</v>
       </c>
       <c r="P803" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="804" spans="1:16">
@@ -41588,7 +41594,7 @@
         <v>0.5106027000769942</v>
       </c>
       <c r="D804" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E804">
         <v>2.329329691737918</v>
@@ -41624,7 +41630,7 @@
         <v>1</v>
       </c>
       <c r="P804" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="805" spans="1:16">
@@ -41638,7 +41644,7 @@
         <v>0.4893560218813207</v>
       </c>
       <c r="D805" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E805">
         <v>2.083774301434204</v>
@@ -41688,7 +41694,7 @@
         <v>0.2452632261943108</v>
       </c>
       <c r="D806" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E806">
         <v>2.083774301434204</v>
@@ -41738,7 +41744,7 @@
         <v>3.38720643044401</v>
       </c>
       <c r="D807" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E807">
         <v>1.346565161657761</v>
@@ -41788,7 +41794,7 @@
         <v>0.03330516332946587</v>
       </c>
       <c r="D808" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E808">
         <v>1.648359228337185</v>
@@ -41838,7 +41844,7 @@
         <v>-0.2252326821759354</v>
       </c>
       <c r="D809" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E809">
         <v>1.648359228337185</v>
@@ -41888,7 +41894,7 @@
         <v>2.979030594147371</v>
       </c>
       <c r="D810" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E810">
         <v>0.9008321958333205</v>
@@ -41938,7 +41944,7 @@
         <v>-0.3050434949915584</v>
       </c>
       <c r="D811" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E811">
         <v>1.325320464057839</v>
@@ -41974,7 +41980,7 @@
         <v>1</v>
       </c>
       <c r="P811" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="812" spans="1:16">
@@ -41988,7 +41994,7 @@
         <v>-0.5742982663261245</v>
       </c>
       <c r="D812" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E812">
         <v>1.325320464057839</v>
@@ -42024,7 +42030,7 @@
         <v>1</v>
       </c>
       <c r="P812" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="813" spans="1:16">
@@ -42038,7 +42044,7 @@
         <v>2.676200890003035</v>
       </c>
       <c r="D813" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E813">
         <v>0.570138484533139</v>
@@ -42074,7 +42080,7 @@
         <v>1</v>
       </c>
       <c r="P813" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="814" spans="1:16">
@@ -42088,7 +42094,7 @@
         <v>-1.542729235915701</v>
       </c>
       <c r="D814" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E814">
         <v>0.8740710626510406</v>
@@ -42138,7 +42144,7 @@
         <v>-1.06190425457612</v>
       </c>
       <c r="D815" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E815">
         <v>0.8740710626510406</v>
@@ -42188,7 +42194,7 @@
         <v>2.253181308968607</v>
       </c>
       <c r="D816" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E816">
         <v>0.1081959693489338</v>
@@ -42238,7 +42244,7 @@
         <v>-1.645106114375984</v>
       </c>
       <c r="D817" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E817">
         <v>0.7789101756240804</v>
@@ -42288,7 +42294,7 @@
         <v>-1.164732132500994</v>
       </c>
       <c r="D818" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E818">
         <v>0.7789101756240804</v>
@@ -42338,7 +42344,7 @@
         <v>1.705918320624114</v>
       </c>
       <c r="D819" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E819">
         <v>0.01078008499905536</v>
@@ -42388,7 +42394,7 @@
         <v>2.163973614874138</v>
       </c>
       <c r="D820" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E820">
         <v>0.01078008499905536</v>
@@ -42438,7 +42444,7 @@
         <v>2.083749225749141</v>
       </c>
       <c r="D821" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E821">
         <v>-0.02146380625091737</v>
@@ -42488,7 +42494,7 @@
         <v>-1.354990011712744</v>
       </c>
       <c r="D822" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E822">
         <v>1.048577566205335</v>
@@ -42538,7 +42544,7 @@
         <v>-0.8733379853326184</v>
       </c>
       <c r="D823" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E823">
         <v>1.048577566205335</v>
@@ -42588,7 +42594,7 @@
         <v>1.965361355164372</v>
       </c>
       <c r="D824" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E824">
         <v>0.2868376981059342</v>
@@ -42638,7 +42644,7 @@
         <v>2.41677081798775</v>
       </c>
       <c r="D825" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E825">
         <v>0.2868376981059342</v>
@@ -42688,7 +42694,7 @@
         <v>2.335779602159679</v>
       </c>
       <c r="D826" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E826">
         <v>0.246925539825213</v>
@@ -42738,7 +42744,7 @@
         <v>-1.093559587288276</v>
       </c>
       <c r="D827" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E827">
         <v>-1.564638644835625</v>
@@ -42788,7 +42794,7 @@
         <v>-1.266714738768137</v>
       </c>
       <c r="D828" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E828">
         <v>0.4727739583005963</v>
@@ -42824,7 +42830,7 @@
         <v>1</v>
       </c>
       <c r="P828" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="829" spans="1:16">
@@ -42838,7 +42844,7 @@
         <v>-0.7846738345336348</v>
       </c>
       <c r="D829" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E829">
         <v>0.5188966710041001</v>
@@ -42874,7 +42880,7 @@
         <v>1</v>
       </c>
       <c r="P829" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="830" spans="1:16">
@@ -42888,7 +42894,7 @@
         <v>2.044303559603822</v>
       </c>
       <c r="D830" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E830">
         <v>0.3708353146523429</v>
@@ -42924,7 +42930,7 @@
         <v>1</v>
       </c>
       <c r="P830" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="831" spans="1:16">
@@ -42938,7 +42944,7 @@
         <v>2.412466315043719</v>
       </c>
       <c r="D831" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E831">
         <v>0.3285898892453361</v>
@@ -42974,7 +42980,7 @@
         <v>1</v>
       </c>
       <c r="P831" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="832" spans="1:16">
@@ -42988,7 +42994,7 @@
         <v>-1.016717323262487</v>
       </c>
       <c r="D832" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E832">
         <v>-1.725082876878652</v>
@@ -43024,7 +43030,7 @@
         <v>1</v>
       </c>
       <c r="P832" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="833" spans="1:16">
@@ -43038,7 +43044,7 @@
         <v>-1.012419255686936</v>
       </c>
       <c r="D833" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E833">
         <v>0.7130663861460427</v>
@@ -43088,7 +43094,7 @@
         <v>2.271713176632382</v>
       </c>
       <c r="D834" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E834">
         <v>0.563841217205912</v>
@@ -43138,7 +43144,7 @@
         <v>2.633378514442889</v>
       </c>
       <c r="D835" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E835">
         <v>0.563841217205912</v>
@@ -43188,7 +43194,7 @@
         <v>-0.7953570260957719</v>
       </c>
       <c r="D836" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E836">
         <v>-0.6798364854873604</v>
@@ -43238,7 +43244,7 @@
         <v>-1.154980882524804</v>
       </c>
       <c r="D837" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E837">
         <v>0.3632888214250194</v>
@@ -43274,7 +43280,7 @@
         <v>1</v>
       </c>
       <c r="P837" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="838" spans="1:16">
@@ -43288,7 +43294,7 @@
         <v>2.144224144702488</v>
       </c>
       <c r="D838" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="E838">
         <v>0.3406232020973725</v>
@@ -43324,7 +43330,7 @@
         <v>1</v>
       </c>
       <c r="P838" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="839" spans="1:16">
@@ -43338,7 +43344,7 @@
         <v>2.509532026282422</v>
       </c>
       <c r="D839" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="E839">
         <v>0.3406232020973725</v>
@@ -43374,7 +43380,7 @@
         <v>1</v>
       </c>
       <c r="P839" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="840" spans="1:16">
@@ -43424,7 +43430,7 @@
         <v>1</v>
       </c>
       <c r="P840" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="841" spans="1:16">
@@ -43438,7 +43444,7 @@
         <v>-0.7435135480053319</v>
       </c>
       <c r="D841" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E841">
         <v>0.7484730002152737</v>
@@ -43588,7 +43594,7 @@
         <v>-0.3742444036399846</v>
       </c>
       <c r="D844" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E844">
         <v>1.094154467958163</v>
@@ -43624,7 +43630,7 @@
         <v>1</v>
       </c>
       <c r="P844" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="845" spans="1:16">
@@ -43674,7 +43680,7 @@
         <v>1</v>
       </c>
       <c r="P845" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="846" spans="1:16">
@@ -43724,7 +43730,7 @@
         <v>1</v>
       </c>
       <c r="P846" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="847" spans="1:16">
@@ -43738,7 +43744,7 @@
         <v>-0.2301600625778306</v>
       </c>
       <c r="D847" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E847">
         <v>1.229035183710177</v>
@@ -43774,7 +43780,7 @@
         <v>1</v>
       </c>
       <c r="P847" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="848" spans="1:16">
@@ -43824,7 +43830,7 @@
         <v>1</v>
       </c>
       <c r="P848" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="849" spans="1:16">
@@ -43874,7 +43880,7 @@
         <v>1</v>
       </c>
       <c r="P849" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="850" spans="1:16">
@@ -43888,7 +43894,7 @@
         <v>-0.008911774850371756</v>
       </c>
       <c r="D850" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="E850">
         <v>0.5721947646345491</v>
@@ -43924,7 +43930,7 @@
         <v>1</v>
       </c>
       <c r="P850" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="851" spans="1:16">
@@ -43938,7 +43944,7 @@
         <v>-0.1112036199752922</v>
       </c>
       <c r="D851" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E851">
         <v>1.340393087027532</v>
@@ -44088,7 +44094,7 @@
         <v>0.09903988671845454</v>
       </c>
       <c r="D854" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E854">
         <v>1.106317252320714</v>
@@ -44138,7 +44144,7 @@
         <v>-0.06944114310240224</v>
       </c>
       <c r="D855" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E855">
         <v>1.379487916699293</v>
@@ -44174,7 +44180,7 @@
         <v>1</v>
       </c>
       <c r="P855" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="856" spans="1:16">
@@ -44224,7 +44230,7 @@
         <v>1</v>
       </c>
       <c r="P856" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="857" spans="1:16">
@@ -44274,7 +44280,7 @@
         <v>1</v>
       </c>
       <c r="P857" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="858" spans="1:16">
@@ -44288,7 +44294,7 @@
         <v>0.1369388745414319</v>
       </c>
       <c r="D858" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E858">
         <v>1.371101739245933</v>
@@ -44324,7 +44330,7 @@
         <v>1</v>
       </c>
       <c r="P858" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="859" spans="1:16">
@@ -44338,7 +44344,7 @@
         <v>12.65888206048432</v>
       </c>
       <c r="D859" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="E859">
         <v>13.67315026490144</v>
@@ -44374,7 +44380,7 @@
         <v>1</v>
       </c>
       <c r="P859" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="860" spans="1:16">
@@ -44388,10 +44394,10 @@
         <v>15.13291000897221</v>
       </c>
       <c r="D860" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E860">
-        <v>14.93509436792566</v>
+        <v>14.41567539327389</v>
       </c>
       <c r="F860">
         <v>-1</v>
@@ -44400,10 +44406,10 @@
         <v>0.05132708999102778</v>
       </c>
       <c r="H860">
-        <v>0.05104490563207434</v>
+        <v>0.04934432460672612</v>
       </c>
       <c r="I860">
-        <v>0.1978156410465495</v>
+        <v>0.7172346156983274</v>
       </c>
       <c r="J860">
         <v>0.8436871790688943</v>
@@ -44415,16 +44421,16 @@
         <v>33.23</v>
       </c>
       <c r="M860">
-        <v>21.4</v>
+        <v>20.7</v>
       </c>
       <c r="N860">
-        <v>32.99</v>
+        <v>31.88</v>
       </c>
       <c r="O860">
         <v>1</v>
       </c>
       <c r="P860" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="861" spans="1:16">
@@ -44438,7 +44444,7 @@
         <v>12.57849638595733</v>
       </c>
       <c r="D861" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="E861">
         <v>13.59897621067881</v>
@@ -44474,7 +44480,7 @@
         <v>1</v>
       </c>
       <c r="P861" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="862" spans="1:16">
@@ -44488,10 +44494,10 @@
         <v>15.0545339763084</v>
       </c>
       <c r="D862" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E862">
-        <v>14.85690102997668</v>
+        <v>14.34003978133258</v>
       </c>
       <c r="F862">
         <v>-1</v>
@@ -44500,10 +44506,10 @@
         <v>0.0514054660236916</v>
       </c>
       <c r="H862">
-        <v>0.05112309897002332</v>
+        <v>0.04941996021866742</v>
       </c>
       <c r="I862">
-        <v>0.1976329463317157</v>
+        <v>0.714494194975817</v>
       </c>
       <c r="J862">
         <v>0.8473410733655758</v>
@@ -44515,16 +44521,16 @@
         <v>33.23</v>
       </c>
       <c r="M862">
-        <v>21.4</v>
+        <v>20.7</v>
       </c>
       <c r="N862">
-        <v>32.99</v>
+        <v>31.88</v>
       </c>
       <c r="O862">
         <v>1</v>
       </c>
       <c r="P862" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="863" spans="1:16">
@@ -44538,7 +44544,7 @@
         <v>12.51871891898833</v>
       </c>
       <c r="D863" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="E863">
         <v>13.54381791161196</v>
@@ -44574,7 +44580,7 @@
         <v>1</v>
       </c>
       <c r="P863" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="864" spans="1:16">
@@ -44588,10 +44594,10 @@
         <v>14.99625094601362</v>
       </c>
       <c r="D864" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E864">
-        <v>14.79875385756138</v>
+        <v>14.28379461922993</v>
       </c>
       <c r="F864">
         <v>-1</v>
@@ -44600,10 +44606,10 @@
         <v>0.05146374905398637</v>
       </c>
       <c r="H864">
-        <v>0.05118124614243862</v>
+        <v>0.04947620538077007</v>
       </c>
       <c r="I864">
-        <v>0.1974970884522413</v>
+        <v>0.7124563267836912</v>
       </c>
       <c r="J864">
         <v>0.8500582309550758</v>
@@ -44615,16 +44621,16 @@
         <v>33.23</v>
       </c>
       <c r="M864">
-        <v>21.4</v>
+        <v>20.7</v>
       </c>
       <c r="N864">
-        <v>32.99</v>
+        <v>31.88</v>
       </c>
       <c r="O864">
         <v>1</v>
       </c>
       <c r="P864" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="865" spans="1:16">
@@ -44638,10 +44644,10 @@
         <v>14.9624405975191</v>
       </c>
       <c r="D865" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E865">
-        <v>14.76502232106801</v>
+        <v>14.2511664507527</v>
       </c>
       <c r="F865">
         <v>-1</v>
@@ -44650,10 +44656,10 @@
         <v>0.05149755940248089</v>
       </c>
       <c r="H865">
-        <v>0.05121497767893199</v>
+        <v>0.0495088335492473</v>
       </c>
       <c r="I865">
-        <v>0.1974182764510886</v>
+        <v>0.7112741467663994</v>
       </c>
       <c r="J865">
         <v>0.8516344709781304</v>
@@ -44665,10 +44671,10 @@
         <v>33.23</v>
       </c>
       <c r="M865">
-        <v>21.4</v>
+        <v>20.7</v>
       </c>
       <c r="N865">
-        <v>32.99</v>
+        <v>31.88</v>
       </c>
       <c r="O865">
         <v>1</v>
@@ -44682,49 +44688,99 @@
         <v>0</v>
       </c>
       <c r="B866" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C866">
-        <v>14.8812849270668</v>
+        <v>12.74453569833766</v>
       </c>
       <c r="D866" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="E866">
-        <v>14.68405582467271</v>
+        <v>13.6867028791849</v>
       </c>
       <c r="F866">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G866">
-        <v>0.05157871507293319</v>
+        <v>0.04841546430166234</v>
       </c>
       <c r="H866">
-        <v>0.05129594417532729</v>
+        <v>0.0486732971208151</v>
       </c>
       <c r="I866">
-        <v>0.1972291023940898</v>
+        <v>0.9421671808472425</v>
       </c>
       <c r="J866">
         <v>0.8554179521180978</v>
       </c>
       <c r="K866">
+        <v>20.85</v>
+      </c>
+      <c r="L866">
+        <v>30.58</v>
+      </c>
+      <c r="M866">
+        <v>20.45</v>
+      </c>
+      <c r="N866">
+        <v>31.18</v>
+      </c>
+      <c r="O866">
+        <v>1</v>
+      </c>
+      <c r="P866" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="867" spans="1:16">
+      <c r="A867" s="1">
+        <v>1</v>
+      </c>
+      <c r="B867" t="s">
+        <v>155</v>
+      </c>
+      <c r="C867">
+        <v>14.8812849270668</v>
+      </c>
+      <c r="D867" t="s">
+        <v>268</v>
+      </c>
+      <c r="E867">
+        <v>14.17284839115538</v>
+      </c>
+      <c r="F867">
+        <v>-1</v>
+      </c>
+      <c r="G867">
+        <v>0.05157871507293319</v>
+      </c>
+      <c r="H867">
+        <v>0.04958715160884462</v>
+      </c>
+      <c r="I867">
+        <v>0.7084365359114244</v>
+      </c>
+      <c r="J867">
+        <v>0.8554179521180978</v>
+      </c>
+      <c r="K867">
         <v>21.45</v>
       </c>
-      <c r="L866">
+      <c r="L867">
         <v>33.23</v>
       </c>
-      <c r="M866">
-        <v>21.4</v>
-      </c>
-      <c r="N866">
-        <v>32.99</v>
-      </c>
-      <c r="O866">
-        <v>1</v>
-      </c>
-      <c r="P866" t="s">
-        <v>351</v>
+      <c r="M867">
+        <v>20.7</v>
+      </c>
+      <c r="N867">
+        <v>31.88</v>
+      </c>
+      <c r="O867">
+        <v>1</v>
+      </c>
+      <c r="P867" t="s">
+        <v>353</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-00763-000063.xlsx
+++ b/s60_signal/position-00763-000063.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2613" uniqueCount="354">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2637" uniqueCount="354">
   <si>
     <t>trade_time</t>
   </si>
@@ -478,13 +478,16 @@
     <t>2021-03-19</t>
   </si>
   <si>
-    <t>2021-11-26</t>
+    <t>2021-11-25</t>
   </si>
   <si>
     <t>2021-12-15</t>
   </si>
   <si>
-    <t>2021-12-02</t>
+    <t>2021-12-23</t>
+  </si>
+  <si>
+    <t>2021-12-28</t>
   </si>
   <si>
     <t>2017-03-17</t>
@@ -817,13 +820,10 @@
     <t>2021-03-26</t>
   </si>
   <si>
-    <t>2021-12-06</t>
+    <t>2021-12-08</t>
   </si>
   <si>
-    <t>2021-12-20</t>
-  </si>
-  <si>
-    <t>2021-12-08</t>
+    <t>2021-12-29</t>
   </si>
   <si>
     <t>2017-02-08</t>
@@ -1072,7 +1072,7 @@
     <t>2021-11-24</t>
   </si>
   <si>
-    <t>2021-11-25</t>
+    <t>2021-11-26</t>
   </si>
   <si>
     <t>2021-11-29</t>
@@ -1433,7 +1433,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P867"/>
+  <dimension ref="A1:P875"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -1494,7 +1494,7 @@
         <v>8.357775317423281</v>
       </c>
       <c r="D2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E2">
         <v>9.239078272099615</v>
@@ -1544,7 +1544,7 @@
         <v>9.433191964550923</v>
       </c>
       <c r="D3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E3">
         <v>9.285575452539577</v>
@@ -1594,7 +1594,7 @@
         <v>9.420218808988363</v>
       </c>
       <c r="D4" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E4">
         <v>9.285575452539577</v>
@@ -1644,7 +1644,7 @@
         <v>9.27302954676334</v>
       </c>
       <c r="D5" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E5">
         <v>9.285575452539577</v>
@@ -1694,7 +1694,7 @@
         <v>8.163141562328137</v>
       </c>
       <c r="D6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E6">
         <v>8.870417830135191</v>
@@ -1744,7 +1744,7 @@
         <v>8.167981542028786</v>
       </c>
       <c r="D7" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E7">
         <v>8.870417830135191</v>
@@ -1794,7 +1794,7 @@
         <v>9.039124544167011</v>
       </c>
       <c r="D8" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E8">
         <v>9.113918803782131</v>
@@ -1844,7 +1844,7 @@
         <v>9.052076876787602</v>
       </c>
       <c r="D9" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E9">
         <v>9.113918803782131</v>
@@ -1894,7 +1894,7 @@
         <v>8.972076876787604</v>
       </c>
       <c r="D10" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E10">
         <v>9.113918803782131</v>
@@ -1944,7 +1944,7 @@
         <v>1.247895028504875</v>
       </c>
       <c r="D11" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E11">
         <v>5.93332434483856</v>
@@ -1994,7 +1994,7 @@
         <v>2.464515501370315</v>
       </c>
       <c r="D12" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E12">
         <v>5.93332434483856</v>
@@ -2094,7 +2094,7 @@
         <v>1.224092499726471</v>
       </c>
       <c r="D14" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E14">
         <v>5.913320521841428</v>
@@ -2144,7 +2144,7 @@
         <v>2.442814384300704</v>
       </c>
       <c r="D15" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E15">
         <v>5.913320521841428</v>
@@ -2194,7 +2194,7 @@
         <v>8.399951396166678</v>
       </c>
       <c r="D16" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E16">
         <v>7.154665097353277</v>
@@ -2244,7 +2244,7 @@
         <v>1.231818368992485</v>
       </c>
       <c r="D17" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E17">
         <v>5.919813400087062</v>
@@ -2294,7 +2294,7 @@
         <v>2.449858173427781</v>
       </c>
       <c r="D18" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E18">
         <v>5.919813400087062</v>
@@ -2394,7 +2394,7 @@
         <v>1.145797529921555</v>
       </c>
       <c r="D20" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E20">
         <v>5.847520844331356</v>
@@ -2444,7 +2444,7 @@
         <v>2.37143170385038</v>
       </c>
       <c r="D21" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E21">
         <v>5.847520844331356</v>
@@ -2494,7 +2494,7 @@
         <v>8.323251570058975</v>
       </c>
       <c r="D22" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E22">
         <v>6.49770468378167</v>
@@ -2544,7 +2544,7 @@
         <v>8.298928068060523</v>
       </c>
       <c r="D23" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E23">
         <v>6.513844529583032</v>
@@ -2694,7 +2694,7 @@
         <v>4.521898732172186</v>
       </c>
       <c r="D26" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E26">
         <v>7.471272137184702</v>
@@ -2844,7 +2844,7 @@
         <v>10.06347633639325</v>
       </c>
       <c r="D29" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E29">
         <v>8.926863738767604</v>
@@ -3044,7 +3044,7 @@
         <v>10.57243502356749</v>
       </c>
       <c r="D33" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E33">
         <v>11.2289160904059</v>
@@ -3094,7 +3094,7 @@
         <v>10.58025171866791</v>
       </c>
       <c r="D34" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E34">
         <v>11.2289160904059</v>
@@ -3144,7 +3144,7 @@
         <v>6.89098969886382</v>
       </c>
       <c r="D35" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E35">
         <v>9.162922766970905</v>
@@ -3344,7 +3344,7 @@
         <v>10.57710841036202</v>
       </c>
       <c r="D39" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E39">
         <v>10.91875227586742</v>
@@ -3394,7 +3394,7 @@
         <v>10.58544939256899</v>
       </c>
       <c r="D40" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E40">
         <v>10.91875227586742</v>
@@ -3594,7 +3594,7 @@
         <v>10.50706987192051</v>
       </c>
       <c r="D44" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E44">
         <v>9.836117792760128</v>
@@ -3794,7 +3794,7 @@
         <v>11.00643298606593</v>
       </c>
       <c r="D48" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E48">
         <v>10.08970532444388</v>
@@ -4144,7 +4144,7 @@
         <v>10.96451987407661</v>
       </c>
       <c r="D55" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E55">
         <v>9.918825279734797</v>
@@ -4230,7 +4230,7 @@
         <v>1</v>
       </c>
       <c r="P56" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="57" spans="1:16">
@@ -4280,7 +4280,7 @@
         <v>1</v>
       </c>
       <c r="P57" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="58" spans="1:16">
@@ -4330,7 +4330,7 @@
         <v>1</v>
       </c>
       <c r="P58" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="59" spans="1:16">
@@ -4380,7 +4380,7 @@
         <v>1</v>
       </c>
       <c r="P59" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="60" spans="1:16">
@@ -4430,7 +4430,7 @@
         <v>1</v>
       </c>
       <c r="P60" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="61" spans="1:16">
@@ -4480,7 +4480,7 @@
         <v>1</v>
       </c>
       <c r="P61" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="62" spans="1:16">
@@ -4544,7 +4544,7 @@
         <v>10.70295290100141</v>
       </c>
       <c r="D63" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E63">
         <v>8.905400692050126</v>
@@ -4594,7 +4594,7 @@
         <v>11.20304517915771</v>
       </c>
       <c r="D64" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E64">
         <v>8.905400692050126</v>
@@ -4694,7 +4694,7 @@
         <v>10.69564352718713</v>
       </c>
       <c r="D66" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E66">
         <v>10.68408451836947</v>
@@ -4744,7 +4744,7 @@
         <v>11.03068966626528</v>
       </c>
       <c r="D67" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E67">
         <v>10.68408451836947</v>
@@ -4844,7 +4844,7 @@
         <v>10.52605158161457</v>
       </c>
       <c r="D69" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E69">
         <v>8.71498607743235</v>
@@ -4894,7 +4894,7 @@
         <v>11.02061569354003</v>
       </c>
       <c r="D70" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E70">
         <v>8.71498607743235</v>
@@ -4994,7 +4994,7 @@
         <v>10.52396325368498</v>
       </c>
       <c r="D72" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E72">
         <v>8.806051581614568</v>
@@ -5044,7 +5044,7 @@
         <v>10.8562453096477</v>
       </c>
       <c r="D73" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E73">
         <v>8.806051581614568</v>
@@ -5094,7 +5094,7 @@
         <v>10.34525014922946</v>
       </c>
       <c r="D74" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E74">
         <v>8.520373424517821</v>
@@ -5144,7 +5144,7 @@
         <v>10.83416421639288</v>
       </c>
       <c r="D75" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E75">
         <v>8.520373424517821</v>
@@ -5294,7 +5294,7 @@
         <v>10.34849797468624</v>
       </c>
       <c r="D78" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E78">
         <v>8.625250149229462</v>
@@ -5344,7 +5344,7 @@
         <v>10.67795500826794</v>
       </c>
       <c r="D79" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E79">
         <v>8.625250149229462</v>
@@ -5394,7 +5394,7 @@
         <v>10.18864383981015</v>
       </c>
       <c r="D80" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E80">
         <v>8.351804133128983</v>
@@ -5430,7 +5430,7 @@
         <v>1</v>
       </c>
       <c r="P80" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="81" spans="1:16">
@@ -5444,7 +5444,7 @@
         <v>10.67266395980422</v>
       </c>
       <c r="D81" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E81">
         <v>8.351804133128983</v>
@@ -5480,7 +5480,7 @@
         <v>1</v>
       </c>
       <c r="P81" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="82" spans="1:16">
@@ -5530,7 +5530,7 @@
         <v>1</v>
       </c>
       <c r="P82" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="83" spans="1:16">
@@ -5580,7 +5580,7 @@
         <v>1</v>
       </c>
       <c r="P83" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="84" spans="1:16">
@@ -5594,7 +5594,7 @@
         <v>10.19651372648243</v>
       </c>
       <c r="D84" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E84">
         <v>8.468643839810152</v>
@@ -5630,7 +5630,7 @@
         <v>1</v>
       </c>
       <c r="P84" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="85" spans="1:16">
@@ -5644,7 +5644,7 @@
         <v>10.52352378647946</v>
       </c>
       <c r="D85" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E85">
         <v>8.468643839810152</v>
@@ -5680,7 +5680,7 @@
         <v>1</v>
       </c>
       <c r="P85" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="86" spans="1:16">
@@ -5694,7 +5694,7 @@
         <v>-1.278554542763944</v>
       </c>
       <c r="D86" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E86">
         <v>0.01420169243589342</v>
@@ -5744,7 +5744,7 @@
         <v>-2.406586639852707</v>
       </c>
       <c r="D87" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E87">
         <v>0.01420169243589342</v>
@@ -5844,7 +5844,7 @@
         <v>-1.341212522415489</v>
       </c>
       <c r="D89" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E89">
         <v>0.1246199151405953</v>
@@ -5894,7 +5894,7 @@
         <v>-2.475362406493851</v>
       </c>
       <c r="D90" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E90">
         <v>0.1246199151405953</v>
@@ -5994,7 +5994,7 @@
         <v>-2.566016320350375</v>
       </c>
       <c r="D92" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E92">
         <v>0.02954385914472724</v>
@@ -6144,7 +6144,7 @@
         <v>-2.663355023194697</v>
       </c>
       <c r="D95" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E95">
         <v>0.03872013419191234</v>
@@ -6294,7 +6294,7 @@
         <v>-2.748103967913549</v>
       </c>
       <c r="D98" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E98">
         <v>-0.04760949385741853</v>
@@ -6344,7 +6344,7 @@
         <v>1.170412609918055</v>
       </c>
       <c r="D99" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E99">
         <v>1.469846093587645</v>
@@ -6394,7 +6394,7 @@
         <v>1.197090465141786</v>
       </c>
       <c r="D100" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E100">
         <v>1.469846093587645</v>
@@ -6444,7 +6444,7 @@
         <v>-2.807295369205091</v>
       </c>
       <c r="D101" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E101">
         <v>0.3363998775430197</v>
@@ -6644,7 +6644,7 @@
         <v>1.819034812951433</v>
       </c>
       <c r="D105" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E105">
         <v>1.780382458905816</v>
@@ -6694,7 +6694,7 @@
         <v>1.278232359359254</v>
       </c>
       <c r="D106" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E106">
         <v>1.780382458905816</v>
@@ -6744,7 +6744,7 @@
         <v>-1.27500579580901</v>
       </c>
       <c r="D107" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E107">
         <v>0.204597470791132</v>
@@ -6794,7 +6794,7 @@
         <v>-1.164182632644362</v>
       </c>
       <c r="D108" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E108">
         <v>0.204597470791132</v>
@@ -6944,7 +6944,7 @@
         <v>-1.330656541117063</v>
       </c>
       <c r="D111" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E111">
         <v>0.1498300706466971</v>
@@ -6994,7 +6994,7 @@
         <v>-1.089957636312631</v>
       </c>
       <c r="D112" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E112">
         <v>0.1498300706466971</v>
@@ -7044,7 +7044,7 @@
         <v>1.663161219313913</v>
       </c>
       <c r="D113" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E113">
         <v>1.394552474924428</v>
@@ -7094,7 +7094,7 @@
         <v>2.020453841772007</v>
       </c>
       <c r="D114" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E114">
         <v>1.394552474924428</v>
@@ -7430,7 +7430,7 @@
         <v>1</v>
       </c>
       <c r="P120" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="121" spans="1:16">
@@ -7480,7 +7480,7 @@
         <v>1</v>
       </c>
       <c r="P121" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="122" spans="1:16">
@@ -7530,7 +7530,7 @@
         <v>1</v>
       </c>
       <c r="P122" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="123" spans="1:16">
@@ -7580,7 +7580,7 @@
         <v>1</v>
       </c>
       <c r="P123" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="124" spans="1:16">
@@ -7630,7 +7630,7 @@
         <v>1</v>
       </c>
       <c r="P124" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="125" spans="1:16">
@@ -7744,7 +7744,7 @@
         <v>1.583716178161136</v>
       </c>
       <c r="D127" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E127">
         <v>1.731188504841963</v>
@@ -7794,7 +7794,7 @@
         <v>1.943294205912665</v>
       </c>
       <c r="D128" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E128">
         <v>1.731188504841963</v>
@@ -7844,7 +7844,7 @@
         <v>1.440029121201585</v>
       </c>
       <c r="D129" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E129">
         <v>1.731188504841963</v>
@@ -7930,7 +7930,7 @@
         <v>1</v>
       </c>
       <c r="P130" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="131" spans="1:16">
@@ -7980,7 +7980,7 @@
         <v>1</v>
       </c>
       <c r="P131" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="132" spans="1:16">
@@ -8030,7 +8030,7 @@
         <v>1</v>
       </c>
       <c r="P132" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="133" spans="1:16">
@@ -8080,7 +8080,7 @@
         <v>1</v>
       </c>
       <c r="P133" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="134" spans="1:16">
@@ -8130,7 +8130,7 @@
         <v>1</v>
       </c>
       <c r="P134" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="135" spans="1:16">
@@ -8144,7 +8144,7 @@
         <v>-0.8820242128746258</v>
       </c>
       <c r="D135" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E135">
         <v>0.3526024044326252</v>
@@ -8180,7 +8180,7 @@
         <v>1</v>
       </c>
       <c r="P135" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="136" spans="1:16">
@@ -8194,7 +8194,7 @@
         <v>-1.173427909927172</v>
       </c>
       <c r="D136" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E136">
         <v>0.3526024044326252</v>
@@ -8230,7 +8230,7 @@
         <v>1</v>
       </c>
       <c r="P136" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="137" spans="1:16">
@@ -8280,7 +8280,7 @@
         <v>1</v>
       </c>
       <c r="P137" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="138" spans="1:16">
@@ -8330,7 +8330,7 @@
         <v>1</v>
       </c>
       <c r="P138" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="139" spans="1:16">
@@ -8380,7 +8380,7 @@
         <v>1</v>
       </c>
       <c r="P139" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="140" spans="1:16">
@@ -8694,7 +8694,7 @@
         <v>1.916709703800588</v>
       </c>
       <c r="D146" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E146">
         <v>1.625228926806798</v>
@@ -8744,7 +8744,7 @@
         <v>1.775844332123576</v>
       </c>
       <c r="D147" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E147">
         <v>1.625228926806798</v>
@@ -8794,7 +8794,7 @@
         <v>1.706459737440355</v>
       </c>
       <c r="D148" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E148">
         <v>1.625228926806798</v>
@@ -8844,7 +8844,7 @@
         <v>1.898407474064776</v>
       </c>
       <c r="D149" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E149">
         <v>1.579058157468399</v>
@@ -8894,7 +8894,7 @@
         <v>1.757671173119327</v>
       </c>
       <c r="D150" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E150">
         <v>1.579058157468399</v>
@@ -8944,7 +8944,7 @@
         <v>1.688493091606606</v>
       </c>
       <c r="D151" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E151">
         <v>1.579058157468399</v>
@@ -9594,7 +9594,7 @@
         <v>2.0418888555804</v>
       </c>
       <c r="D164" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E164">
         <v>2.091052252009925</v>
@@ -9644,7 +9644,7 @@
         <v>2.437529947263654</v>
       </c>
       <c r="D165" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E165">
         <v>2.091052252009925</v>
@@ -9694,7 +9694,7 @@
         <v>2.035427646090795</v>
       </c>
       <c r="D166" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E166">
         <v>1.677256780401082</v>
@@ -9744,7 +9744,7 @@
         <v>2.4319519246827</v>
       </c>
       <c r="D167" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E167">
         <v>1.677256780401082</v>
@@ -9930,7 +9930,7 @@
         <v>1</v>
       </c>
       <c r="P170" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="171" spans="1:16">
@@ -9980,7 +9980,7 @@
         <v>1</v>
       </c>
       <c r="P171" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="172" spans="1:16">
@@ -10030,7 +10030,7 @@
         <v>1</v>
       </c>
       <c r="P172" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="173" spans="1:16">
@@ -10044,7 +10044,7 @@
         <v>2.053037839433713</v>
       </c>
       <c r="D173" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E173">
         <v>2.029053723158555</v>
@@ -10080,7 +10080,7 @@
         <v>1</v>
       </c>
       <c r="P173" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="174" spans="1:16">
@@ -10194,7 +10194,7 @@
         <v>2.072439051471395</v>
       </c>
       <c r="D176" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E176">
         <v>2.198537473651809</v>
@@ -10230,7 +10230,7 @@
         <v>1</v>
       </c>
       <c r="P176" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="177" spans="1:16">
@@ -10244,7 +10244,7 @@
         <v>2.176038435736924</v>
       </c>
       <c r="D177" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E177">
         <v>2.198537473651809</v>
@@ -10280,7 +10280,7 @@
         <v>1</v>
       </c>
       <c r="P177" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="178" spans="1:16">
@@ -10394,7 +10394,7 @@
         <v>2.199572666349018</v>
       </c>
       <c r="D180" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E180">
         <v>2.369622868222606</v>
@@ -10594,7 +10594,7 @@
         <v>2.441204477380014</v>
       </c>
       <c r="D184" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E184">
         <v>3.019740173907834</v>
@@ -10694,7 +10694,7 @@
         <v>2.450942264059425</v>
       </c>
       <c r="D186" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E186">
         <v>3.396065694761221</v>
@@ -10744,7 +10744,7 @@
         <v>2.93271297523739</v>
       </c>
       <c r="D187" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E187">
         <v>3.396065694761221</v>
@@ -10844,7 +10844,7 @@
         <v>2.613291041571109</v>
       </c>
       <c r="D189" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E189">
         <v>1.747095958240026</v>
@@ -10894,7 +10894,7 @@
         <v>2.94332933323569</v>
       </c>
       <c r="D190" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E190">
         <v>3.513960124909904</v>
@@ -11044,7 +11044,7 @@
         <v>2.630002520413537</v>
       </c>
       <c r="D193" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E193">
         <v>1.763414225815572</v>
@@ -11094,7 +11094,7 @@
         <v>2.960405936825934</v>
       </c>
       <c r="D194" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E194">
         <v>2.688557154970242</v>
@@ -11294,7 +11294,7 @@
         <v>2.642059072099817</v>
       </c>
       <c r="D198" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E198">
         <v>1.775187093932763</v>
@@ -11344,7 +11344,7 @@
         <v>2.972725908969226</v>
       </c>
       <c r="D199" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E199">
         <v>2.375803028433923</v>
@@ -11494,7 +11494,7 @@
         <v>2.666955617984192</v>
       </c>
       <c r="D202" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E202">
         <v>1.799497838737505</v>
@@ -11544,7 +11544,7 @@
         <v>2.998166412998973</v>
       </c>
       <c r="D203" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E203">
         <v>1.736641978102437</v>
@@ -11694,7 +11694,7 @@
         <v>2.973643871143521</v>
       </c>
       <c r="D206" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E206">
         <v>1.818524938691256</v>
@@ -11744,7 +11744,7 @@
         <v>3.018077732744034</v>
       </c>
       <c r="D207" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E207">
         <v>1.759533446033025</v>
@@ -11894,7 +11894,7 @@
         <v>2.990082102112254</v>
       </c>
       <c r="D210" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E210">
         <v>1.83485077149952</v>
@@ -11944,7 +11944,7 @@
         <v>3.03516225313547</v>
       </c>
       <c r="D211" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E211">
         <v>1.779175024575153</v>
@@ -12030,7 +12030,7 @@
         <v>1</v>
       </c>
       <c r="P212" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="213" spans="1:16">
@@ -12080,7 +12080,7 @@
         <v>1</v>
       </c>
       <c r="P213" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="214" spans="1:16">
@@ -12094,7 +12094,7 @@
         <v>3.005496469975766</v>
       </c>
       <c r="D214" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E214">
         <v>1.850159741975929</v>
@@ -12130,7 +12130,7 @@
         <v>1</v>
       </c>
       <c r="P214" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="215" spans="1:16">
@@ -12144,7 +12144,7 @@
         <v>3.051182655974811</v>
       </c>
       <c r="D215" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E215">
         <v>1.797593217971041</v>
@@ -12180,7 +12180,7 @@
         <v>1</v>
       </c>
       <c r="P215" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="216" spans="1:16">
@@ -12294,7 +12294,7 @@
         <v>3.018931533510157</v>
       </c>
       <c r="D218" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E218">
         <v>1.863502941828035</v>
@@ -12344,7 +12344,7 @@
         <v>3.06514593568235</v>
       </c>
       <c r="D219" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E219">
         <v>1.813646396450594</v>
@@ -12494,7 +12494,7 @@
         <v>3.033933076549712</v>
       </c>
       <c r="D222" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E222">
         <v>1.878401910214327</v>
@@ -12544,7 +12544,7 @@
         <v>3.080737282978161</v>
       </c>
       <c r="D223" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E223">
         <v>1.831571317108114</v>
@@ -12594,7 +12594,7 @@
         <v>1.639859271051932</v>
       </c>
       <c r="D224" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E224">
         <v>1.9209216037227</v>
@@ -12744,7 +12744,7 @@
         <v>3.05833801181463</v>
       </c>
       <c r="D227" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E227">
         <v>1.902639974127007</v>
@@ -12794,7 +12794,7 @@
         <v>3.106101728518452</v>
       </c>
       <c r="D228" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E228">
         <v>1.860732085911838</v>
@@ -12880,7 +12880,7 @@
         <v>1</v>
       </c>
       <c r="P229" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="230" spans="1:16">
@@ -12930,7 +12930,7 @@
         <v>1</v>
       </c>
       <c r="P230" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="231" spans="1:16">
@@ -12944,7 +12944,7 @@
         <v>3.085055612872655</v>
       </c>
       <c r="D231" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E231">
         <v>1.929174890733353</v>
@@ -12980,7 +12980,7 @@
         <v>1</v>
       </c>
       <c r="P231" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="232" spans="1:16">
@@ -12994,7 +12994,7 @@
         <v>3.13386976517363</v>
       </c>
       <c r="D232" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E232">
         <v>1.892656193842708</v>
@@ -13030,7 +13030,7 @@
         <v>1</v>
       </c>
       <c r="P232" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="233" spans="1:16">
@@ -13094,7 +13094,7 @@
         <v>3.103034611570727</v>
       </c>
       <c r="D234" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E234">
         <v>1.947030956106994</v>
@@ -13144,7 +13144,7 @@
         <v>3.152555630487182</v>
       </c>
       <c r="D235" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E235">
         <v>1.914138792287073</v>
@@ -13194,7 +13194,7 @@
         <v>1.641725609550694</v>
       </c>
       <c r="D236" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E236">
         <v>1.89319910743864</v>
@@ -13280,7 +13280,7 @@
         <v>1</v>
       </c>
       <c r="P237" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="238" spans="1:16">
@@ -13294,7 +13294,7 @@
         <v>3.11979974827751</v>
       </c>
       <c r="D238" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E238">
         <v>1.963681459400396</v>
@@ -13330,7 +13330,7 @@
         <v>1</v>
       </c>
       <c r="P238" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="239" spans="1:16">
@@ -13344,7 +13344,7 @@
         <v>3.169979909320897</v>
       </c>
       <c r="D239" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E239">
         <v>1.934170981275177</v>
@@ -13380,7 +13380,7 @@
         <v>1</v>
       </c>
       <c r="P239" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="240" spans="1:16">
@@ -13394,7 +13394,7 @@
         <v>1.664480342106565</v>
       </c>
       <c r="D240" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E240">
         <v>2.221652319966786</v>
@@ -13430,7 +13430,7 @@
         <v>1</v>
       </c>
       <c r="P240" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="241" spans="1:16">
@@ -13494,7 +13494,7 @@
         <v>3.136490860930856</v>
       </c>
       <c r="D242" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E242">
         <v>1.980258444787738</v>
@@ -13544,7 +13544,7 @@
         <v>3.187327253753777</v>
       </c>
       <c r="D243" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E243">
         <v>1.954114721009688</v>
@@ -13744,7 +13744,7 @@
         <v>3.154470288152615</v>
       </c>
       <c r="D247" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E247">
         <v>1.998114935754989</v>
@@ -13794,7 +13794,7 @@
         <v>3.206013564438956</v>
       </c>
       <c r="D248" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E248">
         <v>1.975597831484915</v>
@@ -13980,7 +13980,7 @@
         <v>1</v>
       </c>
       <c r="P251" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="252" spans="1:16">
@@ -14030,7 +14030,7 @@
         <v>1</v>
       </c>
       <c r="P252" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="253" spans="1:16">
@@ -14044,7 +14044,7 @@
         <v>3.175183381627829</v>
       </c>
       <c r="D253" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E253">
         <v>2.406837822852639</v>
@@ -14080,7 +14080,7 @@
         <v>1</v>
       </c>
       <c r="P253" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="254" spans="1:16">
@@ -14094,7 +14094,7 @@
         <v>3.227541018854222</v>
       </c>
       <c r="D254" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E254">
         <v>2.000347322662993</v>
@@ -14130,7 +14130,7 @@
         <v>1</v>
       </c>
       <c r="P254" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="255" spans="1:16">
@@ -14180,7 +14180,7 @@
         <v>1</v>
       </c>
       <c r="P255" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="256" spans="1:16">
@@ -14230,7 +14230,7 @@
         <v>1</v>
       </c>
       <c r="P256" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="257" spans="1:16">
@@ -14344,7 +14344,7 @@
         <v>3.194491499183421</v>
       </c>
       <c r="D259" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E259">
         <v>2.42485873257119</v>
@@ -14394,7 +14394,7 @@
         <v>3.247608258980375</v>
       </c>
       <c r="D260" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E260">
         <v>2.023418047742236</v>
@@ -14644,7 +14644,7 @@
         <v>3.213727962726566</v>
       </c>
       <c r="D265" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E265">
         <v>2.442812765211459</v>
@@ -14694,7 +14694,7 @@
         <v>3.26760102792778</v>
       </c>
       <c r="D266" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E266">
         <v>2.046403155463022</v>
@@ -14894,7 +14894,7 @@
         <v>3.233647867837396</v>
       </c>
       <c r="D270" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E270">
         <v>2.461404676648234</v>
@@ -14944,7 +14944,7 @@
         <v>3.288304108795105</v>
       </c>
       <c r="D271" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E271">
         <v>2.070204888236475</v>
@@ -15144,7 +15144,7 @@
         <v>3.249417008017017</v>
       </c>
       <c r="D275" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E275">
         <v>2.476122540815881</v>
@@ -15194,7 +15194,7 @@
         <v>3.304693232263839</v>
       </c>
       <c r="D276" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E276">
         <v>2.089046989066485</v>
@@ -15344,7 +15344,7 @@
         <v>1.914875661806953</v>
       </c>
       <c r="D279" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E279">
         <v>2.109898465499843</v>
@@ -15430,7 +15430,7 @@
         <v>1</v>
       </c>
       <c r="P280" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="281" spans="1:16">
@@ -15444,7 +15444,7 @@
         <v>3.261163134684622</v>
       </c>
       <c r="D281" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E281">
         <v>2.487085592372312</v>
@@ -15480,7 +15480,7 @@
         <v>1</v>
       </c>
       <c r="P281" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="282" spans="1:16">
@@ -15494,7 +15494,7 @@
         <v>3.316901172458547</v>
       </c>
       <c r="D282" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E282">
         <v>2.103082104520595</v>
@@ -15530,7 +15530,7 @@
         <v>1</v>
       </c>
       <c r="P282" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="283" spans="1:16">
@@ -15580,7 +15580,7 @@
         <v>1</v>
       </c>
       <c r="P283" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="284" spans="1:16">
@@ -15630,7 +15630,7 @@
         <v>1</v>
       </c>
       <c r="P284" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="285" spans="1:16">
@@ -15644,7 +15644,7 @@
         <v>1.930296217842372</v>
       </c>
       <c r="D285" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E285">
         <v>2.383746445952788</v>
@@ -15680,7 +15680,7 @@
         <v>1</v>
       </c>
       <c r="P285" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="286" spans="1:16">
@@ -15730,7 +15730,7 @@
         <v>1</v>
       </c>
       <c r="P286" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="287" spans="1:16">
@@ -15744,7 +15744,7 @@
         <v>3.267778188252251</v>
       </c>
       <c r="D287" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E287">
         <v>2.493259642368766</v>
@@ -15780,7 +15780,7 @@
         <v>1</v>
       </c>
       <c r="P287" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="288" spans="1:16">
@@ -15794,7 +15794,7 @@
         <v>3.323776305055329</v>
       </c>
       <c r="D288" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E288">
         <v>2.110986245450121</v>
@@ -15830,7 +15830,7 @@
         <v>1</v>
       </c>
       <c r="P288" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="289" spans="1:16">
@@ -15880,7 +15880,7 @@
         <v>1</v>
       </c>
       <c r="P289" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="290" spans="1:16">
@@ -15930,7 +15930,7 @@
         <v>1</v>
       </c>
       <c r="P290" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="291" spans="1:16">
@@ -15980,7 +15980,7 @@
         <v>1</v>
       </c>
       <c r="P291" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="292" spans="1:16">
@@ -15994,7 +15994,7 @@
         <v>3.278598009747792</v>
       </c>
       <c r="D292" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E292">
         <v>2.503358142431271</v>
@@ -16044,7 +16044,7 @@
         <v>3.335021521242147</v>
       </c>
       <c r="D293" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E293">
         <v>2.123914544980693</v>
@@ -16194,7 +16194,7 @@
         <v>1.953185079463765</v>
       </c>
       <c r="D296" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E296">
         <v>1.673185079463764</v>
@@ -16244,7 +16244,7 @@
         <v>1.838424946780282</v>
       </c>
       <c r="D297" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E297">
         <v>1.673185079463764</v>
@@ -16294,7 +16294,7 @@
         <v>3.286491586851236</v>
       </c>
       <c r="D298" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E298">
         <v>2.510725481061151</v>
@@ -16344,7 +16344,7 @@
         <v>3.343225444112052</v>
       </c>
       <c r="D299" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E299">
         <v>2.133346357622241</v>
@@ -16494,7 +16494,7 @@
         <v>1.963547929404697</v>
       </c>
       <c r="D302" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E302">
         <v>2.040362444937774</v>
@@ -16544,7 +16544,7 @@
         <v>1.849314035194777</v>
       </c>
       <c r="D303" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E303">
         <v>2.040362444937774</v>
@@ -16594,7 +16594,7 @@
         <v>3.287218803551511</v>
       </c>
       <c r="D304" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E304">
         <v>2.511404216648074</v>
@@ -16644,7 +16644,7 @@
         <v>3.34398125223815</v>
       </c>
       <c r="D305" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E305">
         <v>2.134215288346162</v>
@@ -16794,7 +16794,7 @@
         <v>1.964502634406085</v>
       </c>
       <c r="D308" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E308">
         <v>2.034789980466009</v>
@@ -16844,7 +16844,7 @@
         <v>1.850317221309513</v>
       </c>
       <c r="D309" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E309">
         <v>2.034789980466009</v>
@@ -16894,7 +16894,7 @@
         <v>3.309574328279867</v>
       </c>
       <c r="D310" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E310">
         <v>2.532269373061208</v>
@@ -16944,7 +16944,7 @@
         <v>3.367215712126766</v>
       </c>
       <c r="D311" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E311">
         <v>2.160927274303631</v>
@@ -17194,7 +17194,7 @@
         <v>3.386581638751728</v>
       </c>
       <c r="D316" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E316">
         <v>2.183191719551736</v>
@@ -17294,7 +17294,7 @@
         <v>2.018313648949551</v>
       </c>
       <c r="D318" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E318">
         <v>2.020805677582523</v>
@@ -17344,7 +17344,7 @@
         <v>1.906860826435267</v>
       </c>
       <c r="D319" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E319">
         <v>2.020805677582523</v>
@@ -17394,7 +17394,7 @@
         <v>1.784750528729781</v>
       </c>
       <c r="D320" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E320">
         <v>2.020805677582523</v>
@@ -17444,7 +17444,7 @@
         <v>3.376305833526885</v>
       </c>
       <c r="D321" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E321">
         <v>2.171377923742256</v>
@@ -17480,7 +17480,7 @@
         <v>1</v>
       </c>
       <c r="P321" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="322" spans="1:16">
@@ -17530,7 +17530,7 @@
         <v>1</v>
       </c>
       <c r="P322" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="323" spans="1:16">
@@ -17580,7 +17580,7 @@
         <v>1</v>
       </c>
       <c r="P323" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="324" spans="1:16">
@@ -17630,7 +17630,7 @@
         <v>1</v>
       </c>
       <c r="P324" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="325" spans="1:16">
@@ -17644,7 +17644,7 @@
         <v>3.346413966869674</v>
       </c>
       <c r="D325" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E325">
         <v>2.137012109937338</v>
@@ -17680,7 +17680,7 @@
         <v>1</v>
       </c>
       <c r="P325" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="326" spans="1:16">
@@ -17730,7 +17730,7 @@
         <v>1</v>
       </c>
       <c r="P326" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="327" spans="1:16">
@@ -17744,7 +17744,7 @@
         <v>1.853546169841817</v>
       </c>
       <c r="D327" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E327">
         <v>1.909412654865697</v>
@@ -17780,7 +17780,7 @@
         <v>1</v>
       </c>
       <c r="P327" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="328" spans="1:16">
@@ -17794,7 +17794,7 @@
         <v>1.729057523143315</v>
       </c>
       <c r="D328" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E328">
         <v>1.909412654865697</v>
@@ -17830,7 +17830,7 @@
         <v>1</v>
       </c>
       <c r="P328" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="329" spans="1:16">
@@ -17844,7 +17844,7 @@
         <v>1.90213361560998</v>
       </c>
       <c r="D329" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E329">
         <v>1.909412654865697</v>
@@ -17880,7 +17880,7 @@
         <v>1</v>
       </c>
       <c r="P329" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="330" spans="1:16">
@@ -17894,7 +17894,7 @@
         <v>3.335708401471214</v>
       </c>
       <c r="D330" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E330">
         <v>2.124704231296676</v>
@@ -17994,7 +17994,7 @@
         <v>1.839336644715903</v>
       </c>
       <c r="D332" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E332">
         <v>2.572020438006287</v>
@@ -18044,7 +18044,7 @@
         <v>1.714214115855647</v>
       </c>
       <c r="D333" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E333">
         <v>2.572020438006287</v>
@@ -18094,7 +18094,7 @@
         <v>1.88846993345668</v>
       </c>
       <c r="D334" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E334">
         <v>2.572020438006287</v>
@@ -18144,7 +18144,7 @@
         <v>3.319807569063805</v>
       </c>
       <c r="D335" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E335">
         <v>2.106423504565129</v>
@@ -18244,7 +18244,7 @@
         <v>1.818231428017253</v>
       </c>
       <c r="D337" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E337">
         <v>2.552327466291189</v>
@@ -18294,7 +18294,7 @@
         <v>1.692167402501294</v>
       </c>
       <c r="D338" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E338">
         <v>2.552327466291189</v>
@@ -18344,7 +18344,7 @@
         <v>1.86817544998933</v>
       </c>
       <c r="D339" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E339">
         <v>2.552327466291189</v>
@@ -18394,7 +18394,7 @@
         <v>3.297653300651016</v>
       </c>
       <c r="D340" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E340">
         <v>2.080953383478715</v>
@@ -18430,7 +18430,7 @@
         <v>1</v>
       </c>
       <c r="P340" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="341" spans="1:16">
@@ -18480,7 +18480,7 @@
         <v>1</v>
       </c>
       <c r="P341" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="342" spans="1:16">
@@ -18494,7 +18494,7 @@
         <v>1.788826009252247</v>
       </c>
       <c r="D342" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E342">
         <v>2.524889696365481</v>
@@ -18530,7 +18530,7 @@
         <v>1</v>
       </c>
       <c r="P342" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="343" spans="1:16">
@@ -18544,7 +18544,7 @@
         <v>1.661450217843427</v>
       </c>
       <c r="D343" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E343">
         <v>2.524889696365481</v>
@@ -18580,7 +18580,7 @@
         <v>1</v>
       </c>
       <c r="P343" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="344" spans="1:16">
@@ -18594,7 +18594,7 @@
         <v>1.839899607409848</v>
       </c>
       <c r="D344" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E344">
         <v>2.524889696365481</v>
@@ -18630,7 +18630,7 @@
         <v>1</v>
       </c>
       <c r="P344" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="345" spans="1:16">
@@ -18644,7 +18644,7 @@
         <v>3.263703117123406</v>
       </c>
       <c r="D345" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E345">
         <v>2.041921840245493</v>
@@ -18744,7 +18744,7 @@
         <v>1.743763841313463</v>
       </c>
       <c r="D347" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E347">
         <v>2.48284284077948</v>
@@ -18794,7 +18794,7 @@
         <v>1.614377841669459</v>
       </c>
       <c r="D348" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E348">
         <v>2.48284284077948</v>
@@ -18844,7 +18844,7 @@
         <v>1.796568452118031</v>
       </c>
       <c r="D349" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E349">
         <v>2.48284284077948</v>
@@ -18894,7 +18894,7 @@
         <v>3.242126022559422</v>
       </c>
       <c r="D350" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E350">
         <v>2.017115279225386</v>
@@ -18930,7 +18930,7 @@
         <v>1</v>
       </c>
       <c r="P350" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="351" spans="1:16">
@@ -18980,7 +18980,7 @@
         <v>1</v>
       </c>
       <c r="P351" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="352" spans="1:16">
@@ -18994,7 +18994,7 @@
         <v>1.715124506916858</v>
       </c>
       <c r="D352" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E352">
         <v>2.456119893071122</v>
@@ -19030,7 +19030,7 @@
         <v>1</v>
       </c>
       <c r="P352" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="353" spans="1:16">
@@ -19044,7 +19044,7 @@
         <v>1.584460916147354</v>
       </c>
       <c r="D353" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E353">
         <v>2.456119893071122</v>
@@ -19080,7 +19080,7 @@
         <v>1</v>
       </c>
       <c r="P353" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="354" spans="1:16">
@@ -19094,7 +19094,7 @@
         <v>1.769029265635051</v>
       </c>
       <c r="D354" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E354">
         <v>2.456119893071122</v>
@@ -19130,7 +19130,7 @@
         <v>1</v>
       </c>
       <c r="P354" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="355" spans="1:16">
@@ -19144,7 +19144,7 @@
         <v>3.218796578894542</v>
       </c>
       <c r="D355" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E355">
         <v>1.990294093169876</v>
@@ -19244,7 +19244,7 @@
         <v>1.684159274947191</v>
       </c>
       <c r="D357" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E357">
         <v>2.427226684058535</v>
@@ -19294,7 +19294,7 @@
         <v>1.552114335539635</v>
       </c>
       <c r="D358" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E358">
         <v>2.427226684058535</v>
@@ -19344,7 +19344,7 @@
         <v>1.739253528325928</v>
       </c>
       <c r="D359" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E359">
         <v>2.427226684058535</v>
@@ -19394,7 +19394,7 @@
         <v>3.223084813618858</v>
       </c>
       <c r="D360" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E360">
         <v>1.995224152499308</v>
@@ -19430,7 +19430,7 @@
         <v>1</v>
       </c>
       <c r="P360" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="361" spans="1:16">
@@ -19444,7 +19444,7 @@
         <v>1.689851060181606</v>
       </c>
       <c r="D361" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E361">
         <v>2.432537606340457</v>
@@ -19480,7 +19480,7 @@
         <v>1</v>
       </c>
       <c r="P361" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="362" spans="1:16">
@@ -19494,7 +19494,7 @@
         <v>1.558060029409038</v>
       </c>
       <c r="D362" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E362">
         <v>2.432537606340457</v>
@@ -19530,7 +19530,7 @@
         <v>1</v>
       </c>
       <c r="P362" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="363" spans="1:16">
@@ -19544,7 +19544,7 @@
         <v>1.5546355793606</v>
       </c>
       <c r="D363" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E363">
         <v>2.429478755941318</v>
@@ -19594,7 +19594,7 @@
         <v>2.749895863416445</v>
       </c>
       <c r="D364" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E364">
         <v>2.144120683335579</v>
@@ -19630,7 +19630,7 @@
         <v>1</v>
       </c>
       <c r="P364" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="365" spans="1:16">
@@ -19644,7 +19644,7 @@
         <v>1.575757316392718</v>
       </c>
       <c r="D365" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E365">
         <v>2.448345503254703</v>
@@ -19680,7 +19680,7 @@
         <v>1</v>
       </c>
       <c r="P365" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="366" spans="1:16">
@@ -19694,7 +19694,7 @@
         <v>1.708690594836302</v>
       </c>
       <c r="D366" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E366">
         <v>1.95524223097577</v>
@@ -19730,7 +19730,7 @@
         <v>1</v>
       </c>
       <c r="P366" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="367" spans="1:16">
@@ -19744,7 +19744,7 @@
         <v>2.776972324350222</v>
       </c>
       <c r="D367" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E367">
         <v>2.170167242074328</v>
@@ -19780,7 +19780,7 @@
         <v>1</v>
       </c>
       <c r="P367" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="368" spans="1:16">
@@ -19794,7 +19794,7 @@
         <v>1.603764011567165</v>
       </c>
       <c r="D368" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E368">
         <v>2.473362159798427</v>
@@ -19830,7 +19830,7 @@
         <v>1</v>
       </c>
       <c r="P368" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="369" spans="1:16">
@@ -19844,7 +19844,7 @@
         <v>1.733308579562596</v>
       </c>
       <c r="D369" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E369">
         <v>2.069952921130998</v>
@@ -19880,7 +19880,7 @@
         <v>1</v>
       </c>
       <c r="P369" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="370" spans="1:16">
@@ -19894,7 +19894,7 @@
         <v>2.804318151096002</v>
       </c>
       <c r="D370" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E370">
         <v>2.196472920808915</v>
@@ -19930,7 +19930,7 @@
         <v>1</v>
       </c>
       <c r="P370" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="371" spans="1:16">
@@ -19944,7 +19944,7 @@
         <v>1.632049326839176</v>
       </c>
       <c r="D371" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E371">
         <v>2.498627690521825</v>
@@ -19980,7 +19980,7 @@
         <v>1</v>
       </c>
       <c r="P371" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="372" spans="1:16">
@@ -19994,7 +19994,7 @@
         <v>1.758171472346181</v>
       </c>
       <c r="D372" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E372">
         <v>2.648741745065742</v>
@@ -20030,7 +20030,7 @@
         <v>1</v>
       </c>
       <c r="P372" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="373" spans="1:16">
@@ -20044,7 +20044,7 @@
         <v>1.836308899819077</v>
       </c>
       <c r="D373" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E373">
         <v>2.387421432319158</v>
@@ -20080,7 +20080,7 @@
         <v>1</v>
       </c>
       <c r="P373" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="374" spans="1:16">
@@ -20130,7 +20130,7 @@
         <v>1</v>
       </c>
       <c r="P374" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="375" spans="1:16">
@@ -20144,7 +20144,7 @@
         <v>1.66686196794393</v>
       </c>
       <c r="D375" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E375">
         <v>2.529723679551338</v>
@@ -20180,7 +20180,7 @@
         <v>1</v>
       </c>
       <c r="P375" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="376" spans="1:16">
@@ -20194,7 +20194,7 @@
         <v>1.844881242140559</v>
       </c>
       <c r="D376" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E376">
         <v>2.529723679551338</v>
@@ -20230,7 +20230,7 @@
         <v>1</v>
       </c>
       <c r="P376" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="377" spans="1:16">
@@ -20244,7 +20244,7 @@
         <v>1.788771907765661</v>
       </c>
       <c r="D377" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E377">
         <v>2.679961622497764</v>
@@ -20280,7 +20280,7 @@
         <v>1</v>
       </c>
       <c r="P377" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="378" spans="1:16">
@@ -20294,7 +20294,7 @@
         <v>1.861508767932467</v>
       </c>
       <c r="D378" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E378">
         <v>2.411732640096055</v>
@@ -20330,7 +20330,7 @@
         <v>1</v>
       </c>
       <c r="P378" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="379" spans="1:16">
@@ -20380,7 +20380,7 @@
         <v>1</v>
       </c>
       <c r="P379" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="380" spans="1:16">
@@ -20394,7 +20394,7 @@
         <v>1.693616991646184</v>
       </c>
       <c r="D380" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E380">
         <v>2.55362229502915</v>
@@ -20430,7 +20430,7 @@
         <v>1</v>
       </c>
       <c r="P380" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="381" spans="1:16">
@@ -20444,7 +20444,7 @@
         <v>1.869509828609061</v>
       </c>
       <c r="D381" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E381">
         <v>2.55362229502915</v>
@@ -20480,7 +20480,7 @@
         <v>1</v>
       </c>
       <c r="P381" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="382" spans="1:16">
@@ -20494,7 +20494,7 @@
         <v>2.574954921244757</v>
       </c>
       <c r="D382" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E382">
         <v>2.17950982860906</v>
@@ -20530,7 +20530,7 @@
         <v>1</v>
       </c>
       <c r="P382" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="383" spans="1:16">
@@ -20544,7 +20544,7 @@
         <v>1.812289668813548</v>
       </c>
       <c r="D383" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E383">
         <v>2.703955451583056</v>
@@ -20580,7 +20580,7 @@
         <v>1</v>
       </c>
       <c r="P383" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="384" spans="1:16">
@@ -20594,7 +20594,7 @@
         <v>1.878354735459471</v>
       </c>
       <c r="D384" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E384">
         <v>2.42798454327702</v>
@@ -20630,7 +20630,7 @@
         <v>1</v>
       </c>
       <c r="P384" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="385" spans="1:16">
@@ -20680,7 +20680,7 @@
         <v>1</v>
       </c>
       <c r="P385" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="386" spans="1:16">
@@ -20694,7 +20694,7 @@
         <v>1.711502571778759</v>
       </c>
       <c r="D386" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E386">
         <v>2.569598382620882</v>
@@ -20730,7 +20730,7 @@
         <v>1</v>
       </c>
       <c r="P386" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="387" spans="1:16">
@@ -20744,7 +20744,7 @@
         <v>1.885973897627895</v>
       </c>
       <c r="D387" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E387">
         <v>2.569598382620882</v>
@@ -20780,7 +20780,7 @@
         <v>1</v>
       </c>
       <c r="P387" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="388" spans="1:16">
@@ -20794,7 +20794,7 @@
         <v>2.591185607841933</v>
       </c>
       <c r="D388" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E388">
         <v>2.195973897627894</v>
@@ -20830,7 +20830,7 @@
         <v>1</v>
       </c>
       <c r="P388" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="389" spans="1:16">
@@ -20844,7 +20844,7 @@
         <v>1.828011157399832</v>
       </c>
       <c r="D389" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E389">
         <v>2.719995188926148</v>
@@ -20880,7 +20880,7 @@
         <v>1</v>
       </c>
       <c r="P389" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="390" spans="1:16">
@@ -20894,7 +20894,7 @@
         <v>1.884937981108568</v>
       </c>
       <c r="D390" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E390">
         <v>2.434335634167709</v>
@@ -20994,7 +20994,7 @@
         <v>1.718492088255065</v>
       </c>
       <c r="D392" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E392">
         <v>2.575841687373739</v>
@@ -21044,7 +21044,7 @@
         <v>1.892407900932305</v>
       </c>
       <c r="D393" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E393">
         <v>2.575841687373739</v>
@@ -21094,7 +21094,7 @@
         <v>1.834154967256232</v>
       </c>
       <c r="D394" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E394">
         <v>2.726263367403121</v>
@@ -21144,7 +21144,7 @@
         <v>2.791624887079966</v>
       </c>
       <c r="D395" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E395">
         <v>2.637829766815571</v>
@@ -21194,7 +21194,7 @@
         <v>1.897004594528006</v>
       </c>
       <c r="D396" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E396">
         <v>2.445976724695786</v>
@@ -21294,7 +21294,7 @@
         <v>1.731303366734398</v>
       </c>
       <c r="D398" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E398">
         <v>2.587285213702252</v>
@@ -21344,7 +21344,7 @@
         <v>1.904200963921582</v>
       </c>
       <c r="D399" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E399">
         <v>2.587285213702252</v>
@@ -21394,7 +21394,7 @@
         <v>1.845416126631299</v>
       </c>
       <c r="D400" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E400">
         <v>2.737752485469994</v>
@@ -21444,7 +21444,7 @@
         <v>2.802612496024871</v>
       </c>
       <c r="D401" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E401">
         <v>2.813453713263602</v>
@@ -21494,7 +21494,7 @@
         <v>1.915149243214803</v>
       </c>
       <c r="D402" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E402">
         <v>2.463481511716044</v>
@@ -21594,7 +21594,7 @@
         <v>1.750567773337632</v>
       </c>
       <c r="D404" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E404">
         <v>2.60449292209162</v>
@@ -21644,7 +21644,7 @@
         <v>1.921934272965604</v>
       </c>
       <c r="D405" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E405">
         <v>2.60449292209162</v>
@@ -21694,7 +21694,7 @@
         <v>1.862349608592151</v>
       </c>
       <c r="D406" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E406">
         <v>2.75502875046649</v>
@@ -21744,7 +21744,7 @@
         <v>2.819134638342948</v>
       </c>
       <c r="D407" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E407">
         <v>2.769730713091974</v>
@@ -21794,7 +21794,7 @@
         <v>1.92753511972947</v>
       </c>
       <c r="D408" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E408">
         <v>2.475430606691152</v>
@@ -21894,7 +21894,7 @@
         <v>1.76371801754653</v>
       </c>
       <c r="D410" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E410">
         <v>2.616239225637646</v>
@@ -21944,7 +21944,7 @@
         <v>1.934039361347697</v>
       </c>
       <c r="D411" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E411">
         <v>2.616239225637646</v>
@@ -21994,7 +21994,7 @@
         <v>1.873908720049794</v>
       </c>
       <c r="D412" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E412">
         <v>2.766821852034614</v>
@@ -22044,7 +22044,7 @@
         <v>2.830412961668017</v>
       </c>
       <c r="D413" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E413">
         <v>2.221708855759843</v>
@@ -22094,7 +22094,7 @@
         <v>1.937685341557977</v>
       </c>
       <c r="D414" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E414">
         <v>2.485222886188172</v>
@@ -22130,7 +22130,7 @@
         <v>1</v>
       </c>
       <c r="P414" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="415" spans="1:16">
@@ -22180,7 +22180,7 @@
         <v>1</v>
       </c>
       <c r="P415" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="416" spans="1:16">
@@ -22194,7 +22194,7 @@
         <v>1.774494638455131</v>
       </c>
       <c r="D416" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E416">
         <v>2.625865317623621</v>
@@ -22230,7 +22230,7 @@
         <v>1</v>
       </c>
       <c r="P416" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="417" spans="1:16">
@@ -22244,7 +22244,7 @@
         <v>1.943959477391676</v>
       </c>
       <c r="D417" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E417">
         <v>2.625865317623621</v>
@@ -22280,7 +22280,7 @@
         <v>1</v>
       </c>
       <c r="P417" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="418" spans="1:16">
@@ -22294,7 +22294,7 @@
         <v>1.883381408179421</v>
       </c>
       <c r="D418" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E418">
         <v>2.776486294984675</v>
@@ -22330,7 +22330,7 @@
         <v>1</v>
       </c>
       <c r="P418" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="419" spans="1:16">
@@ -22344,7 +22344,7 @@
         <v>2.839655544013116</v>
       </c>
       <c r="D419" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E419">
         <v>2.231475567947474</v>
@@ -22380,7 +22380,7 @@
         <v>1</v>
       </c>
       <c r="P419" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="420" spans="1:16">
@@ -22394,7 +22394,7 @@
         <v>1.950149148490695</v>
       </c>
       <c r="D420" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E420">
         <v>2.49724716340538</v>
@@ -22494,7 +22494,7 @@
         <v>1.787727622389998</v>
       </c>
       <c r="D422" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E422">
         <v>2.637685527472915</v>
@@ -22544,7 +22544,7 @@
         <v>1.956140729507283</v>
       </c>
       <c r="D423" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E423">
         <v>2.637685527472915</v>
@@ -22594,7 +22594,7 @@
         <v>1.895013248150637</v>
       </c>
       <c r="D424" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E424">
         <v>2.788353597303487</v>
@@ -22644,7 +22644,7 @@
         <v>2.85100482916722</v>
       </c>
       <c r="D425" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E425">
         <v>2.243468450185002</v>
@@ -22744,7 +22744,7 @@
         <v>1.796280604882195</v>
       </c>
       <c r="D427" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E427">
         <v>2.645325380161676</v>
@@ -22794,7 +22794,7 @@
         <v>1.964013937590256</v>
       </c>
       <c r="D428" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E428">
         <v>2.645325380161676</v>
@@ -22844,7 +22844,7 @@
         <v>1.902531350198938</v>
       </c>
       <c r="D429" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E429">
         <v>2.796023887652364</v>
@@ -22894,7 +22894,7 @@
         <v>2.858340305254835</v>
       </c>
       <c r="D430" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E430">
         <v>2.251219907627515</v>
@@ -22980,7 +22980,7 @@
         <v>1</v>
       </c>
       <c r="P431" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="432" spans="1:16">
@@ -22994,7 +22994,7 @@
         <v>1.81059278070445</v>
       </c>
       <c r="D432" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E432">
         <v>2.658109565682619</v>
@@ -23030,7 +23030,7 @@
         <v>1</v>
       </c>
       <c r="P432" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="433" spans="1:16">
@@ -23044,7 +23044,7 @@
         <v>1.977188609521534</v>
       </c>
       <c r="D433" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E433">
         <v>2.658109565682619</v>
@@ -23080,7 +23080,7 @@
         <v>1</v>
       </c>
       <c r="P433" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="434" spans="1:16">
@@ -23094,7 +23094,7 @@
         <v>1.915111803679711</v>
       </c>
       <c r="D434" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E434">
         <v>2.808859006183351</v>
@@ -23130,7 +23130,7 @@
         <v>1</v>
       </c>
       <c r="P434" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="435" spans="1:16">
@@ -23144,7 +23144,7 @@
         <v>2.870615160675342</v>
       </c>
       <c r="D435" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E435">
         <v>2.26419084751862</v>
@@ -23180,7 +23180,7 @@
         <v>1</v>
       </c>
       <c r="P435" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="436" spans="1:16">
@@ -23230,7 +23230,7 @@
         <v>1</v>
       </c>
       <c r="P436" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="437" spans="1:16">
@@ -23244,7 +23244,7 @@
         <v>1.82632056259726</v>
       </c>
       <c r="D437" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E437">
         <v>2.672158224953424</v>
@@ -23280,7 +23280,7 @@
         <v>1</v>
       </c>
       <c r="P437" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="438" spans="1:16">
@@ -23294,7 +23294,7 @@
         <v>1.991666377906849</v>
       </c>
       <c r="D438" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E438">
         <v>2.672158224953424</v>
@@ -23330,7 +23330,7 @@
         <v>1</v>
       </c>
       <c r="P438" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="439" spans="1:16">
@@ -23344,7 +23344,7 @@
         <v>1.928936579934245</v>
       </c>
       <c r="D439" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E439">
         <v>2.822963636208222</v>
@@ -23380,7 +23380,7 @@
         <v>1</v>
       </c>
       <c r="P439" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="440" spans="1:16">
@@ -23394,7 +23394,7 @@
         <v>2.884104112405478</v>
       </c>
       <c r="D440" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E440">
         <v>2.278444732887671</v>
@@ -23430,7 +23430,7 @@
         <v>1</v>
       </c>
       <c r="P440" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="441" spans="1:16">
@@ -23444,7 +23444,7 @@
         <v>1.850091985515281</v>
       </c>
       <c r="D441" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E441">
         <v>2.693391773538558</v>
@@ -23494,7 +23494,7 @@
         <v>2.013548494377055</v>
       </c>
       <c r="D442" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E442">
         <v>2.693391773538558</v>
@@ -23544,7 +23544,7 @@
         <v>1.949831745274995</v>
       </c>
       <c r="D443" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E443">
         <v>2.844281780604454</v>
@@ -23594,7 +23594,7 @@
         <v>2.90449170287965</v>
       </c>
       <c r="D444" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E444">
         <v>2.29998846611349</v>
@@ -23644,7 +23644,7 @@
         <v>1.883787347386825</v>
       </c>
       <c r="D445" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E445">
         <v>2.723489765815277</v>
@@ -23694,7 +23694,7 @@
         <v>2.044565814439117</v>
       </c>
       <c r="D446" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E446">
         <v>2.723489765815277</v>
@@ -23744,7 +23744,7 @@
         <v>2.74752944335815</v>
       </c>
       <c r="D447" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E447">
         <v>2.354565814439116</v>
@@ -23794,7 +23794,7 @@
         <v>1.979450088272404</v>
       </c>
       <c r="D448" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E448">
         <v>2.874499685200998</v>
@@ -23844,7 +23844,7 @@
         <v>2.933390571958093</v>
       </c>
       <c r="D449" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E449">
         <v>2.330526136896243</v>
@@ -23944,7 +23944,7 @@
         <v>1.920897553279229</v>
       </c>
       <c r="D451" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E451">
         <v>2.756638028018099</v>
@@ -23994,7 +23994,7 @@
         <v>2.078726573362612</v>
       </c>
       <c r="D452" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E452">
         <v>2.756638028018099</v>
@@ -24044,7 +24044,7 @@
         <v>2.012070091316616</v>
       </c>
       <c r="D453" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E453">
         <v>2.907780012193474</v>
@@ -24094,7 +24094,7 @@
         <v>2.965218186264387</v>
       </c>
       <c r="D454" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E454">
         <v>2.364158636661127</v>
@@ -24144,7 +24144,7 @@
         <v>1.971362962924253</v>
       </c>
       <c r="D455" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E455">
         <v>2.801715671508852</v>
@@ -24194,7 +24194,7 @@
         <v>2.125181090426125</v>
       </c>
       <c r="D456" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E456">
         <v>2.801715671508852</v>
@@ -24244,7 +24244,7 @@
         <v>2.056429365986798</v>
       </c>
       <c r="D457" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E457">
         <v>2.95303724788937</v>
@@ -24294,7 +24294,7 @@
         <v>3.008499907703719</v>
       </c>
       <c r="D458" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E458">
         <v>2.409894784904068</v>
@@ -24344,7 +24344,7 @@
         <v>2.008171638992437</v>
       </c>
       <c r="D459" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E459">
         <v>2.834594595683633</v>
@@ -24380,7 +24380,7 @@
         <v>1</v>
       </c>
       <c r="P459" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="460" spans="1:16">
@@ -24394,7 +24394,7 @@
         <v>2.159064284529219</v>
       </c>
       <c r="D460" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E460">
         <v>2.834594595683633</v>
@@ -24430,7 +24430,7 @@
         <v>1</v>
       </c>
       <c r="P460" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="461" spans="1:16">
@@ -24444,7 +24444,7 @@
         <v>2.088784323242461</v>
       </c>
       <c r="D461" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E461">
         <v>2.986047163793931</v>
@@ -24480,7 +24480,7 @@
         <v>1</v>
       </c>
       <c r="P461" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="462" spans="1:16">
@@ -24494,7 +24494,7 @@
         <v>3.040068914580697</v>
       </c>
       <c r="D462" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E462">
         <v>2.443254012088044</v>
@@ -24530,7 +24530,7 @@
         <v>1</v>
       </c>
       <c r="P462" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="463" spans="1:16">
@@ -24544,7 +24544,7 @@
         <v>2.067700645146257</v>
       </c>
       <c r="D463" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E463">
         <v>2.887768191927794</v>
@@ -24594,7 +24594,7 @@
         <v>2.213862041083626</v>
       </c>
       <c r="D464" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E464">
         <v>2.887768191927794</v>
@@ -24644,7 +24644,7 @@
         <v>2.914425852356924</v>
       </c>
       <c r="D465" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E465">
         <v>2.523862041083625</v>
@@ -24694,7 +24694,7 @@
         <v>2.141110531498665</v>
       </c>
       <c r="D466" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E466">
         <v>3.039432607035081</v>
@@ -24744,7 +24744,7 @@
         <v>3.091124040854972</v>
       </c>
       <c r="D467" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E467">
         <v>2.497204380654495</v>
@@ -24794,7 +24794,7 @@
         <v>2.102053433035913</v>
       </c>
       <c r="D468" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E468">
         <v>2.918453422391508</v>
@@ -24830,7 +24830,7 @@
         <v>1</v>
       </c>
       <c r="P468" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="469" spans="1:16">
@@ -24844,7 +24844,7 @@
         <v>2.245484536222857</v>
       </c>
       <c r="D469" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E469">
         <v>2.918453422391508</v>
@@ -24880,7 +24880,7 @@
         <v>1</v>
       </c>
       <c r="P469" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="470" spans="1:16">
@@ -24894,7 +24894,7 @@
         <v>2.945600090477427</v>
       </c>
       <c r="D470" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E470">
         <v>2.555484536222856</v>
@@ -24930,7 +24930,7 @@
         <v>1</v>
       </c>
       <c r="P470" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="471" spans="1:16">
@@ -24944,7 +24944,7 @@
         <v>2.171306754305586</v>
       </c>
       <c r="D471" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E471">
         <v>3.070240089412991</v>
@@ -24980,7 +24980,7 @@
         <v>1</v>
       </c>
       <c r="P471" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="472" spans="1:16">
@@ -24994,7 +24994,7 @@
         <v>3.120586752176706</v>
       </c>
       <c r="D472" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E472">
         <v>2.528337868136934</v>
@@ -25030,7 +25030,7 @@
         <v>1</v>
       </c>
       <c r="P472" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="473" spans="1:16">
@@ -25044,7 +25044,7 @@
         <v>2.150109762840597</v>
       </c>
       <c r="D473" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E473">
         <v>2.961379183177897</v>
@@ -25080,7 +25080,7 @@
         <v>1</v>
       </c>
       <c r="P473" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="474" spans="1:16">
@@ -25094,7 +25094,7 @@
         <v>2.289721442425034</v>
       </c>
       <c r="D474" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E474">
         <v>2.961379183177897</v>
@@ -25130,7 +25130,7 @@
         <v>1</v>
       </c>
       <c r="P474" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="475" spans="1:16">
@@ -25144,7 +25144,7 @@
         <v>2.989209927132926</v>
       </c>
       <c r="D475" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E475">
         <v>2.599721442425032</v>
@@ -25180,7 +25180,7 @@
         <v>1</v>
       </c>
       <c r="P475" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="476" spans="1:16">
@@ -25194,7 +25194,7 @@
         <v>2.213548439222873</v>
       </c>
       <c r="D476" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E476">
         <v>3.113336869166659</v>
@@ -25230,7 +25230,7 @@
         <v>1</v>
       </c>
       <c r="P476" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="477" spans="1:16">
@@ -25244,7 +25244,7 @@
         <v>3.161802323290331</v>
       </c>
       <c r="D477" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E477">
         <v>2.571890698470007</v>
@@ -25280,7 +25280,7 @@
         <v>1</v>
       </c>
       <c r="P477" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="478" spans="1:16">
@@ -25294,7 +25294,7 @@
         <v>2.189716387261424</v>
       </c>
       <c r="D478" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E478">
         <v>2.99675734235807</v>
@@ -25344,7 +25344,7 @@
         <v>2.326180209388927</v>
       </c>
       <c r="D479" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E479">
         <v>2.99675734235807</v>
@@ -25394,7 +25394,7 @@
         <v>2.248362803037622</v>
       </c>
       <c r="D480" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E480">
         <v>3.148855977188184</v>
@@ -25444,7 +25444,7 @@
         <v>3.19577099405695</v>
       </c>
       <c r="D481" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E481">
         <v>2.607785670068477</v>
@@ -25494,7 +25494,7 @@
         <v>2.215826782258592</v>
       </c>
       <c r="D482" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E482">
         <v>3.020080150700736</v>
@@ -25530,7 +25530,7 @@
         <v>1</v>
       </c>
       <c r="P482" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="483" spans="1:16">
@@ -25544,7 +25544,7 @@
         <v>2.350215400987747</v>
       </c>
       <c r="D483" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E483">
         <v>3.020080150700736</v>
@@ -25580,7 +25580,7 @@
         <v>1</v>
       </c>
       <c r="P483" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="484" spans="1:16">
@@ -25594,7 +25594,7 @@
         <v>2.271313933159689</v>
       </c>
       <c r="D484" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E484">
         <v>3.172271705086001</v>
@@ -25630,7 +25630,7 @@
         <v>1</v>
       </c>
       <c r="P484" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="485" spans="1:16">
@@ -25644,7 +25644,7 @@
         <v>3.218164606848116</v>
       </c>
       <c r="D485" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E485">
         <v>2.631449183446694</v>
@@ -25680,7 +25680,7 @@
         <v>1</v>
       </c>
       <c r="P485" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="486" spans="1:16">
@@ -25730,7 +25730,7 @@
         <v>1</v>
       </c>
       <c r="P486" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="487" spans="1:16">
@@ -25744,7 +25744,7 @@
         <v>2.227304742320833</v>
       </c>
       <c r="D487" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E487">
         <v>3.030332705774125</v>
@@ -25780,7 +25780,7 @@
         <v>1</v>
       </c>
       <c r="P487" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="488" spans="1:16">
@@ -25794,7 +25794,7 @@
         <v>2.360781115113841</v>
       </c>
       <c r="D488" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E488">
         <v>3.030332705774125</v>
@@ -25830,7 +25830,7 @@
         <v>1</v>
       </c>
       <c r="P488" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="489" spans="1:16">
@@ -25844,7 +25844,7 @@
         <v>2.28140310090123</v>
       </c>
       <c r="D489" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E489">
         <v>3.182565106992353</v>
@@ -25880,7 +25880,7 @@
         <v>1</v>
       </c>
       <c r="P489" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="490" spans="1:16">
@@ -25894,7 +25894,7 @@
         <v>3.228008693591889</v>
       </c>
       <c r="D490" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E490">
         <v>2.641851510240944</v>
@@ -25930,7 +25930,7 @@
         <v>1</v>
       </c>
       <c r="P490" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="491" spans="1:16">
@@ -25944,7 +25944,7 @@
         <v>2.326764722017106</v>
       </c>
       <c r="D491" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E491">
         <v>2.338905512271317</v>
@@ -25980,7 +25980,7 @@
         <v>1</v>
       </c>
       <c r="P491" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="492" spans="1:16">
@@ -25994,7 +25994,7 @@
         <v>2.245345573811253</v>
       </c>
       <c r="D492" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E492">
         <v>3.046447469845635</v>
@@ -26030,7 +26030,7 @@
         <v>1</v>
       </c>
       <c r="P492" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="493" spans="1:16">
@@ -26044,7 +26044,7 @@
         <v>2.377388096414631</v>
       </c>
       <c r="D493" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E493">
         <v>3.046447469845635</v>
@@ -26080,7 +26080,7 @@
         <v>1</v>
       </c>
       <c r="P493" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="494" spans="1:16">
@@ -26094,7 +26094,7 @@
         <v>2.297261055983554</v>
       </c>
       <c r="D494" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E494">
         <v>3.198744073311161</v>
@@ -26130,7 +26130,7 @@
         <v>1</v>
       </c>
       <c r="P494" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="495" spans="1:16">
@@ -26144,7 +26144,7 @@
         <v>3.243481435190432</v>
       </c>
       <c r="D495" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E495">
         <v>2.658201682552544</v>
@@ -26180,7 +26180,7 @@
         <v>1</v>
       </c>
       <c r="P495" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="496" spans="1:16">
@@ -26230,7 +26230,7 @@
         <v>1</v>
       </c>
       <c r="P496" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="497" spans="1:16">
@@ -26244,7 +26244,7 @@
         <v>2.301170929293026</v>
       </c>
       <c r="D497" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E497">
         <v>3.202733093853617</v>
@@ -26294,7 +26294,7 @@
         <v>3.247296331820319</v>
       </c>
       <c r="D498" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E498">
         <v>2.662232914952593</v>
@@ -26394,7 +26394,7 @@
         <v>2.309276220482282</v>
       </c>
       <c r="D500" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E500">
         <v>3.211002459763304</v>
@@ -26430,7 +26430,7 @@
         <v>1</v>
       </c>
       <c r="P500" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="501" spans="1:16">
@@ -26444,7 +26444,7 @@
         <v>3.25520473334506</v>
       </c>
       <c r="D501" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E501">
         <v>2.670589787379843</v>
@@ -26480,7 +26480,7 @@
         <v>1</v>
       </c>
       <c r="P501" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="502" spans="1:16">
@@ -26494,7 +26494,7 @@
         <v>2.35659384998981</v>
       </c>
       <c r="D502" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E502">
         <v>2.377701080695644</v>
@@ -26530,7 +26530,7 @@
         <v>1</v>
       </c>
       <c r="P502" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="503" spans="1:16">
@@ -26544,7 +26544,7 @@
         <v>2.318802840630408</v>
       </c>
       <c r="D503" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E503">
         <v>3.220721926473129</v>
@@ -26594,7 +26594,7 @@
         <v>3.264499937619139</v>
       </c>
       <c r="D504" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E504">
         <v>2.680412105589244</v>
@@ -26744,7 +26744,7 @@
         <v>2.968469110715926</v>
       </c>
       <c r="D507" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E507">
         <v>3.65607053595874</v>
@@ -26780,7 +26780,7 @@
         <v>1</v>
       </c>
       <c r="P507" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="508" spans="1:16">
@@ -26794,7 +26794,7 @@
         <v>3.056098677724048</v>
       </c>
       <c r="D508" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E508">
         <v>3.65607053595874</v>
@@ -26830,7 +26830,7 @@
         <v>1</v>
       </c>
       <c r="P508" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="509" spans="1:16">
@@ -26844,7 +26844,7 @@
         <v>3.085552267926261</v>
       </c>
       <c r="D509" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E509">
         <v>3.65607053595874</v>
@@ -26880,7 +26880,7 @@
         <v>1</v>
       </c>
       <c r="P509" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="510" spans="1:16">
@@ -26894,7 +26894,7 @@
         <v>3.115403587495276</v>
       </c>
       <c r="D510" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E510">
         <v>4.899694426383849</v>
@@ -26930,7 +26930,7 @@
         <v>1</v>
       </c>
       <c r="P510" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="511" spans="1:16">
@@ -26944,7 +26944,7 @@
         <v>2.857657467623699</v>
       </c>
       <c r="D511" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E511">
         <v>4.899694426383849</v>
@@ -26980,7 +26980,7 @@
         <v>1</v>
       </c>
       <c r="P511" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="512" spans="1:16">
@@ -26994,7 +26994,7 @@
         <v>4.634833021734408</v>
       </c>
       <c r="D512" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E512">
         <v>3.48240231940969</v>
@@ -27030,7 +27030,7 @@
         <v>1</v>
       </c>
       <c r="P512" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="513" spans="1:16">
@@ -27044,7 +27044,7 @@
         <v>3.013404560606677</v>
       </c>
       <c r="D513" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E513">
         <v>3.707166946903694</v>
@@ -27080,7 +27080,7 @@
         <v>1</v>
       </c>
       <c r="P513" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="514" spans="1:16">
@@ -27094,7 +27094,7 @@
         <v>3.101938488870459</v>
       </c>
       <c r="D514" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E514">
         <v>3.707166946903694</v>
@@ -27130,7 +27130,7 @@
         <v>1</v>
       </c>
       <c r="P514" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="515" spans="1:16">
@@ -27144,7 +27144,7 @@
         <v>3.133031233848563</v>
       </c>
       <c r="D515" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E515">
         <v>3.707166946903694</v>
@@ -27180,7 +27180,7 @@
         <v>1</v>
       </c>
       <c r="P515" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="516" spans="1:16">
@@ -27194,7 +27194,7 @@
         <v>2.923647577997855</v>
       </c>
       <c r="D516" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E516">
         <v>4.966814988327585</v>
@@ -27230,7 +27230,7 @@
         <v>1</v>
       </c>
       <c r="P516" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="517" spans="1:16">
@@ -27244,7 +27244,7 @@
         <v>4.706192777064061</v>
       </c>
       <c r="D517" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E517">
         <v>3.555881671432303</v>
@@ -27280,7 +27280,7 @@
         <v>1</v>
       </c>
       <c r="P517" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="518" spans="1:16">
@@ -27294,7 +27294,7 @@
         <v>3.058294813446018</v>
       </c>
       <c r="D518" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E518">
         <v>3.758211963968808</v>
@@ -27344,7 +27344,7 @@
         <v>3.147732193339273</v>
       </c>
       <c r="D519" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E519">
         <v>3.758211963968808</v>
@@ -27394,7 +27394,7 @@
         <v>3.18046244439579</v>
       </c>
       <c r="D520" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E520">
         <v>3.758211963968808</v>
@@ -27444,7 +27444,7 @@
         <v>3.225680173488445</v>
       </c>
       <c r="D521" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E521">
         <v>5.033868038952384</v>
@@ -27494,7 +27494,7 @@
         <v>2.989571314085818</v>
       </c>
       <c r="D522" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E522">
         <v>5.033868038952384</v>
@@ -27544,7 +27544,7 @@
         <v>4.77748075720201</v>
       </c>
       <c r="D523" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E523">
         <v>3.629287116326825</v>
@@ -27594,7 +27594,7 @@
         <v>3.100990526217007</v>
       </c>
       <c r="D524" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E524">
         <v>5.097643081613452</v>
@@ -27644,7 +27644,7 @@
         <v>3.19128719089559</v>
       </c>
       <c r="D525" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E525">
         <v>5.097643081613452</v>
@@ -27694,7 +27694,7 @@
         <v>3.225574895625517</v>
       </c>
       <c r="D526" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E526">
         <v>5.097643081613452</v>
@@ -27744,7 +27744,7 @@
         <v>3.205781960817575</v>
       </c>
       <c r="D527" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E527">
         <v>5.097643081613452</v>
@@ -27794,7 +27794,7 @@
         <v>3.27809654539346</v>
       </c>
       <c r="D528" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E528">
         <v>5.097643081613452</v>
@@ -27844,7 +27844,7 @@
         <v>3.052272250765228</v>
       </c>
       <c r="D529" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E529">
         <v>5.097643081613452</v>
@@ -27894,7 +27894,7 @@
         <v>4.845283697294303</v>
       </c>
       <c r="D530" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E530">
         <v>3.699104005134728</v>
@@ -27944,7 +27944,7 @@
         <v>3.135431759672713</v>
       </c>
       <c r="D531" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E531">
         <v>5.149088320265843</v>
@@ -27994,7 +27994,7 @@
         <v>3.226421581251035</v>
       </c>
       <c r="D532" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E532">
         <v>5.149088320265843</v>
@@ -28044,7 +28044,7 @@
         <v>3.261965632861735</v>
       </c>
       <c r="D533" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E533">
         <v>5.149088320265843</v>
@@ -28094,7 +28094,7 @@
         <v>3.248497754763896</v>
       </c>
       <c r="D534" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E534">
         <v>5.149088320265843</v>
@@ -28144,7 +28144,7 @@
         <v>3.320379116277444</v>
       </c>
       <c r="D535" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E535">
         <v>5.149088320265843</v>
@@ -28194,7 +28194,7 @@
         <v>3.102851043292947</v>
       </c>
       <c r="D536" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E536">
         <v>5.149088320265843</v>
@@ -28244,7 +28244,7 @@
         <v>4.899978108914215</v>
       </c>
       <c r="D537" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E537">
         <v>3.755423003238402</v>
@@ -28294,7 +28294,7 @@
         <v>3.340758667101504</v>
       </c>
       <c r="D538" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E538">
         <v>5.455787317211367</v>
@@ -28344,7 +28344,7 @@
         <v>3.596337846972439</v>
       </c>
       <c r="D539" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E539">
         <v>5.455787317211367</v>
@@ -28394,7 +28394,7 @@
         <v>3.478914818069512</v>
       </c>
       <c r="D540" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E540">
         <v>5.455787317211367</v>
@@ -28444,7 +28444,7 @@
         <v>3.503154774543503</v>
       </c>
       <c r="D541" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E541">
         <v>5.455787317211367</v>
@@ -28494,7 +28494,7 @@
         <v>3.572453407661722</v>
       </c>
       <c r="D542" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E542">
         <v>5.455787317211367</v>
@@ -28544,7 +28544,7 @@
         <v>3.404384583447808</v>
       </c>
       <c r="D543" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E543">
         <v>5.455787317211367</v>
@@ -28594,7 +28594,7 @@
         <v>5.25250104043668</v>
       </c>
       <c r="D544" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E544">
         <v>5.56320240731846</v>
@@ -28644,7 +28644,7 @@
         <v>3.408744253943432</v>
       </c>
       <c r="D545" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E545">
         <v>5.557338115167074</v>
@@ -28694,7 +28694,7 @@
         <v>3.550748645676077</v>
       </c>
       <c r="D546" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E546">
         <v>5.557338115167074</v>
@@ -28744,7 +28744,7 @@
         <v>3.587474005519777</v>
       </c>
       <c r="D547" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E547">
         <v>5.557338115167074</v>
@@ -28794,7 +28794,7 @@
         <v>3.655917474023632</v>
       </c>
       <c r="D548" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E548">
         <v>5.557338115167074</v>
@@ -28844,7 +28844,7 @@
         <v>3.504225052174785</v>
       </c>
       <c r="D549" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E549">
         <v>5.557338115167074</v>
@@ -28894,7 +28894,7 @@
         <v>5.346996730323884</v>
       </c>
       <c r="D550" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E550">
         <v>5.864438002961421</v>
@@ -28944,7 +28944,7 @@
         <v>5.267444590560391</v>
       </c>
       <c r="D551" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E551">
         <v>5.864438002961421</v>
@@ -28994,7 +28994,7 @@
         <v>3.796322429340982</v>
       </c>
       <c r="D552" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E552">
         <v>5.685955718590687</v>
@@ -29044,7 +29044,7 @@
         <v>3.641728676729411</v>
       </c>
       <c r="D553" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E553">
         <v>5.685955718590687</v>
@@ -29094,7 +29094,7 @@
         <v>3.69426723244667</v>
       </c>
       <c r="D554" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E554">
         <v>5.685955718590687</v>
@@ -29144,7 +29144,7 @@
         <v>3.761627605342749</v>
       </c>
       <c r="D555" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E555">
         <v>5.685955718590687</v>
@@ -29194,7 +29194,7 @@
         <v>3.630676464382844</v>
       </c>
       <c r="D556" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E556">
         <v>5.685955718590687</v>
@@ -29244,7 +29244,7 @@
         <v>5.466678794983334</v>
       </c>
       <c r="D557" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E557">
         <v>5.209318422087254</v>
@@ -29294,7 +29294,7 @@
         <v>5.390917489847062</v>
       </c>
       <c r="D558" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E558">
         <v>5.209318422087254</v>
@@ -29344,7 +29344,7 @@
         <v>4.159051079599863</v>
       </c>
       <c r="D559" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E559">
         <v>5.343391662540899</v>
@@ -29380,7 +29380,7 @@
         <v>1</v>
       </c>
       <c r="P559" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="560" spans="1:16">
@@ -29394,7 +29394,7 @@
         <v>4.237780255555339</v>
       </c>
       <c r="D560" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E560">
         <v>5.313343652467495</v>
@@ -29430,7 +29430,7 @@
         <v>1</v>
       </c>
       <c r="P560" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="561" spans="1:16">
@@ -29444,7 +29444,7 @@
         <v>4.283295642394084</v>
       </c>
       <c r="D561" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E561">
         <v>5.313343652467495</v>
@@ -29480,7 +29480,7 @@
         <v>1</v>
       </c>
       <c r="P561" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="562" spans="1:16">
@@ -29530,7 +29530,7 @@
         <v>1</v>
       </c>
       <c r="P562" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="563" spans="1:16">
@@ -29544,7 +29544,7 @@
         <v>4.047954928502808</v>
       </c>
       <c r="D563" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E563">
         <v>5.235960539108905</v>
@@ -29594,7 +29594,7 @@
         <v>4.137221058995326</v>
       </c>
       <c r="D564" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E564">
         <v>5.202705629828571</v>
@@ -29644,7 +29644,7 @@
         <v>4.169450720548237</v>
       </c>
       <c r="D565" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E565">
         <v>5.202705629828571</v>
@@ -29694,7 +29694,7 @@
         <v>6.314817655301979</v>
       </c>
       <c r="D566" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E566">
         <v>6.624319057953503</v>
@@ -29744,7 +29744,7 @@
         <v>4.059730080999771</v>
       </c>
       <c r="D567" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E567">
         <v>5.117447902330046</v>
@@ -29794,7 +29794,7 @@
         <v>4.081721754571493</v>
       </c>
       <c r="D568" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E568">
         <v>5.117447902330046</v>
@@ -29894,7 +29894,7 @@
         <v>4.030557457706422</v>
       </c>
       <c r="D570" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E570">
         <v>5.085351371462874</v>
@@ -29930,7 +29930,7 @@
         <v>1</v>
       </c>
       <c r="P570" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="571" spans="1:16">
@@ -29944,7 +29944,7 @@
         <v>4.048694889476288</v>
       </c>
       <c r="D571" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E571">
         <v>5.085351371462874</v>
@@ -29980,7 +29980,7 @@
         <v>1</v>
       </c>
       <c r="P571" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="572" spans="1:16">
@@ -30030,7 +30030,7 @@
         <v>1</v>
       </c>
       <c r="P572" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="573" spans="1:16">
@@ -30044,7 +30044,7 @@
         <v>3.737521317704196</v>
       </c>
       <c r="D573" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E573">
         <v>4.762944866631269</v>
@@ -30080,7 +30080,7 @@
         <v>1</v>
       </c>
       <c r="P573" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="574" spans="1:16">
@@ -30094,7 +30094,7 @@
         <v>3.716943268562606</v>
       </c>
       <c r="D574" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E574">
         <v>4.762944866631269</v>
@@ -30130,7 +30130,7 @@
         <v>1</v>
       </c>
       <c r="P574" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="575" spans="1:16">
@@ -30180,7 +30180,7 @@
         <v>1</v>
       </c>
       <c r="P575" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="576" spans="1:16">
@@ -30230,7 +30230,7 @@
         <v>1</v>
       </c>
       <c r="P576" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="577" spans="1:16">
@@ -30244,7 +30244,7 @@
         <v>3.710853293730853</v>
       </c>
       <c r="D577" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E577">
         <v>4.733603965539871</v>
@@ -30294,7 +30294,7 @@
         <v>3.686751906570006</v>
       </c>
       <c r="D578" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E578">
         <v>4.733603965539871</v>
@@ -31644,7 +31644,7 @@
         <v>6.312844467716282</v>
       </c>
       <c r="D605" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E605">
         <v>7.044140001633426</v>
@@ -31980,7 +31980,7 @@
         <v>1</v>
       </c>
       <c r="P611" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="612" spans="1:16">
@@ -32030,7 +32030,7 @@
         <v>1</v>
       </c>
       <c r="P612" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="613" spans="1:16">
@@ -32080,7 +32080,7 @@
         <v>1</v>
       </c>
       <c r="P613" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="614" spans="1:16">
@@ -32130,7 +32130,7 @@
         <v>1</v>
       </c>
       <c r="P614" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="615" spans="1:16">
@@ -32180,7 +32180,7 @@
         <v>1</v>
       </c>
       <c r="P615" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="616" spans="1:16">
@@ -32230,7 +32230,7 @@
         <v>1</v>
       </c>
       <c r="P616" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="617" spans="1:16">
@@ -32280,7 +32280,7 @@
         <v>1</v>
       </c>
       <c r="P617" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="618" spans="1:16">
@@ -32330,7 +32330,7 @@
         <v>1</v>
       </c>
       <c r="P618" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="619" spans="1:16">
@@ -32380,7 +32380,7 @@
         <v>1</v>
       </c>
       <c r="P619" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="620" spans="1:16">
@@ -32430,7 +32430,7 @@
         <v>1</v>
       </c>
       <c r="P620" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="621" spans="1:16">
@@ -32480,7 +32480,7 @@
         <v>1</v>
       </c>
       <c r="P621" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="622" spans="1:16">
@@ -32494,7 +32494,7 @@
         <v>6.52789956231641</v>
       </c>
       <c r="D622" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E622">
         <v>6.970266187949232</v>
@@ -32530,7 +32530,7 @@
         <v>1</v>
       </c>
       <c r="P622" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="623" spans="1:16">
@@ -32694,7 +32694,7 @@
         <v>2.603543847706</v>
       </c>
       <c r="D626" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E626">
         <v>4.770094008155837</v>
@@ -32994,7 +32994,7 @@
         <v>2.478182256708074</v>
       </c>
       <c r="D632" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E632">
         <v>4.645810796435313</v>
@@ -33244,7 +33244,7 @@
         <v>2.30694018299906</v>
       </c>
       <c r="D637" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E637">
         <v>4.476041772822722</v>
@@ -33294,7 +33294,7 @@
         <v>5.979313720333828</v>
       </c>
       <c r="D638" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E638">
         <v>6.921637837986275</v>
@@ -33344,7 +33344,7 @@
         <v>6.118014825265853</v>
       </c>
       <c r="D639" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E639">
         <v>6.921637837986275</v>
@@ -33394,7 +33394,7 @@
         <v>2.180042495856011</v>
       </c>
       <c r="D640" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E640">
         <v>4.350235678687355</v>
@@ -33594,7 +33594,7 @@
         <v>2.005501953213372</v>
       </c>
       <c r="D644" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E644">
         <v>4.177196560067447</v>
@@ -33644,7 +33644,7 @@
         <v>6.03048720269387</v>
       </c>
       <c r="D645" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E645">
         <v>7.646218976894719</v>
@@ -33694,7 +33694,7 @@
         <v>6.160487202693869</v>
       </c>
       <c r="D646" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E646">
         <v>7.646218976894719</v>
@@ -33794,7 +33794,7 @@
         <v>5.929250610805834</v>
       </c>
       <c r="D648" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="E648">
         <v>6.44678700451809</v>
@@ -33844,7 +33844,7 @@
         <v>6.059250610805833</v>
       </c>
       <c r="D649" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="E649">
         <v>6.44678700451809</v>
@@ -33944,7 +33944,7 @@
         <v>6.444007644774246</v>
       </c>
       <c r="D651" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E651">
         <v>5.9080963375586</v>
@@ -33994,7 +33994,7 @@
         <v>5.977845942063905</v>
       </c>
       <c r="D652" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E652">
         <v>5.9080963375586</v>
@@ -34094,7 +34094,7 @@
         <v>6.325113724849238</v>
       </c>
       <c r="D654" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E654">
         <v>5.966484401224733</v>
@@ -34144,7 +34144,7 @@
         <v>6.616965483162407</v>
       </c>
       <c r="D655" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E655">
         <v>5.966484401224733</v>
@@ -34394,7 +34394,7 @@
         <v>6.182411935806901</v>
       </c>
       <c r="D660" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E660">
         <v>5.820555041914538</v>
@@ -34444,7 +34444,7 @@
         <v>6.479370608860847</v>
       </c>
       <c r="D661" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E661">
         <v>5.820555041914538</v>
@@ -34494,7 +34494,7 @@
         <v>6.247760471854665</v>
       </c>
       <c r="D662" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E662">
         <v>5.820555041914538</v>
@@ -34644,7 +34644,7 @@
         <v>6.052746661470383</v>
       </c>
       <c r="D665" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E665">
         <v>5.747828147206722</v>
@@ -34694,7 +34694,7 @@
         <v>6.354345707327784</v>
       </c>
       <c r="D666" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E666">
         <v>5.747828147206722</v>
@@ -34744,7 +34744,7 @@
         <v>6.106229101349317</v>
       </c>
       <c r="D667" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E667">
         <v>5.747828147206722</v>
@@ -34894,7 +34894,7 @@
         <v>5.992378168346487</v>
       </c>
       <c r="D670" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E670">
         <v>5.919638041522585</v>
@@ -34944,7 +34944,7 @@
         <v>6.296137640849427</v>
       </c>
       <c r="D671" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E671">
         <v>5.919638041522585</v>
@@ -34994,7 +34994,7 @@
         <v>6.0403360886604</v>
       </c>
       <c r="D672" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E672">
         <v>5.919638041522585</v>
@@ -35080,7 +35080,7 @@
         <v>1</v>
       </c>
       <c r="P673" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="674" spans="1:16">
@@ -35130,7 +35130,7 @@
         <v>1</v>
       </c>
       <c r="P674" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="675" spans="1:16">
@@ -35144,7 +35144,7 @@
         <v>5.931074248482098</v>
       </c>
       <c r="D675" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E675">
         <v>5.817063063996034</v>
@@ -35180,7 +35180,7 @@
         <v>1</v>
       </c>
       <c r="P675" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="676" spans="1:16">
@@ -35194,7 +35194,7 @@
         <v>6.237027624047666</v>
       </c>
       <c r="D676" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E676">
         <v>5.817063063996034</v>
@@ -35230,7 +35230,7 @@
         <v>1</v>
       </c>
       <c r="P676" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="677" spans="1:16">
@@ -35244,7 +35244,7 @@
         <v>5.973422045250139</v>
       </c>
       <c r="D677" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E677">
         <v>5.817063063996034</v>
@@ -35280,7 +35280,7 @@
         <v>1</v>
       </c>
       <c r="P677" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="678" spans="1:16">
@@ -35394,7 +35394,7 @@
         <v>5.839386641650073</v>
       </c>
       <c r="D680" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E680">
         <v>4.893781158276536</v>
@@ -35444,7 +35444,7 @@
         <v>6.148621271038877</v>
       </c>
       <c r="D681" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E681">
         <v>4.893781158276536</v>
@@ -35494,7 +35494,7 @@
         <v>5.873343803641564</v>
       </c>
       <c r="D682" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E682">
         <v>4.893781158276536</v>
@@ -35594,7 +35594,7 @@
         <v>6.049313264972337</v>
       </c>
       <c r="D684" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E684">
         <v>4.936335249131968</v>
@@ -35644,7 +35644,7 @@
         <v>6.175722584965069</v>
       </c>
       <c r="D685" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E685">
         <v>4.936335249131968</v>
@@ -35694,7 +35694,7 @@
         <v>5.760924613317037</v>
       </c>
       <c r="D686" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E686">
         <v>4.936335249131968</v>
@@ -35844,7 +35844,7 @@
         <v>5.905539797299475</v>
       </c>
       <c r="D689" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="E689">
         <v>5.270502414665344</v>
@@ -35894,7 +35894,7 @@
         <v>6.021734035283636</v>
       </c>
       <c r="D690" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="E690">
         <v>5.270502414665344</v>
@@ -36044,7 +36044,7 @@
         <v>5.810134805942958</v>
       </c>
       <c r="D693" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="E693">
         <v>4.46837075668304</v>
@@ -36094,7 +36094,7 @@
         <v>5.919550534467003</v>
       </c>
       <c r="D694" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="E694">
         <v>4.46837075668304</v>
@@ -36144,7 +36144,7 @@
         <v>5.597681787127293</v>
       </c>
       <c r="D695" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="E695">
         <v>5.175448484795162</v>
@@ -36194,7 +36194,7 @@
         <v>5.69200276245871</v>
       </c>
       <c r="D696" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="E696">
         <v>5.175448484795162</v>
@@ -36444,7 +36444,7 @@
         <v>10.58920111380781</v>
       </c>
       <c r="D701" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E701">
         <v>10.63805069137965</v>
@@ -36544,7 +36544,7 @@
         <v>13.29070024337744</v>
       </c>
       <c r="D703" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E703">
         <v>12.1104855745369</v>
@@ -36644,7 +36644,7 @@
         <v>13.05967948318782</v>
       </c>
       <c r="D705" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E705">
         <v>11.87581437344135</v>
@@ -36744,7 +36744,7 @@
         <v>12.8170626988293</v>
       </c>
       <c r="D707" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E707">
         <v>10.97022453374666</v>
@@ -36844,7 +36844,7 @@
         <v>12.5987805539735</v>
       </c>
       <c r="D709" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E709">
         <v>10.73863851098768</v>
@@ -37044,7 +37044,7 @@
         <v>12.45336310880131</v>
       </c>
       <c r="D713" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E713">
         <v>10.58435815154991</v>
@@ -37394,7 +37394,7 @@
         <v>12.29210392935995</v>
       </c>
       <c r="D720" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E720">
         <v>10.41327053453538</v>
@@ -37444,7 +37444,7 @@
         <v>9.171282848330055</v>
       </c>
       <c r="D721" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E721">
         <v>6.850968108671186</v>
@@ -37494,7 +37494,7 @@
         <v>8.830116243154617</v>
       </c>
       <c r="D722" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E722">
         <v>6.850968108671186</v>
@@ -37694,7 +37694,7 @@
         <v>12.09795277153261</v>
       </c>
       <c r="D726" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E726">
         <v>10.20728623616326</v>
@@ -37744,7 +37744,7 @@
         <v>8.629829382822578</v>
       </c>
       <c r="D727" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="E727">
         <v>7.040051561279032</v>
@@ -37944,7 +37944,7 @@
         <v>11.86477339723001</v>
       </c>
       <c r="D731" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E731">
         <v>9.95989502640656</v>
@@ -37994,7 +37994,7 @@
         <v>8.389280908654889</v>
       </c>
       <c r="D732" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E732">
         <v>6.803093216210396</v>
@@ -38244,7 +38244,7 @@
         <v>7.721090409497048</v>
       </c>
       <c r="D737" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E737">
         <v>6.845979077114176</v>
@@ -38444,7 +38444,7 @@
         <v>7.431928747420816</v>
       </c>
       <c r="D741" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E741">
         <v>6.954602200047407</v>
@@ -38694,7 +38694,7 @@
         <v>7.15411432552343</v>
       </c>
       <c r="D746" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E746">
         <v>7.077702572180645</v>
@@ -38994,7 +38994,7 @@
         <v>6.656074286112602</v>
       </c>
       <c r="D752" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E752">
         <v>7.106777983579878</v>
@@ -39744,7 +39744,7 @@
         <v>5.189787984798581</v>
       </c>
       <c r="D767" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E767">
         <v>6.127393152460147</v>
@@ -39794,7 +39794,7 @@
         <v>5.337615079752425</v>
       </c>
       <c r="D768" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E768">
         <v>6.127393152460147</v>
@@ -39944,7 +39944,7 @@
         <v>4.573548410677798</v>
       </c>
       <c r="D771" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E771">
         <v>5.983161604764781</v>
@@ -39994,7 +39994,7 @@
         <v>4.718587091269107</v>
       </c>
       <c r="D772" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E772">
         <v>5.983161604764781</v>
@@ -41394,7 +41394,7 @@
         <v>1.03967143846625</v>
       </c>
       <c r="D800" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E800">
         <v>2.609188567947417</v>
@@ -41444,7 +41444,7 @@
         <v>0.8130094478294367</v>
       </c>
       <c r="D801" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E801">
         <v>2.609188567947417</v>
@@ -41544,7 +41544,7 @@
         <v>0.7465491084079581</v>
       </c>
       <c r="D803" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E803">
         <v>2.329329691737918</v>
@@ -41594,7 +41594,7 @@
         <v>0.5106027000769942</v>
       </c>
       <c r="D804" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E804">
         <v>2.329329691737918</v>
@@ -41644,7 +41644,7 @@
         <v>0.4893560218813207</v>
       </c>
       <c r="D805" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E805">
         <v>2.083774301434204</v>
@@ -41694,7 +41694,7 @@
         <v>0.2452632261943108</v>
       </c>
       <c r="D806" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E806">
         <v>2.083774301434204</v>
@@ -41744,7 +41744,7 @@
         <v>3.38720643044401</v>
       </c>
       <c r="D807" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E807">
         <v>1.346565161657761</v>
@@ -41794,7 +41794,7 @@
         <v>0.03330516332946587</v>
       </c>
       <c r="D808" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E808">
         <v>1.648359228337185</v>
@@ -41844,7 +41844,7 @@
         <v>-0.2252326821759354</v>
       </c>
       <c r="D809" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E809">
         <v>1.648359228337185</v>
@@ -41894,7 +41894,7 @@
         <v>2.979030594147371</v>
       </c>
       <c r="D810" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E810">
         <v>0.9008321958333205</v>
@@ -41944,7 +41944,7 @@
         <v>-0.3050434949915584</v>
       </c>
       <c r="D811" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E811">
         <v>1.325320464057839</v>
@@ -41994,7 +41994,7 @@
         <v>-0.5742982663261245</v>
       </c>
       <c r="D812" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E812">
         <v>1.325320464057839</v>
@@ -42044,7 +42044,7 @@
         <v>2.676200890003035</v>
       </c>
       <c r="D813" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E813">
         <v>0.570138484533139</v>
@@ -42094,7 +42094,7 @@
         <v>-1.542729235915701</v>
       </c>
       <c r="D814" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E814">
         <v>0.8740710626510406</v>
@@ -42144,7 +42144,7 @@
         <v>-1.06190425457612</v>
       </c>
       <c r="D815" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E815">
         <v>0.8740710626510406</v>
@@ -42194,7 +42194,7 @@
         <v>2.253181308968607</v>
       </c>
       <c r="D816" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E816">
         <v>0.1081959693489338</v>
@@ -42244,7 +42244,7 @@
         <v>-1.645106114375984</v>
       </c>
       <c r="D817" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E817">
         <v>0.7789101756240804</v>
@@ -42294,7 +42294,7 @@
         <v>-1.164732132500994</v>
       </c>
       <c r="D818" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E818">
         <v>0.7789101756240804</v>
@@ -42344,7 +42344,7 @@
         <v>1.705918320624114</v>
       </c>
       <c r="D819" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E819">
         <v>0.01078008499905536</v>
@@ -42394,7 +42394,7 @@
         <v>2.163973614874138</v>
       </c>
       <c r="D820" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E820">
         <v>0.01078008499905536</v>
@@ -42444,7 +42444,7 @@
         <v>2.083749225749141</v>
       </c>
       <c r="D821" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E821">
         <v>-0.02146380625091737</v>
@@ -42494,7 +42494,7 @@
         <v>-1.354990011712744</v>
       </c>
       <c r="D822" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E822">
         <v>1.048577566205335</v>
@@ -42544,7 +42544,7 @@
         <v>-0.8733379853326184</v>
       </c>
       <c r="D823" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E823">
         <v>1.048577566205335</v>
@@ -42594,7 +42594,7 @@
         <v>1.965361355164372</v>
       </c>
       <c r="D824" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E824">
         <v>0.2868376981059342</v>
@@ -42644,7 +42644,7 @@
         <v>2.41677081798775</v>
       </c>
       <c r="D825" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E825">
         <v>0.2868376981059342</v>
@@ -42694,7 +42694,7 @@
         <v>2.335779602159679</v>
       </c>
       <c r="D826" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E826">
         <v>0.246925539825213</v>
@@ -42744,7 +42744,7 @@
         <v>-1.093559587288276</v>
       </c>
       <c r="D827" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E827">
         <v>-1.564638644835625</v>
@@ -42794,7 +42794,7 @@
         <v>-1.266714738768137</v>
       </c>
       <c r="D828" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E828">
         <v>0.4727739583005963</v>
@@ -42830,7 +42830,7 @@
         <v>1</v>
       </c>
       <c r="P828" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="829" spans="1:16">
@@ -42844,7 +42844,7 @@
         <v>-0.7846738345336348</v>
       </c>
       <c r="D829" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E829">
         <v>0.5188966710041001</v>
@@ -42880,7 +42880,7 @@
         <v>1</v>
       </c>
       <c r="P829" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="830" spans="1:16">
@@ -42894,7 +42894,7 @@
         <v>2.044303559603822</v>
       </c>
       <c r="D830" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E830">
         <v>0.3708353146523429</v>
@@ -42930,7 +42930,7 @@
         <v>1</v>
       </c>
       <c r="P830" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="831" spans="1:16">
@@ -42944,7 +42944,7 @@
         <v>2.412466315043719</v>
       </c>
       <c r="D831" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E831">
         <v>0.3285898892453361</v>
@@ -42980,7 +42980,7 @@
         <v>1</v>
       </c>
       <c r="P831" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="832" spans="1:16">
@@ -42994,7 +42994,7 @@
         <v>-1.016717323262487</v>
       </c>
       <c r="D832" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E832">
         <v>-1.725082876878652</v>
@@ -43030,7 +43030,7 @@
         <v>1</v>
       </c>
       <c r="P832" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="833" spans="1:16">
@@ -43044,7 +43044,7 @@
         <v>-1.012419255686936</v>
       </c>
       <c r="D833" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E833">
         <v>0.7130663861460427</v>
@@ -43094,7 +43094,7 @@
         <v>2.271713176632382</v>
       </c>
       <c r="D834" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E834">
         <v>0.563841217205912</v>
@@ -43144,7 +43144,7 @@
         <v>2.633378514442889</v>
       </c>
       <c r="D835" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E835">
         <v>0.563841217205912</v>
@@ -43194,7 +43194,7 @@
         <v>-0.7953570260957719</v>
       </c>
       <c r="D836" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="E836">
         <v>-0.6798364854873604</v>
@@ -43244,7 +43244,7 @@
         <v>-1.154980882524804</v>
       </c>
       <c r="D837" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E837">
         <v>0.3632888214250194</v>
@@ -43280,7 +43280,7 @@
         <v>1</v>
       </c>
       <c r="P837" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="838" spans="1:16">
@@ -43294,7 +43294,7 @@
         <v>2.144224144702488</v>
       </c>
       <c r="D838" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="E838">
         <v>0.3406232020973725</v>
@@ -43330,7 +43330,7 @@
         <v>1</v>
       </c>
       <c r="P838" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="839" spans="1:16">
@@ -43344,7 +43344,7 @@
         <v>2.509532026282422</v>
       </c>
       <c r="D839" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="E839">
         <v>0.3406232020973725</v>
@@ -43380,7 +43380,7 @@
         <v>1</v>
       </c>
       <c r="P839" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="840" spans="1:16">
@@ -43430,7 +43430,7 @@
         <v>1</v>
       </c>
       <c r="P840" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="841" spans="1:16">
@@ -43444,7 +43444,7 @@
         <v>-0.7435135480053319</v>
       </c>
       <c r="D841" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E841">
         <v>0.7484730002152737</v>
@@ -43594,7 +43594,7 @@
         <v>-0.3742444036399846</v>
       </c>
       <c r="D844" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E844">
         <v>1.094154467958163</v>
@@ -43744,7 +43744,7 @@
         <v>-0.2301600625778306</v>
       </c>
       <c r="D847" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E847">
         <v>1.229035183710177</v>
@@ -43894,7 +43894,7 @@
         <v>-0.008911774850371756</v>
       </c>
       <c r="D850" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E850">
         <v>0.5721947646345491</v>
@@ -43944,7 +43944,7 @@
         <v>-0.1112036199752922</v>
       </c>
       <c r="D851" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E851">
         <v>1.340393087027532</v>
@@ -44094,7 +44094,7 @@
         <v>0.09903988671845454</v>
       </c>
       <c r="D854" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E854">
         <v>1.106317252320714</v>
@@ -44144,7 +44144,7 @@
         <v>-0.06944114310240224</v>
       </c>
       <c r="D855" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E855">
         <v>1.379487916699293</v>
@@ -44180,7 +44180,7 @@
         <v>1</v>
       </c>
       <c r="P855" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="856" spans="1:16">
@@ -44230,7 +44230,7 @@
         <v>1</v>
       </c>
       <c r="P856" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="857" spans="1:16">
@@ -44280,7 +44280,7 @@
         <v>1</v>
       </c>
       <c r="P857" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="858" spans="1:16">
@@ -44294,7 +44294,7 @@
         <v>0.1369388745414319</v>
       </c>
       <c r="D858" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="E858">
         <v>1.371101739245933</v>
@@ -44330,7 +44330,7 @@
         <v>1</v>
       </c>
       <c r="P858" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="859" spans="1:16">
@@ -44341,40 +44341,40 @@
         <v>154</v>
       </c>
       <c r="C859">
-        <v>12.65888206048432</v>
+        <v>13.05048539408954</v>
       </c>
       <c r="D859" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E859">
-        <v>13.67315026490144</v>
+        <v>13.92659718804111</v>
       </c>
       <c r="F859">
         <v>1</v>
       </c>
       <c r="G859">
-        <v>0.04978111793951567</v>
+        <v>0.05126951460591046</v>
       </c>
       <c r="H859">
-        <v>0.04792684973509856</v>
+        <v>0.04843340281195889</v>
       </c>
       <c r="I859">
-        <v>1.014268204417121</v>
+        <v>0.8761117939515692</v>
       </c>
       <c r="J859">
         <v>0.8436871790688943</v>
       </c>
       <c r="K859">
-        <v>22</v>
+        <v>22.65</v>
       </c>
       <c r="L859">
-        <v>31.22</v>
+        <v>32.16</v>
       </c>
       <c r="M859">
-        <v>20.3</v>
+        <v>20.45</v>
       </c>
       <c r="N859">
-        <v>30.8</v>
+        <v>31.18</v>
       </c>
       <c r="O859">
         <v>1</v>
@@ -44394,10 +44394,10 @@
         <v>15.13291000897221</v>
       </c>
       <c r="D860" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E860">
-        <v>14.41567539327389</v>
+        <v>14.86820052164633</v>
       </c>
       <c r="F860">
         <v>-1</v>
@@ -44406,10 +44406,10 @@
         <v>0.05132708999102778</v>
       </c>
       <c r="H860">
-        <v>0.04934432460672612</v>
+        <v>0.05047179947835367</v>
       </c>
       <c r="I860">
-        <v>0.7172346156983274</v>
+        <v>0.2647094873258844</v>
       </c>
       <c r="J860">
         <v>0.8436871790688943</v>
@@ -44421,10 +44421,10 @@
         <v>33.23</v>
       </c>
       <c r="M860">
-        <v>20.7</v>
+        <v>21.1</v>
       </c>
       <c r="N860">
-        <v>31.88</v>
+        <v>32.67</v>
       </c>
       <c r="O860">
         <v>1</v>
@@ -44435,102 +44435,102 @@
     </row>
     <row r="861" spans="1:16">
       <c r="A861" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B861" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C861">
-        <v>12.57849638595733</v>
+        <v>14.79164744478599</v>
       </c>
       <c r="D861" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="E861">
-        <v>13.59897621067881</v>
+        <v>14.86820052164633</v>
       </c>
       <c r="F861">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G861">
-        <v>0.04986150361404267</v>
+        <v>0.05064835255521401</v>
       </c>
       <c r="H861">
-        <v>0.0480010237893212</v>
+        <v>0.05047179947835367</v>
       </c>
       <c r="I861">
-        <v>1.02047982472148</v>
+        <v>-0.07655307686033552</v>
       </c>
       <c r="J861">
-        <v>0.8473410733655758</v>
+        <v>0.8436871790688943</v>
       </c>
       <c r="K861">
-        <v>22</v>
+        <v>21.25</v>
       </c>
       <c r="L861">
-        <v>31.22</v>
+        <v>32.72</v>
       </c>
       <c r="M861">
-        <v>20.3</v>
+        <v>21.1</v>
       </c>
       <c r="N861">
-        <v>30.8</v>
+        <v>32.67</v>
       </c>
       <c r="O861">
         <v>1</v>
       </c>
       <c r="P861" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="862" spans="1:16">
       <c r="A862" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B862" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C862">
-        <v>15.0545339763084</v>
+        <v>15.14601616269289</v>
       </c>
       <c r="D862" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E862">
-        <v>14.34003978133258</v>
+        <v>14.86820052164633</v>
       </c>
       <c r="F862">
         <v>-1</v>
       </c>
       <c r="G862">
-        <v>0.0514054660236916</v>
+        <v>0.05083398383730712</v>
       </c>
       <c r="H862">
-        <v>0.04941996021866742</v>
+        <v>0.05047179947835367</v>
       </c>
       <c r="I862">
-        <v>0.714494194975817</v>
+        <v>0.2778156410465584</v>
       </c>
       <c r="J862">
-        <v>0.8473410733655758</v>
+        <v>0.8436871790688943</v>
       </c>
       <c r="K862">
-        <v>21.45</v>
+        <v>21.15</v>
       </c>
       <c r="L862">
-        <v>33.23</v>
+        <v>32.99</v>
       </c>
       <c r="M862">
-        <v>20.7</v>
+        <v>21.1</v>
       </c>
       <c r="N862">
-        <v>31.88</v>
+        <v>32.67</v>
       </c>
       <c r="O862">
         <v>1</v>
       </c>
       <c r="P862" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="863" spans="1:16">
@@ -44541,46 +44541,46 @@
         <v>154</v>
       </c>
       <c r="C863">
-        <v>12.51871891898833</v>
+        <v>12.9677246882697</v>
       </c>
       <c r="D863" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E863">
-        <v>13.54381791161196</v>
+        <v>13.85187504967397</v>
       </c>
       <c r="F863">
         <v>1</v>
       </c>
       <c r="G863">
-        <v>0.04992128108101167</v>
+        <v>0.05135227531173029</v>
       </c>
       <c r="H863">
-        <v>0.04805618208838804</v>
+        <v>0.04850812495032602</v>
       </c>
       <c r="I863">
-        <v>1.025098992623629</v>
+        <v>0.8841503614042701</v>
       </c>
       <c r="J863">
-        <v>0.8500582309550758</v>
+        <v>0.8473410733655758</v>
       </c>
       <c r="K863">
-        <v>22</v>
+        <v>22.65</v>
       </c>
       <c r="L863">
-        <v>31.22</v>
+        <v>32.16</v>
       </c>
       <c r="M863">
-        <v>20.3</v>
+        <v>20.45</v>
       </c>
       <c r="N863">
-        <v>30.8</v>
+        <v>31.18</v>
       </c>
       <c r="O863">
         <v>1</v>
       </c>
       <c r="P863" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="864" spans="1:16">
@@ -44591,28 +44591,28 @@
         <v>155</v>
       </c>
       <c r="C864">
-        <v>14.99625094601362</v>
+        <v>15.0545339763084</v>
       </c>
       <c r="D864" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E864">
-        <v>14.28379461922993</v>
+        <v>14.79110335198635</v>
       </c>
       <c r="F864">
         <v>-1</v>
       </c>
       <c r="G864">
-        <v>0.05146374905398637</v>
+        <v>0.0514054660236916</v>
       </c>
       <c r="H864">
-        <v>0.04947620538077007</v>
+        <v>0.05054889664801365</v>
       </c>
       <c r="I864">
-        <v>0.7124563267836912</v>
+        <v>0.2634306243220443</v>
       </c>
       <c r="J864">
-        <v>0.8500582309550758</v>
+        <v>0.8473410733655758</v>
       </c>
       <c r="K864">
         <v>21.45</v>
@@ -44621,148 +44621,148 @@
         <v>33.23</v>
       </c>
       <c r="M864">
-        <v>20.7</v>
+        <v>21.1</v>
       </c>
       <c r="N864">
-        <v>31.88</v>
+        <v>32.67</v>
       </c>
       <c r="O864">
         <v>1</v>
       </c>
       <c r="P864" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="865" spans="1:16">
       <c r="A865" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B865" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C865">
-        <v>14.9624405975191</v>
+        <v>14.71400219098151</v>
       </c>
       <c r="D865" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E865">
-        <v>14.2511664507527</v>
+        <v>14.79110335198635</v>
       </c>
       <c r="F865">
         <v>-1</v>
       </c>
       <c r="G865">
-        <v>0.05149755940248089</v>
+        <v>0.05072599780901849</v>
       </c>
       <c r="H865">
-        <v>0.0495088335492473</v>
+        <v>0.05054889664801365</v>
       </c>
       <c r="I865">
-        <v>0.7112741467663994</v>
+        <v>-0.07710116100484043</v>
       </c>
       <c r="J865">
-        <v>0.8516344709781304</v>
+        <v>0.8473410733655758</v>
       </c>
       <c r="K865">
-        <v>21.45</v>
+        <v>21.25</v>
       </c>
       <c r="L865">
-        <v>33.23</v>
+        <v>32.72</v>
       </c>
       <c r="M865">
-        <v>20.7</v>
+        <v>21.1</v>
       </c>
       <c r="N865">
-        <v>31.88</v>
+        <v>32.67</v>
       </c>
       <c r="O865">
         <v>1</v>
       </c>
       <c r="P865" t="s">
-        <v>154</v>
+        <v>351</v>
       </c>
     </row>
     <row r="866" spans="1:16">
       <c r="A866" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B866" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C866">
-        <v>12.74453569833766</v>
+        <v>15.06873629831808</v>
       </c>
       <c r="D866" t="s">
         <v>269</v>
       </c>
       <c r="E866">
-        <v>13.6867028791849</v>
+        <v>14.79110335198635</v>
       </c>
       <c r="F866">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G866">
-        <v>0.04841546430166234</v>
+        <v>0.05091126370168193</v>
       </c>
       <c r="H866">
-        <v>0.0486732971208151</v>
+        <v>0.05054889664801365</v>
       </c>
       <c r="I866">
-        <v>0.9421671808472425</v>
+        <v>0.2776329463317246</v>
       </c>
       <c r="J866">
-        <v>0.8554179521180978</v>
+        <v>0.8473410733655758</v>
       </c>
       <c r="K866">
-        <v>20.85</v>
+        <v>21.15</v>
       </c>
       <c r="L866">
-        <v>30.58</v>
+        <v>32.99</v>
       </c>
       <c r="M866">
-        <v>20.45</v>
+        <v>21.1</v>
       </c>
       <c r="N866">
-        <v>31.18</v>
+        <v>32.67</v>
       </c>
       <c r="O866">
         <v>1</v>
       </c>
       <c r="P866" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
     </row>
     <row r="867" spans="1:16">
       <c r="A867" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B867" t="s">
         <v>155</v>
       </c>
       <c r="C867">
-        <v>14.8812849270668</v>
+        <v>14.99625094601362</v>
       </c>
       <c r="D867" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E867">
-        <v>14.17284839115538</v>
+        <v>14.7337713268479</v>
       </c>
       <c r="F867">
         <v>-1</v>
       </c>
       <c r="G867">
-        <v>0.05157871507293319</v>
+        <v>0.05146374905398637</v>
       </c>
       <c r="H867">
-        <v>0.04958715160884462</v>
+        <v>0.05060622867315211</v>
       </c>
       <c r="I867">
-        <v>0.7084365359114244</v>
+        <v>0.2624796191657204</v>
       </c>
       <c r="J867">
-        <v>0.8554179521180978</v>
+        <v>0.8500582309550758</v>
       </c>
       <c r="K867">
         <v>21.45</v>
@@ -44771,15 +44771,415 @@
         <v>33.23</v>
       </c>
       <c r="M867">
-        <v>20.7</v>
+        <v>21.1</v>
       </c>
       <c r="N867">
-        <v>31.88</v>
+        <v>32.67</v>
       </c>
       <c r="O867">
         <v>1</v>
       </c>
       <c r="P867" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="868" spans="1:16">
+      <c r="A868" s="1">
+        <v>1</v>
+      </c>
+      <c r="B868" t="s">
+        <v>156</v>
+      </c>
+      <c r="C868">
+        <v>14.65626259220464</v>
+      </c>
+      <c r="D868" t="s">
+        <v>269</v>
+      </c>
+      <c r="E868">
+        <v>14.7337713268479</v>
+      </c>
+      <c r="F868">
+        <v>-1</v>
+      </c>
+      <c r="G868">
+        <v>0.05078373740779536</v>
+      </c>
+      <c r="H868">
+        <v>0.05060622867315211</v>
+      </c>
+      <c r="I868">
+        <v>-0.07750873464326347</v>
+      </c>
+      <c r="J868">
+        <v>0.8500582309550758</v>
+      </c>
+      <c r="K868">
+        <v>21.25</v>
+      </c>
+      <c r="L868">
+        <v>32.72</v>
+      </c>
+      <c r="M868">
+        <v>21.1</v>
+      </c>
+      <c r="N868">
+        <v>32.67</v>
+      </c>
+      <c r="O868">
+        <v>1</v>
+      </c>
+      <c r="P868" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="869" spans="1:16">
+      <c r="A869" s="1">
+        <v>2</v>
+      </c>
+      <c r="B869" t="s">
+        <v>157</v>
+      </c>
+      <c r="C869">
+        <v>15.01126841530015</v>
+      </c>
+      <c r="D869" t="s">
+        <v>269</v>
+      </c>
+      <c r="E869">
+        <v>14.7337713268479</v>
+      </c>
+      <c r="F869">
+        <v>-1</v>
+      </c>
+      <c r="G869">
+        <v>0.05096873158469985</v>
+      </c>
+      <c r="H869">
+        <v>0.05060622867315211</v>
+      </c>
+      <c r="I869">
+        <v>0.2774970884522503</v>
+      </c>
+      <c r="J869">
+        <v>0.8500582309550758</v>
+      </c>
+      <c r="K869">
+        <v>21.15</v>
+      </c>
+      <c r="L869">
+        <v>32.99</v>
+      </c>
+      <c r="M869">
+        <v>21.1</v>
+      </c>
+      <c r="N869">
+        <v>32.67</v>
+      </c>
+      <c r="O869">
+        <v>1</v>
+      </c>
+      <c r="P869" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="870" spans="1:16">
+      <c r="A870" s="1">
+        <v>0</v>
+      </c>
+      <c r="B870" t="s">
+        <v>155</v>
+      </c>
+      <c r="C870">
+        <v>14.9624405975191</v>
+      </c>
+      <c r="D870" t="s">
+        <v>269</v>
+      </c>
+      <c r="E870">
+        <v>14.70051266236145</v>
+      </c>
+      <c r="F870">
+        <v>-1</v>
+      </c>
+      <c r="G870">
+        <v>0.05149755940248089</v>
+      </c>
+      <c r="H870">
+        <v>0.05063948733763856</v>
+      </c>
+      <c r="I870">
+        <v>0.2619279351576509</v>
+      </c>
+      <c r="J870">
+        <v>0.8516344709781304</v>
+      </c>
+      <c r="K870">
+        <v>21.45</v>
+      </c>
+      <c r="L870">
+        <v>33.23</v>
+      </c>
+      <c r="M870">
+        <v>21.1</v>
+      </c>
+      <c r="N870">
+        <v>32.67</v>
+      </c>
+      <c r="O870">
+        <v>1</v>
+      </c>
+      <c r="P870" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="871" spans="1:16">
+      <c r="A871" s="1">
+        <v>1</v>
+      </c>
+      <c r="B871" t="s">
+        <v>156</v>
+      </c>
+      <c r="C871">
+        <v>14.62276749171473</v>
+      </c>
+      <c r="D871" t="s">
+        <v>269</v>
+      </c>
+      <c r="E871">
+        <v>14.70051266236145</v>
+      </c>
+      <c r="F871">
+        <v>-1</v>
+      </c>
+      <c r="G871">
+        <v>0.05081723250828527</v>
+      </c>
+      <c r="H871">
+        <v>0.05063948733763856</v>
+      </c>
+      <c r="I871">
+        <v>-0.07774517064672182</v>
+      </c>
+      <c r="J871">
+        <v>0.8516344709781304</v>
+      </c>
+      <c r="K871">
+        <v>21.25</v>
+      </c>
+      <c r="L871">
+        <v>32.72</v>
+      </c>
+      <c r="M871">
+        <v>21.1</v>
+      </c>
+      <c r="N871">
+        <v>32.67</v>
+      </c>
+      <c r="O871">
+        <v>1</v>
+      </c>
+      <c r="P871" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="872" spans="1:16">
+      <c r="A872" s="1">
+        <v>2</v>
+      </c>
+      <c r="B872" t="s">
+        <v>157</v>
+      </c>
+      <c r="C872">
+        <v>14.97793093881254</v>
+      </c>
+      <c r="D872" t="s">
+        <v>269</v>
+      </c>
+      <c r="E872">
+        <v>14.70051266236145</v>
+      </c>
+      <c r="F872">
+        <v>-1</v>
+      </c>
+      <c r="G872">
+        <v>0.05100206906118745</v>
+      </c>
+      <c r="H872">
+        <v>0.05063948733763856</v>
+      </c>
+      <c r="I872">
+        <v>0.277418276451094</v>
+      </c>
+      <c r="J872">
+        <v>0.8516344709781304</v>
+      </c>
+      <c r="K872">
+        <v>21.15</v>
+      </c>
+      <c r="L872">
+        <v>32.99</v>
+      </c>
+      <c r="M872">
+        <v>21.1</v>
+      </c>
+      <c r="N872">
+        <v>32.67</v>
+      </c>
+      <c r="O872">
+        <v>1</v>
+      </c>
+      <c r="P872" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="873" spans="1:16">
+      <c r="A873" s="1">
+        <v>0</v>
+      </c>
+      <c r="B873" t="s">
+        <v>155</v>
+      </c>
+      <c r="C873">
+        <v>14.8812849270668</v>
+      </c>
+      <c r="D873" t="s">
+        <v>269</v>
+      </c>
+      <c r="E873">
+        <v>14.62068121030814</v>
+      </c>
+      <c r="F873">
+        <v>-1</v>
+      </c>
+      <c r="G873">
+        <v>0.05157871507293319</v>
+      </c>
+      <c r="H873">
+        <v>0.05071931878969187</v>
+      </c>
+      <c r="I873">
+        <v>0.2606037167586628</v>
+      </c>
+      <c r="J873">
+        <v>0.8554179521180978</v>
+      </c>
+      <c r="K873">
+        <v>21.45</v>
+      </c>
+      <c r="L873">
+        <v>33.23</v>
+      </c>
+      <c r="M873">
+        <v>21.1</v>
+      </c>
+      <c r="N873">
+        <v>32.67</v>
+      </c>
+      <c r="O873">
+        <v>1</v>
+      </c>
+      <c r="P873" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="874" spans="1:16">
+      <c r="A874" s="1">
+        <v>1</v>
+      </c>
+      <c r="B874" t="s">
+        <v>156</v>
+      </c>
+      <c r="C874">
+        <v>14.54236851749042</v>
+      </c>
+      <c r="D874" t="s">
+        <v>269</v>
+      </c>
+      <c r="E874">
+        <v>14.62068121030814</v>
+      </c>
+      <c r="F874">
+        <v>-1</v>
+      </c>
+      <c r="G874">
+        <v>0.05089763148250958</v>
+      </c>
+      <c r="H874">
+        <v>0.05071931878969187</v>
+      </c>
+      <c r="I874">
+        <v>-0.07831269281771824</v>
+      </c>
+      <c r="J874">
+        <v>0.8554179521180978</v>
+      </c>
+      <c r="K874">
+        <v>21.25</v>
+      </c>
+      <c r="L874">
+        <v>32.72</v>
+      </c>
+      <c r="M874">
+        <v>21.1</v>
+      </c>
+      <c r="N874">
+        <v>32.67</v>
+      </c>
+      <c r="O874">
+        <v>1</v>
+      </c>
+      <c r="P874" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="875" spans="1:16">
+      <c r="A875" s="1">
+        <v>2</v>
+      </c>
+      <c r="B875" t="s">
+        <v>157</v>
+      </c>
+      <c r="C875">
+        <v>14.89791031270223</v>
+      </c>
+      <c r="D875" t="s">
+        <v>269</v>
+      </c>
+      <c r="E875">
+        <v>14.62068121030814</v>
+      </c>
+      <c r="F875">
+        <v>-1</v>
+      </c>
+      <c r="G875">
+        <v>0.05108208968729777</v>
+      </c>
+      <c r="H875">
+        <v>0.05071931878969187</v>
+      </c>
+      <c r="I875">
+        <v>0.2772291023940952</v>
+      </c>
+      <c r="J875">
+        <v>0.8554179521180978</v>
+      </c>
+      <c r="K875">
+        <v>21.15</v>
+      </c>
+      <c r="L875">
+        <v>32.99</v>
+      </c>
+      <c r="M875">
+        <v>21.1</v>
+      </c>
+      <c r="N875">
+        <v>32.67</v>
+      </c>
+      <c r="O875">
+        <v>1</v>
+      </c>
+      <c r="P875" t="s">
         <v>353</v>
       </c>
     </row>
